--- a/data/BPE.MI.xlsx
+++ b/data/BPE.MI.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2261" uniqueCount="2261">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2262" uniqueCount="2262">
   <si>
     <t xml:space="preserve">date</t>
   </si>
@@ -44,28 +44,28 @@
     <t xml:space="preserve">BPE.MI</t>
   </si>
   <si>
-    <t xml:space="preserve">3.26970100402832</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.12443375587463</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.05299091339111</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.9839289188385</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.98631143569946</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.96249628067017</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.10538244247437</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.94582724571228</t>
+    <t xml:space="preserve">3.2697012424469</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.12443399429321</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.05299115180969</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.98392939567566</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.98631119728088</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.96249651908875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.10538196563721</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.9458270072937</t>
   </si>
   <si>
     <t xml:space="preserve">2.68863272666931</t>
@@ -74,34 +74,34 @@
     <t xml:space="preserve">2.67672538757324</t>
   </si>
   <si>
-    <t xml:space="preserve">2.48144841194153</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.75531244277954</t>
+    <t xml:space="preserve">2.48144817352295</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.7553129196167</t>
   </si>
   <si>
     <t xml:space="preserve">2.7243537902832</t>
   </si>
   <si>
-    <t xml:space="preserve">2.65291142463684</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.80770444869995</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.6933958530426</t>
+    <t xml:space="preserve">2.65291094779968</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.80770421028137</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.69339537620544</t>
   </si>
   <si>
     <t xml:space="preserve">2.49097394943237</t>
   </si>
   <si>
-    <t xml:space="preserve">2.61957097053528</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.55527281761169</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.38142824172974</t>
+    <t xml:space="preserve">2.61957120895386</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.55527257919312</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.38142848014832</t>
   </si>
   <si>
     <t xml:space="preserve">2.18424582481384</t>
@@ -113,259 +113,259 @@
     <t xml:space="preserve">2.14709520339966</t>
   </si>
   <si>
-    <t xml:space="preserve">1.89085412025452</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.84989392757416</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.9775378704071</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.7879763841629</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.99373173713684</t>
+    <t xml:space="preserve">1.89085388183594</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.84989356994629</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.97753775119781</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.78797626495361</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.99373161792755</t>
   </si>
   <si>
     <t xml:space="preserve">2.19567656517029</t>
   </si>
   <si>
-    <t xml:space="preserve">2.30236458778381</t>
+    <t xml:space="preserve">2.30236434936523</t>
   </si>
   <si>
     <t xml:space="preserve">2.35761427879333</t>
   </si>
   <si>
-    <t xml:space="preserve">2.3433256149292</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.20329761505127</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.42667627334595</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.33475184440613</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.18615078926086</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.24044752120972</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.28236079216003</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.24330520629883</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.27664494514465</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.38857269287109</t>
+    <t xml:space="preserve">2.34332489967346</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.20329785346985</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.42667555809021</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.33475208282471</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.18615102767944</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.24044728279114</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.28236103057861</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.24330568313599</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.27664518356323</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.38857245445251</t>
   </si>
   <si>
     <t xml:space="preserve">2.34713554382324</t>
   </si>
   <si>
-    <t xml:space="preserve">2.35666155815125</t>
+    <t xml:space="preserve">2.35666131973267</t>
   </si>
   <si>
     <t xml:space="preserve">2.23473215103149</t>
   </si>
   <si>
-    <t xml:space="preserve">2.20234513282776</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.22711157798767</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.24711585044861</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.43381929397583</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.46715974807739</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.38619041442871</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.2242534160614</t>
+    <t xml:space="preserve">2.2023446559906</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.22711205482483</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.24711608886719</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.43381977081299</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.46715998649597</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.38619065284729</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.22425317764282</t>
   </si>
   <si>
     <t xml:space="preserve">2.24902057647705</t>
   </si>
   <si>
-    <t xml:space="preserve">2.26902461051941</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.26330971717834</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.22996926307678</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.16900491714478</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.0794632434845</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.05850625038147</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.99277853965759</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.02897715568542</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.9137157201767</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.90323722362518</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.79083359241486</t>
+    <t xml:space="preserve">2.26902413368225</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.26330947875977</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.2299690246582</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.1690046787262</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.07946300506592</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.05850601196289</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.99277901649475</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.02897667884827</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.91371560096741</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.90323674678802</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.79083371162415</t>
   </si>
   <si>
     <t xml:space="preserve">2.0470757484436</t>
   </si>
   <si>
-    <t xml:space="preserve">2.14614343643188</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.06041169166565</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.29664945602417</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.40047979354858</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.40762400627136</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.3271312713623</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.39571666717529</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.47192215919495</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.48382878303528</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.39809846878052</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.47668528556824</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.43858289718628</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.53383994102478</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.43143796920776</t>
+    <t xml:space="preserve">2.14614319801331</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.06041193008423</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.29664921760559</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.40047931671143</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.4076235294342</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.32713174819946</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.39571690559387</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.47192239761353</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.48382925987244</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.3980987071991</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.47668504714966</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.43858313560486</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.53383946418762</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.43143773078918</t>
   </si>
   <si>
     <t xml:space="preserve">2.34237241744995</t>
   </si>
   <si>
-    <t xml:space="preserve">2.23949480056763</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.21472835540771</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.15281081199646</t>
+    <t xml:space="preserve">2.23949503898621</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.21472859382629</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.15281105041504</t>
   </si>
   <si>
     <t xml:space="preserve">2.09660935401917</t>
   </si>
   <si>
-    <t xml:space="preserve">2.09089374542236</t>
+    <t xml:space="preserve">2.09089350700378</t>
   </si>
   <si>
     <t xml:space="preserve">2.0851788520813</t>
   </si>
   <si>
-    <t xml:space="preserve">2.05279111862183</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.04993319511414</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.0813684463501</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.19662952423096</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.09375166893005</t>
+    <t xml:space="preserve">2.05279135704041</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.04993295669556</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.08136868476868</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.19662880897522</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.09375190734863</t>
   </si>
   <si>
     <t xml:space="preserve">2.12042355537415</t>
   </si>
   <si>
-    <t xml:space="preserve">2.07852172851562</t>
+    <t xml:space="preserve">2.0785219669342</t>
   </si>
   <si>
     <t xml:space="preserve">2.24223065376282</t>
   </si>
   <si>
-    <t xml:space="preserve">2.35429334640503</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.3084933757782</t>
+    <t xml:space="preserve">2.35429310798645</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.30849385261536</t>
   </si>
   <si>
     <t xml:space="preserve">2.31434106826782</t>
   </si>
   <si>
-    <t xml:space="preserve">2.33675360679626</t>
+    <t xml:space="preserve">2.33675408363342</t>
   </si>
   <si>
     <t xml:space="preserve">2.21592044830322</t>
   </si>
   <si>
-    <t xml:space="preserve">2.12042331695557</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.18766164779663</t>
+    <t xml:space="preserve">2.12042379379272</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.18766140937805</t>
   </si>
   <si>
     <t xml:space="preserve">2.09995985031128</t>
   </si>
   <si>
-    <t xml:space="preserve">2.09021496772766</t>
+    <t xml:space="preserve">2.09021520614624</t>
   </si>
   <si>
     <t xml:space="preserve">2.11749958992004</t>
   </si>
   <si>
-    <t xml:space="preserve">2.15745282173157</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.01615643501282</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.89337396621704</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.83977890014648</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.83393251895905</t>
+    <t xml:space="preserve">2.15745306015015</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.01615619659424</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.89337408542633</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.83977878093719</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.83393275737762</t>
   </si>
   <si>
     <t xml:space="preserve">1.78618371486664</t>
@@ -374,40 +374,40 @@
     <t xml:space="preserve">1.96353590488434</t>
   </si>
   <si>
-    <t xml:space="preserve">2.05221104621887</t>
+    <t xml:space="preserve">2.05221128463745</t>
   </si>
   <si>
     <t xml:space="preserve">2.10483169555664</t>
   </si>
   <si>
-    <t xml:space="preserve">2.09606194496155</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.25684762001038</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.70140612125397</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.68386566638947</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.64391243457794</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.55426239967346</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.59713888168335</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.52015590667725</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.41783797740936</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.41881263256073</t>
+    <t xml:space="preserve">2.09606218338013</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.25684785842896</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.70140624046326</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.68386590480804</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.64391231536865</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.55426228046417</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.59713876247406</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.52015602588654</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.41783821582794</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.41881287097931</t>
   </si>
   <si>
     <t xml:space="preserve">1.31746864318848</t>
@@ -422,28 +422,28 @@
     <t xml:space="preserve">1.52990114688873</t>
   </si>
   <si>
-    <t xml:space="preserve">1.65463197231293</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.57180285453796</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.63904058933258</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.65852952003479</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.66827428340912</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.65268266201019</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.67022299766541</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.72381818294525</t>
+    <t xml:space="preserve">1.65463173389435</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.57180261611938</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.63904070854187</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.65852963924408</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.6682745218277</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.6526825428009</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.67022311687469</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.72381830215454</t>
   </si>
   <si>
     <t xml:space="preserve">1.71115028858185</t>
@@ -458,16 +458,16 @@
     <t xml:space="preserve">1.75012874603271</t>
   </si>
   <si>
-    <t xml:space="preserve">1.6955589056015</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.78813290596008</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.68678891658783</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.47825443744659</t>
+    <t xml:space="preserve">1.69555878639221</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.78813278675079</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.68678915500641</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.47825419902802</t>
   </si>
   <si>
     <t xml:space="preserve">1.53769659996033</t>
@@ -479,37 +479,37 @@
     <t xml:space="preserve">1.74720573425293</t>
   </si>
   <si>
-    <t xml:space="preserve">1.71504771709442</t>
+    <t xml:space="preserve">1.715047955513</t>
   </si>
   <si>
     <t xml:space="preserve">1.74915409088135</t>
   </si>
   <si>
-    <t xml:space="preserve">1.73843550682068</t>
+    <t xml:space="preserve">1.73843538761139</t>
   </si>
   <si>
     <t xml:space="preserve">1.73746085166931</t>
   </si>
   <si>
-    <t xml:space="preserve">1.71309947967529</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.70043158531189</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.63709127902985</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.66632521152496</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.56985366344452</t>
+    <t xml:space="preserve">1.71309971809387</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.70043122768402</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.63709115982056</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.66632544994354</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.56985378265381</t>
   </si>
   <si>
     <t xml:space="preserve">1.58057296276093</t>
   </si>
   <si>
-    <t xml:space="preserve">1.67119753360748</t>
+    <t xml:space="preserve">1.67119765281677</t>
   </si>
   <si>
     <t xml:space="preserve">1.70725226402283</t>
@@ -527,31 +527,31 @@
     <t xml:space="preserve">1.6809424161911</t>
   </si>
   <si>
-    <t xml:space="preserve">1.71212494373322</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.73551154136658</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.70432901382446</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.76182222366333</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.7647453546524</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.72966527938843</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.69653367996216</t>
+    <t xml:space="preserve">1.71212482452393</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.73551177978516</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.70432913303375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.76182210445404</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.76474547386169</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.72966504096985</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.69653344154358</t>
   </si>
   <si>
     <t xml:space="preserve">1.65170872211456</t>
   </si>
   <si>
-    <t xml:space="preserve">1.59616410732269</t>
+    <t xml:space="preserve">1.59616434574127</t>
   </si>
   <si>
     <t xml:space="preserve">1.620525598526</t>
@@ -560,49 +560,49 @@
     <t xml:space="preserve">1.55133926868439</t>
   </si>
   <si>
-    <t xml:space="preserve">1.62442338466644</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.6283210515976</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.55523693561554</t>
+    <t xml:space="preserve">1.62442362308502</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.62832117080688</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.55523681640625</t>
   </si>
   <si>
     <t xml:space="preserve">1.53087556362152</t>
   </si>
   <si>
-    <t xml:space="preserve">1.56498193740845</t>
+    <t xml:space="preserve">1.56498181819916</t>
   </si>
   <si>
     <t xml:space="preserve">1.56790518760681</t>
   </si>
   <si>
-    <t xml:space="preserve">1.61370480060577</t>
+    <t xml:space="preserve">1.61370468139648</t>
   </si>
   <si>
     <t xml:space="preserve">1.57667529582977</t>
   </si>
   <si>
-    <t xml:space="preserve">1.65073382854462</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.65560638904572</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.63221871852875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.69068646430969</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.79300510883331</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.8329576253891</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.7530517578125</t>
+    <t xml:space="preserve">1.65073394775391</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.65560626983643</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.63221883773804</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.69068658351898</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.79300546646118</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.83295774459839</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.75305199623108</t>
   </si>
   <si>
     <t xml:space="preserve">1.84465086460114</t>
@@ -611,19 +611,19 @@
     <t xml:space="preserve">1.88363003730774</t>
   </si>
   <si>
-    <t xml:space="preserve">1.98010158538818</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.07462382316589</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.06975126266479</t>
+    <t xml:space="preserve">1.9801013469696</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.07462406158447</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.06975102424622</t>
   </si>
   <si>
     <t xml:space="preserve">2.12237238883972</t>
   </si>
   <si>
-    <t xml:space="preserve">2.03369688987732</t>
+    <t xml:space="preserve">2.03369665145874</t>
   </si>
   <si>
     <t xml:space="preserve">2.06682825088501</t>
@@ -632,160 +632,160 @@
     <t xml:space="preserve">2.11555123329163</t>
   </si>
   <si>
-    <t xml:space="preserve">2.10970449447632</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.08241939544678</t>
+    <t xml:space="preserve">2.10970401763916</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.08241963386536</t>
   </si>
   <si>
     <t xml:space="preserve">2.06487917900085</t>
   </si>
   <si>
-    <t xml:space="preserve">1.9489187002182</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.9245570898056</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.90311884880066</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.9693820476532</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.0064115524292</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.03564524650574</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.0366199016571</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.01518154144287</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.00543689727783</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.94696950912476</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.86414015293121</t>
+    <t xml:space="preserve">1.94891858100891</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.92455720901489</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.90311896800995</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.96938192844391</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.00641179084778</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.03564548492432</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.03661966323853</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.01518201828003</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.00543665885925</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.9469690322876</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.86414039134979</t>
   </si>
   <si>
     <t xml:space="preserve">1.82613694667816</t>
   </si>
   <si>
-    <t xml:space="preserve">1.81834089756012</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.85537087917328</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.84562563896179</t>
+    <t xml:space="preserve">1.81834053993225</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.85537075996399</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.84562599658966</t>
   </si>
   <si>
     <t xml:space="preserve">1.85147225856781</t>
   </si>
   <si>
-    <t xml:space="preserve">1.82321262359619</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.84660077095032</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.99471807479858</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.9547655582428</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.08729195594788</t>
+    <t xml:space="preserve">1.82321298122406</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.84660053253174</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.99471819400787</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.95476567745209</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.0872917175293</t>
   </si>
   <si>
     <t xml:space="preserve">2.30459570884705</t>
   </si>
   <si>
-    <t xml:space="preserve">2.33772730827332</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.30167293548584</t>
+    <t xml:space="preserve">2.33772754669189</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.30167269706726</t>
   </si>
   <si>
     <t xml:space="preserve">2.34454917907715</t>
   </si>
   <si>
-    <t xml:space="preserve">2.39424657821655</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.3552680015564</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.41860842704773</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.43858456611633</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.42153143882751</t>
+    <t xml:space="preserve">2.39424681663513</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.35526776313782</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.41860818862915</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.43858432769775</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.42153096199036</t>
   </si>
   <si>
     <t xml:space="preserve">2.43614840507507</t>
   </si>
   <si>
-    <t xml:space="preserve">2.48974323272705</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.51410484313965</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.52141356468201</t>
+    <t xml:space="preserve">2.48974370956421</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.51410508155823</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.52141332626343</t>
   </si>
   <si>
     <t xml:space="preserve">2.46538209915161</t>
   </si>
   <si>
-    <t xml:space="preserve">2.56770038604736</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.66514539718628</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.6212956905365</t>
+    <t xml:space="preserve">2.56770014762878</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.66514563560486</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.62129521369934</t>
   </si>
   <si>
     <t xml:space="preserve">2.58231663703918</t>
   </si>
   <si>
-    <t xml:space="preserve">2.45320153236389</t>
+    <t xml:space="preserve">2.45320177078247</t>
   </si>
   <si>
     <t xml:space="preserve">2.44102001190186</t>
   </si>
   <si>
-    <t xml:space="preserve">2.58718919754028</t>
+    <t xml:space="preserve">2.58718943595886</t>
   </si>
   <si>
     <t xml:space="preserve">2.56282782554626</t>
   </si>
   <si>
-    <t xml:space="preserve">2.60424256324768</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.6139874458313</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.75528430938721</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.79913425445557</t>
+    <t xml:space="preserve">2.60424304008484</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.61398720741272</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.75528335571289</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.79913401603699</t>
   </si>
   <si>
     <t xml:space="preserve">2.73335862159729</t>
   </si>
   <si>
-    <t xml:space="preserve">2.74066615104675</t>
+    <t xml:space="preserve">2.74066686630249</t>
   </si>
   <si>
     <t xml:space="preserve">2.77477288246155</t>
@@ -794,31 +794,31 @@
     <t xml:space="preserve">2.73092246055603</t>
   </si>
   <si>
-    <t xml:space="preserve">2.60180640220642</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.55308294296265</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.61155080795288</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.62373113632202</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.68707132339478</t>
+    <t xml:space="preserve">2.601806640625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.5530834197998</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.6115505695343</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.62373089790344</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.68707156181335</t>
   </si>
   <si>
     <t xml:space="preserve">2.53359413146973</t>
   </si>
   <si>
-    <t xml:space="preserve">2.44589233398438</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.47512626647949</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.31726431846619</t>
+    <t xml:space="preserve">2.44589281082153</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.47512674331665</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.31726384162903</t>
   </si>
   <si>
     <t xml:space="preserve">2.32505941390991</t>
@@ -833,22 +833,22 @@
     <t xml:space="preserve">2.26269435882568</t>
   </si>
   <si>
-    <t xml:space="preserve">2.19253301620483</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.16914629936218</t>
+    <t xml:space="preserve">2.19253349304199</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.16914653778076</t>
   </si>
   <si>
     <t xml:space="preserve">2.1662232875824</t>
   </si>
   <si>
-    <t xml:space="preserve">2.08339428901672</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.0463650226593</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.01713109016418</t>
+    <t xml:space="preserve">2.08339405059814</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.04636478424072</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.01713085174561</t>
   </si>
   <si>
     <t xml:space="preserve">2.18278908729553</t>
@@ -857,7 +857,7 @@
     <t xml:space="preserve">2.19155931472778</t>
   </si>
   <si>
-    <t xml:space="preserve">2.28997921943665</t>
+    <t xml:space="preserve">2.28997945785522</t>
   </si>
   <si>
     <t xml:space="preserve">2.22761392593384</t>
@@ -866,28 +866,28 @@
     <t xml:space="preserve">2.13406562805176</t>
   </si>
   <si>
-    <t xml:space="preserve">2.13893795013428</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.21007370948792</t>
+    <t xml:space="preserve">2.13893818855286</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.21007347106934</t>
   </si>
   <si>
     <t xml:space="preserve">2.28218388557434</t>
   </si>
   <si>
-    <t xml:space="preserve">2.24417948722839</t>
+    <t xml:space="preserve">2.24417972564697</t>
   </si>
   <si>
     <t xml:space="preserve">2.18668675422668</t>
   </si>
   <si>
-    <t xml:space="preserve">2.19058442115784</t>
+    <t xml:space="preserve">2.19058465957642</t>
   </si>
   <si>
     <t xml:space="preserve">2.29972434043884</t>
   </si>
   <si>
-    <t xml:space="preserve">2.27243876457214</t>
+    <t xml:space="preserve">2.2724392414093</t>
   </si>
   <si>
     <t xml:space="preserve">2.340651512146</t>
@@ -899,22 +899,22 @@
     <t xml:space="preserve">2.41568493843079</t>
   </si>
   <si>
-    <t xml:space="preserve">2.38839936256409</t>
+    <t xml:space="preserve">2.38839983940125</t>
   </si>
   <si>
     <t xml:space="preserve">2.34552311897278</t>
   </si>
   <si>
-    <t xml:space="preserve">2.36014032363892</t>
+    <t xml:space="preserve">2.3601405620575</t>
   </si>
   <si>
     <t xml:space="preserve">2.31629014015198</t>
   </si>
   <si>
-    <t xml:space="preserve">2.28510713577271</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.28023457527161</t>
+    <t xml:space="preserve">2.28510665893555</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.28023433685303</t>
   </si>
   <si>
     <t xml:space="preserve">2.2003288269043</t>
@@ -926,22 +926,22 @@
     <t xml:space="preserve">2.21494579315186</t>
   </si>
   <si>
-    <t xml:space="preserve">2.23151183128357</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.19545722007751</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.14283585548401</t>
+    <t xml:space="preserve">2.23151135444641</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.19545698165894</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.14283561706543</t>
   </si>
   <si>
     <t xml:space="preserve">2.12529611587524</t>
   </si>
   <si>
-    <t xml:space="preserve">2.23346042633057</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.3874249458313</t>
+    <t xml:space="preserve">2.23346018791199</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.38742470741272</t>
   </si>
   <si>
     <t xml:space="preserve">2.4225058555603</t>
@@ -953,10 +953,10 @@
     <t xml:space="preserve">2.44345688819885</t>
   </si>
   <si>
-    <t xml:space="preserve">2.50679683685303</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.54333901405334</t>
+    <t xml:space="preserve">2.50679659843445</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.54333853721619</t>
   </si>
   <si>
     <t xml:space="preserve">2.47999906539917</t>
@@ -965,10 +965,10 @@
     <t xml:space="preserve">2.46050977706909</t>
   </si>
   <si>
-    <t xml:space="preserve">2.32116198539734</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.28413224220276</t>
+    <t xml:space="preserve">2.32116174697876</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.28413248062134</t>
   </si>
   <si>
     <t xml:space="preserve">2.36793613433838</t>
@@ -986,31 +986,31 @@
     <t xml:space="preserve">2.28315830230713</t>
   </si>
   <si>
-    <t xml:space="preserve">2.27230000495911</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.27328705787659</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.30487394332886</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.30191278457642</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.27526092529297</t>
+    <t xml:space="preserve">2.27229976654053</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.27328729629517</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.30487370491028</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.301913022995</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.27526116371155</t>
   </si>
   <si>
     <t xml:space="preserve">2.20616436004639</t>
   </si>
   <si>
-    <t xml:space="preserve">2.20715188980103</t>
+    <t xml:space="preserve">2.20715165138245</t>
   </si>
   <si>
     <t xml:space="preserve">2.15187430381775</t>
   </si>
   <si>
-    <t xml:space="preserve">2.19728016853333</t>
+    <t xml:space="preserve">2.19728064537048</t>
   </si>
   <si>
     <t xml:space="preserve">2.16964197158813</t>
@@ -1019,43 +1019,43 @@
     <t xml:space="preserve">2.13015794754028</t>
   </si>
   <si>
-    <t xml:space="preserve">2.09758400917053</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.10153198242188</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.17951273918152</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.172602891922</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.12719702720642</t>
+    <t xml:space="preserve">2.09758377075195</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.10153222084045</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.1795129776001</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.17260313034058</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.12719678878784</t>
   </si>
   <si>
     <t xml:space="preserve">2.18050003051758</t>
   </si>
   <si>
-    <t xml:space="preserve">2.15878391265869</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.06106066703796</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.07389307022095</t>
+    <t xml:space="preserve">2.15878367424011</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.06106042861938</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.07389283180237</t>
   </si>
   <si>
     <t xml:space="preserve">2.02059006690979</t>
   </si>
   <si>
-    <t xml:space="preserve">2.11140275001526</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.10251951217651</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.15779590606689</t>
+    <t xml:space="preserve">2.11140251159668</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.10251903533936</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.15779638290405</t>
   </si>
   <si>
     <t xml:space="preserve">2.17062854766846</t>
@@ -1064,25 +1064,25 @@
     <t xml:space="preserve">2.19037103652954</t>
   </si>
   <si>
-    <t xml:space="preserve">2.1785249710083</t>
+    <t xml:space="preserve">2.17852568626404</t>
   </si>
   <si>
     <t xml:space="preserve">2.15483522415161</t>
   </si>
   <si>
-    <t xml:space="preserve">2.29401636123657</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.37199687957764</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.3147451877594</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.32066798210144</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.31375765800476</t>
+    <t xml:space="preserve">2.29401659965515</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.37199640274048</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.31474494934082</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.32066822052002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.31375789642334</t>
   </si>
   <si>
     <t xml:space="preserve">2.34534549713135</t>
@@ -1091,13 +1091,13 @@
     <t xml:space="preserve">2.38779067993164</t>
   </si>
   <si>
-    <t xml:space="preserve">2.43813276290894</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.44504189491272</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.44306802749634</t>
+    <t xml:space="preserve">2.43813252449036</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.44504237174988</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.4430685043335</t>
   </si>
   <si>
     <t xml:space="preserve">2.45787453651428</t>
@@ -1112,7 +1112,7 @@
     <t xml:space="preserve">2.32955193519592</t>
   </si>
   <si>
-    <t xml:space="preserve">2.30388784408569</t>
+    <t xml:space="preserve">2.30388760566711</t>
   </si>
   <si>
     <t xml:space="preserve">2.27624821662903</t>
@@ -1124,25 +1124,25 @@
     <t xml:space="preserve">2.32165479660034</t>
   </si>
   <si>
-    <t xml:space="preserve">2.29598999023438</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.29204154014587</t>
+    <t xml:space="preserve">2.29599022865295</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.29204177856445</t>
   </si>
   <si>
     <t xml:space="preserve">2.33646154403687</t>
   </si>
   <si>
-    <t xml:space="preserve">2.47761607170105</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.44405460357666</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.42628765106201</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.34040975570679</t>
+    <t xml:space="preserve">2.47761631011963</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.44405484199524</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.42628741264343</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.34040999412537</t>
   </si>
   <si>
     <t xml:space="preserve">2.41839027404785</t>
@@ -1151,22 +1151,22 @@
     <t xml:space="preserve">2.40753245353699</t>
   </si>
   <si>
-    <t xml:space="preserve">2.38088083267212</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.34929394721985</t>
+    <t xml:space="preserve">2.38088059425354</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.34929370880127</t>
   </si>
   <si>
     <t xml:space="preserve">2.31968092918396</t>
   </si>
   <si>
-    <t xml:space="preserve">2.34238338470459</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.35225486755371</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.29105472564697</t>
+    <t xml:space="preserve">2.34238362312317</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.35225510597229</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.29105496406555</t>
   </si>
   <si>
     <t xml:space="preserve">2.31573247909546</t>
@@ -1175,34 +1175,34 @@
     <t xml:space="preserve">2.33547425270081</t>
   </si>
   <si>
-    <t xml:space="preserve">2.36706137657166</t>
+    <t xml:space="preserve">2.36706209182739</t>
   </si>
   <si>
     <t xml:space="preserve">2.3315258026123</t>
   </si>
   <si>
-    <t xml:space="preserve">2.29500389099121</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.25551891326904</t>
+    <t xml:space="preserve">2.29500365257263</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.2555193901062</t>
   </si>
   <si>
     <t xml:space="preserve">2.2357771396637</t>
   </si>
   <si>
-    <t xml:space="preserve">2.29993891716003</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.37101006507874</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.32362914085388</t>
+    <t xml:space="preserve">2.29993915557861</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.37101030349731</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.32362937927246</t>
   </si>
   <si>
     <t xml:space="preserve">2.26440286636353</t>
   </si>
   <si>
-    <t xml:space="preserve">2.28513193130493</t>
+    <t xml:space="preserve">2.28513216972351</t>
   </si>
   <si>
     <t xml:space="preserve">2.31277108192444</t>
@@ -1220,13 +1220,13 @@
     <t xml:space="preserve">2.44701671600342</t>
   </si>
   <si>
-    <t xml:space="preserve">2.48748779296875</t>
+    <t xml:space="preserve">2.48748731613159</t>
   </si>
   <si>
     <t xml:space="preserve">2.49735856056213</t>
   </si>
   <si>
-    <t xml:space="preserve">2.53931045532227</t>
+    <t xml:space="preserve">2.53930997848511</t>
   </si>
   <si>
     <t xml:space="preserve">2.53190660476685</t>
@@ -1235,16 +1235,16 @@
     <t xml:space="preserve">2.45688700675964</t>
   </si>
   <si>
-    <t xml:space="preserve">2.41542935371399</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.28414511680603</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.21702218055725</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.16865491867065</t>
+    <t xml:space="preserve">2.41542911529541</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.28414487838745</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.21702265739441</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.16865468025208</t>
   </si>
   <si>
     <t xml:space="preserve">2.1923451423645</t>
@@ -1253,49 +1253,49 @@
     <t xml:space="preserve">2.16766762733459</t>
   </si>
   <si>
-    <t xml:space="preserve">2.1617443561554</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.09264779090881</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.09955739974976</t>
+    <t xml:space="preserve">2.16174483299255</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.09264826774597</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.09955763816833</t>
   </si>
   <si>
     <t xml:space="preserve">2.12028670310974</t>
   </si>
   <si>
-    <t xml:space="preserve">2.09659671783447</t>
+    <t xml:space="preserve">2.09659624099731</t>
   </si>
   <si>
     <t xml:space="preserve">2.06402254104614</t>
   </si>
   <si>
-    <t xml:space="preserve">2.07488036155701</t>
+    <t xml:space="preserve">2.07488059997559</t>
   </si>
   <si>
     <t xml:space="preserve">2.06500935554504</t>
   </si>
   <si>
-    <t xml:space="preserve">2.05908679962158</t>
+    <t xml:space="preserve">2.05908703804016</t>
   </si>
   <si>
     <t xml:space="preserve">2.13410615921021</t>
   </si>
   <si>
-    <t xml:space="preserve">2.07981562614441</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.04625463485718</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.00775742530823</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.91990637779236</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.11041641235352</t>
+    <t xml:space="preserve">2.07981538772583</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.04625487327576</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.00775766372681</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.91990602016449</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.11041593551636</t>
   </si>
   <si>
     <t xml:space="preserve">2.08771252632141</t>
@@ -1319,22 +1319,22 @@
     <t xml:space="preserve">2.03835797309875</t>
   </si>
   <si>
-    <t xml:space="preserve">2.02651286125183</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.08672523498535</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.18346118927002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.26835131645203</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.20122909545898</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.26045489311218</t>
+    <t xml:space="preserve">2.02651262283325</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.08672547340393</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.18346095085144</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.26835155487061</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.20122885704041</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.26045441627502</t>
   </si>
   <si>
     <t xml:space="preserve">2.24860978126526</t>
@@ -1343,46 +1343,46 @@
     <t xml:space="preserve">2.22097086906433</t>
   </si>
   <si>
-    <t xml:space="preserve">2.29302906990051</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.2397255897522</t>
+    <t xml:space="preserve">2.29302883148193</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.23972582817078</t>
   </si>
   <si>
     <t xml:space="preserve">2.09857058525085</t>
   </si>
   <si>
-    <t xml:space="preserve">2.05711221694946</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.05119037628174</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.11930012702942</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.10745429992676</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.1094286441803</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.06797075271606</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.07882881164551</t>
+    <t xml:space="preserve">2.05711197853088</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.05119013786316</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.119300365448</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.10745453834534</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.10942888259888</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.06797099113464</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.07882857322693</t>
   </si>
   <si>
     <t xml:space="preserve">2.1360809803009</t>
   </si>
   <si>
-    <t xml:space="preserve">2.07784128189087</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.05316376686096</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.09363532066345</t>
+    <t xml:space="preserve">2.07784152030945</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.05316400527954</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.09363555908203</t>
   </si>
   <si>
     <t xml:space="preserve">2.09560942649841</t>
@@ -1394,73 +1394,70 @@
     <t xml:space="preserve">2.22788095474243</t>
   </si>
   <si>
-    <t xml:space="preserve">2.25058388710022</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.22590661048889</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.18247389793396</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.28315854072571</t>
+    <t xml:space="preserve">2.25058364868164</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.22590613365173</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.18247365951538</t>
   </si>
   <si>
     <t xml:space="preserve">2.37594485282898</t>
   </si>
   <si>
-    <t xml:space="preserve">2.3739709854126</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.3912456035614</t>
+    <t xml:space="preserve">2.37397146224976</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.39124536514282</t>
   </si>
   <si>
     <t xml:space="preserve">2.29944515228271</t>
   </si>
   <si>
-    <t xml:space="preserve">2.31819987297058</t>
+    <t xml:space="preserve">2.31820011138916</t>
   </si>
   <si>
     <t xml:space="preserve">2.30043196678162</t>
   </si>
   <si>
-    <t xml:space="preserve">2.23775148391724</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.24614143371582</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.32461619377136</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.27427434921265</t>
+    <t xml:space="preserve">2.23775100708008</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.2461416721344</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.32461643218994</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.27427458763123</t>
   </si>
   <si>
     <t xml:space="preserve">2.2441680431366</t>
   </si>
   <si>
-    <t xml:space="preserve">2.36064553260803</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.36508703231812</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.35521602630615</t>
+    <t xml:space="preserve">2.36064505577087</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.36508727073669</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.35521578788757</t>
   </si>
   <si>
     <t xml:space="preserve">2.35916423797607</t>
   </si>
   <si>
-    <t xml:space="preserve">2.31227779388428</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.4001293182373</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.40062284469604</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.40506529808044</t>
+    <t xml:space="preserve">2.3122775554657</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.40012979507446</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.40062308311462</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.40506482124329</t>
   </si>
   <si>
     <t xml:space="preserve">2.40259695053101</t>
@@ -1469,25 +1466,25 @@
     <t xml:space="preserve">2.43122243881226</t>
   </si>
   <si>
-    <t xml:space="preserve">2.41098737716675</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.22738718986511</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.3186936378479</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.35028123855591</t>
+    <t xml:space="preserve">2.41098690032959</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.22738695144653</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.31869339942932</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.35028100013733</t>
   </si>
   <si>
     <t xml:space="preserve">2.27674198150635</t>
   </si>
   <si>
-    <t xml:space="preserve">2.31918692588806</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.26687073707581</t>
+    <t xml:space="preserve">2.31918740272522</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.26687097549438</t>
   </si>
   <si>
     <t xml:space="preserve">2.27131271362305</t>
@@ -1496,49 +1493,49 @@
     <t xml:space="preserve">2.29796457290649</t>
   </si>
   <si>
-    <t xml:space="preserve">2.3058614730835</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.29006791114807</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.2456476688385</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.25206422805786</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.23232269287109</t>
+    <t xml:space="preserve">2.30586123466492</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.29006767272949</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.24564814567566</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.25206470489502</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.23232245445251</t>
   </si>
   <si>
     <t xml:space="preserve">2.24762272834778</t>
   </si>
   <si>
-    <t xml:space="preserve">2.22886729240417</t>
+    <t xml:space="preserve">2.22886753082275</t>
   </si>
   <si>
     <t xml:space="preserve">2.23084163665771</t>
   </si>
   <si>
-    <t xml:space="preserve">2.31721258163452</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.32560300827026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.33448696136475</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.35817766189575</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.40851998329163</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.37989401817322</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.38631010055542</t>
+    <t xml:space="preserve">2.3172128200531</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.32560324668884</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.33448672294617</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.35817790031433</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.40851926803589</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.37989377975464</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.38630986213684</t>
   </si>
   <si>
     <t xml:space="preserve">2.41197443008423</t>
@@ -1547,7 +1544,7 @@
     <t xml:space="preserve">2.36804842948914</t>
   </si>
   <si>
-    <t xml:space="preserve">2.33843541145325</t>
+    <t xml:space="preserve">2.33843517303467</t>
   </si>
   <si>
     <t xml:space="preserve">2.35324215888977</t>
@@ -1559,10 +1556,10 @@
     <t xml:space="preserve">2.35373592376709</t>
   </si>
   <si>
-    <t xml:space="preserve">2.33596777915955</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.32856512069702</t>
+    <t xml:space="preserve">2.33596754074097</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.32856488227844</t>
   </si>
   <si>
     <t xml:space="preserve">2.42036485671997</t>
@@ -1571,43 +1568,43 @@
     <t xml:space="preserve">2.42924880981445</t>
   </si>
   <si>
-    <t xml:space="preserve">2.47662925720215</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.51216459274292</t>
+    <t xml:space="preserve">2.47662973403931</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.5121648311615</t>
   </si>
   <si>
     <t xml:space="preserve">2.54079055786133</t>
   </si>
   <si>
-    <t xml:space="preserve">2.46626448631287</t>
+    <t xml:space="preserve">2.46626496315002</t>
   </si>
   <si>
     <t xml:space="preserve">2.46675848960876</t>
   </si>
   <si>
-    <t xml:space="preserve">2.30290031433105</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.32412958145142</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.36153364181519</t>
+    <t xml:space="preserve">2.30290007591248</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.32413005828857</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.36153388023376</t>
   </si>
   <si>
     <t xml:space="preserve">2.38731265068054</t>
   </si>
   <si>
-    <t xml:space="preserve">2.35799551010132</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.31048178672791</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.17552256584167</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.06583666801453</t>
+    <t xml:space="preserve">2.3579957485199</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.31048202514648</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.1755223274231</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.06583690643311</t>
   </si>
   <si>
     <t xml:space="preserve">2.07341861724854</t>
@@ -1625,10 +1622,10 @@
     <t xml:space="preserve">2.09768056869507</t>
   </si>
   <si>
-    <t xml:space="preserve">2.09667062759399</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.13710713386536</t>
+    <t xml:space="preserve">2.09667038917542</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.13710737228394</t>
   </si>
   <si>
     <t xml:space="preserve">2.07948422431946</t>
@@ -1637,10 +1634,10 @@
     <t xml:space="preserve">2.16996288299561</t>
   </si>
   <si>
-    <t xml:space="preserve">2.1957414150238</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.23112368583679</t>
+    <t xml:space="preserve">2.19574165344238</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.23112392425537</t>
   </si>
   <si>
     <t xml:space="preserve">2.25841903686523</t>
@@ -1652,7 +1649,7 @@
     <t xml:space="preserve">2.18866467475891</t>
   </si>
   <si>
-    <t xml:space="preserve">2.26296830177307</t>
+    <t xml:space="preserve">2.26296806335449</t>
   </si>
   <si>
     <t xml:space="preserve">2.32008600234985</t>
@@ -1664,100 +1661,100 @@
     <t xml:space="preserve">2.41764044761658</t>
   </si>
   <si>
-    <t xml:space="preserve">2.36810541152954</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.38124775886536</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.3473801612854</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.36861109733582</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.37922501564026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.37012672424316</t>
+    <t xml:space="preserve">2.36810517311096</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.38124752044678</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.34738063812256</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.36861062049866</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.37922549247742</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.37012696266174</t>
   </si>
   <si>
     <t xml:space="preserve">2.37265467643738</t>
   </si>
   <si>
-    <t xml:space="preserve">2.36355566978455</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.41005897521973</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.41814589500427</t>
+    <t xml:space="preserve">2.36355638504028</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.41005873680115</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.41814613342285</t>
   </si>
   <si>
     <t xml:space="preserve">2.37113785743713</t>
   </si>
   <si>
-    <t xml:space="preserve">2.33171129226685</t>
+    <t xml:space="preserve">2.33171153068542</t>
   </si>
   <si>
     <t xml:space="preserve">2.34788632392883</t>
   </si>
   <si>
-    <t xml:space="preserve">2.38023638725281</t>
+    <t xml:space="preserve">2.38023614883423</t>
   </si>
   <si>
     <t xml:space="preserve">2.33828282356262</t>
   </si>
   <si>
-    <t xml:space="preserve">2.29481267929077</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.34131526947021</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.33878779411316</t>
+    <t xml:space="preserve">2.29481291770935</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.34131550788879</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.33878755569458</t>
   </si>
   <si>
     <t xml:space="preserve">2.37315940856934</t>
   </si>
   <si>
-    <t xml:space="preserve">2.40652060508728</t>
+    <t xml:space="preserve">2.40652084350586</t>
   </si>
   <si>
     <t xml:space="preserve">2.38276338577271</t>
   </si>
   <si>
-    <t xml:space="preserve">2.41662907600403</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.40550947189331</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.31958055496216</t>
+    <t xml:space="preserve">2.41662955284119</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.40550923347473</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.31958031654358</t>
   </si>
   <si>
     <t xml:space="preserve">2.3135142326355</t>
   </si>
   <si>
-    <t xml:space="preserve">2.31503129005432</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.33524942398071</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.19725728034973</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.1724898815155</t>
+    <t xml:space="preserve">2.31503081321716</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.33524918556213</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.19725775718689</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.17249011993408</t>
   </si>
   <si>
     <t xml:space="preserve">2.14216184616089</t>
   </si>
   <si>
-    <t xml:space="preserve">2.08908772468567</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.06937527656555</t>
+    <t xml:space="preserve">2.08908748626709</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.06937503814697</t>
   </si>
   <si>
     <t xml:space="preserve">2.06684803962708</t>
@@ -1766,16 +1763,16 @@
     <t xml:space="preserve">2.02186131477356</t>
   </si>
   <si>
-    <t xml:space="preserve">2.02236676216125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.06735277175903</t>
+    <t xml:space="preserve">2.02236652374268</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.06735253334045</t>
   </si>
   <si>
     <t xml:space="preserve">2.0663423538208</t>
   </si>
   <si>
-    <t xml:space="preserve">2.05016660690308</t>
+    <t xml:space="preserve">2.05016708374023</t>
   </si>
   <si>
     <t xml:space="preserve">2.04511308670044</t>
@@ -1787,16 +1784,16 @@
     <t xml:space="preserve">2.00416994094849</t>
   </si>
   <si>
-    <t xml:space="preserve">2.01680660247803</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.94098722934723</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.92026281356812</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.92936134338379</t>
+    <t xml:space="preserve">2.01680636405945</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.94098711013794</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.9202629327774</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.92936158180237</t>
   </si>
   <si>
     <t xml:space="preserve">2.00012612342834</t>
@@ -1805,37 +1802,37 @@
     <t xml:space="preserve">2.0855495929718</t>
   </si>
   <si>
-    <t xml:space="preserve">2.08959341049194</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.14519429206848</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.13458037376404</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.13660168647766</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.12952494621277</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.17855548858643</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.21141052246094</t>
+    <t xml:space="preserve">2.08959364891052</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.14519476890564</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.13458013534546</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.13660192489624</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.12952566146851</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.178555727005</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.21141076087952</t>
   </si>
   <si>
     <t xml:space="preserve">2.19068670272827</t>
   </si>
   <si>
-    <t xml:space="preserve">2.14873337745667</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.17350125312805</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.20029091835022</t>
+    <t xml:space="preserve">2.14873361587524</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.17350077629089</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.20029067993164</t>
   </si>
   <si>
     <t xml:space="preserve">2.22253060340881</t>
@@ -1844,115 +1841,115 @@
     <t xml:space="preserve">2.01579523086548</t>
   </si>
   <si>
-    <t xml:space="preserve">1.93643748760223</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.90257155895233</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.87780320644379</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.88942933082581</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.85505759716034</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.82422411441803</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.78783047199249</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.82675123214722</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.79237973690033</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.80602741241455</t>
+    <t xml:space="preserve">1.93643772602081</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.90257179737091</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.8778030872345</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.88942921161652</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.85505771636963</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.82422423362732</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.78783059120178</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.8267514705658</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.79237961769104</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.80602729320526</t>
   </si>
   <si>
     <t xml:space="preserve">1.8186639547348</t>
   </si>
   <si>
-    <t xml:space="preserve">1.80299484729767</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.80552196502686</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.76660120487213</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.77317237854004</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.70847272872925</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.67157363891602</t>
+    <t xml:space="preserve">1.80299496650696</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.80552208423615</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.76660084724426</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.77317249774933</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.70847284793854</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.67157351970673</t>
   </si>
   <si>
     <t xml:space="preserve">1.62405967712402</t>
   </si>
   <si>
-    <t xml:space="preserve">1.66146445274353</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.64882791042328</t>
+    <t xml:space="preserve">1.66146457195282</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.64882779121399</t>
   </si>
   <si>
     <t xml:space="preserve">1.72161495685577</t>
   </si>
   <si>
-    <t xml:space="preserve">1.71150517463684</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.69735205173492</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.70746171474457</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.7767106294632</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.71554911136627</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.70291256904602</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.73374581336975</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.74688816070557</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.76255738735199</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.76508474349976</t>
+    <t xml:space="preserve">1.71150541305542</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.69735217094421</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.70746183395386</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.77671039104462</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.71554923057556</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.70291233062744</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.73374605178833</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.74688839912415</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.76255750656128</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.76508522033691</t>
   </si>
   <si>
     <t xml:space="preserve">1.71352756023407</t>
   </si>
   <si>
-    <t xml:space="preserve">1.72768008708954</t>
+    <t xml:space="preserve">1.72768032550812</t>
   </si>
   <si>
     <t xml:space="preserve">1.69634175300598</t>
   </si>
   <si>
-    <t xml:space="preserve">1.71201086044312</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.69229793548584</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.75345885753632</t>
+    <t xml:space="preserve">1.71201109886169</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.69229805469513</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.75345873832703</t>
   </si>
   <si>
     <t xml:space="preserve">1.76356840133667</t>
@@ -1967,7 +1964,7 @@
     <t xml:space="preserve">1.79389631748199</t>
   </si>
   <si>
-    <t xml:space="preserve">1.8100711107254</t>
+    <t xml:space="preserve">1.81007122993469</t>
   </si>
   <si>
     <t xml:space="preserve">1.81916952133179</t>
@@ -1976,22 +1973,22 @@
     <t xml:space="preserve">1.90307724475861</t>
   </si>
   <si>
-    <t xml:space="preserve">1.87072682380676</t>
+    <t xml:space="preserve">1.87072694301605</t>
   </si>
   <si>
     <t xml:space="preserve">1.90560412406921</t>
   </si>
   <si>
-    <t xml:space="preserve">1.84494853019714</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.81563138961792</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.7847980260849</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.76761209964752</t>
+    <t xml:space="preserve">1.84494841098785</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.81563127040863</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.78479790687561</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.76761221885681</t>
   </si>
   <si>
     <t xml:space="preserve">1.76053595542908</t>
@@ -2000,28 +1997,28 @@
     <t xml:space="preserve">1.73324024677277</t>
   </si>
   <si>
-    <t xml:space="preserve">1.69937443733215</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.69128704071045</t>
+    <t xml:space="preserve">1.69937431812286</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.69128692150116</t>
   </si>
   <si>
     <t xml:space="preserve">1.72565853595734</t>
   </si>
   <si>
-    <t xml:space="preserve">1.69280290603638</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.68016648292542</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.65742111206055</t>
+    <t xml:space="preserve">1.69280302524567</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.68016624450684</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.65742087364197</t>
   </si>
   <si>
     <t xml:space="preserve">1.70038557052612</t>
   </si>
   <si>
-    <t xml:space="preserve">1.66601383686066</t>
+    <t xml:space="preserve">1.66601395606995</t>
   </si>
   <si>
     <t xml:space="preserve">1.65489327907562</t>
@@ -2036,61 +2033,61 @@
     <t xml:space="preserve">1.68319964408875</t>
   </si>
   <si>
-    <t xml:space="preserve">1.67612254619598</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.68117737770081</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.65287172794342</t>
+    <t xml:space="preserve">1.67612266540527</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.6811774969101</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.65287160873413</t>
   </si>
   <si>
     <t xml:space="preserve">1.58918249607086</t>
   </si>
   <si>
-    <t xml:space="preserve">1.51386857032776</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.54722929000854</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.55329501628876</t>
+    <t xml:space="preserve">1.51386845111847</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.54722917079926</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.55329489707947</t>
   </si>
   <si>
     <t xml:space="preserve">1.54419648647308</t>
   </si>
   <si>
-    <t xml:space="preserve">1.55228364467621</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.5436909198761</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.52094495296478</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.52549386024475</t>
+    <t xml:space="preserve">1.5522837638855</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.54369103908539</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.52094483375549</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.52549397945404</t>
   </si>
   <si>
     <t xml:space="preserve">1.59221577644348</t>
   </si>
   <si>
-    <t xml:space="preserve">1.57300782203674</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.57705128192902</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.59069895744324</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.49415576457977</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.49870431423187</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.50123202800751</t>
+    <t xml:space="preserve">1.57300758361816</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.57705140113831</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.59069907665253</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.49415564537048</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.49870419502258</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.50123178958893</t>
   </si>
   <si>
     <t xml:space="preserve">1.50375890731812</t>
@@ -2099,52 +2096,52 @@
     <t xml:space="preserve">1.53914165496826</t>
   </si>
   <si>
-    <t xml:space="preserve">1.52347254753113</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.65792632102966</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.72666966915131</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.70897841453552</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.70240712165833</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.78125977516174</t>
+    <t xml:space="preserve">1.52347242832184</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.65792644023895</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.72666990756989</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.70897829532623</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.70240700244904</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.78125989437103</t>
   </si>
   <si>
     <t xml:space="preserve">1.7741836309433</t>
   </si>
   <si>
-    <t xml:space="preserve">1.75901913642883</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.73071336746216</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.75093185901642</t>
+    <t xml:space="preserve">1.75901901721954</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.73071348667145</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.75093162059784</t>
   </si>
   <si>
     <t xml:space="preserve">1.76862335205078</t>
   </si>
   <si>
-    <t xml:space="preserve">1.78024864196777</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.82826781272888</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.86921000480652</t>
+    <t xml:space="preserve">1.78024876117706</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.82826793193817</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.8692102432251</t>
   </si>
   <si>
     <t xml:space="preserve">1.8641562461853</t>
   </si>
   <si>
-    <t xml:space="preserve">1.8580904006958</t>
+    <t xml:space="preserve">1.85809016227722</t>
   </si>
   <si>
     <t xml:space="preserve">1.87325489521027</t>
@@ -2153,55 +2150,55 @@
     <t xml:space="preserve">1.81815838813782</t>
   </si>
   <si>
-    <t xml:space="preserve">1.7994567155838</t>
+    <t xml:space="preserve">1.79945683479309</t>
   </si>
   <si>
     <t xml:space="preserve">1.78833603858948</t>
   </si>
   <si>
-    <t xml:space="preserve">1.79895102977753</t>
+    <t xml:space="preserve">1.7989513874054</t>
   </si>
   <si>
     <t xml:space="preserve">1.8353443145752</t>
   </si>
   <si>
-    <t xml:space="preserve">1.87224388122559</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.8863959312439</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.88690197467804</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.87022149562836</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.84444272518158</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.83686077594757</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.82119178771973</t>
+    <t xml:space="preserve">1.8722437620163</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.88639605045319</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.88690161705017</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.87022137641907</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.84444260597229</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.83686089515686</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.82119154930115</t>
   </si>
   <si>
     <t xml:space="preserve">1.8500030040741</t>
   </si>
   <si>
-    <t xml:space="preserve">1.84242141246796</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.84039890766144</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.8656724691391</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.85151970386505</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.86971569061279</t>
+    <t xml:space="preserve">1.84242117404938</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.84039902687073</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.86567223072052</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.85151958465576</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.86971580982208</t>
   </si>
   <si>
     <t xml:space="preserve">1.87173819541931</t>
@@ -2210,22 +2207,22 @@
     <t xml:space="preserve">1.88791275024414</t>
   </si>
   <si>
-    <t xml:space="preserve">1.8889240026474</t>
+    <t xml:space="preserve">1.88892388343811</t>
   </si>
   <si>
     <t xml:space="preserve">1.91874647140503</t>
   </si>
   <si>
-    <t xml:space="preserve">1.95463478565216</t>
+    <t xml:space="preserve">1.95463454723358</t>
   </si>
   <si>
     <t xml:space="preserve">2.00619196891785</t>
   </si>
   <si>
-    <t xml:space="preserve">2.04005813598633</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.09414267539978</t>
+    <t xml:space="preserve">2.04005789756775</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.0941424369812</t>
   </si>
   <si>
     <t xml:space="preserve">2.11436176300049</t>
@@ -2234,64 +2231,64 @@
     <t xml:space="preserve">2.09363698959351</t>
   </si>
   <si>
-    <t xml:space="preserve">2.07544112205505</t>
+    <t xml:space="preserve">2.0754406452179</t>
   </si>
   <si>
     <t xml:space="preserve">2.10930705070496</t>
   </si>
   <si>
-    <t xml:space="preserve">2.12649297714233</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.13255786895752</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.16541385650635</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.13053631782532</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.12396502494812</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.07999014854431</t>
+    <t xml:space="preserve">2.12649273872375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.13255763053894</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.16541337966919</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.13053679466248</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.12396478652954</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.07999038696289</t>
   </si>
   <si>
     <t xml:space="preserve">2.068363904953</t>
   </si>
   <si>
-    <t xml:space="preserve">2.02388334274292</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.00164246559143</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.97131490707397</t>
+    <t xml:space="preserve">2.02388310432434</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.00164294242859</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.97131478786469</t>
   </si>
   <si>
     <t xml:space="preserve">1.98900592327118</t>
   </si>
   <si>
-    <t xml:space="preserve">1.95412886142731</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.99810457229614</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.94467735290527</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.89345955848694</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.8532178401947</t>
+    <t xml:space="preserve">1.95412909984589</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.99810469150543</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.94467723369598</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.89345967769623</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.85321772098541</t>
   </si>
   <si>
     <t xml:space="preserve">1.82865512371063</t>
   </si>
   <si>
-    <t xml:space="preserve">1.84746944904327</t>
+    <t xml:space="preserve">1.84746968746185</t>
   </si>
   <si>
     <t xml:space="preserve">1.79834306240082</t>
@@ -2312,7 +2309,7 @@
     <t xml:space="preserve">1.75444209575653</t>
   </si>
   <si>
-    <t xml:space="preserve">1.78527748584747</t>
+    <t xml:space="preserve">1.78527760505676</t>
   </si>
   <si>
     <t xml:space="preserve">1.75287461280823</t>
@@ -2321,22 +2318,22 @@
     <t xml:space="preserve">1.73197019100189</t>
   </si>
   <si>
-    <t xml:space="preserve">1.7288339138031</t>
+    <t xml:space="preserve">1.72883379459381</t>
   </si>
   <si>
     <t xml:space="preserve">1.78318679332733</t>
   </si>
   <si>
-    <t xml:space="preserve">1.79991042613983</t>
+    <t xml:space="preserve">1.79991054534912</t>
   </si>
   <si>
     <t xml:space="preserve">1.7795284986496</t>
   </si>
   <si>
-    <t xml:space="preserve">1.8009557723999</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.79468405246735</t>
+    <t xml:space="preserve">1.80095565319061</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.79468393325806</t>
   </si>
   <si>
     <t xml:space="preserve">1.8082720041275</t>
@@ -2345,10 +2342,10 @@
     <t xml:space="preserve">1.84903693199158</t>
   </si>
   <si>
-    <t xml:space="preserve">1.88353073596954</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.88143992424011</t>
+    <t xml:space="preserve">1.88353049755096</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.88143980503082</t>
   </si>
   <si>
     <t xml:space="preserve">1.9133198261261</t>
@@ -2357,22 +2354,22 @@
     <t xml:space="preserve">1.89241528511047</t>
   </si>
   <si>
-    <t xml:space="preserve">1.89136970043182</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.90234446525574</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.87255525588989</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.86262512207031</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.90077686309814</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.9749892950058</t>
+    <t xml:space="preserve">1.89136958122253</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.90234434604645</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.87255537509918</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.86262536048889</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.90077698230743</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.97498893737793</t>
   </si>
   <si>
     <t xml:space="preserve">2.03247737884521</t>
@@ -2381,19 +2378,22 @@
     <t xml:space="preserve">2.03665828704834</t>
   </si>
   <si>
-    <t xml:space="preserve">2.01836657524109</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.01000475883484</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.99328064918518</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.0021653175354</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.98805463314056</t>
+    <t xml:space="preserve">2.01836633682251</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.00164270401001</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.01000452041626</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.99328100681305</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.00216555595398</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.98805487155914</t>
   </si>
   <si>
     <t xml:space="preserve">2.01627659797668</t>
@@ -2411,7 +2411,7 @@
     <t xml:space="preserve">1.95460724830627</t>
   </si>
   <si>
-    <t xml:space="preserve">1.90495812892914</t>
+    <t xml:space="preserve">1.90495789051056</t>
   </si>
   <si>
     <t xml:space="preserve">1.88927888870239</t>
@@ -2420,16 +2420,16 @@
     <t xml:space="preserve">1.86941957473755</t>
   </si>
   <si>
-    <t xml:space="preserve">1.8438104391098</t>
+    <t xml:space="preserve">1.84381055831909</t>
   </si>
   <si>
     <t xml:space="preserve">1.77168929576874</t>
   </si>
   <si>
-    <t xml:space="preserve">1.76071393489838</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.80775010585785</t>
+    <t xml:space="preserve">1.7607136964798</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.80775022506714</t>
   </si>
   <si>
     <t xml:space="preserve">1.78005111217499</t>
@@ -2438,19 +2438,19 @@
     <t xml:space="preserve">1.80722761154175</t>
   </si>
   <si>
-    <t xml:space="preserve">1.78214108943939</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.8161119222641</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.67239093780518</t>
+    <t xml:space="preserve">1.78214120864868</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.81611204147339</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.67239081859589</t>
   </si>
   <si>
     <t xml:space="preserve">1.63685250282288</t>
   </si>
   <si>
-    <t xml:space="preserve">1.65566718578339</t>
+    <t xml:space="preserve">1.6556670665741</t>
   </si>
   <si>
     <t xml:space="preserve">1.5741378068924</t>
@@ -2459,10 +2459,10 @@
     <t xml:space="preserve">1.60863077640533</t>
   </si>
   <si>
-    <t xml:space="preserve">1.62483251094818</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.57309234142303</t>
+    <t xml:space="preserve">1.62483263015747</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.57309246063232</t>
   </si>
   <si>
     <t xml:space="preserve">1.60026884078979</t>
@@ -2471,13 +2471,13 @@
     <t xml:space="preserve">1.60654067993164</t>
   </si>
   <si>
-    <t xml:space="preserve">1.59295237064362</t>
+    <t xml:space="preserve">1.59295225143433</t>
   </si>
   <si>
     <t xml:space="preserve">1.60392713546753</t>
   </si>
   <si>
-    <t xml:space="preserve">1.67657160758972</t>
+    <t xml:space="preserve">1.67657172679901</t>
   </si>
   <si>
     <t xml:space="preserve">1.665074467659</t>
@@ -2492,67 +2492,67 @@
     <t xml:space="preserve">1.68806934356689</t>
   </si>
   <si>
-    <t xml:space="preserve">1.71629106998444</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.73353755474091</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.73876368999481</t>
+    <t xml:space="preserve">1.71629118919373</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.73353743553162</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.7387638092041</t>
   </si>
   <si>
     <t xml:space="preserve">1.74712562561035</t>
   </si>
   <si>
-    <t xml:space="preserve">1.80618226528168</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.8265643119812</t>
+    <t xml:space="preserve">1.80618238449097</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.82656407356262</t>
   </si>
   <si>
     <t xml:space="preserve">1.80879497528076</t>
   </si>
   <si>
-    <t xml:space="preserve">1.83649432659149</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.88300788402557</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.89189255237579</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.83022248744965</t>
+    <t xml:space="preserve">1.83649408817291</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.88300776481628</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.8918924331665</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.83022236824036</t>
   </si>
   <si>
     <t xml:space="preserve">1.84119772911072</t>
   </si>
   <si>
-    <t xml:space="preserve">1.92168164253235</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.86419332027435</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.83597147464752</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.81663489341736</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.82760953903198</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.85112774372101</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.8229056596756</t>
+    <t xml:space="preserve">1.92168188095093</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.86419343948364</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.83597123622894</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.81663501262665</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.82760977745056</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.85112750530243</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.82290589809418</t>
   </si>
   <si>
     <t xml:space="preserve">1.83388125896454</t>
   </si>
   <si>
-    <t xml:space="preserve">1.81715655326843</t>
+    <t xml:space="preserve">1.81715667247772</t>
   </si>
   <si>
     <t xml:space="preserve">1.82342863082886</t>
@@ -2561,22 +2561,22 @@
     <t xml:space="preserve">1.83440411090851</t>
   </si>
   <si>
-    <t xml:space="preserve">1.90129959583282</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.92220437526703</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.9634917974472</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.99223566055298</t>
+    <t xml:space="preserve">1.9012998342514</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.92220449447632</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.96349167823792</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.99223554134369</t>
   </si>
   <si>
     <t xml:space="preserve">2.04658842086792</t>
   </si>
   <si>
-    <t xml:space="preserve">2.09989619255066</t>
+    <t xml:space="preserve">2.0998957157135</t>
   </si>
   <si>
     <t xml:space="preserve">2.12289142608643</t>
@@ -2588,13 +2588,13 @@
     <t xml:space="preserve">2.11139321327209</t>
   </si>
   <si>
-    <t xml:space="preserve">2.11034846305847</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.12602663040161</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.126549243927</t>
+    <t xml:space="preserve">2.11034870147705</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.12602686882019</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.12654948234558</t>
   </si>
   <si>
     <t xml:space="preserve">2.08630752563477</t>
@@ -2609,7 +2609,7 @@
     <t xml:space="preserve">2.15790700912476</t>
   </si>
   <si>
-    <t xml:space="preserve">2.18299245834351</t>
+    <t xml:space="preserve">2.18299269676208</t>
   </si>
   <si>
     <t xml:space="preserve">2.1976261138916</t>
@@ -2633,16 +2633,16 @@
     <t xml:space="preserve">2.26504445075989</t>
   </si>
   <si>
-    <t xml:space="preserve">2.28176808357239</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.30946731567383</t>
+    <t xml:space="preserve">2.28176832199097</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.30946755409241</t>
   </si>
   <si>
     <t xml:space="preserve">2.37636303901672</t>
   </si>
   <si>
-    <t xml:space="preserve">2.40824317932129</t>
+    <t xml:space="preserve">2.40824341773987</t>
   </si>
   <si>
     <t xml:space="preserve">2.39465498924255</t>
@@ -2654,10 +2654,10 @@
     <t xml:space="preserve">2.35023212432861</t>
   </si>
   <si>
-    <t xml:space="preserve">2.34448313713074</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.32357859611511</t>
+    <t xml:space="preserve">2.34448289871216</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.32357835769653</t>
   </si>
   <si>
     <t xml:space="preserve">2.29326558113098</t>
@@ -2669,109 +2669,109 @@
     <t xml:space="preserve">2.2498881816864</t>
   </si>
   <si>
-    <t xml:space="preserve">2.2666118144989</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.29431104660034</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.30633187294006</t>
+    <t xml:space="preserve">2.26661205291748</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.29431128501892</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.30633163452148</t>
   </si>
   <si>
     <t xml:space="preserve">2.32880473136902</t>
   </si>
   <si>
-    <t xml:space="preserve">2.30110573768616</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.32566833496094</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.32253289222717</t>
+    <t xml:space="preserve">2.30110549926758</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.32566857337952</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.32253265380859</t>
   </si>
   <si>
     <t xml:space="preserve">2.35336756706238</t>
   </si>
   <si>
-    <t xml:space="preserve">2.33612132072449</t>
+    <t xml:space="preserve">2.33612108230591</t>
   </si>
   <si>
     <t xml:space="preserve">2.36538767814636</t>
   </si>
   <si>
-    <t xml:space="preserve">2.38315653800964</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.36016130447388</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.35702586174011</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.32775902748108</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.34291458129883</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.40144896507263</t>
+    <t xml:space="preserve">2.38315677642822</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.36016154289246</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.35702562332153</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.32775926589966</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.34291481971741</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.40144872665405</t>
   </si>
   <si>
     <t xml:space="preserve">2.39988136291504</t>
   </si>
   <si>
-    <t xml:space="preserve">2.350754737854</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.35754823684692</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.38002109527588</t>
+    <t xml:space="preserve">2.35075497627258</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.3575484752655</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.38002133369446</t>
   </si>
   <si>
     <t xml:space="preserve">2.41242408752441</t>
   </si>
   <si>
-    <t xml:space="preserve">2.41451406478882</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.40406227111816</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.41190147399902</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.39047408103943</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.38420248031616</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.4030168056488</t>
+    <t xml:space="preserve">2.41451382637024</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.40406250953674</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.41190123558044</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.39047431945801</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.38420224189758</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.40301704406738</t>
   </si>
   <si>
     <t xml:space="preserve">2.38838338851929</t>
   </si>
   <si>
-    <t xml:space="preserve">2.41869497299194</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.33037185668945</t>
+    <t xml:space="preserve">2.41869521141052</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.33037209510803</t>
   </si>
   <si>
     <t xml:space="preserve">2.33089470863342</t>
   </si>
   <si>
-    <t xml:space="preserve">2.31626105308533</t>
+    <t xml:space="preserve">2.31626081466675</t>
   </si>
   <si>
     <t xml:space="preserve">2.36329770088196</t>
   </si>
   <si>
-    <t xml:space="preserve">2.34239220619202</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.26086354255676</t>
+    <t xml:space="preserve">2.34239196777344</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.26086378097534</t>
   </si>
   <si>
     <t xml:space="preserve">2.1688814163208</t>
@@ -2789,19 +2789,19 @@
     <t xml:space="preserve">2.26608991622925</t>
   </si>
   <si>
-    <t xml:space="preserve">2.27497458457947</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.28542685508728</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.36956882476807</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.34918665885925</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.42705655097961</t>
+    <t xml:space="preserve">2.27497434616089</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.28542637825012</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.36956858634949</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.34918689727783</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.42705702781677</t>
   </si>
   <si>
     <t xml:space="preserve">2.16417789459229</t>
@@ -2813,52 +2813,52 @@
     <t xml:space="preserve">2.19187712669373</t>
   </si>
   <si>
-    <t xml:space="preserve">2.12811756134033</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.00477838516235</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.00686955451965</t>
+    <t xml:space="preserve">2.12811779975891</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.00477814674377</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.00686931610107</t>
   </si>
   <si>
     <t xml:space="preserve">2.05129194259644</t>
   </si>
   <si>
-    <t xml:space="preserve">1.97446620464325</t>
+    <t xml:space="preserve">1.97446632385254</t>
   </si>
   <si>
     <t xml:space="preserve">1.88091695308685</t>
   </si>
   <si>
-    <t xml:space="preserve">1.73771822452545</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.69277262687683</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.63110339641571</t>
+    <t xml:space="preserve">1.73771834373474</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.69277274608612</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.631103515625</t>
   </si>
   <si>
     <t xml:space="preserve">1.59661066532135</t>
   </si>
   <si>
-    <t xml:space="preserve">1.37972271442413</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.31282699108124</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.31596255302429</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.08235001564026</t>
+    <t xml:space="preserve">1.37972259521484</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.31282687187195</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.315962433815</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.08234989643097</t>
   </si>
   <si>
     <t xml:space="preserve">1.32484710216522</t>
   </si>
   <si>
-    <t xml:space="preserve">1.22345852851868</t>
+    <t xml:space="preserve">1.22345840930939</t>
   </si>
   <si>
     <t xml:space="preserve">1.21927750110626</t>
@@ -2867,22 +2867,22 @@
     <t xml:space="preserve">1.18687474727631</t>
   </si>
   <si>
-    <t xml:space="preserve">1.20516669750214</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.34575164318085</t>
+    <t xml:space="preserve">1.20516645908356</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.34575176239014</t>
   </si>
   <si>
     <t xml:space="preserve">1.53441858291626</t>
   </si>
   <si>
-    <t xml:space="preserve">1.57256984710693</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.548006772995</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.51769483089447</t>
+    <t xml:space="preserve">1.57256972789764</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.54800665378571</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.51769471168518</t>
   </si>
   <si>
     <t xml:space="preserve">1.41996455192566</t>
@@ -2891,19 +2891,19 @@
     <t xml:space="preserve">1.41944181919098</t>
   </si>
   <si>
-    <t xml:space="preserve">1.46334207057953</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.4210090637207</t>
+    <t xml:space="preserve">1.46334183216095</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.42100942134857</t>
   </si>
   <si>
     <t xml:space="preserve">1.40951180458069</t>
   </si>
   <si>
-    <t xml:space="preserve">1.40271735191345</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.42989373207092</t>
+    <t xml:space="preserve">1.40271723270416</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.42989385128021</t>
   </si>
   <si>
     <t xml:space="preserve">1.42414546012878</t>
@@ -2912,7 +2912,7 @@
     <t xml:space="preserve">1.35411357879639</t>
   </si>
   <si>
-    <t xml:space="preserve">1.36717915534973</t>
+    <t xml:space="preserve">1.36717903614044</t>
   </si>
   <si>
     <t xml:space="preserve">1.306032538414</t>
@@ -2921,7 +2921,7 @@
     <t xml:space="preserve">1.20987021923065</t>
   </si>
   <si>
-    <t xml:space="preserve">1.15760827064514</t>
+    <t xml:space="preserve">1.15760838985443</t>
   </si>
   <si>
     <t xml:space="preserve">1.16962838172913</t>
@@ -2930,34 +2930,34 @@
     <t xml:space="preserve">1.1706737279892</t>
   </si>
   <si>
-    <t xml:space="preserve">1.1199791431427</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.11841106414795</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.15604019165039</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.10795915126801</t>
+    <t xml:space="preserve">1.11997902393341</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.11841094493866</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.1560400724411</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.10795903205872</t>
   </si>
   <si>
     <t xml:space="preserve">1.1393164396286</t>
   </si>
   <si>
-    <t xml:space="preserve">1.2109158039093</t>
+    <t xml:space="preserve">1.21091568470001</t>
   </si>
   <si>
     <t xml:space="preserve">1.23025226593018</t>
   </si>
   <si>
-    <t xml:space="preserve">1.17694473266602</t>
+    <t xml:space="preserve">1.17694461345673</t>
   </si>
   <si>
     <t xml:space="preserve">1.15185904502869</t>
   </si>
   <si>
-    <t xml:space="preserve">1.14976823329926</t>
+    <t xml:space="preserve">1.14976835250854</t>
   </si>
   <si>
     <t xml:space="preserve">1.13618004322052</t>
@@ -2966,22 +2966,22 @@
     <t xml:space="preserve">1.11736631393433</t>
   </si>
   <si>
-    <t xml:space="preserve">1.10482275485992</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.09750628471375</t>
+    <t xml:space="preserve">1.10482263565063</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.09750616550446</t>
   </si>
   <si>
     <t xml:space="preserve">1.06092262268066</t>
   </si>
   <si>
-    <t xml:space="preserve">1.05256056785583</t>
+    <t xml:space="preserve">1.05256068706512</t>
   </si>
   <si>
     <t xml:space="preserve">1.04890239238739</t>
   </si>
   <si>
-    <t xml:space="preserve">1.09102869033813</t>
+    <t xml:space="preserve">1.09102857112885</t>
   </si>
   <si>
     <t xml:space="preserve">1.03023862838745</t>
@@ -2990,10 +2990,10 @@
     <t xml:space="preserve">1.01237452030182</t>
   </si>
   <si>
-    <t xml:space="preserve">0.99317729473114</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.993977606296539</t>
+    <t xml:space="preserve">0.993177235126495</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.993977665901184</t>
   </si>
   <si>
     <t xml:space="preserve">0.996643543243408</t>
@@ -3005,13 +3005,13 @@
     <t xml:space="preserve">1.14062082767487</t>
   </si>
   <si>
-    <t xml:space="preserve">1.18648028373718</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.14488756656647</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.17314922809601</t>
+    <t xml:space="preserve">1.18648040294647</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.14488768577576</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.1731493473053</t>
   </si>
   <si>
     <t xml:space="preserve">1.1944797039032</t>
@@ -3020,7 +3020,7 @@
     <t xml:space="preserve">1.23287332057953</t>
   </si>
   <si>
-    <t xml:space="preserve">1.23340654373169</t>
+    <t xml:space="preserve">1.23340666294098</t>
   </si>
   <si>
     <t xml:space="preserve">1.35338819026947</t>
@@ -3029,22 +3029,22 @@
     <t xml:space="preserve">1.41897749900818</t>
   </si>
   <si>
-    <t xml:space="preserve">1.39871430397034</t>
+    <t xml:space="preserve">1.39871442317963</t>
   </si>
   <si>
     <t xml:space="preserve">1.32832491397858</t>
   </si>
   <si>
-    <t xml:space="preserve">1.24353861808777</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.2152761220932</t>
+    <t xml:space="preserve">1.24353873729706</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.21527624130249</t>
   </si>
   <si>
     <t xml:space="preserve">1.22647476196289</t>
   </si>
   <si>
-    <t xml:space="preserve">1.30699515342712</t>
+    <t xml:space="preserve">1.30699527263641</t>
   </si>
   <si>
     <t xml:space="preserve">1.28086626529694</t>
@@ -3053,10 +3053,10 @@
     <t xml:space="preserve">1.24567115306854</t>
   </si>
   <si>
-    <t xml:space="preserve">1.25846970081329</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.20994341373444</t>
+    <t xml:space="preserve">1.25846982002258</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.20994353294373</t>
   </si>
   <si>
     <t xml:space="preserve">1.23980605602264</t>
@@ -3068,22 +3068,22 @@
     <t xml:space="preserve">1.18594706058502</t>
   </si>
   <si>
-    <t xml:space="preserve">1.15875136852264</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.17954862117767</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.15661871433258</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.16515064239502</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.15981793403625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.19501221179962</t>
+    <t xml:space="preserve">1.15875124931335</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.17954850196838</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.15661883354187</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.16515076160431</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.15981805324554</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.19501233100891</t>
   </si>
   <si>
     <t xml:space="preserve">1.18168115615845</t>
@@ -3095,16 +3095,16 @@
     <t xml:space="preserve">1.14542019367218</t>
   </si>
   <si>
-    <t xml:space="preserve">1.20301175117493</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.32885837554932</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.32992517948151</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.33685684204102</t>
+    <t xml:space="preserve">1.20301163196564</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.32885825634003</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.32992506027222</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.33685696125031</t>
   </si>
   <si>
     <t xml:space="preserve">1.35445415973663</t>
@@ -3113,16 +3113,16 @@
     <t xml:space="preserve">1.3261923789978</t>
   </si>
   <si>
-    <t xml:space="preserve">1.37205195426941</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.35925328731537</t>
+    <t xml:space="preserve">1.3720520734787</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.35925340652466</t>
   </si>
   <si>
     <t xml:space="preserve">1.31232786178589</t>
   </si>
   <si>
-    <t xml:space="preserve">1.29259741306305</t>
+    <t xml:space="preserve">1.29259729385376</t>
   </si>
   <si>
     <t xml:space="preserve">1.23873925209045</t>
@@ -3137,22 +3137,22 @@
     <t xml:space="preserve">1.18754708766937</t>
   </si>
   <si>
-    <t xml:space="preserve">1.13688838481903</t>
+    <t xml:space="preserve">1.13688826560974</t>
   </si>
   <si>
     <t xml:space="preserve">1.10755980014801</t>
   </si>
   <si>
-    <t xml:space="preserve">1.09316205978394</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.15928471088409</t>
+    <t xml:space="preserve">1.09316194057465</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.1592845916748</t>
   </si>
   <si>
     <t xml:space="preserve">1.24780452251434</t>
   </si>
   <si>
-    <t xml:space="preserve">1.26380169391632</t>
+    <t xml:space="preserve">1.26380157470703</t>
   </si>
   <si>
     <t xml:space="preserve">1.26486825942993</t>
@@ -3161,22 +3161,22 @@
     <t xml:space="preserve">1.23500669002533</t>
   </si>
   <si>
-    <t xml:space="preserve">1.238205909729</t>
+    <t xml:space="preserve">1.23820602893829</t>
   </si>
   <si>
     <t xml:space="preserve">1.24940454959869</t>
   </si>
   <si>
-    <t xml:space="preserve">1.2291407585144</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.21580970287323</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.25260376930237</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.25207054615021</t>
+    <t xml:space="preserve">1.22914087772369</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.21580958366394</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.25260388851166</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.25207042694092</t>
   </si>
   <si>
     <t xml:space="preserve">1.24300527572632</t>
@@ -3188,31 +3188,31 @@
     <t xml:space="preserve">1.22700726985931</t>
   </si>
   <si>
-    <t xml:space="preserve">1.19394636154175</t>
+    <t xml:space="preserve">1.19394648075104</t>
   </si>
   <si>
     <t xml:space="preserve">1.19074630737305</t>
   </si>
   <si>
-    <t xml:space="preserve">1.15288591384888</t>
+    <t xml:space="preserve">1.15288627147675</t>
   </si>
   <si>
     <t xml:space="preserve">1.16408383846283</t>
   </si>
   <si>
-    <t xml:space="preserve">1.15821862220764</t>
+    <t xml:space="preserve">1.15821874141693</t>
   </si>
   <si>
     <t xml:space="preserve">1.12675619125366</t>
   </si>
   <si>
-    <t xml:space="preserve">1.1422210931778</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.1715499162674</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.16834986209869</t>
+    <t xml:space="preserve">1.14222097396851</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.17155003547668</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.16834998130798</t>
   </si>
   <si>
     <t xml:space="preserve">1.16781663894653</t>
@@ -3224,7 +3224,7 @@
     <t xml:space="preserve">1.16195130348206</t>
   </si>
   <si>
-    <t xml:space="preserve">1.15181958675385</t>
+    <t xml:space="preserve">1.15181946754456</t>
   </si>
   <si>
     <t xml:space="preserve">1.10489320755005</t>
@@ -3233,13 +3233,13 @@
     <t xml:space="preserve">1.07503151893616</t>
   </si>
   <si>
-    <t xml:space="preserve">1.07716393470764</t>
+    <t xml:space="preserve">1.07716417312622</t>
   </si>
   <si>
     <t xml:space="preserve">1.04516899585724</t>
   </si>
   <si>
-    <t xml:space="preserve">1.0425032377243</t>
+    <t xml:space="preserve">1.04250299930573</t>
   </si>
   <si>
     <t xml:space="preserve">1.06969881057739</t>
@@ -3248,85 +3248,85 @@
     <t xml:space="preserve">1.03983724117279</t>
   </si>
   <si>
-    <t xml:space="preserve">1.06010019779205</t>
+    <t xml:space="preserve">1.06010031700134</t>
   </si>
   <si>
     <t xml:space="preserve">1.03877055644989</t>
   </si>
   <si>
-    <t xml:space="preserve">1.01050817966461</t>
+    <t xml:space="preserve">1.01050806045532</t>
   </si>
   <si>
     <t xml:space="preserve">0.935909509658813</t>
   </si>
   <si>
-    <t xml:space="preserve">0.974905788898468</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.9339399933815</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.94260585308075</t>
+    <t xml:space="preserve">0.974905729293823</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.933940052986145</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.942605912685394</t>
   </si>
   <si>
     <t xml:space="preserve">0.947332739830017</t>
   </si>
   <si>
-    <t xml:space="preserve">0.923304736614227</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.876036465167999</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.879581689834595</t>
+    <t xml:space="preserve">0.923304677009583</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.876036584377289</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.87958163022995</t>
   </si>
   <si>
     <t xml:space="preserve">0.874854803085327</t>
   </si>
   <si>
-    <t xml:space="preserve">0.945757031440735</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.933152198791504</t>
+    <t xml:space="preserve">0.945757150650024</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.933152258396149</t>
   </si>
   <si>
     <t xml:space="preserve">1.02414333820343</t>
   </si>
   <si>
-    <t xml:space="preserve">0.958755791187286</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.934727847576141</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.948120474815369</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.938666760921478</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.879975497722626</t>
+    <t xml:space="preserve">0.958755850791931</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.934727787971497</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.948120594024658</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.938666820526123</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.879975557327271</t>
   </si>
   <si>
     <t xml:space="preserve">0.816557466983795</t>
   </si>
   <si>
-    <t xml:space="preserve">0.806315958499908</t>
+    <t xml:space="preserve">0.806316018104553</t>
   </si>
   <si>
     <t xml:space="preserve">0.80119526386261</t>
   </si>
   <si>
-    <t xml:space="preserve">0.83113169670105</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.85240250825882</t>
+    <t xml:space="preserve">0.831131756305695</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.852402448654175</t>
   </si>
   <si>
     <t xml:space="preserve">0.872097551822662</t>
   </si>
   <si>
-    <t xml:space="preserve">0.853190183639526</t>
+    <t xml:space="preserve">0.853190243244171</t>
   </si>
   <si>
     <t xml:space="preserve">0.825617134571075</t>
@@ -3335,13 +3335,13 @@
     <t xml:space="preserve">0.948514401912689</t>
   </si>
   <si>
-    <t xml:space="preserve">0.940636336803436</t>
+    <t xml:space="preserve">0.940636277198792</t>
   </si>
   <si>
     <t xml:space="preserve">0.97608745098114</t>
   </si>
   <si>
-    <t xml:space="preserve">1.03950560092926</t>
+    <t xml:space="preserve">1.03950548171997</t>
   </si>
   <si>
     <t xml:space="preserve">1.05171656608582</t>
@@ -3353,10 +3353,10 @@
     <t xml:space="preserve">1.1230126619339</t>
   </si>
   <si>
-    <t xml:space="preserve">1.16949319839478</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.19430887699127</t>
+    <t xml:space="preserve">1.16949307918549</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.19430875778198</t>
   </si>
   <si>
     <t xml:space="preserve">1.19706606864929</t>
@@ -3365,13 +3365,13 @@
     <t xml:space="preserve">1.20100510120392</t>
   </si>
   <si>
-    <t xml:space="preserve">1.16988682746887</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.19036972522736</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.15413093566895</t>
+    <t xml:space="preserve">1.16988694667816</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.19036984443665</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.15413081645966</t>
   </si>
   <si>
     <t xml:space="preserve">1.17067468166351</t>
@@ -3383,13 +3383,13 @@
     <t xml:space="preserve">1.16870522499084</t>
   </si>
   <si>
-    <t xml:space="preserve">1.16003930568695</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.15373694896698</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.16161501407623</t>
+    <t xml:space="preserve">1.16003942489624</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.15373706817627</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.16161489486694</t>
   </si>
   <si>
     <t xml:space="preserve">1.19509649276733</t>
@@ -3404,7 +3404,7 @@
     <t xml:space="preserve">1.16397833824158</t>
   </si>
   <si>
-    <t xml:space="preserve">1.14822220802307</t>
+    <t xml:space="preserve">1.14822232723236</t>
   </si>
   <si>
     <t xml:space="preserve">1.15531265735626</t>
@@ -3413,49 +3413,49 @@
     <t xml:space="preserve">1.14388942718506</t>
   </si>
   <si>
-    <t xml:space="preserve">1.09780299663544</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.12261879444122</t>
+    <t xml:space="preserve">1.09780287742615</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.12261867523193</t>
   </si>
   <si>
     <t xml:space="preserve">1.16594791412354</t>
   </si>
   <si>
-    <t xml:space="preserve">1.18170392513275</t>
+    <t xml:space="preserve">1.18170380592346</t>
   </si>
   <si>
     <t xml:space="preserve">1.17343199253082</t>
   </si>
   <si>
-    <t xml:space="preserve">1.15176737308502</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.16122114658356</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.2230635881424</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.29869258403778</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.28411841392517</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.31050956249237</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.31247925758362</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.29632914066315</t>
+    <t xml:space="preserve">1.15176749229431</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.16122102737427</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.22306346893311</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.29869270324707</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.28411817550659</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.31050968170166</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.31247913837433</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.29632925987244</t>
   </si>
   <si>
     <t xml:space="preserve">1.27584648132324</t>
   </si>
   <si>
-    <t xml:space="preserve">1.26757442951202</t>
+    <t xml:space="preserve">1.26757454872131</t>
   </si>
   <si>
     <t xml:space="preserve">1.2955414056778</t>
@@ -3467,25 +3467,25 @@
     <t xml:space="preserve">1.29908657073975</t>
   </si>
   <si>
-    <t xml:space="preserve">1.27624022960663</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.24118316173553</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.20376241207123</t>
+    <t xml:space="preserve">1.27624034881592</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.24118292331696</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.20376229286194</t>
   </si>
   <si>
     <t xml:space="preserve">1.23724400997162</t>
   </si>
   <si>
-    <t xml:space="preserve">1.20061135292053</t>
+    <t xml:space="preserve">1.20061123371124</t>
   </si>
   <si>
     <t xml:space="preserve">1.22779035568237</t>
   </si>
   <si>
-    <t xml:space="preserve">1.20770156383514</t>
+    <t xml:space="preserve">1.20770144462585</t>
   </si>
   <si>
     <t xml:space="preserve">1.21636724472046</t>
@@ -3500,25 +3500,25 @@
     <t xml:space="preserve">1.50430917739868</t>
   </si>
   <si>
-    <t xml:space="preserve">1.47279691696167</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.49682509899139</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.4696456193924</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.46688854694366</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.48343241214752</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.46176791191101</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.43498253822327</t>
+    <t xml:space="preserve">1.47279715538025</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.49682486057281</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.46964585781097</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.46688842773438</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.48343229293823</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.46176779270172</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.43498241901398</t>
   </si>
   <si>
     <t xml:space="preserve">1.41016662120819</t>
@@ -3527,22 +3527,22 @@
     <t xml:space="preserve">1.46610069274902</t>
   </si>
   <si>
-    <t xml:space="preserve">1.44483006000519</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.44443619251251</t>
+    <t xml:space="preserve">1.4448299407959</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.44443607330322</t>
   </si>
   <si>
     <t xml:space="preserve">1.46767628192902</t>
   </si>
   <si>
-    <t xml:space="preserve">1.42946779727936</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.46728241443634</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.45192039012909</t>
+    <t xml:space="preserve">1.42946791648865</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.46728229522705</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.4519202709198</t>
   </si>
   <si>
     <t xml:space="preserve">1.4605860710144</t>
@@ -3554,16 +3554,16 @@
     <t xml:space="preserve">1.56300032138824</t>
   </si>
   <si>
-    <t xml:space="preserve">1.55630397796631</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.54330539703369</t>
+    <t xml:space="preserve">1.5563040971756</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.5433052778244</t>
   </si>
   <si>
     <t xml:space="preserve">1.55197131633759</t>
   </si>
   <si>
-    <t xml:space="preserve">1.53385186195374</t>
+    <t xml:space="preserve">1.53385174274445</t>
   </si>
   <si>
     <t xml:space="preserve">1.56772720813751</t>
@@ -3572,13 +3572,13 @@
     <t xml:space="preserve">1.61657106876373</t>
   </si>
   <si>
-    <t xml:space="preserve">1.60475397109985</t>
+    <t xml:space="preserve">1.60475385189056</t>
   </si>
   <si>
     <t xml:space="preserve">1.54094195365906</t>
   </si>
   <si>
-    <t xml:space="preserve">1.50233948230743</t>
+    <t xml:space="preserve">1.50233960151672</t>
   </si>
   <si>
     <t xml:space="preserve">1.50076401233673</t>
@@ -3587,10 +3587,10 @@
     <t xml:space="preserve">1.52164077758789</t>
   </si>
   <si>
-    <t xml:space="preserve">1.51021778583527</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.51100528240204</t>
+    <t xml:space="preserve">1.51021766662598</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.51100552082062</t>
   </si>
   <si>
     <t xml:space="preserve">1.49524939060211</t>
@@ -3599,58 +3599,58 @@
     <t xml:space="preserve">1.49643111228943</t>
   </si>
   <si>
-    <t xml:space="preserve">1.47831165790558</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.49800670146942</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.49603724479675</t>
+    <t xml:space="preserve">1.47831153869629</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.49800658226013</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.49603712558746</t>
   </si>
   <si>
     <t xml:space="preserve">1.48973476886749</t>
   </si>
   <si>
-    <t xml:space="preserve">1.46452510356903</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.47319102287292</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.49958229064941</t>
+    <t xml:space="preserve">1.46452498435974</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.47319090366364</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.4995824098587</t>
   </si>
   <si>
     <t xml:space="preserve">1.48264455795288</t>
   </si>
   <si>
-    <t xml:space="preserve">1.4913102388382</t>
+    <t xml:space="preserve">1.49131035804749</t>
   </si>
   <si>
     <t xml:space="preserve">1.49012875556946</t>
   </si>
   <si>
-    <t xml:space="preserve">1.53700304031372</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.45428347587585</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.42198371887207</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.42434704303741</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.43143725395203</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.47555446624756</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.4594042301178</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.49209833145142</t>
+    <t xml:space="preserve">1.53700280189514</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.45428359508514</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.42198383808136</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.4243471622467</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.43143749237061</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.47555434703827</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.45940434932709</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.49209821224213</t>
   </si>
   <si>
     <t xml:space="preserve">1.48303854465485</t>
@@ -3659,16 +3659,16 @@
     <t xml:space="preserve">1.47673606872559</t>
   </si>
   <si>
-    <t xml:space="preserve">1.49367392063141</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.52282249927521</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.51533842086792</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.57402968406677</t>
+    <t xml:space="preserve">1.49367380142212</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.52282238006592</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.51533830165863</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.57402980327606</t>
   </si>
   <si>
     <t xml:space="preserve">1.588210105896</t>
@@ -3689,22 +3689,22 @@
     <t xml:space="preserve">1.55748581886292</t>
   </si>
   <si>
-    <t xml:space="preserve">1.54291141033173</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.57127249240875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.67216503620148</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.70914554595947</t>
+    <t xml:space="preserve">1.54291152954102</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.57127237319946</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.67216491699219</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.70914566516876</t>
   </si>
   <si>
     <t xml:space="preserve">1.62714517116547</t>
   </si>
   <si>
-    <t xml:space="preserve">1.64804720878601</t>
+    <t xml:space="preserve">1.6480473279953</t>
   </si>
   <si>
     <t xml:space="preserve">1.63759613037109</t>
@@ -3716,28 +3716,28 @@
     <t xml:space="preserve">1.63518440723419</t>
   </si>
   <si>
-    <t xml:space="preserve">1.64322376251221</t>
+    <t xml:space="preserve">1.64322364330292</t>
   </si>
   <si>
     <t xml:space="preserve">1.63598847389221</t>
   </si>
   <si>
-    <t xml:space="preserve">1.62553739547729</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.64724326133728</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.63679242134094</t>
+    <t xml:space="preserve">1.62553751468658</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.64724349975586</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.63679230213165</t>
   </si>
   <si>
     <t xml:space="preserve">1.6504590511322</t>
   </si>
   <si>
-    <t xml:space="preserve">1.63840019702911</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.63277244567871</t>
+    <t xml:space="preserve">1.6384003162384</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.632772564888</t>
   </si>
   <si>
     <t xml:space="preserve">1.64081180095673</t>
@@ -3746,10 +3746,10 @@
     <t xml:space="preserve">1.61508643627167</t>
   </si>
   <si>
-    <t xml:space="preserve">1.59257638454437</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.58091950416565</t>
+    <t xml:space="preserve">1.59257650375366</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.58091962337494</t>
   </si>
   <si>
     <t xml:space="preserve">1.54514479637146</t>
@@ -3758,7 +3758,7 @@
     <t xml:space="preserve">1.5600174665451</t>
   </si>
   <si>
-    <t xml:space="preserve">1.53951728343964</t>
+    <t xml:space="preserve">1.53951716423035</t>
   </si>
   <si>
     <t xml:space="preserve">1.51901721954346</t>
@@ -3767,13 +3767,13 @@
     <t xml:space="preserve">1.53589975833893</t>
   </si>
   <si>
-    <t xml:space="preserve">1.52906632423401</t>
+    <t xml:space="preserve">1.52906620502472</t>
   </si>
   <si>
     <t xml:space="preserve">1.48042893409729</t>
   </si>
   <si>
-    <t xml:space="preserve">1.46836984157562</t>
+    <t xml:space="preserve">1.46836996078491</t>
   </si>
   <si>
     <t xml:space="preserve">1.47560524940491</t>
@@ -3782,7 +3782,7 @@
     <t xml:space="preserve">1.48444843292236</t>
   </si>
   <si>
-    <t xml:space="preserve">1.47399747371674</t>
+    <t xml:space="preserve">1.47399735450745</t>
   </si>
   <si>
     <t xml:space="preserve">1.48565435409546</t>
@@ -3791,46 +3791,46 @@
     <t xml:space="preserve">1.44626200199127</t>
   </si>
   <si>
-    <t xml:space="preserve">1.43339908123016</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.38677144050598</t>
+    <t xml:space="preserve">1.43339920043945</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.38677155971527</t>
   </si>
   <si>
     <t xml:space="preserve">1.41812467575073</t>
   </si>
   <si>
-    <t xml:space="preserve">1.424556016922</t>
+    <t xml:space="preserve">1.42455589771271</t>
   </si>
   <si>
     <t xml:space="preserve">1.37591862678528</t>
   </si>
   <si>
-    <t xml:space="preserve">1.36988914012909</t>
+    <t xml:space="preserve">1.3698890209198</t>
   </si>
   <si>
     <t xml:space="preserve">1.35863411426544</t>
   </si>
   <si>
-    <t xml:space="preserve">1.31482005119324</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.24809443950653</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.25814354419708</t>
+    <t xml:space="preserve">1.31482017040253</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.24809420108795</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.25814342498779</t>
   </si>
   <si>
     <t xml:space="preserve">1.27422201633453</t>
   </si>
   <si>
-    <t xml:space="preserve">1.29673171043396</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.29793787002563</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.31763398647308</t>
+    <t xml:space="preserve">1.29673182964325</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.29793775081635</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.31763386726379</t>
   </si>
   <si>
     <t xml:space="preserve">1.30235934257507</t>
@@ -3842,52 +3842,52 @@
     <t xml:space="preserve">1.30718290805817</t>
   </si>
   <si>
-    <t xml:space="preserve">1.32366323471069</t>
+    <t xml:space="preserve">1.32366347312927</t>
   </si>
   <si>
     <t xml:space="preserve">1.32326138019562</t>
   </si>
   <si>
-    <t xml:space="preserve">1.30517303943634</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.31361424922943</t>
+    <t xml:space="preserve">1.30517315864563</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.31361436843872</t>
   </si>
   <si>
     <t xml:space="preserve">1.45349729061127</t>
   </si>
   <si>
-    <t xml:space="preserve">1.45028150081635</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.4446542263031</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.48726212978363</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.476811170578</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.46917390823364</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.45108544826508</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.42535996437073</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.43500709533691</t>
+    <t xml:space="preserve">1.45028173923492</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.44465410709381</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.48726224899292</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.47681105136871</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.46917378902435</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.45108556747437</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.42535984516144</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.43500685691833</t>
   </si>
   <si>
     <t xml:space="preserve">1.41169321537018</t>
   </si>
   <si>
-    <t xml:space="preserve">1.40686976909637</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.43701696395874</t>
+    <t xml:space="preserve">1.40686964988708</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.43701684474945</t>
   </si>
   <si>
     <t xml:space="preserve">1.44224238395691</t>
@@ -3899,31 +3899,31 @@
     <t xml:space="preserve">1.4530953168869</t>
   </si>
   <si>
-    <t xml:space="preserve">1.47600734233856</t>
+    <t xml:space="preserve">1.47600710391998</t>
   </si>
   <si>
     <t xml:space="preserve">1.45872282981873</t>
   </si>
   <si>
-    <t xml:space="preserve">1.48123264312744</t>
+    <t xml:space="preserve">1.48123276233673</t>
   </si>
   <si>
     <t xml:space="preserve">1.49047791957855</t>
   </si>
   <si>
-    <t xml:space="preserve">1.48364460468292</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.50092887878418</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.46153664588928</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.45068359375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.46475219726562</t>
+    <t xml:space="preserve">1.48364448547363</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.50092899799347</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.46153652667999</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.45068347454071</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.46475231647491</t>
   </si>
   <si>
     <t xml:space="preserve">1.45631098747253</t>
@@ -3932,13 +3932,13 @@
     <t xml:space="preserve">1.45510506629944</t>
   </si>
   <si>
-    <t xml:space="preserve">1.43782079219818</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.36104583740234</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.37873232364655</t>
+    <t xml:space="preserve">1.43782067298889</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.36104571819305</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.37873220443726</t>
   </si>
   <si>
     <t xml:space="preserve">1.41892850399017</t>
@@ -3950,7 +3950,7 @@
     <t xml:space="preserve">1.47439932823181</t>
   </si>
   <si>
-    <t xml:space="preserve">1.53107607364655</t>
+    <t xml:space="preserve">1.53107619285583</t>
   </si>
   <si>
     <t xml:space="preserve">1.52343881130219</t>
@@ -3959,13 +3959,13 @@
     <t xml:space="preserve">1.5624293088913</t>
   </si>
   <si>
-    <t xml:space="preserve">1.55398797988892</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.59137070178986</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.57810580730438</t>
+    <t xml:space="preserve">1.55398786067963</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.59137058258057</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.57810568809509</t>
   </si>
   <si>
     <t xml:space="preserve">1.63357675075531</t>
@@ -3989,34 +3989,34 @@
     <t xml:space="preserve">1.65608644485474</t>
   </si>
   <si>
-    <t xml:space="preserve">1.65849840641022</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.67055726051331</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.64643943309784</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.64563536643982</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.64965510368347</t>
+    <t xml:space="preserve">1.65849828720093</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.6705573797226</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.64643955230713</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.64563548564911</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.64965522289276</t>
   </si>
   <si>
     <t xml:space="preserve">1.60945892333984</t>
   </si>
   <si>
-    <t xml:space="preserve">1.6279491186142</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.52303683757782</t>
+    <t xml:space="preserve">1.62794923782349</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.52303695678711</t>
   </si>
   <si>
     <t xml:space="preserve">1.51419365406036</t>
   </si>
   <si>
-    <t xml:space="preserve">1.54152715206146</t>
+    <t xml:space="preserve">1.54152727127075</t>
   </si>
   <si>
     <t xml:space="preserve">1.53911530971527</t>
@@ -4037,7 +4037,7 @@
     <t xml:space="preserve">1.54635059833527</t>
   </si>
   <si>
-    <t xml:space="preserve">1.53630173206329</t>
+    <t xml:space="preserve">1.53630149364471</t>
   </si>
   <si>
     <t xml:space="preserve">1.54836046695709</t>
@@ -4064,7 +4064,7 @@
     <t xml:space="preserve">1.36426162719727</t>
   </si>
   <si>
-    <t xml:space="preserve">1.35340869426727</t>
+    <t xml:space="preserve">1.35340857505798</t>
   </si>
   <si>
     <t xml:space="preserve">1.35220265388489</t>
@@ -4073,55 +4073,55 @@
     <t xml:space="preserve">1.39119303226471</t>
   </si>
   <si>
-    <t xml:space="preserve">1.37792837619781</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.365065574646</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.40807557106018</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.42013430595398</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.39561450481415</t>
+    <t xml:space="preserve">1.37792825698853</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.36506545543671</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.40807545185089</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.42013442516327</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.39561462402344</t>
   </si>
   <si>
     <t xml:space="preserve">1.40284991264343</t>
   </si>
   <si>
-    <t xml:space="preserve">1.39239907264709</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.4936934709549</t>
+    <t xml:space="preserve">1.39239895343781</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.49369359016418</t>
   </si>
   <si>
     <t xml:space="preserve">1.43018352985382</t>
   </si>
   <si>
-    <t xml:space="preserve">1.42777168750763</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.39280080795288</t>
+    <t xml:space="preserve">1.42777180671692</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.39280092716217</t>
   </si>
   <si>
     <t xml:space="preserve">1.42897760868073</t>
   </si>
   <si>
-    <t xml:space="preserve">1.41651678085327</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.43983066082001</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.45751678943634</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.46877193450928</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.46555602550507</t>
+    <t xml:space="preserve">1.41651666164398</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.43983054161072</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.45751690864563</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.46877205371857</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.46555614471436</t>
   </si>
   <si>
     <t xml:space="preserve">1.51539945602417</t>
@@ -4133,22 +4133,22 @@
     <t xml:space="preserve">1.54032123088837</t>
   </si>
   <si>
-    <t xml:space="preserve">1.55157613754272</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.54996836185455</t>
+    <t xml:space="preserve">1.55157625675201</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.54996824264526</t>
   </si>
   <si>
     <t xml:space="preserve">1.57730174064636</t>
   </si>
   <si>
-    <t xml:space="preserve">1.57167434692383</t>
+    <t xml:space="preserve">1.57167446613312</t>
   </si>
   <si>
     <t xml:space="preserve">1.55639970302582</t>
   </si>
   <si>
-    <t xml:space="preserve">1.54192900657654</t>
+    <t xml:space="preserve">1.54192912578583</t>
   </si>
   <si>
     <t xml:space="preserve">1.51298773288727</t>
@@ -4157,28 +4157,28 @@
     <t xml:space="preserve">1.44264435768127</t>
   </si>
   <si>
-    <t xml:space="preserve">1.43741869926453</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.50293862819672</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.53831148147583</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.47962486743927</t>
+    <t xml:space="preserve">1.43741881847382</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.5029388666153</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.53831136226654</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.47962498664856</t>
   </si>
   <si>
     <t xml:space="preserve">1.49087989330292</t>
   </si>
   <si>
-    <t xml:space="preserve">1.55881154537201</t>
+    <t xml:space="preserve">1.55881142616272</t>
   </si>
   <si>
     <t xml:space="preserve">1.58936071395874</t>
   </si>
   <si>
-    <t xml:space="preserve">1.57328224182129</t>
+    <t xml:space="preserve">1.573282122612</t>
   </si>
   <si>
     <t xml:space="preserve">1.63116490840912</t>
@@ -4187,19 +4187,19 @@
     <t xml:space="preserve">1.62875306606293</t>
   </si>
   <si>
-    <t xml:space="preserve">1.65367472171783</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.59016454219818</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.73567509651184</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.7147730588913</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.6231255531311</t>
+    <t xml:space="preserve">1.65367460250854</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.59016466140747</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.73567497730255</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.71477293968201</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.62312567234039</t>
   </si>
   <si>
     <t xml:space="preserve">1.57569396495819</t>
@@ -4208,34 +4208,34 @@
     <t xml:space="preserve">1.45590901374817</t>
   </si>
   <si>
-    <t xml:space="preserve">1.48243856430054</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.33572208881378</t>
+    <t xml:space="preserve">1.48243868350983</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.33572220802307</t>
   </si>
   <si>
     <t xml:space="preserve">1.33049666881561</t>
   </si>
   <si>
-    <t xml:space="preserve">1.26095712184906</t>
+    <t xml:space="preserve">1.26095724105835</t>
   </si>
   <si>
     <t xml:space="preserve">1.12750554084778</t>
   </si>
   <si>
-    <t xml:space="preserve">1.06922090053558</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.12670147418976</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.2392510175705</t>
+    <t xml:space="preserve">1.06922101974487</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.12670171260834</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.23925113677979</t>
   </si>
   <si>
     <t xml:space="preserve">1.14639782905579</t>
   </si>
   <si>
-    <t xml:space="preserve">1.13996636867523</t>
+    <t xml:space="preserve">1.13996624946594</t>
   </si>
   <si>
     <t xml:space="preserve">1.18659389019012</t>
@@ -4250,7 +4250,7 @@
     <t xml:space="preserve">1.27020227909088</t>
   </si>
   <si>
-    <t xml:space="preserve">1.26216304302216</t>
+    <t xml:space="preserve">1.26216316223145</t>
   </si>
   <si>
     <t xml:space="preserve">1.27864348888397</t>
@@ -4262,7 +4262,7 @@
     <t xml:space="preserve">1.24688839912415</t>
   </si>
   <si>
-    <t xml:space="preserve">1.25532972812653</t>
+    <t xml:space="preserve">1.25532960891724</t>
   </si>
   <si>
     <t xml:space="preserve">1.27140820026398</t>
@@ -4274,16 +4274,16 @@
     <t xml:space="preserve">1.31964373588562</t>
   </si>
   <si>
-    <t xml:space="preserve">1.27783966064453</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.29190826416016</t>
+    <t xml:space="preserve">1.27783954143524</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.29190838336945</t>
   </si>
   <si>
     <t xml:space="preserve">1.23643743991852</t>
   </si>
   <si>
-    <t xml:space="preserve">1.23844730854034</t>
+    <t xml:space="preserve">1.23844718933105</t>
   </si>
   <si>
     <t xml:space="preserve">1.28748667240143</t>
@@ -4295,46 +4295,46 @@
     <t xml:space="preserve">1.24447667598724</t>
   </si>
   <si>
-    <t xml:space="preserve">1.24729037284851</t>
+    <t xml:space="preserve">1.24729025363922</t>
   </si>
   <si>
     <t xml:space="preserve">1.26015329360962</t>
   </si>
   <si>
-    <t xml:space="preserve">1.26578056812286</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.3103985786438</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.31924176216125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.30034935474396</t>
+    <t xml:space="preserve">1.26578068733215</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.31039845943451</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.31924164295197</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.30034947395325</t>
   </si>
   <si>
     <t xml:space="preserve">1.2866827249527</t>
   </si>
   <si>
-    <t xml:space="preserve">1.27181017398834</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.28105521202087</t>
+    <t xml:space="preserve">1.27181029319763</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.28105533123016</t>
   </si>
   <si>
     <t xml:space="preserve">1.27261412143707</t>
   </si>
   <si>
-    <t xml:space="preserve">1.2903003692627</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.2818591594696</t>
+    <t xml:space="preserve">1.29030048847198</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.28185927867889</t>
   </si>
   <si>
     <t xml:space="preserve">1.25050616264343</t>
   </si>
   <si>
-    <t xml:space="preserve">1.23121178150177</t>
+    <t xml:space="preserve">1.23121190071106</t>
   </si>
   <si>
     <t xml:space="preserve">1.23281967639923</t>
@@ -4346,7 +4346,7 @@
     <t xml:space="preserve">1.36667335033417</t>
   </si>
   <si>
-    <t xml:space="preserve">1.40003621578217</t>
+    <t xml:space="preserve">1.40003633499146</t>
   </si>
   <si>
     <t xml:space="preserve">1.40043818950653</t>
@@ -4361,13 +4361,13 @@
     <t xml:space="preserve">1.41249704360962</t>
   </si>
   <si>
-    <t xml:space="preserve">1.42134034633636</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.40405595302582</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.49854755401611</t>
+    <t xml:space="preserve">1.42134022712708</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.40405583381653</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.4985476732254</t>
   </si>
   <si>
     <t xml:space="preserve">1.51436567306519</t>
@@ -4382,10 +4382,10 @@
     <t xml:space="preserve">1.56931233406067</t>
   </si>
   <si>
-    <t xml:space="preserve">1.56889629364014</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.59553694725037</t>
+    <t xml:space="preserve">1.56889617443085</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.59553706645966</t>
   </si>
   <si>
     <t xml:space="preserve">1.59179055690765</t>
@@ -4403,7 +4403,7 @@
     <t xml:space="preserve">1.56847989559174</t>
   </si>
   <si>
-    <t xml:space="preserve">1.61426889896393</t>
+    <t xml:space="preserve">1.61426877975464</t>
   </si>
   <si>
     <t xml:space="preserve">1.62425911426544</t>
@@ -4421,7 +4421,7 @@
     <t xml:space="preserve">1.43194556236267</t>
   </si>
   <si>
-    <t xml:space="preserve">1.37117111682892</t>
+    <t xml:space="preserve">1.37117099761963</t>
   </si>
   <si>
     <t xml:space="preserve">1.3969794511795</t>
@@ -4439,16 +4439,16 @@
     <t xml:space="preserve">1.35785067081451</t>
   </si>
   <si>
-    <t xml:space="preserve">1.40197455883026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.38074505329132</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.37866377830505</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.35826706886292</t>
+    <t xml:space="preserve">1.40197467803955</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.38074517250061</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.37866389751434</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.35826694965363</t>
   </si>
   <si>
     <t xml:space="preserve">1.3049852848053</t>
@@ -4460,16 +4460,16 @@
     <t xml:space="preserve">1.26377522945404</t>
   </si>
   <si>
-    <t xml:space="preserve">1.19967067241669</t>
+    <t xml:space="preserve">1.1996705532074</t>
   </si>
   <si>
     <t xml:space="preserve">1.18093883991241</t>
   </si>
   <si>
-    <t xml:space="preserve">1.24212956428528</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.25711488723755</t>
+    <t xml:space="preserve">1.24212944507599</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.25711500644684</t>
   </si>
   <si>
     <t xml:space="preserve">1.2000869512558</t>
@@ -4481,25 +4481,25 @@
     <t xml:space="preserve">1.14014506340027</t>
   </si>
   <si>
-    <t xml:space="preserve">1.06979644298553</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.07645678520203</t>
+    <t xml:space="preserve">1.06979656219482</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.07645666599274</t>
   </si>
   <si>
     <t xml:space="preserve">1.09060966968536</t>
   </si>
   <si>
-    <t xml:space="preserve">1.16470468044281</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.13140344619751</t>
+    <t xml:space="preserve">1.16470456123352</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.1314035654068</t>
   </si>
   <si>
     <t xml:space="preserve">1.09602105617523</t>
   </si>
   <si>
-    <t xml:space="preserve">1.07853817939758</t>
+    <t xml:space="preserve">1.07853806018829</t>
   </si>
   <si>
     <t xml:space="preserve">1.10642778873444</t>
@@ -4508,13 +4508,13 @@
     <t xml:space="preserve">1.0756242275238</t>
   </si>
   <si>
-    <t xml:space="preserve">1.09643745422363</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.09893488883972</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.12391090393066</t>
+    <t xml:space="preserve">1.09643733501434</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.09893500804901</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.12391078472137</t>
   </si>
   <si>
     <t xml:space="preserve">1.13598239421844</t>
@@ -4523,7 +4523,7 @@
     <t xml:space="preserve">1.15471422672272</t>
   </si>
   <si>
-    <t xml:space="preserve">1.20091938972473</t>
+    <t xml:space="preserve">1.20091950893402</t>
   </si>
   <si>
     <t xml:space="preserve">1.19301044940948</t>
@@ -4532,10 +4532,10 @@
     <t xml:space="preserve">1.30873167514801</t>
   </si>
   <si>
-    <t xml:space="preserve">1.34036767482758</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.3511905670166</t>
+    <t xml:space="preserve">1.34036779403687</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.35119044780731</t>
   </si>
   <si>
     <t xml:space="preserve">1.38199388980865</t>
@@ -4556,10 +4556,10 @@
     <t xml:space="preserve">1.275430560112</t>
   </si>
   <si>
-    <t xml:space="preserve">1.29332995414734</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.29291355609894</t>
+    <t xml:space="preserve">1.29332983493805</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.29291367530823</t>
   </si>
   <si>
     <t xml:space="preserve">1.27334916591644</t>
@@ -4601,25 +4601,25 @@
     <t xml:space="preserve">1.35285544395447</t>
   </si>
   <si>
-    <t xml:space="preserve">1.33911895751953</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.38948678970337</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.39489805698395</t>
+    <t xml:space="preserve">1.33911883831024</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.38948667049408</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.39489817619324</t>
   </si>
   <si>
     <t xml:space="preserve">1.40363967418671</t>
   </si>
   <si>
-    <t xml:space="preserve">1.41071605682373</t>
+    <t xml:space="preserve">1.41071617603302</t>
   </si>
   <si>
     <t xml:space="preserve">1.38657295703888</t>
   </si>
   <si>
-    <t xml:space="preserve">1.39781188964844</t>
+    <t xml:space="preserve">1.39781200885773</t>
   </si>
   <si>
     <t xml:space="preserve">1.44443345069885</t>
@@ -4628,10 +4628,10 @@
     <t xml:space="preserve">1.3869891166687</t>
   </si>
   <si>
-    <t xml:space="preserve">1.38532412052155</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.35493695735931</t>
+    <t xml:space="preserve">1.38532400131226</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.35493683815002</t>
   </si>
   <si>
     <t xml:space="preserve">1.33329117298126</t>
@@ -4652,13 +4652,13 @@
     <t xml:space="preserve">1.37241995334625</t>
   </si>
   <si>
-    <t xml:space="preserve">1.33037734031677</t>
+    <t xml:space="preserve">1.33037745952606</t>
   </si>
   <si>
     <t xml:space="preserve">1.34786033630371</t>
   </si>
   <si>
-    <t xml:space="preserve">1.33162593841553</t>
+    <t xml:space="preserve">1.33162605762482</t>
   </si>
   <si>
     <t xml:space="preserve">1.32121956348419</t>
@@ -4682,22 +4682,22 @@
     <t xml:space="preserve">1.43069684505463</t>
   </si>
   <si>
-    <t xml:space="preserve">1.44984483718872</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.49105501174927</t>
+    <t xml:space="preserve">1.44984495639801</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.49105489253998</t>
   </si>
   <si>
     <t xml:space="preserve">1.4818971157074</t>
   </si>
   <si>
-    <t xml:space="preserve">1.48397850990295</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.52602100372314</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.53601133823395</t>
+    <t xml:space="preserve">1.48397839069366</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.52602112293243</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.53601145744324</t>
   </si>
   <si>
     <t xml:space="preserve">1.55890572071075</t>
@@ -4709,16 +4709,16 @@
     <t xml:space="preserve">1.6034460067749</t>
   </si>
   <si>
-    <t xml:space="preserve">1.60469472408295</t>
+    <t xml:space="preserve">1.60469484329224</t>
   </si>
   <si>
     <t xml:space="preserve">1.67587578296661</t>
   </si>
   <si>
-    <t xml:space="preserve">1.70667922496796</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.57555639743805</t>
+    <t xml:space="preserve">1.70667934417725</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.57555651664734</t>
   </si>
   <si>
     <t xml:space="preserve">1.53184878826141</t>
@@ -4730,7 +4730,7 @@
     <t xml:space="preserve">1.54225528240204</t>
   </si>
   <si>
-    <t xml:space="preserve">1.56181979179382</t>
+    <t xml:space="preserve">1.56181967258453</t>
   </si>
   <si>
     <t xml:space="preserve">1.56723117828369</t>
@@ -4745,10 +4745,10 @@
     <t xml:space="preserve">1.59761834144592</t>
   </si>
   <si>
-    <t xml:space="preserve">1.61551761627197</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.62883806228638</t>
+    <t xml:space="preserve">1.61551773548126</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.62883818149567</t>
   </si>
   <si>
     <t xml:space="preserve">1.63966083526611</t>
@@ -4757,7 +4757,7 @@
     <t xml:space="preserve">1.62467551231384</t>
   </si>
   <si>
-    <t xml:space="preserve">1.63175201416016</t>
+    <t xml:space="preserve">1.63175189495087</t>
   </si>
   <si>
     <t xml:space="preserve">1.64174222946167</t>
@@ -4766,16 +4766,16 @@
     <t xml:space="preserve">1.62259411811829</t>
   </si>
   <si>
-    <t xml:space="preserve">1.61468505859375</t>
+    <t xml:space="preserve">1.61468517780304</t>
   </si>
   <si>
     <t xml:space="preserve">1.60594367980957</t>
   </si>
   <si>
-    <t xml:space="preserve">1.61302006244659</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.61759901046753</t>
+    <t xml:space="preserve">1.61302018165588</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.61759889125824</t>
   </si>
   <si>
     <t xml:space="preserve">1.62550795078278</t>
@@ -4784,7 +4784,7 @@
     <t xml:space="preserve">1.62509179115295</t>
   </si>
   <si>
-    <t xml:space="preserve">1.63508212566376</t>
+    <t xml:space="preserve">1.63508200645447</t>
   </si>
   <si>
     <t xml:space="preserve">1.6230103969574</t>
@@ -4796,7 +4796,7 @@
     <t xml:space="preserve">1.56514978408813</t>
   </si>
   <si>
-    <t xml:space="preserve">1.55307805538177</t>
+    <t xml:space="preserve">1.55307817459106</t>
   </si>
   <si>
     <t xml:space="preserve">1.62009656429291</t>
@@ -4805,10 +4805,10 @@
     <t xml:space="preserve">1.61884772777557</t>
   </si>
   <si>
-    <t xml:space="preserve">1.61093878746033</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.59720194339752</t>
+    <t xml:space="preserve">1.61093866825104</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.59720206260681</t>
   </si>
   <si>
     <t xml:space="preserve">1.63133561611176</t>
@@ -4823,76 +4823,76 @@
     <t xml:space="preserve">1.69002878665924</t>
   </si>
   <si>
-    <t xml:space="preserve">1.7341525554657</t>
+    <t xml:space="preserve">1.73415267467499</t>
   </si>
   <si>
     <t xml:space="preserve">1.74247789382935</t>
   </si>
   <si>
-    <t xml:space="preserve">1.75663089752197</t>
+    <t xml:space="preserve">1.75663077831268</t>
   </si>
   <si>
     <t xml:space="preserve">1.75579833984375</t>
   </si>
   <si>
-    <t xml:space="preserve">1.76578879356384</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.82323288917542</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.8432137966156</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.81490790843964</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.87484979629517</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.87318468093872</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.90898334980011</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.92063856124878</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.94811189174652</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.95227456092834</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.99306857585907</t>
+    <t xml:space="preserve">1.76578867435455</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.82323312759399</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.84321367740631</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.81490778923035</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.87484967708588</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.87318456172943</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.90898323059082</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.92063868045807</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.94811177253723</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.95227468013763</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.99306833744049</t>
   </si>
   <si>
     <t xml:space="preserve">2.02387189865112</t>
   </si>
   <si>
-    <t xml:space="preserve">2.0230393409729</t>
+    <t xml:space="preserve">2.02303957939148</t>
   </si>
   <si>
     <t xml:space="preserve">2.09546899795532</t>
   </si>
   <si>
-    <t xml:space="preserve">2.16456890106201</t>
+    <t xml:space="preserve">2.16456866264343</t>
   </si>
   <si>
     <t xml:space="preserve">2.10462713241577</t>
   </si>
   <si>
-    <t xml:space="preserve">2.11461734771729</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.14958333969116</t>
+    <t xml:space="preserve">2.11461710929871</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.14958357810974</t>
   </si>
   <si>
     <t xml:space="preserve">2.11961245536804</t>
   </si>
   <si>
-    <t xml:space="preserve">2.14042568206787</t>
+    <t xml:space="preserve">2.14042544364929</t>
   </si>
   <si>
     <t xml:space="preserve">2.12544012069702</t>
@@ -4907,7 +4907,7 @@
     <t xml:space="preserve">2.15874099731445</t>
   </si>
   <si>
-    <t xml:space="preserve">2.2261757850647</t>
+    <t xml:space="preserve">2.22617602348328</t>
   </si>
   <si>
     <t xml:space="preserve">2.32441377639771</t>
@@ -4916,25 +4916,25 @@
     <t xml:space="preserve">2.28695034980774</t>
   </si>
   <si>
-    <t xml:space="preserve">2.2752947807312</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.17539167404175</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.19786977767944</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.14708590507507</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.20869278907776</t>
+    <t xml:space="preserve">2.27529501914978</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.17539143562317</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.19787001609802</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.14708566665649</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.20869302749634</t>
   </si>
   <si>
     <t xml:space="preserve">2.23699879646301</t>
   </si>
   <si>
-    <t xml:space="preserve">2.21701812744141</t>
+    <t xml:space="preserve">2.21701788902283</t>
   </si>
   <si>
     <t xml:space="preserve">2.23033833503723</t>
@@ -4943,7 +4943,7 @@
     <t xml:space="preserve">2.24865412712097</t>
   </si>
   <si>
-    <t xml:space="preserve">2.29277777671814</t>
+    <t xml:space="preserve">2.29277801513672</t>
   </si>
   <si>
     <t xml:space="preserve">2.29527544975281</t>
@@ -4955,61 +4955,61 @@
     <t xml:space="preserve">2.34522700309753</t>
   </si>
   <si>
-    <t xml:space="preserve">2.24032855033875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.02720189094543</t>
+    <t xml:space="preserve">2.24032878875732</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.02720212936401</t>
   </si>
   <si>
     <t xml:space="preserve">2.06050300598145</t>
   </si>
   <si>
-    <t xml:space="preserve">1.91148090362549</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.91564357280731</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.86236178874969</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.88900279998779</t>
+    <t xml:space="preserve">1.91148066520691</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.9156436920166</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.86236166954041</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.8890026807785</t>
   </si>
   <si>
     <t xml:space="preserve">1.98141312599182</t>
   </si>
   <si>
-    <t xml:space="preserve">1.95310711860657</t>
+    <t xml:space="preserve">1.95310699939728</t>
   </si>
   <si>
     <t xml:space="preserve">1.91730856895447</t>
   </si>
   <si>
-    <t xml:space="preserve">1.83988356590271</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.86152923107147</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.86735701560974</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.91814088821411</t>
+    <t xml:space="preserve">1.839883685112</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.86152935028076</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.86735689640045</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.91814076900482</t>
   </si>
   <si>
     <t xml:space="preserve">1.90648555755615</t>
   </si>
   <si>
-    <t xml:space="preserve">1.89233267307281</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.93895411491394</t>
+    <t xml:space="preserve">1.8923327922821</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.93895423412323</t>
   </si>
   <si>
     <t xml:space="preserve">1.93812167644501</t>
   </si>
   <si>
-    <t xml:space="preserve">1.96809256076813</t>
+    <t xml:space="preserve">1.96809267997742</t>
   </si>
   <si>
     <t xml:space="preserve">1.96476233005524</t>
@@ -5018,7 +5018,7 @@
     <t xml:space="preserve">2.00305867195129</t>
   </si>
   <si>
-    <t xml:space="preserve">1.99639856815338</t>
+    <t xml:space="preserve">1.99639844894409</t>
   </si>
   <si>
     <t xml:space="preserve">2.08964157104492</t>
@@ -5027,16 +5027,16 @@
     <t xml:space="preserve">2.09963202476501</t>
   </si>
   <si>
-    <t xml:space="preserve">2.18538212776184</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.22284579277039</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.25281667709351</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.28528499603271</t>
+    <t xml:space="preserve">2.18538188934326</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.22284603118896</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.25281691551208</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.28528523445129</t>
   </si>
   <si>
     <t xml:space="preserve">2.27612733840942</t>
@@ -5045,10 +5045,10 @@
     <t xml:space="preserve">2.12294244766235</t>
   </si>
   <si>
-    <t xml:space="preserve">2.20785999298096</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.1187801361084</t>
+    <t xml:space="preserve">2.20786023139954</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.11877989768982</t>
   </si>
   <si>
     <t xml:space="preserve">2.08547902107239</t>
@@ -5063,10 +5063,10 @@
     <t xml:space="preserve">2.17039680480957</t>
   </si>
   <si>
-    <t xml:space="preserve">2.28362035751343</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.27279734611511</t>
+    <t xml:space="preserve">2.28362011909485</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.27279758453369</t>
   </si>
   <si>
     <t xml:space="preserve">2.22201299667358</t>
@@ -5081,10 +5081,10 @@
     <t xml:space="preserve">2.25697922706604</t>
   </si>
   <si>
-    <t xml:space="preserve">2.24282622337341</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.24782180786133</t>
+    <t xml:space="preserve">2.24282646179199</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.24782156944275</t>
   </si>
   <si>
     <t xml:space="preserve">2.27570152282715</t>
@@ -6795,6 +6795,9 @@
   </si>
   <si>
     <t xml:space="preserve">9.24600028991699</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.55000019073486</t>
   </si>
 </sst>
 </file>
@@ -20827,7 +20830,7 @@
         <v>3.13125896453857</v>
       </c>
       <c r="G527" t="s">
-        <v>463</v>
+        <v>323</v>
       </c>
       <c r="H527" t="s">
         <v>9</v>
@@ -20879,7 +20882,7 @@
         <v>3.25851202011108</v>
       </c>
       <c r="G529" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
       <c r="H529" t="s">
         <v>9</v>
@@ -20905,7 +20908,7 @@
         <v>3.25580501556396</v>
       </c>
       <c r="G530" t="s">
-        <v>465</v>
+        <v>464</v>
       </c>
       <c r="H530" t="s">
         <v>9</v>
@@ -20931,7 +20934,7 @@
         <v>3.27949595451355</v>
       </c>
       <c r="G531" t="s">
-        <v>466</v>
+        <v>465</v>
       </c>
       <c r="H531" t="s">
         <v>9</v>
@@ -20957,7 +20960,7 @@
         <v>3.15359592437744</v>
       </c>
       <c r="G532" t="s">
-        <v>467</v>
+        <v>466</v>
       </c>
       <c r="H532" t="s">
         <v>9</v>
@@ -20983,7 +20986,7 @@
         <v>3.17931699752808</v>
       </c>
       <c r="G533" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
       <c r="H533" t="s">
         <v>9</v>
@@ -21009,7 +21012,7 @@
         <v>3.15494894981384</v>
       </c>
       <c r="G534" t="s">
-        <v>469</v>
+        <v>468</v>
       </c>
       <c r="H534" t="s">
         <v>9</v>
@@ -21035,7 +21038,7 @@
         <v>3.15494894981384</v>
       </c>
       <c r="G535" t="s">
-        <v>469</v>
+        <v>468</v>
       </c>
       <c r="H535" t="s">
         <v>9</v>
@@ -21061,7 +21064,7 @@
         <v>3.06898498535156</v>
       </c>
       <c r="G536" t="s">
-        <v>470</v>
+        <v>469</v>
       </c>
       <c r="H536" t="s">
         <v>9</v>
@@ -21087,7 +21090,7 @@
         <v>3.08049201965332</v>
       </c>
       <c r="G537" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="H537" t="s">
         <v>9</v>
@@ -21113,7 +21116,7 @@
         <v>3.18811702728271</v>
       </c>
       <c r="G538" t="s">
-        <v>472</v>
+        <v>471</v>
       </c>
       <c r="H538" t="s">
         <v>9</v>
@@ -21191,7 +21194,7 @@
         <v>3.11907505989075</v>
       </c>
       <c r="G541" t="s">
-        <v>473</v>
+        <v>472</v>
       </c>
       <c r="H541" t="s">
         <v>9</v>
@@ -21217,7 +21220,7 @@
         <v>3.0777850151062</v>
       </c>
       <c r="G542" t="s">
-        <v>474</v>
+        <v>473</v>
       </c>
       <c r="H542" t="s">
         <v>9</v>
@@ -21243,7 +21246,7 @@
         <v>3.23752903938293</v>
       </c>
       <c r="G543" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="H543" t="s">
         <v>9</v>
@@ -21269,7 +21272,7 @@
         <v>3.24362111091614</v>
       </c>
       <c r="G544" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="H544" t="s">
         <v>9</v>
@@ -21321,7 +21324,7 @@
         <v>3.23008298873901</v>
       </c>
       <c r="G546" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="H546" t="s">
         <v>9</v>
@@ -21373,7 +21376,7 @@
         <v>3.23549795150757</v>
       </c>
       <c r="G548" t="s">
-        <v>478</v>
+        <v>477</v>
       </c>
       <c r="H548" t="s">
         <v>9</v>
@@ -21399,7 +21402,7 @@
         <v>3.1711950302124</v>
       </c>
       <c r="G549" t="s">
-        <v>479</v>
+        <v>478</v>
       </c>
       <c r="H549" t="s">
         <v>9</v>
@@ -21425,7 +21428,7 @@
         <v>3.29168009757996</v>
       </c>
       <c r="G550" t="s">
-        <v>480</v>
+        <v>479</v>
       </c>
       <c r="H550" t="s">
         <v>9</v>
@@ -21451,7 +21454,7 @@
         <v>3.29235696792603</v>
       </c>
       <c r="G551" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
       <c r="H551" t="s">
         <v>9</v>
@@ -21477,7 +21480,7 @@
         <v>3.29844903945923</v>
       </c>
       <c r="G552" t="s">
-        <v>482</v>
+        <v>481</v>
       </c>
       <c r="H552" t="s">
         <v>9</v>
@@ -21503,7 +21506,7 @@
         <v>3.29506397247314</v>
       </c>
       <c r="G553" t="s">
-        <v>483</v>
+        <v>482</v>
       </c>
       <c r="H553" t="s">
         <v>9</v>
@@ -21529,7 +21532,7 @@
         <v>3.33432292938232</v>
       </c>
       <c r="G554" t="s">
-        <v>484</v>
+        <v>483</v>
       </c>
       <c r="H554" t="s">
         <v>9</v>
@@ -21555,7 +21558,7 @@
         <v>3.3065710067749</v>
       </c>
       <c r="G555" t="s">
-        <v>485</v>
+        <v>484</v>
       </c>
       <c r="H555" t="s">
         <v>9</v>
@@ -21581,7 +21584,7 @@
         <v>3.05477094650269</v>
       </c>
       <c r="G556" t="s">
-        <v>486</v>
+        <v>485</v>
       </c>
       <c r="H556" t="s">
         <v>9</v>
@@ -21633,7 +21636,7 @@
         <v>3.17999410629272</v>
       </c>
       <c r="G558" t="s">
-        <v>487</v>
+        <v>486</v>
       </c>
       <c r="H558" t="s">
         <v>9</v>
@@ -21659,7 +21662,7 @@
         <v>3.22331500053406</v>
       </c>
       <c r="G559" t="s">
-        <v>488</v>
+        <v>487</v>
       </c>
       <c r="H559" t="s">
         <v>9</v>
@@ -21685,7 +21688,7 @@
         <v>3.15359592437744</v>
       </c>
       <c r="G560" t="s">
-        <v>467</v>
+        <v>466</v>
       </c>
       <c r="H560" t="s">
         <v>9</v>
@@ -21711,7 +21714,7 @@
         <v>3.12245893478394</v>
       </c>
       <c r="G561" t="s">
-        <v>489</v>
+        <v>488</v>
       </c>
       <c r="H561" t="s">
         <v>9</v>
@@ -21737,7 +21740,7 @@
         <v>3.18067097663879</v>
       </c>
       <c r="G562" t="s">
-        <v>490</v>
+        <v>489</v>
       </c>
       <c r="H562" t="s">
         <v>9</v>
@@ -21763,7 +21766,7 @@
         <v>3.10892105102539</v>
       </c>
       <c r="G563" t="s">
-        <v>491</v>
+        <v>490</v>
       </c>
       <c r="H563" t="s">
         <v>9</v>
@@ -21789,7 +21792,7 @@
         <v>3.11501288414001</v>
       </c>
       <c r="G564" t="s">
-        <v>492</v>
+        <v>491</v>
       </c>
       <c r="H564" t="s">
         <v>9</v>
@@ -21841,7 +21844,7 @@
         <v>3.15156507492065</v>
       </c>
       <c r="G566" t="s">
-        <v>493</v>
+        <v>492</v>
       </c>
       <c r="H566" t="s">
         <v>9</v>
@@ -21867,7 +21870,7 @@
         <v>3.16239500045776</v>
       </c>
       <c r="G567" t="s">
-        <v>494</v>
+        <v>493</v>
       </c>
       <c r="H567" t="s">
         <v>9</v>
@@ -21893,7 +21896,7 @@
         <v>3.14073491096497</v>
       </c>
       <c r="G568" t="s">
-        <v>495</v>
+        <v>494</v>
       </c>
       <c r="H568" t="s">
         <v>9</v>
@@ -21919,7 +21922,7 @@
         <v>3.07981491088867</v>
       </c>
       <c r="G569" t="s">
-        <v>496</v>
+        <v>495</v>
       </c>
       <c r="H569" t="s">
         <v>9</v>
@@ -21945,7 +21948,7 @@
         <v>3.08861494064331</v>
       </c>
       <c r="G570" t="s">
-        <v>497</v>
+        <v>496</v>
       </c>
       <c r="H570" t="s">
         <v>9</v>
@@ -21971,7 +21974,7 @@
         <v>3.06153988838196</v>
       </c>
       <c r="G571" t="s">
-        <v>498</v>
+        <v>497</v>
       </c>
       <c r="H571" t="s">
         <v>9</v>
@@ -21997,7 +22000,7 @@
         <v>3.08252310752869</v>
       </c>
       <c r="G572" t="s">
-        <v>499</v>
+        <v>498</v>
       </c>
       <c r="H572" t="s">
         <v>9</v>
@@ -22075,7 +22078,7 @@
         <v>3.05680108070374</v>
       </c>
       <c r="G575" t="s">
-        <v>500</v>
+        <v>499</v>
       </c>
       <c r="H575" t="s">
         <v>9</v>
@@ -22101,7 +22104,7 @@
         <v>3.05950903892517</v>
       </c>
       <c r="G576" t="s">
-        <v>501</v>
+        <v>500</v>
       </c>
       <c r="H576" t="s">
         <v>9</v>
@@ -22127,7 +22130,7 @@
         <v>3.17796301841736</v>
       </c>
       <c r="G577" t="s">
-        <v>502</v>
+        <v>501</v>
       </c>
       <c r="H577" t="s">
         <v>9</v>
@@ -22179,7 +22182,7 @@
         <v>3.17999410629272</v>
       </c>
       <c r="G579" t="s">
-        <v>487</v>
+        <v>486</v>
       </c>
       <c r="H579" t="s">
         <v>9</v>
@@ -22205,7 +22208,7 @@
         <v>3.18947005271912</v>
       </c>
       <c r="G580" t="s">
-        <v>503</v>
+        <v>502</v>
       </c>
       <c r="H580" t="s">
         <v>9</v>
@@ -22283,7 +22286,7 @@
         <v>3.20165395736694</v>
       </c>
       <c r="G583" t="s">
-        <v>504</v>
+        <v>503</v>
       </c>
       <c r="H583" t="s">
         <v>9</v>
@@ -22309,7 +22312,7 @@
         <v>3.23414492607117</v>
       </c>
       <c r="G584" t="s">
-        <v>505</v>
+        <v>504</v>
       </c>
       <c r="H584" t="s">
         <v>9</v>
@@ -22335,7 +22338,7 @@
         <v>3.30318689346313</v>
       </c>
       <c r="G585" t="s">
-        <v>506</v>
+        <v>505</v>
       </c>
       <c r="H585" t="s">
         <v>9</v>
@@ -22361,7 +22364,7 @@
         <v>3.26392793655396</v>
       </c>
       <c r="G586" t="s">
-        <v>507</v>
+        <v>506</v>
       </c>
       <c r="H586" t="s">
         <v>9</v>
@@ -22387,7 +22390,7 @@
         <v>3.27272701263428</v>
       </c>
       <c r="G587" t="s">
-        <v>508</v>
+        <v>507</v>
       </c>
       <c r="H587" t="s">
         <v>9</v>
@@ -22413,7 +22416,7 @@
         <v>3.30792498588562</v>
       </c>
       <c r="G588" t="s">
-        <v>509</v>
+        <v>508</v>
       </c>
       <c r="H588" t="s">
         <v>9</v>
@@ -22439,7 +22442,7 @@
         <v>3.30792498588562</v>
       </c>
       <c r="G589" t="s">
-        <v>509</v>
+        <v>508</v>
       </c>
       <c r="H589" t="s">
         <v>9</v>
@@ -22465,7 +22468,7 @@
         <v>3.24768209457397</v>
       </c>
       <c r="G590" t="s">
-        <v>510</v>
+        <v>509</v>
       </c>
       <c r="H590" t="s">
         <v>9</v>
@@ -22491,7 +22494,7 @@
         <v>3.2070689201355</v>
       </c>
       <c r="G591" t="s">
-        <v>511</v>
+        <v>510</v>
       </c>
       <c r="H591" t="s">
         <v>9</v>
@@ -22517,7 +22520,7 @@
         <v>3.22737598419189</v>
       </c>
       <c r="G592" t="s">
-        <v>512</v>
+        <v>511</v>
       </c>
       <c r="H592" t="s">
         <v>9</v>
@@ -22543,7 +22546,7 @@
         <v>3.2118079662323</v>
       </c>
       <c r="G593" t="s">
-        <v>513</v>
+        <v>512</v>
       </c>
       <c r="H593" t="s">
         <v>9</v>
@@ -22569,7 +22572,7 @@
         <v>3.24362111091614</v>
       </c>
       <c r="G594" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="H594" t="s">
         <v>9</v>
@@ -22595,7 +22598,7 @@
         <v>3.22805309295654</v>
       </c>
       <c r="G595" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="H595" t="s">
         <v>9</v>
@@ -22647,7 +22650,7 @@
         <v>3.20368504524231</v>
       </c>
       <c r="G597" t="s">
-        <v>515</v>
+        <v>514</v>
       </c>
       <c r="H597" t="s">
         <v>9</v>
@@ -22673,7 +22676,7 @@
         <v>3.19353199005127</v>
       </c>
       <c r="G598" t="s">
-        <v>516</v>
+        <v>515</v>
       </c>
       <c r="H598" t="s">
         <v>9</v>
@@ -22725,7 +22728,7 @@
         <v>3.31943202018738</v>
       </c>
       <c r="G600" t="s">
-        <v>517</v>
+        <v>516</v>
       </c>
       <c r="H600" t="s">
         <v>9</v>
@@ -22751,7 +22754,7 @@
         <v>3.33161592483521</v>
       </c>
       <c r="G601" t="s">
-        <v>518</v>
+        <v>517</v>
       </c>
       <c r="H601" t="s">
         <v>9</v>
@@ -22777,7 +22780,7 @@
         <v>3.39659690856934</v>
       </c>
       <c r="G602" t="s">
-        <v>519</v>
+        <v>518</v>
       </c>
       <c r="H602" t="s">
         <v>9</v>
@@ -22803,7 +22806,7 @@
         <v>3.44533205032349</v>
       </c>
       <c r="G603" t="s">
-        <v>520</v>
+        <v>519</v>
       </c>
       <c r="H603" t="s">
         <v>9</v>
@@ -22829,7 +22832,7 @@
         <v>3.48459100723267</v>
       </c>
       <c r="G604" t="s">
-        <v>521</v>
+        <v>520</v>
       </c>
       <c r="H604" t="s">
         <v>9</v>
@@ -22855,7 +22858,7 @@
         <v>3.38238191604614</v>
       </c>
       <c r="G605" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="H605" t="s">
         <v>9</v>
@@ -22881,7 +22884,7 @@
         <v>3.38305902481079</v>
       </c>
       <c r="G606" t="s">
-        <v>523</v>
+        <v>522</v>
       </c>
       <c r="H606" t="s">
         <v>9</v>
@@ -22907,7 +22910,7 @@
         <v>3.15833401679993</v>
       </c>
       <c r="G607" t="s">
-        <v>524</v>
+        <v>523</v>
       </c>
       <c r="H607" t="s">
         <v>9</v>
@@ -22933,7 +22936,7 @@
         <v>3.11230611801147</v>
       </c>
       <c r="G608" t="s">
-        <v>525</v>
+        <v>524</v>
       </c>
       <c r="H608" t="s">
         <v>9</v>
@@ -22959,7 +22962,7 @@
         <v>3.16239500045776</v>
       </c>
       <c r="G609" t="s">
-        <v>526</v>
+        <v>525</v>
       </c>
       <c r="H609" t="s">
         <v>9</v>
@@ -22985,7 +22988,7 @@
         <v>3.19691610336304</v>
       </c>
       <c r="G610" t="s">
-        <v>527</v>
+        <v>526</v>
       </c>
       <c r="H610" t="s">
         <v>9</v>
@@ -23011,7 +23014,7 @@
         <v>3.15765690803528</v>
       </c>
       <c r="G611" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="H611" t="s">
         <v>9</v>
@@ -23037,7 +23040,7 @@
         <v>3.09402990341187</v>
       </c>
       <c r="G612" t="s">
-        <v>529</v>
+        <v>528</v>
       </c>
       <c r="H612" t="s">
         <v>9</v>
@@ -23063,7 +23066,7 @@
         <v>2.91330194473267</v>
       </c>
       <c r="G613" t="s">
-        <v>530</v>
+        <v>529</v>
       </c>
       <c r="H613" t="s">
         <v>9</v>
@@ -23089,7 +23092,7 @@
         <v>2.76641893386841</v>
       </c>
       <c r="G614" t="s">
-        <v>531</v>
+        <v>530</v>
       </c>
       <c r="H614" t="s">
         <v>9</v>
@@ -23115,7 +23118,7 @@
         <v>2.77657198905945</v>
       </c>
       <c r="G615" t="s">
-        <v>532</v>
+        <v>531</v>
       </c>
       <c r="H615" t="s">
         <v>9</v>
@@ -23141,7 +23144,7 @@
         <v>2.7772490978241</v>
       </c>
       <c r="G616" t="s">
-        <v>533</v>
+        <v>532</v>
       </c>
       <c r="H616" t="s">
         <v>9</v>
@@ -23167,7 +23170,7 @@
         <v>2.99588203430176</v>
       </c>
       <c r="G617" t="s">
-        <v>534</v>
+        <v>533</v>
       </c>
       <c r="H617" t="s">
         <v>9</v>
@@ -23193,7 +23196,7 @@
         <v>2.90788698196411</v>
       </c>
       <c r="G618" t="s">
-        <v>535</v>
+        <v>534</v>
       </c>
       <c r="H618" t="s">
         <v>9</v>
@@ -23219,7 +23222,7 @@
         <v>2.80906200408936</v>
       </c>
       <c r="G619" t="s">
-        <v>536</v>
+        <v>535</v>
       </c>
       <c r="H619" t="s">
         <v>9</v>
@@ -23245,7 +23248,7 @@
         <v>2.80770897865295</v>
       </c>
       <c r="G620" t="s">
-        <v>537</v>
+        <v>536</v>
       </c>
       <c r="H620" t="s">
         <v>9</v>
@@ -23271,7 +23274,7 @@
         <v>2.86185908317566</v>
       </c>
       <c r="G621" t="s">
-        <v>538</v>
+        <v>537</v>
       </c>
       <c r="H621" t="s">
         <v>9</v>
@@ -23297,7 +23300,7 @@
         <v>2.78469491004944</v>
       </c>
       <c r="G622" t="s">
-        <v>539</v>
+        <v>538</v>
       </c>
       <c r="H622" t="s">
         <v>9</v>
@@ -23323,7 +23326,7 @@
         <v>2.90585708618164</v>
       </c>
       <c r="G623" t="s">
-        <v>540</v>
+        <v>539</v>
       </c>
       <c r="H623" t="s">
         <v>9</v>
@@ -23349,7 +23352,7 @@
         <v>2.94037795066833</v>
       </c>
       <c r="G624" t="s">
-        <v>541</v>
+        <v>540</v>
       </c>
       <c r="H624" t="s">
         <v>9</v>
@@ -23375,7 +23378,7 @@
         <v>2.98775911331177</v>
       </c>
       <c r="G625" t="s">
-        <v>542</v>
+        <v>541</v>
       </c>
       <c r="H625" t="s">
         <v>9</v>
@@ -23401,7 +23404,7 @@
         <v>3.02431106567383</v>
       </c>
       <c r="G626" t="s">
-        <v>543</v>
+        <v>542</v>
       </c>
       <c r="H626" t="s">
         <v>9</v>
@@ -23427,7 +23430,7 @@
         <v>2.94511604309082</v>
       </c>
       <c r="G627" t="s">
-        <v>544</v>
+        <v>543</v>
       </c>
       <c r="H627" t="s">
         <v>9</v>
@@ -23453,7 +23456,7 @@
         <v>2.93090105056763</v>
       </c>
       <c r="G628" t="s">
-        <v>545</v>
+        <v>544</v>
       </c>
       <c r="H628" t="s">
         <v>9</v>
@@ -23479,7 +23482,7 @@
         <v>3.03040289878845</v>
       </c>
       <c r="G629" t="s">
-        <v>546</v>
+        <v>545</v>
       </c>
       <c r="H629" t="s">
         <v>9</v>
@@ -23505,7 +23508,7 @@
         <v>3.10689091682434</v>
       </c>
       <c r="G630" t="s">
-        <v>547</v>
+        <v>546</v>
       </c>
       <c r="H630" t="s">
         <v>9</v>
@@ -23531,7 +23534,7 @@
         <v>3.01551198959351</v>
       </c>
       <c r="G631" t="s">
-        <v>548</v>
+        <v>547</v>
       </c>
       <c r="H631" t="s">
         <v>9</v>
@@ -23557,7 +23560,7 @@
         <v>3.23752903938293</v>
       </c>
       <c r="G632" t="s">
-        <v>549</v>
+        <v>548</v>
       </c>
       <c r="H632" t="s">
         <v>9</v>
@@ -23583,7 +23586,7 @@
         <v>3.1711950302124</v>
       </c>
       <c r="G633" t="s">
-        <v>550</v>
+        <v>549</v>
       </c>
       <c r="H633" t="s">
         <v>9</v>
@@ -23609,7 +23612,7 @@
         <v>3.18879389762878</v>
       </c>
       <c r="G634" t="s">
-        <v>551</v>
+        <v>550</v>
       </c>
       <c r="H634" t="s">
         <v>9</v>
@@ -23635,7 +23638,7 @@
         <v>3.14344191551208</v>
       </c>
       <c r="G635" t="s">
-        <v>552</v>
+        <v>551</v>
       </c>
       <c r="H635" t="s">
         <v>9</v>
@@ -23661,7 +23664,7 @@
         <v>3.17187190055847</v>
       </c>
       <c r="G636" t="s">
-        <v>553</v>
+        <v>552</v>
       </c>
       <c r="H636" t="s">
         <v>9</v>
@@ -23687,7 +23690,7 @@
         <v>3.18608593940735</v>
       </c>
       <c r="G637" t="s">
-        <v>554</v>
+        <v>553</v>
       </c>
       <c r="H637" t="s">
         <v>9</v>
@@ -23713,7 +23716,7 @@
         <v>3.14344191551208</v>
       </c>
       <c r="G638" t="s">
-        <v>552</v>
+        <v>551</v>
       </c>
       <c r="H638" t="s">
         <v>9</v>
@@ -23739,7 +23742,7 @@
         <v>3.17390203475952</v>
       </c>
       <c r="G639" t="s">
-        <v>555</v>
+        <v>554</v>
       </c>
       <c r="H639" t="s">
         <v>9</v>
@@ -23765,7 +23768,7 @@
         <v>3.17728710174561</v>
       </c>
       <c r="G640" t="s">
-        <v>556</v>
+        <v>555</v>
       </c>
       <c r="H640" t="s">
         <v>9</v>
@@ -23791,7 +23794,7 @@
         <v>3.1651029586792</v>
       </c>
       <c r="G641" t="s">
-        <v>557</v>
+        <v>556</v>
       </c>
       <c r="H641" t="s">
         <v>9</v>
@@ -23817,7 +23820,7 @@
         <v>3.22737598419189</v>
       </c>
       <c r="G642" t="s">
-        <v>558</v>
+        <v>557</v>
       </c>
       <c r="H642" t="s">
         <v>9</v>
@@ -23843,7 +23846,7 @@
         <v>3.238205909729</v>
       </c>
       <c r="G643" t="s">
-        <v>559</v>
+        <v>558</v>
       </c>
       <c r="H643" t="s">
         <v>9</v>
@@ -23869,7 +23872,7 @@
         <v>3.17525601387024</v>
       </c>
       <c r="G644" t="s">
-        <v>560</v>
+        <v>559</v>
       </c>
       <c r="H644" t="s">
         <v>9</v>
@@ -23895,7 +23898,7 @@
         <v>3.12245893478394</v>
       </c>
       <c r="G645" t="s">
-        <v>561</v>
+        <v>560</v>
       </c>
       <c r="H645" t="s">
         <v>9</v>
@@ -23921,7 +23924,7 @@
         <v>3.16239500045776</v>
       </c>
       <c r="G646" t="s">
-        <v>526</v>
+        <v>525</v>
       </c>
       <c r="H646" t="s">
         <v>9</v>
@@ -23947,7 +23950,7 @@
         <v>3.14411902427673</v>
       </c>
       <c r="G647" t="s">
-        <v>562</v>
+        <v>561</v>
       </c>
       <c r="H647" t="s">
         <v>9</v>
@@ -23973,7 +23976,7 @@
         <v>3.1651029586792</v>
       </c>
       <c r="G648" t="s">
-        <v>557</v>
+        <v>556</v>
       </c>
       <c r="H648" t="s">
         <v>9</v>
@@ -23999,7 +24002,7 @@
         <v>3.18743991851807</v>
       </c>
       <c r="G649" t="s">
-        <v>563</v>
+        <v>562</v>
       </c>
       <c r="H649" t="s">
         <v>9</v>
@@ -24025,7 +24028,7 @@
         <v>3.16239500045776</v>
       </c>
       <c r="G650" t="s">
-        <v>526</v>
+        <v>525</v>
       </c>
       <c r="H650" t="s">
         <v>9</v>
@@ -24051,7 +24054,7 @@
         <v>3.13125896453857</v>
       </c>
       <c r="G651" t="s">
-        <v>564</v>
+        <v>563</v>
       </c>
       <c r="H651" t="s">
         <v>9</v>
@@ -24077,7 +24080,7 @@
         <v>3.09402990341187</v>
       </c>
       <c r="G652" t="s">
-        <v>529</v>
+        <v>528</v>
       </c>
       <c r="H652" t="s">
         <v>9</v>
@@ -24103,7 +24106,7 @@
         <v>3.07304692268372</v>
       </c>
       <c r="G653" t="s">
-        <v>565</v>
+        <v>564</v>
       </c>
       <c r="H653" t="s">
         <v>9</v>
@@ -24129,7 +24132,7 @@
         <v>3.13531994819641</v>
       </c>
       <c r="G654" t="s">
-        <v>566</v>
+        <v>565</v>
       </c>
       <c r="H654" t="s">
         <v>9</v>
@@ -24155,7 +24158,7 @@
         <v>3.13193488121033</v>
       </c>
       <c r="G655" t="s">
-        <v>567</v>
+        <v>566</v>
       </c>
       <c r="H655" t="s">
         <v>9</v>
@@ -24181,7 +24184,7 @@
         <v>3.17796301841736</v>
       </c>
       <c r="G656" t="s">
-        <v>568</v>
+        <v>567</v>
       </c>
       <c r="H656" t="s">
         <v>9</v>
@@ -24207,7 +24210,7 @@
         <v>3.22263789176941</v>
       </c>
       <c r="G657" t="s">
-        <v>569</v>
+        <v>568</v>
       </c>
       <c r="H657" t="s">
         <v>9</v>
@@ -24233,7 +24236,7 @@
         <v>3.19082403182983</v>
       </c>
       <c r="G658" t="s">
-        <v>570</v>
+        <v>569</v>
       </c>
       <c r="H658" t="s">
         <v>9</v>
@@ -24259,7 +24262,7 @@
         <v>3.23617506027222</v>
       </c>
       <c r="G659" t="s">
-        <v>571</v>
+        <v>570</v>
       </c>
       <c r="H659" t="s">
         <v>9</v>
@@ -24285,7 +24288,7 @@
         <v>3.22128391265869</v>
       </c>
       <c r="G660" t="s">
-        <v>572</v>
+        <v>571</v>
       </c>
       <c r="H660" t="s">
         <v>9</v>
@@ -24311,7 +24314,7 @@
         <v>3.10621404647827</v>
       </c>
       <c r="G661" t="s">
-        <v>573</v>
+        <v>572</v>
       </c>
       <c r="H661" t="s">
         <v>9</v>
@@ -24337,7 +24340,7 @@
         <v>3.0980908870697</v>
       </c>
       <c r="G662" t="s">
-        <v>574</v>
+        <v>573</v>
       </c>
       <c r="H662" t="s">
         <v>9</v>
@@ -24363,7 +24366,7 @@
         <v>3.10012197494507</v>
       </c>
       <c r="G663" t="s">
-        <v>575</v>
+        <v>574</v>
       </c>
       <c r="H663" t="s">
         <v>9</v>
@@ -24389,7 +24392,7 @@
         <v>3.12719702720642</v>
       </c>
       <c r="G664" t="s">
-        <v>576</v>
+        <v>575</v>
       </c>
       <c r="H664" t="s">
         <v>9</v>
@@ -24415,7 +24418,7 @@
         <v>2.94240808486938</v>
       </c>
       <c r="G665" t="s">
-        <v>577</v>
+        <v>576</v>
       </c>
       <c r="H665" t="s">
         <v>9</v>
@@ -24441,7 +24444,7 @@
         <v>2.90924096107483</v>
       </c>
       <c r="G666" t="s">
-        <v>578</v>
+        <v>577</v>
       </c>
       <c r="H666" t="s">
         <v>9</v>
@@ -24467,7 +24470,7 @@
         <v>2.86862802505493</v>
       </c>
       <c r="G667" t="s">
-        <v>579</v>
+        <v>578</v>
       </c>
       <c r="H667" t="s">
         <v>9</v>
@@ -24493,7 +24496,7 @@
         <v>2.7975549697876</v>
       </c>
       <c r="G668" t="s">
-        <v>580</v>
+        <v>579</v>
       </c>
       <c r="H668" t="s">
         <v>9</v>
@@ -24519,7 +24522,7 @@
         <v>2.77115702629089</v>
       </c>
       <c r="G669" t="s">
-        <v>581</v>
+        <v>580</v>
       </c>
       <c r="H669" t="s">
         <v>9</v>
@@ -24545,7 +24548,7 @@
         <v>2.76777291297913</v>
       </c>
       <c r="G670" t="s">
-        <v>582</v>
+        <v>581</v>
       </c>
       <c r="H670" t="s">
         <v>9</v>
@@ -24571,7 +24574,7 @@
         <v>2.70753002166748</v>
       </c>
       <c r="G671" t="s">
-        <v>583</v>
+        <v>582</v>
       </c>
       <c r="H671" t="s">
         <v>9</v>
@@ -24597,7 +24600,7 @@
         <v>2.70820689201355</v>
       </c>
       <c r="G672" t="s">
-        <v>584</v>
+        <v>583</v>
       </c>
       <c r="H672" t="s">
         <v>9</v>
@@ -24623,7 +24626,7 @@
         <v>2.76844906806946</v>
       </c>
       <c r="G673" t="s">
-        <v>585</v>
+        <v>584</v>
       </c>
       <c r="H673" t="s">
         <v>9</v>
@@ -24649,7 +24652,7 @@
         <v>2.76709604263306</v>
       </c>
       <c r="G674" t="s">
-        <v>586</v>
+        <v>585</v>
       </c>
       <c r="H674" t="s">
         <v>9</v>
@@ -24675,7 +24678,7 @@
         <v>2.74543499946594</v>
       </c>
       <c r="G675" t="s">
-        <v>587</v>
+        <v>586</v>
       </c>
       <c r="H675" t="s">
         <v>9</v>
@@ -24701,7 +24704,7 @@
         <v>2.73866701126099</v>
       </c>
       <c r="G676" t="s">
-        <v>588</v>
+        <v>587</v>
       </c>
       <c r="H676" t="s">
         <v>9</v>
@@ -24727,7 +24730,7 @@
         <v>2.72783708572388</v>
       </c>
       <c r="G677" t="s">
-        <v>589</v>
+        <v>588</v>
       </c>
       <c r="H677" t="s">
         <v>9</v>
@@ -24753,7 +24756,7 @@
         <v>2.6838390827179</v>
       </c>
       <c r="G678" t="s">
-        <v>590</v>
+        <v>589</v>
       </c>
       <c r="H678" t="s">
         <v>9</v>
@@ -24779,7 +24782,7 @@
         <v>2.70076107978821</v>
       </c>
       <c r="G679" t="s">
-        <v>591</v>
+        <v>590</v>
       </c>
       <c r="H679" t="s">
         <v>9</v>
@@ -24805,7 +24808,7 @@
         <v>2.59922909736633</v>
       </c>
       <c r="G680" t="s">
-        <v>592</v>
+        <v>591</v>
       </c>
       <c r="H680" t="s">
         <v>9</v>
@@ -24831,7 +24834,7 @@
         <v>2.57147693634033</v>
       </c>
       <c r="G681" t="s">
-        <v>593</v>
+        <v>592</v>
       </c>
       <c r="H681" t="s">
         <v>9</v>
@@ -24857,7 +24860,7 @@
         <v>2.58366107940674</v>
       </c>
       <c r="G682" t="s">
-        <v>594</v>
+        <v>593</v>
       </c>
       <c r="H682" t="s">
         <v>9</v>
@@ -24883,7 +24886,7 @@
         <v>2.67842388153076</v>
       </c>
       <c r="G683" t="s">
-        <v>595</v>
+        <v>594</v>
       </c>
       <c r="H683" t="s">
         <v>9</v>
@@ -24909,7 +24912,7 @@
         <v>2.79281711578369</v>
       </c>
       <c r="G684" t="s">
-        <v>596</v>
+        <v>595</v>
       </c>
       <c r="H684" t="s">
         <v>9</v>
@@ -24935,7 +24938,7 @@
         <v>2.79823207855225</v>
       </c>
       <c r="G685" t="s">
-        <v>597</v>
+        <v>596</v>
       </c>
       <c r="H685" t="s">
         <v>9</v>
@@ -24961,7 +24964,7 @@
         <v>2.77657198905945</v>
       </c>
       <c r="G686" t="s">
-        <v>532</v>
+        <v>531</v>
       </c>
       <c r="H686" t="s">
         <v>9</v>
@@ -24987,7 +24990,7 @@
         <v>2.87268900871277</v>
       </c>
       <c r="G687" t="s">
-        <v>598</v>
+        <v>597</v>
       </c>
       <c r="H687" t="s">
         <v>9</v>
@@ -25013,7 +25016,7 @@
         <v>2.85847496986389</v>
       </c>
       <c r="G688" t="s">
-        <v>599</v>
+        <v>598</v>
       </c>
       <c r="H688" t="s">
         <v>9</v>
@@ -25039,7 +25042,7 @@
         <v>2.86118197441101</v>
       </c>
       <c r="G689" t="s">
-        <v>600</v>
+        <v>599</v>
       </c>
       <c r="H689" t="s">
         <v>9</v>
@@ -25065,7 +25068,7 @@
         <v>2.85170602798462</v>
       </c>
       <c r="G690" t="s">
-        <v>601</v>
+        <v>600</v>
       </c>
       <c r="H690" t="s">
         <v>9</v>
@@ -25091,7 +25094,7 @@
         <v>2.87268900871277</v>
       </c>
       <c r="G691" t="s">
-        <v>598</v>
+        <v>597</v>
       </c>
       <c r="H691" t="s">
         <v>9</v>
@@ -25117,7 +25120,7 @@
         <v>2.90788698196411</v>
       </c>
       <c r="G692" t="s">
-        <v>535</v>
+        <v>534</v>
       </c>
       <c r="H692" t="s">
         <v>9</v>
@@ -25143,7 +25146,7 @@
         <v>2.91736388206482</v>
       </c>
       <c r="G693" t="s">
-        <v>602</v>
+        <v>601</v>
       </c>
       <c r="H693" t="s">
         <v>9</v>
@@ -25169,7 +25172,7 @@
         <v>2.96136093139648</v>
       </c>
       <c r="G694" t="s">
-        <v>603</v>
+        <v>602</v>
       </c>
       <c r="H694" t="s">
         <v>9</v>
@@ -25195,7 +25198,7 @@
         <v>2.93360900878906</v>
       </c>
       <c r="G695" t="s">
-        <v>604</v>
+        <v>603</v>
       </c>
       <c r="H695" t="s">
         <v>9</v>
@@ -25221,7 +25224,7 @@
         <v>2.87742805480957</v>
       </c>
       <c r="G696" t="s">
-        <v>605</v>
+        <v>604</v>
       </c>
       <c r="H696" t="s">
         <v>9</v>
@@ -25247,7 +25250,7 @@
         <v>2.91059494018555</v>
       </c>
       <c r="G697" t="s">
-        <v>606</v>
+        <v>605</v>
       </c>
       <c r="H697" t="s">
         <v>9</v>
@@ -25273,7 +25276,7 @@
         <v>2.94647002220154</v>
       </c>
       <c r="G698" t="s">
-        <v>607</v>
+        <v>606</v>
       </c>
       <c r="H698" t="s">
         <v>9</v>
@@ -25299,7 +25302,7 @@
         <v>2.97625207901001</v>
       </c>
       <c r="G699" t="s">
-        <v>608</v>
+        <v>607</v>
       </c>
       <c r="H699" t="s">
         <v>9</v>
@@ -25325,7 +25328,7 @@
         <v>2.94511604309082</v>
       </c>
       <c r="G700" t="s">
-        <v>544</v>
+        <v>543</v>
       </c>
       <c r="H700" t="s">
         <v>9</v>
@@ -25351,7 +25354,7 @@
         <v>2.69940710067749</v>
       </c>
       <c r="G701" t="s">
-        <v>609</v>
+        <v>608</v>
       </c>
       <c r="H701" t="s">
         <v>9</v>
@@ -25377,7 +25380,7 @@
         <v>2.59313702583313</v>
       </c>
       <c r="G702" t="s">
-        <v>610</v>
+        <v>609</v>
       </c>
       <c r="H702" t="s">
         <v>9</v>
@@ -25403,7 +25406,7 @@
         <v>2.54778599739075</v>
       </c>
       <c r="G703" t="s">
-        <v>611</v>
+        <v>610</v>
       </c>
       <c r="H703" t="s">
         <v>9</v>
@@ -25429,7 +25432,7 @@
         <v>2.51461791992188</v>
       </c>
       <c r="G704" t="s">
-        <v>612</v>
+        <v>611</v>
       </c>
       <c r="H704" t="s">
         <v>9</v>
@@ -25455,7 +25458,7 @@
         <v>2.53018689155579</v>
       </c>
       <c r="G705" t="s">
-        <v>613</v>
+        <v>612</v>
       </c>
       <c r="H705" t="s">
         <v>9</v>
@@ -25481,7 +25484,7 @@
         <v>2.48415899276733</v>
       </c>
       <c r="G706" t="s">
-        <v>614</v>
+        <v>613</v>
       </c>
       <c r="H706" t="s">
         <v>9</v>
@@ -25507,7 +25510,7 @@
         <v>2.44286894798279</v>
       </c>
       <c r="G707" t="s">
-        <v>615</v>
+        <v>614</v>
       </c>
       <c r="H707" t="s">
         <v>9</v>
@@ -25533,7 +25536,7 @@
         <v>2.3941330909729</v>
       </c>
       <c r="G708" t="s">
-        <v>616</v>
+        <v>615</v>
       </c>
       <c r="H708" t="s">
         <v>9</v>
@@ -25559,7 +25562,7 @@
         <v>2.44625306129456</v>
       </c>
       <c r="G709" t="s">
-        <v>617</v>
+        <v>616</v>
       </c>
       <c r="H709" t="s">
         <v>9</v>
@@ -25585,7 +25588,7 @@
         <v>2.40022492408752</v>
       </c>
       <c r="G710" t="s">
-        <v>618</v>
+        <v>617</v>
       </c>
       <c r="H710" t="s">
         <v>9</v>
@@ -25611,7 +25614,7 @@
         <v>2.41850090026855</v>
       </c>
       <c r="G711" t="s">
-        <v>619</v>
+        <v>618</v>
       </c>
       <c r="H711" t="s">
         <v>9</v>
@@ -25637,7 +25640,7 @@
         <v>2.43542289733887</v>
       </c>
       <c r="G712" t="s">
-        <v>620</v>
+        <v>619</v>
       </c>
       <c r="H712" t="s">
         <v>9</v>
@@ -25663,7 +25666,7 @@
         <v>2.41443991661072</v>
       </c>
       <c r="G713" t="s">
-        <v>621</v>
+        <v>620</v>
       </c>
       <c r="H713" t="s">
         <v>9</v>
@@ -25689,7 +25692,7 @@
         <v>2.41782402992249</v>
       </c>
       <c r="G714" t="s">
-        <v>622</v>
+        <v>621</v>
       </c>
       <c r="H714" t="s">
         <v>9</v>
@@ -25715,7 +25718,7 @@
         <v>2.36570405960083</v>
       </c>
       <c r="G715" t="s">
-        <v>623</v>
+        <v>622</v>
       </c>
       <c r="H715" t="s">
         <v>9</v>
@@ -25741,7 +25744,7 @@
         <v>2.37450408935547</v>
       </c>
       <c r="G716" t="s">
-        <v>624</v>
+        <v>623</v>
       </c>
       <c r="H716" t="s">
         <v>9</v>
@@ -25767,7 +25770,7 @@
         <v>2.28786301612854</v>
       </c>
       <c r="G717" t="s">
-        <v>625</v>
+        <v>624</v>
       </c>
       <c r="H717" t="s">
         <v>9</v>
@@ -25793,7 +25796,7 @@
         <v>2.238450050354</v>
       </c>
       <c r="G718" t="s">
-        <v>626</v>
+        <v>625</v>
       </c>
       <c r="H718" t="s">
         <v>9</v>
@@ -25819,7 +25822,7 @@
         <v>2.17482304573059</v>
       </c>
       <c r="G719" t="s">
-        <v>627</v>
+        <v>626</v>
       </c>
       <c r="H719" t="s">
         <v>9</v>
@@ -25845,7 +25848,7 @@
         <v>2.2249128818512</v>
       </c>
       <c r="G720" t="s">
-        <v>628</v>
+        <v>627</v>
       </c>
       <c r="H720" t="s">
         <v>9</v>
@@ -25871,7 +25874,7 @@
         <v>2.20799088478088</v>
       </c>
       <c r="G721" t="s">
-        <v>629</v>
+        <v>628</v>
       </c>
       <c r="H721" t="s">
         <v>9</v>
@@ -25897,7 +25900,7 @@
         <v>2.30546188354492</v>
       </c>
       <c r="G722" t="s">
-        <v>630</v>
+        <v>629</v>
       </c>
       <c r="H722" t="s">
         <v>9</v>
@@ -25923,7 +25926,7 @@
         <v>2.29192399978638</v>
       </c>
       <c r="G723" t="s">
-        <v>631</v>
+        <v>630</v>
       </c>
       <c r="H723" t="s">
         <v>9</v>
@@ -25949,7 +25952,7 @@
         <v>2.2729709148407</v>
       </c>
       <c r="G724" t="s">
-        <v>632</v>
+        <v>631</v>
       </c>
       <c r="H724" t="s">
         <v>9</v>
@@ -25975,7 +25978,7 @@
         <v>2.28650903701782</v>
       </c>
       <c r="G725" t="s">
-        <v>633</v>
+        <v>632</v>
       </c>
       <c r="H725" t="s">
         <v>9</v>
@@ -26001,7 +26004,7 @@
         <v>2.37924194335938</v>
       </c>
       <c r="G726" t="s">
-        <v>634</v>
+        <v>633</v>
       </c>
       <c r="H726" t="s">
         <v>9</v>
@@ -26027,7 +26030,7 @@
         <v>2.29733896255493</v>
       </c>
       <c r="G727" t="s">
-        <v>635</v>
+        <v>634</v>
       </c>
       <c r="H727" t="s">
         <v>9</v>
@@ -26053,7 +26056,7 @@
         <v>2.28041696548462</v>
       </c>
       <c r="G728" t="s">
-        <v>636</v>
+        <v>635</v>
       </c>
       <c r="H728" t="s">
         <v>9</v>
@@ -26079,7 +26082,7 @@
         <v>2.32170701026917</v>
       </c>
       <c r="G729" t="s">
-        <v>637</v>
+        <v>636</v>
       </c>
       <c r="H729" t="s">
         <v>9</v>
@@ -26105,7 +26108,7 @@
         <v>2.33930611610413</v>
       </c>
       <c r="G730" t="s">
-        <v>638</v>
+        <v>637</v>
       </c>
       <c r="H730" t="s">
         <v>9</v>
@@ -26131,7 +26134,7 @@
         <v>2.36028909683228</v>
       </c>
       <c r="G731" t="s">
-        <v>639</v>
+        <v>638</v>
       </c>
       <c r="H731" t="s">
         <v>9</v>
@@ -26157,7 +26160,7 @@
         <v>2.36367392539978</v>
       </c>
       <c r="G732" t="s">
-        <v>640</v>
+        <v>639</v>
       </c>
       <c r="H732" t="s">
         <v>9</v>
@@ -26183,7 +26186,7 @@
         <v>2.36570405960083</v>
       </c>
       <c r="G733" t="s">
-        <v>623</v>
+        <v>622</v>
       </c>
       <c r="H733" t="s">
         <v>9</v>
@@ -26209,7 +26212,7 @@
         <v>2.29463195800781</v>
       </c>
       <c r="G734" t="s">
-        <v>641</v>
+        <v>640</v>
       </c>
       <c r="H734" t="s">
         <v>9</v>
@@ -26235,7 +26238,7 @@
         <v>2.31358408927917</v>
       </c>
       <c r="G735" t="s">
-        <v>642</v>
+        <v>641</v>
       </c>
       <c r="H735" t="s">
         <v>9</v>
@@ -26261,7 +26264,7 @@
         <v>2.2716178894043</v>
       </c>
       <c r="G736" t="s">
-        <v>643</v>
+        <v>642</v>
       </c>
       <c r="H736" t="s">
         <v>9</v>
@@ -26287,7 +26290,7 @@
         <v>2.29260110855103</v>
       </c>
       <c r="G737" t="s">
-        <v>644</v>
+        <v>643</v>
       </c>
       <c r="H737" t="s">
         <v>9</v>
@@ -26313,7 +26316,7 @@
         <v>2.26620292663574</v>
       </c>
       <c r="G738" t="s">
-        <v>645</v>
+        <v>644</v>
       </c>
       <c r="H738" t="s">
         <v>9</v>
@@ -26339,7 +26342,7 @@
         <v>2.34810495376587</v>
       </c>
       <c r="G739" t="s">
-        <v>646</v>
+        <v>645</v>
       </c>
       <c r="H739" t="s">
         <v>9</v>
@@ -26365,7 +26368,7 @@
         <v>2.36164307594299</v>
       </c>
       <c r="G740" t="s">
-        <v>647</v>
+        <v>646</v>
       </c>
       <c r="H740" t="s">
         <v>9</v>
@@ -26391,7 +26394,7 @@
         <v>2.36299705505371</v>
       </c>
       <c r="G741" t="s">
-        <v>648</v>
+        <v>647</v>
       </c>
       <c r="H741" t="s">
         <v>9</v>
@@ -26417,7 +26420,7 @@
         <v>2.48957395553589</v>
       </c>
       <c r="G742" t="s">
-        <v>649</v>
+        <v>648</v>
       </c>
       <c r="H742" t="s">
         <v>9</v>
@@ -26443,7 +26446,7 @@
         <v>2.40225601196289</v>
       </c>
       <c r="G743" t="s">
-        <v>650</v>
+        <v>649</v>
       </c>
       <c r="H743" t="s">
         <v>9</v>
@@ -26469,7 +26472,7 @@
         <v>2.42391610145569</v>
       </c>
       <c r="G744" t="s">
-        <v>651</v>
+        <v>650</v>
       </c>
       <c r="H744" t="s">
         <v>9</v>
@@ -26495,7 +26498,7 @@
         <v>2.40022492408752</v>
       </c>
       <c r="G745" t="s">
-        <v>618</v>
+        <v>617</v>
       </c>
       <c r="H745" t="s">
         <v>9</v>
@@ -26521,7 +26524,7 @@
         <v>2.43610000610352</v>
       </c>
       <c r="G746" t="s">
-        <v>652</v>
+        <v>651</v>
       </c>
       <c r="H746" t="s">
         <v>9</v>
@@ -26547,7 +26550,7 @@
         <v>2.5484631061554</v>
       </c>
       <c r="G747" t="s">
-        <v>653</v>
+        <v>652</v>
       </c>
       <c r="H747" t="s">
         <v>9</v>
@@ -26573,7 +26576,7 @@
         <v>2.50514197349548</v>
       </c>
       <c r="G748" t="s">
-        <v>654</v>
+        <v>653</v>
       </c>
       <c r="H748" t="s">
         <v>9</v>
@@ -26599,7 +26602,7 @@
         <v>2.55184698104858</v>
       </c>
       <c r="G749" t="s">
-        <v>655</v>
+        <v>654</v>
       </c>
       <c r="H749" t="s">
         <v>9</v>
@@ -26625,7 +26628,7 @@
         <v>2.47062110900879</v>
       </c>
       <c r="G750" t="s">
-        <v>656</v>
+        <v>655</v>
       </c>
       <c r="H750" t="s">
         <v>9</v>
@@ -26651,7 +26654,7 @@
         <v>2.43136191368103</v>
       </c>
       <c r="G751" t="s">
-        <v>657</v>
+        <v>656</v>
       </c>
       <c r="H751" t="s">
         <v>9</v>
@@ -26677,7 +26680,7 @@
         <v>2.39007210731506</v>
       </c>
       <c r="G752" t="s">
-        <v>658</v>
+        <v>657</v>
       </c>
       <c r="H752" t="s">
         <v>9</v>
@@ -26703,7 +26706,7 @@
         <v>2.33930611610413</v>
       </c>
       <c r="G753" t="s">
-        <v>638</v>
+        <v>637</v>
       </c>
       <c r="H753" t="s">
         <v>9</v>
@@ -26729,7 +26732,7 @@
         <v>2.36705803871155</v>
       </c>
       <c r="G754" t="s">
-        <v>659</v>
+        <v>658</v>
       </c>
       <c r="H754" t="s">
         <v>9</v>
@@ -26755,7 +26758,7 @@
         <v>2.35758209228516</v>
       </c>
       <c r="G755" t="s">
-        <v>660</v>
+        <v>659</v>
       </c>
       <c r="H755" t="s">
         <v>9</v>
@@ -26781,7 +26784,7 @@
         <v>2.32102990150452</v>
       </c>
       <c r="G756" t="s">
-        <v>661</v>
+        <v>660</v>
       </c>
       <c r="H756" t="s">
         <v>9</v>
@@ -26807,7 +26810,7 @@
         <v>2.27567911148071</v>
       </c>
       <c r="G757" t="s">
-        <v>662</v>
+        <v>661</v>
       </c>
       <c r="H757" t="s">
         <v>9</v>
@@ -26833,7 +26836,7 @@
         <v>2.26484894752502</v>
       </c>
       <c r="G758" t="s">
-        <v>663</v>
+        <v>662</v>
       </c>
       <c r="H758" t="s">
         <v>9</v>
@@ -26859,7 +26862,7 @@
         <v>2.31087708473206</v>
       </c>
       <c r="G759" t="s">
-        <v>664</v>
+        <v>663</v>
       </c>
       <c r="H759" t="s">
         <v>9</v>
@@ -26885,7 +26888,7 @@
         <v>2.26687908172607</v>
       </c>
       <c r="G760" t="s">
-        <v>665</v>
+        <v>664</v>
       </c>
       <c r="H760" t="s">
         <v>9</v>
@@ -26911,7 +26914,7 @@
         <v>2.24995708465576</v>
       </c>
       <c r="G761" t="s">
-        <v>666</v>
+        <v>665</v>
       </c>
       <c r="H761" t="s">
         <v>9</v>
@@ -26937,7 +26940,7 @@
         <v>2.21949791908264</v>
       </c>
       <c r="G762" t="s">
-        <v>667</v>
+        <v>666</v>
       </c>
       <c r="H762" t="s">
         <v>9</v>
@@ -26963,7 +26966,7 @@
         <v>2.27703309059143</v>
       </c>
       <c r="G763" t="s">
-        <v>668</v>
+        <v>667</v>
       </c>
       <c r="H763" t="s">
         <v>9</v>
@@ -26989,7 +26992,7 @@
         <v>2.2310049533844</v>
       </c>
       <c r="G764" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="H764" t="s">
         <v>9</v>
@@ -27015,7 +27018,7 @@
         <v>2.21611309051514</v>
       </c>
       <c r="G765" t="s">
-        <v>670</v>
+        <v>669</v>
       </c>
       <c r="H765" t="s">
         <v>9</v>
@@ -27041,7 +27044,7 @@
         <v>2.29057002067566</v>
       </c>
       <c r="G766" t="s">
-        <v>671</v>
+        <v>670</v>
       </c>
       <c r="H766" t="s">
         <v>9</v>
@@ -27067,7 +27070,7 @@
         <v>2.30478501319885</v>
       </c>
       <c r="G767" t="s">
-        <v>672</v>
+        <v>671</v>
       </c>
       <c r="H767" t="s">
         <v>9</v>
@@ -27093,7 +27096,7 @@
         <v>2.25401902198792</v>
       </c>
       <c r="G768" t="s">
-        <v>673</v>
+        <v>672</v>
       </c>
       <c r="H768" t="s">
         <v>9</v>
@@ -27119,7 +27122,7 @@
         <v>2.24454188346863</v>
       </c>
       <c r="G769" t="s">
-        <v>674</v>
+        <v>673</v>
       </c>
       <c r="H769" t="s">
         <v>9</v>
@@ -27145,7 +27148,7 @@
         <v>2.25131106376648</v>
       </c>
       <c r="G770" t="s">
-        <v>675</v>
+        <v>674</v>
       </c>
       <c r="H770" t="s">
         <v>9</v>
@@ -27171,7 +27174,7 @@
         <v>2.21340608596802</v>
       </c>
       <c r="G771" t="s">
-        <v>676</v>
+        <v>675</v>
       </c>
       <c r="H771" t="s">
         <v>9</v>
@@ -27197,7 +27200,7 @@
         <v>2.12811803817749</v>
       </c>
       <c r="G772" t="s">
-        <v>677</v>
+        <v>676</v>
       </c>
       <c r="H772" t="s">
         <v>9</v>
@@ -27223,7 +27226,7 @@
         <v>2.02726292610168</v>
       </c>
       <c r="G773" t="s">
-        <v>678</v>
+        <v>677</v>
       </c>
       <c r="H773" t="s">
         <v>9</v>
@@ -27249,7 +27252,7 @@
         <v>2.071937084198</v>
       </c>
       <c r="G774" t="s">
-        <v>679</v>
+        <v>678</v>
       </c>
       <c r="H774" t="s">
         <v>9</v>
@@ -27275,7 +27278,7 @@
         <v>2.08006000518799</v>
       </c>
       <c r="G775" t="s">
-        <v>680</v>
+        <v>679</v>
       </c>
       <c r="H775" t="s">
         <v>9</v>
@@ -27301,7 +27304,7 @@
         <v>2.06787610054016</v>
       </c>
       <c r="G776" t="s">
-        <v>681</v>
+        <v>680</v>
       </c>
       <c r="H776" t="s">
         <v>9</v>
@@ -27327,7 +27330,7 @@
         <v>2.07870602607727</v>
       </c>
       <c r="G777" t="s">
-        <v>682</v>
+        <v>681</v>
       </c>
       <c r="H777" t="s">
         <v>9</v>
@@ -27353,7 +27356,7 @@
         <v>2.06719899177551</v>
       </c>
       <c r="G778" t="s">
-        <v>683</v>
+        <v>682</v>
       </c>
       <c r="H778" t="s">
         <v>9</v>
@@ -27379,7 +27382,7 @@
         <v>2.03673911094666</v>
       </c>
       <c r="G779" t="s">
-        <v>684</v>
+        <v>683</v>
       </c>
       <c r="H779" t="s">
         <v>9</v>
@@ -27405,7 +27408,7 @@
         <v>2.04283094406128</v>
       </c>
       <c r="G780" t="s">
-        <v>685</v>
+        <v>684</v>
       </c>
       <c r="H780" t="s">
         <v>9</v>
@@ -27431,7 +27434,7 @@
         <v>2.13217997550964</v>
       </c>
       <c r="G781" t="s">
-        <v>686</v>
+        <v>685</v>
       </c>
       <c r="H781" t="s">
         <v>9</v>
@@ -27457,7 +27460,7 @@
         <v>2.10645794868469</v>
       </c>
       <c r="G782" t="s">
-        <v>687</v>
+        <v>686</v>
       </c>
       <c r="H782" t="s">
         <v>9</v>
@@ -27483,7 +27486,7 @@
         <v>2.11187291145325</v>
       </c>
       <c r="G783" t="s">
-        <v>688</v>
+        <v>687</v>
       </c>
       <c r="H783" t="s">
         <v>9</v>
@@ -27509,7 +27512,7 @@
         <v>2.13014888763428</v>
       </c>
       <c r="G784" t="s">
-        <v>689</v>
+        <v>688</v>
       </c>
       <c r="H784" t="s">
         <v>9</v>
@@ -27535,7 +27538,7 @@
         <v>2.00086498260498</v>
       </c>
       <c r="G785" t="s">
-        <v>690</v>
+        <v>689</v>
       </c>
       <c r="H785" t="s">
         <v>9</v>
@@ -27561,7 +27564,7 @@
         <v>2.00695610046387</v>
       </c>
       <c r="G786" t="s">
-        <v>691</v>
+        <v>690</v>
       </c>
       <c r="H786" t="s">
         <v>9</v>
@@ -27587,7 +27590,7 @@
         <v>2.01034092903137</v>
       </c>
       <c r="G787" t="s">
-        <v>692</v>
+        <v>691</v>
       </c>
       <c r="H787" t="s">
         <v>9</v>
@@ -27613,7 +27616,7 @@
         <v>2.01372504234314</v>
       </c>
       <c r="G788" t="s">
-        <v>693</v>
+        <v>692</v>
       </c>
       <c r="H788" t="s">
         <v>9</v>
@@ -27639,7 +27642,7 @@
         <v>2.06110692024231</v>
       </c>
       <c r="G789" t="s">
-        <v>694</v>
+        <v>693</v>
       </c>
       <c r="H789" t="s">
         <v>9</v>
@@ -27665,7 +27668,7 @@
         <v>2.04012393951416</v>
       </c>
       <c r="G790" t="s">
-        <v>695</v>
+        <v>694</v>
       </c>
       <c r="H790" t="s">
         <v>9</v>
@@ -27691,7 +27694,7 @@
         <v>2.22017502784729</v>
       </c>
       <c r="G791" t="s">
-        <v>696</v>
+        <v>695</v>
       </c>
       <c r="H791" t="s">
         <v>9</v>
@@ -27717,7 +27720,7 @@
         <v>2.31223106384277</v>
       </c>
       <c r="G792" t="s">
-        <v>697</v>
+        <v>696</v>
       </c>
       <c r="H792" t="s">
         <v>9</v>
@@ -27743,7 +27746,7 @@
         <v>2.30546188354492</v>
       </c>
       <c r="G793" t="s">
-        <v>630</v>
+        <v>629</v>
       </c>
       <c r="H793" t="s">
         <v>9</v>
@@ -27769,7 +27772,7 @@
         <v>2.28853988647461</v>
       </c>
       <c r="G794" t="s">
-        <v>698</v>
+        <v>697</v>
       </c>
       <c r="H794" t="s">
         <v>9</v>
@@ -27795,7 +27798,7 @@
         <v>2.27974009513855</v>
       </c>
       <c r="G795" t="s">
-        <v>699</v>
+        <v>698</v>
       </c>
       <c r="H795" t="s">
         <v>9</v>
@@ -27821,7 +27824,7 @@
         <v>2.38533401489258</v>
       </c>
       <c r="G796" t="s">
-        <v>700</v>
+        <v>699</v>
       </c>
       <c r="H796" t="s">
         <v>9</v>
@@ -27847,7 +27850,7 @@
         <v>2.37585806846619</v>
       </c>
       <c r="G797" t="s">
-        <v>701</v>
+        <v>700</v>
       </c>
       <c r="H797" t="s">
         <v>9</v>
@@ -27873,7 +27876,7 @@
         <v>2.37450408935547</v>
       </c>
       <c r="G798" t="s">
-        <v>624</v>
+        <v>623</v>
       </c>
       <c r="H798" t="s">
         <v>9</v>
@@ -27899,7 +27902,7 @@
         <v>2.35555100440979</v>
       </c>
       <c r="G799" t="s">
-        <v>702</v>
+        <v>701</v>
       </c>
       <c r="H799" t="s">
         <v>9</v>
@@ -27925,7 +27928,7 @@
         <v>2.31764602661133</v>
       </c>
       <c r="G800" t="s">
-        <v>703</v>
+        <v>702</v>
       </c>
       <c r="H800" t="s">
         <v>9</v>
@@ -27951,7 +27954,7 @@
         <v>2.34472107887268</v>
       </c>
       <c r="G801" t="s">
-        <v>704</v>
+        <v>703</v>
       </c>
       <c r="H801" t="s">
         <v>9</v>
@@ -27977,7 +27980,7 @@
         <v>2.36841201782227</v>
       </c>
       <c r="G802" t="s">
-        <v>705</v>
+        <v>704</v>
       </c>
       <c r="H802" t="s">
         <v>9</v>
@@ -28003,7 +28006,7 @@
         <v>2.38398003578186</v>
       </c>
       <c r="G803" t="s">
-        <v>706</v>
+        <v>705</v>
       </c>
       <c r="H803" t="s">
         <v>9</v>
@@ -28029,7 +28032,7 @@
         <v>2.44828391075134</v>
       </c>
       <c r="G804" t="s">
-        <v>707</v>
+        <v>706</v>
       </c>
       <c r="H804" t="s">
         <v>9</v>
@@ -28055,7 +28058,7 @@
         <v>2.51461791992188</v>
       </c>
       <c r="G805" t="s">
-        <v>612</v>
+        <v>611</v>
       </c>
       <c r="H805" t="s">
         <v>9</v>
@@ -28081,7 +28084,7 @@
         <v>2.50311088562012</v>
       </c>
       <c r="G806" t="s">
-        <v>708</v>
+        <v>707</v>
       </c>
       <c r="H806" t="s">
         <v>9</v>
@@ -28107,7 +28110,7 @@
         <v>2.49634289741516</v>
       </c>
       <c r="G807" t="s">
-        <v>709</v>
+        <v>708</v>
       </c>
       <c r="H807" t="s">
         <v>9</v>
@@ -28133,7 +28136,7 @@
         <v>2.48821997642517</v>
       </c>
       <c r="G808" t="s">
-        <v>710</v>
+        <v>709</v>
       </c>
       <c r="H808" t="s">
         <v>9</v>
@@ -28159,7 +28162,7 @@
         <v>2.50852704048157</v>
       </c>
       <c r="G809" t="s">
-        <v>711</v>
+        <v>710</v>
       </c>
       <c r="H809" t="s">
         <v>9</v>
@@ -28185,7 +28188,7 @@
         <v>2.4347460269928</v>
       </c>
       <c r="G810" t="s">
-        <v>712</v>
+        <v>711</v>
       </c>
       <c r="H810" t="s">
         <v>9</v>
@@ -28211,7 +28214,7 @@
         <v>2.37924194335938</v>
       </c>
       <c r="G811" t="s">
-        <v>634</v>
+        <v>633</v>
       </c>
       <c r="H811" t="s">
         <v>9</v>
@@ -28237,7 +28240,7 @@
         <v>2.40970206260681</v>
       </c>
       <c r="G812" t="s">
-        <v>713</v>
+        <v>712</v>
       </c>
       <c r="H812" t="s">
         <v>9</v>
@@ -28263,7 +28266,7 @@
         <v>2.39480996131897</v>
       </c>
       <c r="G813" t="s">
-        <v>714</v>
+        <v>713</v>
       </c>
       <c r="H813" t="s">
         <v>9</v>
@@ -28289,7 +28292,7 @@
         <v>2.40902495384216</v>
       </c>
       <c r="G814" t="s">
-        <v>715</v>
+        <v>714</v>
       </c>
       <c r="H814" t="s">
         <v>9</v>
@@ -28315,7 +28318,7 @@
         <v>2.45776009559631</v>
       </c>
       <c r="G815" t="s">
-        <v>716</v>
+        <v>715</v>
       </c>
       <c r="H815" t="s">
         <v>9</v>
@@ -28341,7 +28344,7 @@
         <v>2.44286894798279</v>
       </c>
       <c r="G816" t="s">
-        <v>615</v>
+        <v>614</v>
       </c>
       <c r="H816" t="s">
         <v>9</v>
@@ -28367,7 +28370,7 @@
         <v>2.50717306137085</v>
       </c>
       <c r="G817" t="s">
-        <v>717</v>
+        <v>716</v>
       </c>
       <c r="H817" t="s">
         <v>9</v>
@@ -28393,7 +28396,7 @@
         <v>2.52612495422363</v>
       </c>
       <c r="G818" t="s">
-        <v>718</v>
+        <v>717</v>
       </c>
       <c r="H818" t="s">
         <v>9</v>
@@ -28419,7 +28422,7 @@
         <v>2.52680206298828</v>
       </c>
       <c r="G819" t="s">
-        <v>719</v>
+        <v>718</v>
       </c>
       <c r="H819" t="s">
         <v>9</v>
@@ -28445,7 +28448,7 @@
         <v>2.50446510314941</v>
       </c>
       <c r="G820" t="s">
-        <v>720</v>
+        <v>719</v>
       </c>
       <c r="H820" t="s">
         <v>9</v>
@@ -28471,7 +28474,7 @@
         <v>2.46994400024414</v>
       </c>
       <c r="G821" t="s">
-        <v>721</v>
+        <v>720</v>
       </c>
       <c r="H821" t="s">
         <v>9</v>
@@ -28497,7 +28500,7 @@
         <v>2.4597909450531</v>
       </c>
       <c r="G822" t="s">
-        <v>722</v>
+        <v>721</v>
       </c>
       <c r="H822" t="s">
         <v>9</v>
@@ -28523,7 +28526,7 @@
         <v>2.43880796432495</v>
       </c>
       <c r="G823" t="s">
-        <v>723</v>
+        <v>722</v>
       </c>
       <c r="H823" t="s">
         <v>9</v>
@@ -28549,7 +28552,7 @@
         <v>2.47739005088806</v>
       </c>
       <c r="G824" t="s">
-        <v>724</v>
+        <v>723</v>
       </c>
       <c r="H824" t="s">
         <v>9</v>
@@ -28575,7 +28578,7 @@
         <v>2.46723699569702</v>
       </c>
       <c r="G825" t="s">
-        <v>725</v>
+        <v>724</v>
       </c>
       <c r="H825" t="s">
         <v>9</v>
@@ -28601,7 +28604,7 @@
         <v>2.46452903747559</v>
       </c>
       <c r="G826" t="s">
-        <v>726</v>
+        <v>725</v>
       </c>
       <c r="H826" t="s">
         <v>9</v>
@@ -28627,7 +28630,7 @@
         <v>2.49837303161621</v>
       </c>
       <c r="G827" t="s">
-        <v>727</v>
+        <v>726</v>
       </c>
       <c r="H827" t="s">
         <v>9</v>
@@ -28653,7 +28656,7 @@
         <v>2.47942090034485</v>
       </c>
       <c r="G828" t="s">
-        <v>728</v>
+        <v>727</v>
       </c>
       <c r="H828" t="s">
         <v>9</v>
@@ -28679,7 +28682,7 @@
         <v>2.49837303161621</v>
       </c>
       <c r="G829" t="s">
-        <v>727</v>
+        <v>726</v>
       </c>
       <c r="H829" t="s">
         <v>9</v>
@@ -28705,7 +28708,7 @@
         <v>2.50378799438477</v>
       </c>
       <c r="G830" t="s">
-        <v>729</v>
+        <v>728</v>
       </c>
       <c r="H830" t="s">
         <v>9</v>
@@ -28731,7 +28734,7 @@
         <v>2.5064959526062</v>
       </c>
       <c r="G831" t="s">
-        <v>730</v>
+        <v>729</v>
       </c>
       <c r="H831" t="s">
         <v>9</v>
@@ -28757,7 +28760,7 @@
         <v>2.528156042099</v>
       </c>
       <c r="G832" t="s">
-        <v>731</v>
+        <v>730</v>
       </c>
       <c r="H832" t="s">
         <v>9</v>
@@ -28783,7 +28786,7 @@
         <v>2.52951002120972</v>
       </c>
       <c r="G833" t="s">
-        <v>732</v>
+        <v>731</v>
       </c>
       <c r="H833" t="s">
         <v>9</v>
@@ -28809,7 +28812,7 @@
         <v>2.54778599739075</v>
       </c>
       <c r="G834" t="s">
-        <v>611</v>
+        <v>610</v>
       </c>
       <c r="H834" t="s">
         <v>9</v>
@@ -28835,7 +28838,7 @@
         <v>2.56944608688354</v>
       </c>
       <c r="G835" t="s">
-        <v>733</v>
+        <v>732</v>
       </c>
       <c r="H835" t="s">
         <v>9</v>
@@ -28861,7 +28864,7 @@
         <v>2.61750507354736</v>
       </c>
       <c r="G836" t="s">
-        <v>734</v>
+        <v>733</v>
       </c>
       <c r="H836" t="s">
         <v>9</v>
@@ -28887,7 +28890,7 @@
         <v>2.68654704093933</v>
       </c>
       <c r="G837" t="s">
-        <v>735</v>
+        <v>734</v>
       </c>
       <c r="H837" t="s">
         <v>9</v>
@@ -28913,7 +28916,7 @@
         <v>2.73189806938171</v>
       </c>
       <c r="G838" t="s">
-        <v>736</v>
+        <v>735</v>
       </c>
       <c r="H838" t="s">
         <v>9</v>
@@ -28939,7 +28942,7 @@
         <v>2.80432391166687</v>
       </c>
       <c r="G839" t="s">
-        <v>737</v>
+        <v>736</v>
       </c>
       <c r="H839" t="s">
         <v>9</v>
@@ -28965,7 +28968,7 @@
         <v>2.83139991760254</v>
       </c>
       <c r="G840" t="s">
-        <v>738</v>
+        <v>737</v>
       </c>
       <c r="H840" t="s">
         <v>9</v>
@@ -28991,7 +28994,7 @@
         <v>2.8036470413208</v>
       </c>
       <c r="G841" t="s">
-        <v>739</v>
+        <v>738</v>
       </c>
       <c r="H841" t="s">
         <v>9</v>
@@ -29017,7 +29020,7 @@
         <v>2.77927994728088</v>
       </c>
       <c r="G842" t="s">
-        <v>740</v>
+        <v>739</v>
       </c>
       <c r="H842" t="s">
         <v>9</v>
@@ -29043,7 +29046,7 @@
         <v>2.82463097572327</v>
       </c>
       <c r="G843" t="s">
-        <v>741</v>
+        <v>740</v>
       </c>
       <c r="H843" t="s">
         <v>9</v>
@@ -29069,7 +29072,7 @@
         <v>2.84764504432678</v>
       </c>
       <c r="G844" t="s">
-        <v>742</v>
+        <v>741</v>
       </c>
       <c r="H844" t="s">
         <v>9</v>
@@ -29095,7 +29098,7 @@
         <v>2.85576701164246</v>
       </c>
       <c r="G845" t="s">
-        <v>743</v>
+        <v>742</v>
       </c>
       <c r="H845" t="s">
         <v>9</v>
@@ -29121,7 +29124,7 @@
         <v>2.89976501464844</v>
       </c>
       <c r="G846" t="s">
-        <v>744</v>
+        <v>743</v>
       </c>
       <c r="H846" t="s">
         <v>9</v>
@@ -29147,7 +29150,7 @@
         <v>2.85306000709534</v>
       </c>
       <c r="G847" t="s">
-        <v>745</v>
+        <v>744</v>
       </c>
       <c r="H847" t="s">
         <v>9</v>
@@ -29173,7 +29176,7 @@
         <v>2.8442599773407</v>
       </c>
       <c r="G848" t="s">
-        <v>746</v>
+        <v>745</v>
       </c>
       <c r="H848" t="s">
         <v>9</v>
@@ -29199,7 +29202,7 @@
         <v>2.80906200408936</v>
       </c>
       <c r="G849" t="s">
-        <v>536</v>
+        <v>535</v>
       </c>
       <c r="H849" t="s">
         <v>9</v>
@@ -29225,7 +29228,7 @@
         <v>2.78537201881409</v>
       </c>
       <c r="G850" t="s">
-        <v>747</v>
+        <v>746</v>
       </c>
       <c r="H850" t="s">
         <v>9</v>
@@ -29251,7 +29254,7 @@
         <v>2.76980304718018</v>
       </c>
       <c r="G851" t="s">
-        <v>748</v>
+        <v>747</v>
       </c>
       <c r="H851" t="s">
         <v>9</v>
@@ -29277,7 +29280,7 @@
         <v>2.71023797988892</v>
       </c>
       <c r="G852" t="s">
-        <v>749</v>
+        <v>748</v>
       </c>
       <c r="H852" t="s">
         <v>9</v>
@@ -29303,7 +29306,7 @@
         <v>2.68045496940613</v>
       </c>
       <c r="G853" t="s">
-        <v>750</v>
+        <v>749</v>
       </c>
       <c r="H853" t="s">
         <v>9</v>
@@ -29329,7 +29332,7 @@
         <v>2.63984203338623</v>
       </c>
       <c r="G854" t="s">
-        <v>751</v>
+        <v>750</v>
       </c>
       <c r="H854" t="s">
         <v>9</v>
@@ -29355,7 +29358,7 @@
         <v>2.66353297233582</v>
       </c>
       <c r="G855" t="s">
-        <v>752</v>
+        <v>751</v>
       </c>
       <c r="H855" t="s">
         <v>9</v>
@@ -29381,7 +29384,7 @@
         <v>2.61682796478271</v>
       </c>
       <c r="G856" t="s">
-        <v>753</v>
+        <v>752</v>
       </c>
       <c r="H856" t="s">
         <v>9</v>
@@ -29407,7 +29410,7 @@
         <v>2.67571711540222</v>
       </c>
       <c r="G857" t="s">
-        <v>754</v>
+        <v>753</v>
       </c>
       <c r="H857" t="s">
         <v>9</v>
@@ -29433,7 +29436,7 @@
         <v>2.68045496940613</v>
       </c>
       <c r="G858" t="s">
-        <v>750</v>
+        <v>749</v>
       </c>
       <c r="H858" t="s">
         <v>9</v>
@@ -29459,7 +29462,7 @@
         <v>2.51868009567261</v>
       </c>
       <c r="G859" t="s">
-        <v>755</v>
+        <v>754</v>
       </c>
       <c r="H859" t="s">
         <v>9</v>
@@ -29485,7 +29488,7 @@
         <v>2.45234489440918</v>
       </c>
       <c r="G860" t="s">
-        <v>756</v>
+        <v>755</v>
       </c>
       <c r="H860" t="s">
         <v>9</v>
@@ -29511,7 +29514,7 @@
         <v>2.40022492408752</v>
       </c>
       <c r="G861" t="s">
-        <v>757</v>
+        <v>756</v>
       </c>
       <c r="H861" t="s">
         <v>9</v>
@@ -29537,7 +29540,7 @@
         <v>2.36841201782227</v>
       </c>
       <c r="G862" t="s">
-        <v>758</v>
+        <v>757</v>
       </c>
       <c r="H862" t="s">
         <v>9</v>
@@ -29563,7 +29566,7 @@
         <v>2.3927800655365</v>
       </c>
       <c r="G863" t="s">
-        <v>759</v>
+        <v>758</v>
       </c>
       <c r="H863" t="s">
         <v>9</v>
@@ -29589,7 +29592,7 @@
         <v>2.32915306091309</v>
       </c>
       <c r="G864" t="s">
-        <v>760</v>
+        <v>759</v>
       </c>
       <c r="H864" t="s">
         <v>9</v>
@@ -29615,7 +29618,7 @@
         <v>2.33050608634949</v>
       </c>
       <c r="G865" t="s">
-        <v>761</v>
+        <v>760</v>
       </c>
       <c r="H865" t="s">
         <v>9</v>
@@ -29641,7 +29644,7 @@
         <v>2.3183228969574</v>
       </c>
       <c r="G866" t="s">
-        <v>762</v>
+        <v>761</v>
       </c>
       <c r="H866" t="s">
         <v>9</v>
@@ -29667,7 +29670,7 @@
         <v>2.30207705497742</v>
       </c>
       <c r="G867" t="s">
-        <v>763</v>
+        <v>762</v>
       </c>
       <c r="H867" t="s">
         <v>9</v>
@@ -29693,7 +29696,7 @@
         <v>2.29057002067566</v>
       </c>
       <c r="G868" t="s">
-        <v>764</v>
+        <v>763</v>
       </c>
       <c r="H868" t="s">
         <v>9</v>
@@ -29719,7 +29722,7 @@
         <v>2.27229404449463</v>
       </c>
       <c r="G869" t="s">
-        <v>765</v>
+        <v>764</v>
       </c>
       <c r="H869" t="s">
         <v>9</v>
@@ -29745,7 +29748,7 @@
         <v>2.31223106384277</v>
       </c>
       <c r="G870" t="s">
-        <v>766</v>
+        <v>765</v>
       </c>
       <c r="H870" t="s">
         <v>9</v>
@@ -29771,7 +29774,7 @@
         <v>2.27026391029358</v>
       </c>
       <c r="G871" t="s">
-        <v>767</v>
+        <v>766</v>
       </c>
       <c r="H871" t="s">
         <v>9</v>
@@ -29797,7 +29800,7 @@
         <v>2.24318909645081</v>
       </c>
       <c r="G872" t="s">
-        <v>768</v>
+        <v>767</v>
       </c>
       <c r="H872" t="s">
         <v>9</v>
@@ -29823,7 +29826,7 @@
         <v>2.23912692070007</v>
       </c>
       <c r="G873" t="s">
-        <v>769</v>
+        <v>768</v>
       </c>
       <c r="H873" t="s">
         <v>9</v>
@@ -29849,7 +29852,7 @@
         <v>2.30952310562134</v>
       </c>
       <c r="G874" t="s">
-        <v>770</v>
+        <v>769</v>
       </c>
       <c r="H874" t="s">
         <v>9</v>
@@ -29875,7 +29878,7 @@
         <v>2.33118295669556</v>
       </c>
       <c r="G875" t="s">
-        <v>771</v>
+        <v>770</v>
       </c>
       <c r="H875" t="s">
         <v>9</v>
@@ -29901,7 +29904,7 @@
         <v>2.30478501319885</v>
       </c>
       <c r="G876" t="s">
-        <v>772</v>
+        <v>771</v>
       </c>
       <c r="H876" t="s">
         <v>9</v>
@@ -29927,7 +29930,7 @@
         <v>2.33253693580627</v>
       </c>
       <c r="G877" t="s">
-        <v>773</v>
+        <v>772</v>
       </c>
       <c r="H877" t="s">
         <v>9</v>
@@ -29953,7 +29956,7 @@
         <v>2.32441401481628</v>
       </c>
       <c r="G878" t="s">
-        <v>774</v>
+        <v>773</v>
       </c>
       <c r="H878" t="s">
         <v>9</v>
@@ -29979,7 +29982,7 @@
         <v>2.34201288223267</v>
       </c>
       <c r="G879" t="s">
-        <v>775</v>
+        <v>774</v>
       </c>
       <c r="H879" t="s">
         <v>9</v>
@@ -30005,7 +30008,7 @@
         <v>2.39480996131897</v>
       </c>
       <c r="G880" t="s">
-        <v>776</v>
+        <v>775</v>
       </c>
       <c r="H880" t="s">
         <v>9</v>
@@ -30031,7 +30034,7 @@
         <v>2.4394850730896</v>
       </c>
       <c r="G881" t="s">
-        <v>777</v>
+        <v>776</v>
       </c>
       <c r="H881" t="s">
         <v>9</v>
@@ -30057,7 +30060,7 @@
         <v>2.43677711486816</v>
       </c>
       <c r="G882" t="s">
-        <v>778</v>
+        <v>777</v>
       </c>
       <c r="H882" t="s">
         <v>9</v>
@@ -30083,7 +30086,7 @@
         <v>2.47806692123413</v>
       </c>
       <c r="G883" t="s">
-        <v>779</v>
+        <v>778</v>
       </c>
       <c r="H883" t="s">
         <v>9</v>
@@ -30109,7 +30112,7 @@
         <v>2.45099210739136</v>
       </c>
       <c r="G884" t="s">
-        <v>780</v>
+        <v>779</v>
       </c>
       <c r="H884" t="s">
         <v>9</v>
@@ -30135,7 +30138,7 @@
         <v>2.39480996131897</v>
       </c>
       <c r="G885" t="s">
-        <v>776</v>
+        <v>775</v>
       </c>
       <c r="H885" t="s">
         <v>9</v>
@@ -30161,7 +30164,7 @@
         <v>2.44963788986206</v>
       </c>
       <c r="G886" t="s">
-        <v>781</v>
+        <v>780</v>
       </c>
       <c r="H886" t="s">
         <v>9</v>
@@ -30187,7 +30190,7 @@
         <v>2.46385192871094</v>
       </c>
       <c r="G887" t="s">
-        <v>782</v>
+        <v>781</v>
       </c>
       <c r="H887" t="s">
         <v>9</v>
@@ -30213,7 +30216,7 @@
         <v>2.42527008056641</v>
       </c>
       <c r="G888" t="s">
-        <v>783</v>
+        <v>782</v>
       </c>
       <c r="H888" t="s">
         <v>9</v>
@@ -30239,7 +30242,7 @@
         <v>2.41240906715393</v>
       </c>
       <c r="G889" t="s">
-        <v>784</v>
+        <v>783</v>
       </c>
       <c r="H889" t="s">
         <v>9</v>
@@ -30265,7 +30268,7 @@
         <v>2.46182203292847</v>
       </c>
       <c r="G890" t="s">
-        <v>785</v>
+        <v>784</v>
       </c>
       <c r="H890" t="s">
         <v>9</v>
@@ -30291,7 +30294,7 @@
         <v>2.55793905258179</v>
       </c>
       <c r="G891" t="s">
-        <v>786</v>
+        <v>785</v>
       </c>
       <c r="H891" t="s">
         <v>9</v>
@@ -30317,7 +30320,7 @@
         <v>2.63239598274231</v>
       </c>
       <c r="G892" t="s">
-        <v>787</v>
+        <v>786</v>
       </c>
       <c r="H892" t="s">
         <v>9</v>
@@ -30343,7 +30346,7 @@
         <v>2.63781094551086</v>
       </c>
       <c r="G893" t="s">
-        <v>788</v>
+        <v>787</v>
       </c>
       <c r="H893" t="s">
         <v>9</v>
@@ -30369,7 +30372,7 @@
         <v>2.61412000656128</v>
       </c>
       <c r="G894" t="s">
-        <v>789</v>
+        <v>788</v>
       </c>
       <c r="H894" t="s">
         <v>9</v>
@@ -30395,7 +30398,7 @@
         <v>2.59245991706848</v>
       </c>
       <c r="G895" t="s">
-        <v>750</v>
+        <v>789</v>
       </c>
       <c r="H895" t="s">
         <v>9</v>
@@ -30577,7 +30580,7 @@
         <v>2.59245991706848</v>
       </c>
       <c r="G902" t="s">
-        <v>750</v>
+        <v>789</v>
       </c>
       <c r="H902" t="s">
         <v>9</v>
@@ -30967,7 +30970,7 @@
         <v>2.32915306091309</v>
       </c>
       <c r="G917" t="s">
-        <v>760</v>
+        <v>759</v>
       </c>
       <c r="H917" t="s">
         <v>9</v>
@@ -31903,7 +31906,7 @@
         <v>2.40022492408752</v>
       </c>
       <c r="G953" t="s">
-        <v>757</v>
+        <v>756</v>
       </c>
       <c r="H953" t="s">
         <v>9</v>
@@ -32033,7 +32036,7 @@
         <v>2.36841201782227</v>
       </c>
       <c r="G958" t="s">
-        <v>758</v>
+        <v>757</v>
       </c>
       <c r="H958" t="s">
         <v>9</v>
@@ -34633,7 +34636,7 @@
         <v>2.30478501319885</v>
       </c>
       <c r="G1058" t="s">
-        <v>772</v>
+        <v>771</v>
       </c>
       <c r="H1058" t="s">
         <v>9</v>
@@ -71899,7 +71902,7 @@
     </row>
     <row r="2492">
       <c r="A2492" s="1" t="n">
-        <v>45947.6493055556</v>
+        <v>45947.2916666667</v>
       </c>
       <c r="B2492" t="n">
         <v>15242514</v>
@@ -71920,6 +71923,32 @@
         <v>2260</v>
       </c>
       <c r="H2492" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2493">
+      <c r="A2493" s="1" t="n">
+        <v>45950.6494097222</v>
+      </c>
+      <c r="B2493" t="n">
+        <v>13166658</v>
+      </c>
+      <c r="C2493" t="n">
+        <v>9.66800022125244</v>
+      </c>
+      <c r="D2493" t="n">
+        <v>9.44799995422363</v>
+      </c>
+      <c r="E2493" t="n">
+        <v>9.48999977111816</v>
+      </c>
+      <c r="F2493" t="n">
+        <v>9.55000019073486</v>
+      </c>
+      <c r="G2493" t="s">
+        <v>2261</v>
+      </c>
+      <c r="H2493" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/BPE.MI.xlsx
+++ b/data/BPE.MI.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2275" uniqueCount="2275">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2276" uniqueCount="2276">
   <si>
     <t xml:space="preserve">date</t>
   </si>
@@ -44,13 +44,13 @@
     <t xml:space="preserve">BPE.MI</t>
   </si>
   <si>
-    <t xml:space="preserve">3.26970076560974</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.12443423271179</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.05299067497253</t>
+    <t xml:space="preserve">3.26970148086548</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.12443399429321</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.05299139022827</t>
   </si>
   <si>
     <t xml:space="preserve">2.98392915725708</t>
@@ -62,7 +62,7 @@
     <t xml:space="preserve">2.96249628067017</t>
   </si>
   <si>
-    <t xml:space="preserve">3.10538196563721</t>
+    <t xml:space="preserve">3.10538220405579</t>
   </si>
   <si>
     <t xml:space="preserve">2.94582724571228</t>
@@ -80,85 +80,85 @@
     <t xml:space="preserve">2.7553129196167</t>
   </si>
   <si>
-    <t xml:space="preserve">2.7243537902832</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.65291118621826</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.80770397186279</t>
+    <t xml:space="preserve">2.72435355186462</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.65291142463684</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.80770421028137</t>
   </si>
   <si>
     <t xml:space="preserve">2.69339561462402</t>
   </si>
   <si>
-    <t xml:space="preserve">2.49097418785095</t>
+    <t xml:space="preserve">2.49097442626953</t>
   </si>
   <si>
     <t xml:space="preserve">2.61957097053528</t>
   </si>
   <si>
-    <t xml:space="preserve">2.55527234077454</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.38142824172974</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.18424582481384</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.19281888008118</t>
+    <t xml:space="preserve">2.55527257919312</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.38142800331116</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.18424558639526</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.1928186416626</t>
   </si>
   <si>
     <t xml:space="preserve">2.14709568023682</t>
   </si>
   <si>
-    <t xml:space="preserve">1.89085423946381</t>
+    <t xml:space="preserve">1.89085412025452</t>
   </si>
   <si>
     <t xml:space="preserve">1.84989356994629</t>
   </si>
   <si>
-    <t xml:space="preserve">1.97753775119781</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.78797626495361</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.99373173713684</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.19567632675171</t>
+    <t xml:space="preserve">1.97753763198853</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.7879763841629</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.99373137950897</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.19567680358887</t>
   </si>
   <si>
     <t xml:space="preserve">2.30236482620239</t>
   </si>
   <si>
-    <t xml:space="preserve">2.35761427879333</t>
+    <t xml:space="preserve">2.35761451721191</t>
   </si>
   <si>
     <t xml:space="preserve">2.34332537651062</t>
   </si>
   <si>
-    <t xml:space="preserve">2.20329737663269</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.42667531967163</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.33475208282471</t>
+    <t xml:space="preserve">2.20329761505127</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.42667555809021</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.33475232124329</t>
   </si>
   <si>
     <t xml:space="preserve">2.18615078926086</t>
   </si>
   <si>
-    <t xml:space="preserve">2.24044752120972</t>
+    <t xml:space="preserve">2.24044728279114</t>
   </si>
   <si>
     <t xml:space="preserve">2.28236103057861</t>
   </si>
   <si>
-    <t xml:space="preserve">2.24330568313599</t>
+    <t xml:space="preserve">2.24330520629883</t>
   </si>
   <si>
     <t xml:space="preserve">2.27664494514465</t>
@@ -170,22 +170,22 @@
     <t xml:space="preserve">2.34713530540466</t>
   </si>
   <si>
-    <t xml:space="preserve">2.35666131973267</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.23473238945007</t>
+    <t xml:space="preserve">2.35666155815125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.23473215103149</t>
   </si>
   <si>
     <t xml:space="preserve">2.20234489440918</t>
   </si>
   <si>
-    <t xml:space="preserve">2.22711229324341</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.24711561203003</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.43381977081299</t>
+    <t xml:space="preserve">2.22711157798767</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.24711585044861</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.43381953239441</t>
   </si>
   <si>
     <t xml:space="preserve">2.46716022491455</t>
@@ -194,16 +194,16 @@
     <t xml:space="preserve">2.38619089126587</t>
   </si>
   <si>
-    <t xml:space="preserve">2.22425365447998</t>
+    <t xml:space="preserve">2.2242534160614</t>
   </si>
   <si>
     <t xml:space="preserve">2.24902057647705</t>
   </si>
   <si>
-    <t xml:space="preserve">2.26902413368225</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.26330971717834</t>
+    <t xml:space="preserve">2.26902437210083</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.26330995559692</t>
   </si>
   <si>
     <t xml:space="preserve">2.22996926307678</t>
@@ -212,121 +212,121 @@
     <t xml:space="preserve">2.1690046787262</t>
   </si>
   <si>
-    <t xml:space="preserve">2.07946300506592</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.05850648880005</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.99277889728546</t>
+    <t xml:space="preserve">2.07946348190308</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.05850601196289</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.99277901649475</t>
   </si>
   <si>
     <t xml:space="preserve">2.02897691726685</t>
   </si>
   <si>
-    <t xml:space="preserve">1.91371560096741</t>
+    <t xml:space="preserve">1.91371548175812</t>
   </si>
   <si>
     <t xml:space="preserve">1.9032369852066</t>
   </si>
   <si>
-    <t xml:space="preserve">1.79083395004272</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.04707598686218</t>
+    <t xml:space="preserve">1.79083371162415</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.04707551002502</t>
   </si>
   <si>
     <t xml:space="preserve">2.14614319801331</t>
   </si>
   <si>
-    <t xml:space="preserve">2.06041169166565</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.29664969444275</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.40048003196716</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.40762400627136</t>
+    <t xml:space="preserve">2.06041193008423</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.29664945602417</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.40047931671143</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.4076235294342</t>
   </si>
   <si>
     <t xml:space="preserve">2.32713174819946</t>
   </si>
   <si>
-    <t xml:space="preserve">2.39571690559387</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.47192215919495</t>
+    <t xml:space="preserve">2.39571666717529</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.47192239761353</t>
   </si>
   <si>
     <t xml:space="preserve">2.48382925987244</t>
   </si>
   <si>
-    <t xml:space="preserve">2.39809846878052</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.47668504714966</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.43858289718628</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.5338397026062</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.43143773078918</t>
+    <t xml:space="preserve">2.39809799194336</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.47668528556824</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.4385826587677</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.53383946418762</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.43143796920776</t>
   </si>
   <si>
     <t xml:space="preserve">2.34237241744995</t>
   </si>
   <si>
-    <t xml:space="preserve">2.23949551582336</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.21472859382629</t>
+    <t xml:space="preserve">2.23949527740479</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.21472835540771</t>
   </si>
   <si>
     <t xml:space="preserve">2.15281105041504</t>
   </si>
   <si>
-    <t xml:space="preserve">2.09660935401917</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.09089374542236</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.0851788520813</t>
+    <t xml:space="preserve">2.09660959243774</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.09089350700378</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.08517861366272</t>
   </si>
   <si>
     <t xml:space="preserve">2.05279135704041</t>
   </si>
   <si>
-    <t xml:space="preserve">2.04993343353271</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.0813684463501</t>
+    <t xml:space="preserve">2.04993319511414</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.08136868476868</t>
   </si>
   <si>
     <t xml:space="preserve">2.1966290473938</t>
   </si>
   <si>
-    <t xml:space="preserve">2.09375190734863</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.12042379379272</t>
+    <t xml:space="preserve">2.09375166893005</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.12042331695557</t>
   </si>
   <si>
     <t xml:space="preserve">2.07852172851562</t>
   </si>
   <si>
-    <t xml:space="preserve">2.24223065376282</t>
+    <t xml:space="preserve">2.24223041534424</t>
   </si>
   <si>
     <t xml:space="preserve">2.35429334640503</t>
   </si>
   <si>
-    <t xml:space="preserve">2.30849385261536</t>
+    <t xml:space="preserve">2.3084933757782</t>
   </si>
   <si>
     <t xml:space="preserve">2.31434059143066</t>
@@ -344,160 +344,160 @@
     <t xml:space="preserve">2.18766140937805</t>
   </si>
   <si>
-    <t xml:space="preserve">2.09996032714844</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.09021496772766</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.11749958992004</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.15745258331299</t>
+    <t xml:space="preserve">2.0999596118927</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.0902156829834</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.11749982833862</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.15745282173157</t>
   </si>
   <si>
     <t xml:space="preserve">2.01615643501282</t>
   </si>
   <si>
-    <t xml:space="preserve">1.89337408542633</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.83977878093719</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.83393263816833</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.78618371486664</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.96353590488434</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.05221104621887</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.10483169555664</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.09606218338013</t>
+    <t xml:space="preserve">1.89337384700775</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.83977866172791</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.83393228054047</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.78618383407593</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.96353578567505</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.05221080780029</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.10483145713806</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.09606266021729</t>
   </si>
   <si>
     <t xml:space="preserve">2.25684785842896</t>
   </si>
   <si>
-    <t xml:space="preserve">1.70140600204468</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.68386602401733</t>
+    <t xml:space="preserve">1.70140588283539</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.68386578559875</t>
   </si>
   <si>
     <t xml:space="preserve">1.64391231536865</t>
   </si>
   <si>
-    <t xml:space="preserve">1.55426216125488</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.59713900089264</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.52015590667725</t>
+    <t xml:space="preserve">1.55426239967346</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.59713876247406</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.52015602588654</t>
   </si>
   <si>
     <t xml:space="preserve">1.41783809661865</t>
   </si>
   <si>
-    <t xml:space="preserve">1.41881275177002</t>
+    <t xml:space="preserve">1.41881287097931</t>
   </si>
   <si>
     <t xml:space="preserve">1.31746876239777</t>
   </si>
   <si>
-    <t xml:space="preserve">1.25802636146545</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.46168839931488</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.52990090847015</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.65463185310364</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.57180273532867</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.63904082775116</t>
+    <t xml:space="preserve">1.25802648067474</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.46168863773346</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.52990102767944</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.65463197231293</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.57180261611938</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.63904070854187</t>
   </si>
   <si>
     <t xml:space="preserve">1.65852952003479</t>
   </si>
   <si>
-    <t xml:space="preserve">1.66827464103699</t>
+    <t xml:space="preserve">1.6682745218277</t>
   </si>
   <si>
     <t xml:space="preserve">1.65268266201019</t>
   </si>
   <si>
-    <t xml:space="preserve">1.67022299766541</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.72381794452667</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.71115005016327</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.66535031795502</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.67314624786377</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.75012910366058</t>
+    <t xml:space="preserve">1.67022311687469</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.72381806373596</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.71115016937256</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.66535067558289</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.67314612865448</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.75012874603271</t>
   </si>
   <si>
     <t xml:space="preserve">1.69555914402008</t>
   </si>
   <si>
-    <t xml:space="preserve">1.78813302516937</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.68678867816925</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.47825443744659</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.53769636154175</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.54549217224121</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.74720549583435</t>
+    <t xml:space="preserve">1.78813290596008</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.68678879737854</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.4782543182373</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.53769648075104</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.54549193382263</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.74720561504364</t>
   </si>
   <si>
     <t xml:space="preserve">1.715047955513</t>
   </si>
   <si>
-    <t xml:space="preserve">1.74915421009064</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.7384352684021</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.73746109008789</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.71309983730316</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.70043158531189</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.63709151744843</t>
+    <t xml:space="preserve">1.74915432929993</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.73843514919281</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.7374609708786</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.71309947967529</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.70043122768402</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.63709127902985</t>
   </si>
   <si>
     <t xml:space="preserve">1.66632521152496</t>
@@ -506,118 +506,118 @@
     <t xml:space="preserve">1.56985366344452</t>
   </si>
   <si>
-    <t xml:space="preserve">1.58057296276093</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.67119789123535</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.70725226402283</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.65755474567413</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.62344884872437</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.66924870014191</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.68094229698181</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.71212482452393</t>
+    <t xml:space="preserve">1.58057284355164</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.67119753360748</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.70725238323212</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.65755498409271</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.62344896793365</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.66924810409546</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.6809424161911</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.71212494373322</t>
   </si>
   <si>
     <t xml:space="preserve">1.73551166057587</t>
   </si>
   <si>
-    <t xml:space="preserve">1.70432925224304</t>
+    <t xml:space="preserve">1.70432913303375</t>
   </si>
   <si>
     <t xml:space="preserve">1.76182222366333</t>
   </si>
   <si>
-    <t xml:space="preserve">1.76474571228027</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.72966516017914</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.69653332233429</t>
+    <t xml:space="preserve">1.76474559307098</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.72966527938843</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.69653356075287</t>
   </si>
   <si>
     <t xml:space="preserve">1.65170860290527</t>
   </si>
   <si>
-    <t xml:space="preserve">1.5961639881134</t>
+    <t xml:space="preserve">1.59616434574127</t>
   </si>
   <si>
     <t xml:space="preserve">1.620525598526</t>
   </si>
   <si>
-    <t xml:space="preserve">1.5513391494751</t>
+    <t xml:space="preserve">1.55133950710297</t>
   </si>
   <si>
     <t xml:space="preserve">1.62442350387573</t>
   </si>
   <si>
-    <t xml:space="preserve">1.62832117080688</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.55523705482483</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.53087568283081</t>
+    <t xml:space="preserve">1.62832129001617</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.55523693561554</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.53087532520294</t>
   </si>
   <si>
     <t xml:space="preserve">1.56498181819916</t>
   </si>
   <si>
-    <t xml:space="preserve">1.56790518760681</t>
+    <t xml:space="preserve">1.56790506839752</t>
   </si>
   <si>
     <t xml:space="preserve">1.61370468139648</t>
   </si>
   <si>
-    <t xml:space="preserve">1.57667517662048</t>
+    <t xml:space="preserve">1.57667529582977</t>
   </si>
   <si>
     <t xml:space="preserve">1.65073394775391</t>
   </si>
   <si>
-    <t xml:space="preserve">1.65560626983643</t>
+    <t xml:space="preserve">1.65560638904572</t>
   </si>
   <si>
     <t xml:space="preserve">1.63221883773804</t>
   </si>
   <si>
-    <t xml:space="preserve">1.69068670272827</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.7930052280426</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.83295822143555</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.75305199623108</t>
+    <t xml:space="preserve">1.69068658351898</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.79300534725189</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.83295786380768</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.7530517578125</t>
   </si>
   <si>
     <t xml:space="preserve">1.84465098381042</t>
   </si>
   <si>
-    <t xml:space="preserve">1.88362979888916</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.98010146617889</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.07462382316589</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.06975126266479</t>
+    <t xml:space="preserve">1.88363015651703</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.9801013469696</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.07462406158447</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.06975150108337</t>
   </si>
   <si>
     <t xml:space="preserve">2.12237215042114</t>
@@ -632,85 +632,85 @@
     <t xml:space="preserve">2.11555123329163</t>
   </si>
   <si>
-    <t xml:space="preserve">2.10970425605774</t>
+    <t xml:space="preserve">2.10970401763916</t>
   </si>
   <si>
     <t xml:space="preserve">2.08241939544678</t>
   </si>
   <si>
-    <t xml:space="preserve">2.06487941741943</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.9489187002182</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.9245570898056</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.90311884880066</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.96938216686249</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.00641107559204</t>
+    <t xml:space="preserve">2.06487917900085</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.94891846179962</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.92455720901489</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.90311896800995</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.96938228607178</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.0064115524292</t>
   </si>
   <si>
     <t xml:space="preserve">2.03564524650574</t>
   </si>
   <si>
-    <t xml:space="preserve">2.03662014007568</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.01518154144287</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.00543689727783</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.94696938991547</t>
+    <t xml:space="preserve">2.03661966323853</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.01518201828003</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.00543642044067</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.94696915149689</t>
   </si>
   <si>
     <t xml:space="preserve">1.86414003372192</t>
   </si>
   <si>
-    <t xml:space="preserve">1.82613730430603</t>
+    <t xml:space="preserve">1.82613694667816</t>
   </si>
   <si>
     <t xml:space="preserve">1.81834065914154</t>
   </si>
   <si>
-    <t xml:space="preserve">1.85537087917328</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.84562563896179</t>
+    <t xml:space="preserve">1.85537099838257</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.84562587738037</t>
   </si>
   <si>
     <t xml:space="preserve">1.85147213935852</t>
   </si>
   <si>
-    <t xml:space="preserve">1.82321286201477</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.84660053253174</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.99471795558929</t>
+    <t xml:space="preserve">1.82321321964264</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.84660041332245</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.99471807479858</t>
   </si>
   <si>
     <t xml:space="preserve">1.9547655582428</t>
   </si>
   <si>
-    <t xml:space="preserve">2.08729219436646</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.3045961856842</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.33772730827332</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.30167269706726</t>
+    <t xml:space="preserve">2.0872917175293</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.30459594726562</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.33772778511047</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.30167293548584</t>
   </si>
   <si>
     <t xml:space="preserve">2.34454917907715</t>
@@ -719,25 +719,25 @@
     <t xml:space="preserve">2.39424681663513</t>
   </si>
   <si>
-    <t xml:space="preserve">2.35526776313782</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.41860818862915</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.43858432769775</t>
+    <t xml:space="preserve">2.3552680015564</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.41860747337341</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.43858456611633</t>
   </si>
   <si>
     <t xml:space="preserve">2.42153143882751</t>
   </si>
   <si>
-    <t xml:space="preserve">2.43614864349365</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.48974394798279</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.51410508155823</t>
+    <t xml:space="preserve">2.43614816665649</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.48974370956421</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.51410484313965</t>
   </si>
   <si>
     <t xml:space="preserve">2.52141332626343</t>
@@ -752,13 +752,13 @@
     <t xml:space="preserve">2.66514587402344</t>
   </si>
   <si>
-    <t xml:space="preserve">2.62129521369934</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.58231639862061</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.45320129394531</t>
+    <t xml:space="preserve">2.6212956905365</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.58231663703918</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.45320153236389</t>
   </si>
   <si>
     <t xml:space="preserve">2.44102025032043</t>
@@ -770,7 +770,7 @@
     <t xml:space="preserve">2.56282782554626</t>
   </si>
   <si>
-    <t xml:space="preserve">2.60424256324768</t>
+    <t xml:space="preserve">2.6042423248291</t>
   </si>
   <si>
     <t xml:space="preserve">2.61398720741272</t>
@@ -782,58 +782,58 @@
     <t xml:space="preserve">2.79913425445557</t>
   </si>
   <si>
-    <t xml:space="preserve">2.73335814476013</t>
+    <t xml:space="preserve">2.73335862159729</t>
   </si>
   <si>
     <t xml:space="preserve">2.74066662788391</t>
   </si>
   <si>
-    <t xml:space="preserve">2.77477312088013</t>
+    <t xml:space="preserve">2.77477288246155</t>
   </si>
   <si>
     <t xml:space="preserve">2.73092246055603</t>
   </si>
   <si>
-    <t xml:space="preserve">2.60180640220642</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.55308318138123</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.61155033111572</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.6237313747406</t>
+    <t xml:space="preserve">2.601806640625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.5530834197998</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.6115505695343</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.62373113632202</t>
   </si>
   <si>
     <t xml:space="preserve">2.68707156181335</t>
   </si>
   <si>
-    <t xml:space="preserve">2.53359389305115</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.44589257240295</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.47512674331665</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.31726408004761</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.32505989074707</t>
+    <t xml:space="preserve">2.53359413146973</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.44589233398438</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.47512626647949</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.31726384162903</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.32505941390991</t>
   </si>
   <si>
     <t xml:space="preserve">2.4049654006958</t>
   </si>
   <si>
-    <t xml:space="preserve">2.34357476234436</t>
+    <t xml:space="preserve">2.34357452392578</t>
   </si>
   <si>
     <t xml:space="preserve">2.26269388198853</t>
   </si>
   <si>
-    <t xml:space="preserve">2.19253301620483</t>
+    <t xml:space="preserve">2.19253325462341</t>
   </si>
   <si>
     <t xml:space="preserve">2.16914653778076</t>
@@ -851,37 +851,37 @@
     <t xml:space="preserve">2.01713109016418</t>
   </si>
   <si>
-    <t xml:space="preserve">2.18278908729553</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.1915590763092</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.28997921943665</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.227614402771</t>
+    <t xml:space="preserve">2.18278884887695</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.19155931472778</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.2899796962738</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.22761416435242</t>
   </si>
   <si>
     <t xml:space="preserve">2.13406562805176</t>
   </si>
   <si>
-    <t xml:space="preserve">2.13893795013428</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.21007370948792</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.28218412399292</t>
+    <t xml:space="preserve">2.13893747329712</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.21007347106934</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.28218364715576</t>
   </si>
   <si>
     <t xml:space="preserve">2.24417996406555</t>
   </si>
   <si>
-    <t xml:space="preserve">2.18668675422668</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.19058442115784</t>
+    <t xml:space="preserve">2.18668699264526</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.19058465957642</t>
   </si>
   <si>
     <t xml:space="preserve">2.29972386360168</t>
@@ -896,46 +896,46 @@
     <t xml:space="preserve">2.34942150115967</t>
   </si>
   <si>
-    <t xml:space="preserve">2.41568470001221</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.38839936256409</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.34552335739136</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.3601405620575</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.31629014015198</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.28510665893555</t>
+    <t xml:space="preserve">2.41568493843079</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.38839960098267</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.34552311897278</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.36014032363892</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.3162899017334</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.28510689735413</t>
   </si>
   <si>
     <t xml:space="preserve">2.28023457527161</t>
   </si>
   <si>
-    <t xml:space="preserve">2.20032858848572</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.21689438819885</t>
+    <t xml:space="preserve">2.2003288269043</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.21689462661743</t>
   </si>
   <si>
     <t xml:space="preserve">2.21494603157043</t>
   </si>
   <si>
-    <t xml:space="preserve">2.23151159286499</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.19545698165894</t>
+    <t xml:space="preserve">2.23151183128357</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.19545722007751</t>
   </si>
   <si>
     <t xml:space="preserve">2.14283561706543</t>
   </si>
   <si>
-    <t xml:space="preserve">2.12529611587524</t>
+    <t xml:space="preserve">2.12529635429382</t>
   </si>
   <si>
     <t xml:space="preserve">2.23346042633057</t>
@@ -947,7 +947,7 @@
     <t xml:space="preserve">2.4225058555603</t>
   </si>
   <si>
-    <t xml:space="preserve">2.36988520622253</t>
+    <t xml:space="preserve">2.36988568305969</t>
   </si>
   <si>
     <t xml:space="preserve">2.44345688819885</t>
@@ -968,7 +968,7 @@
     <t xml:space="preserve">2.32116174697876</t>
   </si>
   <si>
-    <t xml:space="preserve">2.28413271903992</t>
+    <t xml:space="preserve">2.28413248062134</t>
   </si>
   <si>
     <t xml:space="preserve">2.3679358959198</t>
@@ -977,31 +977,31 @@
     <t xml:space="preserve">2.32895731925964</t>
   </si>
   <si>
-    <t xml:space="preserve">2.27536177635193</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.24905228614807</t>
+    <t xml:space="preserve">2.27536201477051</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.24905204772949</t>
   </si>
   <si>
     <t xml:space="preserve">2.28315830230713</t>
   </si>
   <si>
-    <t xml:space="preserve">2.27230000495911</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.27328705787659</t>
+    <t xml:space="preserve">2.27229976654053</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.27328729629517</t>
   </si>
   <si>
     <t xml:space="preserve">2.30487394332886</t>
   </si>
   <si>
-    <t xml:space="preserve">2.301913022995</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.27526092529297</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.20616459846497</t>
+    <t xml:space="preserve">2.30191254615784</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.27526116371155</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.20616436004639</t>
   </si>
   <si>
     <t xml:space="preserve">2.20715165138245</t>
@@ -1010,16 +1010,16 @@
     <t xml:space="preserve">2.15187430381775</t>
   </si>
   <si>
-    <t xml:space="preserve">2.19728088378906</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.16964221000671</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.1301577091217</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.09758400917053</t>
+    <t xml:space="preserve">2.1972804069519</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.16964197158813</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.13015794754028</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.09758353233337</t>
   </si>
   <si>
     <t xml:space="preserve">2.10153198242188</t>
@@ -1028,34 +1028,34 @@
     <t xml:space="preserve">2.17951273918152</t>
   </si>
   <si>
-    <t xml:space="preserve">2.17260336875916</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.12719678878784</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.18050003051758</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.15878391265869</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.06106090545654</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.07389307022095</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.02058982849121</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.11140275001526</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.10251927375793</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.15779638290405</t>
+    <t xml:space="preserve">2.17260313034058</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.12719655036926</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.180499792099</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.15878367424011</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.06106066703796</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.07389283180237</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.02059006690979</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.1114022731781</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.10251951217651</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.15779662132263</t>
   </si>
   <si>
     <t xml:space="preserve">2.17062854766846</t>
@@ -1067,25 +1067,25 @@
     <t xml:space="preserve">2.17852520942688</t>
   </si>
   <si>
-    <t xml:space="preserve">2.15483522415161</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.29401659965515</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.37199640274048</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.31474494934082</t>
+    <t xml:space="preserve">2.15483546257019</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.29401612281799</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.37199664115906</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.3147451877594</t>
   </si>
   <si>
     <t xml:space="preserve">2.32066798210144</t>
   </si>
   <si>
-    <t xml:space="preserve">2.31375813484192</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.34534549713135</t>
+    <t xml:space="preserve">2.31375789642334</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.34534573554993</t>
   </si>
   <si>
     <t xml:space="preserve">2.38779091835022</t>
@@ -1094,13 +1094,13 @@
     <t xml:space="preserve">2.43813300132751</t>
   </si>
   <si>
-    <t xml:space="preserve">2.44504237174988</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.44306826591492</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.45787453651428</t>
+    <t xml:space="preserve">2.4450421333313</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.4430685043335</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.4578742980957</t>
   </si>
   <si>
     <t xml:space="preserve">2.3779194355011</t>
@@ -1115,7 +1115,7 @@
     <t xml:space="preserve">2.30388736724854</t>
   </si>
   <si>
-    <t xml:space="preserve">2.27624821662903</t>
+    <t xml:space="preserve">2.27624797821045</t>
   </si>
   <si>
     <t xml:space="preserve">2.30980944633484</t>
@@ -1124,19 +1124,19 @@
     <t xml:space="preserve">2.32165479660034</t>
   </si>
   <si>
-    <t xml:space="preserve">2.29598999023438</t>
+    <t xml:space="preserve">2.29599022865295</t>
   </si>
   <si>
     <t xml:space="preserve">2.29204154014587</t>
   </si>
   <si>
-    <t xml:space="preserve">2.33646130561829</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.47761631011963</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.44405484199524</t>
+    <t xml:space="preserve">2.33646154403687</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.47761607170105</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.44405460357666</t>
   </si>
   <si>
     <t xml:space="preserve">2.42628765106201</t>
@@ -1145,73 +1145,73 @@
     <t xml:space="preserve">2.34040999412537</t>
   </si>
   <si>
-    <t xml:space="preserve">2.41839051246643</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.40753269195557</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.38088059425354</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.34929394721985</t>
+    <t xml:space="preserve">2.41839027404785</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.40753245353699</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.38088035583496</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.34929370880127</t>
   </si>
   <si>
     <t xml:space="preserve">2.31968092918396</t>
   </si>
   <si>
-    <t xml:space="preserve">2.34238362312317</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.35225486755371</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.29105496406555</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.31573295593262</t>
+    <t xml:space="preserve">2.34238338470459</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.35225510597229</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.29105472564697</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.31573247909546</t>
   </si>
   <si>
     <t xml:space="preserve">2.33547425270081</t>
   </si>
   <si>
-    <t xml:space="preserve">2.36706209182739</t>
+    <t xml:space="preserve">2.36706161499023</t>
   </si>
   <si>
     <t xml:space="preserve">2.33152556419373</t>
   </si>
   <si>
-    <t xml:space="preserve">2.29500365257263</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.25551915168762</t>
+    <t xml:space="preserve">2.29500341415405</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.2555193901062</t>
   </si>
   <si>
     <t xml:space="preserve">2.23577737808228</t>
   </si>
   <si>
-    <t xml:space="preserve">2.29993891716003</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.37101030349731</t>
+    <t xml:space="preserve">2.29993915557861</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.37101006507874</t>
   </si>
   <si>
     <t xml:space="preserve">2.32362937927246</t>
   </si>
   <si>
-    <t xml:space="preserve">2.26440358161926</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.28513193130493</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.31277132034302</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.36113858222961</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.30882263183594</t>
+    <t xml:space="preserve">2.26440286636353</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.28513240814209</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.31277108192444</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.36113882064819</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.30882239341736</t>
   </si>
   <si>
     <t xml:space="preserve">2.37693214416504</t>
@@ -1226,13 +1226,13 @@
     <t xml:space="preserve">2.49735879898071</t>
   </si>
   <si>
-    <t xml:space="preserve">2.53931069374084</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.53190636634827</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.45688700675964</t>
+    <t xml:space="preserve">2.53931045532227</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.53190660476685</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.45688724517822</t>
   </si>
   <si>
     <t xml:space="preserve">2.41542935371399</t>
@@ -1241,7 +1241,7 @@
     <t xml:space="preserve">2.28414487838745</t>
   </si>
   <si>
-    <t xml:space="preserve">2.21702218055725</t>
+    <t xml:space="preserve">2.21702194213867</t>
   </si>
   <si>
     <t xml:space="preserve">2.16865468025208</t>
@@ -1259,40 +1259,40 @@
     <t xml:space="preserve">2.09264826774597</t>
   </si>
   <si>
-    <t xml:space="preserve">2.09955763816833</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.12028646469116</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.09659647941589</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.06402254104614</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.07488036155701</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.06500887870789</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.05908703804016</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.13410592079163</t>
+    <t xml:space="preserve">2.09955739974976</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.12028670310974</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.09659624099731</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.06402230262756</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.07488012313843</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.06500935554504</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.05908679962158</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.13410615921021</t>
   </si>
   <si>
     <t xml:space="preserve">2.07981586456299</t>
   </si>
   <si>
-    <t xml:space="preserve">2.04625463485718</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.00775742530823</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.91990602016449</t>
+    <t xml:space="preserve">2.0462543964386</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.00775766372681</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.91990613937378</t>
   </si>
   <si>
     <t xml:space="preserve">2.11041617393494</t>
@@ -1301,10 +1301,10 @@
     <t xml:space="preserve">2.08771276473999</t>
   </si>
   <si>
-    <t xml:space="preserve">2.10646772384644</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.06007432937622</t>
+    <t xml:space="preserve">2.10646820068359</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.06007385253906</t>
   </si>
   <si>
     <t xml:space="preserve">2.10350584983826</t>
@@ -1313,10 +1313,10 @@
     <t xml:space="preserve">2.03342223167419</t>
   </si>
   <si>
-    <t xml:space="preserve">2.06698393821716</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.03835797309875</t>
+    <t xml:space="preserve">2.06698346138</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.03835773468018</t>
   </si>
   <si>
     <t xml:space="preserve">2.02651262283325</t>
@@ -1334,10 +1334,10 @@
     <t xml:space="preserve">2.20122885704041</t>
   </si>
   <si>
-    <t xml:space="preserve">2.2604546546936</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.24860978126526</t>
+    <t xml:space="preserve">2.26045489311218</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.24861025810242</t>
   </si>
   <si>
     <t xml:space="preserve">2.22097063064575</t>
@@ -1346,40 +1346,40 @@
     <t xml:space="preserve">2.29302906990051</t>
   </si>
   <si>
-    <t xml:space="preserve">2.23972582817078</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.0985701084137</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.05711221694946</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.05119013786316</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.11929988861084</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.10745453834534</t>
+    <t xml:space="preserve">2.2397255897522</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.09857034683228</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.05711245536804</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.05119037628174</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.11930012702942</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.10745429992676</t>
   </si>
   <si>
     <t xml:space="preserve">2.10942888259888</t>
   </si>
   <si>
-    <t xml:space="preserve">2.06797122955322</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.07882857322693</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.1360809803009</t>
+    <t xml:space="preserve">2.06797075271606</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.07882833480835</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.13608074188232</t>
   </si>
   <si>
     <t xml:space="preserve">2.07784128189087</t>
   </si>
   <si>
-    <t xml:space="preserve">2.05316424369812</t>
+    <t xml:space="preserve">2.05316400527954</t>
   </si>
   <si>
     <t xml:space="preserve">2.09363532066345</t>
@@ -1394,16 +1394,16 @@
     <t xml:space="preserve">2.22788071632385</t>
   </si>
   <si>
-    <t xml:space="preserve">2.25058388710022</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.22590613365173</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.18247389793396</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.37594485282898</t>
+    <t xml:space="preserve">2.25058364868164</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.22590637207031</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.18247365951538</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.37594509124756</t>
   </si>
   <si>
     <t xml:space="preserve">2.37397122383118</t>
@@ -1412,28 +1412,28 @@
     <t xml:space="preserve">2.39124536514282</t>
   </si>
   <si>
-    <t xml:space="preserve">2.29944539070129</t>
+    <t xml:space="preserve">2.29944515228271</t>
   </si>
   <si>
     <t xml:space="preserve">2.31819987297058</t>
   </si>
   <si>
-    <t xml:space="preserve">2.3004322052002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.23775124549866</t>
+    <t xml:space="preserve">2.30043196678162</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.23775148391724</t>
   </si>
   <si>
     <t xml:space="preserve">2.2461416721344</t>
   </si>
   <si>
-    <t xml:space="preserve">2.32461619377136</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.27427434921265</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.24416780471802</t>
+    <t xml:space="preserve">2.32461643218994</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.2742748260498</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.24416756629944</t>
   </si>
   <si>
     <t xml:space="preserve">2.36064505577087</t>
@@ -1448,13 +1448,13 @@
     <t xml:space="preserve">2.35916423797607</t>
   </si>
   <si>
-    <t xml:space="preserve">2.31227779388428</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.40012955665588</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.4006233215332</t>
+    <t xml:space="preserve">2.31227803230286</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.4001293182373</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.40062308311462</t>
   </si>
   <si>
     <t xml:space="preserve">2.40506505966187</t>
@@ -1466,46 +1466,46 @@
     <t xml:space="preserve">2.43122291564941</t>
   </si>
   <si>
-    <t xml:space="preserve">2.41098713874817</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.22738695144653</t>
+    <t xml:space="preserve">2.41098737716675</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.22738718986511</t>
   </si>
   <si>
     <t xml:space="preserve">2.3186936378479</t>
   </si>
   <si>
-    <t xml:space="preserve">2.35028100013733</t>
+    <t xml:space="preserve">2.35028123855591</t>
   </si>
   <si>
     <t xml:space="preserve">2.27674198150635</t>
   </si>
   <si>
-    <t xml:space="preserve">2.31918692588806</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.26687049865723</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.27131271362305</t>
+    <t xml:space="preserve">2.31918716430664</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.26687073707581</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.27131247520447</t>
   </si>
   <si>
     <t xml:space="preserve">2.29796457290649</t>
   </si>
   <si>
-    <t xml:space="preserve">2.30586123466492</t>
+    <t xml:space="preserve">2.30586099624634</t>
   </si>
   <si>
     <t xml:space="preserve">2.29006767272949</t>
   </si>
   <si>
-    <t xml:space="preserve">2.24564743041992</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.25206446647644</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.23232293128967</t>
+    <t xml:space="preserve">2.24564814567566</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.25206422805786</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.23232245445251</t>
   </si>
   <si>
     <t xml:space="preserve">2.2476224899292</t>
@@ -1514,58 +1514,58 @@
     <t xml:space="preserve">2.22886729240417</t>
   </si>
   <si>
-    <t xml:space="preserve">2.23084163665771</t>
+    <t xml:space="preserve">2.23084187507629</t>
   </si>
   <si>
     <t xml:space="preserve">2.31721258163452</t>
   </si>
   <si>
-    <t xml:space="preserve">2.32560300827026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.33448696136475</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.35817766189575</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.40851998329163</t>
+    <t xml:space="preserve">2.32560324668884</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.33448719978333</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.35817790031433</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.40851974487305</t>
   </si>
   <si>
     <t xml:space="preserve">2.37989401817322</t>
   </si>
   <si>
-    <t xml:space="preserve">2.38630986213684</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.41197443008423</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.36804819107056</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.33843517303467</t>
+    <t xml:space="preserve">2.38630962371826</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.41197419166565</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.36804866790771</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.33843541145325</t>
   </si>
   <si>
     <t xml:space="preserve">2.35324215888977</t>
   </si>
   <si>
-    <t xml:space="preserve">2.34189057350159</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.35373544692993</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.33596777915955</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.32856464385986</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.42036461830139</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.42924857139587</t>
+    <t xml:space="preserve">2.34189081192017</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.35373592376709</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.33596801757812</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.32856488227844</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.42036485671997</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.42924880981445</t>
   </si>
   <si>
     <t xml:space="preserve">2.47662973403931</t>
@@ -1574,58 +1574,58 @@
     <t xml:space="preserve">2.5121648311615</t>
   </si>
   <si>
-    <t xml:space="preserve">2.54079055786133</t>
+    <t xml:space="preserve">2.54079031944275</t>
   </si>
   <si>
     <t xml:space="preserve">2.46626472473145</t>
   </si>
   <si>
-    <t xml:space="preserve">2.46675825119019</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.30290031433105</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.32412981987</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.36153411865234</t>
+    <t xml:space="preserve">2.46675848960876</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.30290007591248</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.32412958145142</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.36153388023376</t>
   </si>
   <si>
     <t xml:space="preserve">2.38731265068054</t>
   </si>
   <si>
-    <t xml:space="preserve">2.35799551010132</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.31048202514648</t>
+    <t xml:space="preserve">2.3579957485199</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.31048178672791</t>
   </si>
   <si>
     <t xml:space="preserve">2.1755223274231</t>
   </si>
   <si>
-    <t xml:space="preserve">2.06583690643311</t>
+    <t xml:space="preserve">2.06583666801453</t>
   </si>
   <si>
     <t xml:space="preserve">2.07341861724854</t>
   </si>
   <si>
-    <t xml:space="preserve">2.07392430305481</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.23718929290771</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.17147874832153</t>
+    <t xml:space="preserve">2.07392454147339</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.23718953132629</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.17147898674011</t>
   </si>
   <si>
     <t xml:space="preserve">2.09768056869507</t>
   </si>
   <si>
-    <t xml:space="preserve">2.09667038917542</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.13710737228394</t>
+    <t xml:space="preserve">2.09667062759399</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.13710689544678</t>
   </si>
   <si>
     <t xml:space="preserve">2.07948422431946</t>
@@ -1637,64 +1637,64 @@
     <t xml:space="preserve">2.1957414150238</t>
   </si>
   <si>
-    <t xml:space="preserve">2.23112392425537</t>
+    <t xml:space="preserve">2.23112368583679</t>
   </si>
   <si>
     <t xml:space="preserve">2.25841903686523</t>
   </si>
   <si>
-    <t xml:space="preserve">2.19927930831909</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.18866491317749</t>
+    <t xml:space="preserve">2.19927978515625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.18866443634033</t>
   </si>
   <si>
     <t xml:space="preserve">2.26296806335449</t>
   </si>
   <si>
-    <t xml:space="preserve">2.32008576393127</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.25184798240662</t>
+    <t xml:space="preserve">2.3200855255127</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.25184845924377</t>
   </si>
   <si>
     <t xml:space="preserve">2.41764068603516</t>
   </si>
   <si>
-    <t xml:space="preserve">2.36810517311096</t>
+    <t xml:space="preserve">2.36810541152954</t>
   </si>
   <si>
     <t xml:space="preserve">2.38124752044678</t>
   </si>
   <si>
-    <t xml:space="preserve">2.34738063812256</t>
+    <t xml:space="preserve">2.34738039970398</t>
   </si>
   <si>
     <t xml:space="preserve">2.36861085891724</t>
   </si>
   <si>
-    <t xml:space="preserve">2.37922501564026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.37012672424316</t>
+    <t xml:space="preserve">2.37922525405884</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.37012696266174</t>
   </si>
   <si>
     <t xml:space="preserve">2.37265467643738</t>
   </si>
   <si>
-    <t xml:space="preserve">2.3635561466217</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.41005849838257</t>
+    <t xml:space="preserve">2.36355590820312</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.41005873680115</t>
   </si>
   <si>
     <t xml:space="preserve">2.41814613342285</t>
   </si>
   <si>
-    <t xml:space="preserve">2.37113809585571</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.331711769104</t>
+    <t xml:space="preserve">2.37113785743713</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.33171153068542</t>
   </si>
   <si>
     <t xml:space="preserve">2.34788608551025</t>
@@ -1721,43 +1721,43 @@
     <t xml:space="preserve">2.4065203666687</t>
   </si>
   <si>
-    <t xml:space="preserve">2.38276314735413</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.41662979125977</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.40550923347473</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.31958031654358</t>
+    <t xml:space="preserve">2.38276338577271</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.41662931442261</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.40550971031189</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.31958055496216</t>
   </si>
   <si>
     <t xml:space="preserve">2.31351447105408</t>
   </si>
   <si>
-    <t xml:space="preserve">2.31503105163574</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.33524918556213</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.19725751876831</t>
+    <t xml:space="preserve">2.31503129005432</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.33524966239929</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.19725775718689</t>
   </si>
   <si>
     <t xml:space="preserve">2.1724898815155</t>
   </si>
   <si>
-    <t xml:space="preserve">2.14216208457947</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.08908748626709</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.06937503814697</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.06684803962708</t>
+    <t xml:space="preserve">2.14216184616089</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.08908796310425</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.06937527656555</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.0668478012085</t>
   </si>
   <si>
     <t xml:space="preserve">2.02186131477356</t>
@@ -1766,70 +1766,70 @@
     <t xml:space="preserve">2.02236676216125</t>
   </si>
   <si>
-    <t xml:space="preserve">2.06735301017761</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.0663423538208</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.05016708374023</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.04511284828186</t>
+    <t xml:space="preserve">2.06735277175903</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.06634259223938</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.05016660690308</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.04511260986328</t>
   </si>
   <si>
     <t xml:space="preserve">2.03702569007874</t>
   </si>
   <si>
-    <t xml:space="preserve">2.00416970252991</t>
+    <t xml:space="preserve">2.00416994094849</t>
   </si>
   <si>
     <t xml:space="preserve">2.01680636405945</t>
   </si>
   <si>
-    <t xml:space="preserve">1.94098687171936</t>
+    <t xml:space="preserve">1.94098675251007</t>
   </si>
   <si>
     <t xml:space="preserve">1.9202629327774</t>
   </si>
   <si>
-    <t xml:space="preserve">1.92936158180237</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.00012612342834</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.08554983139038</t>
+    <t xml:space="preserve">1.92936134338379</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.00012588500977</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.0855495929718</t>
   </si>
   <si>
     <t xml:space="preserve">2.08959341049194</t>
   </si>
   <si>
-    <t xml:space="preserve">2.14519429206848</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.13458013534546</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.13660144805908</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.12952542304993</t>
+    <t xml:space="preserve">2.14519500732422</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.13457989692688</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.13660168647766</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.12952518463135</t>
   </si>
   <si>
     <t xml:space="preserve">2.178555727005</t>
   </si>
   <si>
-    <t xml:space="preserve">2.2114109992981</t>
+    <t xml:space="preserve">2.21141052246094</t>
   </si>
   <si>
     <t xml:space="preserve">2.19068670272827</t>
   </si>
   <si>
-    <t xml:space="preserve">2.14873337745667</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.17350077629089</t>
+    <t xml:space="preserve">2.14873361587524</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.17350101470947</t>
   </si>
   <si>
     <t xml:space="preserve">2.20029067993164</t>
@@ -1841,58 +1841,58 @@
     <t xml:space="preserve">2.01579546928406</t>
   </si>
   <si>
-    <t xml:space="preserve">1.93643760681152</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.90257167816162</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.8778030872345</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.8894294500351</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.85505771636963</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.82422435283661</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.7878303527832</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.8267514705658</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.79237985610962</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.80602729320526</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.8186639547348</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.80299496650696</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.80552172660828</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.76660084724426</t>
+    <t xml:space="preserve">1.93643748760223</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.90257155895233</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.87780320644379</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.88942933082581</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.85505783557892</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.82422399520874</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.78783047199249</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.82675123214722</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.79237961769104</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.80602705478668</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.81866383552551</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.80299472808838</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.80552184581757</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.76660108566284</t>
   </si>
   <si>
     <t xml:space="preserve">1.77317225933075</t>
   </si>
   <si>
-    <t xml:space="preserve">1.70847272872925</t>
+    <t xml:space="preserve">1.70847284793854</t>
   </si>
   <si>
     <t xml:space="preserve">1.67157351970673</t>
   </si>
   <si>
-    <t xml:space="preserve">1.62405967712402</t>
+    <t xml:space="preserve">1.62405955791473</t>
   </si>
   <si>
     <t xml:space="preserve">1.66146457195282</t>
@@ -1907,22 +1907,22 @@
     <t xml:space="preserve">1.71150529384613</t>
   </si>
   <si>
-    <t xml:space="preserve">1.69735193252563</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.70746171474457</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.77671039104462</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.71554911136627</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.70291221141815</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.73374617099762</t>
+    <t xml:space="preserve">1.69735205173492</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.70746183395386</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.77671051025391</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.71554923057556</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.70291244983673</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.73374593257904</t>
   </si>
   <si>
     <t xml:space="preserve">1.74688816070557</t>
@@ -1931,25 +1931,25 @@
     <t xml:space="preserve">1.76255738735199</t>
   </si>
   <si>
-    <t xml:space="preserve">1.76508474349976</t>
+    <t xml:space="preserve">1.76508498191833</t>
   </si>
   <si>
     <t xml:space="preserve">1.71352756023407</t>
   </si>
   <si>
-    <t xml:space="preserve">1.72767996788025</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.69634175300598</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.71201109886169</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.69229781627655</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.75345897674561</t>
+    <t xml:space="preserve">1.72768032550812</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.69634163379669</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.7120109796524</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.69229793548584</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.75345873832703</t>
   </si>
   <si>
     <t xml:space="preserve">1.76356852054596</t>
@@ -1958,19 +1958,19 @@
     <t xml:space="preserve">1.76457953453064</t>
   </si>
   <si>
-    <t xml:space="preserve">1.85910141468048</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.79389655590057</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.81007158756256</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.8191694021225</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.90307724475861</t>
+    <t xml:space="preserve">1.85910165309906</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.79389631748199</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.81007146835327</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.81916928291321</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.9030773639679</t>
   </si>
   <si>
     <t xml:space="preserve">1.87072694301605</t>
@@ -1982,7 +1982,7 @@
     <t xml:space="preserve">1.84494829177856</t>
   </si>
   <si>
-    <t xml:space="preserve">1.81563127040863</t>
+    <t xml:space="preserve">1.81563138961792</t>
   </si>
   <si>
     <t xml:space="preserve">1.7847980260849</t>
@@ -1991,10 +1991,10 @@
     <t xml:space="preserve">1.76761209964752</t>
   </si>
   <si>
-    <t xml:space="preserve">1.76053595542908</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.73324048519135</t>
+    <t xml:space="preserve">1.7605357170105</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.73324036598206</t>
   </si>
   <si>
     <t xml:space="preserve">1.69937455654144</t>
@@ -2003,7 +2003,7 @@
     <t xml:space="preserve">1.69128704071045</t>
   </si>
   <si>
-    <t xml:space="preserve">1.72565877437592</t>
+    <t xml:space="preserve">1.72565853595734</t>
   </si>
   <si>
     <t xml:space="preserve">1.69280290603638</t>
@@ -2012,22 +2012,22 @@
     <t xml:space="preserve">1.68016636371613</t>
   </si>
   <si>
-    <t xml:space="preserve">1.65742075443268</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.70038557052612</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.66601383686066</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.65489315986633</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.71049416065216</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.72110950946808</t>
+    <t xml:space="preserve">1.65742087364197</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.70038545131683</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.66601395606995</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.65489339828491</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.71049427986145</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.72110939025879</t>
   </si>
   <si>
     <t xml:space="preserve">1.68319976329803</t>
@@ -2036,70 +2036,70 @@
     <t xml:space="preserve">1.67612254619598</t>
   </si>
   <si>
-    <t xml:space="preserve">1.6811774969101</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.65287172794342</t>
+    <t xml:space="preserve">1.68117761611938</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.652871966362</t>
   </si>
   <si>
     <t xml:space="preserve">1.58918249607086</t>
   </si>
   <si>
-    <t xml:space="preserve">1.51386857032776</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.54722917079926</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.55329489707947</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.54419648647308</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.55228364467621</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.5436909198761</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.52094495296478</t>
+    <t xml:space="preserve">1.51386845111847</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.54722905158997</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.55329501628876</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.54419636726379</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.55228388309479</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.54369115829468</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.52094483375549</t>
   </si>
   <si>
     <t xml:space="preserve">1.52549397945404</t>
   </si>
   <si>
-    <t xml:space="preserve">1.59221577644348</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.57300770282745</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.57705128192902</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.59069907665253</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.49415564537048</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.49870407581329</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.50123178958893</t>
+    <t xml:space="preserve">1.59221589565277</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.57300758361816</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.57705140113831</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.59069895744324</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.49415552616119</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.49870419502258</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.50123190879822</t>
   </si>
   <si>
     <t xml:space="preserve">1.50375890731812</t>
   </si>
   <si>
-    <t xml:space="preserve">1.53914165496826</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.52347242832184</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.65792655944824</t>
+    <t xml:space="preserve">1.53914153575897</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.52347254753113</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.65792632102966</t>
   </si>
   <si>
     <t xml:space="preserve">1.7266697883606</t>
@@ -2108,130 +2108,130 @@
     <t xml:space="preserve">1.70897817611694</t>
   </si>
   <si>
-    <t xml:space="preserve">1.70240688323975</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.78125977516174</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.7741836309433</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.75901925563812</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.73071348667145</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.75093185901642</t>
+    <t xml:space="preserve">1.70240700244904</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.78125989437103</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.77418351173401</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.75901937484741</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.73071336746216</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.75093197822571</t>
   </si>
   <si>
     <t xml:space="preserve">1.76862335205078</t>
   </si>
   <si>
-    <t xml:space="preserve">1.78024852275848</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.82826769351959</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.8692102432251</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.8641562461853</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.8580904006958</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.87325477600098</t>
+    <t xml:space="preserve">1.78024864196777</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.82826781272888</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.86921036243439</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.86415612697601</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.85809051990509</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.8732545375824</t>
   </si>
   <si>
     <t xml:space="preserve">1.81815826892853</t>
   </si>
   <si>
-    <t xml:space="preserve">1.79945683479309</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.78833603858948</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.79895102977753</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.83534407615662</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.87224364280701</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.8863959312439</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.88690161705017</t>
+    <t xml:space="preserve">1.7994567155838</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.78833591938019</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.79895126819611</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.8353443145752</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.87224388122559</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.88639605045319</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.88690173625946</t>
   </si>
   <si>
     <t xml:space="preserve">1.87022149562836</t>
   </si>
   <si>
-    <t xml:space="preserve">1.84444260597229</t>
+    <t xml:space="preserve">1.84444272518158</t>
   </si>
   <si>
     <t xml:space="preserve">1.83686065673828</t>
   </si>
   <si>
-    <t xml:space="preserve">1.82119166851044</t>
+    <t xml:space="preserve">1.82119154930115</t>
   </si>
   <si>
     <t xml:space="preserve">1.8500030040741</t>
   </si>
   <si>
-    <t xml:space="preserve">1.84242141246796</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.84039902687073</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.86567223072052</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.85151958465576</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.86971580982208</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.87173795700073</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.88791286945343</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.88892352581024</t>
+    <t xml:space="preserve">1.84242105484009</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.8403993844986</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.8656724691391</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.85151970386505</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.86971592903137</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.87173807621002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.88791263103485</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.8889240026474</t>
   </si>
   <si>
     <t xml:space="preserve">1.91874635219574</t>
   </si>
   <si>
-    <t xml:space="preserve">1.95463466644287</t>
+    <t xml:space="preserve">1.95463454723358</t>
   </si>
   <si>
     <t xml:space="preserve">2.00619196891785</t>
   </si>
   <si>
-    <t xml:space="preserve">2.04005837440491</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.0941424369812</t>
+    <t xml:space="preserve">2.04005789756775</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.09414267539978</t>
   </si>
   <si>
     <t xml:space="preserve">2.11436152458191</t>
   </si>
   <si>
-    <t xml:space="preserve">2.09363722801208</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.07544112205505</t>
+    <t xml:space="preserve">2.09363698959351</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.0754406452179</t>
   </si>
   <si>
     <t xml:space="preserve">2.10930681228638</t>
@@ -2243,16 +2243,16 @@
     <t xml:space="preserve">2.13255786895752</t>
   </si>
   <si>
-    <t xml:space="preserve">2.16541361808777</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.1305365562439</t>
+    <t xml:space="preserve">2.16541337966919</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.13053631782532</t>
   </si>
   <si>
     <t xml:space="preserve">2.12396478652954</t>
   </si>
   <si>
-    <t xml:space="preserve">2.07998991012573</t>
+    <t xml:space="preserve">2.07999014854431</t>
   </si>
   <si>
     <t xml:space="preserve">2.068363904953</t>
@@ -2261,7 +2261,7 @@
     <t xml:space="preserve">2.02388334274292</t>
   </si>
   <si>
-    <t xml:space="preserve">2.00164270401001</t>
+    <t xml:space="preserve">2.00164294242859</t>
   </si>
   <si>
     <t xml:space="preserve">1.97131478786469</t>
@@ -2270,7 +2270,7 @@
     <t xml:space="preserve">1.98900628089905</t>
   </si>
   <si>
-    <t xml:space="preserve">1.95412886142731</t>
+    <t xml:space="preserve">1.95412874221802</t>
   </si>
   <si>
     <t xml:space="preserve">1.99810469150543</t>
@@ -2279,34 +2279,34 @@
     <t xml:space="preserve">1.94467711448669</t>
   </si>
   <si>
-    <t xml:space="preserve">1.89345955848694</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.85321760177612</t>
+    <t xml:space="preserve">1.89345943927765</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.85321772098541</t>
   </si>
   <si>
     <t xml:space="preserve">1.82865512371063</t>
   </si>
   <si>
-    <t xml:space="preserve">1.84746980667114</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.79834306240082</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.79938781261444</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.78998124599457</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.77743768692017</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.76855313777924</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.75444209575653</t>
+    <t xml:space="preserve">1.84746956825256</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.79834318161011</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.79938793182373</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.78998112678528</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.77743756771088</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.76855301856995</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.75444221496582</t>
   </si>
   <si>
     <t xml:space="preserve">1.78527760505676</t>
@@ -2315,64 +2315,64 @@
     <t xml:space="preserve">1.75287461280823</t>
   </si>
   <si>
-    <t xml:space="preserve">1.7319700717926</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.72883367538452</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.78318667411804</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.79991042613983</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.77952837944031</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.8009557723999</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.79468417167664</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.8082720041275</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.84903693199158</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.88353049755096</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.88143992424011</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.9133198261261</t>
+    <t xml:space="preserve">1.73197019100189</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.72883379459381</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.78318691253662</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.79991054534912</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.7795284986496</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.80095565319061</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.79468381404877</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.80827212333679</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.849036693573</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.88353061676025</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.8814400434494</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.91331958770752</t>
   </si>
   <si>
     <t xml:space="preserve">1.89241528511047</t>
   </si>
   <si>
-    <t xml:space="preserve">1.89136970043182</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.90234422683716</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.87255525588989</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.8626252412796</t>
+    <t xml:space="preserve">1.89136981964111</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.90234410762787</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.87255537509918</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.86262500286102</t>
   </si>
   <si>
     <t xml:space="preserve">1.90077710151672</t>
   </si>
   <si>
-    <t xml:space="preserve">1.97498881816864</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.03247761726379</t>
+    <t xml:space="preserve">1.97498905658722</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.03247737884521</t>
   </si>
   <si>
     <t xml:space="preserve">2.03665828704834</t>
@@ -2387,34 +2387,34 @@
     <t xml:space="preserve">1.99328100681305</t>
   </si>
   <si>
-    <t xml:space="preserve">2.0021653175354</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.98805463314056</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.01627635955811</t>
+    <t xml:space="preserve">2.00216555595398</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.98805475234985</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.01627612113953</t>
   </si>
   <si>
     <t xml:space="preserve">1.98387384414673</t>
   </si>
   <si>
-    <t xml:space="preserve">1.95878803730011</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.96505916118622</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.95460724830627</t>
+    <t xml:space="preserve">1.95878827571869</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.96505928039551</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.9546070098877</t>
   </si>
   <si>
     <t xml:space="preserve">1.90495789051056</t>
   </si>
   <si>
-    <t xml:space="preserve">1.88927888870239</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.86941969394684</t>
+    <t xml:space="preserve">1.8892787694931</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.86941981315613</t>
   </si>
   <si>
     <t xml:space="preserve">1.84381055831909</t>
@@ -2423,13 +2423,13 @@
     <t xml:space="preserve">1.77168917655945</t>
   </si>
   <si>
-    <t xml:space="preserve">1.7607136964798</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.80775046348572</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.7800509929657</t>
+    <t xml:space="preserve">1.76071393489838</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.80775034427643</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.78005111217499</t>
   </si>
   <si>
     <t xml:space="preserve">1.80722761154175</t>
@@ -2438,7 +2438,7 @@
     <t xml:space="preserve">1.78214108943939</t>
   </si>
   <si>
-    <t xml:space="preserve">1.81611204147339</t>
+    <t xml:space="preserve">1.8161119222641</t>
   </si>
   <si>
     <t xml:space="preserve">1.67239093780518</t>
@@ -2450,7 +2450,7 @@
     <t xml:space="preserve">1.6556670665741</t>
   </si>
   <si>
-    <t xml:space="preserve">1.57413768768311</t>
+    <t xml:space="preserve">1.5741378068924</t>
   </si>
   <si>
     <t xml:space="preserve">1.60863089561462</t>
@@ -2465,7 +2465,7 @@
     <t xml:space="preserve">1.60026884078979</t>
   </si>
   <si>
-    <t xml:space="preserve">1.60654067993164</t>
+    <t xml:space="preserve">1.60654079914093</t>
   </si>
   <si>
     <t xml:space="preserve">1.59295248985291</t>
@@ -2477,25 +2477,25 @@
     <t xml:space="preserve">1.67657172679901</t>
   </si>
   <si>
-    <t xml:space="preserve">1.66507434844971</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.69799900054932</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.68441092967987</t>
+    <t xml:space="preserve">1.665074467659</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.69799911975861</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.68441081047058</t>
   </si>
   <si>
     <t xml:space="preserve">1.6880692243576</t>
   </si>
   <si>
-    <t xml:space="preserve">1.71629118919373</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.73353755474091</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.73876392841339</t>
+    <t xml:space="preserve">1.71629095077515</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.73353743553162</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.7387638092041</t>
   </si>
   <si>
     <t xml:space="preserve">1.74712562561035</t>
@@ -2504,25 +2504,25 @@
     <t xml:space="preserve">1.80618238449097</t>
   </si>
   <si>
-    <t xml:space="preserve">1.8265643119812</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.80879497528076</t>
+    <t xml:space="preserve">1.82656419277191</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.80879485607147</t>
   </si>
   <si>
     <t xml:space="preserve">1.83649432659149</t>
   </si>
   <si>
-    <t xml:space="preserve">1.88300788402557</t>
+    <t xml:space="preserve">1.88300764560699</t>
   </si>
   <si>
     <t xml:space="preserve">1.89189231395721</t>
   </si>
   <si>
-    <t xml:space="preserve">1.83022224903107</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.84119784832001</t>
+    <t xml:space="preserve">1.83022201061249</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.84119772911072</t>
   </si>
   <si>
     <t xml:space="preserve">1.92168164253235</t>
@@ -2534,7 +2534,7 @@
     <t xml:space="preserve">1.83597111701965</t>
   </si>
   <si>
-    <t xml:space="preserve">1.81663489341736</t>
+    <t xml:space="preserve">1.81663501262665</t>
   </si>
   <si>
     <t xml:space="preserve">1.82760965824127</t>
@@ -2543,106 +2543,106 @@
     <t xml:space="preserve">1.85112774372101</t>
   </si>
   <si>
-    <t xml:space="preserve">1.82290601730347</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.83388137817383</t>
+    <t xml:space="preserve">1.82290577888489</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.83388161659241</t>
   </si>
   <si>
     <t xml:space="preserve">1.81715667247772</t>
   </si>
   <si>
-    <t xml:space="preserve">1.82342875003815</t>
+    <t xml:space="preserve">1.82342863082886</t>
   </si>
   <si>
     <t xml:space="preserve">1.83440411090851</t>
   </si>
   <si>
-    <t xml:space="preserve">1.9012998342514</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.92220413684845</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.96349155902863</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.9922354221344</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.04658818244934</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.09989547729492</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.122891664505</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.15111231803894</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.11139345169067</t>
+    <t xml:space="preserve">1.90129971504211</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.92220437526703</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.96349143981934</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.99223530292511</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.04658842086792</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.0998957157135</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.12289142608643</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.15111207962036</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.11139321327209</t>
   </si>
   <si>
     <t xml:space="preserve">2.11034870147705</t>
   </si>
   <si>
-    <t xml:space="preserve">2.12602686882019</t>
+    <t xml:space="preserve">2.12602663040161</t>
   </si>
   <si>
     <t xml:space="preserve">2.12654948234558</t>
   </si>
   <si>
-    <t xml:space="preserve">2.08630752563477</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.0941469669342</t>
+    <t xml:space="preserve">2.08630776405334</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.09414672851562</t>
   </si>
   <si>
     <t xml:space="preserve">2.09048867225647</t>
   </si>
   <si>
-    <t xml:space="preserve">2.15790700912476</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.18299269676208</t>
+    <t xml:space="preserve">2.15790724754333</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.18299245834351</t>
   </si>
   <si>
     <t xml:space="preserve">2.19762635231018</t>
   </si>
   <si>
-    <t xml:space="preserve">2.22950625419617</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.20494246482849</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.24152636528015</t>
+    <t xml:space="preserve">2.22950649261475</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.20494270324707</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.24152612686157</t>
   </si>
   <si>
     <t xml:space="preserve">2.25772738456726</t>
   </si>
   <si>
-    <t xml:space="preserve">2.27288389205933</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.26504445075989</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.28176832199097</t>
+    <t xml:space="preserve">2.27288365364075</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.26504468917847</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.28176856040955</t>
   </si>
   <si>
     <t xml:space="preserve">2.30946731567383</t>
   </si>
   <si>
-    <t xml:space="preserve">2.37636280059814</t>
+    <t xml:space="preserve">2.37636303901672</t>
   </si>
   <si>
     <t xml:space="preserve">2.40824317932129</t>
   </si>
   <si>
-    <t xml:space="preserve">2.39465475082397</t>
+    <t xml:space="preserve">2.39465498924255</t>
   </si>
   <si>
     <t xml:space="preserve">2.33716654777527</t>
@@ -2654,10 +2654,10 @@
     <t xml:space="preserve">2.34448289871216</t>
   </si>
   <si>
-    <t xml:space="preserve">2.32357811927795</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.29326558113098</t>
+    <t xml:space="preserve">2.32357835769653</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.29326581954956</t>
   </si>
   <si>
     <t xml:space="preserve">2.29692482948303</t>
@@ -2672,19 +2672,19 @@
     <t xml:space="preserve">2.29431104660034</t>
   </si>
   <si>
-    <t xml:space="preserve">2.30633211135864</t>
+    <t xml:space="preserve">2.30633187294006</t>
   </si>
   <si>
     <t xml:space="preserve">2.32880473136902</t>
   </si>
   <si>
-    <t xml:space="preserve">2.30110549926758</t>
+    <t xml:space="preserve">2.30110597610474</t>
   </si>
   <si>
     <t xml:space="preserve">2.32566833496094</t>
   </si>
   <si>
-    <t xml:space="preserve">2.32253289222717</t>
+    <t xml:space="preserve">2.32253313064575</t>
   </si>
   <si>
     <t xml:space="preserve">2.35336780548096</t>
@@ -2696,31 +2696,31 @@
     <t xml:space="preserve">2.36538791656494</t>
   </si>
   <si>
-    <t xml:space="preserve">2.3831570148468</t>
+    <t xml:space="preserve">2.38315677642822</t>
   </si>
   <si>
     <t xml:space="preserve">2.36016130447388</t>
   </si>
   <si>
-    <t xml:space="preserve">2.35702586174011</t>
+    <t xml:space="preserve">2.35702610015869</t>
   </si>
   <si>
     <t xml:space="preserve">2.32775902748108</t>
   </si>
   <si>
-    <t xml:space="preserve">2.34291505813599</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.40144872665405</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.39988112449646</t>
+    <t xml:space="preserve">2.34291481971741</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.40144896507263</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.39988136291504</t>
   </si>
   <si>
     <t xml:space="preserve">2.350754737854</t>
   </si>
   <si>
-    <t xml:space="preserve">2.3575484752655</t>
+    <t xml:space="preserve">2.35754823684692</t>
   </si>
   <si>
     <t xml:space="preserve">2.38002133369446</t>
@@ -2735,13 +2735,13 @@
     <t xml:space="preserve">2.40406250953674</t>
   </si>
   <si>
-    <t xml:space="preserve">2.4119017124176</t>
+    <t xml:space="preserve">2.41190147399902</t>
   </si>
   <si>
     <t xml:space="preserve">2.39047431945801</t>
   </si>
   <si>
-    <t xml:space="preserve">2.38420224189758</t>
+    <t xml:space="preserve">2.38420248031616</t>
   </si>
   <si>
     <t xml:space="preserve">2.4030168056488</t>
@@ -2771,25 +2771,25 @@
     <t xml:space="preserve">2.26086378097534</t>
   </si>
   <si>
-    <t xml:space="preserve">2.16888165473938</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.21330451965332</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.26295375823975</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.28751754760742</t>
+    <t xml:space="preserve">2.1688814163208</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.21330428123474</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.26295351982117</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.28751730918884</t>
   </si>
   <si>
     <t xml:space="preserve">2.26609015464783</t>
   </si>
   <si>
-    <t xml:space="preserve">2.27497434616089</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.28542685508728</t>
+    <t xml:space="preserve">2.27497458457947</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.2854266166687</t>
   </si>
   <si>
     <t xml:space="preserve">2.36956858634949</t>
@@ -2798,13 +2798,13 @@
     <t xml:space="preserve">2.34918689727783</t>
   </si>
   <si>
-    <t xml:space="preserve">2.42705655097961</t>
+    <t xml:space="preserve">2.42705702781677</t>
   </si>
   <si>
     <t xml:space="preserve">2.16417789459229</t>
   </si>
   <si>
-    <t xml:space="preserve">2.1568615436554</t>
+    <t xml:space="preserve">2.15686130523682</t>
   </si>
   <si>
     <t xml:space="preserve">2.19187712669373</t>
@@ -2813,7 +2813,7 @@
     <t xml:space="preserve">2.12811803817749</t>
   </si>
   <si>
-    <t xml:space="preserve">2.00477814674377</t>
+    <t xml:space="preserve">2.00477838516235</t>
   </si>
   <si>
     <t xml:space="preserve">2.0068690776825</t>
@@ -2825,7 +2825,7 @@
     <t xml:space="preserve">1.97446644306183</t>
   </si>
   <si>
-    <t xml:space="preserve">1.88091695308685</t>
+    <t xml:space="preserve">1.88091683387756</t>
   </si>
   <si>
     <t xml:space="preserve">1.73771822452545</t>
@@ -2834,16 +2834,16 @@
     <t xml:space="preserve">1.69277262687683</t>
   </si>
   <si>
-    <t xml:space="preserve">1.631103515625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.59661054611206</t>
+    <t xml:space="preserve">1.63110363483429</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.59661066532135</t>
   </si>
   <si>
     <t xml:space="preserve">1.37972259521484</t>
   </si>
   <si>
-    <t xml:space="preserve">1.31282699108124</t>
+    <t xml:space="preserve">1.31282687187195</t>
   </si>
   <si>
     <t xml:space="preserve">1.31596255302429</t>
@@ -2858,13 +2858,13 @@
     <t xml:space="preserve">1.22345852851868</t>
   </si>
   <si>
-    <t xml:space="preserve">1.21927750110626</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.18687474727631</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.20516669750214</t>
+    <t xml:space="preserve">1.21927762031555</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.18687462806702</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.20516657829285</t>
   </si>
   <si>
     <t xml:space="preserve">1.34575164318085</t>
@@ -2876,10 +2876,10 @@
     <t xml:space="preserve">1.57256972789764</t>
   </si>
   <si>
-    <t xml:space="preserve">1.54800689220428</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.51769483089447</t>
+    <t xml:space="preserve">1.548006772995</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.51769495010376</t>
   </si>
   <si>
     <t xml:space="preserve">1.41996455192566</t>
@@ -2897,7 +2897,7 @@
     <t xml:space="preserve">1.40951180458069</t>
   </si>
   <si>
-    <t xml:space="preserve">1.40271723270416</t>
+    <t xml:space="preserve">1.40271735191345</t>
   </si>
   <si>
     <t xml:space="preserve">1.42989385128021</t>
@@ -2909,7 +2909,7 @@
     <t xml:space="preserve">1.35411357879639</t>
   </si>
   <si>
-    <t xml:space="preserve">1.36717915534973</t>
+    <t xml:space="preserve">1.36717891693115</t>
   </si>
   <si>
     <t xml:space="preserve">1.306032538414</t>
@@ -2918,22 +2918,22 @@
     <t xml:space="preserve">1.20987033843994</t>
   </si>
   <si>
-    <t xml:space="preserve">1.15760815143585</t>
+    <t xml:space="preserve">1.15760827064514</t>
   </si>
   <si>
     <t xml:space="preserve">1.16962838172913</t>
   </si>
   <si>
-    <t xml:space="preserve">1.17067360877991</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.1199791431427</t>
+    <t xml:space="preserve">1.1706737279892</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.11997902393341</t>
   </si>
   <si>
     <t xml:space="preserve">1.11841106414795</t>
   </si>
   <si>
-    <t xml:space="preserve">1.15604019165039</t>
+    <t xml:space="preserve">1.1560400724411</t>
   </si>
   <si>
     <t xml:space="preserve">1.10795903205872</t>
@@ -2954,10 +2954,10 @@
     <t xml:space="preserve">1.15185916423798</t>
   </si>
   <si>
-    <t xml:space="preserve">1.14976835250854</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.13618016242981</t>
+    <t xml:space="preserve">1.14976823329926</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.13618004322052</t>
   </si>
   <si>
     <t xml:space="preserve">1.11736631393433</t>
@@ -2975,7 +2975,7 @@
     <t xml:space="preserve">1.05256080627441</t>
   </si>
   <si>
-    <t xml:space="preserve">1.04890251159668</t>
+    <t xml:space="preserve">1.04890263080597</t>
   </si>
   <si>
     <t xml:space="preserve">1.09102869033813</t>
@@ -2987,19 +2987,19 @@
     <t xml:space="preserve">1.01237452030182</t>
   </si>
   <si>
-    <t xml:space="preserve">0.993177175521851</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.993977606296539</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.996643543243408</t>
+    <t xml:space="preserve">0.99317729473114</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.993977665901184</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.996643483638763</t>
   </si>
   <si>
     <t xml:space="preserve">1.10062718391418</t>
   </si>
   <si>
-    <t xml:space="preserve">1.14062082767487</t>
+    <t xml:space="preserve">1.14062070846558</t>
   </si>
   <si>
     <t xml:space="preserve">1.18648028373718</t>
@@ -3014,37 +3014,37 @@
     <t xml:space="preserve">1.1944797039032</t>
   </si>
   <si>
-    <t xml:space="preserve">1.23287332057953</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.23340654373169</t>
+    <t xml:space="preserve">1.23287320137024</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.23340666294098</t>
   </si>
   <si>
     <t xml:space="preserve">1.35338819026947</t>
   </si>
   <si>
-    <t xml:space="preserve">1.41897749900818</t>
+    <t xml:space="preserve">1.41897761821747</t>
   </si>
   <si>
     <t xml:space="preserve">1.39871430397034</t>
   </si>
   <si>
-    <t xml:space="preserve">1.32832515239716</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.24353861808777</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.21527624130249</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.22647476196289</t>
+    <t xml:space="preserve">1.32832503318787</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.24353873729706</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.2152761220932</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.22647488117218</t>
   </si>
   <si>
     <t xml:space="preserve">1.3069953918457</t>
   </si>
   <si>
-    <t xml:space="preserve">1.28086614608765</t>
+    <t xml:space="preserve">1.28086626529694</t>
   </si>
   <si>
     <t xml:space="preserve">1.24567115306854</t>
@@ -3059,16 +3059,16 @@
     <t xml:space="preserve">1.23980605602264</t>
   </si>
   <si>
-    <t xml:space="preserve">1.17688179016113</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.18594694137573</t>
+    <t xml:space="preserve">1.17688167095184</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.18594706058502</t>
   </si>
   <si>
     <t xml:space="preserve">1.15875136852264</t>
   </si>
   <si>
-    <t xml:space="preserve">1.17954862117767</t>
+    <t xml:space="preserve">1.17954850196838</t>
   </si>
   <si>
     <t xml:space="preserve">1.15661871433258</t>
@@ -3080,34 +3080,34 @@
     <t xml:space="preserve">1.15981793403625</t>
   </si>
   <si>
-    <t xml:space="preserve">1.1950124502182</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.18168115615845</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.176349401474</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.14542007446289</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.20301163196564</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.32885825634003</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.32992517948151</t>
+    <t xml:space="preserve">1.19501233100891</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.18168103694916</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.17634928226471</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.14542019367218</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.20301151275635</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.32885849475861</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.32992506027222</t>
   </si>
   <si>
     <t xml:space="preserve">1.33685696125031</t>
   </si>
   <si>
-    <t xml:space="preserve">1.35445415973663</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.32619249820709</t>
+    <t xml:space="preserve">1.35445404052734</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.3261923789978</t>
   </si>
   <si>
     <t xml:space="preserve">1.3720520734787</t>
@@ -3116,7 +3116,7 @@
     <t xml:space="preserve">1.35925340652466</t>
   </si>
   <si>
-    <t xml:space="preserve">1.31232786178589</t>
+    <t xml:space="preserve">1.31232798099518</t>
   </si>
   <si>
     <t xml:space="preserve">1.29259741306305</t>
@@ -3125,16 +3125,16 @@
     <t xml:space="preserve">1.23873925209045</t>
   </si>
   <si>
-    <t xml:space="preserve">1.24247193336487</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.20247840881348</t>
+    <t xml:space="preserve">1.24247181415558</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.20247828960419</t>
   </si>
   <si>
     <t xml:space="preserve">1.18754708766937</t>
   </si>
   <si>
-    <t xml:space="preserve">1.13688826560974</t>
+    <t xml:space="preserve">1.13688814640045</t>
   </si>
   <si>
     <t xml:space="preserve">1.1075599193573</t>
@@ -3146,10 +3146,10 @@
     <t xml:space="preserve">1.1592845916748</t>
   </si>
   <si>
-    <t xml:space="preserve">1.24780464172363</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.26380181312561</t>
+    <t xml:space="preserve">1.24780452251434</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.26380169391632</t>
   </si>
   <si>
     <t xml:space="preserve">1.26486825942993</t>
@@ -3161,28 +3161,28 @@
     <t xml:space="preserve">1.23820602893829</t>
   </si>
   <si>
-    <t xml:space="preserve">1.24940466880798</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.2291407585144</t>
+    <t xml:space="preserve">1.24940454959869</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.22914063930511</t>
   </si>
   <si>
     <t xml:space="preserve">1.21580946445465</t>
   </si>
   <si>
-    <t xml:space="preserve">1.25260388851166</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.25207042694092</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.24300539493561</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.2691342830658</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.22700715065002</t>
+    <t xml:space="preserve">1.25260376930237</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.25207054615021</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.24300527572632</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.26913440227509</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.22700726985931</t>
   </si>
   <si>
     <t xml:space="preserve">1.19394648075104</t>
@@ -3194,16 +3194,16 @@
     <t xml:space="preserve">1.15288615226746</t>
   </si>
   <si>
-    <t xml:space="preserve">1.16408383846283</t>
+    <t xml:space="preserve">1.16408395767212</t>
   </si>
   <si>
     <t xml:space="preserve">1.15821874141693</t>
   </si>
   <si>
-    <t xml:space="preserve">1.12675642967224</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.14222097396851</t>
+    <t xml:space="preserve">1.12675631046295</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.14222073554993</t>
   </si>
   <si>
     <t xml:space="preserve">1.1715499162674</t>
@@ -3212,22 +3212,22 @@
     <t xml:space="preserve">1.16834986209869</t>
   </si>
   <si>
-    <t xml:space="preserve">1.16781663894653</t>
+    <t xml:space="preserve">1.16781651973724</t>
   </si>
   <si>
     <t xml:space="preserve">1.15341949462891</t>
   </si>
   <si>
-    <t xml:space="preserve">1.16195130348206</t>
+    <t xml:space="preserve">1.16195142269135</t>
   </si>
   <si>
     <t xml:space="preserve">1.15181946754456</t>
   </si>
   <si>
-    <t xml:space="preserve">1.10489320755005</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.07503163814545</t>
+    <t xml:space="preserve">1.10489308834076</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.07503151893616</t>
   </si>
   <si>
     <t xml:space="preserve">1.07716405391693</t>
@@ -3236,7 +3236,7 @@
     <t xml:space="preserve">1.04516911506653</t>
   </si>
   <si>
-    <t xml:space="preserve">1.04250311851501</t>
+    <t xml:space="preserve">1.0425032377243</t>
   </si>
   <si>
     <t xml:space="preserve">1.06969881057739</t>
@@ -3245,13 +3245,13 @@
     <t xml:space="preserve">1.03983724117279</t>
   </si>
   <si>
-    <t xml:space="preserve">1.06010019779205</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.03877055644989</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.01050817966461</t>
+    <t xml:space="preserve">1.06010031700134</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.03877067565918</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.01050806045532</t>
   </si>
   <si>
     <t xml:space="preserve">0.935909450054169</t>
@@ -3260,10 +3260,10 @@
     <t xml:space="preserve">0.974905669689178</t>
   </si>
   <si>
-    <t xml:space="preserve">0.933940052986145</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.942605793476105</t>
+    <t xml:space="preserve">0.933939933776855</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.94260585308075</t>
   </si>
   <si>
     <t xml:space="preserve">0.947332620620728</t>
@@ -3278,61 +3278,61 @@
     <t xml:space="preserve">0.879581689834595</t>
   </si>
   <si>
-    <t xml:space="preserve">0.874854862689972</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.945757031440735</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.933152258396149</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.02414333820343</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.958755791187286</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.934727787971497</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.948120474815369</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.938666820526123</t>
+    <t xml:space="preserve">0.874854803085327</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.94575697183609</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.933152318000793</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.02414345741272</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.958755850791931</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.934727847576141</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.948120534420013</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.938666760921478</t>
   </si>
   <si>
     <t xml:space="preserve">0.879975557327271</t>
   </si>
   <si>
-    <t xml:space="preserve">0.81655740737915</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.806315958499908</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.80119526386261</t>
+    <t xml:space="preserve">0.816557347774506</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.806315898895264</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.801195204257965</t>
   </si>
   <si>
     <t xml:space="preserve">0.831131756305695</t>
   </si>
   <si>
-    <t xml:space="preserve">0.852402448654175</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.872097492218018</t>
+    <t xml:space="preserve">0.85240250825882</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.872097551822662</t>
   </si>
   <si>
     <t xml:space="preserve">0.853190302848816</t>
   </si>
   <si>
-    <t xml:space="preserve">0.82561719417572</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.948514401912689</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.940636336803436</t>
+    <t xml:space="preserve">0.825617134571075</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.948514342308044</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.940636217594147</t>
   </si>
   <si>
     <t xml:space="preserve">0.97608745098114</t>
@@ -3347,37 +3347,37 @@
     <t xml:space="preserve">1.11592233181</t>
   </si>
   <si>
-    <t xml:space="preserve">1.1230126619339</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.16949307918549</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.19430887699127</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.19706606864929</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.20100510120392</t>
+    <t xml:space="preserve">1.12301278114319</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.1694929599762</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.19430875778198</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.19706618785858</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.20100522041321</t>
   </si>
   <si>
     <t xml:space="preserve">1.16988694667816</t>
   </si>
   <si>
-    <t xml:space="preserve">1.19036972522736</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.15413105487823</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.17067468166351</t>
+    <t xml:space="preserve">1.19036984443665</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.15413093566895</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.17067456245422</t>
   </si>
   <si>
     <t xml:space="preserve">1.15806996822357</t>
   </si>
   <si>
-    <t xml:space="preserve">1.16870522499084</t>
+    <t xml:space="preserve">1.16870510578156</t>
   </si>
   <si>
     <t xml:space="preserve">1.16003942489624</t>
@@ -3386,25 +3386,25 @@
     <t xml:space="preserve">1.15373694896698</t>
   </si>
   <si>
-    <t xml:space="preserve">1.16161501407623</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.19509661197662</t>
+    <t xml:space="preserve">1.16161489486694</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.19509673118591</t>
   </si>
   <si>
     <t xml:space="preserve">1.15570640563965</t>
   </si>
   <si>
-    <t xml:space="preserve">1.15294909477234</t>
+    <t xml:space="preserve">1.15294921398163</t>
   </si>
   <si>
     <t xml:space="preserve">1.16397845745087</t>
   </si>
   <si>
-    <t xml:space="preserve">1.14822220802307</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.15531265735626</t>
+    <t xml:space="preserve">1.14822232723236</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.15531253814697</t>
   </si>
   <si>
     <t xml:space="preserve">1.14388942718506</t>
@@ -3419,7 +3419,7 @@
     <t xml:space="preserve">1.16594791412354</t>
   </si>
   <si>
-    <t xml:space="preserve">1.18170392513275</t>
+    <t xml:space="preserve">1.18170404434204</t>
   </si>
   <si>
     <t xml:space="preserve">1.17343211174011</t>
@@ -3431,25 +3431,25 @@
     <t xml:space="preserve">1.16122102737427</t>
   </si>
   <si>
-    <t xml:space="preserve">1.2230635881424</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.29869258403778</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.28411841392517</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.31050956249237</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.31247913837433</t>
+    <t xml:space="preserve">1.22306346893311</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.29869270324707</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.28411829471588</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.31050968170166</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.31247925758362</t>
   </si>
   <si>
     <t xml:space="preserve">1.29632914066315</t>
   </si>
   <si>
-    <t xml:space="preserve">1.27584636211395</t>
+    <t xml:space="preserve">1.27584624290466</t>
   </si>
   <si>
     <t xml:space="preserve">1.26757442951202</t>
@@ -3467,25 +3467,25 @@
     <t xml:space="preserve">1.27624022960663</t>
   </si>
   <si>
-    <t xml:space="preserve">1.24118316173553</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.20376253128052</t>
+    <t xml:space="preserve">1.24118304252625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.20376241207123</t>
   </si>
   <si>
     <t xml:space="preserve">1.23724412918091</t>
   </si>
   <si>
-    <t xml:space="preserve">1.20061135292053</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.22779047489166</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.20770144462585</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.21636736392975</t>
+    <t xml:space="preserve">1.20061123371124</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.22779059410095</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.20770132541656</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.21636724472046</t>
   </si>
   <si>
     <t xml:space="preserve">1.33768880367279</t>
@@ -3494,25 +3494,25 @@
     <t xml:space="preserve">1.40071308612823</t>
   </si>
   <si>
-    <t xml:space="preserve">1.50430917739868</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.47279691696167</t>
+    <t xml:space="preserve">1.50430905818939</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.47279715538025</t>
   </si>
   <si>
     <t xml:space="preserve">1.4968249797821</t>
   </si>
   <si>
-    <t xml:space="preserve">1.46964585781097</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.46688842773438</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.48343241214752</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.46176767349243</t>
+    <t xml:space="preserve">1.46964573860168</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.46688854694366</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.48343229293823</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.46176779270172</t>
   </si>
   <si>
     <t xml:space="preserve">1.43498253822327</t>
@@ -3524,64 +3524,64 @@
     <t xml:space="preserve">1.46610069274902</t>
   </si>
   <si>
-    <t xml:space="preserve">1.44483017921448</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.44443619251251</t>
+    <t xml:space="preserve">1.44483006000519</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.44443607330322</t>
   </si>
   <si>
     <t xml:space="preserve">1.46767628192902</t>
   </si>
   <si>
-    <t xml:space="preserve">1.42946803569794</t>
+    <t xml:space="preserve">1.42946791648865</t>
   </si>
   <si>
     <t xml:space="preserve">1.46728229522705</t>
   </si>
   <si>
-    <t xml:space="preserve">1.45192039012909</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.4605860710144</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.52203464508057</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.56300044059753</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.55630397796631</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.54330551624298</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.55197107791901</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.53385174274445</t>
+    <t xml:space="preserve">1.4519202709198</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.46058595180511</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.52203476428986</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.56300032138824</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.5563040971756</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.54330539703369</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.5519711971283</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.53385162353516</t>
   </si>
   <si>
     <t xml:space="preserve">1.56772720813751</t>
   </si>
   <si>
-    <t xml:space="preserve">1.61657118797302</t>
+    <t xml:space="preserve">1.61657106876373</t>
   </si>
   <si>
     <t xml:space="preserve">1.60475385189056</t>
   </si>
   <si>
-    <t xml:space="preserve">1.54094183444977</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.50233948230743</t>
+    <t xml:space="preserve">1.54094195365906</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.50233960151672</t>
   </si>
   <si>
     <t xml:space="preserve">1.50076389312744</t>
   </si>
   <si>
-    <t xml:space="preserve">1.5216406583786</t>
+    <t xml:space="preserve">1.52164077758789</t>
   </si>
   <si>
     <t xml:space="preserve">1.51021766662598</t>
@@ -3596,7 +3596,7 @@
     <t xml:space="preserve">1.49643111228943</t>
   </si>
   <si>
-    <t xml:space="preserve">1.47831153869629</t>
+    <t xml:space="preserve">1.47831165790558</t>
   </si>
   <si>
     <t xml:space="preserve">1.49800670146942</t>
@@ -3608,16 +3608,16 @@
     <t xml:space="preserve">1.48973488807678</t>
   </si>
   <si>
-    <t xml:space="preserve">1.46452510356903</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.47319090366364</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.49958229064941</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.48264443874359</t>
+    <t xml:space="preserve">1.46452498435974</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.47319102287292</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.4995824098587</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.48264455795288</t>
   </si>
   <si>
     <t xml:space="preserve">1.49131035804749</t>
@@ -3626,13 +3626,13 @@
     <t xml:space="preserve">1.49012863636017</t>
   </si>
   <si>
-    <t xml:space="preserve">1.53700292110443</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.45428371429443</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.42198359966278</t>
+    <t xml:space="preserve">1.53700304031372</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.45428359508514</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.42198371887207</t>
   </si>
   <si>
     <t xml:space="preserve">1.4243471622467</t>
@@ -3650,13 +3650,13 @@
     <t xml:space="preserve">1.49209821224213</t>
   </si>
   <si>
-    <t xml:space="preserve">1.48303854465485</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.4767359495163</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.49367380142212</t>
+    <t xml:space="preserve">1.48303842544556</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.47673606872559</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.49367392063141</t>
   </si>
   <si>
     <t xml:space="preserve">1.52282249927521</t>
@@ -3665,25 +3665,25 @@
     <t xml:space="preserve">1.51533830165863</t>
   </si>
   <si>
-    <t xml:space="preserve">1.57402956485748</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.588210105896</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.56457591056824</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.57954430580139</t>
+    <t xml:space="preserve">1.57402968406677</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.58821022510529</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.56457602977753</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.57954442501068</t>
   </si>
   <si>
     <t xml:space="preserve">1.58033215999603</t>
   </si>
   <si>
-    <t xml:space="preserve">1.58742237091064</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.55748581886292</t>
+    <t xml:space="preserve">1.58742249011993</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.55748569965363</t>
   </si>
   <si>
     <t xml:space="preserve">1.54291152954102</t>
@@ -3692,10 +3692,10 @@
     <t xml:space="preserve">1.57127225399017</t>
   </si>
   <si>
-    <t xml:space="preserve">1.67216515541077</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.70914542675018</t>
+    <t xml:space="preserve">1.67216491699219</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.70914554595947</t>
   </si>
   <si>
     <t xml:space="preserve">1.62714517116547</t>
@@ -3704,19 +3704,19 @@
     <t xml:space="preserve">1.6480473279953</t>
   </si>
   <si>
-    <t xml:space="preserve">1.63759613037109</t>
+    <t xml:space="preserve">1.63759624958038</t>
   </si>
   <si>
     <t xml:space="preserve">1.63036108016968</t>
   </si>
   <si>
-    <t xml:space="preserve">1.63518440723419</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.64322364330292</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.63598835468292</t>
+    <t xml:space="preserve">1.63518452644348</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.64322352409363</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.63598847389221</t>
   </si>
   <si>
     <t xml:space="preserve">1.62553739547729</t>
@@ -3737,7 +3737,7 @@
     <t xml:space="preserve">1.632772564888</t>
   </si>
   <si>
-    <t xml:space="preserve">1.64081168174744</t>
+    <t xml:space="preserve">1.64081180095673</t>
   </si>
   <si>
     <t xml:space="preserve">1.61508643627167</t>
@@ -3746,13 +3746,13 @@
     <t xml:space="preserve">1.59257638454437</t>
   </si>
   <si>
-    <t xml:space="preserve">1.58091950416565</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.54514479637146</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.56001734733582</t>
+    <t xml:space="preserve">1.58091962337494</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.54514491558075</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.5600174665451</t>
   </si>
   <si>
     <t xml:space="preserve">1.53951728343964</t>
@@ -3761,31 +3761,31 @@
     <t xml:space="preserve">1.51901721954346</t>
   </si>
   <si>
-    <t xml:space="preserve">1.53589987754822</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.52906620502472</t>
+    <t xml:space="preserve">1.53589963912964</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.52906632423401</t>
   </si>
   <si>
     <t xml:space="preserve">1.480428814888</t>
   </si>
   <si>
-    <t xml:space="preserve">1.46836984157562</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.47560524940491</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.48444843292236</t>
+    <t xml:space="preserve">1.46836996078491</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.4756053686142</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.48444855213165</t>
   </si>
   <si>
     <t xml:space="preserve">1.47399747371674</t>
   </si>
   <si>
-    <t xml:space="preserve">1.48565423488617</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.44626188278198</t>
+    <t xml:space="preserve">1.48565435409546</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.44626200199127</t>
   </si>
   <si>
     <t xml:space="preserve">1.43339920043945</t>
@@ -3800,10 +3800,10 @@
     <t xml:space="preserve">1.42455589771271</t>
   </si>
   <si>
-    <t xml:space="preserve">1.37591862678528</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.36988914012909</t>
+    <t xml:space="preserve">1.37591850757599</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.3698890209198</t>
   </si>
   <si>
     <t xml:space="preserve">1.35863411426544</t>
@@ -3815,10 +3815,10 @@
     <t xml:space="preserve">1.24809432029724</t>
   </si>
   <si>
-    <t xml:space="preserve">1.25814342498779</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.27422189712524</t>
+    <t xml:space="preserve">1.25814354419708</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.27422201633453</t>
   </si>
   <si>
     <t xml:space="preserve">1.29673182964325</t>
@@ -3836,52 +3836,52 @@
     <t xml:space="preserve">1.30356526374817</t>
   </si>
   <si>
-    <t xml:space="preserve">1.30718290805817</t>
+    <t xml:space="preserve">1.30718278884888</t>
   </si>
   <si>
     <t xml:space="preserve">1.32366335391998</t>
   </si>
   <si>
-    <t xml:space="preserve">1.32326149940491</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.30517315864563</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.31361413002014</t>
+    <t xml:space="preserve">1.32326138019562</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.30517292022705</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.31361424922943</t>
   </si>
   <si>
     <t xml:space="preserve">1.45349729061127</t>
   </si>
   <si>
-    <t xml:space="preserve">1.45028150081635</t>
+    <t xml:space="preserve">1.45028162002563</t>
   </si>
   <si>
     <t xml:space="preserve">1.44465410709381</t>
   </si>
   <si>
-    <t xml:space="preserve">1.48726212978363</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.476811170578</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.46917378902435</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.45108532905579</t>
+    <t xml:space="preserve">1.48726224899292</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.47681105136871</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.46917390823364</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.45108556747437</t>
   </si>
   <si>
     <t xml:space="preserve">1.42535996437073</t>
   </si>
   <si>
-    <t xml:space="preserve">1.43500709533691</t>
+    <t xml:space="preserve">1.43500697612762</t>
   </si>
   <si>
     <t xml:space="preserve">1.41169309616089</t>
   </si>
   <si>
-    <t xml:space="preserve">1.4068695306778</t>
+    <t xml:space="preserve">1.40686964988708</t>
   </si>
   <si>
     <t xml:space="preserve">1.43701684474945</t>
@@ -3893,34 +3893,34 @@
     <t xml:space="preserve">1.47238957881927</t>
   </si>
   <si>
-    <t xml:space="preserve">1.4530953168869</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.47600734233856</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.45872294902802</t>
+    <t xml:space="preserve">1.45309543609619</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.47600722312927</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.45872282981873</t>
   </si>
   <si>
     <t xml:space="preserve">1.48123264312744</t>
   </si>
   <si>
-    <t xml:space="preserve">1.49047780036926</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.48364448547363</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.50092887878418</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.46153664588928</t>
+    <t xml:space="preserve">1.49047791957855</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.48364436626434</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.50092899799347</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.4615364074707</t>
   </si>
   <si>
     <t xml:space="preserve">1.45068359375</t>
   </si>
   <si>
-    <t xml:space="preserve">1.46475231647491</t>
+    <t xml:space="preserve">1.46475219726562</t>
   </si>
   <si>
     <t xml:space="preserve">1.45631098747253</t>
@@ -3932,16 +3932,16 @@
     <t xml:space="preserve">1.43782079219818</t>
   </si>
   <si>
-    <t xml:space="preserve">1.36104571819305</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.37873232364655</t>
+    <t xml:space="preserve">1.36104583740234</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.37873220443726</t>
   </si>
   <si>
     <t xml:space="preserve">1.41892862319946</t>
   </si>
   <si>
-    <t xml:space="preserve">1.43862473964691</t>
+    <t xml:space="preserve">1.43862462043762</t>
   </si>
   <si>
     <t xml:space="preserve">1.4743994474411</t>
@@ -3950,37 +3950,37 @@
     <t xml:space="preserve">1.53107607364655</t>
   </si>
   <si>
-    <t xml:space="preserve">1.52343893051147</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.56242918968201</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.55398797988892</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.59137070178986</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.57810580730438</t>
+    <t xml:space="preserve">1.52343881130219</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.5624293088913</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.55398786067963</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.59137058258057</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.57810568809509</t>
   </si>
   <si>
     <t xml:space="preserve">1.63357663154602</t>
   </si>
   <si>
-    <t xml:space="preserve">1.61589026451111</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.63438045978546</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.66010618209839</t>
+    <t xml:space="preserve">1.61589014530182</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.63438057899475</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.6601060628891</t>
   </si>
   <si>
     <t xml:space="preserve">1.66171395778656</t>
   </si>
   <si>
-    <t xml:space="preserve">1.6552826166153</t>
+    <t xml:space="preserve">1.65528249740601</t>
   </si>
   <si>
     <t xml:space="preserve">1.65608656406403</t>
@@ -3989,31 +3989,31 @@
     <t xml:space="preserve">1.65849828720093</t>
   </si>
   <si>
-    <t xml:space="preserve">1.6705573797226</t>
+    <t xml:space="preserve">1.67055714130402</t>
   </si>
   <si>
     <t xml:space="preserve">1.64643943309784</t>
   </si>
   <si>
-    <t xml:space="preserve">1.64563536643982</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.64965522289276</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.60945904254913</t>
+    <t xml:space="preserve">1.64563548564911</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.64965510368347</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.60945880413055</t>
   </si>
   <si>
     <t xml:space="preserve">1.6279491186142</t>
   </si>
   <si>
-    <t xml:space="preserve">1.52303683757782</t>
+    <t xml:space="preserve">1.52303695678711</t>
   </si>
   <si>
     <t xml:space="preserve">1.51419365406036</t>
   </si>
   <si>
-    <t xml:space="preserve">1.54152715206146</t>
+    <t xml:space="preserve">1.54152727127075</t>
   </si>
   <si>
     <t xml:space="preserve">1.53911542892456</t>
@@ -4025,7 +4025,7 @@
     <t xml:space="preserve">1.54715466499329</t>
   </si>
   <si>
-    <t xml:space="preserve">1.54273295402527</t>
+    <t xml:space="preserve">1.54273319244385</t>
   </si>
   <si>
     <t xml:space="preserve">1.5350958108902</t>
@@ -4043,76 +4043,76 @@
     <t xml:space="preserve">1.52826237678528</t>
   </si>
   <si>
-    <t xml:space="preserve">1.48485028743744</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.44425225257874</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.44987976551056</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.44304609298706</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.42576169967651</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.36426150798798</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.35340869426727</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.35220265388489</t>
+    <t xml:space="preserve">1.48485040664673</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.44425213336945</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.44987964630127</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.44304621219635</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.4257618188858</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.36426174640656</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.35340857505798</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.35220277309418</t>
   </si>
   <si>
     <t xml:space="preserve">1.39119303226471</t>
   </si>
   <si>
-    <t xml:space="preserve">1.37792837619781</t>
+    <t xml:space="preserve">1.37792825698853</t>
   </si>
   <si>
     <t xml:space="preserve">1.36506545543671</t>
   </si>
   <si>
-    <t xml:space="preserve">1.40807557106018</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.42013430595398</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.39561450481415</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.40284991264343</t>
+    <t xml:space="preserve">1.40807545185089</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.42013442516327</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.39561462402344</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.40285003185272</t>
   </si>
   <si>
     <t xml:space="preserve">1.39239895343781</t>
   </si>
   <si>
-    <t xml:space="preserve">1.4936934709549</t>
+    <t xml:space="preserve">1.49369359016418</t>
   </si>
   <si>
     <t xml:space="preserve">1.43018352985382</t>
   </si>
   <si>
-    <t xml:space="preserve">1.42777180671692</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.39280092716217</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.42897748947144</t>
+    <t xml:space="preserve">1.42777168750763</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.39280080795288</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.42897760868073</t>
   </si>
   <si>
     <t xml:space="preserve">1.41651666164398</t>
   </si>
   <si>
-    <t xml:space="preserve">1.43983054161072</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.45751678943634</t>
+    <t xml:space="preserve">1.43983066082001</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.45751690864563</t>
   </si>
   <si>
     <t xml:space="preserve">1.46877193450928</t>
@@ -4127,10 +4127,10 @@
     <t xml:space="preserve">1.54434084892273</t>
   </si>
   <si>
-    <t xml:space="preserve">1.54032123088837</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.55157613754272</t>
+    <t xml:space="preserve">1.54032135009766</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.55157625675201</t>
   </si>
   <si>
     <t xml:space="preserve">1.54996824264526</t>
@@ -4139,13 +4139,13 @@
     <t xml:space="preserve">1.57730185985565</t>
   </si>
   <si>
-    <t xml:space="preserve">1.57167434692383</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.55639982223511</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.54192900657654</t>
+    <t xml:space="preserve">1.57167422771454</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.55639970302582</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.54192912578583</t>
   </si>
   <si>
     <t xml:space="preserve">1.51298773288727</t>
@@ -4166,13 +4166,13 @@
     <t xml:space="preserve">1.47962486743927</t>
   </si>
   <si>
-    <t xml:space="preserve">1.49087989330292</t>
+    <t xml:space="preserve">1.49088001251221</t>
   </si>
   <si>
     <t xml:space="preserve">1.55881154537201</t>
   </si>
   <si>
-    <t xml:space="preserve">1.58936071395874</t>
+    <t xml:space="preserve">1.58936059474945</t>
   </si>
   <si>
     <t xml:space="preserve">1.57328224182129</t>
@@ -4181,40 +4181,40 @@
     <t xml:space="preserve">1.63116490840912</t>
   </si>
   <si>
-    <t xml:space="preserve">1.62875306606293</t>
+    <t xml:space="preserve">1.62875318527222</t>
   </si>
   <si>
     <t xml:space="preserve">1.65367460250854</t>
   </si>
   <si>
-    <t xml:space="preserve">1.59016454219818</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.73567509651184</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.71477317810059</t>
+    <t xml:space="preserve">1.59016466140747</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.73567521572113</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.71477293968201</t>
   </si>
   <si>
     <t xml:space="preserve">1.62312567234039</t>
   </si>
   <si>
-    <t xml:space="preserve">1.57569396495819</t>
+    <t xml:space="preserve">1.57569408416748</t>
   </si>
   <si>
     <t xml:space="preserve">1.45590901374817</t>
   </si>
   <si>
-    <t xml:space="preserve">1.48243868350983</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.33572208881378</t>
+    <t xml:space="preserve">1.48243856430054</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.33572220802307</t>
   </si>
   <si>
     <t xml:space="preserve">1.3304967880249</t>
   </si>
   <si>
-    <t xml:space="preserve">1.26095724105835</t>
+    <t xml:space="preserve">1.26095712184906</t>
   </si>
   <si>
     <t xml:space="preserve">1.12750554084778</t>
@@ -4226,19 +4226,19 @@
     <t xml:space="preserve">1.12670147418976</t>
   </si>
   <si>
-    <t xml:space="preserve">1.2392510175705</t>
+    <t xml:space="preserve">1.23925113677979</t>
   </si>
   <si>
     <t xml:space="preserve">1.14639782905579</t>
   </si>
   <si>
-    <t xml:space="preserve">1.13996636867523</t>
+    <t xml:space="preserve">1.13996624946594</t>
   </si>
   <si>
     <t xml:space="preserve">1.18659400939941</t>
   </si>
   <si>
-    <t xml:space="preserve">1.21071183681488</t>
+    <t xml:space="preserve">1.21071171760559</t>
   </si>
   <si>
     <t xml:space="preserve">1.29954552650452</t>
@@ -4262,16 +4262,16 @@
     <t xml:space="preserve">1.25532972812653</t>
   </si>
   <si>
-    <t xml:space="preserve">1.27140820026398</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.34617340564728</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.31964373588562</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.27783954143524</t>
+    <t xml:space="preserve">1.27140808105469</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.34617328643799</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.31964361667633</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.27783942222595</t>
   </si>
   <si>
     <t xml:space="preserve">1.29190826416016</t>
@@ -4280,19 +4280,19 @@
     <t xml:space="preserve">1.23643743991852</t>
   </si>
   <si>
-    <t xml:space="preserve">1.23844718933105</t>
+    <t xml:space="preserve">1.23844730854034</t>
   </si>
   <si>
     <t xml:space="preserve">1.28748667240143</t>
   </si>
   <si>
-    <t xml:space="preserve">1.28547692298889</t>
+    <t xml:space="preserve">1.2854768037796</t>
   </si>
   <si>
     <t xml:space="preserve">1.24447667598724</t>
   </si>
   <si>
-    <t xml:space="preserve">1.24729025363922</t>
+    <t xml:space="preserve">1.24729037284851</t>
   </si>
   <si>
     <t xml:space="preserve">1.26015317440033</t>
@@ -4301,16 +4301,16 @@
     <t xml:space="preserve">1.26578068733215</t>
   </si>
   <si>
-    <t xml:space="preserve">1.31039845943451</t>
+    <t xml:space="preserve">1.3103985786438</t>
   </si>
   <si>
     <t xml:space="preserve">1.31924176216125</t>
   </si>
   <si>
-    <t xml:space="preserve">1.30034947395325</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.28668260574341</t>
+    <t xml:space="preserve">1.30034935474396</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.2866827249527</t>
   </si>
   <si>
     <t xml:space="preserve">1.27181017398834</t>
@@ -4322,16 +4322,16 @@
     <t xml:space="preserve">1.27261400222778</t>
   </si>
   <si>
-    <t xml:space="preserve">1.2903003692627</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.28185904026031</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.25050616264343</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.23121178150177</t>
+    <t xml:space="preserve">1.29030048847198</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.2818591594696</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.25050604343414</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.23121190071106</t>
   </si>
   <si>
     <t xml:space="preserve">1.23281967639923</t>
@@ -4352,10 +4352,10 @@
     <t xml:space="preserve">1.38757538795471</t>
   </si>
   <si>
-    <t xml:space="preserve">1.41933035850525</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.41249704360962</t>
+    <t xml:space="preserve">1.41933047771454</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.41249716281891</t>
   </si>
   <si>
     <t xml:space="preserve">1.42134034633636</t>
@@ -4373,16 +4373,16 @@
     <t xml:space="preserve">1.55682456493378</t>
   </si>
   <si>
-    <t xml:space="preserve">1.57597255706787</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.56931233406067</t>
+    <t xml:space="preserve">1.57597267627716</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.56931245326996</t>
   </si>
   <si>
     <t xml:space="preserve">1.56889617443085</t>
   </si>
   <si>
-    <t xml:space="preserve">1.59553694725037</t>
+    <t xml:space="preserve">1.59553706645966</t>
   </si>
   <si>
     <t xml:space="preserve">1.59179055690765</t>
@@ -4394,13 +4394,13 @@
     <t xml:space="preserve">1.5509968996048</t>
   </si>
   <si>
-    <t xml:space="preserve">1.60760855674744</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.56847989559174</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.61426889896393</t>
+    <t xml:space="preserve">1.60760867595673</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.56847977638245</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.61426877975464</t>
   </si>
   <si>
     <t xml:space="preserve">1.62425911426544</t>
@@ -4418,7 +4418,7 @@
     <t xml:space="preserve">1.43194556236267</t>
   </si>
   <si>
-    <t xml:space="preserve">1.37117099761963</t>
+    <t xml:space="preserve">1.37117111682892</t>
   </si>
   <si>
     <t xml:space="preserve">1.3969794511795</t>
@@ -4427,28 +4427,28 @@
     <t xml:space="preserve">1.42195522785187</t>
   </si>
   <si>
-    <t xml:space="preserve">1.42861533164978</t>
+    <t xml:space="preserve">1.42861545085907</t>
   </si>
   <si>
     <t xml:space="preserve">1.4265341758728</t>
   </si>
   <si>
-    <t xml:space="preserve">1.35785067081451</t>
+    <t xml:space="preserve">1.3578507900238</t>
   </si>
   <si>
     <t xml:space="preserve">1.40197455883026</t>
   </si>
   <si>
-    <t xml:space="preserve">1.38074517250061</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.37866377830505</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.35826706886292</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.30498516559601</t>
+    <t xml:space="preserve">1.38074505329132</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.37866389751434</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.35826694965363</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.3049852848053</t>
   </si>
   <si>
     <t xml:space="preserve">1.26460778713226</t>
@@ -4463,13 +4463,13 @@
     <t xml:space="preserve">1.18093883991241</t>
   </si>
   <si>
-    <t xml:space="preserve">1.24212956428528</t>
+    <t xml:space="preserve">1.24212944507599</t>
   </si>
   <si>
     <t xml:space="preserve">1.25711500644684</t>
   </si>
   <si>
-    <t xml:space="preserve">1.2000869512558</t>
+    <t xml:space="preserve">1.20008683204651</t>
   </si>
   <si>
     <t xml:space="preserve">1.1705322265625</t>
@@ -4481,7 +4481,7 @@
     <t xml:space="preserve">1.06979656219482</t>
   </si>
   <si>
-    <t xml:space="preserve">1.07645678520203</t>
+    <t xml:space="preserve">1.07645666599274</t>
   </si>
   <si>
     <t xml:space="preserve">1.09060966968536</t>
@@ -4490,16 +4490,16 @@
     <t xml:space="preserve">1.16470456123352</t>
   </si>
   <si>
-    <t xml:space="preserve">1.1314035654068</t>
+    <t xml:space="preserve">1.13140344619751</t>
   </si>
   <si>
     <t xml:space="preserve">1.09602105617523</t>
   </si>
   <si>
-    <t xml:space="preserve">1.07853806018829</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.10642778873444</t>
+    <t xml:space="preserve">1.07853817939758</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.10642766952515</t>
   </si>
   <si>
     <t xml:space="preserve">1.0756242275238</t>
@@ -4508,19 +4508,19 @@
     <t xml:space="preserve">1.09643745422363</t>
   </si>
   <si>
-    <t xml:space="preserve">1.09893500804901</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.12391090393066</t>
+    <t xml:space="preserve">1.09893488883972</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.12391066551208</t>
   </si>
   <si>
     <t xml:space="preserve">1.13598239421844</t>
   </si>
   <si>
-    <t xml:space="preserve">1.15471410751343</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.20091950893402</t>
+    <t xml:space="preserve">1.15471422672272</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.20091938972473</t>
   </si>
   <si>
     <t xml:space="preserve">1.19301044940948</t>
@@ -4532,10 +4532,10 @@
     <t xml:space="preserve">1.34036767482758</t>
   </si>
   <si>
-    <t xml:space="preserve">1.3511905670166</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.38199388980865</t>
+    <t xml:space="preserve">1.35119044780731</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.38199400901794</t>
   </si>
   <si>
     <t xml:space="preserve">1.36326217651367</t>
@@ -4547,7 +4547,7 @@
     <t xml:space="preserve">1.3640946149826</t>
   </si>
   <si>
-    <t xml:space="preserve">1.31955456733704</t>
+    <t xml:space="preserve">1.31955444812775</t>
   </si>
   <si>
     <t xml:space="preserve">1.275430560112</t>
@@ -4574,7 +4574,7 @@
     <t xml:space="preserve">1.25295233726501</t>
   </si>
   <si>
-    <t xml:space="preserve">1.23546934127808</t>
+    <t xml:space="preserve">1.23546922206879</t>
   </si>
   <si>
     <t xml:space="preserve">1.2654402256012</t>
@@ -4583,10 +4583,10 @@
     <t xml:space="preserve">1.22756028175354</t>
   </si>
   <si>
-    <t xml:space="preserve">1.23005795478821</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.21257495880127</t>
+    <t xml:space="preserve">1.23005783557892</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.21257483959198</t>
   </si>
   <si>
     <t xml:space="preserve">1.25003850460052</t>
@@ -4595,7 +4595,7 @@
     <t xml:space="preserve">1.2887510061264</t>
   </si>
   <si>
-    <t xml:space="preserve">1.35285544395447</t>
+    <t xml:space="preserve">1.35285556316376</t>
   </si>
   <si>
     <t xml:space="preserve">1.33911883831024</t>
@@ -4607,7 +4607,7 @@
     <t xml:space="preserve">1.39489817619324</t>
   </si>
   <si>
-    <t xml:space="preserve">1.40363955497742</t>
+    <t xml:space="preserve">1.40363967418671</t>
   </si>
   <si>
     <t xml:space="preserve">1.41071605682373</t>
@@ -4616,7 +4616,7 @@
     <t xml:space="preserve">1.38657295703888</t>
   </si>
   <si>
-    <t xml:space="preserve">1.39781200885773</t>
+    <t xml:space="preserve">1.39781188964844</t>
   </si>
   <si>
     <t xml:space="preserve">1.44443345069885</t>
@@ -4628,34 +4628,34 @@
     <t xml:space="preserve">1.38532412052155</t>
   </si>
   <si>
-    <t xml:space="preserve">1.35493695735931</t>
+    <t xml:space="preserve">1.35493683815002</t>
   </si>
   <si>
     <t xml:space="preserve">1.33329117298126</t>
   </si>
   <si>
-    <t xml:space="preserve">1.29541122913361</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.31622445583344</t>
+    <t xml:space="preserve">1.29541110992432</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.31622433662415</t>
   </si>
   <si>
     <t xml:space="preserve">1.34161639213562</t>
   </si>
   <si>
-    <t xml:space="preserve">1.39864432811737</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.37241995334625</t>
+    <t xml:space="preserve">1.39864456653595</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.37241983413696</t>
   </si>
   <si>
     <t xml:space="preserve">1.33037745952606</t>
   </si>
   <si>
-    <t xml:space="preserve">1.347860455513</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.33162593841553</t>
+    <t xml:space="preserve">1.34786033630371</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.33162605762482</t>
   </si>
   <si>
     <t xml:space="preserve">1.32121956348419</t>
@@ -4664,25 +4664,25 @@
     <t xml:space="preserve">1.3541042804718</t>
   </si>
   <si>
-    <t xml:space="preserve">1.3769987821579</t>
+    <t xml:space="preserve">1.37699890136719</t>
   </si>
   <si>
     <t xml:space="preserve">1.4065535068512</t>
   </si>
   <si>
-    <t xml:space="preserve">1.41571128368378</t>
+    <t xml:space="preserve">1.41571140289307</t>
   </si>
   <si>
     <t xml:space="preserve">1.42611789703369</t>
   </si>
   <si>
-    <t xml:space="preserve">1.43069684505463</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.44984483718872</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.49105501174927</t>
+    <t xml:space="preserve">1.43069672584534</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.44984495639801</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.49105489253998</t>
   </si>
   <si>
     <t xml:space="preserve">1.4818971157074</t>
@@ -4691,10 +4691,10 @@
     <t xml:space="preserve">1.48397850990295</t>
   </si>
   <si>
-    <t xml:space="preserve">1.52602112293243</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.53601133823395</t>
+    <t xml:space="preserve">1.52602100372314</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.53601145744324</t>
   </si>
   <si>
     <t xml:space="preserve">1.55890572071075</t>
@@ -4712,7 +4712,7 @@
     <t xml:space="preserve">1.6758759021759</t>
   </si>
   <si>
-    <t xml:space="preserve">1.70667922496796</t>
+    <t xml:space="preserve">1.70667934417725</t>
   </si>
   <si>
     <t xml:space="preserve">1.57555639743805</t>
@@ -4724,16 +4724,16 @@
     <t xml:space="preserve">1.5639009475708</t>
   </si>
   <si>
-    <t xml:space="preserve">1.54225528240204</t>
+    <t xml:space="preserve">1.54225516319275</t>
   </si>
   <si>
     <t xml:space="preserve">1.56181967258453</t>
   </si>
   <si>
-    <t xml:space="preserve">1.56723117828369</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.58970940113068</t>
+    <t xml:space="preserve">1.5672310590744</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.58970928192139</t>
   </si>
   <si>
     <t xml:space="preserve">1.59387195110321</t>
@@ -4748,7 +4748,7 @@
     <t xml:space="preserve">1.62883818149567</t>
   </si>
   <si>
-    <t xml:space="preserve">1.63966083526611</t>
+    <t xml:space="preserve">1.6396609544754</t>
   </si>
   <si>
     <t xml:space="preserve">1.62467551231384</t>
@@ -4763,7 +4763,7 @@
     <t xml:space="preserve">1.62259411811829</t>
   </si>
   <si>
-    <t xml:space="preserve">1.61468517780304</t>
+    <t xml:space="preserve">1.61468505859375</t>
   </si>
   <si>
     <t xml:space="preserve">1.60594356060028</t>
@@ -4772,13 +4772,13 @@
     <t xml:space="preserve">1.61302006244659</t>
   </si>
   <si>
-    <t xml:space="preserve">1.61759889125824</t>
+    <t xml:space="preserve">1.61759901046753</t>
   </si>
   <si>
     <t xml:space="preserve">1.62550795078278</t>
   </si>
   <si>
-    <t xml:space="preserve">1.62509167194366</t>
+    <t xml:space="preserve">1.62509179115295</t>
   </si>
   <si>
     <t xml:space="preserve">1.63508200645447</t>
@@ -4790,13 +4790,13 @@
     <t xml:space="preserve">1.56639862060547</t>
   </si>
   <si>
-    <t xml:space="preserve">1.56514978408813</t>
+    <t xml:space="preserve">1.56514990329742</t>
   </si>
   <si>
     <t xml:space="preserve">1.55307817459106</t>
   </si>
   <si>
-    <t xml:space="preserve">1.62009644508362</t>
+    <t xml:space="preserve">1.62009656429291</t>
   </si>
   <si>
     <t xml:space="preserve">1.61884772777557</t>
@@ -4805,7 +4805,7 @@
     <t xml:space="preserve">1.61093866825104</t>
   </si>
   <si>
-    <t xml:space="preserve">1.59720206260681</t>
+    <t xml:space="preserve">1.59720194339752</t>
   </si>
   <si>
     <t xml:space="preserve">1.63133561611176</t>
@@ -4829,19 +4829,19 @@
     <t xml:space="preserve">1.75663089752197</t>
   </si>
   <si>
-    <t xml:space="preserve">1.75579833984375</t>
+    <t xml:space="preserve">1.75579822063446</t>
   </si>
   <si>
     <t xml:space="preserve">1.76578867435455</t>
   </si>
   <si>
-    <t xml:space="preserve">1.82323312759399</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.8432137966156</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.81490790843964</t>
+    <t xml:space="preserve">1.8232330083847</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.84321367740631</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.81490778923035</t>
   </si>
   <si>
     <t xml:space="preserve">1.87484967708588</t>
@@ -4850,13 +4850,13 @@
     <t xml:space="preserve">1.87318456172943</t>
   </si>
   <si>
-    <t xml:space="preserve">1.90898334980011</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.92063856124878</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.94811189174652</t>
+    <t xml:space="preserve">1.90898311138153</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.9206383228302</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.94811177253723</t>
   </si>
   <si>
     <t xml:space="preserve">1.95227468013763</t>
@@ -4868,7 +4868,7 @@
     <t xml:space="preserve">2.02387189865112</t>
   </si>
   <si>
-    <t xml:space="preserve">2.0230393409729</t>
+    <t xml:space="preserve">2.02303957939148</t>
   </si>
   <si>
     <t xml:space="preserve">2.09546899795532</t>
@@ -4880,13 +4880,13 @@
     <t xml:space="preserve">2.10462713241577</t>
   </si>
   <si>
-    <t xml:space="preserve">2.11461734771729</t>
+    <t xml:space="preserve">2.11461710929871</t>
   </si>
   <si>
     <t xml:space="preserve">2.14958357810974</t>
   </si>
   <si>
-    <t xml:space="preserve">2.11961245536804</t>
+    <t xml:space="preserve">2.11961221694946</t>
   </si>
   <si>
     <t xml:space="preserve">2.14042568206787</t>
@@ -4904,7 +4904,7 @@
     <t xml:space="preserve">2.15874099731445</t>
   </si>
   <si>
-    <t xml:space="preserve">2.2261757850647</t>
+    <t xml:space="preserve">2.22617602348328</t>
   </si>
   <si>
     <t xml:space="preserve">2.32441377639771</t>
@@ -4919,7 +4919,7 @@
     <t xml:space="preserve">2.17539167404175</t>
   </si>
   <si>
-    <t xml:space="preserve">2.19787001609802</t>
+    <t xml:space="preserve">2.19786977767944</t>
   </si>
   <si>
     <t xml:space="preserve">2.14708566665649</t>
@@ -4928,7 +4928,7 @@
     <t xml:space="preserve">2.20869278907776</t>
   </si>
   <si>
-    <t xml:space="preserve">2.23699879646301</t>
+    <t xml:space="preserve">2.23699855804443</t>
   </si>
   <si>
     <t xml:space="preserve">2.21701812744141</t>
@@ -4946,7 +4946,7 @@
     <t xml:space="preserve">2.29527544975281</t>
   </si>
   <si>
-    <t xml:space="preserve">2.35355234146118</t>
+    <t xml:space="preserve">2.35355257987976</t>
   </si>
   <si>
     <t xml:space="preserve">2.34522700309753</t>
@@ -4955,22 +4955,22 @@
     <t xml:space="preserve">2.24032855033875</t>
   </si>
   <si>
-    <t xml:space="preserve">2.02720212936401</t>
+    <t xml:space="preserve">2.02720189094543</t>
   </si>
   <si>
     <t xml:space="preserve">2.06050300598145</t>
   </si>
   <si>
-    <t xml:space="preserve">1.91148066520691</t>
+    <t xml:space="preserve">1.91148090362549</t>
   </si>
   <si>
     <t xml:space="preserve">1.91564357280731</t>
   </si>
   <si>
-    <t xml:space="preserve">1.86236178874969</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.88900279998779</t>
+    <t xml:space="preserve">1.86236166954041</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.88900256156921</t>
   </si>
   <si>
     <t xml:space="preserve">1.98141312599182</t>
@@ -4979,7 +4979,7 @@
     <t xml:space="preserve">1.95310711860657</t>
   </si>
   <si>
-    <t xml:space="preserve">1.91730856895447</t>
+    <t xml:space="preserve">1.91730844974518</t>
   </si>
   <si>
     <t xml:space="preserve">1.839883685112</t>
@@ -4991,10 +4991,10 @@
     <t xml:space="preserve">1.86735689640045</t>
   </si>
   <si>
-    <t xml:space="preserve">1.91814088821411</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.90648555755615</t>
+    <t xml:space="preserve">1.9181410074234</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.90648567676544</t>
   </si>
   <si>
     <t xml:space="preserve">1.89233267307281</t>
@@ -5003,19 +5003,19 @@
     <t xml:space="preserve">1.93895411491394</t>
   </si>
   <si>
-    <t xml:space="preserve">1.93812167644501</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.96809267997742</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.96476233005524</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.00305843353271</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.99639856815338</t>
+    <t xml:space="preserve">1.9381217956543</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.96809279918671</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.96476221084595</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.00305867195129</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.99639844894409</t>
   </si>
   <si>
     <t xml:space="preserve">2.08964157104492</t>
@@ -5030,16 +5030,16 @@
     <t xml:space="preserve">2.22284579277039</t>
   </si>
   <si>
-    <t xml:space="preserve">2.25281691551208</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.28528499603271</t>
+    <t xml:space="preserve">2.25281667709351</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.28528523445129</t>
   </si>
   <si>
     <t xml:space="preserve">2.276127576828</t>
   </si>
   <si>
-    <t xml:space="preserve">2.12294244766235</t>
+    <t xml:space="preserve">2.12294268608093</t>
   </si>
   <si>
     <t xml:space="preserve">2.20786023139954</t>
@@ -5048,7 +5048,7 @@
     <t xml:space="preserve">2.11877989768982</t>
   </si>
   <si>
-    <t xml:space="preserve">2.08547902107239</t>
+    <t xml:space="preserve">2.08547878265381</t>
   </si>
   <si>
     <t xml:space="preserve">2.12127757072449</t>
@@ -5060,10 +5060,10 @@
     <t xml:space="preserve">2.17039656639099</t>
   </si>
   <si>
-    <t xml:space="preserve">2.28362035751343</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.27279758453369</t>
+    <t xml:space="preserve">2.28362011909485</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.27279734611511</t>
   </si>
   <si>
     <t xml:space="preserve">2.22201299667358</t>
@@ -5072,7 +5072,7 @@
     <t xml:space="preserve">2.27196478843689</t>
   </si>
   <si>
-    <t xml:space="preserve">2.25781178474426</t>
+    <t xml:space="preserve">2.25781154632568</t>
   </si>
   <si>
     <t xml:space="preserve">2.25697922706604</t>
@@ -5081,10 +5081,10 @@
     <t xml:space="preserve">2.24282646179199</t>
   </si>
   <si>
-    <t xml:space="preserve">2.24782180786133</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.27570152282715</t>
+    <t xml:space="preserve">2.24782133102417</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.27570128440857</t>
   </si>
   <si>
     <t xml:space="preserve">2.25392007827759</t>
@@ -5105,10 +5105,10 @@
     <t xml:space="preserve">2.1180055141449</t>
   </si>
   <si>
-    <t xml:space="preserve">2.08228421211243</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.13717317581177</t>
+    <t xml:space="preserve">2.08228445053101</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.13717293739319</t>
   </si>
   <si>
     <t xml:space="preserve">2.18509149551392</t>
@@ -5120,7 +5120,7 @@
     <t xml:space="preserve">2.17986416816711</t>
   </si>
   <si>
-    <t xml:space="preserve">2.17550802230835</t>
+    <t xml:space="preserve">2.17550778388977</t>
   </si>
   <si>
     <t xml:space="preserve">2.17637896537781</t>
@@ -5156,31 +5156,31 @@
     <t xml:space="preserve">2.39157748222351</t>
   </si>
   <si>
-    <t xml:space="preserve">2.33930253982544</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.30880904197693</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.35237145423889</t>
+    <t xml:space="preserve">2.33930277824402</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.30880880355835</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.35237121582031</t>
   </si>
   <si>
     <t xml:space="preserve">2.36892509460449</t>
   </si>
   <si>
-    <t xml:space="preserve">2.40029001235962</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.42381358146667</t>
+    <t xml:space="preserve">2.4002902507782</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.42381381988525</t>
   </si>
   <si>
     <t xml:space="preserve">2.45082235336304</t>
   </si>
   <si>
-    <t xml:space="preserve">2.38896369934082</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.37676644325256</t>
+    <t xml:space="preserve">2.3889639377594</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.37676620483398</t>
   </si>
   <si>
     <t xml:space="preserve">2.32187747955322</t>
@@ -5195,10 +5195,10 @@
     <t xml:space="preserve">2.46476244926453</t>
   </si>
   <si>
-    <t xml:space="preserve">2.50396871566772</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.55885744094849</t>
+    <t xml:space="preserve">2.50396847724915</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.55885720252991</t>
   </si>
   <si>
     <t xml:space="preserve">2.53794741630554</t>
@@ -5213,22 +5213,22 @@
     <t xml:space="preserve">2.55711483955383</t>
   </si>
   <si>
-    <t xml:space="preserve">2.6093897819519</t>
+    <t xml:space="preserve">2.60938954353333</t>
   </si>
   <si>
     <t xml:space="preserve">2.62768602371216</t>
   </si>
   <si>
-    <t xml:space="preserve">2.64685344696045</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.6616644859314</t>
+    <t xml:space="preserve">2.64685368537903</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.66166472434998</t>
   </si>
   <si>
     <t xml:space="preserve">2.7653431892395</t>
   </si>
   <si>
-    <t xml:space="preserve">2.72090935707092</t>
+    <t xml:space="preserve">2.7209095954895</t>
   </si>
   <si>
     <t xml:space="preserve">2.73136448860168</t>
@@ -5243,7 +5243,7 @@
     <t xml:space="preserve">2.61897349357605</t>
   </si>
   <si>
-    <t xml:space="preserve">2.51180982589722</t>
+    <t xml:space="preserve">2.51180958747864</t>
   </si>
   <si>
     <t xml:space="preserve">2.47086095809937</t>
@@ -5255,7 +5255,7 @@
     <t xml:space="preserve">2.20600175857544</t>
   </si>
   <si>
-    <t xml:space="preserve">2.2547914981842</t>
+    <t xml:space="preserve">2.25479173660278</t>
   </si>
   <si>
     <t xml:space="preserve">2.30271005630493</t>
@@ -5264,7 +5264,7 @@
     <t xml:space="preserve">2.36369752883911</t>
   </si>
   <si>
-    <t xml:space="preserve">2.37241005897522</t>
+    <t xml:space="preserve">2.3724102973938</t>
   </si>
   <si>
     <t xml:space="preserve">2.3384313583374</t>
@@ -5276,22 +5276,22 @@
     <t xml:space="preserve">2.39593386650085</t>
   </si>
   <si>
-    <t xml:space="preserve">2.39244866371155</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.36718249320984</t>
+    <t xml:space="preserve">2.39244890213013</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.36718273162842</t>
   </si>
   <si>
     <t xml:space="preserve">2.42032885551453</t>
   </si>
   <si>
-    <t xml:space="preserve">2.44036769866943</t>
+    <t xml:space="preserve">2.44036746025085</t>
   </si>
   <si>
     <t xml:space="preserve">2.46389126777649</t>
   </si>
   <si>
-    <t xml:space="preserve">2.42904114723206</t>
+    <t xml:space="preserve">2.42904138565063</t>
   </si>
   <si>
     <t xml:space="preserve">2.41510128974915</t>
@@ -5300,7 +5300,7 @@
     <t xml:space="preserve">2.38809251785278</t>
   </si>
   <si>
-    <t xml:space="preserve">2.28441405296326</t>
+    <t xml:space="preserve">2.28441381454468</t>
   </si>
   <si>
     <t xml:space="preserve">2.25304889678955</t>
@@ -5309,10 +5309,10 @@
     <t xml:space="preserve">2.27134537696838</t>
   </si>
   <si>
-    <t xml:space="preserve">2.33407497406006</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.41161632537842</t>
+    <t xml:space="preserve">2.33407521247864</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.41161608695984</t>
   </si>
   <si>
     <t xml:space="preserve">2.43688249588013</t>
@@ -5324,19 +5324,19 @@
     <t xml:space="preserve">2.494384765625</t>
   </si>
   <si>
-    <t xml:space="preserve">2.60329079627991</t>
+    <t xml:space="preserve">2.60329103469849</t>
   </si>
   <si>
     <t xml:space="preserve">2.59980583190918</t>
   </si>
   <si>
-    <t xml:space="preserve">2.57802486419678</t>
+    <t xml:space="preserve">2.5780246257782</t>
   </si>
   <si>
     <t xml:space="preserve">2.46301984786987</t>
   </si>
   <si>
-    <t xml:space="preserve">2.43514013290405</t>
+    <t xml:space="preserve">2.43513989448547</t>
   </si>
   <si>
     <t xml:space="preserve">2.52400755882263</t>
@@ -5360,7 +5360,7 @@
     <t xml:space="preserve">2.42120003700256</t>
   </si>
   <si>
-    <t xml:space="preserve">2.5109384059906</t>
+    <t xml:space="preserve">2.51093864440918</t>
   </si>
   <si>
     <t xml:space="preserve">2.58063840866089</t>
@@ -5372,19 +5372,19 @@
     <t xml:space="preserve">2.57889604568481</t>
   </si>
   <si>
-    <t xml:space="preserve">2.63901209831238</t>
+    <t xml:space="preserve">2.63901233673096</t>
   </si>
   <si>
     <t xml:space="preserve">2.66427850723267</t>
   </si>
   <si>
-    <t xml:space="preserve">2.62855696678162</t>
+    <t xml:space="preserve">2.6285572052002</t>
   </si>
   <si>
     <t xml:space="preserve">2.49177098274231</t>
   </si>
   <si>
-    <t xml:space="preserve">2.59719228744507</t>
+    <t xml:space="preserve">2.59719204902649</t>
   </si>
   <si>
     <t xml:space="preserve">2.52923488616943</t>
@@ -5396,7 +5396,7 @@
     <t xml:space="preserve">2.53881859779358</t>
   </si>
   <si>
-    <t xml:space="preserve">2.55014491081238</t>
+    <t xml:space="preserve">2.5501446723938</t>
   </si>
   <si>
     <t xml:space="preserve">2.67386198043823</t>
@@ -5408,19 +5408,19 @@
     <t xml:space="preserve">2.73659205436707</t>
   </si>
   <si>
-    <t xml:space="preserve">2.74878931045532</t>
+    <t xml:space="preserve">2.7487895488739</t>
   </si>
   <si>
     <t xml:space="preserve">2.78189706802368</t>
   </si>
   <si>
-    <t xml:space="preserve">2.7601158618927</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.85943794250488</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.86989283561707</t>
+    <t xml:space="preserve">2.76011562347412</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.85943818092346</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.86989307403564</t>
   </si>
   <si>
     <t xml:space="preserve">3.07463645935059</t>
@@ -5432,7 +5432,7 @@
     <t xml:space="preserve">3.1033878326416</t>
   </si>
   <si>
-    <t xml:space="preserve">3.01713418960571</t>
+    <t xml:space="preserve">3.01713395118713</t>
   </si>
   <si>
     <t xml:space="preserve">3.03543019294739</t>
@@ -5456,7 +5456,7 @@
     <t xml:space="preserve">2.95353293418884</t>
   </si>
   <si>
-    <t xml:space="preserve">2.91868281364441</t>
+    <t xml:space="preserve">2.91868305206299</t>
   </si>
   <si>
     <t xml:space="preserve">3.01277780532837</t>
@@ -5480,25 +5480,25 @@
     <t xml:space="preserve">2.92216801643372</t>
   </si>
   <si>
-    <t xml:space="preserve">2.94569182395935</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.90909934043884</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.89777278900146</t>
+    <t xml:space="preserve">2.94569158554077</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.90909910202026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.89777302742004</t>
   </si>
   <si>
     <t xml:space="preserve">2.72700834274292</t>
   </si>
   <si>
-    <t xml:space="preserve">2.66689205169678</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.67211937904358</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.67124843597412</t>
+    <t xml:space="preserve">2.66689229011536</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.67211961746216</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.67124819755554</t>
   </si>
   <si>
     <t xml:space="preserve">2.63204193115234</t>
@@ -5516,22 +5516,22 @@
     <t xml:space="preserve">2.63639855384827</t>
   </si>
   <si>
-    <t xml:space="preserve">2.71568202972412</t>
+    <t xml:space="preserve">2.7156822681427</t>
   </si>
   <si>
     <t xml:space="preserve">2.80106425285339</t>
   </si>
   <si>
-    <t xml:space="preserve">2.85595297813416</t>
+    <t xml:space="preserve">2.85595321655273</t>
   </si>
   <si>
     <t xml:space="preserve">2.85682439804077</t>
   </si>
   <si>
-    <t xml:space="preserve">2.74704694747925</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.75924444198608</t>
+    <t xml:space="preserve">2.74704718589783</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.75924468040466</t>
   </si>
   <si>
     <t xml:space="preserve">2.70609831809998</t>
@@ -5543,7 +5543,7 @@
     <t xml:space="preserve">2.76621437072754</t>
   </si>
   <si>
-    <t xml:space="preserve">2.75314593315125</t>
+    <t xml:space="preserve">2.75314569473267</t>
   </si>
   <si>
     <t xml:space="preserve">2.78015446662903</t>
@@ -5558,7 +5558,7 @@
     <t xml:space="preserve">2.8768630027771</t>
   </si>
   <si>
-    <t xml:space="preserve">2.86640787124634</t>
+    <t xml:space="preserve">2.86640810966492</t>
   </si>
   <si>
     <t xml:space="preserve">2.91781163215637</t>
@@ -5579,13 +5579,13 @@
     <t xml:space="preserve">2.92303919792175</t>
   </si>
   <si>
-    <t xml:space="preserve">2.89951539039612</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.95614671707153</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.02846026420593</t>
+    <t xml:space="preserve">2.8995156288147</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.95614647865295</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.02846050262451</t>
   </si>
   <si>
     <t xml:space="preserve">3.05111289024353</t>
@@ -5600,7 +5600,7 @@
     <t xml:space="preserve">3.06156778335571</t>
   </si>
   <si>
-    <t xml:space="preserve">3.09554624557495</t>
+    <t xml:space="preserve">3.09554648399353</t>
   </si>
   <si>
     <t xml:space="preserve">3.11035752296448</t>
@@ -5609,7 +5609,7 @@
     <t xml:space="preserve">3.07028007507324</t>
   </si>
   <si>
-    <t xml:space="preserve">3.06331038475037</t>
+    <t xml:space="preserve">3.06331014633179</t>
   </si>
   <si>
     <t xml:space="preserve">2.99186778068542</t>
@@ -5618,7 +5618,7 @@
     <t xml:space="preserve">3.10948634147644</t>
   </si>
   <si>
-    <t xml:space="preserve">3.14520764350891</t>
+    <t xml:space="preserve">3.14520740509033</t>
   </si>
   <si>
     <t xml:space="preserve">3.21316504478455</t>
@@ -5630,7 +5630,7 @@
     <t xml:space="preserve">3.26718258857727</t>
   </si>
   <si>
-    <t xml:space="preserve">3.2314612865448</t>
+    <t xml:space="preserve">3.23146152496338</t>
   </si>
   <si>
     <t xml:space="preserve">3.22884774208069</t>
@@ -5648,22 +5648,22 @@
     <t xml:space="preserve">3.34210968017578</t>
   </si>
   <si>
-    <t xml:space="preserve">3.30028986930847</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.31074476242065</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.38131618499756</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.48412322998047</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.4632134437561</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.45362949371338</t>
+    <t xml:space="preserve">3.30029010772705</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.31074500083923</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.38131594657898</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.48412346839905</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.46321320533752</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.45362973213196</t>
   </si>
   <si>
     <t xml:space="preserve">3.50154829025269</t>
@@ -5672,16 +5672,16 @@
     <t xml:space="preserve">3.57124805450439</t>
   </si>
   <si>
-    <t xml:space="preserve">3.67144179344177</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.70716309547424</t>
+    <t xml:space="preserve">3.67144203186035</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.70716285705566</t>
   </si>
   <si>
     <t xml:space="preserve">3.68189668655396</t>
   </si>
   <si>
-    <t xml:space="preserve">3.6862530708313</t>
+    <t xml:space="preserve">3.68625283241272</t>
   </si>
   <si>
     <t xml:space="preserve">3.76553654670715</t>
@@ -5690,25 +5690,25 @@
     <t xml:space="preserve">3.87182903289795</t>
   </si>
   <si>
-    <t xml:space="preserve">3.78121948242188</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.81606936454773</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.80735635757446</t>
+    <t xml:space="preserve">3.7812192440033</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.81606912612915</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.80735659599304</t>
   </si>
   <si>
     <t xml:space="preserve">3.8979663848877</t>
   </si>
   <si>
-    <t xml:space="preserve">3.86921501159668</t>
+    <t xml:space="preserve">3.86921525001526</t>
   </si>
   <si>
     <t xml:space="preserve">3.82739520072937</t>
   </si>
   <si>
-    <t xml:space="preserve">3.87270021438599</t>
+    <t xml:space="preserve">3.87270045280457</t>
   </si>
   <si>
     <t xml:space="preserve">3.80822777748108</t>
@@ -5717,43 +5717,43 @@
     <t xml:space="preserve">3.87618494033813</t>
   </si>
   <si>
-    <t xml:space="preserve">3.72545909881592</t>
+    <t xml:space="preserve">3.7254593372345</t>
   </si>
   <si>
     <t xml:space="preserve">3.72371673583984</t>
   </si>
   <si>
-    <t xml:space="preserve">3.71848917007446</t>
+    <t xml:space="preserve">3.71848964691162</t>
   </si>
   <si>
     <t xml:space="preserve">3.66969919204712</t>
   </si>
   <si>
-    <t xml:space="preserve">3.77163553237915</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.84743404388428</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.84307765960693</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.93281626701355</t>
+    <t xml:space="preserve">3.77163529396057</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.8474338054657</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.84307742118835</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.93281650543213</t>
   </si>
   <si>
     <t xml:space="preserve">4.06786012649536</t>
   </si>
   <si>
-    <t xml:space="preserve">4.03736591339111</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.11490774154663</t>
+    <t xml:space="preserve">4.03736639022827</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.11490726470947</t>
   </si>
   <si>
     <t xml:space="preserve">4.168053150177</t>
   </si>
   <si>
-    <t xml:space="preserve">4.19767618179321</t>
+    <t xml:space="preserve">4.19767570495605</t>
   </si>
   <si>
     <t xml:space="preserve">4.26127672195435</t>
@@ -5771,7 +5771,7 @@
     <t xml:space="preserve">4.29874086380005</t>
   </si>
   <si>
-    <t xml:space="preserve">4.27434635162354</t>
+    <t xml:space="preserve">4.27434587478638</t>
   </si>
   <si>
     <t xml:space="preserve">4.14714384078979</t>
@@ -5789,7 +5789,7 @@
     <t xml:space="preserve">4.36669826507568</t>
   </si>
   <si>
-    <t xml:space="preserve">4.50435543060303</t>
+    <t xml:space="preserve">4.50435590744019</t>
   </si>
   <si>
     <t xml:space="preserve">4.61239051818848</t>
@@ -6837,6 +6837,9 @@
   </si>
   <si>
     <t xml:space="preserve">10.8549995422363</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.8149995803833</t>
   </si>
 </sst>
 </file>
@@ -72383,7 +72386,7 @@
     </row>
     <row r="2509">
       <c r="A2509" s="1" t="n">
-        <v>45972.6912615741</v>
+        <v>45972.3333333333</v>
       </c>
       <c r="B2509" t="n">
         <v>13624837</v>
@@ -72404,6 +72407,32 @@
         <v>2274</v>
       </c>
       <c r="H2509" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2510">
+      <c r="A2510" s="1" t="n">
+        <v>45973.6914930556</v>
+      </c>
+      <c r="B2510" t="n">
+        <v>14370045</v>
+      </c>
+      <c r="C2510" t="n">
+        <v>10.9399995803833</v>
+      </c>
+      <c r="D2510" t="n">
+        <v>10.789999961853</v>
+      </c>
+      <c r="E2510" t="n">
+        <v>10.8900003433228</v>
+      </c>
+      <c r="F2510" t="n">
+        <v>10.8149995803833</v>
+      </c>
+      <c r="G2510" t="s">
+        <v>2275</v>
+      </c>
+      <c r="H2510" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/BPE.MI.xlsx
+++ b/data/BPE.MI.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2278" uniqueCount="2278">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2279" uniqueCount="2279">
   <si>
     <t xml:space="preserve">date</t>
   </si>
@@ -44,85 +44,85 @@
     <t xml:space="preserve">BPE.MI</t>
   </si>
   <si>
-    <t xml:space="preserve">3.2697012424469</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.12443447113037</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.05299091339111</t>
+    <t xml:space="preserve">3.26970100402832</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.12443494796753</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.05299115180969</t>
   </si>
   <si>
     <t xml:space="preserve">2.98392939567566</t>
   </si>
   <si>
-    <t xml:space="preserve">2.98631119728088</t>
+    <t xml:space="preserve">2.98631143569946</t>
   </si>
   <si>
     <t xml:space="preserve">2.96249628067017</t>
   </si>
   <si>
-    <t xml:space="preserve">3.10538220405579</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.9458270072937</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.68863201141357</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.67672562599182</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.48144793510437</t>
+    <t xml:space="preserve">3.10538196563721</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.94582724571228</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.68863272666931</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.67672538757324</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.48144841194153</t>
   </si>
   <si>
     <t xml:space="preserve">2.75531268119812</t>
   </si>
   <si>
-    <t xml:space="preserve">2.72435402870178</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.65291118621826</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.80770421028137</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.69339537620544</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.49097418785095</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.61957049369812</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.55527210235596</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.38142824172974</t>
+    <t xml:space="preserve">2.7243537902832</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.65291094779968</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.80770397186279</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.69339489936829</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.49097394943237</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.6195707321167</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.55527281761169</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.38142848014832</t>
   </si>
   <si>
     <t xml:space="preserve">2.18424558639526</t>
   </si>
   <si>
-    <t xml:space="preserve">2.19281911849976</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.14709568023682</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.89085423946381</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.849893450737</t>
+    <t xml:space="preserve">2.19281888008118</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.14709544181824</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.89085400104523</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.84989380836487</t>
   </si>
   <si>
     <t xml:space="preserve">1.97753763198853</t>
   </si>
   <si>
-    <t xml:space="preserve">1.78797614574432</t>
+    <t xml:space="preserve">1.78797626495361</t>
   </si>
   <si>
     <t xml:space="preserve">1.99373137950897</t>
@@ -131,19 +131,19 @@
     <t xml:space="preserve">2.19567680358887</t>
   </si>
   <si>
-    <t xml:space="preserve">2.30236458778381</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.35761427879333</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.34332513809204</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.20329761505127</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.42667555809021</t>
+    <t xml:space="preserve">2.30236482620239</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.35761451721191</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.34332537651062</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.20329737663269</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.42667579650879</t>
   </si>
   <si>
     <t xml:space="preserve">2.33475208282471</t>
@@ -152,34 +152,34 @@
     <t xml:space="preserve">2.18615102767944</t>
   </si>
   <si>
-    <t xml:space="preserve">2.24044752120972</t>
+    <t xml:space="preserve">2.24044728279114</t>
   </si>
   <si>
     <t xml:space="preserve">2.28236079216003</t>
   </si>
   <si>
-    <t xml:space="preserve">2.24330568313599</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.27664470672607</t>
+    <t xml:space="preserve">2.24330544471741</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.27664518356323</t>
   </si>
   <si>
     <t xml:space="preserve">2.38857269287109</t>
   </si>
   <si>
-    <t xml:space="preserve">2.34713554382324</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.35666131973267</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.23473191261292</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.20234489440918</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.22711205482483</t>
+    <t xml:space="preserve">2.34713530540466</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.35666155815125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.23473262786865</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.2023446559906</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.22711181640625</t>
   </si>
   <si>
     <t xml:space="preserve">2.24711585044861</t>
@@ -188,76 +188,76 @@
     <t xml:space="preserve">2.43381977081299</t>
   </si>
   <si>
-    <t xml:space="preserve">2.46716022491455</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.38619065284729</t>
+    <t xml:space="preserve">2.46715998649597</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.38619089126587</t>
   </si>
   <si>
     <t xml:space="preserve">2.2242534160614</t>
   </si>
   <si>
-    <t xml:space="preserve">2.24902033805847</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.26902437210083</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.26330971717834</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.2299690246582</t>
+    <t xml:space="preserve">2.24902057647705</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.26902461051941</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.26330947875977</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.22996926307678</t>
   </si>
   <si>
     <t xml:space="preserve">2.16900491714478</t>
   </si>
   <si>
-    <t xml:space="preserve">2.07946276664734</t>
+    <t xml:space="preserve">2.0794632434845</t>
   </si>
   <si>
     <t xml:space="preserve">2.05850648880005</t>
   </si>
   <si>
-    <t xml:space="preserve">1.99277889728546</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.028977394104</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.91371548175812</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.90323710441589</t>
+    <t xml:space="preserve">1.99277853965759</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.02897691726685</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.91371536254883</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.90323686599731</t>
   </si>
   <si>
     <t xml:space="preserve">1.79083371162415</t>
   </si>
   <si>
-    <t xml:space="preserve">2.04707551002502</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.14614343643188</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.06041169166565</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.29664969444275</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.40047955513</t>
+    <t xml:space="preserve">2.0470757484436</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.14614319801331</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.06041193008423</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.29664921760559</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.40047979354858</t>
   </si>
   <si>
     <t xml:space="preserve">2.40762376785278</t>
   </si>
   <si>
-    <t xml:space="preserve">2.32713174819946</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.39571690559387</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.47192239761353</t>
+    <t xml:space="preserve">2.32713150978088</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.39571666717529</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.47192192077637</t>
   </si>
   <si>
     <t xml:space="preserve">2.48382925987244</t>
@@ -272,10 +272,10 @@
     <t xml:space="preserve">2.4385826587677</t>
   </si>
   <si>
-    <t xml:space="preserve">2.5338397026062</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.43143796920776</t>
+    <t xml:space="preserve">2.53383946418762</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.43143773078918</t>
   </si>
   <si>
     <t xml:space="preserve">2.34237265586853</t>
@@ -287,34 +287,34 @@
     <t xml:space="preserve">2.21472859382629</t>
   </si>
   <si>
-    <t xml:space="preserve">2.15281081199646</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.09660983085632</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.09089350700378</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.08517861366272</t>
+    <t xml:space="preserve">2.15281128883362</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.09660935401917</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.09089374542236</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.0851788520813</t>
   </si>
   <si>
     <t xml:space="preserve">2.05279135704041</t>
   </si>
   <si>
-    <t xml:space="preserve">2.04993295669556</t>
+    <t xml:space="preserve">2.04993319511414</t>
   </si>
   <si>
     <t xml:space="preserve">2.08136868476868</t>
   </si>
   <si>
-    <t xml:space="preserve">2.19662928581238</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.09375190734863</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.12042331695557</t>
+    <t xml:space="preserve">2.1966290473938</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.09375214576721</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.12042355537415</t>
   </si>
   <si>
     <t xml:space="preserve">2.0785219669342</t>
@@ -329,16 +329,16 @@
     <t xml:space="preserve">2.30849385261536</t>
   </si>
   <si>
-    <t xml:space="preserve">2.31434082984924</t>
+    <t xml:space="preserve">2.31434106826782</t>
   </si>
   <si>
     <t xml:space="preserve">2.33675384521484</t>
   </si>
   <si>
-    <t xml:space="preserve">2.21592044830322</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.18766164779663</t>
+    <t xml:space="preserve">2.2159206867218</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.18766140937805</t>
   </si>
   <si>
     <t xml:space="preserve">2.09995985031128</t>
@@ -347,88 +347,88 @@
     <t xml:space="preserve">2.09021496772766</t>
   </si>
   <si>
-    <t xml:space="preserve">2.11749982833862</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.15745282173157</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.01615643501282</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.89337384700775</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.83977913856506</t>
+    <t xml:space="preserve">2.11749935150146</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.15745258331299</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.01615619659424</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.89337396621704</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.83977866172791</t>
   </si>
   <si>
     <t xml:space="preserve">1.83393251895905</t>
   </si>
   <si>
-    <t xml:space="preserve">1.78618347644806</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.96353590488434</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.05221104621887</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.10483169555664</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.09606194496155</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.25684785842896</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.70140624046326</t>
+    <t xml:space="preserve">1.78618383407593</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.96353566646576</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.05221080780029</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.10483193397522</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.09606218338013</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.25684762001038</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.70140600204468</t>
   </si>
   <si>
     <t xml:space="preserve">1.68386566638947</t>
   </si>
   <si>
-    <t xml:space="preserve">1.64391243457794</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.55426228046417</t>
+    <t xml:space="preserve">1.64391231536865</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.55426251888275</t>
   </si>
   <si>
     <t xml:space="preserve">1.59713888168335</t>
   </si>
   <si>
-    <t xml:space="preserve">1.52015602588654</t>
+    <t xml:space="preserve">1.52015626430511</t>
   </si>
   <si>
     <t xml:space="preserve">1.41783809661865</t>
   </si>
   <si>
-    <t xml:space="preserve">1.41881287097931</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.31746888160706</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.25802648067474</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.46168863773346</t>
+    <t xml:space="preserve">1.41881275177002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.31746876239777</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.25802624225616</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.46168839931488</t>
   </si>
   <si>
     <t xml:space="preserve">1.52990102767944</t>
   </si>
   <si>
-    <t xml:space="preserve">1.65463161468506</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.57180297374725</t>
+    <t xml:space="preserve">1.65463197231293</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.57180285453796</t>
   </si>
   <si>
     <t xml:space="preserve">1.63904058933258</t>
   </si>
   <si>
-    <t xml:space="preserve">1.65852963924408</t>
+    <t xml:space="preserve">1.65852952003479</t>
   </si>
   <si>
     <t xml:space="preserve">1.6682745218277</t>
@@ -437,55 +437,55 @@
     <t xml:space="preserve">1.65268266201019</t>
   </si>
   <si>
-    <t xml:space="preserve">1.67022275924683</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.72381842136383</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.71115028858185</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.6653505563736</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.67314624786377</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.75012898445129</t>
+    <t xml:space="preserve">1.67022311687469</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.72381818294525</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.71115040779114</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.66535067558289</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.67314612865448</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.75012862682343</t>
   </si>
   <si>
     <t xml:space="preserve">1.69555902481079</t>
   </si>
   <si>
-    <t xml:space="preserve">1.78813290596008</t>
+    <t xml:space="preserve">1.78813278675079</t>
   </si>
   <si>
     <t xml:space="preserve">1.68678879737854</t>
   </si>
   <si>
-    <t xml:space="preserve">1.47825455665588</t>
+    <t xml:space="preserve">1.47825467586517</t>
   </si>
   <si>
     <t xml:space="preserve">1.53769659996033</t>
   </si>
   <si>
-    <t xml:space="preserve">1.54549193382263</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.74720561504364</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.71504807472229</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.74915432929993</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.7384352684021</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.73746085166931</t>
+    <t xml:space="preserve">1.54549217224121</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.74720573425293</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.71504819393158</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.74915397167206</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.73843538761139</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.7374609708786</t>
   </si>
   <si>
     <t xml:space="preserve">1.713099360466</t>
@@ -494,40 +494,40 @@
     <t xml:space="preserve">1.70043122768402</t>
   </si>
   <si>
-    <t xml:space="preserve">1.63709151744843</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.66632544994354</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.56985366344452</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.58057308197021</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.67119777202606</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.70725214481354</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.65755498409271</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.62344896793365</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.66924822330475</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.68094229698181</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.71212470531464</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.73551189899445</t>
+    <t xml:space="preserve">1.63709139823914</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.66632521152496</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.56985378265381</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.58057296276093</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.67119753360748</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.70725226402283</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.65755486488342</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.62344872951508</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.66924858093262</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.6809424161911</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.71212494373322</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.73551142215729</t>
   </si>
   <si>
     <t xml:space="preserve">1.70432901382446</t>
@@ -536,91 +536,91 @@
     <t xml:space="preserve">1.76182222366333</t>
   </si>
   <si>
-    <t xml:space="preserve">1.7647453546524</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.72966504096985</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.69653344154358</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.65170872211456</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.59616410732269</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.62052571773529</t>
+    <t xml:space="preserve">1.76474571228027</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.72966527938843</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.69653379917145</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.65170848369598</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.59616422653198</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.620525598526</t>
   </si>
   <si>
     <t xml:space="preserve">1.55133926868439</t>
   </si>
   <si>
-    <t xml:space="preserve">1.62442350387573</t>
+    <t xml:space="preserve">1.62442326545715</t>
   </si>
   <si>
     <t xml:space="preserve">1.6283210515976</t>
   </si>
   <si>
-    <t xml:space="preserve">1.55523705482483</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.53087544441223</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.56498169898987</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.56790506839752</t>
+    <t xml:space="preserve">1.55523717403412</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.53087568283081</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.56498193740845</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.56790494918823</t>
   </si>
   <si>
     <t xml:space="preserve">1.61370468139648</t>
   </si>
   <si>
-    <t xml:space="preserve">1.57667517662048</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.65073418617249</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.65560626983643</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.63221883773804</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.69068670272827</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.7930052280426</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.83295786380768</t>
+    <t xml:space="preserve">1.57667529582977</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.6507340669632</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.655606508255</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.63221907615662</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.69068658351898</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.79300546646118</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.83295774459839</t>
   </si>
   <si>
     <t xml:space="preserve">1.75305187702179</t>
   </si>
   <si>
-    <t xml:space="preserve">1.84465098381042</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.88362967967987</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.98010182380676</t>
+    <t xml:space="preserve">1.84465134143829</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.88362991809845</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.98010194301605</t>
   </si>
   <si>
     <t xml:space="preserve">2.07462406158447</t>
   </si>
   <si>
-    <t xml:space="preserve">2.06975150108337</t>
+    <t xml:space="preserve">2.06975126266479</t>
   </si>
   <si>
     <t xml:space="preserve">2.12237215042114</t>
   </si>
   <si>
-    <t xml:space="preserve">2.03369688987732</t>
+    <t xml:space="preserve">2.03369665145874</t>
   </si>
   <si>
     <t xml:space="preserve">2.06682825088501</t>
@@ -635,130 +635,130 @@
     <t xml:space="preserve">2.08241963386536</t>
   </si>
   <si>
-    <t xml:space="preserve">2.06487894058228</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.9489187002182</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.92455697059631</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.90311884880066</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.96938228607178</t>
+    <t xml:space="preserve">2.06487941741943</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.94891846179962</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.92455720901489</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.90311896800995</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.9693820476532</t>
   </si>
   <si>
     <t xml:space="preserve">2.00641131401062</t>
   </si>
   <si>
-    <t xml:space="preserve">2.03564548492432</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.03662014007568</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.01518154144287</t>
+    <t xml:space="preserve">2.03564500808716</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.03662037849426</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.01518177986145</t>
   </si>
   <si>
     <t xml:space="preserve">2.00543665885925</t>
   </si>
   <si>
-    <t xml:space="preserve">1.94696950912476</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.86414039134979</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.82613682746887</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.81834053993225</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.8553706407547</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.8456255197525</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.85147225856781</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.82321310043335</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.84660053253174</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.99471807479858</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.95476531982422</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.08729219436646</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.3045961856842</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.33772778511047</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.30167245864868</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.34454894065857</t>
+    <t xml:space="preserve">1.94696915149689</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.8641402721405</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.82613670825958</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.81834042072296</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.85537075996399</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.84562575817108</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.85147202014923</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.82321298122406</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.84660041332245</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.99471843242645</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.9547655582428</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.08729195594788</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.30459570884705</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.33772754669189</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.30167269706726</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.34454917907715</t>
   </si>
   <si>
     <t xml:space="preserve">2.39424657821655</t>
   </si>
   <si>
-    <t xml:space="preserve">2.3552680015564</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.41860771179199</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.43858456611633</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.42153143882751</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.43614888191223</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.48974347114563</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.51410508155823</t>
+    <t xml:space="preserve">2.35526776313782</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.41860818862915</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.43858408927917</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.42153120040894</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.43614864349365</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.48974370956421</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.51410484313965</t>
   </si>
   <si>
     <t xml:space="preserve">2.52141308784485</t>
   </si>
   <si>
-    <t xml:space="preserve">2.46538257598877</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.56770038604736</t>
+    <t xml:space="preserve">2.46538209915161</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.56770014762878</t>
   </si>
   <si>
     <t xml:space="preserve">2.66514611244202</t>
   </si>
   <si>
-    <t xml:space="preserve">2.62129521369934</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.58231687545776</t>
+    <t xml:space="preserve">2.62129545211792</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.58231663703918</t>
   </si>
   <si>
     <t xml:space="preserve">2.45320153236389</t>
   </si>
   <si>
-    <t xml:space="preserve">2.44102025032043</t>
+    <t xml:space="preserve">2.44102048873901</t>
   </si>
   <si>
     <t xml:space="preserve">2.58718919754028</t>
@@ -767,19 +767,19 @@
     <t xml:space="preserve">2.56282782554626</t>
   </si>
   <si>
-    <t xml:space="preserve">2.60424256324768</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.61398696899414</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.75528407096863</t>
+    <t xml:space="preserve">2.6042423248291</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.6139874458313</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.75528359413147</t>
   </si>
   <si>
     <t xml:space="preserve">2.79913401603699</t>
   </si>
   <si>
-    <t xml:space="preserve">2.73335814476013</t>
+    <t xml:space="preserve">2.73335838317871</t>
   </si>
   <si>
     <t xml:space="preserve">2.74066638946533</t>
@@ -788,7 +788,7 @@
     <t xml:space="preserve">2.77477288246155</t>
   </si>
   <si>
-    <t xml:space="preserve">2.73092246055603</t>
+    <t xml:space="preserve">2.73092222213745</t>
   </si>
   <si>
     <t xml:space="preserve">2.60180640220642</t>
@@ -800,34 +800,34 @@
     <t xml:space="preserve">2.61155009269714</t>
   </si>
   <si>
-    <t xml:space="preserve">2.62373113632202</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.68707132339478</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.53359413146973</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.44589281082153</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.47512626647949</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.31726408004761</t>
+    <t xml:space="preserve">2.6237313747406</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.68707180023193</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.53359389305115</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.44589257240295</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.47512650489807</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.31726384162903</t>
   </si>
   <si>
     <t xml:space="preserve">2.32505941390991</t>
   </si>
   <si>
-    <t xml:space="preserve">2.4049654006958</t>
+    <t xml:space="preserve">2.40496563911438</t>
   </si>
   <si>
     <t xml:space="preserve">2.34357452392578</t>
   </si>
   <si>
-    <t xml:space="preserve">2.2626941204071</t>
+    <t xml:space="preserve">2.26269388198853</t>
   </si>
   <si>
     <t xml:space="preserve">2.19253301620483</t>
@@ -836,19 +836,19 @@
     <t xml:space="preserve">2.16914629936218</t>
   </si>
   <si>
-    <t xml:space="preserve">2.1662232875824</t>
+    <t xml:space="preserve">2.16622304916382</t>
   </si>
   <si>
     <t xml:space="preserve">2.08339405059814</t>
   </si>
   <si>
-    <t xml:space="preserve">2.04636478424072</t>
+    <t xml:space="preserve">2.0463650226593</t>
   </si>
   <si>
     <t xml:space="preserve">2.01713109016418</t>
   </si>
   <si>
-    <t xml:space="preserve">2.18278884887695</t>
+    <t xml:space="preserve">2.18278932571411</t>
   </si>
   <si>
     <t xml:space="preserve">2.19155931472778</t>
@@ -860,28 +860,28 @@
     <t xml:space="preserve">2.22761416435242</t>
   </si>
   <si>
-    <t xml:space="preserve">2.13406538963318</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.13893818855286</t>
+    <t xml:space="preserve">2.13406562805176</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.1389377117157</t>
   </si>
   <si>
     <t xml:space="preserve">2.21007370948792</t>
   </si>
   <si>
-    <t xml:space="preserve">2.28218388557434</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.24417972564697</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.18668675422668</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.19058465957642</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.29972434043884</t>
+    <t xml:space="preserve">2.28218364715576</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.24417996406555</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.18668651580811</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.19058442115784</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.29972410202026</t>
   </si>
   <si>
     <t xml:space="preserve">2.27243900299072</t>
@@ -899,31 +899,31 @@
     <t xml:space="preserve">2.38839960098267</t>
   </si>
   <si>
-    <t xml:space="preserve">2.34552311897278</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.36014032363892</t>
+    <t xml:space="preserve">2.34552335739136</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.3601405620575</t>
   </si>
   <si>
     <t xml:space="preserve">2.31629014015198</t>
   </si>
   <si>
-    <t xml:space="preserve">2.28510665893555</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.28023481369019</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.20032858848572</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.21689438819885</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.21494579315186</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.23151183128357</t>
+    <t xml:space="preserve">2.28510689735413</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.28023457527161</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.2003288269043</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.21689414978027</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.21494555473328</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.23151159286499</t>
   </si>
   <si>
     <t xml:space="preserve">2.19545698165894</t>
@@ -932,34 +932,34 @@
     <t xml:space="preserve">2.14283561706543</t>
   </si>
   <si>
-    <t xml:space="preserve">2.12529611587524</t>
+    <t xml:space="preserve">2.12529635429382</t>
   </si>
   <si>
     <t xml:space="preserve">2.23346018791199</t>
   </si>
   <si>
-    <t xml:space="preserve">2.3874249458313</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.4225058555603</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.36988520622253</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.44345664978027</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.50679683685303</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.54333853721619</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.47999906539917</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.46051001548767</t>
+    <t xml:space="preserve">2.38742542266846</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.42250561714172</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.36988544464111</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.44345688819885</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.50679707527161</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.54333877563477</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.47999882698059</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.46050977706909</t>
   </si>
   <si>
     <t xml:space="preserve">2.32116198539734</t>
@@ -971,40 +971,40 @@
     <t xml:space="preserve">2.36793613433838</t>
   </si>
   <si>
-    <t xml:space="preserve">2.32895755767822</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.27536201477051</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.24905228614807</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.28315806388855</t>
+    <t xml:space="preserve">2.32895731925964</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.27536225318909</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.24905252456665</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.28315854072571</t>
   </si>
   <si>
     <t xml:space="preserve">2.27229976654053</t>
   </si>
   <si>
-    <t xml:space="preserve">2.27328729629517</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.30487418174744</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.30191278457642</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.27526068687439</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.20616459846497</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.2071521282196</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.15187430381775</t>
+    <t xml:space="preserve">2.27328753471375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.30487394332886</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.301913022995</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.27526116371155</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.20616483688354</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.20715188980103</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.15187454223633</t>
   </si>
   <si>
     <t xml:space="preserve">2.1972804069519</t>
@@ -1013,37 +1013,37 @@
     <t xml:space="preserve">2.16964221000671</t>
   </si>
   <si>
-    <t xml:space="preserve">2.13015794754028</t>
+    <t xml:space="preserve">2.13015818595886</t>
   </si>
   <si>
     <t xml:space="preserve">2.09758400917053</t>
   </si>
   <si>
-    <t xml:space="preserve">2.10153198242188</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.1795129776001</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.17260313034058</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.12719655036926</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.180499792099</t>
+    <t xml:space="preserve">2.10153222084045</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.17951273918152</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.17260336875916</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.12719678878784</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.18050003051758</t>
   </si>
   <si>
     <t xml:space="preserve">2.15878367424011</t>
   </si>
   <si>
-    <t xml:space="preserve">2.06106066703796</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.07389259338379</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.02059006690979</t>
+    <t xml:space="preserve">2.06106090545654</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.07389307022095</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.02059030532837</t>
   </si>
   <si>
     <t xml:space="preserve">2.11140275001526</t>
@@ -1052,55 +1052,55 @@
     <t xml:space="preserve">2.10251927375793</t>
   </si>
   <si>
-    <t xml:space="preserve">2.15779614448547</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.17062878608704</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.19037127494812</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.17852544784546</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.15483498573303</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.29401636123657</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.37199687957764</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.3147451877594</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.3206684589386</t>
+    <t xml:space="preserve">2.15779638290405</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.17062854766846</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.19037103652954</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.17852520942688</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.15483546257019</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.29401588439941</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.37199640274048</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.31474494934082</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.32066798210144</t>
   </si>
   <si>
     <t xml:space="preserve">2.31375789642334</t>
   </si>
   <si>
-    <t xml:space="preserve">2.34534549713135</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.38779091835022</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.43813276290894</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.44504189491272</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.44306826591492</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.45787453651428</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.37791919708252</t>
+    <t xml:space="preserve">2.34534573554993</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.3877911567688</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.43813252449036</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.44504237174988</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.44306874275208</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.4578742980957</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.37791967391968</t>
   </si>
   <si>
     <t xml:space="preserve">2.3937132358551</t>
@@ -1112,43 +1112,43 @@
     <t xml:space="preserve">2.30388736724854</t>
   </si>
   <si>
-    <t xml:space="preserve">2.27624845504761</t>
+    <t xml:space="preserve">2.27624821662903</t>
   </si>
   <si>
     <t xml:space="preserve">2.30980968475342</t>
   </si>
   <si>
-    <t xml:space="preserve">2.32165503501892</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.29598999023438</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.29204130172729</t>
+    <t xml:space="preserve">2.32165431976318</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.29599022865295</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.29204154014587</t>
   </si>
   <si>
     <t xml:space="preserve">2.33646154403687</t>
   </si>
   <si>
-    <t xml:space="preserve">2.47761631011963</t>
+    <t xml:space="preserve">2.47761607170105</t>
   </si>
   <si>
     <t xml:space="preserve">2.44405484199524</t>
   </si>
   <si>
-    <t xml:space="preserve">2.42628765106201</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.34040999412537</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.41839027404785</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.40753245353699</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.38088035583496</t>
+    <t xml:space="preserve">2.42628741264343</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.34040975570679</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.41839051246643</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.40753269195557</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.38088083267212</t>
   </si>
   <si>
     <t xml:space="preserve">2.34929370880127</t>
@@ -1157,58 +1157,58 @@
     <t xml:space="preserve">2.31968092918396</t>
   </si>
   <si>
-    <t xml:space="preserve">2.34238362312317</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.35225510597229</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.29105520248413</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.31573224067688</t>
+    <t xml:space="preserve">2.34238338470459</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.35225486755371</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.29105496406555</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.31573271751404</t>
   </si>
   <si>
     <t xml:space="preserve">2.33547425270081</t>
   </si>
   <si>
-    <t xml:space="preserve">2.36706161499023</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.33152556419373</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.29500365257263</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.25551915168762</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.23577761650085</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.29993891716003</t>
+    <t xml:space="preserve">2.36706209182739</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.3315258026123</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.29500341415405</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.2555193901062</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.23577737808228</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.29993915557861</t>
   </si>
   <si>
     <t xml:space="preserve">2.37100982666016</t>
   </si>
   <si>
-    <t xml:space="preserve">2.32362914085388</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.26440286636353</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.28513216972351</t>
+    <t xml:space="preserve">2.32362937927246</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.2644031047821</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.28513193130493</t>
   </si>
   <si>
     <t xml:space="preserve">2.31277132034302</t>
   </si>
   <si>
-    <t xml:space="preserve">2.36113882064819</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.30882215499878</t>
+    <t xml:space="preserve">2.36113858222961</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.30882263183594</t>
   </si>
   <si>
     <t xml:space="preserve">2.37693214416504</t>
@@ -1217,25 +1217,25 @@
     <t xml:space="preserve">2.44701647758484</t>
   </si>
   <si>
-    <t xml:space="preserve">2.48748755455017</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.49735879898071</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.53931045532227</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.53190612792969</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.45688700675964</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.41542887687683</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.28414487838745</t>
+    <t xml:space="preserve">2.48748779296875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.49735856056213</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.53931069374084</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.53190684318542</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.45688724517822</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.41542935371399</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.28414511680603</t>
   </si>
   <si>
     <t xml:space="preserve">2.21702241897583</t>
@@ -1244,16 +1244,16 @@
     <t xml:space="preserve">2.16865468025208</t>
   </si>
   <si>
-    <t xml:space="preserve">2.19234490394592</t>
+    <t xml:space="preserve">2.1923451423645</t>
   </si>
   <si>
     <t xml:space="preserve">2.16766762733459</t>
   </si>
   <si>
-    <t xml:space="preserve">2.16174459457397</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.09264802932739</t>
+    <t xml:space="preserve">2.16174483299255</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.09264826774597</t>
   </si>
   <si>
     <t xml:space="preserve">2.09955739974976</t>
@@ -1262,13 +1262,13 @@
     <t xml:space="preserve">2.12028670310974</t>
   </si>
   <si>
-    <t xml:space="preserve">2.09659647941589</t>
+    <t xml:space="preserve">2.09659624099731</t>
   </si>
   <si>
     <t xml:space="preserve">2.06402277946472</t>
   </si>
   <si>
-    <t xml:space="preserve">2.07488012313843</t>
+    <t xml:space="preserve">2.07488036155701</t>
   </si>
   <si>
     <t xml:space="preserve">2.06500911712646</t>
@@ -1283,7 +1283,7 @@
     <t xml:space="preserve">2.07981562614441</t>
   </si>
   <si>
-    <t xml:space="preserve">2.04625463485718</t>
+    <t xml:space="preserve">2.04625415802002</t>
   </si>
   <si>
     <t xml:space="preserve">2.00775742530823</t>
@@ -1292,10 +1292,10 @@
     <t xml:space="preserve">1.91990602016449</t>
   </si>
   <si>
-    <t xml:space="preserve">2.11041593551636</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.08771252632141</t>
+    <t xml:space="preserve">2.11041617393494</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.08771276473999</t>
   </si>
   <si>
     <t xml:space="preserve">2.10646796226501</t>
@@ -1313,19 +1313,19 @@
     <t xml:space="preserve">2.06698346138</t>
   </si>
   <si>
-    <t xml:space="preserve">2.03835773468018</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.02651286125183</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.08672547340393</t>
+    <t xml:space="preserve">2.03835797309875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.02651262283325</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.08672499656677</t>
   </si>
   <si>
     <t xml:space="preserve">2.18346095085144</t>
   </si>
   <si>
-    <t xml:space="preserve">2.26835131645203</t>
+    <t xml:space="preserve">2.26835155487061</t>
   </si>
   <si>
     <t xml:space="preserve">2.20122885704041</t>
@@ -1337,25 +1337,25 @@
     <t xml:space="preserve">2.24861001968384</t>
   </si>
   <si>
-    <t xml:space="preserve">2.22097086906433</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.29302906990051</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.23972582817078</t>
+    <t xml:space="preserve">2.22097039222717</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.29302883148193</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.23972606658936</t>
   </si>
   <si>
     <t xml:space="preserve">2.09857034683228</t>
   </si>
   <si>
-    <t xml:space="preserve">2.05711197853088</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.05119013786316</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.11929988861084</t>
+    <t xml:space="preserve">2.05711221694946</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.05118989944458</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.11930012702942</t>
   </si>
   <si>
     <t xml:space="preserve">2.10745429992676</t>
@@ -1364,13 +1364,13 @@
     <t xml:space="preserve">2.10942888259888</t>
   </si>
   <si>
-    <t xml:space="preserve">2.06797051429749</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.07882881164551</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.1360809803009</t>
+    <t xml:space="preserve">2.06797075271606</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.07882857322693</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.13608050346375</t>
   </si>
   <si>
     <t xml:space="preserve">2.07784128189087</t>
@@ -1382,22 +1382,22 @@
     <t xml:space="preserve">2.09363532066345</t>
   </si>
   <si>
-    <t xml:space="preserve">2.09560942649841</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.13213181495667</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.22788095474243</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.25058341026306</t>
+    <t xml:space="preserve">2.09560918807983</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.13213205337524</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.22788071632385</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.25058364868164</t>
   </si>
   <si>
     <t xml:space="preserve">2.22590637207031</t>
   </si>
   <si>
-    <t xml:space="preserve">2.1824734210968</t>
+    <t xml:space="preserve">2.18247389793396</t>
   </si>
   <si>
     <t xml:space="preserve">2.28315830230713</t>
@@ -1406,19 +1406,19 @@
     <t xml:space="preserve">2.37594509124756</t>
   </si>
   <si>
-    <t xml:space="preserve">2.3739709854126</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.3912456035614</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.29944539070129</t>
+    <t xml:space="preserve">2.37397122383118</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.39124536514282</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.29944515228271</t>
   </si>
   <si>
     <t xml:space="preserve">2.31820011138916</t>
   </si>
   <si>
-    <t xml:space="preserve">2.30043196678162</t>
+    <t xml:space="preserve">2.3004322052002</t>
   </si>
   <si>
     <t xml:space="preserve">2.23775148391724</t>
@@ -1433,28 +1433,28 @@
     <t xml:space="preserve">2.27427458763123</t>
   </si>
   <si>
-    <t xml:space="preserve">2.2441680431366</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.36064529418945</t>
+    <t xml:space="preserve">2.24416780471802</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.36064505577087</t>
   </si>
   <si>
     <t xml:space="preserve">2.36508727073669</t>
   </si>
   <si>
-    <t xml:space="preserve">2.35521626472473</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.3591639995575</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.31227779388428</t>
+    <t xml:space="preserve">2.35521578788757</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.35916447639465</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.3122775554657</t>
   </si>
   <si>
     <t xml:space="preserve">2.40012907981873</t>
   </si>
   <si>
-    <t xml:space="preserve">2.40062284469604</t>
+    <t xml:space="preserve">2.4006233215332</t>
   </si>
   <si>
     <t xml:space="preserve">2.40506529808044</t>
@@ -1463,22 +1463,22 @@
     <t xml:space="preserve">2.40259695053101</t>
   </si>
   <si>
-    <t xml:space="preserve">2.43122220039368</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.41098737716675</t>
+    <t xml:space="preserve">2.43122267723083</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.41098713874817</t>
   </si>
   <si>
     <t xml:space="preserve">2.22738718986511</t>
   </si>
   <si>
-    <t xml:space="preserve">2.31869387626648</t>
+    <t xml:space="preserve">2.3186936378479</t>
   </si>
   <si>
     <t xml:space="preserve">2.35028100013733</t>
   </si>
   <si>
-    <t xml:space="preserve">2.27674198150635</t>
+    <t xml:space="preserve">2.27674174308777</t>
   </si>
   <si>
     <t xml:space="preserve">2.31918716430664</t>
@@ -1490,16 +1490,16 @@
     <t xml:space="preserve">2.27131247520447</t>
   </si>
   <si>
-    <t xml:space="preserve">2.29796457290649</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.30586099624634</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.29006767272949</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.24564790725708</t>
+    <t xml:space="preserve">2.29796481132507</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.30586123466492</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.29006791114807</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.2456476688385</t>
   </si>
   <si>
     <t xml:space="preserve">2.25206446647644</t>
@@ -1511,37 +1511,37 @@
     <t xml:space="preserve">2.2476224899292</t>
   </si>
   <si>
-    <t xml:space="preserve">2.22886729240417</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.23084187507629</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.31721305847168</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.32560300827026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.33448719978333</t>
+    <t xml:space="preserve">2.22886753082275</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.23084211349487</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.31721234321594</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.32560276985168</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.33448648452759</t>
   </si>
   <si>
     <t xml:space="preserve">2.35817766189575</t>
   </si>
   <si>
-    <t xml:space="preserve">2.40851950645447</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.3798942565918</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.38630962371826</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.41197466850281</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.36804890632629</t>
+    <t xml:space="preserve">2.40851974487305</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.37989377975464</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.38630986213684</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.41197443008423</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.36804819107056</t>
   </si>
   <si>
     <t xml:space="preserve">2.33843541145325</t>
@@ -1550,16 +1550,16 @@
     <t xml:space="preserve">2.35324215888977</t>
   </si>
   <si>
-    <t xml:space="preserve">2.34189081192017</t>
+    <t xml:space="preserve">2.34189057350159</t>
   </si>
   <si>
     <t xml:space="preserve">2.35373592376709</t>
   </si>
   <si>
-    <t xml:space="preserve">2.33596801757812</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.32856488227844</t>
+    <t xml:space="preserve">2.33596777915955</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.32856464385986</t>
   </si>
   <si>
     <t xml:space="preserve">2.42036485671997</t>
@@ -1568,7 +1568,7 @@
     <t xml:space="preserve">2.42924857139587</t>
   </si>
   <si>
-    <t xml:space="preserve">2.47662949562073</t>
+    <t xml:space="preserve">2.47662997245789</t>
   </si>
   <si>
     <t xml:space="preserve">2.5121648311615</t>
@@ -1577,7 +1577,7 @@
     <t xml:space="preserve">2.54079055786133</t>
   </si>
   <si>
-    <t xml:space="preserve">2.46626472473145</t>
+    <t xml:space="preserve">2.46626496315002</t>
   </si>
   <si>
     <t xml:space="preserve">2.46675848960876</t>
@@ -1586,13 +1586,13 @@
     <t xml:space="preserve">2.30290031433105</t>
   </si>
   <si>
-    <t xml:space="preserve">2.32412981987</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.36153364181519</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.38731265068054</t>
+    <t xml:space="preserve">2.32413005828857</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.36153388023376</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.38731288909912</t>
   </si>
   <si>
     <t xml:space="preserve">2.3579957485199</t>
@@ -1601,22 +1601,22 @@
     <t xml:space="preserve">2.31048178672791</t>
   </si>
   <si>
-    <t xml:space="preserve">2.17552256584167</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.06583666801453</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.07341861724854</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.07392430305481</t>
+    <t xml:space="preserve">2.17552208900452</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.06583690643311</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.07341837882996</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.07392406463623</t>
   </si>
   <si>
     <t xml:space="preserve">2.23718953132629</t>
   </si>
   <si>
-    <t xml:space="preserve">2.17147874832153</t>
+    <t xml:space="preserve">2.17147850990295</t>
   </si>
   <si>
     <t xml:space="preserve">2.09768080711365</t>
@@ -1625,25 +1625,25 @@
     <t xml:space="preserve">2.09667038917542</t>
   </si>
   <si>
-    <t xml:space="preserve">2.13710737228394</t>
+    <t xml:space="preserve">2.13710689544678</t>
   </si>
   <si>
     <t xml:space="preserve">2.07948470115662</t>
   </si>
   <si>
-    <t xml:space="preserve">2.16996264457703</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.19574165344238</t>
+    <t xml:space="preserve">2.16996312141418</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.1957414150238</t>
   </si>
   <si>
     <t xml:space="preserve">2.23112368583679</t>
   </si>
   <si>
-    <t xml:space="preserve">2.25841903686523</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.19927978515625</t>
+    <t xml:space="preserve">2.25841879844666</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.19927954673767</t>
   </si>
   <si>
     <t xml:space="preserve">2.18866467475891</t>
@@ -1655,10 +1655,10 @@
     <t xml:space="preserve">2.32008600234985</t>
   </si>
   <si>
-    <t xml:space="preserve">2.25184845924377</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.41764044761658</t>
+    <t xml:space="preserve">2.25184798240662</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.417640209198</t>
   </si>
   <si>
     <t xml:space="preserve">2.36810541152954</t>
@@ -1670,13 +1670,13 @@
     <t xml:space="preserve">2.34738039970398</t>
   </si>
   <si>
-    <t xml:space="preserve">2.36861085891724</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.37922501564026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.37012672424316</t>
+    <t xml:space="preserve">2.36861062049866</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.37922525405884</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.37012696266174</t>
   </si>
   <si>
     <t xml:space="preserve">2.3726544380188</t>
@@ -1685,91 +1685,91 @@
     <t xml:space="preserve">2.36355590820312</t>
   </si>
   <si>
-    <t xml:space="preserve">2.41005873680115</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.41814613342285</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.37113785743713</t>
+    <t xml:space="preserve">2.41005897521973</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.41814589500427</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.37113761901855</t>
   </si>
   <si>
     <t xml:space="preserve">2.33171153068542</t>
   </si>
   <si>
-    <t xml:space="preserve">2.34788608551025</t>
+    <t xml:space="preserve">2.34788632392883</t>
   </si>
   <si>
     <t xml:space="preserve">2.38023638725281</t>
   </si>
   <si>
-    <t xml:space="preserve">2.33828282356262</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.29481244087219</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.34131550788879</t>
+    <t xml:space="preserve">2.3382830619812</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.29481267929077</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.34131526947021</t>
   </si>
   <si>
     <t xml:space="preserve">2.33878755569458</t>
   </si>
   <si>
-    <t xml:space="preserve">2.37315964698792</t>
+    <t xml:space="preserve">2.37315917015076</t>
   </si>
   <si>
     <t xml:space="preserve">2.40652060508728</t>
   </si>
   <si>
-    <t xml:space="preserve">2.38276362419128</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.41662955284119</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.40550947189331</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.31958031654358</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.31351399421692</t>
+    <t xml:space="preserve">2.38276386260986</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.41662931442261</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.40550923347473</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.31958055496216</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.31351447105408</t>
   </si>
   <si>
     <t xml:space="preserve">2.31503129005432</t>
   </si>
   <si>
-    <t xml:space="preserve">2.33524966239929</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.19725751876831</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.17249011993408</t>
+    <t xml:space="preserve">2.33524942398071</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.19725775718689</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.1724898815155</t>
   </si>
   <si>
     <t xml:space="preserve">2.14216184616089</t>
   </si>
   <si>
-    <t xml:space="preserve">2.08908772468567</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.06937527656555</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.0668478012085</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.02186131477356</t>
+    <t xml:space="preserve">2.08908796310425</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.06937503814697</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.06684756278992</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.02186107635498</t>
   </si>
   <si>
     <t xml:space="preserve">2.02236652374268</t>
   </si>
   <si>
-    <t xml:space="preserve">2.06735277175903</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.0663423538208</t>
+    <t xml:space="preserve">2.06735301017761</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.06634259223938</t>
   </si>
   <si>
     <t xml:space="preserve">2.05016684532166</t>
@@ -1778,34 +1778,34 @@
     <t xml:space="preserve">2.04511308670044</t>
   </si>
   <si>
-    <t xml:space="preserve">2.03702592849731</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.00416994094849</t>
+    <t xml:space="preserve">2.03702545166016</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.00416970252991</t>
   </si>
   <si>
     <t xml:space="preserve">2.01680660247803</t>
   </si>
   <si>
-    <t xml:space="preserve">1.94098699092865</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.92026281356812</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.92936158180237</t>
+    <t xml:space="preserve">1.94098711013794</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.92026305198669</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.9293612241745</t>
   </si>
   <si>
     <t xml:space="preserve">2.00012612342834</t>
   </si>
   <si>
-    <t xml:space="preserve">2.08555006980896</t>
+    <t xml:space="preserve">2.08555030822754</t>
   </si>
   <si>
     <t xml:space="preserve">2.08959341049194</t>
   </si>
   <si>
-    <t xml:space="preserve">2.14519453048706</t>
+    <t xml:space="preserve">2.14519429206848</t>
   </si>
   <si>
     <t xml:space="preserve">2.13458013534546</t>
@@ -1814,7 +1814,7 @@
     <t xml:space="preserve">2.13660168647766</t>
   </si>
   <si>
-    <t xml:space="preserve">2.12952542304993</t>
+    <t xml:space="preserve">2.12952589988708</t>
   </si>
   <si>
     <t xml:space="preserve">2.17855548858643</t>
@@ -1823,61 +1823,61 @@
     <t xml:space="preserve">2.21141076087952</t>
   </si>
   <si>
-    <t xml:space="preserve">2.19068694114685</t>
+    <t xml:space="preserve">2.19068670272827</t>
   </si>
   <si>
     <t xml:space="preserve">2.14873337745667</t>
   </si>
   <si>
-    <t xml:space="preserve">2.17350125312805</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.20029091835022</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.22253060340881</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.01579523086548</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.93643796443939</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.90257167816162</t>
+    <t xml:space="preserve">2.17350101470947</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.20029044151306</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.22253036499023</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.01579570770264</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.93643760681152</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.90257143974304</t>
   </si>
   <si>
     <t xml:space="preserve">1.87780296802521</t>
   </si>
   <si>
-    <t xml:space="preserve">1.88942921161652</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.85505759716034</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.8242244720459</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.78783071041107</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.82675123214722</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.79237937927246</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.80602765083313</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.81866383552551</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.80299460887909</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.80552184581757</t>
+    <t xml:space="preserve">1.88942909240723</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.85505783557892</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.82422411441803</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.7878303527832</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.82675135135651</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.79237985610962</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.80602729320526</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.8186639547348</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.80299496650696</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.80552196502686</t>
   </si>
   <si>
     <t xml:space="preserve">1.76660120487213</t>
@@ -1889,16 +1889,16 @@
     <t xml:space="preserve">1.70847272872925</t>
   </si>
   <si>
-    <t xml:space="preserve">1.67157351970673</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.62405967712402</t>
+    <t xml:space="preserve">1.67157340049744</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.62405979633331</t>
   </si>
   <si>
     <t xml:space="preserve">1.66146457195282</t>
   </si>
   <si>
-    <t xml:space="preserve">1.64882791042328</t>
+    <t xml:space="preserve">1.64882814884186</t>
   </si>
   <si>
     <t xml:space="preserve">1.72161495685577</t>
@@ -1913,31 +1913,31 @@
     <t xml:space="preserve">1.70746159553528</t>
   </si>
   <si>
-    <t xml:space="preserve">1.77671039104462</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.71554923057556</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.70291244983673</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.73374593257904</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.74688804149628</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.76255738735199</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.76508510112762</t>
+    <t xml:space="preserve">1.77671027183533</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.71554899215698</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.70291256904602</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.73374581336975</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.74688827991486</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.7625572681427</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.76508498191833</t>
   </si>
   <si>
     <t xml:space="preserve">1.71352756023407</t>
   </si>
   <si>
-    <t xml:space="preserve">1.72768020629883</t>
+    <t xml:space="preserve">1.72768032550812</t>
   </si>
   <si>
     <t xml:space="preserve">1.69634175300598</t>
@@ -1946,10 +1946,10 @@
     <t xml:space="preserve">1.7120109796524</t>
   </si>
   <si>
-    <t xml:space="preserve">1.69229805469513</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.75345897674561</t>
+    <t xml:space="preserve">1.69229793548584</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.75345873832703</t>
   </si>
   <si>
     <t xml:space="preserve">1.76356863975525</t>
@@ -1958,16 +1958,16 @@
     <t xml:space="preserve">1.76457965373993</t>
   </si>
   <si>
-    <t xml:space="preserve">1.85910129547119</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.79389631748199</t>
+    <t xml:space="preserve">1.85910153388977</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.79389619827271</t>
   </si>
   <si>
     <t xml:space="preserve">1.81007122993469</t>
   </si>
   <si>
-    <t xml:space="preserve">1.81916964054108</t>
+    <t xml:space="preserve">1.8191694021225</t>
   </si>
   <si>
     <t xml:space="preserve">1.90307700634003</t>
@@ -1976,88 +1976,88 @@
     <t xml:space="preserve">1.87072682380676</t>
   </si>
   <si>
-    <t xml:space="preserve">1.9056042432785</t>
+    <t xml:space="preserve">1.90560412406921</t>
   </si>
   <si>
     <t xml:space="preserve">1.84494829177856</t>
   </si>
   <si>
-    <t xml:space="preserve">1.81563150882721</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.78479778766632</t>
+    <t xml:space="preserve">1.81563138961792</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.78479814529419</t>
   </si>
   <si>
     <t xml:space="preserve">1.76761221885681</t>
   </si>
   <si>
-    <t xml:space="preserve">1.76053583621979</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.73324036598206</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.69937455654144</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.69128692150116</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.72565853595734</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.69280314445496</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.68016636371613</t>
+    <t xml:space="preserve">1.76053595542908</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.73324012756348</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.69937431812286</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.69128704071045</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.72565865516663</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.69280290603638</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.68016612529755</t>
   </si>
   <si>
     <t xml:space="preserve">1.65742075443268</t>
   </si>
   <si>
-    <t xml:space="preserve">1.70038533210754</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.66601383686066</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.65489327907562</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.71049427986145</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.72110962867737</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.68319976329803</t>
+    <t xml:space="preserve">1.70038545131683</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.66601371765137</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.65489315986633</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.71049439907074</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.72110950946808</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.68319964408875</t>
   </si>
   <si>
     <t xml:space="preserve">1.67612254619598</t>
   </si>
   <si>
-    <t xml:space="preserve">1.6811774969101</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.652871966362</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.58918237686157</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.51386857032776</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.54722905158997</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.55329513549805</t>
+    <t xml:space="preserve">1.68117737770081</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.65287184715271</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.58918249607086</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.51386845111847</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.54722917079926</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.55329501628876</t>
   </si>
   <si>
     <t xml:space="preserve">1.54419660568237</t>
   </si>
   <si>
-    <t xml:space="preserve">1.55228388309479</t>
+    <t xml:space="preserve">1.5522837638855</t>
   </si>
   <si>
     <t xml:space="preserve">1.54369080066681</t>
@@ -2066,13 +2066,13 @@
     <t xml:space="preserve">1.52094483375549</t>
   </si>
   <si>
-    <t xml:space="preserve">1.52549386024475</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.59221589565277</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.57300782203674</t>
+    <t xml:space="preserve">1.52549397945404</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.59221577644348</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.57300770282745</t>
   </si>
   <si>
     <t xml:space="preserve">1.57705128192902</t>
@@ -2084,37 +2084,37 @@
     <t xml:space="preserve">1.49415564537048</t>
   </si>
   <si>
-    <t xml:space="preserve">1.49870419502258</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.50123190879822</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.5037590265274</t>
+    <t xml:space="preserve">1.49870431423187</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.50123178958893</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.50375890731812</t>
   </si>
   <si>
     <t xml:space="preserve">1.53914165496826</t>
   </si>
   <si>
-    <t xml:space="preserve">1.52347254753113</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.65792644023895</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.72666990756989</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.70897817611694</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.70240700244904</t>
+    <t xml:space="preserve">1.52347242832184</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.65792655944824</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.72666966915131</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.70897829532623</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.70240724086761</t>
   </si>
   <si>
     <t xml:space="preserve">1.78125977516174</t>
   </si>
   <si>
-    <t xml:space="preserve">1.77418339252472</t>
+    <t xml:space="preserve">1.7741836309433</t>
   </si>
   <si>
     <t xml:space="preserve">1.75901925563812</t>
@@ -2123,43 +2123,43 @@
     <t xml:space="preserve">1.73071348667145</t>
   </si>
   <si>
-    <t xml:space="preserve">1.75093185901642</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.76862299442291</t>
+    <t xml:space="preserve">1.75093173980713</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.7686231136322</t>
   </si>
   <si>
     <t xml:space="preserve">1.78024876117706</t>
   </si>
   <si>
-    <t xml:space="preserve">1.82826769351959</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.86921000480652</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.86415612697601</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.85809063911438</t>
+    <t xml:space="preserve">1.82826781272888</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.8692102432251</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.86415600776672</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.85809051990509</t>
   </si>
   <si>
     <t xml:space="preserve">1.87325477600098</t>
   </si>
   <si>
-    <t xml:space="preserve">1.81815838813782</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.7994567155838</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.78833603858948</t>
+    <t xml:space="preserve">1.8181586265564</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.79945683479309</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.78833615779877</t>
   </si>
   <si>
     <t xml:space="preserve">1.79895114898682</t>
   </si>
   <si>
-    <t xml:space="preserve">1.83534407615662</t>
+    <t xml:space="preserve">1.83534443378448</t>
   </si>
   <si>
     <t xml:space="preserve">1.8722437620163</t>
@@ -2174,40 +2174,40 @@
     <t xml:space="preserve">1.87022149562836</t>
   </si>
   <si>
-    <t xml:space="preserve">1.84444272518158</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.83686065673828</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.82119154930115</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.85000312328339</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.84242117404938</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.84039950370789</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.86567234992981</t>
+    <t xml:space="preserve">1.84444260597229</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.83686089515686</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.82119166851044</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.85000336170197</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.84242105484009</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.84039902687073</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.86567211151123</t>
   </si>
   <si>
     <t xml:space="preserve">1.85151970386505</t>
   </si>
   <si>
-    <t xml:space="preserve">1.86971569061279</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.87173771858215</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.88791263103485</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.88892364501953</t>
+    <t xml:space="preserve">1.86971604824066</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.87173819541931</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.88791298866272</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.88892376422882</t>
   </si>
   <si>
     <t xml:space="preserve">1.91874647140503</t>
@@ -2216,7 +2216,7 @@
     <t xml:space="preserve">1.95463454723358</t>
   </si>
   <si>
-    <t xml:space="preserve">2.00619220733643</t>
+    <t xml:space="preserve">2.00619196891785</t>
   </si>
   <si>
     <t xml:space="preserve">2.04005813598633</t>
@@ -2234,10 +2234,10 @@
     <t xml:space="preserve">2.07544088363647</t>
   </si>
   <si>
-    <t xml:space="preserve">2.10930681228638</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.12649250030518</t>
+    <t xml:space="preserve">2.10930705070496</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.12649297714233</t>
   </si>
   <si>
     <t xml:space="preserve">2.13255786895752</t>
@@ -2246,130 +2246,130 @@
     <t xml:space="preserve">2.16541361808777</t>
   </si>
   <si>
-    <t xml:space="preserve">2.13053631782532</t>
+    <t xml:space="preserve">2.1305365562439</t>
   </si>
   <si>
     <t xml:space="preserve">2.12396478652954</t>
   </si>
   <si>
-    <t xml:space="preserve">2.07998991012573</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.06836414337158</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.02388334274292</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.00164270401001</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.9713146686554</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.98900640010834</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.95412886142731</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.99810481071472</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.94467711448669</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.89345967769623</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.85321748256683</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.82865476608276</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.84746932983398</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.79834318161011</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.79938769340515</t>
+    <t xml:space="preserve">2.07999014854431</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.068363904953</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.02388310432434</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.00164246559143</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.97131478786469</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.98900651931763</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.95412874221802</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.99810457229614</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.9446769952774</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.89345979690552</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.85321760177612</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.82865512371063</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.84746956825256</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.79834306240082</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.79938781261444</t>
   </si>
   <si>
     <t xml:space="preserve">1.78998112678528</t>
   </si>
   <si>
-    <t xml:space="preserve">1.77743756771088</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.76855301856995</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.75444221496582</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.78527772426605</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.75287461280823</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.7319700717926</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.72883367538452</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.78318679332733</t>
+    <t xml:space="preserve">1.77743780612946</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.76855289936066</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.75444209575653</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.78527760505676</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.75287473201752</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.73196995258331</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.72883379459381</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.78318667411804</t>
   </si>
   <si>
     <t xml:space="preserve">1.79991042613983</t>
   </si>
   <si>
-    <t xml:space="preserve">1.77952873706818</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.8009557723999</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.79468405246735</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.80827212333679</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.84903693199158</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.88353061676025</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.88143956661224</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.91331958770752</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.89241528511047</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.89136934280396</t>
+    <t xml:space="preserve">1.77952861785889</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.80095565319061</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.79468429088593</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.80827224254608</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.84903717041016</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.88353049755096</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.88143980503082</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.91331994533539</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.89241516590118</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.89136970043182</t>
   </si>
   <si>
     <t xml:space="preserve">1.90234434604645</t>
   </si>
   <si>
-    <t xml:space="preserve">1.87255525588989</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.8626252412796</t>
+    <t xml:space="preserve">1.87255501747131</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.86262512207031</t>
   </si>
   <si>
     <t xml:space="preserve">1.90077710151672</t>
   </si>
   <si>
-    <t xml:space="preserve">1.97498917579651</t>
+    <t xml:space="preserve">1.97498905658722</t>
   </si>
   <si>
     <t xml:space="preserve">2.03247761726379</t>
@@ -2378,67 +2378,67 @@
     <t xml:space="preserve">2.03665828704834</t>
   </si>
   <si>
-    <t xml:space="preserve">2.01836657524109</t>
+    <t xml:space="preserve">2.01836681365967</t>
   </si>
   <si>
     <t xml:space="preserve">2.01000475883484</t>
   </si>
   <si>
-    <t xml:space="preserve">1.99328100681305</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.00216579437256</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.98805463314056</t>
+    <t xml:space="preserve">1.99328088760376</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.00216555595398</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.98805475234985</t>
   </si>
   <si>
     <t xml:space="preserve">2.01627659797668</t>
   </si>
   <si>
-    <t xml:space="preserve">1.98387384414673</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.95878803730011</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.96505904197693</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.95460748672485</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.90495789051056</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.88927900791168</t>
+    <t xml:space="preserve">1.98387372493744</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.9587881565094</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.96505880355835</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.95460724830627</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.90495812892914</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.88927888870239</t>
   </si>
   <si>
     <t xml:space="preserve">1.86941981315613</t>
   </si>
   <si>
-    <t xml:space="preserve">1.84381055831909</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.77168929576874</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.76071381568909</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.80775046348572</t>
+    <t xml:space="preserve">1.84381067752838</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.77168941497803</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.76071405410767</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.80775034427643</t>
   </si>
   <si>
     <t xml:space="preserve">1.78005111217499</t>
   </si>
   <si>
-    <t xml:space="preserve">1.80722773075104</t>
+    <t xml:space="preserve">1.80722784996033</t>
   </si>
   <si>
     <t xml:space="preserve">1.78214108943939</t>
   </si>
   <si>
-    <t xml:space="preserve">1.81611216068268</t>
+    <t xml:space="preserve">1.81611227989197</t>
   </si>
   <si>
     <t xml:space="preserve">1.67239081859589</t>
@@ -2447,10 +2447,10 @@
     <t xml:space="preserve">1.63685262203217</t>
   </si>
   <si>
-    <t xml:space="preserve">1.65566718578339</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.5741378068924</t>
+    <t xml:space="preserve">1.65566730499268</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.57413768768311</t>
   </si>
   <si>
     <t xml:space="preserve">1.60863077640533</t>
@@ -2459,124 +2459,124 @@
     <t xml:space="preserve">1.62483263015747</t>
   </si>
   <si>
-    <t xml:space="preserve">1.57309234142303</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.60026895999908</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.60654067993164</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.59295248985291</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.60392713546753</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.6765718460083</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.66507458686829</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.6979992389679</t>
+    <t xml:space="preserve">1.57309222221375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.60026872158051</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.60654056072235</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.59295237064362</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.60392701625824</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.67657172679901</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.665074467659</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.69799935817719</t>
   </si>
   <si>
     <t xml:space="preserve">1.68441092967987</t>
   </si>
   <si>
-    <t xml:space="preserve">1.6880692243576</t>
+    <t xml:space="preserve">1.68806934356689</t>
   </si>
   <si>
     <t xml:space="preserve">1.71629106998444</t>
   </si>
   <si>
-    <t xml:space="preserve">1.73353755474091</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.73876357078552</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.74712586402893</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.80618214607239</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.8265643119812</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.80879509449005</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.83649396896362</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.88300764560699</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.89189255237579</t>
+    <t xml:space="preserve">1.73353731632233</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.7387638092041</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.74712562561035</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.80618238449097</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.82656407356262</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.80879497528076</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.8364942073822</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.88300776481628</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.89189267158508</t>
   </si>
   <si>
     <t xml:space="preserve">1.83022248744965</t>
   </si>
   <si>
-    <t xml:space="preserve">1.8411979675293</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.92168164253235</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.86419308185577</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.83597135543823</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.81663489341736</t>
+    <t xml:space="preserve">1.84119772911072</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.92168188095093</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.86419343948364</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.83597123622894</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.81663501262665</t>
   </si>
   <si>
     <t xml:space="preserve">1.82760965824127</t>
   </si>
   <si>
-    <t xml:space="preserve">1.85112750530243</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.82290589809418</t>
+    <t xml:space="preserve">1.85112774372101</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.82290577888489</t>
   </si>
   <si>
     <t xml:space="preserve">1.83388137817383</t>
   </si>
   <si>
-    <t xml:space="preserve">1.81715667247772</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.82342886924744</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.83440387248993</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.90129947662354</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.92220413684845</t>
+    <t xml:space="preserve">1.8171569108963</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.82342863082886</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.83440411090851</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.90129971504211</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.92220449447632</t>
   </si>
   <si>
     <t xml:space="preserve">1.96349167823792</t>
   </si>
   <si>
-    <t xml:space="preserve">1.99223577976227</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.04658842086792</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.0998957157135</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.12289142608643</t>
+    <t xml:space="preserve">1.9922354221344</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.04658818244934</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.09989595413208</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.122891664505</t>
   </si>
   <si>
     <t xml:space="preserve">2.15111231803894</t>
@@ -2585,16 +2585,16 @@
     <t xml:space="preserve">2.11139321327209</t>
   </si>
   <si>
-    <t xml:space="preserve">2.11034870147705</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.12602663040161</t>
+    <t xml:space="preserve">2.11034846305847</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.12602686882019</t>
   </si>
   <si>
     <t xml:space="preserve">2.12654948234558</t>
   </si>
   <si>
-    <t xml:space="preserve">2.08630800247192</t>
+    <t xml:space="preserve">2.08630776405334</t>
   </si>
   <si>
     <t xml:space="preserve">2.0941469669342</t>
@@ -2612,25 +2612,25 @@
     <t xml:space="preserve">2.1976261138916</t>
   </si>
   <si>
-    <t xml:space="preserve">2.22950649261475</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.20494246482849</t>
+    <t xml:space="preserve">2.22950625419617</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.20494270324707</t>
   </si>
   <si>
     <t xml:space="preserve">2.24152636528015</t>
   </si>
   <si>
-    <t xml:space="preserve">2.25772762298584</t>
+    <t xml:space="preserve">2.25772738456726</t>
   </si>
   <si>
     <t xml:space="preserve">2.27288365364075</t>
   </si>
   <si>
-    <t xml:space="preserve">2.26504468917847</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.28176808357239</t>
+    <t xml:space="preserve">2.26504445075989</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.28176856040955</t>
   </si>
   <si>
     <t xml:space="preserve">2.30946731567383</t>
@@ -2639,10 +2639,10 @@
     <t xml:space="preserve">2.3763632774353</t>
   </si>
   <si>
-    <t xml:space="preserve">2.40824317932129</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.39465475082397</t>
+    <t xml:space="preserve">2.40824341773987</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.39465498924255</t>
   </si>
   <si>
     <t xml:space="preserve">2.33716678619385</t>
@@ -2657,10 +2657,10 @@
     <t xml:space="preserve">2.32357835769653</t>
   </si>
   <si>
-    <t xml:space="preserve">2.29326581954956</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.29692482948303</t>
+    <t xml:space="preserve">2.29326558113098</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.29692459106445</t>
   </si>
   <si>
     <t xml:space="preserve">2.2498881816864</t>
@@ -2675,19 +2675,19 @@
     <t xml:space="preserve">2.30633187294006</t>
   </si>
   <si>
-    <t xml:space="preserve">2.3288049697876</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.30110573768616</t>
+    <t xml:space="preserve">2.32880473136902</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.30110549926758</t>
   </si>
   <si>
     <t xml:space="preserve">2.32566833496094</t>
   </si>
   <si>
-    <t xml:space="preserve">2.32253313064575</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.35336780548096</t>
+    <t xml:space="preserve">2.32253289222717</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.35336756706238</t>
   </si>
   <si>
     <t xml:space="preserve">2.33612132072449</t>
@@ -2696,7 +2696,7 @@
     <t xml:space="preserve">2.36538767814636</t>
   </si>
   <si>
-    <t xml:space="preserve">2.38315653800964</t>
+    <t xml:space="preserve">2.3831570148468</t>
   </si>
   <si>
     <t xml:space="preserve">2.36016130447388</t>
@@ -2711,16 +2711,16 @@
     <t xml:space="preserve">2.34291481971741</t>
   </si>
   <si>
-    <t xml:space="preserve">2.40144896507263</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.39988136291504</t>
+    <t xml:space="preserve">2.40144848823547</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.39988112449646</t>
   </si>
   <si>
     <t xml:space="preserve">2.350754737854</t>
   </si>
   <si>
-    <t xml:space="preserve">2.3575484752655</t>
+    <t xml:space="preserve">2.35754871368408</t>
   </si>
   <si>
     <t xml:space="preserve">2.38002133369446</t>
@@ -2732,16 +2732,16 @@
     <t xml:space="preserve">2.4145143032074</t>
   </si>
   <si>
-    <t xml:space="preserve">2.40406227111816</t>
+    <t xml:space="preserve">2.40406203269958</t>
   </si>
   <si>
     <t xml:space="preserve">2.41190147399902</t>
   </si>
   <si>
-    <t xml:space="preserve">2.39047384262085</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.38420248031616</t>
+    <t xml:space="preserve">2.39047408103943</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.38420224189758</t>
   </si>
   <si>
     <t xml:space="preserve">2.40301704406738</t>
@@ -2756,13 +2756,13 @@
     <t xml:space="preserve">2.33037209510803</t>
   </si>
   <si>
-    <t xml:space="preserve">2.33089470863342</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.31626105308533</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.36329770088196</t>
+    <t xml:space="preserve">2.330894947052</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.31626129150391</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.36329746246338</t>
   </si>
   <si>
     <t xml:space="preserve">2.34239220619202</t>
@@ -2771,52 +2771,52 @@
     <t xml:space="preserve">2.26086354255676</t>
   </si>
   <si>
-    <t xml:space="preserve">2.16888165473938</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.21330404281616</t>
+    <t xml:space="preserve">2.16888189315796</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.21330451965332</t>
   </si>
   <si>
     <t xml:space="preserve">2.26295375823975</t>
   </si>
   <si>
-    <t xml:space="preserve">2.28751707077026</t>
+    <t xml:space="preserve">2.28751730918884</t>
   </si>
   <si>
     <t xml:space="preserve">2.26608991622925</t>
   </si>
   <si>
-    <t xml:space="preserve">2.27497458457947</t>
+    <t xml:space="preserve">2.27497434616089</t>
   </si>
   <si>
     <t xml:space="preserve">2.28542637825012</t>
   </si>
   <si>
-    <t xml:space="preserve">2.36956882476807</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.34918689727783</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.42705678939819</t>
+    <t xml:space="preserve">2.36956858634949</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.34918665885925</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.42705702781677</t>
   </si>
   <si>
     <t xml:space="preserve">2.16417813301086</t>
   </si>
   <si>
-    <t xml:space="preserve">2.1568615436554</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.19187712669373</t>
+    <t xml:space="preserve">2.15686178207397</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.1918773651123</t>
   </si>
   <si>
     <t xml:space="preserve">2.12811779975891</t>
   </si>
   <si>
-    <t xml:space="preserve">2.00477838516235</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.00686931610107</t>
+    <t xml:space="preserve">2.00477814674377</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.0068690776825</t>
   </si>
   <si>
     <t xml:space="preserve">2.05129218101501</t>
@@ -2825,25 +2825,25 @@
     <t xml:space="preserve">1.97446620464325</t>
   </si>
   <si>
-    <t xml:space="preserve">1.88091707229614</t>
+    <t xml:space="preserve">1.88091695308685</t>
   </si>
   <si>
     <t xml:space="preserve">1.73771834373474</t>
   </si>
   <si>
-    <t xml:space="preserve">1.69277262687683</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.631103515625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.59661078453064</t>
+    <t xml:space="preserve">1.69277250766754</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.63110363483429</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.59661066532135</t>
   </si>
   <si>
     <t xml:space="preserve">1.37972247600555</t>
   </si>
   <si>
-    <t xml:space="preserve">1.31282687187195</t>
+    <t xml:space="preserve">1.31282699108124</t>
   </si>
   <si>
     <t xml:space="preserve">1.31596255302429</t>
@@ -2852,25 +2852,25 @@
     <t xml:space="preserve">1.08235001564026</t>
   </si>
   <si>
-    <t xml:space="preserve">1.32484710216522</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.22345852851868</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.21927762031555</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.18687462806702</t>
+    <t xml:space="preserve">1.32484698295593</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.22345840930939</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.21927750110626</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.18687498569489</t>
   </si>
   <si>
     <t xml:space="preserve">1.20516669750214</t>
   </si>
   <si>
-    <t xml:space="preserve">1.34575164318085</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.53441858291626</t>
+    <t xml:space="preserve">1.34575188159943</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.53441846370697</t>
   </si>
   <si>
     <t xml:space="preserve">1.57256972789764</t>
@@ -2882,19 +2882,19 @@
     <t xml:space="preserve">1.51769495010376</t>
   </si>
   <si>
-    <t xml:space="preserve">1.41996455192566</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.41944181919098</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.46334183216095</t>
+    <t xml:space="preserve">1.41996467113495</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.41944193840027</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.46334195137024</t>
   </si>
   <si>
     <t xml:space="preserve">1.42100930213928</t>
   </si>
   <si>
-    <t xml:space="preserve">1.4095116853714</t>
+    <t xml:space="preserve">1.40951192378998</t>
   </si>
   <si>
     <t xml:space="preserve">1.40271735191345</t>
@@ -2903,10 +2903,10 @@
     <t xml:space="preserve">1.42989385128021</t>
   </si>
   <si>
-    <t xml:space="preserve">1.42414534091949</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.35411357879639</t>
+    <t xml:space="preserve">1.42414546012878</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.3541134595871</t>
   </si>
   <si>
     <t xml:space="preserve">1.36717915534973</t>
@@ -2918,7 +2918,7 @@
     <t xml:space="preserve">1.20987021923065</t>
   </si>
   <si>
-    <t xml:space="preserve">1.15760827064514</t>
+    <t xml:space="preserve">1.15760815143585</t>
   </si>
   <si>
     <t xml:space="preserve">1.16962838172913</t>
@@ -2927,31 +2927,31 @@
     <t xml:space="preserve">1.17067384719849</t>
   </si>
   <si>
-    <t xml:space="preserve">1.11997902393341</t>
+    <t xml:space="preserve">1.1199791431427</t>
   </si>
   <si>
     <t xml:space="preserve">1.11841094493866</t>
   </si>
   <si>
-    <t xml:space="preserve">1.1560400724411</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.10795891284943</t>
+    <t xml:space="preserve">1.15604019165039</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.10795903205872</t>
   </si>
   <si>
     <t xml:space="preserve">1.1393164396286</t>
   </si>
   <si>
-    <t xml:space="preserve">1.2109158039093</t>
+    <t xml:space="preserve">1.21091568470001</t>
   </si>
   <si>
     <t xml:space="preserve">1.23025214672089</t>
   </si>
   <si>
-    <t xml:space="preserve">1.17694473266602</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.15185904502869</t>
+    <t xml:space="preserve">1.17694485187531</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.15185916423798</t>
   </si>
   <si>
     <t xml:space="preserve">1.14976835250854</t>
@@ -2960,10 +2960,10 @@
     <t xml:space="preserve">1.13618016242981</t>
   </si>
   <si>
-    <t xml:space="preserve">1.11736619472504</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.10482263565063</t>
+    <t xml:space="preserve">1.11736631393433</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.10482275485992</t>
   </si>
   <si>
     <t xml:space="preserve">1.09750628471375</t>
@@ -2972,16 +2972,16 @@
     <t xml:space="preserve">1.06092262268066</t>
   </si>
   <si>
-    <t xml:space="preserve">1.05256068706512</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.04890251159668</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.09102869033813</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.03023862838745</t>
+    <t xml:space="preserve">1.05256056785583</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.04890239238739</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.09102880954742</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.03023850917816</t>
   </si>
   <si>
     <t xml:space="preserve">1.01237440109253</t>
@@ -2990,19 +2990,19 @@
     <t xml:space="preserve">0.993177235126495</t>
   </si>
   <si>
-    <t xml:space="preserve">0.993977665901184</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.996643602848053</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.10062718391418</t>
+    <t xml:space="preserve">0.993977725505829</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.996643543243408</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.10062730312347</t>
   </si>
   <si>
     <t xml:space="preserve">1.14062082767487</t>
   </si>
   <si>
-    <t xml:space="preserve">1.18648052215576</t>
+    <t xml:space="preserve">1.18648040294647</t>
   </si>
   <si>
     <t xml:space="preserve">1.14488756656647</t>
@@ -3014,49 +3014,49 @@
     <t xml:space="preserve">1.19447982311249</t>
   </si>
   <si>
-    <t xml:space="preserve">1.23287332057953</t>
+    <t xml:space="preserve">1.23287320137024</t>
   </si>
   <si>
     <t xml:space="preserve">1.23340666294098</t>
   </si>
   <si>
-    <t xml:space="preserve">1.35338819026947</t>
+    <t xml:space="preserve">1.35338830947876</t>
   </si>
   <si>
     <t xml:space="preserve">1.41897761821747</t>
   </si>
   <si>
-    <t xml:space="preserve">1.39871430397034</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.32832503318787</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.24353861808777</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.2152761220932</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.22647476196289</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.3069953918457</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.28086614608765</t>
+    <t xml:space="preserve">1.39871442317963</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.32832491397858</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.24353873729706</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.21527624130249</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.2264746427536</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.30699527263641</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.28086626529694</t>
   </si>
   <si>
     <t xml:space="preserve">1.24567115306854</t>
   </si>
   <si>
-    <t xml:space="preserve">1.25846970081329</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.20994341373444</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.23980605602264</t>
+    <t xml:space="preserve">1.25846982002258</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.20994353294373</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.23980593681335</t>
   </si>
   <si>
     <t xml:space="preserve">1.17688179016113</t>
@@ -3065,13 +3065,13 @@
     <t xml:space="preserve">1.18594706058502</t>
   </si>
   <si>
-    <t xml:space="preserve">1.15875136852264</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.17954850196838</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.15661859512329</t>
+    <t xml:space="preserve">1.15875148773193</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.17954862117767</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.15661871433258</t>
   </si>
   <si>
     <t xml:space="preserve">1.16515064239502</t>
@@ -3083,22 +3083,22 @@
     <t xml:space="preserve">1.19501233100891</t>
   </si>
   <si>
-    <t xml:space="preserve">1.18168103694916</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.176349401474</t>
+    <t xml:space="preserve">1.18168115615845</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.17634928226471</t>
   </si>
   <si>
     <t xml:space="preserve">1.14542019367218</t>
   </si>
   <si>
-    <t xml:space="preserve">1.20301163196564</t>
+    <t xml:space="preserve">1.20301175117493</t>
   </si>
   <si>
     <t xml:space="preserve">1.32885825634003</t>
   </si>
   <si>
-    <t xml:space="preserve">1.32992506027222</t>
+    <t xml:space="preserve">1.32992517948151</t>
   </si>
   <si>
     <t xml:space="preserve">1.33685696125031</t>
@@ -3107,46 +3107,46 @@
     <t xml:space="preserve">1.35445404052734</t>
   </si>
   <si>
-    <t xml:space="preserve">1.32619249820709</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.37205195426941</t>
+    <t xml:space="preserve">1.3261923789978</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.3720520734787</t>
   </si>
   <si>
     <t xml:space="preserve">1.35925340652466</t>
   </si>
   <si>
-    <t xml:space="preserve">1.31232786178589</t>
+    <t xml:space="preserve">1.31232798099518</t>
   </si>
   <si>
     <t xml:space="preserve">1.29259741306305</t>
   </si>
   <si>
-    <t xml:space="preserve">1.23873937129974</t>
+    <t xml:space="preserve">1.23873925209045</t>
   </si>
   <si>
     <t xml:space="preserve">1.24247181415558</t>
   </si>
   <si>
-    <t xml:space="preserve">1.20247828960419</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.18754696846008</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.13688814640045</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.1075599193573</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.09316205978394</t>
+    <t xml:space="preserve">1.20247840881348</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.18754708766937</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.13688826560974</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.10755980014801</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.09316194057465</t>
   </si>
   <si>
     <t xml:space="preserve">1.1592845916748</t>
   </si>
   <si>
-    <t xml:space="preserve">1.24780464172363</t>
+    <t xml:space="preserve">1.24780452251434</t>
   </si>
   <si>
     <t xml:space="preserve">1.26380157470703</t>
@@ -3164,16 +3164,16 @@
     <t xml:space="preserve">1.2494044303894</t>
   </si>
   <si>
-    <t xml:space="preserve">1.2291407585144</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.21580946445465</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.25260388851166</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.25207054615021</t>
+    <t xml:space="preserve">1.22914087772369</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.21580958366394</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.25260400772095</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.25207042694092</t>
   </si>
   <si>
     <t xml:space="preserve">1.24300527572632</t>
@@ -3185,19 +3185,19 @@
     <t xml:space="preserve">1.22700726985931</t>
   </si>
   <si>
-    <t xml:space="preserve">1.19394648075104</t>
+    <t xml:space="preserve">1.19394636154175</t>
   </si>
   <si>
     <t xml:space="preserve">1.19074630737305</t>
   </si>
   <si>
-    <t xml:space="preserve">1.15288603305817</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.16408407688141</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.15821874141693</t>
+    <t xml:space="preserve">1.15288615226746</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.16408395767212</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.15821886062622</t>
   </si>
   <si>
     <t xml:space="preserve">1.12675619125366</t>
@@ -3218,19 +3218,19 @@
     <t xml:space="preserve">1.15341949462891</t>
   </si>
   <si>
-    <t xml:space="preserve">1.16195130348206</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.15181958675385</t>
+    <t xml:space="preserve">1.16195142269135</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.15181946754456</t>
   </si>
   <si>
     <t xml:space="preserve">1.10489320755005</t>
   </si>
   <si>
-    <t xml:space="preserve">1.07503151893616</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.07716417312622</t>
+    <t xml:space="preserve">1.07503163814545</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.07716405391693</t>
   </si>
   <si>
     <t xml:space="preserve">1.04516911506653</t>
@@ -3242,85 +3242,85 @@
     <t xml:space="preserve">1.06969892978668</t>
   </si>
   <si>
-    <t xml:space="preserve">1.03983724117279</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.06010019779205</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.03877055644989</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.01050817966461</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.935909569263458</t>
+    <t xml:space="preserve">1.0398371219635</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.06010031700134</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.03877067565918</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.01050794124603</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.935909509658813</t>
   </si>
   <si>
     <t xml:space="preserve">0.974905788898468</t>
   </si>
   <si>
-    <t xml:space="preserve">0.933939933776855</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.94260585308075</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.947332620620728</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.923304796218872</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.876036465167999</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.879581570625305</t>
+    <t xml:space="preserve">0.93394011259079</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.94260573387146</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.947332739830017</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.923304617404938</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.876036584377289</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.879581689834595</t>
   </si>
   <si>
     <t xml:space="preserve">0.874854803085327</t>
   </si>
   <si>
-    <t xml:space="preserve">0.94575709104538</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.933152198791504</t>
+    <t xml:space="preserve">0.945757150650024</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.933152258396149</t>
   </si>
   <si>
     <t xml:space="preserve">1.02414345741272</t>
   </si>
   <si>
-    <t xml:space="preserve">0.958755850791931</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.934727728366852</t>
+    <t xml:space="preserve">0.958755791187286</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.934727787971497</t>
   </si>
   <si>
     <t xml:space="preserve">0.948120534420013</t>
   </si>
   <si>
-    <t xml:space="preserve">0.938666760921478</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.879975497722626</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.816557347774506</t>
+    <t xml:space="preserve">0.938666820526123</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.879975557327271</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.81655740737915</t>
   </si>
   <si>
     <t xml:space="preserve">0.806315958499908</t>
   </si>
   <si>
-    <t xml:space="preserve">0.801195323467255</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.831131756305695</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.85240250825882</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.872097492218018</t>
+    <t xml:space="preserve">0.80119526386261</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.83113169670105</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.852402448654175</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.872097611427307</t>
   </si>
   <si>
     <t xml:space="preserve">0.853190243244171</t>
@@ -3335,28 +3335,28 @@
     <t xml:space="preserve">0.940636336803436</t>
   </si>
   <si>
-    <t xml:space="preserve">0.97608745098114</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.03950560092926</t>
+    <t xml:space="preserve">0.976087510585785</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.03950548171997</t>
   </si>
   <si>
     <t xml:space="preserve">1.05171656608582</t>
   </si>
   <si>
-    <t xml:space="preserve">1.11592233181</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.12301278114319</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.1694929599762</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.19430875778198</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.19706618785858</t>
+    <t xml:space="preserve">1.11592245101929</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.1230126619339</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.16949307918549</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.19430887699127</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.19706606864929</t>
   </si>
   <si>
     <t xml:space="preserve">1.20100522041321</t>
@@ -3365,7 +3365,7 @@
     <t xml:space="preserve">1.16988682746887</t>
   </si>
   <si>
-    <t xml:space="preserve">1.19036972522736</t>
+    <t xml:space="preserve">1.19036984443665</t>
   </si>
   <si>
     <t xml:space="preserve">1.15413093566895</t>
@@ -3374,49 +3374,49 @@
     <t xml:space="preserve">1.17067468166351</t>
   </si>
   <si>
-    <t xml:space="preserve">1.15806996822357</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.16870522499084</t>
+    <t xml:space="preserve">1.15806984901428</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.16870510578156</t>
   </si>
   <si>
     <t xml:space="preserve">1.16003942489624</t>
   </si>
   <si>
-    <t xml:space="preserve">1.15373706817627</t>
+    <t xml:space="preserve">1.15373694896698</t>
   </si>
   <si>
     <t xml:space="preserve">1.16161489486694</t>
   </si>
   <si>
-    <t xml:space="preserve">1.19509661197662</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.15570652484894</t>
+    <t xml:space="preserve">1.19509649276733</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.15570640563965</t>
   </si>
   <si>
     <t xml:space="preserve">1.15294921398163</t>
   </si>
   <si>
-    <t xml:space="preserve">1.16397833824158</t>
+    <t xml:space="preserve">1.16397845745087</t>
   </si>
   <si>
     <t xml:space="preserve">1.14822232723236</t>
   </si>
   <si>
-    <t xml:space="preserve">1.15531241893768</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.14388942718506</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.09780287742615</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.12261855602264</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.16594791412354</t>
+    <t xml:space="preserve">1.15531265735626</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.14388930797577</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.09780299663544</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.12261867523193</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.16594779491425</t>
   </si>
   <si>
     <t xml:space="preserve">1.18170404434204</t>
@@ -3425,55 +3425,55 @@
     <t xml:space="preserve">1.17343211174011</t>
   </si>
   <si>
-    <t xml:space="preserve">1.15176749229431</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.16122102737427</t>
+    <t xml:space="preserve">1.15176737308502</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.16122114658356</t>
   </si>
   <si>
     <t xml:space="preserve">1.2230635881424</t>
   </si>
   <si>
-    <t xml:space="preserve">1.29869258403778</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.28411829471588</t>
+    <t xml:space="preserve">1.29869270324707</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.28411817550659</t>
   </si>
   <si>
     <t xml:space="preserve">1.31050968170166</t>
   </si>
   <si>
-    <t xml:space="preserve">1.31247925758362</t>
+    <t xml:space="preserve">1.31247913837433</t>
   </si>
   <si>
     <t xml:space="preserve">1.29632914066315</t>
   </si>
   <si>
-    <t xml:space="preserve">1.27584636211395</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.26757442951202</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.29554128646851</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.27702808380127</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.29908657073975</t>
+    <t xml:space="preserve">1.27584648132324</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.26757454872131</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.2955414056778</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.27702796459198</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.29908645153046</t>
   </si>
   <si>
     <t xml:space="preserve">1.27624034881592</t>
   </si>
   <si>
-    <t xml:space="preserve">1.24118304252625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.20376241207123</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.23724412918091</t>
+    <t xml:space="preserve">1.24118316173553</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.20376253128052</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.23724400997162</t>
   </si>
   <si>
     <t xml:space="preserve">1.20061123371124</t>
@@ -3482,10 +3482,10 @@
     <t xml:space="preserve">1.22779047489166</t>
   </si>
   <si>
-    <t xml:space="preserve">1.20770144462585</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.21636724472046</t>
+    <t xml:space="preserve">1.20770132541656</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.21636736392975</t>
   </si>
   <si>
     <t xml:space="preserve">1.33768880367279</t>
@@ -3494,10 +3494,10 @@
     <t xml:space="preserve">1.40071308612823</t>
   </si>
   <si>
-    <t xml:space="preserve">1.50430905818939</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.47279715538025</t>
+    <t xml:space="preserve">1.50430917739868</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.47279703617096</t>
   </si>
   <si>
     <t xml:space="preserve">1.4968249797821</t>
@@ -3509,7 +3509,7 @@
     <t xml:space="preserve">1.46688854694366</t>
   </si>
   <si>
-    <t xml:space="preserve">1.48343253135681</t>
+    <t xml:space="preserve">1.48343217372894</t>
   </si>
   <si>
     <t xml:space="preserve">1.46176779270172</t>
@@ -3518,55 +3518,55 @@
     <t xml:space="preserve">1.43498241901398</t>
   </si>
   <si>
-    <t xml:space="preserve">1.41016662120819</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.46610069274902</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.4448299407959</t>
+    <t xml:space="preserve">1.41016674041748</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.46610081195831</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.44483006000519</t>
   </si>
   <si>
     <t xml:space="preserve">1.44443607330322</t>
   </si>
   <si>
-    <t xml:space="preserve">1.46767616271973</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.42946803569794</t>
+    <t xml:space="preserve">1.4676765203476</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.42946779727936</t>
   </si>
   <si>
     <t xml:space="preserve">1.46728241443634</t>
   </si>
   <si>
-    <t xml:space="preserve">1.45192015171051</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.4605860710144</t>
+    <t xml:space="preserve">1.4519202709198</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.46058619022369</t>
   </si>
   <si>
     <t xml:space="preserve">1.52203476428986</t>
   </si>
   <si>
-    <t xml:space="preserve">1.56300020217896</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.5563040971756</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.54330539703369</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.55197131633759</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.53385186195374</t>
+    <t xml:space="preserve">1.56300044059753</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.55630421638489</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.5433052778244</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.5519711971283</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.53385174274445</t>
   </si>
   <si>
     <t xml:space="preserve">1.5677273273468</t>
   </si>
   <si>
-    <t xml:space="preserve">1.61657094955444</t>
+    <t xml:space="preserve">1.61657106876373</t>
   </si>
   <si>
     <t xml:space="preserve">1.60475397109985</t>
@@ -3575,7 +3575,7 @@
     <t xml:space="preserve">1.54094195365906</t>
   </si>
   <si>
-    <t xml:space="preserve">1.50233948230743</t>
+    <t xml:space="preserve">1.50233960151672</t>
   </si>
   <si>
     <t xml:space="preserve">1.50076401233673</t>
@@ -3584,22 +3584,22 @@
     <t xml:space="preserve">1.52164077758789</t>
   </si>
   <si>
-    <t xml:space="preserve">1.51021778583527</t>
+    <t xml:space="preserve">1.51021766662598</t>
   </si>
   <si>
     <t xml:space="preserve">1.51100540161133</t>
   </si>
   <si>
-    <t xml:space="preserve">1.49524939060211</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.49643111228943</t>
+    <t xml:space="preserve">1.4952495098114</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.49643123149872</t>
   </si>
   <si>
     <t xml:space="preserve">1.47831177711487</t>
   </si>
   <si>
-    <t xml:space="preserve">1.49800670146942</t>
+    <t xml:space="preserve">1.49800682067871</t>
   </si>
   <si>
     <t xml:space="preserve">1.49603724479675</t>
@@ -3611,31 +3611,31 @@
     <t xml:space="preserve">1.46452510356903</t>
   </si>
   <si>
-    <t xml:space="preserve">1.47319090366364</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.4995824098587</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.48264443874359</t>
+    <t xml:space="preserve">1.47319102287292</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.49958229064941</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.48264455795288</t>
   </si>
   <si>
     <t xml:space="preserve">1.49131035804749</t>
   </si>
   <si>
-    <t xml:space="preserve">1.49012863636017</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.53700292110443</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.45428371429443</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.42198359966278</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.4243471622467</t>
+    <t xml:space="preserve">1.49012875556946</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.53700304031372</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.45428359508514</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.42198371887207</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.42434728145599</t>
   </si>
   <si>
     <t xml:space="preserve">1.43143749237061</t>
@@ -3647,7 +3647,7 @@
     <t xml:space="preserve">1.4594042301178</t>
   </si>
   <si>
-    <t xml:space="preserve">1.49209821224213</t>
+    <t xml:space="preserve">1.49209809303284</t>
   </si>
   <si>
     <t xml:space="preserve">1.48303854465485</t>
@@ -3659,16 +3659,16 @@
     <t xml:space="preserve">1.49367380142212</t>
   </si>
   <si>
-    <t xml:space="preserve">1.52282238006592</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.51533830165863</t>
+    <t xml:space="preserve">1.52282249927521</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.51533818244934</t>
   </si>
   <si>
     <t xml:space="preserve">1.57402968406677</t>
   </si>
   <si>
-    <t xml:space="preserve">1.588210105896</t>
+    <t xml:space="preserve">1.58821022510529</t>
   </si>
   <si>
     <t xml:space="preserve">1.56457602977753</t>
@@ -3683,25 +3683,25 @@
     <t xml:space="preserve">1.58742237091064</t>
   </si>
   <si>
-    <t xml:space="preserve">1.55748581886292</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.54291164875031</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.57127225399017</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.67216503620148</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.70914554595947</t>
+    <t xml:space="preserve">1.5574859380722</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.54291152954102</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.57127237319946</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.67216491699219</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.70914566516876</t>
   </si>
   <si>
     <t xml:space="preserve">1.62714517116547</t>
   </si>
   <si>
-    <t xml:space="preserve">1.6480473279953</t>
+    <t xml:space="preserve">1.64804720878601</t>
   </si>
   <si>
     <t xml:space="preserve">1.63759624958038</t>
@@ -3719,13 +3719,13 @@
     <t xml:space="preserve">1.63598847389221</t>
   </si>
   <si>
-    <t xml:space="preserve">1.62553739547729</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.64724338054657</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.63679230213165</t>
+    <t xml:space="preserve">1.62553751468658</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.64724349975586</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.63679242134094</t>
   </si>
   <si>
     <t xml:space="preserve">1.6504590511322</t>
@@ -3737,13 +3737,13 @@
     <t xml:space="preserve">1.632772564888</t>
   </si>
   <si>
-    <t xml:space="preserve">1.64081168174744</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.61508631706238</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.59257638454437</t>
+    <t xml:space="preserve">1.64081180095673</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.61508643627167</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.59257650375366</t>
   </si>
   <si>
     <t xml:space="preserve">1.58091950416565</t>
@@ -3752,34 +3752,34 @@
     <t xml:space="preserve">1.54514479637146</t>
   </si>
   <si>
-    <t xml:space="preserve">1.5600174665451</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.53951740264893</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.51901721954346</t>
+    <t xml:space="preserve">1.56001734733582</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.53951716423035</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.51901710033417</t>
   </si>
   <si>
     <t xml:space="preserve">1.53589963912964</t>
   </si>
   <si>
-    <t xml:space="preserve">1.52906620502472</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.480428814888</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.46836996078491</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.4756053686142</t>
+    <t xml:space="preserve">1.52906608581543</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.48042893409729</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.4683700799942</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.47560524940491</t>
   </si>
   <si>
     <t xml:space="preserve">1.48444843292236</t>
   </si>
   <si>
-    <t xml:space="preserve">1.47399747371674</t>
+    <t xml:space="preserve">1.47399735450745</t>
   </si>
   <si>
     <t xml:space="preserve">1.48565435409546</t>
@@ -3788,10 +3788,10 @@
     <t xml:space="preserve">1.44626200199127</t>
   </si>
   <si>
-    <t xml:space="preserve">1.43339920043945</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.38677144050598</t>
+    <t xml:space="preserve">1.43339908123016</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.38677155971527</t>
   </si>
   <si>
     <t xml:space="preserve">1.41812467575073</t>
@@ -3800,7 +3800,7 @@
     <t xml:space="preserve">1.42455589771271</t>
   </si>
   <si>
-    <t xml:space="preserve">1.37591850757599</t>
+    <t xml:space="preserve">1.37591862678528</t>
   </si>
   <si>
     <t xml:space="preserve">1.3698890209198</t>
@@ -3809,19 +3809,19 @@
     <t xml:space="preserve">1.35863411426544</t>
   </si>
   <si>
-    <t xml:space="preserve">1.31482017040253</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.24809432029724</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.25814354419708</t>
+    <t xml:space="preserve">1.31482005119324</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.24809420108795</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.25814342498779</t>
   </si>
   <si>
     <t xml:space="preserve">1.27422201633453</t>
   </si>
   <si>
-    <t xml:space="preserve">1.29673182964325</t>
+    <t xml:space="preserve">1.29673194885254</t>
   </si>
   <si>
     <t xml:space="preserve">1.29793775081635</t>
@@ -3830,25 +3830,25 @@
     <t xml:space="preserve">1.31763386726379</t>
   </si>
   <si>
-    <t xml:space="preserve">1.30235934257507</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.30356514453888</t>
+    <t xml:space="preserve">1.30235946178436</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.30356526374817</t>
   </si>
   <si>
     <t xml:space="preserve">1.30718290805817</t>
   </si>
   <si>
-    <t xml:space="preserve">1.32366323471069</t>
+    <t xml:space="preserve">1.32366347312927</t>
   </si>
   <si>
     <t xml:space="preserve">1.32326138019562</t>
   </si>
   <si>
-    <t xml:space="preserve">1.30517292022705</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.31361413002014</t>
+    <t xml:space="preserve">1.30517303943634</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.31361436843872</t>
   </si>
   <si>
     <t xml:space="preserve">1.45349729061127</t>
@@ -3863,28 +3863,28 @@
     <t xml:space="preserve">1.48726224899292</t>
   </si>
   <si>
-    <t xml:space="preserve">1.47681105136871</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.46917390823364</t>
+    <t xml:space="preserve">1.476811170578</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.46917378902435</t>
   </si>
   <si>
     <t xml:space="preserve">1.45108544826508</t>
   </si>
   <si>
-    <t xml:space="preserve">1.42535996437073</t>
+    <t xml:space="preserve">1.42535984516144</t>
   </si>
   <si>
     <t xml:space="preserve">1.43500697612762</t>
   </si>
   <si>
-    <t xml:space="preserve">1.41169309616089</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.4068695306778</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.43701696395874</t>
+    <t xml:space="preserve">1.41169321537018</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.40686964988708</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.43701684474945</t>
   </si>
   <si>
     <t xml:space="preserve">1.44224238395691</t>
@@ -3893,13 +3893,13 @@
     <t xml:space="preserve">1.47238957881927</t>
   </si>
   <si>
-    <t xml:space="preserve">1.45309543609619</t>
+    <t xml:space="preserve">1.4530953168869</t>
   </si>
   <si>
     <t xml:space="preserve">1.47600722312927</t>
   </si>
   <si>
-    <t xml:space="preserve">1.45872294902802</t>
+    <t xml:space="preserve">1.45872282981873</t>
   </si>
   <si>
     <t xml:space="preserve">1.48123264312744</t>
@@ -3911,13 +3911,13 @@
     <t xml:space="preserve">1.48364448547363</t>
   </si>
   <si>
-    <t xml:space="preserve">1.50092887878418</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.46153652667999</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.45068359375</t>
+    <t xml:space="preserve">1.50092899799347</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.46153664588928</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.45068347454071</t>
   </si>
   <si>
     <t xml:space="preserve">1.46475219726562</t>
@@ -3947,16 +3947,16 @@
     <t xml:space="preserve">1.47439932823181</t>
   </si>
   <si>
-    <t xml:space="preserve">1.53107619285583</t>
+    <t xml:space="preserve">1.53107607364655</t>
   </si>
   <si>
     <t xml:space="preserve">1.52343881130219</t>
   </si>
   <si>
-    <t xml:space="preserve">1.56242918968201</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.55398786067963</t>
+    <t xml:space="preserve">1.5624293088913</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.55398797988892</t>
   </si>
   <si>
     <t xml:space="preserve">1.59137058258057</t>
@@ -3968,7 +3968,7 @@
     <t xml:space="preserve">1.63357675075531</t>
   </si>
   <si>
-    <t xml:space="preserve">1.61589014530182</t>
+    <t xml:space="preserve">1.61589026451111</t>
   </si>
   <si>
     <t xml:space="preserve">1.63438057899475</t>
@@ -3992,31 +3992,31 @@
     <t xml:space="preserve">1.67055726051331</t>
   </si>
   <si>
-    <t xml:space="preserve">1.64643943309784</t>
+    <t xml:space="preserve">1.64643955230713</t>
   </si>
   <si>
     <t xml:space="preserve">1.64563548564911</t>
   </si>
   <si>
-    <t xml:space="preserve">1.64965510368347</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.60945892333984</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.6279491186142</t>
+    <t xml:space="preserve">1.64965522289276</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.60945880413055</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.62794923782349</t>
   </si>
   <si>
     <t xml:space="preserve">1.52303695678711</t>
   </si>
   <si>
-    <t xml:space="preserve">1.51419365406036</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.54152715206146</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.53911542892456</t>
+    <t xml:space="preserve">1.51419377326965</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.54152727127075</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.53911530971527</t>
   </si>
   <si>
     <t xml:space="preserve">1.52102708816528</t>
@@ -4025,10 +4025,10 @@
     <t xml:space="preserve">1.54715466499329</t>
   </si>
   <si>
-    <t xml:space="preserve">1.54273319244385</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.53509569168091</t>
+    <t xml:space="preserve">1.54273307323456</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.5350958108902</t>
   </si>
   <si>
     <t xml:space="preserve">1.54635059833527</t>
@@ -4043,13 +4043,13 @@
     <t xml:space="preserve">1.52826237678528</t>
   </si>
   <si>
-    <t xml:space="preserve">1.48485028743744</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.44425213336945</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.44987964630127</t>
+    <t xml:space="preserve">1.48485040664673</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.44425201416016</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.44987976551056</t>
   </si>
   <si>
     <t xml:space="preserve">1.44304621219635</t>
@@ -4064,7 +4064,7 @@
     <t xml:space="preserve">1.35340857505798</t>
   </si>
   <si>
-    <t xml:space="preserve">1.35220277309418</t>
+    <t xml:space="preserve">1.35220265388489</t>
   </si>
   <si>
     <t xml:space="preserve">1.39119303226471</t>
@@ -4085,7 +4085,7 @@
     <t xml:space="preserve">1.39561462402344</t>
   </si>
   <si>
-    <t xml:space="preserve">1.40285003185272</t>
+    <t xml:space="preserve">1.40284991264343</t>
   </si>
   <si>
     <t xml:space="preserve">1.39239895343781</t>
@@ -4094,19 +4094,19 @@
     <t xml:space="preserve">1.49369359016418</t>
   </si>
   <si>
-    <t xml:space="preserve">1.43018341064453</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.42777168750763</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.39280080795288</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.42897748947144</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.41651666164398</t>
+    <t xml:space="preserve">1.43018352985382</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.42777180671692</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.39280092716217</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.42897760868073</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.41651678085327</t>
   </si>
   <si>
     <t xml:space="preserve">1.43983066082001</t>
@@ -4115,13 +4115,13 @@
     <t xml:space="preserve">1.45751690864563</t>
   </si>
   <si>
-    <t xml:space="preserve">1.46877193450928</t>
+    <t xml:space="preserve">1.46877205371857</t>
   </si>
   <si>
     <t xml:space="preserve">1.46555614471436</t>
   </si>
   <si>
-    <t xml:space="preserve">1.51539957523346</t>
+    <t xml:space="preserve">1.51539945602417</t>
   </si>
   <si>
     <t xml:space="preserve">1.54434084892273</t>
@@ -4130,7 +4130,7 @@
     <t xml:space="preserve">1.54032135009766</t>
   </si>
   <si>
-    <t xml:space="preserve">1.55157613754272</t>
+    <t xml:space="preserve">1.55157625675201</t>
   </si>
   <si>
     <t xml:space="preserve">1.54996824264526</t>
@@ -4139,7 +4139,7 @@
     <t xml:space="preserve">1.57730185985565</t>
   </si>
   <si>
-    <t xml:space="preserve">1.57167422771454</t>
+    <t xml:space="preserve">1.57167434692383</t>
   </si>
   <si>
     <t xml:space="preserve">1.55639970302582</t>
@@ -4151,10 +4151,10 @@
     <t xml:space="preserve">1.51298773288727</t>
   </si>
   <si>
-    <t xml:space="preserve">1.44264423847198</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.43741869926453</t>
+    <t xml:space="preserve">1.44264435768127</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.43741881847382</t>
   </si>
   <si>
     <t xml:space="preserve">1.50293874740601</t>
@@ -4175,16 +4175,16 @@
     <t xml:space="preserve">1.58936071395874</t>
   </si>
   <si>
-    <t xml:space="preserve">1.573282122612</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.63116502761841</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.62875318527222</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.65367460250854</t>
+    <t xml:space="preserve">1.57328224182129</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.63116478919983</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.62875306606293</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.65367472171783</t>
   </si>
   <si>
     <t xml:space="preserve">1.59016466140747</t>
@@ -4196,25 +4196,25 @@
     <t xml:space="preserve">1.71477293968201</t>
   </si>
   <si>
-    <t xml:space="preserve">1.6231255531311</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.57569396495819</t>
+    <t xml:space="preserve">1.62312567234039</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.57569408416748</t>
   </si>
   <si>
     <t xml:space="preserve">1.45590901374817</t>
   </si>
   <si>
-    <t xml:space="preserve">1.48243856430054</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.33572220802307</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.3304967880249</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.26095712184906</t>
+    <t xml:space="preserve">1.48243868350983</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.33572232723236</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.33049666881561</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.26095724105835</t>
   </si>
   <si>
     <t xml:space="preserve">1.12750554084778</t>
@@ -4223,7 +4223,7 @@
     <t xml:space="preserve">1.06922101974487</t>
   </si>
   <si>
-    <t xml:space="preserve">1.12670147418976</t>
+    <t xml:space="preserve">1.12670159339905</t>
   </si>
   <si>
     <t xml:space="preserve">1.23925113677979</t>
@@ -4235,7 +4235,7 @@
     <t xml:space="preserve">1.13996636867523</t>
   </si>
   <si>
-    <t xml:space="preserve">1.18659400939941</t>
+    <t xml:space="preserve">1.18659389019012</t>
   </si>
   <si>
     <t xml:space="preserve">1.21071183681488</t>
@@ -4253,40 +4253,40 @@
     <t xml:space="preserve">1.27864348888397</t>
   </si>
   <si>
-    <t xml:space="preserve">1.25934934616089</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.24688851833344</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.25532972812653</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.27140820026398</t>
+    <t xml:space="preserve">1.2593492269516</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.24688839912415</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.25532960891724</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.27140831947327</t>
   </si>
   <si>
     <t xml:space="preserve">1.34617328643799</t>
   </si>
   <si>
-    <t xml:space="preserve">1.31964373588562</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.27783942222595</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.29190826416016</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.23643743991852</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.23844730854034</t>
+    <t xml:space="preserve">1.31964361667633</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.27783954143524</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.29190838336945</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.23643732070923</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.23844718933105</t>
   </si>
   <si>
     <t xml:space="preserve">1.28748667240143</t>
   </si>
   <si>
-    <t xml:space="preserve">1.2854768037796</t>
+    <t xml:space="preserve">1.28547692298889</t>
   </si>
   <si>
     <t xml:space="preserve">1.24447667598724</t>
@@ -4301,10 +4301,10 @@
     <t xml:space="preserve">1.26578068733215</t>
   </si>
   <si>
-    <t xml:space="preserve">1.3103985786438</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.31924176216125</t>
+    <t xml:space="preserve">1.31039845943451</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.31924164295197</t>
   </si>
   <si>
     <t xml:space="preserve">1.30034935474396</t>
@@ -4322,13 +4322,13 @@
     <t xml:space="preserve">1.27261412143707</t>
   </si>
   <si>
-    <t xml:space="preserve">1.2903003692627</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.28185904026031</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.25050604343414</t>
+    <t xml:space="preserve">1.29030048847198</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.2818591594696</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.25050616264343</t>
   </si>
   <si>
     <t xml:space="preserve">1.23121178150177</t>
@@ -4343,16 +4343,16 @@
     <t xml:space="preserve">1.36667346954346</t>
   </si>
   <si>
-    <t xml:space="preserve">1.40003633499146</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.40043830871582</t>
+    <t xml:space="preserve">1.40003621578217</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.40043818950653</t>
   </si>
   <si>
     <t xml:space="preserve">1.38757538795471</t>
   </si>
   <si>
-    <t xml:space="preserve">1.41933047771454</t>
+    <t xml:space="preserve">1.41933035850525</t>
   </si>
   <si>
     <t xml:space="preserve">1.41249704360962</t>
@@ -4373,16 +4373,16 @@
     <t xml:space="preserve">1.55682456493378</t>
   </si>
   <si>
-    <t xml:space="preserve">1.57597267627716</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.56931245326996</t>
+    <t xml:space="preserve">1.57597255706787</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.56931233406067</t>
   </si>
   <si>
     <t xml:space="preserve">1.56889617443085</t>
   </si>
   <si>
-    <t xml:space="preserve">1.59553706645966</t>
+    <t xml:space="preserve">1.59553694725037</t>
   </si>
   <si>
     <t xml:space="preserve">1.59179055690765</t>
@@ -4394,13 +4394,13 @@
     <t xml:space="preserve">1.5509968996048</t>
   </si>
   <si>
-    <t xml:space="preserve">1.60760867595673</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.56847977638245</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.61426877975464</t>
+    <t xml:space="preserve">1.60760855674744</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.56847989559174</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.61426889896393</t>
   </si>
   <si>
     <t xml:space="preserve">1.62425911426544</t>
@@ -4418,7 +4418,7 @@
     <t xml:space="preserve">1.43194556236267</t>
   </si>
   <si>
-    <t xml:space="preserve">1.37117111682892</t>
+    <t xml:space="preserve">1.37117099761963</t>
   </si>
   <si>
     <t xml:space="preserve">1.3969794511795</t>
@@ -4427,28 +4427,28 @@
     <t xml:space="preserve">1.42195522785187</t>
   </si>
   <si>
-    <t xml:space="preserve">1.42861545085907</t>
+    <t xml:space="preserve">1.42861533164978</t>
   </si>
   <si>
     <t xml:space="preserve">1.4265341758728</t>
   </si>
   <si>
-    <t xml:space="preserve">1.3578507900238</t>
+    <t xml:space="preserve">1.35785067081451</t>
   </si>
   <si>
     <t xml:space="preserve">1.40197455883026</t>
   </si>
   <si>
-    <t xml:space="preserve">1.38074505329132</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.37866389751434</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.35826694965363</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.3049852848053</t>
+    <t xml:space="preserve">1.38074517250061</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.37866377830505</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.35826706886292</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.30498516559601</t>
   </si>
   <si>
     <t xml:space="preserve">1.26460778713226</t>
@@ -4463,13 +4463,13 @@
     <t xml:space="preserve">1.18093883991241</t>
   </si>
   <si>
-    <t xml:space="preserve">1.24212944507599</t>
+    <t xml:space="preserve">1.24212956428528</t>
   </si>
   <si>
     <t xml:space="preserve">1.25711500644684</t>
   </si>
   <si>
-    <t xml:space="preserve">1.20008683204651</t>
+    <t xml:space="preserve">1.2000869512558</t>
   </si>
   <si>
     <t xml:space="preserve">1.1705322265625</t>
@@ -4481,7 +4481,7 @@
     <t xml:space="preserve">1.06979656219482</t>
   </si>
   <si>
-    <t xml:space="preserve">1.07645666599274</t>
+    <t xml:space="preserve">1.07645678520203</t>
   </si>
   <si>
     <t xml:space="preserve">1.09060966968536</t>
@@ -4490,16 +4490,16 @@
     <t xml:space="preserve">1.16470456123352</t>
   </si>
   <si>
-    <t xml:space="preserve">1.13140344619751</t>
+    <t xml:space="preserve">1.1314035654068</t>
   </si>
   <si>
     <t xml:space="preserve">1.09602105617523</t>
   </si>
   <si>
-    <t xml:space="preserve">1.07853817939758</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.10642766952515</t>
+    <t xml:space="preserve">1.07853806018829</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.10642778873444</t>
   </si>
   <si>
     <t xml:space="preserve">1.0756242275238</t>
@@ -4508,19 +4508,19 @@
     <t xml:space="preserve">1.09643745422363</t>
   </si>
   <si>
-    <t xml:space="preserve">1.09893488883972</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.12391066551208</t>
+    <t xml:space="preserve">1.09893500804901</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.12391090393066</t>
   </si>
   <si>
     <t xml:space="preserve">1.13598239421844</t>
   </si>
   <si>
-    <t xml:space="preserve">1.15471422672272</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.20091938972473</t>
+    <t xml:space="preserve">1.15471410751343</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.20091950893402</t>
   </si>
   <si>
     <t xml:space="preserve">1.19301044940948</t>
@@ -4532,10 +4532,10 @@
     <t xml:space="preserve">1.34036767482758</t>
   </si>
   <si>
-    <t xml:space="preserve">1.35119044780731</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.38199400901794</t>
+    <t xml:space="preserve">1.3511905670166</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.38199388980865</t>
   </si>
   <si>
     <t xml:space="preserve">1.36326217651367</t>
@@ -4547,7 +4547,7 @@
     <t xml:space="preserve">1.3640946149826</t>
   </si>
   <si>
-    <t xml:space="preserve">1.31955444812775</t>
+    <t xml:space="preserve">1.31955456733704</t>
   </si>
   <si>
     <t xml:space="preserve">1.275430560112</t>
@@ -4574,7 +4574,7 @@
     <t xml:space="preserve">1.25295233726501</t>
   </si>
   <si>
-    <t xml:space="preserve">1.23546922206879</t>
+    <t xml:space="preserve">1.23546934127808</t>
   </si>
   <si>
     <t xml:space="preserve">1.2654402256012</t>
@@ -4583,10 +4583,10 @@
     <t xml:space="preserve">1.22756028175354</t>
   </si>
   <si>
-    <t xml:space="preserve">1.23005783557892</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.21257483959198</t>
+    <t xml:space="preserve">1.23005795478821</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.21257495880127</t>
   </si>
   <si>
     <t xml:space="preserve">1.25003850460052</t>
@@ -4595,7 +4595,7 @@
     <t xml:space="preserve">1.2887510061264</t>
   </si>
   <si>
-    <t xml:space="preserve">1.35285556316376</t>
+    <t xml:space="preserve">1.35285544395447</t>
   </si>
   <si>
     <t xml:space="preserve">1.33911883831024</t>
@@ -4607,7 +4607,7 @@
     <t xml:space="preserve">1.39489817619324</t>
   </si>
   <si>
-    <t xml:space="preserve">1.40363967418671</t>
+    <t xml:space="preserve">1.40363955497742</t>
   </si>
   <si>
     <t xml:space="preserve">1.41071605682373</t>
@@ -4616,7 +4616,7 @@
     <t xml:space="preserve">1.38657295703888</t>
   </si>
   <si>
-    <t xml:space="preserve">1.39781188964844</t>
+    <t xml:space="preserve">1.39781200885773</t>
   </si>
   <si>
     <t xml:space="preserve">1.44443345069885</t>
@@ -4628,34 +4628,34 @@
     <t xml:space="preserve">1.38532412052155</t>
   </si>
   <si>
-    <t xml:space="preserve">1.35493683815002</t>
+    <t xml:space="preserve">1.35493695735931</t>
   </si>
   <si>
     <t xml:space="preserve">1.33329117298126</t>
   </si>
   <si>
-    <t xml:space="preserve">1.29541110992432</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.31622433662415</t>
+    <t xml:space="preserve">1.29541122913361</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.31622445583344</t>
   </si>
   <si>
     <t xml:space="preserve">1.34161639213562</t>
   </si>
   <si>
-    <t xml:space="preserve">1.39864456653595</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.37241983413696</t>
+    <t xml:space="preserve">1.39864432811737</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.37241995334625</t>
   </si>
   <si>
     <t xml:space="preserve">1.33037745952606</t>
   </si>
   <si>
-    <t xml:space="preserve">1.34786033630371</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.33162605762482</t>
+    <t xml:space="preserve">1.347860455513</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.33162593841553</t>
   </si>
   <si>
     <t xml:space="preserve">1.32121956348419</t>
@@ -4664,25 +4664,25 @@
     <t xml:space="preserve">1.3541042804718</t>
   </si>
   <si>
-    <t xml:space="preserve">1.37699890136719</t>
+    <t xml:space="preserve">1.3769987821579</t>
   </si>
   <si>
     <t xml:space="preserve">1.4065535068512</t>
   </si>
   <si>
-    <t xml:space="preserve">1.41571140289307</t>
+    <t xml:space="preserve">1.41571128368378</t>
   </si>
   <si>
     <t xml:space="preserve">1.42611789703369</t>
   </si>
   <si>
-    <t xml:space="preserve">1.43069672584534</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.44984495639801</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.49105489253998</t>
+    <t xml:space="preserve">1.43069684505463</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.44984483718872</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.49105501174927</t>
   </si>
   <si>
     <t xml:space="preserve">1.4818971157074</t>
@@ -4691,10 +4691,10 @@
     <t xml:space="preserve">1.48397850990295</t>
   </si>
   <si>
-    <t xml:space="preserve">1.52602100372314</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.53601145744324</t>
+    <t xml:space="preserve">1.52602112293243</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.53601133823395</t>
   </si>
   <si>
     <t xml:space="preserve">1.55890572071075</t>
@@ -4712,7 +4712,7 @@
     <t xml:space="preserve">1.6758759021759</t>
   </si>
   <si>
-    <t xml:space="preserve">1.70667934417725</t>
+    <t xml:space="preserve">1.70667922496796</t>
   </si>
   <si>
     <t xml:space="preserve">1.57555639743805</t>
@@ -4724,16 +4724,16 @@
     <t xml:space="preserve">1.5639009475708</t>
   </si>
   <si>
-    <t xml:space="preserve">1.54225516319275</t>
+    <t xml:space="preserve">1.54225528240204</t>
   </si>
   <si>
     <t xml:space="preserve">1.56181967258453</t>
   </si>
   <si>
-    <t xml:space="preserve">1.5672310590744</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.58970928192139</t>
+    <t xml:space="preserve">1.56723117828369</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.58970940113068</t>
   </si>
   <si>
     <t xml:space="preserve">1.59387195110321</t>
@@ -4748,7 +4748,7 @@
     <t xml:space="preserve">1.62883818149567</t>
   </si>
   <si>
-    <t xml:space="preserve">1.6396609544754</t>
+    <t xml:space="preserve">1.63966083526611</t>
   </si>
   <si>
     <t xml:space="preserve">1.62467551231384</t>
@@ -4763,7 +4763,7 @@
     <t xml:space="preserve">1.62259411811829</t>
   </si>
   <si>
-    <t xml:space="preserve">1.61468505859375</t>
+    <t xml:space="preserve">1.61468517780304</t>
   </si>
   <si>
     <t xml:space="preserve">1.60594356060028</t>
@@ -4772,13 +4772,13 @@
     <t xml:space="preserve">1.61302006244659</t>
   </si>
   <si>
-    <t xml:space="preserve">1.61759901046753</t>
+    <t xml:space="preserve">1.61759889125824</t>
   </si>
   <si>
     <t xml:space="preserve">1.62550795078278</t>
   </si>
   <si>
-    <t xml:space="preserve">1.62509179115295</t>
+    <t xml:space="preserve">1.62509167194366</t>
   </si>
   <si>
     <t xml:space="preserve">1.63508200645447</t>
@@ -4790,13 +4790,13 @@
     <t xml:space="preserve">1.56639862060547</t>
   </si>
   <si>
-    <t xml:space="preserve">1.56514990329742</t>
+    <t xml:space="preserve">1.56514978408813</t>
   </si>
   <si>
     <t xml:space="preserve">1.55307817459106</t>
   </si>
   <si>
-    <t xml:space="preserve">1.62009656429291</t>
+    <t xml:space="preserve">1.62009644508362</t>
   </si>
   <si>
     <t xml:space="preserve">1.61884772777557</t>
@@ -4805,7 +4805,7 @@
     <t xml:space="preserve">1.61093866825104</t>
   </si>
   <si>
-    <t xml:space="preserve">1.59720194339752</t>
+    <t xml:space="preserve">1.59720206260681</t>
   </si>
   <si>
     <t xml:space="preserve">1.63133561611176</t>
@@ -4829,19 +4829,19 @@
     <t xml:space="preserve">1.75663089752197</t>
   </si>
   <si>
-    <t xml:space="preserve">1.75579822063446</t>
+    <t xml:space="preserve">1.75579833984375</t>
   </si>
   <si>
     <t xml:space="preserve">1.76578867435455</t>
   </si>
   <si>
-    <t xml:space="preserve">1.8232330083847</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.84321367740631</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.81490778923035</t>
+    <t xml:space="preserve">1.82323312759399</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.8432137966156</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.81490790843964</t>
   </si>
   <si>
     <t xml:space="preserve">1.87484967708588</t>
@@ -4850,13 +4850,13 @@
     <t xml:space="preserve">1.87318456172943</t>
   </si>
   <si>
-    <t xml:space="preserve">1.90898311138153</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.9206383228302</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.94811177253723</t>
+    <t xml:space="preserve">1.90898334980011</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.92063856124878</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.94811189174652</t>
   </si>
   <si>
     <t xml:space="preserve">1.95227468013763</t>
@@ -4868,7 +4868,7 @@
     <t xml:space="preserve">2.02387189865112</t>
   </si>
   <si>
-    <t xml:space="preserve">2.02303957939148</t>
+    <t xml:space="preserve">2.0230393409729</t>
   </si>
   <si>
     <t xml:space="preserve">2.09546899795532</t>
@@ -4880,13 +4880,13 @@
     <t xml:space="preserve">2.10462713241577</t>
   </si>
   <si>
-    <t xml:space="preserve">2.11461710929871</t>
+    <t xml:space="preserve">2.11461734771729</t>
   </si>
   <si>
     <t xml:space="preserve">2.14958357810974</t>
   </si>
   <si>
-    <t xml:space="preserve">2.11961221694946</t>
+    <t xml:space="preserve">2.11961245536804</t>
   </si>
   <si>
     <t xml:space="preserve">2.14042568206787</t>
@@ -4904,7 +4904,7 @@
     <t xml:space="preserve">2.15874099731445</t>
   </si>
   <si>
-    <t xml:space="preserve">2.22617602348328</t>
+    <t xml:space="preserve">2.2261757850647</t>
   </si>
   <si>
     <t xml:space="preserve">2.32441377639771</t>
@@ -4919,7 +4919,7 @@
     <t xml:space="preserve">2.17539167404175</t>
   </si>
   <si>
-    <t xml:space="preserve">2.19786977767944</t>
+    <t xml:space="preserve">2.19787001609802</t>
   </si>
   <si>
     <t xml:space="preserve">2.14708566665649</t>
@@ -4928,7 +4928,7 @@
     <t xml:space="preserve">2.20869278907776</t>
   </si>
   <si>
-    <t xml:space="preserve">2.23699855804443</t>
+    <t xml:space="preserve">2.23699879646301</t>
   </si>
   <si>
     <t xml:space="preserve">2.21701812744141</t>
@@ -4946,7 +4946,7 @@
     <t xml:space="preserve">2.29527544975281</t>
   </si>
   <si>
-    <t xml:space="preserve">2.35355257987976</t>
+    <t xml:space="preserve">2.35355234146118</t>
   </si>
   <si>
     <t xml:space="preserve">2.34522700309753</t>
@@ -4955,22 +4955,22 @@
     <t xml:space="preserve">2.24032855033875</t>
   </si>
   <si>
-    <t xml:space="preserve">2.02720189094543</t>
+    <t xml:space="preserve">2.02720212936401</t>
   </si>
   <si>
     <t xml:space="preserve">2.06050300598145</t>
   </si>
   <si>
-    <t xml:space="preserve">1.91148090362549</t>
+    <t xml:space="preserve">1.91148066520691</t>
   </si>
   <si>
     <t xml:space="preserve">1.91564357280731</t>
   </si>
   <si>
-    <t xml:space="preserve">1.86236166954041</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.88900256156921</t>
+    <t xml:space="preserve">1.86236178874969</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.88900279998779</t>
   </si>
   <si>
     <t xml:space="preserve">1.98141312599182</t>
@@ -4979,7 +4979,7 @@
     <t xml:space="preserve">1.95310711860657</t>
   </si>
   <si>
-    <t xml:space="preserve">1.91730844974518</t>
+    <t xml:space="preserve">1.91730856895447</t>
   </si>
   <si>
     <t xml:space="preserve">1.839883685112</t>
@@ -4991,10 +4991,10 @@
     <t xml:space="preserve">1.86735689640045</t>
   </si>
   <si>
-    <t xml:space="preserve">1.9181410074234</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.90648567676544</t>
+    <t xml:space="preserve">1.91814088821411</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.90648555755615</t>
   </si>
   <si>
     <t xml:space="preserve">1.89233267307281</t>
@@ -5003,19 +5003,19 @@
     <t xml:space="preserve">1.93895411491394</t>
   </si>
   <si>
-    <t xml:space="preserve">1.9381217956543</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.96809279918671</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.96476221084595</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.00305867195129</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.99639844894409</t>
+    <t xml:space="preserve">1.93812167644501</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.96809267997742</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.96476233005524</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.00305843353271</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.99639856815338</t>
   </si>
   <si>
     <t xml:space="preserve">2.08964157104492</t>
@@ -5030,16 +5030,16 @@
     <t xml:space="preserve">2.22284579277039</t>
   </si>
   <si>
-    <t xml:space="preserve">2.25281667709351</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.28528523445129</t>
+    <t xml:space="preserve">2.25281691551208</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.28528499603271</t>
   </si>
   <si>
     <t xml:space="preserve">2.276127576828</t>
   </si>
   <si>
-    <t xml:space="preserve">2.12294268608093</t>
+    <t xml:space="preserve">2.12294244766235</t>
   </si>
   <si>
     <t xml:space="preserve">2.20786023139954</t>
@@ -5048,7 +5048,7 @@
     <t xml:space="preserve">2.11877989768982</t>
   </si>
   <si>
-    <t xml:space="preserve">2.08547878265381</t>
+    <t xml:space="preserve">2.08547902107239</t>
   </si>
   <si>
     <t xml:space="preserve">2.12127757072449</t>
@@ -5060,10 +5060,10 @@
     <t xml:space="preserve">2.17039656639099</t>
   </si>
   <si>
-    <t xml:space="preserve">2.28362011909485</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.27279734611511</t>
+    <t xml:space="preserve">2.28362035751343</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.27279758453369</t>
   </si>
   <si>
     <t xml:space="preserve">2.22201299667358</t>
@@ -5072,7 +5072,7 @@
     <t xml:space="preserve">2.27196478843689</t>
   </si>
   <si>
-    <t xml:space="preserve">2.25781154632568</t>
+    <t xml:space="preserve">2.25781178474426</t>
   </si>
   <si>
     <t xml:space="preserve">2.25697922706604</t>
@@ -5081,10 +5081,10 @@
     <t xml:space="preserve">2.24282646179199</t>
   </si>
   <si>
-    <t xml:space="preserve">2.24782133102417</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.27570128440857</t>
+    <t xml:space="preserve">2.24782180786133</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.27570152282715</t>
   </si>
   <si>
     <t xml:space="preserve">2.25392007827759</t>
@@ -5105,10 +5105,10 @@
     <t xml:space="preserve">2.1180055141449</t>
   </si>
   <si>
-    <t xml:space="preserve">2.08228445053101</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.13717293739319</t>
+    <t xml:space="preserve">2.08228421211243</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.13717317581177</t>
   </si>
   <si>
     <t xml:space="preserve">2.18509149551392</t>
@@ -5120,7 +5120,7 @@
     <t xml:space="preserve">2.17986416816711</t>
   </si>
   <si>
-    <t xml:space="preserve">2.17550778388977</t>
+    <t xml:space="preserve">2.17550802230835</t>
   </si>
   <si>
     <t xml:space="preserve">2.17637896537781</t>
@@ -5156,31 +5156,31 @@
     <t xml:space="preserve">2.39157748222351</t>
   </si>
   <si>
-    <t xml:space="preserve">2.33930277824402</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.30880880355835</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.35237121582031</t>
+    <t xml:space="preserve">2.33930253982544</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.30880904197693</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.35237145423889</t>
   </si>
   <si>
     <t xml:space="preserve">2.36892509460449</t>
   </si>
   <si>
-    <t xml:space="preserve">2.4002902507782</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.42381381988525</t>
+    <t xml:space="preserve">2.40029001235962</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.42381358146667</t>
   </si>
   <si>
     <t xml:space="preserve">2.45082235336304</t>
   </si>
   <si>
-    <t xml:space="preserve">2.3889639377594</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.37676620483398</t>
+    <t xml:space="preserve">2.38896369934082</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.37676644325256</t>
   </si>
   <si>
     <t xml:space="preserve">2.32187747955322</t>
@@ -5195,10 +5195,10 @@
     <t xml:space="preserve">2.46476244926453</t>
   </si>
   <si>
-    <t xml:space="preserve">2.50396847724915</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.55885720252991</t>
+    <t xml:space="preserve">2.50396871566772</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.55885744094849</t>
   </si>
   <si>
     <t xml:space="preserve">2.53794741630554</t>
@@ -5213,22 +5213,22 @@
     <t xml:space="preserve">2.55711483955383</t>
   </si>
   <si>
-    <t xml:space="preserve">2.60938954353333</t>
+    <t xml:space="preserve">2.6093897819519</t>
   </si>
   <si>
     <t xml:space="preserve">2.62768602371216</t>
   </si>
   <si>
-    <t xml:space="preserve">2.64685368537903</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.66166472434998</t>
+    <t xml:space="preserve">2.64685344696045</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.6616644859314</t>
   </si>
   <si>
     <t xml:space="preserve">2.7653431892395</t>
   </si>
   <si>
-    <t xml:space="preserve">2.7209095954895</t>
+    <t xml:space="preserve">2.72090935707092</t>
   </si>
   <si>
     <t xml:space="preserve">2.73136448860168</t>
@@ -5243,7 +5243,7 @@
     <t xml:space="preserve">2.61897349357605</t>
   </si>
   <si>
-    <t xml:space="preserve">2.51180958747864</t>
+    <t xml:space="preserve">2.51180982589722</t>
   </si>
   <si>
     <t xml:space="preserve">2.47086095809937</t>
@@ -5255,7 +5255,7 @@
     <t xml:space="preserve">2.20600175857544</t>
   </si>
   <si>
-    <t xml:space="preserve">2.25479173660278</t>
+    <t xml:space="preserve">2.2547914981842</t>
   </si>
   <si>
     <t xml:space="preserve">2.30271005630493</t>
@@ -5264,7 +5264,7 @@
     <t xml:space="preserve">2.36369752883911</t>
   </si>
   <si>
-    <t xml:space="preserve">2.3724102973938</t>
+    <t xml:space="preserve">2.37241005897522</t>
   </si>
   <si>
     <t xml:space="preserve">2.3384313583374</t>
@@ -5276,22 +5276,22 @@
     <t xml:space="preserve">2.39593386650085</t>
   </si>
   <si>
-    <t xml:space="preserve">2.39244890213013</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.36718273162842</t>
+    <t xml:space="preserve">2.39244866371155</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.36718249320984</t>
   </si>
   <si>
     <t xml:space="preserve">2.42032885551453</t>
   </si>
   <si>
-    <t xml:space="preserve">2.44036746025085</t>
+    <t xml:space="preserve">2.44036769866943</t>
   </si>
   <si>
     <t xml:space="preserve">2.46389126777649</t>
   </si>
   <si>
-    <t xml:space="preserve">2.42904138565063</t>
+    <t xml:space="preserve">2.42904114723206</t>
   </si>
   <si>
     <t xml:space="preserve">2.41510128974915</t>
@@ -5300,7 +5300,7 @@
     <t xml:space="preserve">2.38809251785278</t>
   </si>
   <si>
-    <t xml:space="preserve">2.28441381454468</t>
+    <t xml:space="preserve">2.28441405296326</t>
   </si>
   <si>
     <t xml:space="preserve">2.25304889678955</t>
@@ -5309,10 +5309,10 @@
     <t xml:space="preserve">2.27134537696838</t>
   </si>
   <si>
-    <t xml:space="preserve">2.33407521247864</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.41161608695984</t>
+    <t xml:space="preserve">2.33407497406006</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.41161632537842</t>
   </si>
   <si>
     <t xml:space="preserve">2.43688249588013</t>
@@ -5324,19 +5324,19 @@
     <t xml:space="preserve">2.494384765625</t>
   </si>
   <si>
-    <t xml:space="preserve">2.60329103469849</t>
+    <t xml:space="preserve">2.60329079627991</t>
   </si>
   <si>
     <t xml:space="preserve">2.59980583190918</t>
   </si>
   <si>
-    <t xml:space="preserve">2.5780246257782</t>
+    <t xml:space="preserve">2.57802486419678</t>
   </si>
   <si>
     <t xml:space="preserve">2.46301984786987</t>
   </si>
   <si>
-    <t xml:space="preserve">2.43513989448547</t>
+    <t xml:space="preserve">2.43514013290405</t>
   </si>
   <si>
     <t xml:space="preserve">2.52400755882263</t>
@@ -5360,7 +5360,7 @@
     <t xml:space="preserve">2.42120003700256</t>
   </si>
   <si>
-    <t xml:space="preserve">2.51093864440918</t>
+    <t xml:space="preserve">2.5109384059906</t>
   </si>
   <si>
     <t xml:space="preserve">2.58063840866089</t>
@@ -5372,19 +5372,19 @@
     <t xml:space="preserve">2.57889604568481</t>
   </si>
   <si>
-    <t xml:space="preserve">2.63901233673096</t>
+    <t xml:space="preserve">2.63901209831238</t>
   </si>
   <si>
     <t xml:space="preserve">2.66427850723267</t>
   </si>
   <si>
-    <t xml:space="preserve">2.6285572052002</t>
+    <t xml:space="preserve">2.62855696678162</t>
   </si>
   <si>
     <t xml:space="preserve">2.49177098274231</t>
   </si>
   <si>
-    <t xml:space="preserve">2.59719204902649</t>
+    <t xml:space="preserve">2.59719228744507</t>
   </si>
   <si>
     <t xml:space="preserve">2.52923488616943</t>
@@ -5396,7 +5396,7 @@
     <t xml:space="preserve">2.53881859779358</t>
   </si>
   <si>
-    <t xml:space="preserve">2.5501446723938</t>
+    <t xml:space="preserve">2.55014491081238</t>
   </si>
   <si>
     <t xml:space="preserve">2.67386198043823</t>
@@ -5408,19 +5408,19 @@
     <t xml:space="preserve">2.73659205436707</t>
   </si>
   <si>
-    <t xml:space="preserve">2.7487895488739</t>
+    <t xml:space="preserve">2.74878931045532</t>
   </si>
   <si>
     <t xml:space="preserve">2.78189706802368</t>
   </si>
   <si>
-    <t xml:space="preserve">2.76011562347412</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.85943818092346</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.86989307403564</t>
+    <t xml:space="preserve">2.7601158618927</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.85943794250488</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.86989283561707</t>
   </si>
   <si>
     <t xml:space="preserve">3.07463645935059</t>
@@ -5432,7 +5432,7 @@
     <t xml:space="preserve">3.1033878326416</t>
   </si>
   <si>
-    <t xml:space="preserve">3.01713395118713</t>
+    <t xml:space="preserve">3.01713418960571</t>
   </si>
   <si>
     <t xml:space="preserve">3.03543019294739</t>
@@ -5456,7 +5456,7 @@
     <t xml:space="preserve">2.95353293418884</t>
   </si>
   <si>
-    <t xml:space="preserve">2.91868305206299</t>
+    <t xml:space="preserve">2.91868281364441</t>
   </si>
   <si>
     <t xml:space="preserve">3.01277780532837</t>
@@ -5480,25 +5480,25 @@
     <t xml:space="preserve">2.92216801643372</t>
   </si>
   <si>
-    <t xml:space="preserve">2.94569158554077</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.90909910202026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.89777302742004</t>
+    <t xml:space="preserve">2.94569182395935</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.90909934043884</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.89777278900146</t>
   </si>
   <si>
     <t xml:space="preserve">2.72700834274292</t>
   </si>
   <si>
-    <t xml:space="preserve">2.66689229011536</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.67211961746216</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.67124819755554</t>
+    <t xml:space="preserve">2.66689205169678</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.67211937904358</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.67124843597412</t>
   </si>
   <si>
     <t xml:space="preserve">2.63204193115234</t>
@@ -5516,22 +5516,22 @@
     <t xml:space="preserve">2.63639855384827</t>
   </si>
   <si>
-    <t xml:space="preserve">2.7156822681427</t>
+    <t xml:space="preserve">2.71568202972412</t>
   </si>
   <si>
     <t xml:space="preserve">2.80106425285339</t>
   </si>
   <si>
-    <t xml:space="preserve">2.85595321655273</t>
+    <t xml:space="preserve">2.85595297813416</t>
   </si>
   <si>
     <t xml:space="preserve">2.85682439804077</t>
   </si>
   <si>
-    <t xml:space="preserve">2.74704718589783</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.75924468040466</t>
+    <t xml:space="preserve">2.74704694747925</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.75924444198608</t>
   </si>
   <si>
     <t xml:space="preserve">2.70609831809998</t>
@@ -5543,7 +5543,7 @@
     <t xml:space="preserve">2.76621437072754</t>
   </si>
   <si>
-    <t xml:space="preserve">2.75314569473267</t>
+    <t xml:space="preserve">2.75314593315125</t>
   </si>
   <si>
     <t xml:space="preserve">2.78015446662903</t>
@@ -5558,7 +5558,7 @@
     <t xml:space="preserve">2.8768630027771</t>
   </si>
   <si>
-    <t xml:space="preserve">2.86640810966492</t>
+    <t xml:space="preserve">2.86640787124634</t>
   </si>
   <si>
     <t xml:space="preserve">2.91781163215637</t>
@@ -5579,13 +5579,13 @@
     <t xml:space="preserve">2.92303919792175</t>
   </si>
   <si>
-    <t xml:space="preserve">2.8995156288147</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.95614647865295</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.02846050262451</t>
+    <t xml:space="preserve">2.89951539039612</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.95614671707153</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.02846026420593</t>
   </si>
   <si>
     <t xml:space="preserve">3.05111289024353</t>
@@ -5600,7 +5600,7 @@
     <t xml:space="preserve">3.06156778335571</t>
   </si>
   <si>
-    <t xml:space="preserve">3.09554648399353</t>
+    <t xml:space="preserve">3.09554624557495</t>
   </si>
   <si>
     <t xml:space="preserve">3.11035752296448</t>
@@ -5609,7 +5609,7 @@
     <t xml:space="preserve">3.07028007507324</t>
   </si>
   <si>
-    <t xml:space="preserve">3.06331014633179</t>
+    <t xml:space="preserve">3.06331038475037</t>
   </si>
   <si>
     <t xml:space="preserve">2.99186778068542</t>
@@ -5618,7 +5618,7 @@
     <t xml:space="preserve">3.10948634147644</t>
   </si>
   <si>
-    <t xml:space="preserve">3.14520740509033</t>
+    <t xml:space="preserve">3.14520764350891</t>
   </si>
   <si>
     <t xml:space="preserve">3.21316504478455</t>
@@ -5630,7 +5630,7 @@
     <t xml:space="preserve">3.26718258857727</t>
   </si>
   <si>
-    <t xml:space="preserve">3.23146152496338</t>
+    <t xml:space="preserve">3.2314612865448</t>
   </si>
   <si>
     <t xml:space="preserve">3.22884774208069</t>
@@ -5648,22 +5648,22 @@
     <t xml:space="preserve">3.34210968017578</t>
   </si>
   <si>
-    <t xml:space="preserve">3.30029010772705</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.31074500083923</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.38131594657898</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.48412346839905</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.46321320533752</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.45362973213196</t>
+    <t xml:space="preserve">3.30028986930847</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.31074476242065</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.38131618499756</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.48412322998047</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.4632134437561</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.45362949371338</t>
   </si>
   <si>
     <t xml:space="preserve">3.50154829025269</t>
@@ -5672,16 +5672,16 @@
     <t xml:space="preserve">3.57124805450439</t>
   </si>
   <si>
-    <t xml:space="preserve">3.67144203186035</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.70716285705566</t>
+    <t xml:space="preserve">3.67144179344177</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.70716309547424</t>
   </si>
   <si>
     <t xml:space="preserve">3.68189668655396</t>
   </si>
   <si>
-    <t xml:space="preserve">3.68625283241272</t>
+    <t xml:space="preserve">3.6862530708313</t>
   </si>
   <si>
     <t xml:space="preserve">3.76553654670715</t>
@@ -5690,25 +5690,25 @@
     <t xml:space="preserve">3.87182903289795</t>
   </si>
   <si>
-    <t xml:space="preserve">3.7812192440033</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.81606912612915</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.80735659599304</t>
+    <t xml:space="preserve">3.78121948242188</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.81606936454773</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.80735635757446</t>
   </si>
   <si>
     <t xml:space="preserve">3.8979663848877</t>
   </si>
   <si>
-    <t xml:space="preserve">3.86921525001526</t>
+    <t xml:space="preserve">3.86921501159668</t>
   </si>
   <si>
     <t xml:space="preserve">3.82739520072937</t>
   </si>
   <si>
-    <t xml:space="preserve">3.87270045280457</t>
+    <t xml:space="preserve">3.87270021438599</t>
   </si>
   <si>
     <t xml:space="preserve">3.80822777748108</t>
@@ -5717,43 +5717,43 @@
     <t xml:space="preserve">3.87618494033813</t>
   </si>
   <si>
-    <t xml:space="preserve">3.7254593372345</t>
+    <t xml:space="preserve">3.72545909881592</t>
   </si>
   <si>
     <t xml:space="preserve">3.72371673583984</t>
   </si>
   <si>
-    <t xml:space="preserve">3.71848964691162</t>
+    <t xml:space="preserve">3.71848917007446</t>
   </si>
   <si>
     <t xml:space="preserve">3.66969919204712</t>
   </si>
   <si>
-    <t xml:space="preserve">3.77163529396057</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.8474338054657</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.84307742118835</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.93281650543213</t>
+    <t xml:space="preserve">3.77163553237915</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.84743404388428</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.84307765960693</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.93281626701355</t>
   </si>
   <si>
     <t xml:space="preserve">4.06786012649536</t>
   </si>
   <si>
-    <t xml:space="preserve">4.03736639022827</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.11490726470947</t>
+    <t xml:space="preserve">4.03736591339111</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.11490774154663</t>
   </si>
   <si>
     <t xml:space="preserve">4.168053150177</t>
   </si>
   <si>
-    <t xml:space="preserve">4.19767570495605</t>
+    <t xml:space="preserve">4.19767618179321</t>
   </si>
   <si>
     <t xml:space="preserve">4.26127672195435</t>
@@ -5771,7 +5771,7 @@
     <t xml:space="preserve">4.29874086380005</t>
   </si>
   <si>
-    <t xml:space="preserve">4.27434587478638</t>
+    <t xml:space="preserve">4.27434635162354</t>
   </si>
   <si>
     <t xml:space="preserve">4.14714384078979</t>
@@ -5789,7 +5789,7 @@
     <t xml:space="preserve">4.36669826507568</t>
   </si>
   <si>
-    <t xml:space="preserve">4.50435590744019</t>
+    <t xml:space="preserve">4.50435543060303</t>
   </si>
   <si>
     <t xml:space="preserve">4.61239051818848</t>
@@ -6846,6 +6846,9 @@
   </si>
   <si>
     <t xml:space="preserve">10.4300003051758</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0749998092651</t>
   </si>
 </sst>
 </file>
@@ -72496,7 +72499,7 @@
     </row>
     <row r="2513">
       <c r="A2513" s="1" t="n">
-        <v>45978.6935069444</v>
+        <v>45978.3333333333</v>
       </c>
       <c r="B2513" t="n">
         <v>7653105</v>
@@ -72517,6 +72520,32 @@
         <v>2277</v>
       </c>
       <c r="H2513" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2514">
+      <c r="A2514" s="1" t="n">
+        <v>45979.691099537</v>
+      </c>
+      <c r="B2514" t="n">
+        <v>11943146</v>
+      </c>
+      <c r="C2514" t="n">
+        <v>10.2950000762939</v>
+      </c>
+      <c r="D2514" t="n">
+        <v>9.94400024414062</v>
+      </c>
+      <c r="E2514" t="n">
+        <v>10.1999998092651</v>
+      </c>
+      <c r="F2514" t="n">
+        <v>10.0749998092651</v>
+      </c>
+      <c r="G2514" t="s">
+        <v>2278</v>
+      </c>
+      <c r="H2514" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/BPE.MI.xlsx
+++ b/data/BPE.MI.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2279" uniqueCount="2279">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2280" uniqueCount="2280">
   <si>
     <t xml:space="preserve">date</t>
   </si>
@@ -38,7 +38,7 @@
     <t xml:space="preserve">ticker</t>
   </si>
   <si>
-    <t xml:space="preserve">3.22921657562256</t>
+    <t xml:space="preserve">3.22921705245972</t>
   </si>
   <si>
     <t xml:space="preserve">BPE.MI</t>
@@ -47,79 +47,79 @@
     <t xml:space="preserve">3.26970100402832</t>
   </si>
   <si>
-    <t xml:space="preserve">3.12443494796753</t>
+    <t xml:space="preserve">3.12443447113037</t>
   </si>
   <si>
     <t xml:space="preserve">3.05299115180969</t>
   </si>
   <si>
-    <t xml:space="preserve">2.98392939567566</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.98631143569946</t>
+    <t xml:space="preserve">2.98392915725708</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.98631119728088</t>
   </si>
   <si>
     <t xml:space="preserve">2.96249628067017</t>
   </si>
   <si>
-    <t xml:space="preserve">3.10538196563721</t>
+    <t xml:space="preserve">3.10538244247437</t>
   </si>
   <si>
     <t xml:space="preserve">2.94582724571228</t>
   </si>
   <si>
-    <t xml:space="preserve">2.68863272666931</t>
+    <t xml:space="preserve">2.68863248825073</t>
   </si>
   <si>
     <t xml:space="preserve">2.67672538757324</t>
   </si>
   <si>
-    <t xml:space="preserve">2.48144841194153</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.75531268119812</t>
+    <t xml:space="preserve">2.48144817352295</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.75531315803528</t>
   </si>
   <si>
     <t xml:space="preserve">2.7243537902832</t>
   </si>
   <si>
-    <t xml:space="preserve">2.65291094779968</t>
+    <t xml:space="preserve">2.65291118621826</t>
   </si>
   <si>
     <t xml:space="preserve">2.80770397186279</t>
   </si>
   <si>
-    <t xml:space="preserve">2.69339489936829</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.49097394943237</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.6195707321167</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.55527281761169</t>
+    <t xml:space="preserve">2.69339561462402</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.49097442626953</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.61957097053528</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.55527257919312</t>
   </si>
   <si>
     <t xml:space="preserve">2.38142848014832</t>
   </si>
   <si>
-    <t xml:space="preserve">2.18424558639526</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.19281888008118</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.14709544181824</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.89085400104523</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.84989380836487</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.97753763198853</t>
+    <t xml:space="preserve">2.18424534797668</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.19281911849976</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.14709568023682</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.8908543586731</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.84989356994629</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.97753775119781</t>
   </si>
   <si>
     <t xml:space="preserve">1.78797626495361</t>
@@ -128,28 +128,28 @@
     <t xml:space="preserve">1.99373137950897</t>
   </si>
   <si>
-    <t xml:space="preserve">2.19567680358887</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.30236482620239</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.35761451721191</t>
+    <t xml:space="preserve">2.19567656517029</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.30236458778381</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.35761404037476</t>
   </si>
   <si>
     <t xml:space="preserve">2.34332537651062</t>
   </si>
   <si>
-    <t xml:space="preserve">2.20329737663269</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.42667579650879</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.33475208282471</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.18615102767944</t>
+    <t xml:space="preserve">2.20329761505127</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.42667555809021</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.33475184440613</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.18615126609802</t>
   </si>
   <si>
     <t xml:space="preserve">2.24044728279114</t>
@@ -158,28 +158,28 @@
     <t xml:space="preserve">2.28236079216003</t>
   </si>
   <si>
-    <t xml:space="preserve">2.24330544471741</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.27664518356323</t>
+    <t xml:space="preserve">2.24330568313599</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.27664470672607</t>
   </si>
   <si>
     <t xml:space="preserve">2.38857269287109</t>
   </si>
   <si>
-    <t xml:space="preserve">2.34713530540466</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.35666155815125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.23473262786865</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.2023446559906</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.22711181640625</t>
+    <t xml:space="preserve">2.34713506698608</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.35666131973267</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.23473215103149</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.20234489440918</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.22711205482483</t>
   </si>
   <si>
     <t xml:space="preserve">2.24711585044861</t>
@@ -188,37 +188,37 @@
     <t xml:space="preserve">2.43381977081299</t>
   </si>
   <si>
-    <t xml:space="preserve">2.46715998649597</t>
+    <t xml:space="preserve">2.46715974807739</t>
   </si>
   <si>
     <t xml:space="preserve">2.38619089126587</t>
   </si>
   <si>
-    <t xml:space="preserve">2.2242534160614</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.24902057647705</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.26902461051941</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.26330947875977</t>
+    <t xml:space="preserve">2.22425389289856</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.24902033805847</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.26902437210083</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.26330971717834</t>
   </si>
   <si>
     <t xml:space="preserve">2.22996926307678</t>
   </si>
   <si>
-    <t xml:space="preserve">2.16900491714478</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.0794632434845</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.05850648880005</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.99277853965759</t>
+    <t xml:space="preserve">2.16900444030762</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.07946300506592</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.05850625038147</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.9927784204483</t>
   </si>
   <si>
     <t xml:space="preserve">2.02897691726685</t>
@@ -227,10 +227,10 @@
     <t xml:space="preserve">1.91371536254883</t>
   </si>
   <si>
-    <t xml:space="preserve">1.90323686599731</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.79083371162415</t>
+    <t xml:space="preserve">1.9032369852066</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.79083383083344</t>
   </si>
   <si>
     <t xml:space="preserve">2.0470757484436</t>
@@ -239,25 +239,25 @@
     <t xml:space="preserve">2.14614319801331</t>
   </si>
   <si>
-    <t xml:space="preserve">2.06041193008423</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.29664921760559</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.40047979354858</t>
+    <t xml:space="preserve">2.06041169166565</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.29664945602417</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.40047955513</t>
   </si>
   <si>
     <t xml:space="preserve">2.40762376785278</t>
   </si>
   <si>
-    <t xml:space="preserve">2.32713150978088</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.39571666717529</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.47192192077637</t>
+    <t xml:space="preserve">2.32713174819946</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.39571690559387</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.47192215919495</t>
   </si>
   <si>
     <t xml:space="preserve">2.48382925987244</t>
@@ -266,19 +266,19 @@
     <t xml:space="preserve">2.39809846878052</t>
   </si>
   <si>
-    <t xml:space="preserve">2.47668528556824</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.4385826587677</t>
+    <t xml:space="preserve">2.47668480873108</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.43858289718628</t>
   </si>
   <si>
     <t xml:space="preserve">2.53383946418762</t>
   </si>
   <si>
-    <t xml:space="preserve">2.43143773078918</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.34237265586853</t>
+    <t xml:space="preserve">2.43143820762634</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.34237241744995</t>
   </si>
   <si>
     <t xml:space="preserve">2.23949527740479</t>
@@ -287,13 +287,13 @@
     <t xml:space="preserve">2.21472859382629</t>
   </si>
   <si>
-    <t xml:space="preserve">2.15281128883362</t>
+    <t xml:space="preserve">2.15281081199646</t>
   </si>
   <si>
     <t xml:space="preserve">2.09660935401917</t>
   </si>
   <si>
-    <t xml:space="preserve">2.09089374542236</t>
+    <t xml:space="preserve">2.09089350700378</t>
   </si>
   <si>
     <t xml:space="preserve">2.0851788520813</t>
@@ -305,85 +305,85 @@
     <t xml:space="preserve">2.04993319511414</t>
   </si>
   <si>
-    <t xml:space="preserve">2.08136868476868</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.1966290473938</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.09375214576721</t>
+    <t xml:space="preserve">2.0813684463501</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.19662928581238</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.09375190734863</t>
   </si>
   <si>
     <t xml:space="preserve">2.12042355537415</t>
   </si>
   <si>
-    <t xml:space="preserve">2.0785219669342</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.24223041534424</t>
+    <t xml:space="preserve">2.07852172851562</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.24223065376282</t>
   </si>
   <si>
     <t xml:space="preserve">2.35429334640503</t>
   </si>
   <si>
-    <t xml:space="preserve">2.30849385261536</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.31434106826782</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.33675384521484</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.2159206867218</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.18766140937805</t>
+    <t xml:space="preserve">2.30849409103394</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.31434082984924</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.33675360679626</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.21592044830322</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.18766117095947</t>
   </si>
   <si>
     <t xml:space="preserve">2.09995985031128</t>
   </si>
   <si>
-    <t xml:space="preserve">2.09021496772766</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.11749935150146</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.15745258331299</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.01615619659424</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.89337396621704</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.83977866172791</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.83393251895905</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.78618383407593</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.96353566646576</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.05221080780029</t>
+    <t xml:space="preserve">2.09021520614624</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.11749982833862</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.15745282173157</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.0161566734314</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.89337408542633</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.83977878093719</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.83393239974976</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.78618371486664</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.96353614330292</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.05221128463745</t>
   </si>
   <si>
     <t xml:space="preserve">2.10483193397522</t>
   </si>
   <si>
-    <t xml:space="preserve">2.09606218338013</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.25684762001038</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.70140600204468</t>
+    <t xml:space="preserve">2.09606194496155</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.25684785842896</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.70140588283539</t>
   </si>
   <si>
     <t xml:space="preserve">1.68386566638947</t>
@@ -392,13 +392,13 @@
     <t xml:space="preserve">1.64391231536865</t>
   </si>
   <si>
-    <t xml:space="preserve">1.55426251888275</t>
+    <t xml:space="preserve">1.55426228046417</t>
   </si>
   <si>
     <t xml:space="preserve">1.59713888168335</t>
   </si>
   <si>
-    <t xml:space="preserve">1.52015626430511</t>
+    <t xml:space="preserve">1.52015602588654</t>
   </si>
   <si>
     <t xml:space="preserve">1.41783809661865</t>
@@ -407,34 +407,34 @@
     <t xml:space="preserve">1.41881275177002</t>
   </si>
   <si>
-    <t xml:space="preserve">1.31746876239777</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.25802624225616</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.46168839931488</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.52990102767944</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.65463197231293</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.57180285453796</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.63904058933258</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.65852952003479</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.6682745218277</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.65268266201019</t>
+    <t xml:space="preserve">1.31746864318848</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.25802659988403</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.46168851852417</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.52990090847015</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.65463173389435</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.57180297374725</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.63904094696045</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.65852963924408</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.66827464103699</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.6526825428009</t>
   </si>
   <si>
     <t xml:space="preserve">1.67022311687469</t>
@@ -446,31 +446,31 @@
     <t xml:space="preserve">1.71115040779114</t>
   </si>
   <si>
-    <t xml:space="preserve">1.66535067558289</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.67314612865448</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.75012862682343</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.69555902481079</t>
+    <t xml:space="preserve">1.66535079479218</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.67314624786377</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.750128865242</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.69555914402008</t>
   </si>
   <si>
     <t xml:space="preserve">1.78813278675079</t>
   </si>
   <si>
-    <t xml:space="preserve">1.68678879737854</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.47825467586517</t>
+    <t xml:space="preserve">1.68678891658783</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.47825443744659</t>
   </si>
   <si>
     <t xml:space="preserve">1.53769659996033</t>
   </si>
   <si>
-    <t xml:space="preserve">1.54549217224121</t>
+    <t xml:space="preserve">1.54549193382263</t>
   </si>
   <si>
     <t xml:space="preserve">1.74720573425293</t>
@@ -482,16 +482,16 @@
     <t xml:space="preserve">1.74915397167206</t>
   </si>
   <si>
-    <t xml:space="preserve">1.73843538761139</t>
+    <t xml:space="preserve">1.73843562602997</t>
   </si>
   <si>
     <t xml:space="preserve">1.7374609708786</t>
   </si>
   <si>
-    <t xml:space="preserve">1.713099360466</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.70043122768402</t>
+    <t xml:space="preserve">1.71309947967529</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.7004314661026</t>
   </si>
   <si>
     <t xml:space="preserve">1.63709139823914</t>
@@ -500,130 +500,130 @@
     <t xml:space="preserve">1.66632521152496</t>
   </si>
   <si>
-    <t xml:space="preserve">1.56985378265381</t>
+    <t xml:space="preserve">1.56985366344452</t>
   </si>
   <si>
     <t xml:space="preserve">1.58057296276093</t>
   </si>
   <si>
-    <t xml:space="preserve">1.67119753360748</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.70725226402283</t>
+    <t xml:space="preserve">1.67119741439819</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.70725214481354</t>
   </si>
   <si>
     <t xml:space="preserve">1.65755486488342</t>
   </si>
   <si>
-    <t xml:space="preserve">1.62344872951508</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.66924858093262</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.6809424161911</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.71212494373322</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.73551142215729</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.70432901382446</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.76182222366333</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.76474571228027</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.72966527938843</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.69653379917145</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.65170848369598</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.59616422653198</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.620525598526</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.55133926868439</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.62442326545715</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.6283210515976</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.55523717403412</t>
+    <t xml:space="preserve">1.62344884872437</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.66924834251404</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.68094229698181</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.71212470531464</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.73551166057587</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.70432913303375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.76182246208191</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.7647453546524</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.72966516017914</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.69653367996216</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.65170872211456</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.59616446495056</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.62052571773529</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.55133938789368</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.62442338466644</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.62832117080688</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.55523705482483</t>
   </si>
   <si>
     <t xml:space="preserve">1.53087568283081</t>
   </si>
   <si>
-    <t xml:space="preserve">1.56498193740845</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.56790494918823</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.61370468139648</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.57667529582977</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.6507340669632</t>
+    <t xml:space="preserve">1.56498181819916</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.56790518760681</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.61370480060577</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.57667541503906</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.65073394775391</t>
   </si>
   <si>
     <t xml:space="preserve">1.655606508255</t>
   </si>
   <si>
-    <t xml:space="preserve">1.63221907615662</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.69068658351898</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.79300546646118</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.83295774459839</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.75305187702179</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.84465134143829</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.88362991809845</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.98010194301605</t>
+    <t xml:space="preserve">1.63221895694733</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.69068646430969</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.79300534725189</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.83295798301697</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.7530517578125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.84465074539185</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.88362979888916</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.98010146617889</t>
   </si>
   <si>
     <t xml:space="preserve">2.07462406158447</t>
   </si>
   <si>
-    <t xml:space="preserve">2.06975126266479</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.12237215042114</t>
+    <t xml:space="preserve">2.06975150108337</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.12237191200256</t>
   </si>
   <si>
     <t xml:space="preserve">2.03369665145874</t>
   </si>
   <si>
-    <t xml:space="preserve">2.06682825088501</t>
+    <t xml:space="preserve">2.06682848930359</t>
   </si>
   <si>
     <t xml:space="preserve">2.11555123329163</t>
@@ -635,31 +635,31 @@
     <t xml:space="preserve">2.08241963386536</t>
   </si>
   <si>
-    <t xml:space="preserve">2.06487941741943</t>
+    <t xml:space="preserve">2.06487894058228</t>
   </si>
   <si>
     <t xml:space="preserve">1.94891846179962</t>
   </si>
   <si>
-    <t xml:space="preserve">1.92455720901489</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.90311896800995</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.9693820476532</t>
+    <t xml:space="preserve">1.92455756664276</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.90311884880066</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.96938240528107</t>
   </si>
   <si>
     <t xml:space="preserve">2.00641131401062</t>
   </si>
   <si>
-    <t xml:space="preserve">2.03564500808716</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.03662037849426</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.01518177986145</t>
+    <t xml:space="preserve">2.03564524650574</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.03662014007568</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.01518154144287</t>
   </si>
   <si>
     <t xml:space="preserve">2.00543665885925</t>
@@ -668,127 +668,127 @@
     <t xml:space="preserve">1.94696915149689</t>
   </si>
   <si>
-    <t xml:space="preserve">1.8641402721405</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.82613670825958</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.81834042072296</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.85537075996399</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.84562575817108</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.85147202014923</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.82321298122406</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.84660041332245</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.99471843242645</t>
+    <t xml:space="preserve">1.86414003372192</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.82613706588745</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.81834053993225</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.85537052154541</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.84562587738037</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.85147213935852</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.82321286201477</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.84660053253174</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.99471795558929</t>
   </si>
   <si>
     <t xml:space="preserve">1.9547655582428</t>
   </si>
   <si>
-    <t xml:space="preserve">2.08729195594788</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.30459570884705</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.33772754669189</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.30167269706726</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.34454917907715</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.39424657821655</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.35526776313782</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.41860818862915</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.43858408927917</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.42153120040894</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.43614864349365</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.48974370956421</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.51410484313965</t>
+    <t xml:space="preserve">2.0872917175293</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.3045961856842</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.33772778511047</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.30167245864868</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.34454941749573</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.39424705505371</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.3552680015564</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.41860771179199</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.43858432769775</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.42153096199036</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.43614888191223</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.48974394798279</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.51410508155823</t>
   </si>
   <si>
     <t xml:space="preserve">2.52141308784485</t>
   </si>
   <si>
-    <t xml:space="preserve">2.46538209915161</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.56770014762878</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.66514611244202</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.62129545211792</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.58231663703918</t>
+    <t xml:space="preserve">2.46538233757019</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.56770038604736</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.66514539718628</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.6212956905365</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.58231687545776</t>
   </si>
   <si>
     <t xml:space="preserve">2.45320153236389</t>
   </si>
   <si>
-    <t xml:space="preserve">2.44102048873901</t>
+    <t xml:space="preserve">2.44102025032043</t>
   </si>
   <si>
     <t xml:space="preserve">2.58718919754028</t>
   </si>
   <si>
-    <t xml:space="preserve">2.56282782554626</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.6042423248291</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.6139874458313</t>
+    <t xml:space="preserve">2.56282758712769</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.60424256324768</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.61398720741272</t>
   </si>
   <si>
     <t xml:space="preserve">2.75528359413147</t>
   </si>
   <si>
-    <t xml:space="preserve">2.79913401603699</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.73335838317871</t>
+    <t xml:space="preserve">2.79913425445557</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.73335814476013</t>
   </si>
   <si>
     <t xml:space="preserve">2.74066638946533</t>
   </si>
   <si>
-    <t xml:space="preserve">2.77477288246155</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.73092222213745</t>
+    <t xml:space="preserve">2.77477312088013</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.73092246055603</t>
   </si>
   <si>
     <t xml:space="preserve">2.60180640220642</t>
@@ -797,16 +797,16 @@
     <t xml:space="preserve">2.55308294296265</t>
   </si>
   <si>
-    <t xml:space="preserve">2.61155009269714</t>
+    <t xml:space="preserve">2.6115505695343</t>
   </si>
   <si>
     <t xml:space="preserve">2.6237313747406</t>
   </si>
   <si>
-    <t xml:space="preserve">2.68707180023193</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.53359389305115</t>
+    <t xml:space="preserve">2.68707156181335</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.53359365463257</t>
   </si>
   <si>
     <t xml:space="preserve">2.44589257240295</t>
@@ -818,43 +818,43 @@
     <t xml:space="preserve">2.31726384162903</t>
   </si>
   <si>
-    <t xml:space="preserve">2.32505941390991</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.40496563911438</t>
+    <t xml:space="preserve">2.32505965232849</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.4049654006958</t>
   </si>
   <si>
     <t xml:space="preserve">2.34357452392578</t>
   </si>
   <si>
-    <t xml:space="preserve">2.26269388198853</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.19253301620483</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.16914629936218</t>
+    <t xml:space="preserve">2.2626941204071</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.19253325462341</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.1691460609436</t>
   </si>
   <si>
     <t xml:space="preserve">2.16622304916382</t>
   </si>
   <si>
-    <t xml:space="preserve">2.08339405059814</t>
+    <t xml:space="preserve">2.0833945274353</t>
   </si>
   <si>
     <t xml:space="preserve">2.0463650226593</t>
   </si>
   <si>
-    <t xml:space="preserve">2.01713109016418</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.18278932571411</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.19155931472778</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.28997945785522</t>
+    <t xml:space="preserve">2.01713085174561</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.18278908729553</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.1915590763092</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.28997921943665</t>
   </si>
   <si>
     <t xml:space="preserve">2.22761416435242</t>
@@ -866,127 +866,127 @@
     <t xml:space="preserve">2.1389377117157</t>
   </si>
   <si>
-    <t xml:space="preserve">2.21007370948792</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.28218364715576</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.24417996406555</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.18668651580811</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.19058442115784</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.29972410202026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.27243900299072</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.340651512146</t>
+    <t xml:space="preserve">2.21007347106934</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.28218388557434</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.24417972564697</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.18668699264526</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.19058465957642</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.29972434043884</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.2724392414093</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.34065175056458</t>
   </si>
   <si>
     <t xml:space="preserve">2.34942150115967</t>
   </si>
   <si>
-    <t xml:space="preserve">2.41568470001221</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.38839960098267</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.34552335739136</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.3601405620575</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.31629014015198</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.28510689735413</t>
+    <t xml:space="preserve">2.41568493843079</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.38839936256409</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.34552359580994</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.36014032363892</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.3162899017334</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.28510713577271</t>
   </si>
   <si>
     <t xml:space="preserve">2.28023457527161</t>
   </si>
   <si>
-    <t xml:space="preserve">2.2003288269043</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.21689414978027</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.21494555473328</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.23151159286499</t>
+    <t xml:space="preserve">2.20032858848572</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.21689462661743</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.21494603157043</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.23151183128357</t>
   </si>
   <si>
     <t xml:space="preserve">2.19545698165894</t>
   </si>
   <si>
-    <t xml:space="preserve">2.14283561706543</t>
+    <t xml:space="preserve">2.14283537864685</t>
   </si>
   <si>
     <t xml:space="preserve">2.12529635429382</t>
   </si>
   <si>
-    <t xml:space="preserve">2.23346018791199</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.38742542266846</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.42250561714172</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.36988544464111</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.44345688819885</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.50679707527161</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.54333877563477</t>
+    <t xml:space="preserve">2.23346066474915</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.38742518424988</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.4225058555603</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.36988496780396</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.44345664978027</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.50679731369019</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.54333901405334</t>
   </si>
   <si>
     <t xml:space="preserve">2.47999882698059</t>
   </si>
   <si>
-    <t xml:space="preserve">2.46050977706909</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.32116198539734</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.28413224220276</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.36793613433838</t>
+    <t xml:space="preserve">2.46050953865051</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.32116174697876</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.28413248062134</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.3679358959198</t>
   </si>
   <si>
     <t xml:space="preserve">2.32895731925964</t>
   </si>
   <si>
-    <t xml:space="preserve">2.27536225318909</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.24905252456665</t>
+    <t xml:space="preserve">2.27536201477051</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.24905228614807</t>
   </si>
   <si>
     <t xml:space="preserve">2.28315854072571</t>
   </si>
   <si>
-    <t xml:space="preserve">2.27229976654053</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.27328753471375</t>
+    <t xml:space="preserve">2.27230000495911</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.27328705787659</t>
   </si>
   <si>
     <t xml:space="preserve">2.30487394332886</t>
@@ -995,7 +995,7 @@
     <t xml:space="preserve">2.301913022995</t>
   </si>
   <si>
-    <t xml:space="preserve">2.27526116371155</t>
+    <t xml:space="preserve">2.27526092529297</t>
   </si>
   <si>
     <t xml:space="preserve">2.20616483688354</t>
@@ -1004,46 +1004,46 @@
     <t xml:space="preserve">2.20715188980103</t>
   </si>
   <si>
-    <t xml:space="preserve">2.15187454223633</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.1972804069519</t>
+    <t xml:space="preserve">2.15187430381775</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.19728064537048</t>
   </si>
   <si>
     <t xml:space="preserve">2.16964221000671</t>
   </si>
   <si>
-    <t xml:space="preserve">2.13015818595886</t>
+    <t xml:space="preserve">2.1301577091217</t>
   </si>
   <si>
     <t xml:space="preserve">2.09758400917053</t>
   </si>
   <si>
-    <t xml:space="preserve">2.10153222084045</t>
+    <t xml:space="preserve">2.10153198242188</t>
   </si>
   <si>
     <t xml:space="preserve">2.17951273918152</t>
   </si>
   <si>
-    <t xml:space="preserve">2.17260336875916</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.12719678878784</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.18050003051758</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.15878367424011</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.06106090545654</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.07389307022095</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.02059030532837</t>
+    <t xml:space="preserve">2.17260313034058</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.12719655036926</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.180499792099</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.15878391265869</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.06106066703796</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.07389283180237</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.02059006690979</t>
   </si>
   <si>
     <t xml:space="preserve">2.11140275001526</t>
@@ -1052,28 +1052,28 @@
     <t xml:space="preserve">2.10251927375793</t>
   </si>
   <si>
-    <t xml:space="preserve">2.15779638290405</t>
+    <t xml:space="preserve">2.15779614448547</t>
   </si>
   <si>
     <t xml:space="preserve">2.17062854766846</t>
   </si>
   <si>
-    <t xml:space="preserve">2.19037103652954</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.17852520942688</t>
+    <t xml:space="preserve">2.19037127494812</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.17852544784546</t>
   </si>
   <si>
     <t xml:space="preserve">2.15483546257019</t>
   </si>
   <si>
-    <t xml:space="preserve">2.29401588439941</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.37199640274048</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.31474494934082</t>
+    <t xml:space="preserve">2.29401636123657</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.37199687957764</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.3147451877594</t>
   </si>
   <si>
     <t xml:space="preserve">2.32066798210144</t>
@@ -1082,31 +1082,31 @@
     <t xml:space="preserve">2.31375789642334</t>
   </si>
   <si>
-    <t xml:space="preserve">2.34534573554993</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.3877911567688</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.43813252449036</t>
+    <t xml:space="preserve">2.34534549713135</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.38779091835022</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.43813300132751</t>
   </si>
   <si>
     <t xml:space="preserve">2.44504237174988</t>
   </si>
   <si>
-    <t xml:space="preserve">2.44306874275208</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.4578742980957</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.37791967391968</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.3937132358551</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.32955193519592</t>
+    <t xml:space="preserve">2.4430685043335</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.45787405967712</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.3779194355011</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.39371275901794</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.3295521736145</t>
   </si>
   <si>
     <t xml:space="preserve">2.30388736724854</t>
@@ -1115,58 +1115,58 @@
     <t xml:space="preserve">2.27624821662903</t>
   </si>
   <si>
-    <t xml:space="preserve">2.30980968475342</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.32165431976318</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.29599022865295</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.29204154014587</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.33646154403687</t>
+    <t xml:space="preserve">2.30980944633484</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.32165479660034</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.2959897518158</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.29204177856445</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.33646130561829</t>
   </si>
   <si>
     <t xml:space="preserve">2.47761607170105</t>
   </si>
   <si>
-    <t xml:space="preserve">2.44405484199524</t>
+    <t xml:space="preserve">2.44405508041382</t>
   </si>
   <si>
     <t xml:space="preserve">2.42628741264343</t>
   </si>
   <si>
-    <t xml:space="preserve">2.34040975570679</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.41839051246643</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.40753269195557</t>
+    <t xml:space="preserve">2.34040999412537</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.41839027404785</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.40753245353699</t>
   </si>
   <si>
     <t xml:space="preserve">2.38088083267212</t>
   </si>
   <si>
-    <t xml:space="preserve">2.34929370880127</t>
+    <t xml:space="preserve">2.34929394721985</t>
   </si>
   <si>
     <t xml:space="preserve">2.31968092918396</t>
   </si>
   <si>
-    <t xml:space="preserve">2.34238338470459</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.35225486755371</t>
+    <t xml:space="preserve">2.34238362312317</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.35225510597229</t>
   </si>
   <si>
     <t xml:space="preserve">2.29105496406555</t>
   </si>
   <si>
-    <t xml:space="preserve">2.31573271751404</t>
+    <t xml:space="preserve">2.31573247909546</t>
   </si>
   <si>
     <t xml:space="preserve">2.33547425270081</t>
@@ -1178,7 +1178,7 @@
     <t xml:space="preserve">2.3315258026123</t>
   </si>
   <si>
-    <t xml:space="preserve">2.29500341415405</t>
+    <t xml:space="preserve">2.29500365257263</t>
   </si>
   <si>
     <t xml:space="preserve">2.2555193901062</t>
@@ -1187,49 +1187,49 @@
     <t xml:space="preserve">2.23577737808228</t>
   </si>
   <si>
-    <t xml:space="preserve">2.29993915557861</t>
+    <t xml:space="preserve">2.29993891716003</t>
   </si>
   <si>
     <t xml:space="preserve">2.37100982666016</t>
   </si>
   <si>
-    <t xml:space="preserve">2.32362937927246</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.2644031047821</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.28513193130493</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.31277132034302</t>
+    <t xml:space="preserve">2.32362914085388</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.26440334320068</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.28513264656067</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.3127715587616</t>
   </si>
   <si>
     <t xml:space="preserve">2.36113858222961</t>
   </si>
   <si>
-    <t xml:space="preserve">2.30882263183594</t>
+    <t xml:space="preserve">2.30882239341736</t>
   </si>
   <si>
     <t xml:space="preserve">2.37693214416504</t>
   </si>
   <si>
-    <t xml:space="preserve">2.44701647758484</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.48748779296875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.49735856056213</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.53931069374084</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.53190684318542</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.45688724517822</t>
+    <t xml:space="preserve">2.447016954422</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.48748731613159</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.49735832214355</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.53931045532227</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.53190660476685</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.45688676834106</t>
   </si>
   <si>
     <t xml:space="preserve">2.41542935371399</t>
@@ -1244,28 +1244,28 @@
     <t xml:space="preserve">2.16865468025208</t>
   </si>
   <si>
-    <t xml:space="preserve">2.1923451423645</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.16766762733459</t>
+    <t xml:space="preserve">2.19234490394592</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.16766738891602</t>
   </si>
   <si>
     <t xml:space="preserve">2.16174483299255</t>
   </si>
   <si>
-    <t xml:space="preserve">2.09264826774597</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.09955739974976</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.12028670310974</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.09659624099731</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.06402277946472</t>
+    <t xml:space="preserve">2.09264802932739</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.09955716133118</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.12028646469116</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.09659647941589</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.06402254104614</t>
   </si>
   <si>
     <t xml:space="preserve">2.07488036155701</t>
@@ -1274,19 +1274,19 @@
     <t xml:space="preserve">2.06500911712646</t>
   </si>
   <si>
-    <t xml:space="preserve">2.05908679962158</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.13410615921021</t>
+    <t xml:space="preserve">2.05908703804016</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.13410592079163</t>
   </si>
   <si>
     <t xml:space="preserve">2.07981562614441</t>
   </si>
   <si>
-    <t xml:space="preserve">2.04625415802002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.00775742530823</t>
+    <t xml:space="preserve">2.04625463485718</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.00775766372681</t>
   </si>
   <si>
     <t xml:space="preserve">1.91990602016449</t>
@@ -1295,34 +1295,34 @@
     <t xml:space="preserve">2.11041617393494</t>
   </si>
   <si>
-    <t xml:space="preserve">2.08771276473999</t>
+    <t xml:space="preserve">2.08771300315857</t>
   </si>
   <si>
     <t xml:space="preserve">2.10646796226501</t>
   </si>
   <si>
-    <t xml:space="preserve">2.06007409095764</t>
+    <t xml:space="preserve">2.06007432937622</t>
   </si>
   <si>
     <t xml:space="preserve">2.10350584983826</t>
   </si>
   <si>
-    <t xml:space="preserve">2.03342223167419</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.06698346138</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.03835797309875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.02651262283325</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.08672499656677</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.18346095085144</t>
+    <t xml:space="preserve">2.03342199325562</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.06698393821716</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.03835773468018</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.02651309967041</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.08672547340393</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.18346118927002</t>
   </si>
   <si>
     <t xml:space="preserve">2.26835155487061</t>
@@ -1337,28 +1337,28 @@
     <t xml:space="preserve">2.24861001968384</t>
   </si>
   <si>
-    <t xml:space="preserve">2.22097039222717</t>
+    <t xml:space="preserve">2.22097063064575</t>
   </si>
   <si>
     <t xml:space="preserve">2.29302883148193</t>
   </si>
   <si>
-    <t xml:space="preserve">2.23972606658936</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.09857034683228</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.05711221694946</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.05118989944458</t>
+    <t xml:space="preserve">2.23972582817078</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.0985701084137</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.05711269378662</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.05119037628174</t>
   </si>
   <si>
     <t xml:space="preserve">2.11930012702942</t>
   </si>
   <si>
-    <t xml:space="preserve">2.10745429992676</t>
+    <t xml:space="preserve">2.10745453834534</t>
   </si>
   <si>
     <t xml:space="preserve">2.10942888259888</t>
@@ -1370,70 +1370,67 @@
     <t xml:space="preserve">2.07882857322693</t>
   </si>
   <si>
-    <t xml:space="preserve">2.13608050346375</t>
+    <t xml:space="preserve">2.1360809803009</t>
   </si>
   <si>
     <t xml:space="preserve">2.07784128189087</t>
   </si>
   <si>
-    <t xml:space="preserve">2.05316376686096</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.09363532066345</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.09560918807983</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.13213205337524</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.22788071632385</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.25058364868164</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.22590637207031</t>
+    <t xml:space="preserve">2.05316400527954</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.09363508224487</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.09560942649841</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.13213181495667</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.22788095474243</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.25058388710022</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.22590613365173</t>
   </si>
   <si>
     <t xml:space="preserve">2.18247389793396</t>
   </si>
   <si>
-    <t xml:space="preserve">2.28315830230713</t>
-  </si>
-  <si>
     <t xml:space="preserve">2.37594509124756</t>
   </si>
   <si>
     <t xml:space="preserve">2.37397122383118</t>
   </si>
   <si>
-    <t xml:space="preserve">2.39124536514282</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.29944515228271</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.31820011138916</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.3004322052002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.23775148391724</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.24614191055298</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.32461643218994</t>
+    <t xml:space="preserve">2.3912456035614</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.29944539070129</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.31819987297058</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.30043196678162</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.23775124549866</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.2461416721344</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.32461619377136</t>
   </si>
   <si>
     <t xml:space="preserve">2.27427458763123</t>
   </si>
   <si>
-    <t xml:space="preserve">2.24416780471802</t>
+    <t xml:space="preserve">2.24416756629944</t>
   </si>
   <si>
     <t xml:space="preserve">2.36064505577087</t>
@@ -1445,43 +1442,43 @@
     <t xml:space="preserve">2.35521578788757</t>
   </si>
   <si>
-    <t xml:space="preserve">2.35916447639465</t>
+    <t xml:space="preserve">2.35916423797607</t>
   </si>
   <si>
     <t xml:space="preserve">2.3122775554657</t>
   </si>
   <si>
-    <t xml:space="preserve">2.40012907981873</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.4006233215332</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.40506529808044</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.40259695053101</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.43122267723083</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.41098713874817</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.22738718986511</t>
+    <t xml:space="preserve">2.40012955665588</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.40062308311462</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.40506505966187</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.40259671211243</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.43122243881226</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.41098761558533</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.22738695144653</t>
   </si>
   <si>
     <t xml:space="preserve">2.3186936378479</t>
   </si>
   <si>
-    <t xml:space="preserve">2.35028100013733</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.27674174308777</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.31918716430664</t>
+    <t xml:space="preserve">2.35028123855591</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.27674198150635</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.31918692588806</t>
   </si>
   <si>
     <t xml:space="preserve">2.26687073707581</t>
@@ -1490,52 +1487,52 @@
     <t xml:space="preserve">2.27131247520447</t>
   </si>
   <si>
-    <t xml:space="preserve">2.29796481132507</t>
+    <t xml:space="preserve">2.29796457290649</t>
   </si>
   <si>
     <t xml:space="preserve">2.30586123466492</t>
   </si>
   <si>
-    <t xml:space="preserve">2.29006791114807</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.2456476688385</t>
+    <t xml:space="preserve">2.29006743431091</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.24564790725708</t>
   </si>
   <si>
     <t xml:space="preserve">2.25206446647644</t>
   </si>
   <si>
-    <t xml:space="preserve">2.23232269287109</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.2476224899292</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.22886753082275</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.23084211349487</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.31721234321594</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.32560276985168</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.33448648452759</t>
+    <t xml:space="preserve">2.23232293128967</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.24762296676636</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.22886729240417</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.23084187507629</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.31721258163452</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.32560300827026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.33448696136475</t>
   </si>
   <si>
     <t xml:space="preserve">2.35817766189575</t>
   </si>
   <si>
-    <t xml:space="preserve">2.40851974487305</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.37989377975464</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.38630986213684</t>
+    <t xml:space="preserve">2.40851950645447</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.37989401817322</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.38630962371826</t>
   </si>
   <si>
     <t xml:space="preserve">2.41197443008423</t>
@@ -1544,31 +1541,31 @@
     <t xml:space="preserve">2.36804819107056</t>
   </si>
   <si>
-    <t xml:space="preserve">2.33843541145325</t>
+    <t xml:space="preserve">2.33843517303467</t>
   </si>
   <si>
     <t xml:space="preserve">2.35324215888977</t>
   </si>
   <si>
-    <t xml:space="preserve">2.34189057350159</t>
+    <t xml:space="preserve">2.34189081192017</t>
   </si>
   <si>
     <t xml:space="preserve">2.35373592376709</t>
   </si>
   <si>
-    <t xml:space="preserve">2.33596777915955</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.32856464385986</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.42036485671997</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.42924857139587</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.47662997245789</t>
+    <t xml:space="preserve">2.33596801757812</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.32856488227844</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.42036461830139</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.42924833297729</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.47662973403931</t>
   </si>
   <si>
     <t xml:space="preserve">2.5121648311615</t>
@@ -1577,22 +1574,22 @@
     <t xml:space="preserve">2.54079055786133</t>
   </si>
   <si>
-    <t xml:space="preserve">2.46626496315002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.46675848960876</t>
+    <t xml:space="preserve">2.46626472473145</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.46675825119019</t>
   </si>
   <si>
     <t xml:space="preserve">2.30290031433105</t>
   </si>
   <si>
-    <t xml:space="preserve">2.32413005828857</t>
+    <t xml:space="preserve">2.32412981987</t>
   </si>
   <si>
     <t xml:space="preserve">2.36153388023376</t>
   </si>
   <si>
-    <t xml:space="preserve">2.38731288909912</t>
+    <t xml:space="preserve">2.38731265068054</t>
   </si>
   <si>
     <t xml:space="preserve">2.3579957485199</t>
@@ -1601,43 +1598,43 @@
     <t xml:space="preserve">2.31048178672791</t>
   </si>
   <si>
-    <t xml:space="preserve">2.17552208900452</t>
+    <t xml:space="preserve">2.1755223274231</t>
   </si>
   <si>
     <t xml:space="preserve">2.06583690643311</t>
   </si>
   <si>
-    <t xml:space="preserve">2.07341837882996</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.07392406463623</t>
+    <t xml:space="preserve">2.07341861724854</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.07392430305481</t>
   </si>
   <si>
     <t xml:space="preserve">2.23718953132629</t>
   </si>
   <si>
-    <t xml:space="preserve">2.17147850990295</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.09768080711365</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.09667038917542</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.13710689544678</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.07948470115662</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.16996312141418</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.1957414150238</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.23112368583679</t>
+    <t xml:space="preserve">2.17147874832153</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.09768056869507</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.09667062759399</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.13710737228394</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.07948422431946</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.16996288299561</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.19574165344238</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.23112392425537</t>
   </si>
   <si>
     <t xml:space="preserve">2.25841879844666</t>
@@ -1649,49 +1646,49 @@
     <t xml:space="preserve">2.18866467475891</t>
   </si>
   <si>
-    <t xml:space="preserve">2.26296806335449</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.32008600234985</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.25184798240662</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.417640209198</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.36810541152954</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.3812472820282</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.34738039970398</t>
+    <t xml:space="preserve">2.26296758651733</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.32008576393127</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.25184845924377</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.41764068603516</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.36810517311096</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.38124752044678</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.34738063812256</t>
   </si>
   <si>
     <t xml:space="preserve">2.36861062049866</t>
   </si>
   <si>
-    <t xml:space="preserve">2.37922525405884</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.37012696266174</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.3726544380188</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.36355590820312</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.41005897521973</t>
+    <t xml:space="preserve">2.37922501564026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.37012672424316</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.37265491485596</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.3635561466217</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.41005873680115</t>
   </si>
   <si>
     <t xml:space="preserve">2.41814589500427</t>
   </si>
   <si>
-    <t xml:space="preserve">2.37113761901855</t>
+    <t xml:space="preserve">2.37113785743713</t>
   </si>
   <si>
     <t xml:space="preserve">2.33171153068542</t>
@@ -1703,40 +1700,40 @@
     <t xml:space="preserve">2.38023638725281</t>
   </si>
   <si>
-    <t xml:space="preserve">2.3382830619812</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.29481267929077</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.34131526947021</t>
+    <t xml:space="preserve">2.33828282356262</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.29481291770935</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.34131550788879</t>
   </si>
   <si>
     <t xml:space="preserve">2.33878755569458</t>
   </si>
   <si>
-    <t xml:space="preserve">2.37315917015076</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.40652060508728</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.38276386260986</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.41662931442261</t>
+    <t xml:space="preserve">2.37315940856934</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.4065203666687</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.38276314735413</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.41662955284119</t>
   </si>
   <si>
     <t xml:space="preserve">2.40550923347473</t>
   </si>
   <si>
-    <t xml:space="preserve">2.31958055496216</t>
+    <t xml:space="preserve">2.31958031654358</t>
   </si>
   <si>
     <t xml:space="preserve">2.31351447105408</t>
   </si>
   <si>
-    <t xml:space="preserve">2.31503129005432</t>
+    <t xml:space="preserve">2.31503105163574</t>
   </si>
   <si>
     <t xml:space="preserve">2.33524942398071</t>
@@ -1745,19 +1742,19 @@
     <t xml:space="preserve">2.19725775718689</t>
   </si>
   <si>
-    <t xml:space="preserve">2.1724898815155</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.14216184616089</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.08908796310425</t>
+    <t xml:space="preserve">2.17249011993408</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.14216208457947</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.08908772468567</t>
   </si>
   <si>
     <t xml:space="preserve">2.06937503814697</t>
   </si>
   <si>
-    <t xml:space="preserve">2.06684756278992</t>
+    <t xml:space="preserve">2.06684803962708</t>
   </si>
   <si>
     <t xml:space="preserve">2.02186107635498</t>
@@ -1766,55 +1763,55 @@
     <t xml:space="preserve">2.02236652374268</t>
   </si>
   <si>
-    <t xml:space="preserve">2.06735301017761</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.06634259223938</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.05016684532166</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.04511308670044</t>
+    <t xml:space="preserve">2.06735277175903</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.0663423538208</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.05016708374023</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.04511284828186</t>
   </si>
   <si>
     <t xml:space="preserve">2.03702545166016</t>
   </si>
   <si>
-    <t xml:space="preserve">2.00416970252991</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.01680660247803</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.94098711013794</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.92026305198669</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.9293612241745</t>
+    <t xml:space="preserve">2.00416994094849</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.01680636405945</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.94098687171936</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.9202629327774</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.92936134338379</t>
   </si>
   <si>
     <t xml:space="preserve">2.00012612342834</t>
   </si>
   <si>
-    <t xml:space="preserve">2.08555030822754</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.08959341049194</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.14519429206848</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.13458013534546</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.13660168647766</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.12952589988708</t>
+    <t xml:space="preserve">2.0855495929718</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.08959364891052</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.14519476890564</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.13457989692688</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.13660144805908</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.12952566146851</t>
   </si>
   <si>
     <t xml:space="preserve">2.17855548858643</t>
@@ -1823,7 +1820,7 @@
     <t xml:space="preserve">2.21141076087952</t>
   </si>
   <si>
-    <t xml:space="preserve">2.19068670272827</t>
+    <t xml:space="preserve">2.19068646430969</t>
   </si>
   <si>
     <t xml:space="preserve">2.14873337745667</t>
@@ -1832,40 +1829,40 @@
     <t xml:space="preserve">2.17350101470947</t>
   </si>
   <si>
-    <t xml:space="preserve">2.20029044151306</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.22253036499023</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.01579570770264</t>
+    <t xml:space="preserve">2.20029067993164</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.22253084182739</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.01579523086548</t>
   </si>
   <si>
     <t xml:space="preserve">1.93643760681152</t>
   </si>
   <si>
-    <t xml:space="preserve">1.90257143974304</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.87780296802521</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.88942909240723</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.85505783557892</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.82422411441803</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.7878303527832</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.82675135135651</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.79237985610962</t>
+    <t xml:space="preserve">1.90257167816162</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.87780284881592</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.88942921161652</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.85505795478821</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.82422435283661</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.78783059120178</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.82675123214722</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.79237949848175</t>
   </si>
   <si>
     <t xml:space="preserve">1.80602729320526</t>
@@ -1874,31 +1871,31 @@
     <t xml:space="preserve">1.8186639547348</t>
   </si>
   <si>
-    <t xml:space="preserve">1.80299496650696</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.80552196502686</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.76660120487213</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.77317261695862</t>
+    <t xml:space="preserve">1.80299472808838</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.80552172660828</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.76660084724426</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.77317273616791</t>
   </si>
   <si>
     <t xml:space="preserve">1.70847272872925</t>
   </si>
   <si>
-    <t xml:space="preserve">1.67157340049744</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.62405979633331</t>
+    <t xml:space="preserve">1.67157351970673</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.62405955791473</t>
   </si>
   <si>
     <t xml:space="preserve">1.66146457195282</t>
   </si>
   <si>
-    <t xml:space="preserve">1.64882814884186</t>
+    <t xml:space="preserve">1.64882791042328</t>
   </si>
   <si>
     <t xml:space="preserve">1.72161495685577</t>
@@ -1907,25 +1904,25 @@
     <t xml:space="preserve">1.71150541305542</t>
   </si>
   <si>
-    <t xml:space="preserve">1.69735205173492</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.70746159553528</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.77671027183533</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.71554899215698</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.70291256904602</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.73374581336975</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.74688827991486</t>
+    <t xml:space="preserve">1.69735193252563</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.70746183395386</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.77671039104462</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.71554911136627</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.70291233062744</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.73374605178833</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.74688804149628</t>
   </si>
   <si>
     <t xml:space="preserve">1.7625572681427</t>
@@ -1934,88 +1931,88 @@
     <t xml:space="preserve">1.76508498191833</t>
   </si>
   <si>
-    <t xml:space="preserve">1.71352756023407</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.72768032550812</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.69634175300598</t>
+    <t xml:space="preserve">1.71352744102478</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.72768008708954</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.69634163379669</t>
   </si>
   <si>
     <t xml:space="preserve">1.7120109796524</t>
   </si>
   <si>
-    <t xml:space="preserve">1.69229793548584</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.75345873832703</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.76356863975525</t>
+    <t xml:space="preserve">1.69229805469513</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.75345897674561</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.76356840133667</t>
   </si>
   <si>
     <t xml:space="preserve">1.76457965373993</t>
   </si>
   <si>
-    <t xml:space="preserve">1.85910153388977</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.79389619827271</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.81007122993469</t>
+    <t xml:space="preserve">1.85910129547119</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.79389655590057</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.8100711107254</t>
   </si>
   <si>
     <t xml:space="preserve">1.8191694021225</t>
   </si>
   <si>
-    <t xml:space="preserve">1.90307700634003</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.87072682380676</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.90560412406921</t>
+    <t xml:space="preserve">1.90307724475861</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.87072694301605</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.90560436248779</t>
   </si>
   <si>
     <t xml:space="preserve">1.84494829177856</t>
   </si>
   <si>
-    <t xml:space="preserve">1.81563138961792</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.78479814529419</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.76761221885681</t>
+    <t xml:space="preserve">1.81563127040863</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.7847980260849</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.76761209964752</t>
   </si>
   <si>
     <t xml:space="preserve">1.76053595542908</t>
   </si>
   <si>
-    <t xml:space="preserve">1.73324012756348</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.69937431812286</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.69128704071045</t>
+    <t xml:space="preserve">1.73324036598206</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.69937443733215</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.69128715991974</t>
   </si>
   <si>
     <t xml:space="preserve">1.72565865516663</t>
   </si>
   <si>
-    <t xml:space="preserve">1.69280290603638</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.68016612529755</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.65742075443268</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.70038545131683</t>
+    <t xml:space="preserve">1.69280302524567</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.68016624450684</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.65742087364197</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.70038557052612</t>
   </si>
   <si>
     <t xml:space="preserve">1.66601371765137</t>
@@ -2027,22 +2024,22 @@
     <t xml:space="preserve">1.71049439907074</t>
   </si>
   <si>
-    <t xml:space="preserve">1.72110950946808</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.68319964408875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.67612254619598</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.68117737770081</t>
+    <t xml:space="preserve">1.72110939025879</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.68319976329803</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.67612266540527</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.6811774969101</t>
   </si>
   <si>
     <t xml:space="preserve">1.65287184715271</t>
   </si>
   <si>
-    <t xml:space="preserve">1.58918249607086</t>
+    <t xml:space="preserve">1.58918261528015</t>
   </si>
   <si>
     <t xml:space="preserve">1.51386845111847</t>
@@ -2051,13 +2048,13 @@
     <t xml:space="preserve">1.54722917079926</t>
   </si>
   <si>
-    <t xml:space="preserve">1.55329501628876</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.54419660568237</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.5522837638855</t>
+    <t xml:space="preserve">1.55329513549805</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.54419648647308</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.55228364467621</t>
   </si>
   <si>
     <t xml:space="preserve">1.54369080066681</t>
@@ -2066,28 +2063,28 @@
     <t xml:space="preserve">1.52094483375549</t>
   </si>
   <si>
-    <t xml:space="preserve">1.52549397945404</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.59221577644348</t>
+    <t xml:space="preserve">1.52549386024475</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.59221565723419</t>
   </si>
   <si>
     <t xml:space="preserve">1.57300770282745</t>
   </si>
   <si>
-    <t xml:space="preserve">1.57705128192902</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.59069907665253</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.49415564537048</t>
+    <t xml:space="preserve">1.5770515203476</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.59069895744324</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.4941554069519</t>
   </si>
   <si>
     <t xml:space="preserve">1.49870431423187</t>
   </si>
   <si>
-    <t xml:space="preserve">1.50123178958893</t>
+    <t xml:space="preserve">1.50123190879822</t>
   </si>
   <si>
     <t xml:space="preserve">1.50375890731812</t>
@@ -2099,25 +2096,25 @@
     <t xml:space="preserve">1.52347242832184</t>
   </si>
   <si>
-    <t xml:space="preserve">1.65792655944824</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.72666966915131</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.70897829532623</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.70240724086761</t>
+    <t xml:space="preserve">1.65792644023895</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.7266697883606</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.70897841453552</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.70240700244904</t>
   </si>
   <si>
     <t xml:space="preserve">1.78125977516174</t>
   </si>
   <si>
-    <t xml:space="preserve">1.7741836309433</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.75901925563812</t>
+    <t xml:space="preserve">1.77418375015259</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.75901937484741</t>
   </si>
   <si>
     <t xml:space="preserve">1.73071348667145</t>
@@ -2138,16 +2135,16 @@
     <t xml:space="preserve">1.8692102432251</t>
   </si>
   <si>
-    <t xml:space="preserve">1.86415600776672</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.85809051990509</t>
+    <t xml:space="preserve">1.8641562461853</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.8580904006958</t>
   </si>
   <si>
     <t xml:space="preserve">1.87325477600098</t>
   </si>
   <si>
-    <t xml:space="preserve">1.8181586265564</t>
+    <t xml:space="preserve">1.81815838813782</t>
   </si>
   <si>
     <t xml:space="preserve">1.79945683479309</t>
@@ -2156,85 +2153,85 @@
     <t xml:space="preserve">1.78833615779877</t>
   </si>
   <si>
-    <t xml:space="preserve">1.79895114898682</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.83534443378448</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.8722437620163</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.88639616966248</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.88690173625946</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.87022149562836</t>
+    <t xml:space="preserve">1.79895102977753</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.83534407615662</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.87224364280701</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.8863959312439</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.88690161705017</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.87022173404694</t>
   </si>
   <si>
     <t xml:space="preserve">1.84444260597229</t>
   </si>
   <si>
-    <t xml:space="preserve">1.83686089515686</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.82119166851044</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.85000336170197</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.84242105484009</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.84039902687073</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.86567211151123</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.85151970386505</t>
+    <t xml:space="preserve">1.83686113357544</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.82119190692902</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.8500030040741</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.84242117404938</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.84039926528931</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.86567199230194</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.85151958465576</t>
   </si>
   <si>
     <t xml:space="preserve">1.86971604824066</t>
   </si>
   <si>
-    <t xml:space="preserve">1.87173819541931</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.88791298866272</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.88892376422882</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.91874647140503</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.95463454723358</t>
+    <t xml:space="preserve">1.87173795700073</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.88791286945343</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.8889240026474</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.91874635219574</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.95463466644287</t>
   </si>
   <si>
     <t xml:space="preserve">2.00619196891785</t>
   </si>
   <si>
-    <t xml:space="preserve">2.04005813598633</t>
+    <t xml:space="preserve">2.04005837440491</t>
   </si>
   <si>
     <t xml:space="preserve">2.09414267539978</t>
   </si>
   <si>
-    <t xml:space="preserve">2.11436152458191</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.09363722801208</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.07544088363647</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.10930705070496</t>
+    <t xml:space="preserve">2.11436176300049</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.09363698959351</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.07544112205505</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.10930681228638</t>
   </si>
   <si>
     <t xml:space="preserve">2.12649297714233</t>
@@ -2249,34 +2246,34 @@
     <t xml:space="preserve">2.1305365562439</t>
   </si>
   <si>
-    <t xml:space="preserve">2.12396478652954</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.07999014854431</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.068363904953</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.02388310432434</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.00164246559143</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.97131478786469</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.98900651931763</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.95412874221802</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.99810457229614</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.9446769952774</t>
+    <t xml:space="preserve">2.12396502494812</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.07998991012573</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.06836414337158</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.0238835811615</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.00164270401001</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.97131502628326</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.98900628089905</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.95412909984589</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.99810469150543</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.94467735290527</t>
   </si>
   <si>
     <t xml:space="preserve">1.89345979690552</t>
@@ -2285,25 +2282,25 @@
     <t xml:space="preserve">1.85321760177612</t>
   </si>
   <si>
-    <t xml:space="preserve">1.82865512371063</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.84746956825256</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.79834306240082</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.79938781261444</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.78998112678528</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.77743780612946</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.76855289936066</t>
+    <t xml:space="preserve">1.82865488529205</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.84746968746185</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.79834294319153</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.79938769340515</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.78998100757599</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.77743768692017</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.76855325698853</t>
   </si>
   <si>
     <t xml:space="preserve">1.75444209575653</t>
@@ -2312,64 +2309,64 @@
     <t xml:space="preserve">1.78527760505676</t>
   </si>
   <si>
-    <t xml:space="preserve">1.75287473201752</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.73196995258331</t>
+    <t xml:space="preserve">1.75287461280823</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.73197031021118</t>
   </si>
   <si>
     <t xml:space="preserve">1.72883379459381</t>
   </si>
   <si>
-    <t xml:space="preserve">1.78318667411804</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.79991042613983</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.77952861785889</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.80095565319061</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.79468429088593</t>
+    <t xml:space="preserve">1.78318679332733</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.79991030693054</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.77952837944031</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.80095589160919</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.79468405246735</t>
   </si>
   <si>
     <t xml:space="preserve">1.80827224254608</t>
   </si>
   <si>
-    <t xml:space="preserve">1.84903717041016</t>
+    <t xml:space="preserve">1.84903693199158</t>
   </si>
   <si>
     <t xml:space="preserve">1.88353049755096</t>
   </si>
   <si>
-    <t xml:space="preserve">1.88143980503082</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.91331994533539</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.89241516590118</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.89136970043182</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.90234434604645</t>
+    <t xml:space="preserve">1.88143968582153</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.9133198261261</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.89241504669189</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.89136946201324</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.90234422683716</t>
   </si>
   <si>
     <t xml:space="preserve">1.87255501747131</t>
   </si>
   <si>
-    <t xml:space="preserve">1.86262512207031</t>
+    <t xml:space="preserve">1.8626252412796</t>
   </si>
   <si>
     <t xml:space="preserve">1.90077710151672</t>
   </si>
   <si>
-    <t xml:space="preserve">1.97498905658722</t>
+    <t xml:space="preserve">1.9749892950058</t>
   </si>
   <si>
     <t xml:space="preserve">2.03247761726379</t>
@@ -2378,61 +2375,64 @@
     <t xml:space="preserve">2.03665828704834</t>
   </si>
   <si>
-    <t xml:space="preserve">2.01836681365967</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.01000475883484</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.99328088760376</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.00216555595398</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.98805475234985</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.01627659797668</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.98387372493744</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.9587881565094</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.96505880355835</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.95460724830627</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.90495812892914</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.88927888870239</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.86941981315613</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.84381067752838</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.77168941497803</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.76071405410767</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.80775034427643</t>
+    <t xml:space="preserve">2.01836657524109</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.00164294242859</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.01000499725342</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.99328100681305</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.0021653175354</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.98805463314056</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.01627635955811</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.98387384414673</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.95878827571869</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.96505892276764</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.9546070098877</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.90495789051056</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.88927865028381</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.86941969394684</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.84381055831909</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.77168917655945</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.76071381568909</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.80775046348572</t>
   </si>
   <si>
     <t xml:space="preserve">1.78005111217499</t>
   </si>
   <si>
-    <t xml:space="preserve">1.80722784996033</t>
+    <t xml:space="preserve">1.80722761154175</t>
   </si>
   <si>
     <t xml:space="preserve">1.78214108943939</t>
@@ -2444,28 +2444,28 @@
     <t xml:space="preserve">1.67239081859589</t>
   </si>
   <si>
-    <t xml:space="preserve">1.63685262203217</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.65566730499268</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.57413768768311</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.60863077640533</t>
+    <t xml:space="preserve">1.63685250282288</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.6556670665741</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.5741378068924</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.60863089561462</t>
   </si>
   <si>
     <t xml:space="preserve">1.62483263015747</t>
   </si>
   <si>
-    <t xml:space="preserve">1.57309222221375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.60026872158051</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.60654056072235</t>
+    <t xml:space="preserve">1.57309246063232</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.60026884078979</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.60654079914093</t>
   </si>
   <si>
     <t xml:space="preserve">1.59295237064362</t>
@@ -2480,28 +2480,28 @@
     <t xml:space="preserve">1.665074467659</t>
   </si>
   <si>
-    <t xml:space="preserve">1.69799935817719</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.68441092967987</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.68806934356689</t>
+    <t xml:space="preserve">1.6979992389679</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.68441104888916</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.6880692243576</t>
   </si>
   <si>
     <t xml:space="preserve">1.71629106998444</t>
   </si>
   <si>
-    <t xml:space="preserve">1.73353731632233</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.7387638092041</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.74712562561035</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.80618238449097</t>
+    <t xml:space="preserve">1.73353755474091</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.73876368999481</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.74712550640106</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.8061820268631</t>
   </si>
   <si>
     <t xml:space="preserve">1.82656407356262</t>
@@ -2510,37 +2510,37 @@
     <t xml:space="preserve">1.80879497528076</t>
   </si>
   <si>
-    <t xml:space="preserve">1.8364942073822</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.88300776481628</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.89189267158508</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.83022248744965</t>
+    <t xml:space="preserve">1.83649432659149</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.88300812244415</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.89189255237579</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.83022224903107</t>
   </si>
   <si>
     <t xml:space="preserve">1.84119772911072</t>
   </si>
   <si>
-    <t xml:space="preserve">1.92168188095093</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.86419343948364</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.83597123622894</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.81663501262665</t>
+    <t xml:space="preserve">1.92168164253235</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.86419332027435</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.83597135543823</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.81663489341736</t>
   </si>
   <si>
     <t xml:space="preserve">1.82760965824127</t>
   </si>
   <si>
-    <t xml:space="preserve">1.85112774372101</t>
+    <t xml:space="preserve">1.8511278629303</t>
   </si>
   <si>
     <t xml:space="preserve">1.82290577888489</t>
@@ -2552,55 +2552,55 @@
     <t xml:space="preserve">1.8171569108963</t>
   </si>
   <si>
-    <t xml:space="preserve">1.82342863082886</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.83440411090851</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.90129971504211</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.92220449447632</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.96349167823792</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.9922354221344</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.04658818244934</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.09989595413208</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.122891664505</t>
+    <t xml:space="preserve">1.82342851161957</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.8344042301178</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.9012998342514</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.92220413684845</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.96349155902863</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.99223566055298</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.04658794403076</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.0998957157135</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.12289118766785</t>
   </si>
   <si>
     <t xml:space="preserve">2.15111231803894</t>
   </si>
   <si>
-    <t xml:space="preserve">2.11139321327209</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.11034846305847</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.12602686882019</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.12654948234558</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.08630776405334</t>
+    <t xml:space="preserve">2.11139345169067</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.11034893989563</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.12602663040161</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.12654972076416</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.08630752563477</t>
   </si>
   <si>
     <t xml:space="preserve">2.0941469669342</t>
   </si>
   <si>
-    <t xml:space="preserve">2.09048867225647</t>
+    <t xml:space="preserve">2.09048843383789</t>
   </si>
   <si>
     <t xml:space="preserve">2.15790700912476</t>
@@ -2609,13 +2609,13 @@
     <t xml:space="preserve">2.18299269676208</t>
   </si>
   <si>
-    <t xml:space="preserve">2.1976261138916</t>
+    <t xml:space="preserve">2.19762635231018</t>
   </si>
   <si>
     <t xml:space="preserve">2.22950625419617</t>
   </si>
   <si>
-    <t xml:space="preserve">2.20494270324707</t>
+    <t xml:space="preserve">2.20494246482849</t>
   </si>
   <si>
     <t xml:space="preserve">2.24152636528015</t>
@@ -2624,49 +2624,49 @@
     <t xml:space="preserve">2.25772738456726</t>
   </si>
   <si>
-    <t xml:space="preserve">2.27288365364075</t>
+    <t xml:space="preserve">2.27288389205933</t>
   </si>
   <si>
     <t xml:space="preserve">2.26504445075989</t>
   </si>
   <si>
-    <t xml:space="preserve">2.28176856040955</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.30946731567383</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.3763632774353</t>
+    <t xml:space="preserve">2.28176832199097</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.30946707725525</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.37636280059814</t>
   </si>
   <si>
     <t xml:space="preserve">2.40824341773987</t>
   </si>
   <si>
-    <t xml:space="preserve">2.39465498924255</t>
+    <t xml:space="preserve">2.39465475082397</t>
   </si>
   <si>
     <t xml:space="preserve">2.33716678619385</t>
   </si>
   <si>
-    <t xml:space="preserve">2.35023212432861</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.34448289871216</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.32357835769653</t>
+    <t xml:space="preserve">2.35023188591003</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.34448313713074</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.32357811927795</t>
   </si>
   <si>
     <t xml:space="preserve">2.29326558113098</t>
   </si>
   <si>
-    <t xml:space="preserve">2.29692459106445</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.2498881816864</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.26661205291748</t>
+    <t xml:space="preserve">2.29692482948303</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.24988794326782</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.2666118144989</t>
   </si>
   <si>
     <t xml:space="preserve">2.29431104660034</t>
@@ -2684,10 +2684,10 @@
     <t xml:space="preserve">2.32566833496094</t>
   </si>
   <si>
-    <t xml:space="preserve">2.32253289222717</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.35336756706238</t>
+    <t xml:space="preserve">2.32253265380859</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.35336780548096</t>
   </si>
   <si>
     <t xml:space="preserve">2.33612132072449</t>
@@ -2696,22 +2696,22 @@
     <t xml:space="preserve">2.36538767814636</t>
   </si>
   <si>
-    <t xml:space="preserve">2.3831570148468</t>
+    <t xml:space="preserve">2.38315677642822</t>
   </si>
   <si>
     <t xml:space="preserve">2.36016130447388</t>
   </si>
   <si>
-    <t xml:space="preserve">2.35702586174011</t>
+    <t xml:space="preserve">2.35702562332153</t>
   </si>
   <si>
     <t xml:space="preserve">2.32775902748108</t>
   </si>
   <si>
-    <t xml:space="preserve">2.34291481971741</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.40144848823547</t>
+    <t xml:space="preserve">2.34291458129883</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.40144872665405</t>
   </si>
   <si>
     <t xml:space="preserve">2.39988112449646</t>
@@ -2720,7 +2720,7 @@
     <t xml:space="preserve">2.350754737854</t>
   </si>
   <si>
-    <t xml:space="preserve">2.35754871368408</t>
+    <t xml:space="preserve">2.3575484752655</t>
   </si>
   <si>
     <t xml:space="preserve">2.38002133369446</t>
@@ -2732,7 +2732,7 @@
     <t xml:space="preserve">2.4145143032074</t>
   </si>
   <si>
-    <t xml:space="preserve">2.40406203269958</t>
+    <t xml:space="preserve">2.40406227111816</t>
   </si>
   <si>
     <t xml:space="preserve">2.41190147399902</t>
@@ -2744,22 +2744,22 @@
     <t xml:space="preserve">2.38420224189758</t>
   </si>
   <si>
-    <t xml:space="preserve">2.40301704406738</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.38838315010071</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.41869497299194</t>
+    <t xml:space="preserve">2.4030168056488</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.38838338851929</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.4186954498291</t>
   </si>
   <si>
     <t xml:space="preserve">2.33037209510803</t>
   </si>
   <si>
-    <t xml:space="preserve">2.330894947052</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.31626129150391</t>
+    <t xml:space="preserve">2.33089470863342</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.31626105308533</t>
   </si>
   <si>
     <t xml:space="preserve">2.36329746246338</t>
@@ -2768,19 +2768,19 @@
     <t xml:space="preserve">2.34239220619202</t>
   </si>
   <si>
-    <t xml:space="preserve">2.26086354255676</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.16888189315796</t>
+    <t xml:space="preserve">2.26086378097534</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.16888165473938</t>
   </si>
   <si>
     <t xml:space="preserve">2.21330451965332</t>
   </si>
   <si>
-    <t xml:space="preserve">2.26295375823975</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.28751730918884</t>
+    <t xml:space="preserve">2.26295351982117</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.28751754760742</t>
   </si>
   <si>
     <t xml:space="preserve">2.26608991622925</t>
@@ -2789,7 +2789,7 @@
     <t xml:space="preserve">2.27497434616089</t>
   </si>
   <si>
-    <t xml:space="preserve">2.28542637825012</t>
+    <t xml:space="preserve">2.2854266166687</t>
   </si>
   <si>
     <t xml:space="preserve">2.36956858634949</t>
@@ -2798,22 +2798,22 @@
     <t xml:space="preserve">2.34918665885925</t>
   </si>
   <si>
-    <t xml:space="preserve">2.42705702781677</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.16417813301086</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.15686178207397</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.1918773651123</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.12811779975891</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.00477814674377</t>
+    <t xml:space="preserve">2.42705678939819</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.16417789459229</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.1568615436554</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.19187688827515</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.12811803817749</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.00477838516235</t>
   </si>
   <si>
     <t xml:space="preserve">2.0068690776825</t>
@@ -2822,25 +2822,25 @@
     <t xml:space="preserve">2.05129218101501</t>
   </si>
   <si>
-    <t xml:space="preserve">1.97446620464325</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.88091695308685</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.73771834373474</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.69277250766754</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.63110363483429</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.59661066532135</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.37972247600555</t>
+    <t xml:space="preserve">1.97446644306183</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.88091683387756</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.73771822452545</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.69277262687683</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.631103515625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.59661054611206</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.37972259521484</t>
   </si>
   <si>
     <t xml:space="preserve">1.31282699108124</t>
@@ -2849,7 +2849,7 @@
     <t xml:space="preserve">1.31596255302429</t>
   </si>
   <si>
-    <t xml:space="preserve">1.08235001564026</t>
+    <t xml:space="preserve">1.08234989643097</t>
   </si>
   <si>
     <t xml:space="preserve">1.32484698295593</t>
@@ -2861,76 +2861,76 @@
     <t xml:space="preserve">1.21927750110626</t>
   </si>
   <si>
-    <t xml:space="preserve">1.18687498569489</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.20516669750214</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.34575188159943</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.53441846370697</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.57256972789764</t>
+    <t xml:space="preserve">1.18687474727631</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.20516657829285</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.34575164318085</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.53441858291626</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.57256984710693</t>
   </si>
   <si>
     <t xml:space="preserve">1.548006772995</t>
   </si>
   <si>
-    <t xml:space="preserve">1.51769495010376</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.41996467113495</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.41944193840027</t>
+    <t xml:space="preserve">1.51769483089447</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.41996455192566</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.41944181919098</t>
   </si>
   <si>
     <t xml:space="preserve">1.46334195137024</t>
   </si>
   <si>
-    <t xml:space="preserve">1.42100930213928</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.40951192378998</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.40271735191345</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.42989385128021</t>
+    <t xml:space="preserve">1.4210090637207</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.40951180458069</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.40271747112274</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.42989373207092</t>
   </si>
   <si>
     <t xml:space="preserve">1.42414546012878</t>
   </si>
   <si>
-    <t xml:space="preserve">1.3541134595871</t>
+    <t xml:space="preserve">1.35411357879639</t>
   </si>
   <si>
     <t xml:space="preserve">1.36717915534973</t>
   </si>
   <si>
-    <t xml:space="preserve">1.30603241920471</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.20987021923065</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.15760815143585</t>
+    <t xml:space="preserve">1.306032538414</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.20987033843994</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.15760827064514</t>
   </si>
   <si>
     <t xml:space="preserve">1.16962838172913</t>
   </si>
   <si>
-    <t xml:space="preserve">1.17067384719849</t>
+    <t xml:space="preserve">1.1706737279892</t>
   </si>
   <si>
     <t xml:space="preserve">1.1199791431427</t>
   </si>
   <si>
-    <t xml:space="preserve">1.11841094493866</t>
+    <t xml:space="preserve">1.11841106414795</t>
   </si>
   <si>
     <t xml:space="preserve">1.15604019165039</t>
@@ -2945,7 +2945,7 @@
     <t xml:space="preserve">1.21091568470001</t>
   </si>
   <si>
-    <t xml:space="preserve">1.23025214672089</t>
+    <t xml:space="preserve">1.23025238513947</t>
   </si>
   <si>
     <t xml:space="preserve">1.17694485187531</t>
@@ -2954,10 +2954,10 @@
     <t xml:space="preserve">1.15185916423798</t>
   </si>
   <si>
-    <t xml:space="preserve">1.14976835250854</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.13618016242981</t>
+    <t xml:space="preserve">1.14976823329926</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.13618004322052</t>
   </si>
   <si>
     <t xml:space="preserve">1.11736631393433</t>
@@ -2969,34 +2969,34 @@
     <t xml:space="preserve">1.09750628471375</t>
   </si>
   <si>
-    <t xml:space="preserve">1.06092262268066</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.05256056785583</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.04890239238739</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.09102880954742</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.03023850917816</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.01237440109253</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.993177235126495</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.993977725505829</t>
+    <t xml:space="preserve">1.06092250347137</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.05256068706512</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.04890251159668</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.09102869033813</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.03023862838745</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.01237452030182</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.99317729473114</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.993977606296539</t>
   </si>
   <si>
     <t xml:space="preserve">0.996643543243408</t>
   </si>
   <si>
-    <t xml:space="preserve">1.10062730312347</t>
+    <t xml:space="preserve">1.10062718391418</t>
   </si>
   <si>
     <t xml:space="preserve">1.14062082767487</t>
@@ -3008,28 +3008,28 @@
     <t xml:space="preserve">1.14488756656647</t>
   </si>
   <si>
-    <t xml:space="preserve">1.17314922809601</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.19447982311249</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.23287320137024</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.23340666294098</t>
+    <t xml:space="preserve">1.17314910888672</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.1944797039032</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.23287332057953</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.23340654373169</t>
   </si>
   <si>
     <t xml:space="preserve">1.35338830947876</t>
   </si>
   <si>
-    <t xml:space="preserve">1.41897761821747</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.39871442317963</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.32832491397858</t>
+    <t xml:space="preserve">1.41897749900818</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.39871430397034</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.32832503318787</t>
   </si>
   <si>
     <t xml:space="preserve">1.24353873729706</t>
@@ -3038,34 +3038,34 @@
     <t xml:space="preserve">1.21527624130249</t>
   </si>
   <si>
-    <t xml:space="preserve">1.2264746427536</t>
+    <t xml:space="preserve">1.22647476196289</t>
   </si>
   <si>
     <t xml:space="preserve">1.30699527263641</t>
   </si>
   <si>
-    <t xml:space="preserve">1.28086626529694</t>
+    <t xml:space="preserve">1.28086614608765</t>
   </si>
   <si>
     <t xml:space="preserve">1.24567115306854</t>
   </si>
   <si>
-    <t xml:space="preserve">1.25846982002258</t>
+    <t xml:space="preserve">1.25846970081329</t>
   </si>
   <si>
     <t xml:space="preserve">1.20994353294373</t>
   </si>
   <si>
-    <t xml:space="preserve">1.23980593681335</t>
+    <t xml:space="preserve">1.23980605602264</t>
   </si>
   <si>
     <t xml:space="preserve">1.17688179016113</t>
   </si>
   <si>
-    <t xml:space="preserve">1.18594706058502</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.15875148773193</t>
+    <t xml:space="preserve">1.18594694137573</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.15875136852264</t>
   </si>
   <si>
     <t xml:space="preserve">1.17954862117767</t>
@@ -3080,22 +3080,22 @@
     <t xml:space="preserve">1.15981793403625</t>
   </si>
   <si>
-    <t xml:space="preserve">1.19501233100891</t>
+    <t xml:space="preserve">1.1950124502182</t>
   </si>
   <si>
     <t xml:space="preserve">1.18168115615845</t>
   </si>
   <si>
-    <t xml:space="preserve">1.17634928226471</t>
+    <t xml:space="preserve">1.176349401474</t>
   </si>
   <si>
     <t xml:space="preserve">1.14542019367218</t>
   </si>
   <si>
-    <t xml:space="preserve">1.20301175117493</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.32885825634003</t>
+    <t xml:space="preserve">1.20301163196564</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.32885837554932</t>
   </si>
   <si>
     <t xml:space="preserve">1.32992517948151</t>
@@ -3104,10 +3104,10 @@
     <t xml:space="preserve">1.33685696125031</t>
   </si>
   <si>
-    <t xml:space="preserve">1.35445404052734</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.3261923789978</t>
+    <t xml:space="preserve">1.35445415973663</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.32619249820709</t>
   </si>
   <si>
     <t xml:space="preserve">1.3720520734787</t>
@@ -3116,7 +3116,7 @@
     <t xml:space="preserve">1.35925340652466</t>
   </si>
   <si>
-    <t xml:space="preserve">1.31232798099518</t>
+    <t xml:space="preserve">1.31232786178589</t>
   </si>
   <si>
     <t xml:space="preserve">1.29259741306305</t>
@@ -3125,52 +3125,52 @@
     <t xml:space="preserve">1.23873925209045</t>
   </si>
   <si>
-    <t xml:space="preserve">1.24247181415558</t>
+    <t xml:space="preserve">1.24247193336487</t>
   </si>
   <si>
     <t xml:space="preserve">1.20247840881348</t>
   </si>
   <si>
-    <t xml:space="preserve">1.18754708766937</t>
+    <t xml:space="preserve">1.18754696846008</t>
   </si>
   <si>
     <t xml:space="preserve">1.13688826560974</t>
   </si>
   <si>
-    <t xml:space="preserve">1.10755980014801</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.09316194057465</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.1592845916748</t>
+    <t xml:space="preserve">1.1075599193573</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.09316205978394</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.15928471088409</t>
   </si>
   <si>
     <t xml:space="preserve">1.24780452251434</t>
   </si>
   <si>
-    <t xml:space="preserve">1.26380157470703</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.26486825942993</t>
+    <t xml:space="preserve">1.26380169391632</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.26486837863922</t>
   </si>
   <si>
     <t xml:space="preserve">1.23500669002533</t>
   </si>
   <si>
-    <t xml:space="preserve">1.238205909729</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.2494044303894</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.22914087772369</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.21580958366394</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.25260400772095</t>
+    <t xml:space="preserve">1.23820602893829</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.24940466880798</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.2291407585144</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.21580946445465</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.25260388851166</t>
   </si>
   <si>
     <t xml:space="preserve">1.25207042694092</t>
@@ -3179,13 +3179,13 @@
     <t xml:space="preserve">1.24300527572632</t>
   </si>
   <si>
-    <t xml:space="preserve">1.2691342830658</t>
+    <t xml:space="preserve">1.26913416385651</t>
   </si>
   <si>
     <t xml:space="preserve">1.22700726985931</t>
   </si>
   <si>
-    <t xml:space="preserve">1.19394636154175</t>
+    <t xml:space="preserve">1.19394648075104</t>
   </si>
   <si>
     <t xml:space="preserve">1.19074630737305</t>
@@ -3194,22 +3194,22 @@
     <t xml:space="preserve">1.15288615226746</t>
   </si>
   <si>
-    <t xml:space="preserve">1.16408395767212</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.15821886062622</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.12675619125366</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.14222085475922</t>
+    <t xml:space="preserve">1.16408383846283</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.15821874141693</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.12675631046295</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.14222097396851</t>
   </si>
   <si>
     <t xml:space="preserve">1.1715499162674</t>
   </si>
   <si>
-    <t xml:space="preserve">1.16834998130798</t>
+    <t xml:space="preserve">1.16834986209869</t>
   </si>
   <si>
     <t xml:space="preserve">1.16781663894653</t>
@@ -3224,7 +3224,7 @@
     <t xml:space="preserve">1.15181946754456</t>
   </si>
   <si>
-    <t xml:space="preserve">1.10489320755005</t>
+    <t xml:space="preserve">1.10489332675934</t>
   </si>
   <si>
     <t xml:space="preserve">1.07503163814545</t>
@@ -3233,46 +3233,46 @@
     <t xml:space="preserve">1.07716405391693</t>
   </si>
   <si>
-    <t xml:space="preserve">1.04516911506653</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.04250311851501</t>
+    <t xml:space="preserve">1.04516899585724</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.0425032377243</t>
   </si>
   <si>
     <t xml:space="preserve">1.06969892978668</t>
   </si>
   <si>
-    <t xml:space="preserve">1.0398371219635</t>
+    <t xml:space="preserve">1.03983724117279</t>
   </si>
   <si>
     <t xml:space="preserve">1.06010031700134</t>
   </si>
   <si>
-    <t xml:space="preserve">1.03877067565918</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.01050794124603</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.935909509658813</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.974905788898468</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.93394011259079</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.94260573387146</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.947332739830017</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.923304617404938</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.876036584377289</t>
+    <t xml:space="preserve">1.03877055644989</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.01050817966461</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.935909569263458</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.974905669689178</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.933940052986145</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.942605793476105</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.947332620620728</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.923304736614227</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.876036524772644</t>
   </si>
   <si>
     <t xml:space="preserve">0.879581689834595</t>
@@ -3287,7 +3287,7 @@
     <t xml:space="preserve">0.933152258396149</t>
   </si>
   <si>
-    <t xml:space="preserve">1.02414345741272</t>
+    <t xml:space="preserve">1.02414333820343</t>
   </si>
   <si>
     <t xml:space="preserve">0.958755791187286</t>
@@ -3296,7 +3296,7 @@
     <t xml:space="preserve">0.934727787971497</t>
   </si>
   <si>
-    <t xml:space="preserve">0.948120534420013</t>
+    <t xml:space="preserve">0.948120474815369</t>
   </si>
   <si>
     <t xml:space="preserve">0.938666820526123</t>
@@ -3305,7 +3305,7 @@
     <t xml:space="preserve">0.879975557327271</t>
   </si>
   <si>
-    <t xml:space="preserve">0.81655740737915</t>
+    <t xml:space="preserve">0.816557347774506</t>
   </si>
   <si>
     <t xml:space="preserve">0.806315958499908</t>
@@ -3314,28 +3314,28 @@
     <t xml:space="preserve">0.80119526386261</t>
   </si>
   <si>
-    <t xml:space="preserve">0.83113169670105</t>
+    <t xml:space="preserve">0.831131756305695</t>
   </si>
   <si>
     <t xml:space="preserve">0.852402448654175</t>
   </si>
   <si>
-    <t xml:space="preserve">0.872097611427307</t>
+    <t xml:space="preserve">0.872097551822662</t>
   </si>
   <si>
     <t xml:space="preserve">0.853190243244171</t>
   </si>
   <si>
-    <t xml:space="preserve">0.825617134571075</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.948514342308044</t>
+    <t xml:space="preserve">0.82561719417572</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.948514401912689</t>
   </si>
   <si>
     <t xml:space="preserve">0.940636336803436</t>
   </si>
   <si>
-    <t xml:space="preserve">0.976087510585785</t>
+    <t xml:space="preserve">0.97608745098114</t>
   </si>
   <si>
     <t xml:space="preserve">1.03950548171997</t>
@@ -3374,10 +3374,10 @@
     <t xml:space="preserve">1.17067468166351</t>
   </si>
   <si>
-    <t xml:space="preserve">1.15806984901428</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.16870510578156</t>
+    <t xml:space="preserve">1.15806996822357</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.16870534420013</t>
   </si>
   <si>
     <t xml:space="preserve">1.16003942489624</t>
@@ -3386,10 +3386,10 @@
     <t xml:space="preserve">1.15373694896698</t>
   </si>
   <si>
-    <t xml:space="preserve">1.16161489486694</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.19509649276733</t>
+    <t xml:space="preserve">1.16161501407623</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.19509661197662</t>
   </si>
   <si>
     <t xml:space="preserve">1.15570640563965</t>
@@ -3398,16 +3398,16 @@
     <t xml:space="preserve">1.15294921398163</t>
   </si>
   <si>
-    <t xml:space="preserve">1.16397845745087</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.14822232723236</t>
+    <t xml:space="preserve">1.16397857666016</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.14822220802307</t>
   </si>
   <si>
     <t xml:space="preserve">1.15531265735626</t>
   </si>
   <si>
-    <t xml:space="preserve">1.14388930797577</t>
+    <t xml:space="preserve">1.14388942718506</t>
   </si>
   <si>
     <t xml:space="preserve">1.09780299663544</t>
@@ -3416,10 +3416,10 @@
     <t xml:space="preserve">1.12261867523193</t>
   </si>
   <si>
-    <t xml:space="preserve">1.16594779491425</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.18170404434204</t>
+    <t xml:space="preserve">1.16594791412354</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.18170392513275</t>
   </si>
   <si>
     <t xml:space="preserve">1.17343211174011</t>
@@ -3428,43 +3428,43 @@
     <t xml:space="preserve">1.15176737308502</t>
   </si>
   <si>
-    <t xml:space="preserve">1.16122114658356</t>
+    <t xml:space="preserve">1.16122102737427</t>
   </si>
   <si>
     <t xml:space="preserve">1.2230635881424</t>
   </si>
   <si>
-    <t xml:space="preserve">1.29869270324707</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.28411817550659</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.31050968170166</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.31247913837433</t>
+    <t xml:space="preserve">1.29869258403778</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.28411841392517</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.31050956249237</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.31247925758362</t>
   </si>
   <si>
     <t xml:space="preserve">1.29632914066315</t>
   </si>
   <si>
-    <t xml:space="preserve">1.27584648132324</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.26757454872131</t>
+    <t xml:space="preserve">1.27584624290466</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.26757442951202</t>
   </si>
   <si>
     <t xml:space="preserve">1.2955414056778</t>
   </si>
   <si>
-    <t xml:space="preserve">1.27702796459198</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.29908645153046</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.27624034881592</t>
+    <t xml:space="preserve">1.27702808380127</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.29908657073975</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.27624022960663</t>
   </si>
   <si>
     <t xml:space="preserve">1.24118316173553</t>
@@ -3473,16 +3473,16 @@
     <t xml:space="preserve">1.20376253128052</t>
   </si>
   <si>
-    <t xml:space="preserve">1.23724400997162</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.20061123371124</t>
+    <t xml:space="preserve">1.23724412918091</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.20061135292053</t>
   </si>
   <si>
     <t xml:space="preserve">1.22779047489166</t>
   </si>
   <si>
-    <t xml:space="preserve">1.20770132541656</t>
+    <t xml:space="preserve">1.20770144462585</t>
   </si>
   <si>
     <t xml:space="preserve">1.21636736392975</t>
@@ -3494,7 +3494,7 @@
     <t xml:space="preserve">1.40071308612823</t>
   </si>
   <si>
-    <t xml:space="preserve">1.50430917739868</t>
+    <t xml:space="preserve">1.50430905818939</t>
   </si>
   <si>
     <t xml:space="preserve">1.47279703617096</t>
@@ -3503,157 +3503,157 @@
     <t xml:space="preserve">1.4968249797821</t>
   </si>
   <si>
-    <t xml:space="preserve">1.46964573860168</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.46688854694366</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.48343217372894</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.46176779270172</t>
+    <t xml:space="preserve">1.46964585781097</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.46688842773438</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.48343229293823</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.46176767349243</t>
   </si>
   <si>
     <t xml:space="preserve">1.43498241901398</t>
   </si>
   <si>
-    <t xml:space="preserve">1.41016674041748</t>
+    <t xml:space="preserve">1.41016662120819</t>
   </si>
   <si>
     <t xml:space="preserve">1.46610081195831</t>
   </si>
   <si>
-    <t xml:space="preserve">1.44483006000519</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.44443607330322</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.4676765203476</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.42946779727936</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.46728241443634</t>
+    <t xml:space="preserve">1.44483017921448</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.44443619251251</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.46767628192902</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.42946791648865</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.46728217601776</t>
   </si>
   <si>
     <t xml:space="preserve">1.4519202709198</t>
   </si>
   <si>
-    <t xml:space="preserve">1.46058619022369</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.52203476428986</t>
+    <t xml:space="preserve">1.4605860710144</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.52203464508057</t>
   </si>
   <si>
     <t xml:space="preserve">1.56300044059753</t>
   </si>
   <si>
-    <t xml:space="preserve">1.55630421638489</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.5433052778244</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.5519711971283</t>
+    <t xml:space="preserve">1.5563040971756</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.54330551624298</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.55197107791901</t>
   </si>
   <si>
     <t xml:space="preserve">1.53385174274445</t>
   </si>
   <si>
-    <t xml:space="preserve">1.5677273273468</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.61657106876373</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.60475397109985</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.54094195365906</t>
+    <t xml:space="preserve">1.56772720813751</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.61657118797302</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.60475385189056</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.54094183444977</t>
   </si>
   <si>
     <t xml:space="preserve">1.50233960151672</t>
   </si>
   <si>
-    <t xml:space="preserve">1.50076401233673</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.52164077758789</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.51021766662598</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.51100540161133</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.4952495098114</t>
+    <t xml:space="preserve">1.50076389312744</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.5216406583786</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.51021754741669</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.51100528240204</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.49524939060211</t>
   </si>
   <si>
     <t xml:space="preserve">1.49643123149872</t>
   </si>
   <si>
-    <t xml:space="preserve">1.47831177711487</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.49800682067871</t>
+    <t xml:space="preserve">1.47831153869629</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.49800670146942</t>
   </si>
   <si>
     <t xml:space="preserve">1.49603724479675</t>
   </si>
   <si>
-    <t xml:space="preserve">1.48973476886749</t>
+    <t xml:space="preserve">1.48973488807678</t>
   </si>
   <si>
     <t xml:space="preserve">1.46452510356903</t>
   </si>
   <si>
-    <t xml:space="preserve">1.47319102287292</t>
+    <t xml:space="preserve">1.47319090366364</t>
   </si>
   <si>
     <t xml:space="preserve">1.49958229064941</t>
   </si>
   <si>
-    <t xml:space="preserve">1.48264455795288</t>
+    <t xml:space="preserve">1.48264443874359</t>
   </si>
   <si>
     <t xml:space="preserve">1.49131035804749</t>
   </si>
   <si>
-    <t xml:space="preserve">1.49012875556946</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.53700304031372</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.45428359508514</t>
+    <t xml:space="preserve">1.49012863636017</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.53700292110443</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.45428371429443</t>
   </si>
   <si>
     <t xml:space="preserve">1.42198371887207</t>
   </si>
   <si>
-    <t xml:space="preserve">1.42434728145599</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.43143749237061</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.47555434703827</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.4594042301178</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.49209809303284</t>
+    <t xml:space="preserve">1.42434704303741</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.43143737316132</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.47555446624756</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.45940446853638</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.49209821224213</t>
   </si>
   <si>
     <t xml:space="preserve">1.48303854465485</t>
   </si>
   <si>
-    <t xml:space="preserve">1.47673606872559</t>
+    <t xml:space="preserve">1.4767359495163</t>
   </si>
   <si>
     <t xml:space="preserve">1.49367380142212</t>
@@ -3662,16 +3662,16 @@
     <t xml:space="preserve">1.52282249927521</t>
   </si>
   <si>
-    <t xml:space="preserve">1.51533818244934</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.57402968406677</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.58821022510529</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.56457602977753</t>
+    <t xml:space="preserve">1.51533830165863</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.57402956485748</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.588210105896</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.56457591056824</t>
   </si>
   <si>
     <t xml:space="preserve">1.57954430580139</t>
@@ -3683,7 +3683,7 @@
     <t xml:space="preserve">1.58742237091064</t>
   </si>
   <si>
-    <t xml:space="preserve">1.5574859380722</t>
+    <t xml:space="preserve">1.55748581886292</t>
   </si>
   <si>
     <t xml:space="preserve">1.54291152954102</t>
@@ -3692,10 +3692,10 @@
     <t xml:space="preserve">1.57127237319946</t>
   </si>
   <si>
-    <t xml:space="preserve">1.67216491699219</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.70914566516876</t>
+    <t xml:space="preserve">1.67216515541077</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.70914554595947</t>
   </si>
   <si>
     <t xml:space="preserve">1.62714517116547</t>
@@ -3710,19 +3710,19 @@
     <t xml:space="preserve">1.63036108016968</t>
   </si>
   <si>
-    <t xml:space="preserve">1.63518452644348</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.64322352409363</t>
+    <t xml:space="preserve">1.63518440723419</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.64322364330292</t>
   </si>
   <si>
     <t xml:space="preserve">1.63598847389221</t>
   </si>
   <si>
-    <t xml:space="preserve">1.62553751468658</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.64724349975586</t>
+    <t xml:space="preserve">1.62553739547729</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.64724338054657</t>
   </si>
   <si>
     <t xml:space="preserve">1.63679242134094</t>
@@ -3743,34 +3743,34 @@
     <t xml:space="preserve">1.61508643627167</t>
   </si>
   <si>
-    <t xml:space="preserve">1.59257650375366</t>
+    <t xml:space="preserve">1.59257638454437</t>
   </si>
   <si>
     <t xml:space="preserve">1.58091950416565</t>
   </si>
   <si>
-    <t xml:space="preserve">1.54514479637146</t>
+    <t xml:space="preserve">1.54514491558075</t>
   </si>
   <si>
     <t xml:space="preserve">1.56001734733582</t>
   </si>
   <si>
-    <t xml:space="preserve">1.53951716423035</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.51901710033417</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.53589963912964</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.52906608581543</t>
+    <t xml:space="preserve">1.53951728343964</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.51901721954346</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.53589975833893</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.52906620502472</t>
   </si>
   <si>
     <t xml:space="preserve">1.48042893409729</t>
   </si>
   <si>
-    <t xml:space="preserve">1.4683700799942</t>
+    <t xml:space="preserve">1.46836984157562</t>
   </si>
   <si>
     <t xml:space="preserve">1.47560524940491</t>
@@ -3779,7 +3779,7 @@
     <t xml:space="preserve">1.48444843292236</t>
   </si>
   <si>
-    <t xml:space="preserve">1.47399735450745</t>
+    <t xml:space="preserve">1.47399747371674</t>
   </si>
   <si>
     <t xml:space="preserve">1.48565435409546</t>
@@ -3788,10 +3788,10 @@
     <t xml:space="preserve">1.44626200199127</t>
   </si>
   <si>
-    <t xml:space="preserve">1.43339908123016</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.38677155971527</t>
+    <t xml:space="preserve">1.43339920043945</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.38677144050598</t>
   </si>
   <si>
     <t xml:space="preserve">1.41812467575073</t>
@@ -3809,10 +3809,10 @@
     <t xml:space="preserve">1.35863411426544</t>
   </si>
   <si>
-    <t xml:space="preserve">1.31482005119324</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.24809420108795</t>
+    <t xml:space="preserve">1.31482017040253</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.24809432029724</t>
   </si>
   <si>
     <t xml:space="preserve">1.25814342498779</t>
@@ -3821,7 +3821,7 @@
     <t xml:space="preserve">1.27422201633453</t>
   </si>
   <si>
-    <t xml:space="preserve">1.29673194885254</t>
+    <t xml:space="preserve">1.29673182964325</t>
   </si>
   <si>
     <t xml:space="preserve">1.29793775081635</t>
@@ -3830,25 +3830,25 @@
     <t xml:space="preserve">1.31763386726379</t>
   </si>
   <si>
-    <t xml:space="preserve">1.30235946178436</t>
+    <t xml:space="preserve">1.30235934257507</t>
   </si>
   <si>
     <t xml:space="preserve">1.30356526374817</t>
   </si>
   <si>
-    <t xml:space="preserve">1.30718290805817</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.32366347312927</t>
+    <t xml:space="preserve">1.30718278884888</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.32366335391998</t>
   </si>
   <si>
     <t xml:space="preserve">1.32326138019562</t>
   </si>
   <si>
-    <t xml:space="preserve">1.30517303943634</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.31361436843872</t>
+    <t xml:space="preserve">1.30517315864563</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.31361424922943</t>
   </si>
   <si>
     <t xml:space="preserve">1.45349729061127</t>
@@ -3857,13 +3857,13 @@
     <t xml:space="preserve">1.45028162002563</t>
   </si>
   <si>
-    <t xml:space="preserve">1.4446542263031</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.48726224899292</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.476811170578</t>
+    <t xml:space="preserve">1.44465410709381</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.48726212978363</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.47681128978729</t>
   </si>
   <si>
     <t xml:space="preserve">1.46917378902435</t>
@@ -3872,10 +3872,10 @@
     <t xml:space="preserve">1.45108544826508</t>
   </si>
   <si>
-    <t xml:space="preserve">1.42535984516144</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.43500697612762</t>
+    <t xml:space="preserve">1.42535996437073</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.43500709533691</t>
   </si>
   <si>
     <t xml:space="preserve">1.41169321537018</t>
@@ -3887,7 +3887,7 @@
     <t xml:space="preserve">1.43701684474945</t>
   </si>
   <si>
-    <t xml:space="preserve">1.44224238395691</t>
+    <t xml:space="preserve">1.4422425031662</t>
   </si>
   <si>
     <t xml:space="preserve">1.47238957881927</t>
@@ -3896,7 +3896,7 @@
     <t xml:space="preserve">1.4530953168869</t>
   </si>
   <si>
-    <t xml:space="preserve">1.47600722312927</t>
+    <t xml:space="preserve">1.47600734233856</t>
   </si>
   <si>
     <t xml:space="preserve">1.45872282981873</t>
@@ -3917,34 +3917,34 @@
     <t xml:space="preserve">1.46153664588928</t>
   </si>
   <si>
-    <t xml:space="preserve">1.45068347454071</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.46475219726562</t>
+    <t xml:space="preserve">1.45068359375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.46475231647491</t>
   </si>
   <si>
     <t xml:space="preserve">1.45631098747253</t>
   </si>
   <si>
-    <t xml:space="preserve">1.45510506629944</t>
+    <t xml:space="preserve">1.45510518550873</t>
   </si>
   <si>
     <t xml:space="preserve">1.43782079219818</t>
   </si>
   <si>
-    <t xml:space="preserve">1.36104583740234</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.37873220443726</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.41892862319946</t>
+    <t xml:space="preserve">1.36104571819305</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.37873232364655</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.41892850399017</t>
   </si>
   <si>
     <t xml:space="preserve">1.43862462043762</t>
   </si>
   <si>
-    <t xml:space="preserve">1.47439932823181</t>
+    <t xml:space="preserve">1.4743994474411</t>
   </si>
   <si>
     <t xml:space="preserve">1.53107607364655</t>
@@ -3959,19 +3959,19 @@
     <t xml:space="preserve">1.55398797988892</t>
   </si>
   <si>
-    <t xml:space="preserve">1.59137058258057</t>
+    <t xml:space="preserve">1.59137070178986</t>
   </si>
   <si>
     <t xml:space="preserve">1.57810580730438</t>
   </si>
   <si>
-    <t xml:space="preserve">1.63357675075531</t>
+    <t xml:space="preserve">1.63357663154602</t>
   </si>
   <si>
     <t xml:space="preserve">1.61589026451111</t>
   </si>
   <si>
-    <t xml:space="preserve">1.63438057899475</t>
+    <t xml:space="preserve">1.63438045978546</t>
   </si>
   <si>
     <t xml:space="preserve">1.66010618209839</t>
@@ -3989,43 +3989,43 @@
     <t xml:space="preserve">1.65849828720093</t>
   </si>
   <si>
-    <t xml:space="preserve">1.67055726051331</t>
+    <t xml:space="preserve">1.6705573797226</t>
   </si>
   <si>
     <t xml:space="preserve">1.64643955230713</t>
   </si>
   <si>
-    <t xml:space="preserve">1.64563548564911</t>
+    <t xml:space="preserve">1.64563536643982</t>
   </si>
   <si>
     <t xml:space="preserve">1.64965522289276</t>
   </si>
   <si>
-    <t xml:space="preserve">1.60945880413055</t>
+    <t xml:space="preserve">1.60945892333984</t>
   </si>
   <si>
     <t xml:space="preserve">1.62794923782349</t>
   </si>
   <si>
-    <t xml:space="preserve">1.52303695678711</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.51419377326965</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.54152727127075</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.53911530971527</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.52102708816528</t>
+    <t xml:space="preserve">1.52303683757782</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.51419365406036</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.54152715206146</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.53911542892456</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.5210268497467</t>
   </si>
   <si>
     <t xml:space="preserve">1.54715466499329</t>
   </si>
   <si>
-    <t xml:space="preserve">1.54273307323456</t>
+    <t xml:space="preserve">1.54273295402527</t>
   </si>
   <si>
     <t xml:space="preserve">1.5350958108902</t>
@@ -4034,7 +4034,7 @@
     <t xml:space="preserve">1.54635059833527</t>
   </si>
   <si>
-    <t xml:space="preserve">1.536301612854</t>
+    <t xml:space="preserve">1.53630149364471</t>
   </si>
   <si>
     <t xml:space="preserve">1.54836046695709</t>
@@ -4046,22 +4046,22 @@
     <t xml:space="preserve">1.48485040664673</t>
   </si>
   <si>
-    <t xml:space="preserve">1.44425201416016</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.44987976551056</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.44304621219635</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.4257618188858</t>
+    <t xml:space="preserve">1.44425213336945</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.44987964630127</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.44304609298706</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.42576169967651</t>
   </si>
   <si>
     <t xml:space="preserve">1.36426162719727</t>
   </si>
   <si>
-    <t xml:space="preserve">1.35340857505798</t>
+    <t xml:space="preserve">1.35340869426727</t>
   </si>
   <si>
     <t xml:space="preserve">1.35220265388489</t>
@@ -4070,22 +4070,22 @@
     <t xml:space="preserve">1.39119303226471</t>
   </si>
   <si>
-    <t xml:space="preserve">1.37792825698853</t>
+    <t xml:space="preserve">1.37792837619781</t>
   </si>
   <si>
     <t xml:space="preserve">1.36506545543671</t>
   </si>
   <si>
-    <t xml:space="preserve">1.40807545185089</t>
+    <t xml:space="preserve">1.40807557106018</t>
   </si>
   <si>
     <t xml:space="preserve">1.42013430595398</t>
   </si>
   <si>
-    <t xml:space="preserve">1.39561462402344</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.40284991264343</t>
+    <t xml:space="preserve">1.39561450481415</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.40285003185272</t>
   </si>
   <si>
     <t xml:space="preserve">1.39239895343781</t>
@@ -4103,37 +4103,37 @@
     <t xml:space="preserve">1.39280092716217</t>
   </si>
   <si>
-    <t xml:space="preserve">1.42897760868073</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.41651678085327</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.43983066082001</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.45751690864563</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.46877205371857</t>
+    <t xml:space="preserve">1.42897748947144</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.41651666164398</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.43983054161072</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.45751678943634</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.46877193450928</t>
   </si>
   <si>
     <t xml:space="preserve">1.46555614471436</t>
   </si>
   <si>
-    <t xml:space="preserve">1.51539945602417</t>
+    <t xml:space="preserve">1.51539957523346</t>
   </si>
   <si>
     <t xml:space="preserve">1.54434084892273</t>
   </si>
   <si>
-    <t xml:space="preserve">1.54032135009766</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.55157625675201</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.54996824264526</t>
+    <t xml:space="preserve">1.54032123088837</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.55157613754272</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.54996836185455</t>
   </si>
   <si>
     <t xml:space="preserve">1.57730185985565</t>
@@ -4145,10 +4145,10 @@
     <t xml:space="preserve">1.55639970302582</t>
   </si>
   <si>
-    <t xml:space="preserve">1.54192912578583</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.51298773288727</t>
+    <t xml:space="preserve">1.54192900657654</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.51298761367798</t>
   </si>
   <si>
     <t xml:space="preserve">1.44264435768127</t>
@@ -4178,40 +4178,40 @@
     <t xml:space="preserve">1.57328224182129</t>
   </si>
   <si>
-    <t xml:space="preserve">1.63116478919983</t>
+    <t xml:space="preserve">1.63116490840912</t>
   </si>
   <si>
     <t xml:space="preserve">1.62875306606293</t>
   </si>
   <si>
-    <t xml:space="preserve">1.65367472171783</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.59016466140747</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.73567497730255</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.71477293968201</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.62312567234039</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.57569408416748</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.45590901374817</t>
+    <t xml:space="preserve">1.65367460250854</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.59016454219818</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.73567509651184</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.71477317810059</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.62312579154968</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.57569396495819</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.45590913295746</t>
   </si>
   <si>
     <t xml:space="preserve">1.48243868350983</t>
   </si>
   <si>
-    <t xml:space="preserve">1.33572232723236</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.33049666881561</t>
+    <t xml:space="preserve">1.33572208881378</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.3304967880249</t>
   </si>
   <si>
     <t xml:space="preserve">1.26095724105835</t>
@@ -4223,10 +4223,10 @@
     <t xml:space="preserve">1.06922101974487</t>
   </si>
   <si>
-    <t xml:space="preserve">1.12670159339905</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.23925113677979</t>
+    <t xml:space="preserve">1.12670147418976</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.2392510175705</t>
   </si>
   <si>
     <t xml:space="preserve">1.1463977098465</t>
@@ -4235,7 +4235,7 @@
     <t xml:space="preserve">1.13996636867523</t>
   </si>
   <si>
-    <t xml:space="preserve">1.18659389019012</t>
+    <t xml:space="preserve">1.18659400939941</t>
   </si>
   <si>
     <t xml:space="preserve">1.21071183681488</t>
@@ -4244,7 +4244,7 @@
     <t xml:space="preserve">1.29954552650452</t>
   </si>
   <si>
-    <t xml:space="preserve">1.27020227909088</t>
+    <t xml:space="preserve">1.27020239830017</t>
   </si>
   <si>
     <t xml:space="preserve">1.26216304302216</t>
@@ -4256,28 +4256,28 @@
     <t xml:space="preserve">1.2593492269516</t>
   </si>
   <si>
-    <t xml:space="preserve">1.24688839912415</t>
+    <t xml:space="preserve">1.24688851833344</t>
   </si>
   <si>
     <t xml:space="preserve">1.25532960891724</t>
   </si>
   <si>
-    <t xml:space="preserve">1.27140831947327</t>
+    <t xml:space="preserve">1.27140820026398</t>
   </si>
   <si>
     <t xml:space="preserve">1.34617328643799</t>
   </si>
   <si>
-    <t xml:space="preserve">1.31964361667633</t>
+    <t xml:space="preserve">1.31964373588562</t>
   </si>
   <si>
     <t xml:space="preserve">1.27783954143524</t>
   </si>
   <si>
-    <t xml:space="preserve">1.29190838336945</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.23643732070923</t>
+    <t xml:space="preserve">1.29190826416016</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.23643743991852</t>
   </si>
   <si>
     <t xml:space="preserve">1.23844718933105</t>
@@ -4304,13 +4304,13 @@
     <t xml:space="preserve">1.31039845943451</t>
   </si>
   <si>
-    <t xml:space="preserve">1.31924164295197</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.30034935474396</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.2866827249527</t>
+    <t xml:space="preserve">1.31924176216125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.30034947395325</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.28668260574341</t>
   </si>
   <si>
     <t xml:space="preserve">1.27181017398834</t>
@@ -4319,13 +4319,13 @@
     <t xml:space="preserve">1.28105533123016</t>
   </si>
   <si>
-    <t xml:space="preserve">1.27261412143707</t>
+    <t xml:space="preserve">1.27261400222778</t>
   </si>
   <si>
     <t xml:space="preserve">1.29030048847198</t>
   </si>
   <si>
-    <t xml:space="preserve">1.2818591594696</t>
+    <t xml:space="preserve">1.28185904026031</t>
   </si>
   <si>
     <t xml:space="preserve">1.25050616264343</t>
@@ -4337,13 +4337,13 @@
     <t xml:space="preserve">1.23281967639923</t>
   </si>
   <si>
-    <t xml:space="preserve">1.22317266464233</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.36667346954346</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.40003621578217</t>
+    <t xml:space="preserve">1.22317254543304</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.36667335033417</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.40003633499146</t>
   </si>
   <si>
     <t xml:space="preserve">1.40043818950653</t>
@@ -4352,10 +4352,10 @@
     <t xml:space="preserve">1.38757538795471</t>
   </si>
   <si>
-    <t xml:space="preserve">1.41933035850525</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.41249704360962</t>
+    <t xml:space="preserve">1.41933023929596</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.41249716281891</t>
   </si>
   <si>
     <t xml:space="preserve">1.42134034633636</t>
@@ -6849,6 +6849,9 @@
   </si>
   <si>
     <t xml:space="preserve">10.0749998092651</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2049999237061</t>
   </si>
 </sst>
 </file>
@@ -20881,7 +20884,7 @@
         <v>3.13125896453857</v>
       </c>
       <c r="G527" t="s">
-        <v>462</v>
+        <v>322</v>
       </c>
       <c r="H527" t="s">
         <v>9</v>
@@ -20933,7 +20936,7 @@
         <v>3.25851202011108</v>
       </c>
       <c r="G529" t="s">
-        <v>463</v>
+        <v>462</v>
       </c>
       <c r="H529" t="s">
         <v>9</v>
@@ -20959,7 +20962,7 @@
         <v>3.25580501556396</v>
       </c>
       <c r="G530" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
       <c r="H530" t="s">
         <v>9</v>
@@ -20985,7 +20988,7 @@
         <v>3.27949595451355</v>
       </c>
       <c r="G531" t="s">
-        <v>465</v>
+        <v>464</v>
       </c>
       <c r="H531" t="s">
         <v>9</v>
@@ -21011,7 +21014,7 @@
         <v>3.15359592437744</v>
       </c>
       <c r="G532" t="s">
-        <v>466</v>
+        <v>465</v>
       </c>
       <c r="H532" t="s">
         <v>9</v>
@@ -21037,7 +21040,7 @@
         <v>3.17931699752808</v>
       </c>
       <c r="G533" t="s">
-        <v>467</v>
+        <v>466</v>
       </c>
       <c r="H533" t="s">
         <v>9</v>
@@ -21063,7 +21066,7 @@
         <v>3.15494894981384</v>
       </c>
       <c r="G534" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
       <c r="H534" t="s">
         <v>9</v>
@@ -21089,7 +21092,7 @@
         <v>3.15494894981384</v>
       </c>
       <c r="G535" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
       <c r="H535" t="s">
         <v>9</v>
@@ -21115,7 +21118,7 @@
         <v>3.06898498535156</v>
       </c>
       <c r="G536" t="s">
-        <v>469</v>
+        <v>468</v>
       </c>
       <c r="H536" t="s">
         <v>9</v>
@@ -21141,7 +21144,7 @@
         <v>3.08049201965332</v>
       </c>
       <c r="G537" t="s">
-        <v>470</v>
+        <v>469</v>
       </c>
       <c r="H537" t="s">
         <v>9</v>
@@ -21167,7 +21170,7 @@
         <v>3.18811702728271</v>
       </c>
       <c r="G538" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="H538" t="s">
         <v>9</v>
@@ -21245,7 +21248,7 @@
         <v>3.11907505989075</v>
       </c>
       <c r="G541" t="s">
-        <v>472</v>
+        <v>471</v>
       </c>
       <c r="H541" t="s">
         <v>9</v>
@@ -21271,7 +21274,7 @@
         <v>3.0777850151062</v>
       </c>
       <c r="G542" t="s">
-        <v>473</v>
+        <v>472</v>
       </c>
       <c r="H542" t="s">
         <v>9</v>
@@ -21297,7 +21300,7 @@
         <v>3.23752903938293</v>
       </c>
       <c r="G543" t="s">
-        <v>474</v>
+        <v>473</v>
       </c>
       <c r="H543" t="s">
         <v>9</v>
@@ -21323,7 +21326,7 @@
         <v>3.24362111091614</v>
       </c>
       <c r="G544" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="H544" t="s">
         <v>9</v>
@@ -21375,7 +21378,7 @@
         <v>3.23008298873901</v>
       </c>
       <c r="G546" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="H546" t="s">
         <v>9</v>
@@ -21427,7 +21430,7 @@
         <v>3.23549795150757</v>
       </c>
       <c r="G548" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="H548" t="s">
         <v>9</v>
@@ -21453,7 +21456,7 @@
         <v>3.1711950302124</v>
       </c>
       <c r="G549" t="s">
-        <v>478</v>
+        <v>477</v>
       </c>
       <c r="H549" t="s">
         <v>9</v>
@@ -21479,7 +21482,7 @@
         <v>3.29168009757996</v>
       </c>
       <c r="G550" t="s">
-        <v>479</v>
+        <v>478</v>
       </c>
       <c r="H550" t="s">
         <v>9</v>
@@ -21505,7 +21508,7 @@
         <v>3.29235696792603</v>
       </c>
       <c r="G551" t="s">
-        <v>480</v>
+        <v>479</v>
       </c>
       <c r="H551" t="s">
         <v>9</v>
@@ -21531,7 +21534,7 @@
         <v>3.29844903945923</v>
       </c>
       <c r="G552" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
       <c r="H552" t="s">
         <v>9</v>
@@ -21557,7 +21560,7 @@
         <v>3.29506397247314</v>
       </c>
       <c r="G553" t="s">
-        <v>482</v>
+        <v>481</v>
       </c>
       <c r="H553" t="s">
         <v>9</v>
@@ -21583,7 +21586,7 @@
         <v>3.33432292938232</v>
       </c>
       <c r="G554" t="s">
-        <v>483</v>
+        <v>482</v>
       </c>
       <c r="H554" t="s">
         <v>9</v>
@@ -21609,7 +21612,7 @@
         <v>3.3065710067749</v>
       </c>
       <c r="G555" t="s">
-        <v>484</v>
+        <v>483</v>
       </c>
       <c r="H555" t="s">
         <v>9</v>
@@ -21635,7 +21638,7 @@
         <v>3.05477094650269</v>
       </c>
       <c r="G556" t="s">
-        <v>485</v>
+        <v>484</v>
       </c>
       <c r="H556" t="s">
         <v>9</v>
@@ -21687,7 +21690,7 @@
         <v>3.17999410629272</v>
       </c>
       <c r="G558" t="s">
-        <v>486</v>
+        <v>485</v>
       </c>
       <c r="H558" t="s">
         <v>9</v>
@@ -21713,7 +21716,7 @@
         <v>3.22331500053406</v>
       </c>
       <c r="G559" t="s">
-        <v>487</v>
+        <v>486</v>
       </c>
       <c r="H559" t="s">
         <v>9</v>
@@ -21739,7 +21742,7 @@
         <v>3.15359592437744</v>
       </c>
       <c r="G560" t="s">
-        <v>466</v>
+        <v>465</v>
       </c>
       <c r="H560" t="s">
         <v>9</v>
@@ -21765,7 +21768,7 @@
         <v>3.12245893478394</v>
       </c>
       <c r="G561" t="s">
-        <v>488</v>
+        <v>487</v>
       </c>
       <c r="H561" t="s">
         <v>9</v>
@@ -21791,7 +21794,7 @@
         <v>3.18067097663879</v>
       </c>
       <c r="G562" t="s">
-        <v>489</v>
+        <v>488</v>
       </c>
       <c r="H562" t="s">
         <v>9</v>
@@ -21817,7 +21820,7 @@
         <v>3.10892105102539</v>
       </c>
       <c r="G563" t="s">
-        <v>490</v>
+        <v>489</v>
       </c>
       <c r="H563" t="s">
         <v>9</v>
@@ -21843,7 +21846,7 @@
         <v>3.11501288414001</v>
       </c>
       <c r="G564" t="s">
-        <v>491</v>
+        <v>490</v>
       </c>
       <c r="H564" t="s">
         <v>9</v>
@@ -21895,7 +21898,7 @@
         <v>3.15156507492065</v>
       </c>
       <c r="G566" t="s">
-        <v>492</v>
+        <v>491</v>
       </c>
       <c r="H566" t="s">
         <v>9</v>
@@ -21921,7 +21924,7 @@
         <v>3.16239500045776</v>
       </c>
       <c r="G567" t="s">
-        <v>493</v>
+        <v>492</v>
       </c>
       <c r="H567" t="s">
         <v>9</v>
@@ -21947,7 +21950,7 @@
         <v>3.14073491096497</v>
       </c>
       <c r="G568" t="s">
-        <v>494</v>
+        <v>493</v>
       </c>
       <c r="H568" t="s">
         <v>9</v>
@@ -21973,7 +21976,7 @@
         <v>3.07981491088867</v>
       </c>
       <c r="G569" t="s">
-        <v>495</v>
+        <v>494</v>
       </c>
       <c r="H569" t="s">
         <v>9</v>
@@ -21999,7 +22002,7 @@
         <v>3.08861494064331</v>
       </c>
       <c r="G570" t="s">
-        <v>496</v>
+        <v>495</v>
       </c>
       <c r="H570" t="s">
         <v>9</v>
@@ -22025,7 +22028,7 @@
         <v>3.06153988838196</v>
       </c>
       <c r="G571" t="s">
-        <v>497</v>
+        <v>496</v>
       </c>
       <c r="H571" t="s">
         <v>9</v>
@@ -22051,7 +22054,7 @@
         <v>3.08252310752869</v>
       </c>
       <c r="G572" t="s">
-        <v>498</v>
+        <v>497</v>
       </c>
       <c r="H572" t="s">
         <v>9</v>
@@ -22129,7 +22132,7 @@
         <v>3.05680108070374</v>
       </c>
       <c r="G575" t="s">
-        <v>499</v>
+        <v>498</v>
       </c>
       <c r="H575" t="s">
         <v>9</v>
@@ -22155,7 +22158,7 @@
         <v>3.05950903892517</v>
       </c>
       <c r="G576" t="s">
-        <v>500</v>
+        <v>499</v>
       </c>
       <c r="H576" t="s">
         <v>9</v>
@@ -22181,7 +22184,7 @@
         <v>3.17796301841736</v>
       </c>
       <c r="G577" t="s">
-        <v>501</v>
+        <v>500</v>
       </c>
       <c r="H577" t="s">
         <v>9</v>
@@ -22233,7 +22236,7 @@
         <v>3.17999410629272</v>
       </c>
       <c r="G579" t="s">
-        <v>486</v>
+        <v>485</v>
       </c>
       <c r="H579" t="s">
         <v>9</v>
@@ -22259,7 +22262,7 @@
         <v>3.18947005271912</v>
       </c>
       <c r="G580" t="s">
-        <v>502</v>
+        <v>501</v>
       </c>
       <c r="H580" t="s">
         <v>9</v>
@@ -22337,7 +22340,7 @@
         <v>3.20165395736694</v>
       </c>
       <c r="G583" t="s">
-        <v>503</v>
+        <v>502</v>
       </c>
       <c r="H583" t="s">
         <v>9</v>
@@ -22363,7 +22366,7 @@
         <v>3.23414492607117</v>
       </c>
       <c r="G584" t="s">
-        <v>504</v>
+        <v>503</v>
       </c>
       <c r="H584" t="s">
         <v>9</v>
@@ -22389,7 +22392,7 @@
         <v>3.30318689346313</v>
       </c>
       <c r="G585" t="s">
-        <v>505</v>
+        <v>504</v>
       </c>
       <c r="H585" t="s">
         <v>9</v>
@@ -22415,7 +22418,7 @@
         <v>3.26392793655396</v>
       </c>
       <c r="G586" t="s">
-        <v>506</v>
+        <v>505</v>
       </c>
       <c r="H586" t="s">
         <v>9</v>
@@ -22441,7 +22444,7 @@
         <v>3.27272701263428</v>
       </c>
       <c r="G587" t="s">
-        <v>507</v>
+        <v>506</v>
       </c>
       <c r="H587" t="s">
         <v>9</v>
@@ -22467,7 +22470,7 @@
         <v>3.30792498588562</v>
       </c>
       <c r="G588" t="s">
-        <v>508</v>
+        <v>507</v>
       </c>
       <c r="H588" t="s">
         <v>9</v>
@@ -22493,7 +22496,7 @@
         <v>3.30792498588562</v>
       </c>
       <c r="G589" t="s">
-        <v>508</v>
+        <v>507</v>
       </c>
       <c r="H589" t="s">
         <v>9</v>
@@ -22519,7 +22522,7 @@
         <v>3.24768209457397</v>
       </c>
       <c r="G590" t="s">
-        <v>509</v>
+        <v>508</v>
       </c>
       <c r="H590" t="s">
         <v>9</v>
@@ -22545,7 +22548,7 @@
         <v>3.2070689201355</v>
       </c>
       <c r="G591" t="s">
-        <v>510</v>
+        <v>509</v>
       </c>
       <c r="H591" t="s">
         <v>9</v>
@@ -22571,7 +22574,7 @@
         <v>3.22737598419189</v>
       </c>
       <c r="G592" t="s">
-        <v>511</v>
+        <v>510</v>
       </c>
       <c r="H592" t="s">
         <v>9</v>
@@ -22597,7 +22600,7 @@
         <v>3.2118079662323</v>
       </c>
       <c r="G593" t="s">
-        <v>512</v>
+        <v>511</v>
       </c>
       <c r="H593" t="s">
         <v>9</v>
@@ -22623,7 +22626,7 @@
         <v>3.24362111091614</v>
       </c>
       <c r="G594" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="H594" t="s">
         <v>9</v>
@@ -22649,7 +22652,7 @@
         <v>3.22805309295654</v>
       </c>
       <c r="G595" t="s">
-        <v>513</v>
+        <v>512</v>
       </c>
       <c r="H595" t="s">
         <v>9</v>
@@ -22701,7 +22704,7 @@
         <v>3.20368504524231</v>
       </c>
       <c r="G597" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="H597" t="s">
         <v>9</v>
@@ -22727,7 +22730,7 @@
         <v>3.19353199005127</v>
       </c>
       <c r="G598" t="s">
-        <v>515</v>
+        <v>514</v>
       </c>
       <c r="H598" t="s">
         <v>9</v>
@@ -22779,7 +22782,7 @@
         <v>3.31943202018738</v>
       </c>
       <c r="G600" t="s">
-        <v>516</v>
+        <v>515</v>
       </c>
       <c r="H600" t="s">
         <v>9</v>
@@ -22805,7 +22808,7 @@
         <v>3.33161592483521</v>
       </c>
       <c r="G601" t="s">
-        <v>517</v>
+        <v>516</v>
       </c>
       <c r="H601" t="s">
         <v>9</v>
@@ -22831,7 +22834,7 @@
         <v>3.39659690856934</v>
       </c>
       <c r="G602" t="s">
-        <v>518</v>
+        <v>517</v>
       </c>
       <c r="H602" t="s">
         <v>9</v>
@@ -22857,7 +22860,7 @@
         <v>3.44533205032349</v>
       </c>
       <c r="G603" t="s">
-        <v>519</v>
+        <v>518</v>
       </c>
       <c r="H603" t="s">
         <v>9</v>
@@ -22883,7 +22886,7 @@
         <v>3.48459100723267</v>
       </c>
       <c r="G604" t="s">
-        <v>520</v>
+        <v>519</v>
       </c>
       <c r="H604" t="s">
         <v>9</v>
@@ -22909,7 +22912,7 @@
         <v>3.38238191604614</v>
       </c>
       <c r="G605" t="s">
-        <v>521</v>
+        <v>520</v>
       </c>
       <c r="H605" t="s">
         <v>9</v>
@@ -22935,7 +22938,7 @@
         <v>3.38305902481079</v>
       </c>
       <c r="G606" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="H606" t="s">
         <v>9</v>
@@ -22961,7 +22964,7 @@
         <v>3.15833401679993</v>
       </c>
       <c r="G607" t="s">
-        <v>523</v>
+        <v>522</v>
       </c>
       <c r="H607" t="s">
         <v>9</v>
@@ -22987,7 +22990,7 @@
         <v>3.11230611801147</v>
       </c>
       <c r="G608" t="s">
-        <v>524</v>
+        <v>523</v>
       </c>
       <c r="H608" t="s">
         <v>9</v>
@@ -23013,7 +23016,7 @@
         <v>3.16239500045776</v>
       </c>
       <c r="G609" t="s">
-        <v>525</v>
+        <v>524</v>
       </c>
       <c r="H609" t="s">
         <v>9</v>
@@ -23039,7 +23042,7 @@
         <v>3.19691610336304</v>
       </c>
       <c r="G610" t="s">
-        <v>526</v>
+        <v>525</v>
       </c>
       <c r="H610" t="s">
         <v>9</v>
@@ -23065,7 +23068,7 @@
         <v>3.15765690803528</v>
       </c>
       <c r="G611" t="s">
-        <v>527</v>
+        <v>526</v>
       </c>
       <c r="H611" t="s">
         <v>9</v>
@@ -23091,7 +23094,7 @@
         <v>3.09402990341187</v>
       </c>
       <c r="G612" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="H612" t="s">
         <v>9</v>
@@ -23117,7 +23120,7 @@
         <v>2.91330194473267</v>
       </c>
       <c r="G613" t="s">
-        <v>529</v>
+        <v>528</v>
       </c>
       <c r="H613" t="s">
         <v>9</v>
@@ -23143,7 +23146,7 @@
         <v>2.76641893386841</v>
       </c>
       <c r="G614" t="s">
-        <v>530</v>
+        <v>529</v>
       </c>
       <c r="H614" t="s">
         <v>9</v>
@@ -23169,7 +23172,7 @@
         <v>2.77657198905945</v>
       </c>
       <c r="G615" t="s">
-        <v>531</v>
+        <v>530</v>
       </c>
       <c r="H615" t="s">
         <v>9</v>
@@ -23195,7 +23198,7 @@
         <v>2.7772490978241</v>
       </c>
       <c r="G616" t="s">
-        <v>532</v>
+        <v>531</v>
       </c>
       <c r="H616" t="s">
         <v>9</v>
@@ -23221,7 +23224,7 @@
         <v>2.99588203430176</v>
       </c>
       <c r="G617" t="s">
-        <v>533</v>
+        <v>532</v>
       </c>
       <c r="H617" t="s">
         <v>9</v>
@@ -23247,7 +23250,7 @@
         <v>2.90788698196411</v>
       </c>
       <c r="G618" t="s">
-        <v>534</v>
+        <v>533</v>
       </c>
       <c r="H618" t="s">
         <v>9</v>
@@ -23273,7 +23276,7 @@
         <v>2.80906200408936</v>
       </c>
       <c r="G619" t="s">
-        <v>535</v>
+        <v>534</v>
       </c>
       <c r="H619" t="s">
         <v>9</v>
@@ -23299,7 +23302,7 @@
         <v>2.80770897865295</v>
       </c>
       <c r="G620" t="s">
-        <v>536</v>
+        <v>535</v>
       </c>
       <c r="H620" t="s">
         <v>9</v>
@@ -23325,7 +23328,7 @@
         <v>2.86185908317566</v>
       </c>
       <c r="G621" t="s">
-        <v>537</v>
+        <v>536</v>
       </c>
       <c r="H621" t="s">
         <v>9</v>
@@ -23351,7 +23354,7 @@
         <v>2.78469491004944</v>
       </c>
       <c r="G622" t="s">
-        <v>538</v>
+        <v>537</v>
       </c>
       <c r="H622" t="s">
         <v>9</v>
@@ -23377,7 +23380,7 @@
         <v>2.90585708618164</v>
       </c>
       <c r="G623" t="s">
-        <v>539</v>
+        <v>538</v>
       </c>
       <c r="H623" t="s">
         <v>9</v>
@@ -23403,7 +23406,7 @@
         <v>2.94037795066833</v>
       </c>
       <c r="G624" t="s">
-        <v>540</v>
+        <v>539</v>
       </c>
       <c r="H624" t="s">
         <v>9</v>
@@ -23429,7 +23432,7 @@
         <v>2.98775911331177</v>
       </c>
       <c r="G625" t="s">
-        <v>541</v>
+        <v>540</v>
       </c>
       <c r="H625" t="s">
         <v>9</v>
@@ -23455,7 +23458,7 @@
         <v>3.02431106567383</v>
       </c>
       <c r="G626" t="s">
-        <v>542</v>
+        <v>541</v>
       </c>
       <c r="H626" t="s">
         <v>9</v>
@@ -23481,7 +23484,7 @@
         <v>2.94511604309082</v>
       </c>
       <c r="G627" t="s">
-        <v>543</v>
+        <v>542</v>
       </c>
       <c r="H627" t="s">
         <v>9</v>
@@ -23507,7 +23510,7 @@
         <v>2.93090105056763</v>
       </c>
       <c r="G628" t="s">
-        <v>544</v>
+        <v>543</v>
       </c>
       <c r="H628" t="s">
         <v>9</v>
@@ -23533,7 +23536,7 @@
         <v>3.03040289878845</v>
       </c>
       <c r="G629" t="s">
-        <v>545</v>
+        <v>544</v>
       </c>
       <c r="H629" t="s">
         <v>9</v>
@@ -23559,7 +23562,7 @@
         <v>3.10689091682434</v>
       </c>
       <c r="G630" t="s">
-        <v>546</v>
+        <v>545</v>
       </c>
       <c r="H630" t="s">
         <v>9</v>
@@ -23585,7 +23588,7 @@
         <v>3.01551198959351</v>
       </c>
       <c r="G631" t="s">
-        <v>547</v>
+        <v>546</v>
       </c>
       <c r="H631" t="s">
         <v>9</v>
@@ -23611,7 +23614,7 @@
         <v>3.23752903938293</v>
       </c>
       <c r="G632" t="s">
-        <v>548</v>
+        <v>547</v>
       </c>
       <c r="H632" t="s">
         <v>9</v>
@@ -23637,7 +23640,7 @@
         <v>3.1711950302124</v>
       </c>
       <c r="G633" t="s">
-        <v>549</v>
+        <v>548</v>
       </c>
       <c r="H633" t="s">
         <v>9</v>
@@ -23663,7 +23666,7 @@
         <v>3.18879389762878</v>
       </c>
       <c r="G634" t="s">
-        <v>550</v>
+        <v>549</v>
       </c>
       <c r="H634" t="s">
         <v>9</v>
@@ -23689,7 +23692,7 @@
         <v>3.14344191551208</v>
       </c>
       <c r="G635" t="s">
-        <v>551</v>
+        <v>550</v>
       </c>
       <c r="H635" t="s">
         <v>9</v>
@@ -23715,7 +23718,7 @@
         <v>3.17187190055847</v>
       </c>
       <c r="G636" t="s">
-        <v>552</v>
+        <v>551</v>
       </c>
       <c r="H636" t="s">
         <v>9</v>
@@ -23741,7 +23744,7 @@
         <v>3.18608593940735</v>
       </c>
       <c r="G637" t="s">
-        <v>553</v>
+        <v>552</v>
       </c>
       <c r="H637" t="s">
         <v>9</v>
@@ -23767,7 +23770,7 @@
         <v>3.14344191551208</v>
       </c>
       <c r="G638" t="s">
-        <v>551</v>
+        <v>550</v>
       </c>
       <c r="H638" t="s">
         <v>9</v>
@@ -23793,7 +23796,7 @@
         <v>3.17390203475952</v>
       </c>
       <c r="G639" t="s">
-        <v>554</v>
+        <v>553</v>
       </c>
       <c r="H639" t="s">
         <v>9</v>
@@ -23819,7 +23822,7 @@
         <v>3.17728710174561</v>
       </c>
       <c r="G640" t="s">
-        <v>555</v>
+        <v>554</v>
       </c>
       <c r="H640" t="s">
         <v>9</v>
@@ -23845,7 +23848,7 @@
         <v>3.1651029586792</v>
       </c>
       <c r="G641" t="s">
-        <v>556</v>
+        <v>555</v>
       </c>
       <c r="H641" t="s">
         <v>9</v>
@@ -23871,7 +23874,7 @@
         <v>3.22737598419189</v>
       </c>
       <c r="G642" t="s">
-        <v>557</v>
+        <v>556</v>
       </c>
       <c r="H642" t="s">
         <v>9</v>
@@ -23897,7 +23900,7 @@
         <v>3.238205909729</v>
       </c>
       <c r="G643" t="s">
-        <v>558</v>
+        <v>557</v>
       </c>
       <c r="H643" t="s">
         <v>9</v>
@@ -23923,7 +23926,7 @@
         <v>3.17525601387024</v>
       </c>
       <c r="G644" t="s">
-        <v>559</v>
+        <v>558</v>
       </c>
       <c r="H644" t="s">
         <v>9</v>
@@ -23949,7 +23952,7 @@
         <v>3.12245893478394</v>
       </c>
       <c r="G645" t="s">
-        <v>560</v>
+        <v>559</v>
       </c>
       <c r="H645" t="s">
         <v>9</v>
@@ -23975,7 +23978,7 @@
         <v>3.16239500045776</v>
       </c>
       <c r="G646" t="s">
-        <v>525</v>
+        <v>524</v>
       </c>
       <c r="H646" t="s">
         <v>9</v>
@@ -24001,7 +24004,7 @@
         <v>3.14411902427673</v>
       </c>
       <c r="G647" t="s">
-        <v>561</v>
+        <v>560</v>
       </c>
       <c r="H647" t="s">
         <v>9</v>
@@ -24027,7 +24030,7 @@
         <v>3.1651029586792</v>
       </c>
       <c r="G648" t="s">
-        <v>556</v>
+        <v>555</v>
       </c>
       <c r="H648" t="s">
         <v>9</v>
@@ -24053,7 +24056,7 @@
         <v>3.18743991851807</v>
       </c>
       <c r="G649" t="s">
-        <v>562</v>
+        <v>561</v>
       </c>
       <c r="H649" t="s">
         <v>9</v>
@@ -24079,7 +24082,7 @@
         <v>3.16239500045776</v>
       </c>
       <c r="G650" t="s">
-        <v>525</v>
+        <v>524</v>
       </c>
       <c r="H650" t="s">
         <v>9</v>
@@ -24105,7 +24108,7 @@
         <v>3.13125896453857</v>
       </c>
       <c r="G651" t="s">
-        <v>563</v>
+        <v>562</v>
       </c>
       <c r="H651" t="s">
         <v>9</v>
@@ -24131,7 +24134,7 @@
         <v>3.09402990341187</v>
       </c>
       <c r="G652" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="H652" t="s">
         <v>9</v>
@@ -24157,7 +24160,7 @@
         <v>3.07304692268372</v>
       </c>
       <c r="G653" t="s">
-        <v>564</v>
+        <v>563</v>
       </c>
       <c r="H653" t="s">
         <v>9</v>
@@ -24183,7 +24186,7 @@
         <v>3.13531994819641</v>
       </c>
       <c r="G654" t="s">
-        <v>565</v>
+        <v>564</v>
       </c>
       <c r="H654" t="s">
         <v>9</v>
@@ -24209,7 +24212,7 @@
         <v>3.13193488121033</v>
       </c>
       <c r="G655" t="s">
-        <v>566</v>
+        <v>565</v>
       </c>
       <c r="H655" t="s">
         <v>9</v>
@@ -24235,7 +24238,7 @@
         <v>3.17796301841736</v>
       </c>
       <c r="G656" t="s">
-        <v>567</v>
+        <v>566</v>
       </c>
       <c r="H656" t="s">
         <v>9</v>
@@ -24261,7 +24264,7 @@
         <v>3.22263789176941</v>
       </c>
       <c r="G657" t="s">
-        <v>568</v>
+        <v>567</v>
       </c>
       <c r="H657" t="s">
         <v>9</v>
@@ -24287,7 +24290,7 @@
         <v>3.19082403182983</v>
       </c>
       <c r="G658" t="s">
-        <v>569</v>
+        <v>568</v>
       </c>
       <c r="H658" t="s">
         <v>9</v>
@@ -24313,7 +24316,7 @@
         <v>3.23617506027222</v>
       </c>
       <c r="G659" t="s">
-        <v>570</v>
+        <v>569</v>
       </c>
       <c r="H659" t="s">
         <v>9</v>
@@ -24339,7 +24342,7 @@
         <v>3.22128391265869</v>
       </c>
       <c r="G660" t="s">
-        <v>571</v>
+        <v>570</v>
       </c>
       <c r="H660" t="s">
         <v>9</v>
@@ -24365,7 +24368,7 @@
         <v>3.10621404647827</v>
       </c>
       <c r="G661" t="s">
-        <v>572</v>
+        <v>571</v>
       </c>
       <c r="H661" t="s">
         <v>9</v>
@@ -24391,7 +24394,7 @@
         <v>3.0980908870697</v>
       </c>
       <c r="G662" t="s">
-        <v>573</v>
+        <v>572</v>
       </c>
       <c r="H662" t="s">
         <v>9</v>
@@ -24417,7 +24420,7 @@
         <v>3.10012197494507</v>
       </c>
       <c r="G663" t="s">
-        <v>574</v>
+        <v>573</v>
       </c>
       <c r="H663" t="s">
         <v>9</v>
@@ -24443,7 +24446,7 @@
         <v>3.12719702720642</v>
       </c>
       <c r="G664" t="s">
-        <v>575</v>
+        <v>574</v>
       </c>
       <c r="H664" t="s">
         <v>9</v>
@@ -24469,7 +24472,7 @@
         <v>2.94240808486938</v>
       </c>
       <c r="G665" t="s">
-        <v>576</v>
+        <v>575</v>
       </c>
       <c r="H665" t="s">
         <v>9</v>
@@ -24495,7 +24498,7 @@
         <v>2.90924096107483</v>
       </c>
       <c r="G666" t="s">
-        <v>577</v>
+        <v>576</v>
       </c>
       <c r="H666" t="s">
         <v>9</v>
@@ -24521,7 +24524,7 @@
         <v>2.86862802505493</v>
       </c>
       <c r="G667" t="s">
-        <v>578</v>
+        <v>577</v>
       </c>
       <c r="H667" t="s">
         <v>9</v>
@@ -24547,7 +24550,7 @@
         <v>2.7975549697876</v>
       </c>
       <c r="G668" t="s">
-        <v>579</v>
+        <v>578</v>
       </c>
       <c r="H668" t="s">
         <v>9</v>
@@ -24573,7 +24576,7 @@
         <v>2.77115702629089</v>
       </c>
       <c r="G669" t="s">
-        <v>580</v>
+        <v>579</v>
       </c>
       <c r="H669" t="s">
         <v>9</v>
@@ -24599,7 +24602,7 @@
         <v>2.76777291297913</v>
       </c>
       <c r="G670" t="s">
-        <v>581</v>
+        <v>580</v>
       </c>
       <c r="H670" t="s">
         <v>9</v>
@@ -24625,7 +24628,7 @@
         <v>2.70753002166748</v>
       </c>
       <c r="G671" t="s">
-        <v>582</v>
+        <v>581</v>
       </c>
       <c r="H671" t="s">
         <v>9</v>
@@ -24651,7 +24654,7 @@
         <v>2.70820689201355</v>
       </c>
       <c r="G672" t="s">
-        <v>583</v>
+        <v>582</v>
       </c>
       <c r="H672" t="s">
         <v>9</v>
@@ -24677,7 +24680,7 @@
         <v>2.76844906806946</v>
       </c>
       <c r="G673" t="s">
-        <v>584</v>
+        <v>583</v>
       </c>
       <c r="H673" t="s">
         <v>9</v>
@@ -24703,7 +24706,7 @@
         <v>2.76709604263306</v>
       </c>
       <c r="G674" t="s">
-        <v>585</v>
+        <v>584</v>
       </c>
       <c r="H674" t="s">
         <v>9</v>
@@ -24729,7 +24732,7 @@
         <v>2.74543499946594</v>
       </c>
       <c r="G675" t="s">
-        <v>586</v>
+        <v>585</v>
       </c>
       <c r="H675" t="s">
         <v>9</v>
@@ -24755,7 +24758,7 @@
         <v>2.73866701126099</v>
       </c>
       <c r="G676" t="s">
-        <v>587</v>
+        <v>586</v>
       </c>
       <c r="H676" t="s">
         <v>9</v>
@@ -24781,7 +24784,7 @@
         <v>2.72783708572388</v>
       </c>
       <c r="G677" t="s">
-        <v>588</v>
+        <v>587</v>
       </c>
       <c r="H677" t="s">
         <v>9</v>
@@ -24807,7 +24810,7 @@
         <v>2.6838390827179</v>
       </c>
       <c r="G678" t="s">
-        <v>589</v>
+        <v>588</v>
       </c>
       <c r="H678" t="s">
         <v>9</v>
@@ -24833,7 +24836,7 @@
         <v>2.70076107978821</v>
       </c>
       <c r="G679" t="s">
-        <v>590</v>
+        <v>589</v>
       </c>
       <c r="H679" t="s">
         <v>9</v>
@@ -24859,7 +24862,7 @@
         <v>2.59922909736633</v>
       </c>
       <c r="G680" t="s">
-        <v>591</v>
+        <v>590</v>
       </c>
       <c r="H680" t="s">
         <v>9</v>
@@ -24885,7 +24888,7 @@
         <v>2.57147693634033</v>
       </c>
       <c r="G681" t="s">
-        <v>592</v>
+        <v>591</v>
       </c>
       <c r="H681" t="s">
         <v>9</v>
@@ -24911,7 +24914,7 @@
         <v>2.58366107940674</v>
       </c>
       <c r="G682" t="s">
-        <v>593</v>
+        <v>592</v>
       </c>
       <c r="H682" t="s">
         <v>9</v>
@@ -24937,7 +24940,7 @@
         <v>2.67842388153076</v>
       </c>
       <c r="G683" t="s">
-        <v>594</v>
+        <v>593</v>
       </c>
       <c r="H683" t="s">
         <v>9</v>
@@ -24963,7 +24966,7 @@
         <v>2.79281711578369</v>
       </c>
       <c r="G684" t="s">
-        <v>595</v>
+        <v>594</v>
       </c>
       <c r="H684" t="s">
         <v>9</v>
@@ -24989,7 +24992,7 @@
         <v>2.79823207855225</v>
       </c>
       <c r="G685" t="s">
-        <v>596</v>
+        <v>595</v>
       </c>
       <c r="H685" t="s">
         <v>9</v>
@@ -25015,7 +25018,7 @@
         <v>2.77657198905945</v>
       </c>
       <c r="G686" t="s">
-        <v>531</v>
+        <v>530</v>
       </c>
       <c r="H686" t="s">
         <v>9</v>
@@ -25041,7 +25044,7 @@
         <v>2.87268900871277</v>
       </c>
       <c r="G687" t="s">
-        <v>597</v>
+        <v>596</v>
       </c>
       <c r="H687" t="s">
         <v>9</v>
@@ -25067,7 +25070,7 @@
         <v>2.85847496986389</v>
       </c>
       <c r="G688" t="s">
-        <v>598</v>
+        <v>597</v>
       </c>
       <c r="H688" t="s">
         <v>9</v>
@@ -25093,7 +25096,7 @@
         <v>2.86118197441101</v>
       </c>
       <c r="G689" t="s">
-        <v>599</v>
+        <v>598</v>
       </c>
       <c r="H689" t="s">
         <v>9</v>
@@ -25119,7 +25122,7 @@
         <v>2.85170602798462</v>
       </c>
       <c r="G690" t="s">
-        <v>600</v>
+        <v>599</v>
       </c>
       <c r="H690" t="s">
         <v>9</v>
@@ -25145,7 +25148,7 @@
         <v>2.87268900871277</v>
       </c>
       <c r="G691" t="s">
-        <v>597</v>
+        <v>596</v>
       </c>
       <c r="H691" t="s">
         <v>9</v>
@@ -25171,7 +25174,7 @@
         <v>2.90788698196411</v>
       </c>
       <c r="G692" t="s">
-        <v>534</v>
+        <v>533</v>
       </c>
       <c r="H692" t="s">
         <v>9</v>
@@ -25197,7 +25200,7 @@
         <v>2.91736388206482</v>
       </c>
       <c r="G693" t="s">
-        <v>601</v>
+        <v>600</v>
       </c>
       <c r="H693" t="s">
         <v>9</v>
@@ -25223,7 +25226,7 @@
         <v>2.96136093139648</v>
       </c>
       <c r="G694" t="s">
-        <v>602</v>
+        <v>601</v>
       </c>
       <c r="H694" t="s">
         <v>9</v>
@@ -25249,7 +25252,7 @@
         <v>2.93360900878906</v>
       </c>
       <c r="G695" t="s">
-        <v>603</v>
+        <v>602</v>
       </c>
       <c r="H695" t="s">
         <v>9</v>
@@ -25275,7 +25278,7 @@
         <v>2.87742805480957</v>
       </c>
       <c r="G696" t="s">
-        <v>604</v>
+        <v>603</v>
       </c>
       <c r="H696" t="s">
         <v>9</v>
@@ -25301,7 +25304,7 @@
         <v>2.91059494018555</v>
       </c>
       <c r="G697" t="s">
-        <v>605</v>
+        <v>604</v>
       </c>
       <c r="H697" t="s">
         <v>9</v>
@@ -25327,7 +25330,7 @@
         <v>2.94647002220154</v>
       </c>
       <c r="G698" t="s">
-        <v>606</v>
+        <v>605</v>
       </c>
       <c r="H698" t="s">
         <v>9</v>
@@ -25353,7 +25356,7 @@
         <v>2.97625207901001</v>
       </c>
       <c r="G699" t="s">
-        <v>607</v>
+        <v>606</v>
       </c>
       <c r="H699" t="s">
         <v>9</v>
@@ -25379,7 +25382,7 @@
         <v>2.94511604309082</v>
       </c>
       <c r="G700" t="s">
-        <v>543</v>
+        <v>542</v>
       </c>
       <c r="H700" t="s">
         <v>9</v>
@@ -25405,7 +25408,7 @@
         <v>2.69940710067749</v>
       </c>
       <c r="G701" t="s">
-        <v>608</v>
+        <v>607</v>
       </c>
       <c r="H701" t="s">
         <v>9</v>
@@ -25431,7 +25434,7 @@
         <v>2.59313702583313</v>
       </c>
       <c r="G702" t="s">
-        <v>609</v>
+        <v>608</v>
       </c>
       <c r="H702" t="s">
         <v>9</v>
@@ -25457,7 +25460,7 @@
         <v>2.54778599739075</v>
       </c>
       <c r="G703" t="s">
-        <v>610</v>
+        <v>609</v>
       </c>
       <c r="H703" t="s">
         <v>9</v>
@@ -25483,7 +25486,7 @@
         <v>2.51461791992188</v>
       </c>
       <c r="G704" t="s">
-        <v>611</v>
+        <v>610</v>
       </c>
       <c r="H704" t="s">
         <v>9</v>
@@ -25509,7 +25512,7 @@
         <v>2.53018689155579</v>
       </c>
       <c r="G705" t="s">
-        <v>612</v>
+        <v>611</v>
       </c>
       <c r="H705" t="s">
         <v>9</v>
@@ -25535,7 +25538,7 @@
         <v>2.48415899276733</v>
       </c>
       <c r="G706" t="s">
-        <v>613</v>
+        <v>612</v>
       </c>
       <c r="H706" t="s">
         <v>9</v>
@@ -25561,7 +25564,7 @@
         <v>2.44286894798279</v>
       </c>
       <c r="G707" t="s">
-        <v>614</v>
+        <v>613</v>
       </c>
       <c r="H707" t="s">
         <v>9</v>
@@ -25587,7 +25590,7 @@
         <v>2.3941330909729</v>
       </c>
       <c r="G708" t="s">
-        <v>615</v>
+        <v>614</v>
       </c>
       <c r="H708" t="s">
         <v>9</v>
@@ -25613,7 +25616,7 @@
         <v>2.44625306129456</v>
       </c>
       <c r="G709" t="s">
-        <v>616</v>
+        <v>615</v>
       </c>
       <c r="H709" t="s">
         <v>9</v>
@@ -25639,7 +25642,7 @@
         <v>2.40022492408752</v>
       </c>
       <c r="G710" t="s">
-        <v>617</v>
+        <v>616</v>
       </c>
       <c r="H710" t="s">
         <v>9</v>
@@ -25665,7 +25668,7 @@
         <v>2.41850090026855</v>
       </c>
       <c r="G711" t="s">
-        <v>618</v>
+        <v>617</v>
       </c>
       <c r="H711" t="s">
         <v>9</v>
@@ -25691,7 +25694,7 @@
         <v>2.43542289733887</v>
       </c>
       <c r="G712" t="s">
-        <v>619</v>
+        <v>618</v>
       </c>
       <c r="H712" t="s">
         <v>9</v>
@@ -25717,7 +25720,7 @@
         <v>2.41443991661072</v>
       </c>
       <c r="G713" t="s">
-        <v>620</v>
+        <v>619</v>
       </c>
       <c r="H713" t="s">
         <v>9</v>
@@ -25743,7 +25746,7 @@
         <v>2.41782402992249</v>
       </c>
       <c r="G714" t="s">
-        <v>621</v>
+        <v>620</v>
       </c>
       <c r="H714" t="s">
         <v>9</v>
@@ -25769,7 +25772,7 @@
         <v>2.36570405960083</v>
       </c>
       <c r="G715" t="s">
-        <v>622</v>
+        <v>621</v>
       </c>
       <c r="H715" t="s">
         <v>9</v>
@@ -25795,7 +25798,7 @@
         <v>2.37450408935547</v>
       </c>
       <c r="G716" t="s">
-        <v>623</v>
+        <v>622</v>
       </c>
       <c r="H716" t="s">
         <v>9</v>
@@ -25821,7 +25824,7 @@
         <v>2.28786301612854</v>
       </c>
       <c r="G717" t="s">
-        <v>624</v>
+        <v>623</v>
       </c>
       <c r="H717" t="s">
         <v>9</v>
@@ -25847,7 +25850,7 @@
         <v>2.238450050354</v>
       </c>
       <c r="G718" t="s">
-        <v>625</v>
+        <v>624</v>
       </c>
       <c r="H718" t="s">
         <v>9</v>
@@ -25873,7 +25876,7 @@
         <v>2.17482304573059</v>
       </c>
       <c r="G719" t="s">
-        <v>626</v>
+        <v>625</v>
       </c>
       <c r="H719" t="s">
         <v>9</v>
@@ -25899,7 +25902,7 @@
         <v>2.2249128818512</v>
       </c>
       <c r="G720" t="s">
-        <v>627</v>
+        <v>626</v>
       </c>
       <c r="H720" t="s">
         <v>9</v>
@@ -25925,7 +25928,7 @@
         <v>2.20799088478088</v>
       </c>
       <c r="G721" t="s">
-        <v>628</v>
+        <v>627</v>
       </c>
       <c r="H721" t="s">
         <v>9</v>
@@ -25951,7 +25954,7 @@
         <v>2.30546188354492</v>
       </c>
       <c r="G722" t="s">
-        <v>629</v>
+        <v>628</v>
       </c>
       <c r="H722" t="s">
         <v>9</v>
@@ -25977,7 +25980,7 @@
         <v>2.29192399978638</v>
       </c>
       <c r="G723" t="s">
-        <v>630</v>
+        <v>629</v>
       </c>
       <c r="H723" t="s">
         <v>9</v>
@@ -26003,7 +26006,7 @@
         <v>2.2729709148407</v>
       </c>
       <c r="G724" t="s">
-        <v>631</v>
+        <v>630</v>
       </c>
       <c r="H724" t="s">
         <v>9</v>
@@ -26029,7 +26032,7 @@
         <v>2.28650903701782</v>
       </c>
       <c r="G725" t="s">
-        <v>632</v>
+        <v>631</v>
       </c>
       <c r="H725" t="s">
         <v>9</v>
@@ -26055,7 +26058,7 @@
         <v>2.37924194335938</v>
       </c>
       <c r="G726" t="s">
-        <v>633</v>
+        <v>632</v>
       </c>
       <c r="H726" t="s">
         <v>9</v>
@@ -26081,7 +26084,7 @@
         <v>2.29733896255493</v>
       </c>
       <c r="G727" t="s">
-        <v>634</v>
+        <v>633</v>
       </c>
       <c r="H727" t="s">
         <v>9</v>
@@ -26107,7 +26110,7 @@
         <v>2.28041696548462</v>
       </c>
       <c r="G728" t="s">
-        <v>635</v>
+        <v>634</v>
       </c>
       <c r="H728" t="s">
         <v>9</v>
@@ -26133,7 +26136,7 @@
         <v>2.32170701026917</v>
       </c>
       <c r="G729" t="s">
-        <v>636</v>
+        <v>635</v>
       </c>
       <c r="H729" t="s">
         <v>9</v>
@@ -26159,7 +26162,7 @@
         <v>2.33930611610413</v>
       </c>
       <c r="G730" t="s">
-        <v>637</v>
+        <v>636</v>
       </c>
       <c r="H730" t="s">
         <v>9</v>
@@ -26185,7 +26188,7 @@
         <v>2.36028909683228</v>
       </c>
       <c r="G731" t="s">
-        <v>638</v>
+        <v>637</v>
       </c>
       <c r="H731" t="s">
         <v>9</v>
@@ -26211,7 +26214,7 @@
         <v>2.36367392539978</v>
       </c>
       <c r="G732" t="s">
-        <v>639</v>
+        <v>638</v>
       </c>
       <c r="H732" t="s">
         <v>9</v>
@@ -26237,7 +26240,7 @@
         <v>2.36570405960083</v>
       </c>
       <c r="G733" t="s">
-        <v>622</v>
+        <v>621</v>
       </c>
       <c r="H733" t="s">
         <v>9</v>
@@ -26263,7 +26266,7 @@
         <v>2.29463195800781</v>
       </c>
       <c r="G734" t="s">
-        <v>640</v>
+        <v>639</v>
       </c>
       <c r="H734" t="s">
         <v>9</v>
@@ -26289,7 +26292,7 @@
         <v>2.31358408927917</v>
       </c>
       <c r="G735" t="s">
-        <v>641</v>
+        <v>640</v>
       </c>
       <c r="H735" t="s">
         <v>9</v>
@@ -26315,7 +26318,7 @@
         <v>2.2716178894043</v>
       </c>
       <c r="G736" t="s">
-        <v>642</v>
+        <v>641</v>
       </c>
       <c r="H736" t="s">
         <v>9</v>
@@ -26341,7 +26344,7 @@
         <v>2.29260110855103</v>
       </c>
       <c r="G737" t="s">
-        <v>643</v>
+        <v>642</v>
       </c>
       <c r="H737" t="s">
         <v>9</v>
@@ -26367,7 +26370,7 @@
         <v>2.26620292663574</v>
       </c>
       <c r="G738" t="s">
-        <v>644</v>
+        <v>643</v>
       </c>
       <c r="H738" t="s">
         <v>9</v>
@@ -26393,7 +26396,7 @@
         <v>2.34810495376587</v>
       </c>
       <c r="G739" t="s">
-        <v>645</v>
+        <v>644</v>
       </c>
       <c r="H739" t="s">
         <v>9</v>
@@ -26419,7 +26422,7 @@
         <v>2.36164307594299</v>
       </c>
       <c r="G740" t="s">
-        <v>646</v>
+        <v>645</v>
       </c>
       <c r="H740" t="s">
         <v>9</v>
@@ -26445,7 +26448,7 @@
         <v>2.36299705505371</v>
       </c>
       <c r="G741" t="s">
-        <v>647</v>
+        <v>646</v>
       </c>
       <c r="H741" t="s">
         <v>9</v>
@@ -26471,7 +26474,7 @@
         <v>2.48957395553589</v>
       </c>
       <c r="G742" t="s">
-        <v>648</v>
+        <v>647</v>
       </c>
       <c r="H742" t="s">
         <v>9</v>
@@ -26497,7 +26500,7 @@
         <v>2.40225601196289</v>
       </c>
       <c r="G743" t="s">
-        <v>649</v>
+        <v>648</v>
       </c>
       <c r="H743" t="s">
         <v>9</v>
@@ -26523,7 +26526,7 @@
         <v>2.42391610145569</v>
       </c>
       <c r="G744" t="s">
-        <v>650</v>
+        <v>649</v>
       </c>
       <c r="H744" t="s">
         <v>9</v>
@@ -26549,7 +26552,7 @@
         <v>2.40022492408752</v>
       </c>
       <c r="G745" t="s">
-        <v>617</v>
+        <v>616</v>
       </c>
       <c r="H745" t="s">
         <v>9</v>
@@ -26575,7 +26578,7 @@
         <v>2.43610000610352</v>
       </c>
       <c r="G746" t="s">
-        <v>651</v>
+        <v>650</v>
       </c>
       <c r="H746" t="s">
         <v>9</v>
@@ -26601,7 +26604,7 @@
         <v>2.5484631061554</v>
       </c>
       <c r="G747" t="s">
-        <v>652</v>
+        <v>651</v>
       </c>
       <c r="H747" t="s">
         <v>9</v>
@@ -26627,7 +26630,7 @@
         <v>2.50514197349548</v>
       </c>
       <c r="G748" t="s">
-        <v>653</v>
+        <v>652</v>
       </c>
       <c r="H748" t="s">
         <v>9</v>
@@ -26653,7 +26656,7 @@
         <v>2.55184698104858</v>
       </c>
       <c r="G749" t="s">
-        <v>654</v>
+        <v>653</v>
       </c>
       <c r="H749" t="s">
         <v>9</v>
@@ -26679,7 +26682,7 @@
         <v>2.47062110900879</v>
       </c>
       <c r="G750" t="s">
-        <v>655</v>
+        <v>654</v>
       </c>
       <c r="H750" t="s">
         <v>9</v>
@@ -26705,7 +26708,7 @@
         <v>2.43136191368103</v>
       </c>
       <c r="G751" t="s">
-        <v>656</v>
+        <v>655</v>
       </c>
       <c r="H751" t="s">
         <v>9</v>
@@ -26731,7 +26734,7 @@
         <v>2.39007210731506</v>
       </c>
       <c r="G752" t="s">
-        <v>657</v>
+        <v>656</v>
       </c>
       <c r="H752" t="s">
         <v>9</v>
@@ -26757,7 +26760,7 @@
         <v>2.33930611610413</v>
       </c>
       <c r="G753" t="s">
-        <v>637</v>
+        <v>636</v>
       </c>
       <c r="H753" t="s">
         <v>9</v>
@@ -26783,7 +26786,7 @@
         <v>2.36705803871155</v>
       </c>
       <c r="G754" t="s">
-        <v>658</v>
+        <v>657</v>
       </c>
       <c r="H754" t="s">
         <v>9</v>
@@ -26809,7 +26812,7 @@
         <v>2.35758209228516</v>
       </c>
       <c r="G755" t="s">
-        <v>659</v>
+        <v>658</v>
       </c>
       <c r="H755" t="s">
         <v>9</v>
@@ -26835,7 +26838,7 @@
         <v>2.32102990150452</v>
       </c>
       <c r="G756" t="s">
-        <v>660</v>
+        <v>659</v>
       </c>
       <c r="H756" t="s">
         <v>9</v>
@@ -26861,7 +26864,7 @@
         <v>2.27567911148071</v>
       </c>
       <c r="G757" t="s">
-        <v>661</v>
+        <v>660</v>
       </c>
       <c r="H757" t="s">
         <v>9</v>
@@ -26887,7 +26890,7 @@
         <v>2.26484894752502</v>
       </c>
       <c r="G758" t="s">
-        <v>662</v>
+        <v>661</v>
       </c>
       <c r="H758" t="s">
         <v>9</v>
@@ -26913,7 +26916,7 @@
         <v>2.31087708473206</v>
       </c>
       <c r="G759" t="s">
-        <v>663</v>
+        <v>662</v>
       </c>
       <c r="H759" t="s">
         <v>9</v>
@@ -26939,7 +26942,7 @@
         <v>2.26687908172607</v>
       </c>
       <c r="G760" t="s">
-        <v>664</v>
+        <v>663</v>
       </c>
       <c r="H760" t="s">
         <v>9</v>
@@ -26965,7 +26968,7 @@
         <v>2.24995708465576</v>
       </c>
       <c r="G761" t="s">
-        <v>665</v>
+        <v>664</v>
       </c>
       <c r="H761" t="s">
         <v>9</v>
@@ -26991,7 +26994,7 @@
         <v>2.21949791908264</v>
       </c>
       <c r="G762" t="s">
-        <v>666</v>
+        <v>665</v>
       </c>
       <c r="H762" t="s">
         <v>9</v>
@@ -27017,7 +27020,7 @@
         <v>2.27703309059143</v>
       </c>
       <c r="G763" t="s">
-        <v>667</v>
+        <v>666</v>
       </c>
       <c r="H763" t="s">
         <v>9</v>
@@ -27043,7 +27046,7 @@
         <v>2.2310049533844</v>
       </c>
       <c r="G764" t="s">
-        <v>668</v>
+        <v>667</v>
       </c>
       <c r="H764" t="s">
         <v>9</v>
@@ -27069,7 +27072,7 @@
         <v>2.21611309051514</v>
       </c>
       <c r="G765" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="H765" t="s">
         <v>9</v>
@@ -27095,7 +27098,7 @@
         <v>2.29057002067566</v>
       </c>
       <c r="G766" t="s">
-        <v>670</v>
+        <v>669</v>
       </c>
       <c r="H766" t="s">
         <v>9</v>
@@ -27121,7 +27124,7 @@
         <v>2.30478501319885</v>
       </c>
       <c r="G767" t="s">
-        <v>671</v>
+        <v>670</v>
       </c>
       <c r="H767" t="s">
         <v>9</v>
@@ -27147,7 +27150,7 @@
         <v>2.25401902198792</v>
       </c>
       <c r="G768" t="s">
-        <v>672</v>
+        <v>671</v>
       </c>
       <c r="H768" t="s">
         <v>9</v>
@@ -27173,7 +27176,7 @@
         <v>2.24454188346863</v>
       </c>
       <c r="G769" t="s">
-        <v>673</v>
+        <v>672</v>
       </c>
       <c r="H769" t="s">
         <v>9</v>
@@ -27199,7 +27202,7 @@
         <v>2.25131106376648</v>
       </c>
       <c r="G770" t="s">
-        <v>674</v>
+        <v>673</v>
       </c>
       <c r="H770" t="s">
         <v>9</v>
@@ -27225,7 +27228,7 @@
         <v>2.21340608596802</v>
       </c>
       <c r="G771" t="s">
-        <v>675</v>
+        <v>674</v>
       </c>
       <c r="H771" t="s">
         <v>9</v>
@@ -27251,7 +27254,7 @@
         <v>2.12811803817749</v>
       </c>
       <c r="G772" t="s">
-        <v>676</v>
+        <v>675</v>
       </c>
       <c r="H772" t="s">
         <v>9</v>
@@ -27277,7 +27280,7 @@
         <v>2.02726292610168</v>
       </c>
       <c r="G773" t="s">
-        <v>677</v>
+        <v>676</v>
       </c>
       <c r="H773" t="s">
         <v>9</v>
@@ -27303,7 +27306,7 @@
         <v>2.071937084198</v>
       </c>
       <c r="G774" t="s">
-        <v>678</v>
+        <v>677</v>
       </c>
       <c r="H774" t="s">
         <v>9</v>
@@ -27329,7 +27332,7 @@
         <v>2.08006000518799</v>
       </c>
       <c r="G775" t="s">
-        <v>679</v>
+        <v>678</v>
       </c>
       <c r="H775" t="s">
         <v>9</v>
@@ -27355,7 +27358,7 @@
         <v>2.06787610054016</v>
       </c>
       <c r="G776" t="s">
-        <v>680</v>
+        <v>679</v>
       </c>
       <c r="H776" t="s">
         <v>9</v>
@@ -27381,7 +27384,7 @@
         <v>2.07870602607727</v>
       </c>
       <c r="G777" t="s">
-        <v>681</v>
+        <v>680</v>
       </c>
       <c r="H777" t="s">
         <v>9</v>
@@ -27407,7 +27410,7 @@
         <v>2.06719899177551</v>
       </c>
       <c r="G778" t="s">
-        <v>682</v>
+        <v>681</v>
       </c>
       <c r="H778" t="s">
         <v>9</v>
@@ -27433,7 +27436,7 @@
         <v>2.03673911094666</v>
       </c>
       <c r="G779" t="s">
-        <v>683</v>
+        <v>682</v>
       </c>
       <c r="H779" t="s">
         <v>9</v>
@@ -27459,7 +27462,7 @@
         <v>2.04283094406128</v>
       </c>
       <c r="G780" t="s">
-        <v>684</v>
+        <v>683</v>
       </c>
       <c r="H780" t="s">
         <v>9</v>
@@ -27485,7 +27488,7 @@
         <v>2.13217997550964</v>
       </c>
       <c r="G781" t="s">
-        <v>685</v>
+        <v>684</v>
       </c>
       <c r="H781" t="s">
         <v>9</v>
@@ -27511,7 +27514,7 @@
         <v>2.10645794868469</v>
       </c>
       <c r="G782" t="s">
-        <v>686</v>
+        <v>685</v>
       </c>
       <c r="H782" t="s">
         <v>9</v>
@@ -27537,7 +27540,7 @@
         <v>2.11187291145325</v>
       </c>
       <c r="G783" t="s">
-        <v>687</v>
+        <v>686</v>
       </c>
       <c r="H783" t="s">
         <v>9</v>
@@ -27563,7 +27566,7 @@
         <v>2.13014888763428</v>
       </c>
       <c r="G784" t="s">
-        <v>688</v>
+        <v>687</v>
       </c>
       <c r="H784" t="s">
         <v>9</v>
@@ -27589,7 +27592,7 @@
         <v>2.00086498260498</v>
       </c>
       <c r="G785" t="s">
-        <v>689</v>
+        <v>688</v>
       </c>
       <c r="H785" t="s">
         <v>9</v>
@@ -27615,7 +27618,7 @@
         <v>2.00695610046387</v>
       </c>
       <c r="G786" t="s">
-        <v>690</v>
+        <v>689</v>
       </c>
       <c r="H786" t="s">
         <v>9</v>
@@ -27641,7 +27644,7 @@
         <v>2.01034092903137</v>
       </c>
       <c r="G787" t="s">
-        <v>691</v>
+        <v>690</v>
       </c>
       <c r="H787" t="s">
         <v>9</v>
@@ -27667,7 +27670,7 @@
         <v>2.01372504234314</v>
       </c>
       <c r="G788" t="s">
-        <v>692</v>
+        <v>691</v>
       </c>
       <c r="H788" t="s">
         <v>9</v>
@@ -27693,7 +27696,7 @@
         <v>2.06110692024231</v>
       </c>
       <c r="G789" t="s">
-        <v>693</v>
+        <v>692</v>
       </c>
       <c r="H789" t="s">
         <v>9</v>
@@ -27719,7 +27722,7 @@
         <v>2.04012393951416</v>
       </c>
       <c r="G790" t="s">
-        <v>694</v>
+        <v>693</v>
       </c>
       <c r="H790" t="s">
         <v>9</v>
@@ -27745,7 +27748,7 @@
         <v>2.22017502784729</v>
       </c>
       <c r="G791" t="s">
-        <v>695</v>
+        <v>694</v>
       </c>
       <c r="H791" t="s">
         <v>9</v>
@@ -27771,7 +27774,7 @@
         <v>2.31223106384277</v>
       </c>
       <c r="G792" t="s">
-        <v>696</v>
+        <v>695</v>
       </c>
       <c r="H792" t="s">
         <v>9</v>
@@ -27797,7 +27800,7 @@
         <v>2.30546188354492</v>
       </c>
       <c r="G793" t="s">
-        <v>629</v>
+        <v>628</v>
       </c>
       <c r="H793" t="s">
         <v>9</v>
@@ -27823,7 +27826,7 @@
         <v>2.28853988647461</v>
       </c>
       <c r="G794" t="s">
-        <v>697</v>
+        <v>696</v>
       </c>
       <c r="H794" t="s">
         <v>9</v>
@@ -27849,7 +27852,7 @@
         <v>2.27974009513855</v>
       </c>
       <c r="G795" t="s">
-        <v>698</v>
+        <v>697</v>
       </c>
       <c r="H795" t="s">
         <v>9</v>
@@ -27875,7 +27878,7 @@
         <v>2.38533401489258</v>
       </c>
       <c r="G796" t="s">
-        <v>699</v>
+        <v>698</v>
       </c>
       <c r="H796" t="s">
         <v>9</v>
@@ -27901,7 +27904,7 @@
         <v>2.37585806846619</v>
       </c>
       <c r="G797" t="s">
-        <v>700</v>
+        <v>699</v>
       </c>
       <c r="H797" t="s">
         <v>9</v>
@@ -27927,7 +27930,7 @@
         <v>2.37450408935547</v>
       </c>
       <c r="G798" t="s">
-        <v>623</v>
+        <v>622</v>
       </c>
       <c r="H798" t="s">
         <v>9</v>
@@ -27953,7 +27956,7 @@
         <v>2.35555100440979</v>
       </c>
       <c r="G799" t="s">
-        <v>701</v>
+        <v>700</v>
       </c>
       <c r="H799" t="s">
         <v>9</v>
@@ -27979,7 +27982,7 @@
         <v>2.31764602661133</v>
       </c>
       <c r="G800" t="s">
-        <v>702</v>
+        <v>701</v>
       </c>
       <c r="H800" t="s">
         <v>9</v>
@@ -28005,7 +28008,7 @@
         <v>2.34472107887268</v>
       </c>
       <c r="G801" t="s">
-        <v>703</v>
+        <v>702</v>
       </c>
       <c r="H801" t="s">
         <v>9</v>
@@ -28031,7 +28034,7 @@
         <v>2.36841201782227</v>
       </c>
       <c r="G802" t="s">
-        <v>704</v>
+        <v>703</v>
       </c>
       <c r="H802" t="s">
         <v>9</v>
@@ -28057,7 +28060,7 @@
         <v>2.38398003578186</v>
       </c>
       <c r="G803" t="s">
-        <v>705</v>
+        <v>704</v>
       </c>
       <c r="H803" t="s">
         <v>9</v>
@@ -28083,7 +28086,7 @@
         <v>2.44828391075134</v>
       </c>
       <c r="G804" t="s">
-        <v>706</v>
+        <v>705</v>
       </c>
       <c r="H804" t="s">
         <v>9</v>
@@ -28109,7 +28112,7 @@
         <v>2.51461791992188</v>
       </c>
       <c r="G805" t="s">
-        <v>611</v>
+        <v>610</v>
       </c>
       <c r="H805" t="s">
         <v>9</v>
@@ -28135,7 +28138,7 @@
         <v>2.50311088562012</v>
       </c>
       <c r="G806" t="s">
-        <v>707</v>
+        <v>706</v>
       </c>
       <c r="H806" t="s">
         <v>9</v>
@@ -28161,7 +28164,7 @@
         <v>2.49634289741516</v>
       </c>
       <c r="G807" t="s">
-        <v>708</v>
+        <v>707</v>
       </c>
       <c r="H807" t="s">
         <v>9</v>
@@ -28187,7 +28190,7 @@
         <v>2.48821997642517</v>
       </c>
       <c r="G808" t="s">
-        <v>709</v>
+        <v>708</v>
       </c>
       <c r="H808" t="s">
         <v>9</v>
@@ -28213,7 +28216,7 @@
         <v>2.50852704048157</v>
       </c>
       <c r="G809" t="s">
-        <v>710</v>
+        <v>709</v>
       </c>
       <c r="H809" t="s">
         <v>9</v>
@@ -28239,7 +28242,7 @@
         <v>2.4347460269928</v>
       </c>
       <c r="G810" t="s">
-        <v>711</v>
+        <v>710</v>
       </c>
       <c r="H810" t="s">
         <v>9</v>
@@ -28265,7 +28268,7 @@
         <v>2.37924194335938</v>
       </c>
       <c r="G811" t="s">
-        <v>633</v>
+        <v>632</v>
       </c>
       <c r="H811" t="s">
         <v>9</v>
@@ -28291,7 +28294,7 @@
         <v>2.40970206260681</v>
       </c>
       <c r="G812" t="s">
-        <v>712</v>
+        <v>711</v>
       </c>
       <c r="H812" t="s">
         <v>9</v>
@@ -28317,7 +28320,7 @@
         <v>2.39480996131897</v>
       </c>
       <c r="G813" t="s">
-        <v>713</v>
+        <v>712</v>
       </c>
       <c r="H813" t="s">
         <v>9</v>
@@ -28343,7 +28346,7 @@
         <v>2.40902495384216</v>
       </c>
       <c r="G814" t="s">
-        <v>714</v>
+        <v>713</v>
       </c>
       <c r="H814" t="s">
         <v>9</v>
@@ -28369,7 +28372,7 @@
         <v>2.45776009559631</v>
       </c>
       <c r="G815" t="s">
-        <v>715</v>
+        <v>714</v>
       </c>
       <c r="H815" t="s">
         <v>9</v>
@@ -28395,7 +28398,7 @@
         <v>2.44286894798279</v>
       </c>
       <c r="G816" t="s">
-        <v>614</v>
+        <v>613</v>
       </c>
       <c r="H816" t="s">
         <v>9</v>
@@ -28421,7 +28424,7 @@
         <v>2.50717306137085</v>
       </c>
       <c r="G817" t="s">
-        <v>716</v>
+        <v>715</v>
       </c>
       <c r="H817" t="s">
         <v>9</v>
@@ -28447,7 +28450,7 @@
         <v>2.52612495422363</v>
       </c>
       <c r="G818" t="s">
-        <v>717</v>
+        <v>716</v>
       </c>
       <c r="H818" t="s">
         <v>9</v>
@@ -28473,7 +28476,7 @@
         <v>2.52680206298828</v>
       </c>
       <c r="G819" t="s">
-        <v>718</v>
+        <v>717</v>
       </c>
       <c r="H819" t="s">
         <v>9</v>
@@ -28499,7 +28502,7 @@
         <v>2.50446510314941</v>
       </c>
       <c r="G820" t="s">
-        <v>719</v>
+        <v>718</v>
       </c>
       <c r="H820" t="s">
         <v>9</v>
@@ -28525,7 +28528,7 @@
         <v>2.46994400024414</v>
       </c>
       <c r="G821" t="s">
-        <v>720</v>
+        <v>719</v>
       </c>
       <c r="H821" t="s">
         <v>9</v>
@@ -28551,7 +28554,7 @@
         <v>2.4597909450531</v>
       </c>
       <c r="G822" t="s">
-        <v>721</v>
+        <v>720</v>
       </c>
       <c r="H822" t="s">
         <v>9</v>
@@ -28577,7 +28580,7 @@
         <v>2.43880796432495</v>
       </c>
       <c r="G823" t="s">
-        <v>722</v>
+        <v>721</v>
       </c>
       <c r="H823" t="s">
         <v>9</v>
@@ -28603,7 +28606,7 @@
         <v>2.47739005088806</v>
       </c>
       <c r="G824" t="s">
-        <v>723</v>
+        <v>722</v>
       </c>
       <c r="H824" t="s">
         <v>9</v>
@@ -28629,7 +28632,7 @@
         <v>2.46723699569702</v>
       </c>
       <c r="G825" t="s">
-        <v>724</v>
+        <v>723</v>
       </c>
       <c r="H825" t="s">
         <v>9</v>
@@ -28655,7 +28658,7 @@
         <v>2.46452903747559</v>
       </c>
       <c r="G826" t="s">
-        <v>725</v>
+        <v>724</v>
       </c>
       <c r="H826" t="s">
         <v>9</v>
@@ -28681,7 +28684,7 @@
         <v>2.49837303161621</v>
       </c>
       <c r="G827" t="s">
-        <v>726</v>
+        <v>725</v>
       </c>
       <c r="H827" t="s">
         <v>9</v>
@@ -28707,7 +28710,7 @@
         <v>2.47942090034485</v>
       </c>
       <c r="G828" t="s">
-        <v>727</v>
+        <v>726</v>
       </c>
       <c r="H828" t="s">
         <v>9</v>
@@ -28733,7 +28736,7 @@
         <v>2.49837303161621</v>
       </c>
       <c r="G829" t="s">
-        <v>726</v>
+        <v>725</v>
       </c>
       <c r="H829" t="s">
         <v>9</v>
@@ -28759,7 +28762,7 @@
         <v>2.50378799438477</v>
       </c>
       <c r="G830" t="s">
-        <v>728</v>
+        <v>727</v>
       </c>
       <c r="H830" t="s">
         <v>9</v>
@@ -28785,7 +28788,7 @@
         <v>2.5064959526062</v>
       </c>
       <c r="G831" t="s">
-        <v>729</v>
+        <v>728</v>
       </c>
       <c r="H831" t="s">
         <v>9</v>
@@ -28811,7 +28814,7 @@
         <v>2.528156042099</v>
       </c>
       <c r="G832" t="s">
-        <v>730</v>
+        <v>729</v>
       </c>
       <c r="H832" t="s">
         <v>9</v>
@@ -28837,7 +28840,7 @@
         <v>2.52951002120972</v>
       </c>
       <c r="G833" t="s">
-        <v>731</v>
+        <v>730</v>
       </c>
       <c r="H833" t="s">
         <v>9</v>
@@ -28863,7 +28866,7 @@
         <v>2.54778599739075</v>
       </c>
       <c r="G834" t="s">
-        <v>610</v>
+        <v>609</v>
       </c>
       <c r="H834" t="s">
         <v>9</v>
@@ -28889,7 +28892,7 @@
         <v>2.56944608688354</v>
       </c>
       <c r="G835" t="s">
-        <v>732</v>
+        <v>731</v>
       </c>
       <c r="H835" t="s">
         <v>9</v>
@@ -28915,7 +28918,7 @@
         <v>2.61750507354736</v>
       </c>
       <c r="G836" t="s">
-        <v>733</v>
+        <v>732</v>
       </c>
       <c r="H836" t="s">
         <v>9</v>
@@ -28941,7 +28944,7 @@
         <v>2.68654704093933</v>
       </c>
       <c r="G837" t="s">
-        <v>734</v>
+        <v>733</v>
       </c>
       <c r="H837" t="s">
         <v>9</v>
@@ -28967,7 +28970,7 @@
         <v>2.73189806938171</v>
       </c>
       <c r="G838" t="s">
-        <v>735</v>
+        <v>734</v>
       </c>
       <c r="H838" t="s">
         <v>9</v>
@@ -28993,7 +28996,7 @@
         <v>2.80432391166687</v>
       </c>
       <c r="G839" t="s">
-        <v>736</v>
+        <v>735</v>
       </c>
       <c r="H839" t="s">
         <v>9</v>
@@ -29019,7 +29022,7 @@
         <v>2.83139991760254</v>
       </c>
       <c r="G840" t="s">
-        <v>737</v>
+        <v>736</v>
       </c>
       <c r="H840" t="s">
         <v>9</v>
@@ -29045,7 +29048,7 @@
         <v>2.8036470413208</v>
       </c>
       <c r="G841" t="s">
-        <v>738</v>
+        <v>737</v>
       </c>
       <c r="H841" t="s">
         <v>9</v>
@@ -29071,7 +29074,7 @@
         <v>2.77927994728088</v>
       </c>
       <c r="G842" t="s">
-        <v>739</v>
+        <v>738</v>
       </c>
       <c r="H842" t="s">
         <v>9</v>
@@ -29097,7 +29100,7 @@
         <v>2.82463097572327</v>
       </c>
       <c r="G843" t="s">
-        <v>740</v>
+        <v>739</v>
       </c>
       <c r="H843" t="s">
         <v>9</v>
@@ -29123,7 +29126,7 @@
         <v>2.84764504432678</v>
       </c>
       <c r="G844" t="s">
-        <v>741</v>
+        <v>740</v>
       </c>
       <c r="H844" t="s">
         <v>9</v>
@@ -29149,7 +29152,7 @@
         <v>2.85576701164246</v>
       </c>
       <c r="G845" t="s">
-        <v>742</v>
+        <v>741</v>
       </c>
       <c r="H845" t="s">
         <v>9</v>
@@ -29175,7 +29178,7 @@
         <v>2.89976501464844</v>
       </c>
       <c r="G846" t="s">
-        <v>743</v>
+        <v>742</v>
       </c>
       <c r="H846" t="s">
         <v>9</v>
@@ -29201,7 +29204,7 @@
         <v>2.85306000709534</v>
       </c>
       <c r="G847" t="s">
-        <v>744</v>
+        <v>743</v>
       </c>
       <c r="H847" t="s">
         <v>9</v>
@@ -29227,7 +29230,7 @@
         <v>2.8442599773407</v>
       </c>
       <c r="G848" t="s">
-        <v>745</v>
+        <v>744</v>
       </c>
       <c r="H848" t="s">
         <v>9</v>
@@ -29253,7 +29256,7 @@
         <v>2.80906200408936</v>
       </c>
       <c r="G849" t="s">
-        <v>535</v>
+        <v>534</v>
       </c>
       <c r="H849" t="s">
         <v>9</v>
@@ -29279,7 +29282,7 @@
         <v>2.78537201881409</v>
       </c>
       <c r="G850" t="s">
-        <v>746</v>
+        <v>745</v>
       </c>
       <c r="H850" t="s">
         <v>9</v>
@@ -29305,7 +29308,7 @@
         <v>2.76980304718018</v>
       </c>
       <c r="G851" t="s">
-        <v>747</v>
+        <v>746</v>
       </c>
       <c r="H851" t="s">
         <v>9</v>
@@ -29331,7 +29334,7 @@
         <v>2.71023797988892</v>
       </c>
       <c r="G852" t="s">
-        <v>748</v>
+        <v>747</v>
       </c>
       <c r="H852" t="s">
         <v>9</v>
@@ -29357,7 +29360,7 @@
         <v>2.68045496940613</v>
       </c>
       <c r="G853" t="s">
-        <v>749</v>
+        <v>748</v>
       </c>
       <c r="H853" t="s">
         <v>9</v>
@@ -29383,7 +29386,7 @@
         <v>2.63984203338623</v>
       </c>
       <c r="G854" t="s">
-        <v>750</v>
+        <v>749</v>
       </c>
       <c r="H854" t="s">
         <v>9</v>
@@ -29409,7 +29412,7 @@
         <v>2.66353297233582</v>
       </c>
       <c r="G855" t="s">
-        <v>751</v>
+        <v>750</v>
       </c>
       <c r="H855" t="s">
         <v>9</v>
@@ -29435,7 +29438,7 @@
         <v>2.61682796478271</v>
       </c>
       <c r="G856" t="s">
-        <v>752</v>
+        <v>751</v>
       </c>
       <c r="H856" t="s">
         <v>9</v>
@@ -29461,7 +29464,7 @@
         <v>2.67571711540222</v>
       </c>
       <c r="G857" t="s">
-        <v>753</v>
+        <v>752</v>
       </c>
       <c r="H857" t="s">
         <v>9</v>
@@ -29487,7 +29490,7 @@
         <v>2.68045496940613</v>
       </c>
       <c r="G858" t="s">
-        <v>749</v>
+        <v>748</v>
       </c>
       <c r="H858" t="s">
         <v>9</v>
@@ -29513,7 +29516,7 @@
         <v>2.51868009567261</v>
       </c>
       <c r="G859" t="s">
-        <v>754</v>
+        <v>753</v>
       </c>
       <c r="H859" t="s">
         <v>9</v>
@@ -29539,7 +29542,7 @@
         <v>2.45234489440918</v>
       </c>
       <c r="G860" t="s">
-        <v>755</v>
+        <v>754</v>
       </c>
       <c r="H860" t="s">
         <v>9</v>
@@ -29565,7 +29568,7 @@
         <v>2.40022492408752</v>
       </c>
       <c r="G861" t="s">
-        <v>756</v>
+        <v>755</v>
       </c>
       <c r="H861" t="s">
         <v>9</v>
@@ -29591,7 +29594,7 @@
         <v>2.36841201782227</v>
       </c>
       <c r="G862" t="s">
-        <v>757</v>
+        <v>756</v>
       </c>
       <c r="H862" t="s">
         <v>9</v>
@@ -29617,7 +29620,7 @@
         <v>2.3927800655365</v>
       </c>
       <c r="G863" t="s">
-        <v>758</v>
+        <v>757</v>
       </c>
       <c r="H863" t="s">
         <v>9</v>
@@ -29643,7 +29646,7 @@
         <v>2.32915306091309</v>
       </c>
       <c r="G864" t="s">
-        <v>759</v>
+        <v>758</v>
       </c>
       <c r="H864" t="s">
         <v>9</v>
@@ -29669,7 +29672,7 @@
         <v>2.33050608634949</v>
       </c>
       <c r="G865" t="s">
-        <v>760</v>
+        <v>759</v>
       </c>
       <c r="H865" t="s">
         <v>9</v>
@@ -29695,7 +29698,7 @@
         <v>2.3183228969574</v>
       </c>
       <c r="G866" t="s">
-        <v>761</v>
+        <v>760</v>
       </c>
       <c r="H866" t="s">
         <v>9</v>
@@ -29721,7 +29724,7 @@
         <v>2.30207705497742</v>
       </c>
       <c r="G867" t="s">
-        <v>762</v>
+        <v>761</v>
       </c>
       <c r="H867" t="s">
         <v>9</v>
@@ -29747,7 +29750,7 @@
         <v>2.29057002067566</v>
       </c>
       <c r="G868" t="s">
-        <v>763</v>
+        <v>762</v>
       </c>
       <c r="H868" t="s">
         <v>9</v>
@@ -29773,7 +29776,7 @@
         <v>2.27229404449463</v>
       </c>
       <c r="G869" t="s">
-        <v>764</v>
+        <v>763</v>
       </c>
       <c r="H869" t="s">
         <v>9</v>
@@ -29799,7 +29802,7 @@
         <v>2.31223106384277</v>
       </c>
       <c r="G870" t="s">
-        <v>765</v>
+        <v>764</v>
       </c>
       <c r="H870" t="s">
         <v>9</v>
@@ -29825,7 +29828,7 @@
         <v>2.27026391029358</v>
       </c>
       <c r="G871" t="s">
-        <v>766</v>
+        <v>765</v>
       </c>
       <c r="H871" t="s">
         <v>9</v>
@@ -29851,7 +29854,7 @@
         <v>2.24318909645081</v>
       </c>
       <c r="G872" t="s">
-        <v>767</v>
+        <v>766</v>
       </c>
       <c r="H872" t="s">
         <v>9</v>
@@ -29877,7 +29880,7 @@
         <v>2.23912692070007</v>
       </c>
       <c r="G873" t="s">
-        <v>768</v>
+        <v>767</v>
       </c>
       <c r="H873" t="s">
         <v>9</v>
@@ -29903,7 +29906,7 @@
         <v>2.30952310562134</v>
       </c>
       <c r="G874" t="s">
-        <v>769</v>
+        <v>768</v>
       </c>
       <c r="H874" t="s">
         <v>9</v>
@@ -29929,7 +29932,7 @@
         <v>2.33118295669556</v>
       </c>
       <c r="G875" t="s">
-        <v>770</v>
+        <v>769</v>
       </c>
       <c r="H875" t="s">
         <v>9</v>
@@ -29955,7 +29958,7 @@
         <v>2.30478501319885</v>
       </c>
       <c r="G876" t="s">
-        <v>771</v>
+        <v>770</v>
       </c>
       <c r="H876" t="s">
         <v>9</v>
@@ -29981,7 +29984,7 @@
         <v>2.33253693580627</v>
       </c>
       <c r="G877" t="s">
-        <v>772</v>
+        <v>771</v>
       </c>
       <c r="H877" t="s">
         <v>9</v>
@@ -30007,7 +30010,7 @@
         <v>2.32441401481628</v>
       </c>
       <c r="G878" t="s">
-        <v>773</v>
+        <v>772</v>
       </c>
       <c r="H878" t="s">
         <v>9</v>
@@ -30033,7 +30036,7 @@
         <v>2.34201288223267</v>
       </c>
       <c r="G879" t="s">
-        <v>774</v>
+        <v>773</v>
       </c>
       <c r="H879" t="s">
         <v>9</v>
@@ -30059,7 +30062,7 @@
         <v>2.39480996131897</v>
       </c>
       <c r="G880" t="s">
-        <v>775</v>
+        <v>774</v>
       </c>
       <c r="H880" t="s">
         <v>9</v>
@@ -30085,7 +30088,7 @@
         <v>2.4394850730896</v>
       </c>
       <c r="G881" t="s">
-        <v>776</v>
+        <v>775</v>
       </c>
       <c r="H881" t="s">
         <v>9</v>
@@ -30111,7 +30114,7 @@
         <v>2.43677711486816</v>
       </c>
       <c r="G882" t="s">
-        <v>777</v>
+        <v>776</v>
       </c>
       <c r="H882" t="s">
         <v>9</v>
@@ -30137,7 +30140,7 @@
         <v>2.47806692123413</v>
       </c>
       <c r="G883" t="s">
-        <v>778</v>
+        <v>777</v>
       </c>
       <c r="H883" t="s">
         <v>9</v>
@@ -30163,7 +30166,7 @@
         <v>2.45099210739136</v>
       </c>
       <c r="G884" t="s">
-        <v>779</v>
+        <v>778</v>
       </c>
       <c r="H884" t="s">
         <v>9</v>
@@ -30189,7 +30192,7 @@
         <v>2.39480996131897</v>
       </c>
       <c r="G885" t="s">
-        <v>775</v>
+        <v>774</v>
       </c>
       <c r="H885" t="s">
         <v>9</v>
@@ -30215,7 +30218,7 @@
         <v>2.44963788986206</v>
       </c>
       <c r="G886" t="s">
-        <v>780</v>
+        <v>779</v>
       </c>
       <c r="H886" t="s">
         <v>9</v>
@@ -30241,7 +30244,7 @@
         <v>2.46385192871094</v>
       </c>
       <c r="G887" t="s">
-        <v>781</v>
+        <v>780</v>
       </c>
       <c r="H887" t="s">
         <v>9</v>
@@ -30267,7 +30270,7 @@
         <v>2.42527008056641</v>
       </c>
       <c r="G888" t="s">
-        <v>782</v>
+        <v>781</v>
       </c>
       <c r="H888" t="s">
         <v>9</v>
@@ -30293,7 +30296,7 @@
         <v>2.41240906715393</v>
       </c>
       <c r="G889" t="s">
-        <v>783</v>
+        <v>782</v>
       </c>
       <c r="H889" t="s">
         <v>9</v>
@@ -30319,7 +30322,7 @@
         <v>2.46182203292847</v>
       </c>
       <c r="G890" t="s">
-        <v>784</v>
+        <v>783</v>
       </c>
       <c r="H890" t="s">
         <v>9</v>
@@ -30345,7 +30348,7 @@
         <v>2.55793905258179</v>
       </c>
       <c r="G891" t="s">
-        <v>785</v>
+        <v>784</v>
       </c>
       <c r="H891" t="s">
         <v>9</v>
@@ -30371,7 +30374,7 @@
         <v>2.63239598274231</v>
       </c>
       <c r="G892" t="s">
-        <v>786</v>
+        <v>785</v>
       </c>
       <c r="H892" t="s">
         <v>9</v>
@@ -30397,7 +30400,7 @@
         <v>2.63781094551086</v>
       </c>
       <c r="G893" t="s">
-        <v>787</v>
+        <v>786</v>
       </c>
       <c r="H893" t="s">
         <v>9</v>
@@ -30423,7 +30426,7 @@
         <v>2.61412000656128</v>
       </c>
       <c r="G894" t="s">
-        <v>788</v>
+        <v>787</v>
       </c>
       <c r="H894" t="s">
         <v>9</v>
@@ -30449,7 +30452,7 @@
         <v>2.59245991706848</v>
       </c>
       <c r="G895" t="s">
-        <v>749</v>
+        <v>788</v>
       </c>
       <c r="H895" t="s">
         <v>9</v>
@@ -30631,7 +30634,7 @@
         <v>2.59245991706848</v>
       </c>
       <c r="G902" t="s">
-        <v>749</v>
+        <v>788</v>
       </c>
       <c r="H902" t="s">
         <v>9</v>
@@ -31021,7 +31024,7 @@
         <v>2.32915306091309</v>
       </c>
       <c r="G917" t="s">
-        <v>759</v>
+        <v>758</v>
       </c>
       <c r="H917" t="s">
         <v>9</v>
@@ -31957,7 +31960,7 @@
         <v>2.40022492408752</v>
       </c>
       <c r="G953" t="s">
-        <v>756</v>
+        <v>755</v>
       </c>
       <c r="H953" t="s">
         <v>9</v>
@@ -32087,7 +32090,7 @@
         <v>2.36841201782227</v>
       </c>
       <c r="G958" t="s">
-        <v>757</v>
+        <v>756</v>
       </c>
       <c r="H958" t="s">
         <v>9</v>
@@ -34687,7 +34690,7 @@
         <v>2.30478501319885</v>
       </c>
       <c r="G1058" t="s">
-        <v>771</v>
+        <v>770</v>
       </c>
       <c r="H1058" t="s">
         <v>9</v>
@@ -72525,7 +72528,7 @@
     </row>
     <row r="2514">
       <c r="A2514" s="1" t="n">
-        <v>45979.691099537</v>
+        <v>45979.3333333333</v>
       </c>
       <c r="B2514" t="n">
         <v>11943146</v>
@@ -72546,6 +72549,32 @@
         <v>2278</v>
       </c>
       <c r="H2514" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2515">
+      <c r="A2515" s="1" t="n">
+        <v>45980.6910069444</v>
+      </c>
+      <c r="B2515" t="n">
+        <v>13016740</v>
+      </c>
+      <c r="C2515" t="n">
+        <v>10.2600002288818</v>
+      </c>
+      <c r="D2515" t="n">
+        <v>9.99600028991699</v>
+      </c>
+      <c r="E2515" t="n">
+        <v>10.1450004577637</v>
+      </c>
+      <c r="F2515" t="n">
+        <v>10.2049999237061</v>
+      </c>
+      <c r="G2515" t="s">
+        <v>2279</v>
+      </c>
+      <c r="H2515" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/BPE.MI.xlsx
+++ b/data/BPE.MI.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2281" uniqueCount="2281">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2282" uniqueCount="2282">
   <si>
     <t xml:space="preserve">date</t>
   </si>
@@ -38,7 +38,7 @@
     <t xml:space="preserve">ticker</t>
   </si>
   <si>
-    <t xml:space="preserve">3.19751119613647</t>
+    <t xml:space="preserve">3.19751167297363</t>
   </si>
   <si>
     <t xml:space="preserve">BPE.MI</t>
@@ -47,10 +47,10 @@
     <t xml:space="preserve">3.23759818077087</t>
   </si>
   <si>
-    <t xml:space="preserve">3.09375739097595</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.02301526069641</t>
+    <t xml:space="preserve">3.09375762939453</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.02301549911499</t>
   </si>
   <si>
     <t xml:space="preserve">2.9546320438385</t>
@@ -65,46 +65,46 @@
     <t xml:space="preserve">3.07489228248596</t>
   </si>
   <si>
-    <t xml:space="preserve">2.91690421104431</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.66223478317261</t>
+    <t xml:space="preserve">2.91690397262573</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.66223454475403</t>
   </si>
   <si>
     <t xml:space="preserve">2.6504442691803</t>
   </si>
   <si>
-    <t xml:space="preserve">2.45708417892456</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.7282600402832</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.69760489463806</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.62686395645142</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.78013682365417</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.66695070266724</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.46651697158813</t>
+    <t xml:space="preserve">2.45708441734314</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.72826027870178</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.69760537147522</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.62686371803284</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.78013706207275</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.66695046424866</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.46651673316956</t>
   </si>
   <si>
     <t xml:space="preserve">2.59385108947754</t>
   </si>
   <si>
-    <t xml:space="preserve">2.53018403053284</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.35804653167725</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.16279983520508</t>
+    <t xml:space="preserve">2.53018379211426</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.3580470085144</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.1627995967865</t>
   </si>
   <si>
     <t xml:space="preserve">2.17128896713257</t>
@@ -113,52 +113,52 @@
     <t xml:space="preserve">2.12601447105408</t>
   </si>
   <si>
-    <t xml:space="preserve">1.87228882312775</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.83173060417175</t>
+    <t xml:space="preserve">1.87228941917419</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.83173084259033</t>
   </si>
   <si>
     <t xml:space="preserve">1.95812165737152</t>
   </si>
   <si>
-    <t xml:space="preserve">1.77042138576508</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.97415637969971</t>
+    <t xml:space="preserve">1.77042126655579</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.974156498909</t>
   </si>
   <si>
     <t xml:space="preserve">2.17411851882935</t>
   </si>
   <si>
-    <t xml:space="preserve">2.2797589302063</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.33446621894836</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.32031750679016</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.18166446685791</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.40284943580627</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.31182861328125</t>
+    <t xml:space="preserve">2.27975916862488</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.33446645736694</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.32031774520874</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.18166494369507</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.40284967422485</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.31182837486267</t>
   </si>
   <si>
     <t xml:space="preserve">2.16468667984009</t>
   </si>
   <si>
-    <t xml:space="preserve">2.21844959259033</t>
+    <t xml:space="preserve">2.21844983100891</t>
   </si>
   <si>
     <t xml:space="preserve">2.2599515914917</t>
   </si>
   <si>
-    <t xml:space="preserve">2.22127938270569</t>
+    <t xml:space="preserve">2.22128009796143</t>
   </si>
   <si>
     <t xml:space="preserve">2.25429177284241</t>
@@ -167,7 +167,7 @@
     <t xml:space="preserve">2.36512041091919</t>
   </si>
   <si>
-    <t xml:space="preserve">2.32409048080444</t>
+    <t xml:space="preserve">2.32409024238586</t>
   </si>
   <si>
     <t xml:space="preserve">2.33352303504944</t>
@@ -176,16 +176,16 @@
     <t xml:space="preserve">2.21279072761536</t>
   </si>
   <si>
-    <t xml:space="preserve">2.18072152137756</t>
+    <t xml:space="preserve">2.18072175979614</t>
   </si>
   <si>
     <t xml:space="preserve">2.20524525642395</t>
   </si>
   <si>
-    <t xml:space="preserve">2.22505259513855</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.40992307662964</t>
+    <t xml:space="preserve">2.22505307197571</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.4099235534668</t>
   </si>
   <si>
     <t xml:space="preserve">2.44293642044067</t>
@@ -194,7 +194,7 @@
     <t xml:space="preserve">2.3627622127533</t>
   </si>
   <si>
-    <t xml:space="preserve">2.20241498947144</t>
+    <t xml:space="preserve">2.20241475105286</t>
   </si>
   <si>
     <t xml:space="preserve">2.2269389629364</t>
@@ -203,16 +203,16 @@
     <t xml:space="preserve">2.24674654006958</t>
   </si>
   <si>
-    <t xml:space="preserve">2.24108791351318</t>
+    <t xml:space="preserve">2.2410876750946</t>
   </si>
   <si>
     <t xml:space="preserve">2.20807456970215</t>
   </si>
   <si>
-    <t xml:space="preserve">2.14770865440369</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.05904603004456</t>
+    <t xml:space="preserve">2.14770841598511</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.05904626846313</t>
   </si>
   <si>
     <t xml:space="preserve">2.03829503059387</t>
@@ -221,49 +221,49 @@
     <t xml:space="preserve">1.97321307659149</t>
   </si>
   <si>
-    <t xml:space="preserve">2.00905585289001</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.89492630958557</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.88455045223236</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.77325069904327</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.02697658538818</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.12507176399231</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.04018211364746</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.27409982681274</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.37691116333008</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.38398480415344</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.304283618927</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.37219476699829</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.44765186309814</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.4594419002533</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.37455320358276</t>
+    <t xml:space="preserve">2.00905561447144</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.89492619037628</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.88455033302307</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.77325081825256</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.0269763469696</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.12507200241089</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.04018187522888</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.27410006523132</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.3769109249115</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.38398504257202</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.30428338050842</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.37219429016113</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.44765210151672</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.45944213867188</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.37455296516418</t>
   </si>
   <si>
     <t xml:space="preserve">2.45236802101135</t>
@@ -272,19 +272,19 @@
     <t xml:space="preserve">2.41463971138</t>
   </si>
   <si>
-    <t xml:space="preserve">2.50896143913269</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.40756511688232</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.31937408447266</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.21750736236572</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.19298362731934</t>
+    <t xml:space="preserve">2.50896120071411</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.4075653553009</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.31937432289124</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.21750664710999</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.19298338890076</t>
   </si>
   <si>
     <t xml:space="preserve">2.13167405128479</t>
@@ -293,25 +293,25 @@
     <t xml:space="preserve">2.07602405548096</t>
   </si>
   <si>
-    <t xml:space="preserve">2.07036447525024</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.06470561027527</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.03263592720032</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.02980613708496</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.06093287467957</t>
+    <t xml:space="preserve">2.07036471366882</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.06470584869385</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.03263640403748</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.02980589866638</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.06093311309814</t>
   </si>
   <si>
     <t xml:space="preserve">2.17506194114685</t>
   </si>
   <si>
-    <t xml:space="preserve">2.07319474220276</t>
+    <t xml:space="preserve">2.07319450378418</t>
   </si>
   <si>
     <t xml:space="preserve">2.09960436820984</t>
@@ -326,13 +326,13 @@
     <t xml:space="preserve">2.3311779499054</t>
   </si>
   <si>
-    <t xml:space="preserve">2.28582787513733</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.29161763191223</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.31381058692932</t>
+    <t xml:space="preserve">2.28582811355591</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.29161787033081</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.3138108253479</t>
   </si>
   <si>
     <t xml:space="preserve">2.19416379928589</t>
@@ -344,70 +344,70 @@
     <t xml:space="preserve">2.07934188842773</t>
   </si>
   <si>
-    <t xml:space="preserve">2.06969261169434</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.09670901298523</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.13627052307129</t>
+    <t xml:space="preserve">2.06969308853149</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.09670925140381</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.13627028465271</t>
   </si>
   <si>
     <t xml:space="preserve">1.99636113643646</t>
   </si>
   <si>
-    <t xml:space="preserve">1.87478399276733</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.82171511650085</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.81592643260956</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.76864624023438</t>
+    <t xml:space="preserve">1.87478411197662</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.82171547412872</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.81592607498169</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.76864647865295</t>
   </si>
   <si>
     <t xml:space="preserve">1.94425702095032</t>
   </si>
   <si>
-    <t xml:space="preserve">2.03206157684326</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.0841658115387</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.07548213005066</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.23468923568726</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.68470072746277</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.66733264923096</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.62777197360992</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.5390020608902</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.58145761489868</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.50523042678833</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.40391731262207</t>
+    <t xml:space="preserve">2.03206181526184</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.08416557312012</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.07548236846924</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.23468947410583</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.68470108509064</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.66733276844025</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.62777185440063</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.53900218009949</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.5814573764801</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.50523054599762</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.40391719341278</t>
   </si>
   <si>
     <t xml:space="preserve">1.40488231182098</t>
   </si>
   <si>
-    <t xml:space="preserve">1.30453324317932</t>
+    <t xml:space="preserve">1.30453312397003</t>
   </si>
   <si>
     <t xml:space="preserve">1.24567461013794</t>
@@ -419,16 +419,16 @@
     <t xml:space="preserve">1.51487982273102</t>
   </si>
   <si>
-    <t xml:space="preserve">1.63838624954224</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.55637049674988</t>
+    <t xml:space="preserve">1.63838589191437</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.55637013912201</t>
   </si>
   <si>
     <t xml:space="preserve">1.62294793128967</t>
   </si>
   <si>
-    <t xml:space="preserve">1.64224553108215</t>
+    <t xml:space="preserve">1.64224565029144</t>
   </si>
   <si>
     <t xml:space="preserve">1.65189468860626</t>
@@ -437,43 +437,43 @@
     <t xml:space="preserve">1.63645589351654</t>
   </si>
   <si>
-    <t xml:space="preserve">1.65382409095764</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.7068932056427</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.69434940814972</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.64899957180023</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.65671849250793</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.73294532299042</t>
+    <t xml:space="preserve">1.65382432937622</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.70689296722412</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.69434952735901</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.64899981021881</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.65671873092651</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.73294544219971</t>
   </si>
   <si>
     <t xml:space="preserve">1.67891144752502</t>
   </si>
   <si>
-    <t xml:space="preserve">1.77057635784149</t>
+    <t xml:space="preserve">1.77057647705078</t>
   </si>
   <si>
     <t xml:space="preserve">1.67022740840912</t>
   </si>
   <si>
-    <t xml:space="preserve">1.46374034881592</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.5225989818573</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.53031778335571</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.73005080223083</t>
+    <t xml:space="preserve">1.46374046802521</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.52259886264801</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.530317902565</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.73005104064941</t>
   </si>
   <si>
     <t xml:space="preserve">1.69820916652679</t>
@@ -482,70 +482,70 @@
     <t xml:space="preserve">1.73198044300079</t>
   </si>
   <si>
-    <t xml:space="preserve">1.72136688232422</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.72040176391602</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.69627964496613</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.68373596668243</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.62101781368256</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.64996457099915</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.55444037914276</t>
+    <t xml:space="preserve">1.72136664390564</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.72040188312531</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.69627976417542</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.68373572826385</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.62101769447327</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.64996480941772</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.55444014072418</t>
   </si>
   <si>
     <t xml:space="preserve">1.56505441665649</t>
   </si>
   <si>
-    <t xml:space="preserve">1.65478909015656</t>
+    <t xml:space="preserve">1.65478885173798</t>
   </si>
   <si>
     <t xml:space="preserve">1.69048964977264</t>
   </si>
   <si>
-    <t xml:space="preserve">1.64128053188324</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.60750925540924</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.65285909175873</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.66443812847137</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.6953147649765</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.71847152709961</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.68759536743164</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.74452376365662</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.74741852283478</t>
+    <t xml:space="preserve">1.64128029346466</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.60750913619995</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.65285897254944</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.66443836688995</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.69531452655792</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.71847188472748</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.68759548664093</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.74452424049377</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.74741864204407</t>
   </si>
   <si>
     <t xml:space="preserve">1.71268260478973</t>
   </si>
   <si>
-    <t xml:space="preserve">1.67987644672394</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.63549149036407</t>
+    <t xml:space="preserve">1.67987632751465</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.63549160957336</t>
   </si>
   <si>
     <t xml:space="preserve">1.58049261569977</t>
@@ -554,76 +554,76 @@
     <t xml:space="preserve">1.60461473464966</t>
   </si>
   <si>
-    <t xml:space="preserve">1.53610742092133</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.60847413539886</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.61233389377594</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.53996706008911</t>
+    <t xml:space="preserve">1.5361076593399</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.60847401618958</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.61233365535736</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.53996694087982</t>
   </si>
   <si>
     <t xml:space="preserve">1.51584506034851</t>
   </si>
   <si>
-    <t xml:space="preserve">1.54961633682251</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.55251085758209</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.59786081314087</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.56119513511658</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.63452649116516</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.63935101032257</t>
+    <t xml:space="preserve">1.54961621761322</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.55251097679138</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.59786069393158</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.56119477748871</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.63452661037445</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.63935112953186</t>
   </si>
   <si>
     <t xml:space="preserve">1.61619317531586</t>
   </si>
   <si>
-    <t xml:space="preserve">1.6740870475769</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.77540123462677</t>
+    <t xml:space="preserve">1.67408668994904</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.77540075778961</t>
   </si>
   <si>
     <t xml:space="preserve">1.81496131420135</t>
   </si>
   <si>
-    <t xml:space="preserve">1.73583984375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.82653987407684</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.86513555049896</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.96066009998322</t>
+    <t xml:space="preserve">1.73583960533142</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.82653963565826</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.86513543128967</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.9606602191925</t>
   </si>
   <si>
     <t xml:space="preserve">2.05425453186035</t>
   </si>
   <si>
-    <t xml:space="preserve">2.04942965507507</t>
+    <t xml:space="preserve">2.04942989349365</t>
   </si>
   <si>
     <t xml:space="preserve">2.10153365135193</t>
   </si>
   <si>
-    <t xml:space="preserve">2.01372933387756</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.0465350151062</t>
+    <t xml:space="preserve">2.01372909545898</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.04653525352478</t>
   </si>
   <si>
     <t xml:space="preserve">2.09477972984314</t>
@@ -632,139 +632,139 @@
     <t xml:space="preserve">2.08899021148682</t>
   </si>
   <si>
-    <t xml:space="preserve">2.06197357177734</t>
+    <t xml:space="preserve">2.06197381019592</t>
   </si>
   <si>
     <t xml:space="preserve">2.04460525512695</t>
   </si>
   <si>
-    <t xml:space="preserve">1.9297833442688</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.90566086769104</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.8844336271286</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.95004594326019</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.98671162128448</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.01565861701965</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.01662349700928</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.99539566040039</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.98574638366699</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.92785322666168</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.84583747386932</t>
+    <t xml:space="preserve">1.92978298664093</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.9056613445282</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.88443303108215</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.95004606246948</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.98671209812164</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.01565909385681</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.01662373542786</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.99539613723755</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.98574674129486</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.92785358428955</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.84583735466003</t>
   </si>
   <si>
     <t xml:space="preserve">1.80820727348328</t>
   </si>
   <si>
-    <t xml:space="preserve">1.80048727989197</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.83715391159058</t>
+    <t xml:space="preserve">1.80048739910126</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.83715415000916</t>
   </si>
   <si>
     <t xml:space="preserve">1.82750499248505</t>
   </si>
   <si>
-    <t xml:space="preserve">1.83329367637634</t>
+    <t xml:space="preserve">1.83329379558563</t>
   </si>
   <si>
     <t xml:space="preserve">1.80531215667725</t>
   </si>
   <si>
-    <t xml:space="preserve">1.82846999168396</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.97513318061829</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.93557298183441</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.06679797172546</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.28196883201599</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.31477451324463</t>
+    <t xml:space="preserve">1.82846975326538</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.975133061409</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.93557274341583</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.06679821014404</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.28196835517883</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.31477475166321</t>
   </si>
   <si>
     <t xml:space="preserve">2.27907419204712</t>
   </si>
   <si>
-    <t xml:space="preserve">2.32152938842773</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.3707389831543</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.33214282989502</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.39486122131348</t>
+    <t xml:space="preserve">2.32152962684631</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.37073874473572</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.3321430683136</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.3948609828949</t>
   </si>
   <si>
     <t xml:space="preserve">2.41464138031006</t>
   </si>
   <si>
-    <t xml:space="preserve">2.39775586128235</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.41222953796387</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.46529817581177</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.48942065238953</t>
+    <t xml:space="preserve">2.39775538444519</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.41222977638245</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.46529841423035</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.48942041397095</t>
   </si>
   <si>
     <t xml:space="preserve">2.496657371521</t>
   </si>
   <si>
-    <t xml:space="preserve">2.44117617607117</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.54248929023743</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.63897848129272</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.59555888175964</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.55696296691895</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.42911529541016</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.41705322265625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.56178665161133</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.53766512870789</t>
+    <t xml:space="preserve">2.44117641448975</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.54248952865601</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.6389787197113</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.59555864334106</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.55696249008179</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.42911505699158</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.41705346107483</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.56178760528564</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.53766489028931</t>
   </si>
   <si>
     <t xml:space="preserve">2.5786726474762</t>
@@ -773,82 +773,82 @@
     <t xml:space="preserve">2.58832216262817</t>
   </si>
   <si>
-    <t xml:space="preserve">2.72823143005371</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.77165126800537</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.7065212726593</t>
+    <t xml:space="preserve">2.72823119163513</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.77165102958679</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.70652174949646</t>
   </si>
   <si>
     <t xml:space="preserve">2.71375751495361</t>
   </si>
   <si>
-    <t xml:space="preserve">2.74752950668335</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.70410895347595</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.57626128196716</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.52801585197449</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.58590936660767</t>
+    <t xml:space="preserve">2.74752879142761</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.70410919189453</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.57626080513</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.52801609039307</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.58590912818909</t>
   </si>
   <si>
     <t xml:space="preserve">2.59797048568726</t>
   </si>
   <si>
-    <t xml:space="preserve">2.66068863868713</t>
+    <t xml:space="preserve">2.66068840026855</t>
   </si>
   <si>
     <t xml:space="preserve">2.50871825218201</t>
   </si>
   <si>
-    <t xml:space="preserve">2.42187786102295</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.45082473754883</t>
+    <t xml:space="preserve">2.42187809944153</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.45082497596741</t>
   </si>
   <si>
     <t xml:space="preserve">2.2945122718811</t>
   </si>
   <si>
-    <t xml:space="preserve">2.3022313117981</t>
+    <t xml:space="preserve">2.30223155021667</t>
   </si>
   <si>
     <t xml:space="preserve">2.38135266304016</t>
   </si>
   <si>
-    <t xml:space="preserve">2.32056474685669</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.24047780036926</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.1710057258606</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.1478488445282</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.14495468139648</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.06293845176697</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.02627277374268</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.99732601642609</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.16135764122009</t>
+    <t xml:space="preserve">2.32056427001953</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.24047803878784</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.17100596427917</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.14784860610962</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.14495444297791</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.06293821334839</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.02627301216125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.99732577800751</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.16135740280151</t>
   </si>
   <si>
     <t xml:space="preserve">2.17004156112671</t>
@@ -857,34 +857,34 @@
     <t xml:space="preserve">2.26749539375305</t>
   </si>
   <si>
-    <t xml:space="preserve">2.20574259757996</t>
+    <t xml:space="preserve">2.20574235916138</t>
   </si>
   <si>
     <t xml:space="preserve">2.11311268806458</t>
   </si>
   <si>
-    <t xml:space="preserve">2.1179370880127</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.18837404251099</t>
+    <t xml:space="preserve">2.11793684959412</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.18837428092957</t>
   </si>
   <si>
     <t xml:space="preserve">2.25977635383606</t>
   </si>
   <si>
-    <t xml:space="preserve">2.22214579582214</t>
+    <t xml:space="preserve">2.22214555740356</t>
   </si>
   <si>
     <t xml:space="preserve">2.16521716117859</t>
   </si>
   <si>
-    <t xml:space="preserve">2.16907620429993</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.27714490890503</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.25012707710266</t>
+    <t xml:space="preserve">2.16907644271851</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.27714467048645</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.25012755393982</t>
   </si>
   <si>
     <t xml:space="preserve">2.31766986846924</t>
@@ -896,34 +896,34 @@
     <t xml:space="preserve">2.39196681976318</t>
   </si>
   <si>
-    <t xml:space="preserve">2.36494922637939</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.32249402999878</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.33696794509888</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.29354763031006</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.26267075538635</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.25784635543823</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.17872524261475</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.19512844085693</t>
+    <t xml:space="preserve">2.36494946479797</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.3224937915802</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.3369677066803</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.29354810714722</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.26267099380493</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.25784659385681</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.17872500419617</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.19512820243835</t>
   </si>
   <si>
     <t xml:space="preserve">2.19319868087769</t>
   </si>
   <si>
-    <t xml:space="preserve">2.20960187911987</t>
+    <t xml:space="preserve">2.20960211753845</t>
   </si>
   <si>
     <t xml:space="preserve">2.17390131950378</t>
@@ -932,10 +932,10 @@
     <t xml:space="preserve">2.12179660797119</t>
   </si>
   <si>
-    <t xml:space="preserve">2.10442924499512</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.21153140068054</t>
+    <t xml:space="preserve">2.10442900657654</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.21153116226196</t>
   </si>
   <si>
     <t xml:space="preserve">2.36398434638977</t>
@@ -947,40 +947,40 @@
     <t xml:space="preserve">2.3466169834137</t>
   </si>
   <si>
-    <t xml:space="preserve">2.41946625709534</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.48218393325806</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.51836752891541</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.45564961433411</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.43635225296021</t>
+    <t xml:space="preserve">2.41946578025818</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.48218417167664</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.51836776733398</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.45564937591553</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.43635129928589</t>
   </si>
   <si>
     <t xml:space="preserve">2.29837155342102</t>
   </si>
   <si>
-    <t xml:space="preserve">2.26170611381531</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.34468650817871</t>
+    <t xml:space="preserve">2.26170587539673</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.34468674659729</t>
   </si>
   <si>
     <t xml:space="preserve">2.30609083175659</t>
   </si>
   <si>
-    <t xml:space="preserve">2.25302171707153</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.22697019577026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.26074147224426</t>
+    <t xml:space="preserve">2.25302195549011</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.22697043418884</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.26074171066284</t>
   </si>
   <si>
     <t xml:space="preserve">2.24998950958252</t>
@@ -989,16 +989,16 @@
     <t xml:space="preserve">2.25096726417542</t>
   </si>
   <si>
-    <t xml:space="preserve">2.28224396705627</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.27931189537048</t>
+    <t xml:space="preserve">2.2822437286377</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.2793116569519</t>
   </si>
   <si>
     <t xml:space="preserve">2.25292158126831</t>
   </si>
   <si>
-    <t xml:space="preserve">2.18450379371643</t>
+    <t xml:space="preserve">2.18450331687927</t>
   </si>
   <si>
     <t xml:space="preserve">2.18548107147217</t>
@@ -1007,55 +1007,55 @@
     <t xml:space="preserve">2.13074636459351</t>
   </si>
   <si>
-    <t xml:space="preserve">2.17570662498474</t>
+    <t xml:space="preserve">2.17570686340332</t>
   </si>
   <si>
     <t xml:space="preserve">2.14833974838257</t>
   </si>
   <si>
-    <t xml:space="preserve">2.10924315452576</t>
+    <t xml:space="preserve">2.10924339294434</t>
   </si>
   <si>
     <t xml:space="preserve">2.07698893547058</t>
   </si>
   <si>
-    <t xml:space="preserve">2.08089828491211</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.15811324119568</t>
+    <t xml:space="preserve">2.08089852333069</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.15811347961426</t>
   </si>
   <si>
     <t xml:space="preserve">2.15127158164978</t>
   </si>
   <si>
-    <t xml:space="preserve">2.10631132125854</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.15909099578857</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.13758826255798</t>
+    <t xml:space="preserve">2.10631108283997</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.15909123420715</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.1375880241394</t>
   </si>
   <si>
     <t xml:space="preserve">2.04082465171814</t>
   </si>
   <si>
-    <t xml:space="preserve">2.05353045463562</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.00075125694275</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.09067225456238</t>
+    <t xml:space="preserve">2.05353093147278</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.00075101852417</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.0906720161438</t>
   </si>
   <si>
     <t xml:space="preserve">2.081876039505</t>
   </si>
   <si>
-    <t xml:space="preserve">2.13661050796509</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.14931654930115</t>
+    <t xml:space="preserve">2.13661026954651</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.14931631088257</t>
   </si>
   <si>
     <t xml:space="preserve">2.16886520385742</t>
@@ -1064,58 +1064,58 @@
     <t xml:space="preserve">2.15713572502136</t>
   </si>
   <si>
-    <t xml:space="preserve">2.1336784362793</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.27149295806885</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.34870743751526</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.29201793670654</t>
+    <t xml:space="preserve">2.13367867469788</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.27149271965027</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.34870767593384</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.29201769828796</t>
   </si>
   <si>
     <t xml:space="preserve">2.29788303375244</t>
   </si>
   <si>
-    <t xml:space="preserve">2.29104065895081</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.32231831550598</t>
+    <t xml:space="preserve">2.29104018211365</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.3223180770874</t>
   </si>
   <si>
     <t xml:space="preserve">2.36434650421143</t>
   </si>
   <si>
-    <t xml:space="preserve">2.41419434547424</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.42103600502014</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.41908168792725</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.43374228477478</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.354572057724</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.37021064758301</t>
+    <t xml:space="preserve">2.41419410705566</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.42103576660156</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.41908144950867</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.43374180793762</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.35457229614258</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.37021040916443</t>
   </si>
   <si>
     <t xml:space="preserve">2.30667948722839</t>
   </si>
   <si>
-    <t xml:space="preserve">2.28126668930054</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.25389885902405</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.2871310710907</t>
+    <t xml:space="preserve">2.28126692771912</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.25389933586121</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.28713083267212</t>
   </si>
   <si>
     <t xml:space="preserve">2.29885983467102</t>
@@ -1124,13 +1124,13 @@
     <t xml:space="preserve">2.27344727516174</t>
   </si>
   <si>
-    <t xml:space="preserve">2.26953768730164</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.31352114677429</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.45328998565674</t>
+    <t xml:space="preserve">2.26953744888306</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.31352138519287</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.45328950881958</t>
   </si>
   <si>
     <t xml:space="preserve">2.42005848884583</t>
@@ -1145,43 +1145,43 @@
     <t xml:space="preserve">2.39464569091797</t>
   </si>
   <si>
-    <t xml:space="preserve">2.38389444351196</t>
+    <t xml:space="preserve">2.38389468193054</t>
   </si>
   <si>
     <t xml:space="preserve">2.35750412940979</t>
   </si>
   <si>
-    <t xml:space="preserve">2.32622766494751</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.29690504074097</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.31938552856445</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.3291597366333</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.26856064796448</t>
+    <t xml:space="preserve">2.32622742652893</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.29690527915955</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.31938505172729</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.32915949821472</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.2685604095459</t>
   </si>
   <si>
     <t xml:space="preserve">2.29299569129944</t>
   </si>
   <si>
-    <t xml:space="preserve">2.31254315376282</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.34382081031799</t>
+    <t xml:space="preserve">2.31254363059998</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.34382104873657</t>
   </si>
   <si>
     <t xml:space="preserve">2.30863404273987</t>
   </si>
   <si>
-    <t xml:space="preserve">2.27247047424316</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.23337388038635</t>
+    <t xml:space="preserve">2.27247023582458</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.23337364196777</t>
   </si>
   <si>
     <t xml:space="preserve">2.21382570266724</t>
@@ -1190,19 +1190,19 @@
     <t xml:space="preserve">2.27735733985901</t>
   </si>
   <si>
-    <t xml:space="preserve">2.3477303981781</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.30081510543823</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.24217057228088</t>
+    <t xml:space="preserve">2.34773063659668</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.30081462860107</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.2421703338623</t>
   </si>
   <si>
     <t xml:space="preserve">2.26269578933716</t>
   </si>
   <si>
-    <t xml:space="preserve">2.29006361961365</t>
+    <t xml:space="preserve">2.29006338119507</t>
   </si>
   <si>
     <t xml:space="preserve">2.33795642852783</t>
@@ -1211,7 +1211,7 @@
     <t xml:space="preserve">2.28615355491638</t>
   </si>
   <si>
-    <t xml:space="preserve">2.35359454154968</t>
+    <t xml:space="preserve">2.35359477996826</t>
   </si>
   <si>
     <t xml:space="preserve">2.42299103736877</t>
@@ -1220,34 +1220,34 @@
     <t xml:space="preserve">2.46306443214417</t>
   </si>
   <si>
-    <t xml:space="preserve">2.47283887863159</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.51437830924988</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.50704765319824</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.43276429176331</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.39171361923218</t>
+    <t xml:space="preserve">2.47283840179443</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.51437854766846</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.50704717636108</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.43276453018188</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.39171385765076</t>
   </si>
   <si>
     <t xml:space="preserve">2.26171827316284</t>
   </si>
   <si>
-    <t xml:space="preserve">2.19525504112244</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.14736247062683</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.17081928253174</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.14638447761536</t>
+    <t xml:space="preserve">2.19525456428528</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.14736223220825</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.17081952095032</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.14638423919678</t>
   </si>
   <si>
     <t xml:space="preserve">2.1405200958252</t>
@@ -1256,61 +1256,61 @@
     <t xml:space="preserve">2.07210183143616</t>
   </si>
   <si>
-    <t xml:space="preserve">2.07894325256348</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.09946894645691</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.07601094245911</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.04375743865967</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.05450868606567</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.04473400115967</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.03887009620667</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.11315298080444</t>
+    <t xml:space="preserve">2.07894349098206</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.09946918487549</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.07601118087769</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.04375720024109</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.05450820922852</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.04473423957825</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.03886985778809</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.11315274238586</t>
   </si>
   <si>
     <t xml:space="preserve">2.05939555168152</t>
   </si>
   <si>
-    <t xml:space="preserve">2.02616333961487</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.98804461956024</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.90105557441711</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.08969521522522</t>
+    <t xml:space="preserve">2.02616405487061</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.98804497718811</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.9010556936264</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.08969569206238</t>
   </si>
   <si>
     <t xml:space="preserve">2.06721472740173</t>
   </si>
   <si>
-    <t xml:space="preserve">2.08578586578369</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.03984761238098</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.08285307884216</t>
+    <t xml:space="preserve">2.08578562736511</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.0398473739624</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.08285284042358</t>
   </si>
   <si>
     <t xml:space="preserve">2.01345729827881</t>
   </si>
   <si>
-    <t xml:space="preserve">2.04668951034546</t>
+    <t xml:space="preserve">2.0466890335083</t>
   </si>
   <si>
     <t xml:space="preserve">2.01834440231323</t>
@@ -1322,7 +1322,7 @@
     <t xml:space="preserve">2.06623697280884</t>
   </si>
   <si>
-    <t xml:space="preserve">2.16202282905579</t>
+    <t xml:space="preserve">2.16202306747437</t>
   </si>
   <si>
     <t xml:space="preserve">2.24607992172241</t>
@@ -1331,22 +1331,22 @@
     <t xml:space="preserve">2.17961645126343</t>
   </si>
   <si>
-    <t xml:space="preserve">2.23826050758362</t>
+    <t xml:space="preserve">2.2382607460022</t>
   </si>
   <si>
     <t xml:space="preserve">2.22653222084045</t>
   </si>
   <si>
-    <t xml:space="preserve">2.19916391372681</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.27051520347595</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.21773552894592</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.07796549797058</t>
+    <t xml:space="preserve">2.19916415214539</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.27051496505737</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.21773529052734</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.07796573638916</t>
   </si>
   <si>
     <t xml:space="preserve">2.03691458702087</t>
@@ -1364,37 +1364,37 @@
     <t xml:space="preserve">2.0887176990509</t>
   </si>
   <si>
-    <t xml:space="preserve">2.0476667881012</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.05841779708862</t>
+    <t xml:space="preserve">2.04766654968262</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.0584180355072</t>
   </si>
   <si>
     <t xml:space="preserve">2.11510801315308</t>
   </si>
   <si>
-    <t xml:space="preserve">2.05744028091431</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.03300523757935</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.07307910919189</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.07503390312195</t>
+    <t xml:space="preserve">2.05744004249573</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.03300547599792</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.07307958602905</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.07503366470337</t>
   </si>
   <si>
     <t xml:space="preserve">2.11119771003723</t>
   </si>
   <si>
-    <t xml:space="preserve">2.20600652694702</t>
+    <t xml:space="preserve">2.20600700378418</t>
   </si>
   <si>
     <t xml:space="preserve">2.22848653793335</t>
   </si>
   <si>
-    <t xml:space="preserve">2.20405149459839</t>
+    <t xml:space="preserve">2.20405173301697</t>
   </si>
   <si>
     <t xml:space="preserve">2.16104531288147</t>
@@ -1403,7 +1403,7 @@
     <t xml:space="preserve">2.35261702537537</t>
   </si>
   <si>
-    <t xml:space="preserve">2.35066294670105</t>
+    <t xml:space="preserve">2.35066223144531</t>
   </si>
   <si>
     <t xml:space="preserve">2.36776733398438</t>
@@ -1412,13 +1412,13 @@
     <t xml:space="preserve">2.27686858177185</t>
   </si>
   <si>
-    <t xml:space="preserve">2.29543924331665</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.27784538269043</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.21578049659729</t>
+    <t xml:space="preserve">2.29543876647949</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.27784514427185</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.21578025817871</t>
   </si>
   <si>
     <t xml:space="preserve">2.2240879535675</t>
@@ -1427,10 +1427,10 @@
     <t xml:space="preserve">2.30179238319397</t>
   </si>
   <si>
-    <t xml:space="preserve">2.25194501876831</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.22213363647461</t>
+    <t xml:space="preserve">2.25194454193115</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.22213339805603</t>
   </si>
   <si>
     <t xml:space="preserve">2.33746743202209</t>
@@ -1439,19 +1439,19 @@
     <t xml:space="preserve">2.34186625480652</t>
   </si>
   <si>
-    <t xml:space="preserve">2.33209180831909</t>
+    <t xml:space="preserve">2.33209156990051</t>
   </si>
   <si>
     <t xml:space="preserve">2.33600115776062</t>
   </si>
   <si>
-    <t xml:space="preserve">2.28957462310791</t>
+    <t xml:space="preserve">2.28957486152649</t>
   </si>
   <si>
     <t xml:space="preserve">2.37656402587891</t>
   </si>
   <si>
-    <t xml:space="preserve">2.37705326080322</t>
+    <t xml:space="preserve">2.37705302238464</t>
   </si>
   <si>
     <t xml:space="preserve">2.38145112991333</t>
@@ -1460,7 +1460,7 @@
     <t xml:space="preserve">2.37900733947754</t>
   </si>
   <si>
-    <t xml:space="preserve">2.40735173225403</t>
+    <t xml:space="preserve">2.40735197067261</t>
   </si>
   <si>
     <t xml:space="preserve">2.38731527328491</t>
@@ -1475,49 +1475,49 @@
     <t xml:space="preserve">2.32720541954041</t>
   </si>
   <si>
-    <t xml:space="preserve">2.25438857078552</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.29641675949097</t>
+    <t xml:space="preserve">2.25438809394836</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.29641652107239</t>
   </si>
   <si>
     <t xml:space="preserve">2.24461364746094</t>
   </si>
   <si>
-    <t xml:space="preserve">2.2490119934082</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.27540230751038</t>
+    <t xml:space="preserve">2.24901223182678</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.27540254592896</t>
   </si>
   <si>
     <t xml:space="preserve">2.28322172164917</t>
   </si>
   <si>
-    <t xml:space="preserve">2.26758289337158</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.22359943389893</t>
+    <t xml:space="preserve">2.26758313179016</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.22359919548035</t>
   </si>
   <si>
     <t xml:space="preserve">2.22995281219482</t>
   </si>
   <si>
-    <t xml:space="preserve">2.21040511131287</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.22555446624756</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.2069833278656</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.20893836021423</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.29446125030518</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.30276942253113</t>
+    <t xml:space="preserve">2.21040487289429</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.22555470466614</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.20698380470276</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.20893859863281</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.29446148872375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.30276989936829</t>
   </si>
   <si>
     <t xml:space="preserve">2.31156611442566</t>
@@ -1532,7 +1532,7 @@
     <t xml:space="preserve">2.35652732849121</t>
   </si>
   <si>
-    <t xml:space="preserve">2.36288022994995</t>
+    <t xml:space="preserve">2.36288070678711</t>
   </si>
   <si>
     <t xml:space="preserve">2.38829278945923</t>
@@ -1547,22 +1547,22 @@
     <t xml:space="preserve">2.33013725280762</t>
   </si>
   <si>
-    <t xml:space="preserve">2.31889724731445</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.33062553405762</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.31303238868713</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.30570197105408</t>
+    <t xml:space="preserve">2.31889748573303</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.33062601089478</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.31303262710571</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.30570220947266</t>
   </si>
   <si>
     <t xml:space="preserve">2.3966007232666</t>
   </si>
   <si>
-    <t xml:space="preserve">2.40539741516113</t>
+    <t xml:space="preserve">2.40539765357971</t>
   </si>
   <si>
     <t xml:space="preserve">2.45231294631958</t>
@@ -1574,61 +1574,61 @@
     <t xml:space="preserve">2.51584386825562</t>
   </si>
   <si>
-    <t xml:space="preserve">2.44205021858215</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.44253849983215</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.28028917312622</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.30131077766418</t>
+    <t xml:space="preserve">2.44204998016357</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.44253873825073</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.2802894115448</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.30131053924561</t>
   </si>
   <si>
     <t xml:space="preserve">2.33834767341614</t>
   </si>
   <si>
-    <t xml:space="preserve">2.36387300491333</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.33484387397766</t>
+    <t xml:space="preserve">2.36387324333191</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.33484411239624</t>
   </si>
   <si>
     <t xml:space="preserve">2.28779673576355</t>
   </si>
   <si>
-    <t xml:space="preserve">2.15416216850281</t>
+    <t xml:space="preserve">2.15416264533997</t>
   </si>
   <si>
     <t xml:space="preserve">2.04555368423462</t>
   </si>
   <si>
-    <t xml:space="preserve">2.05306124687195</t>
+    <t xml:space="preserve">2.05306100845337</t>
   </si>
   <si>
     <t xml:space="preserve">2.05356168746948</t>
   </si>
   <si>
-    <t xml:space="preserve">2.21522402763367</t>
+    <t xml:space="preserve">2.21522378921509</t>
   </si>
   <si>
     <t xml:space="preserve">2.15015840530396</t>
   </si>
   <si>
-    <t xml:space="preserve">2.07708501815796</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.07608461380005</t>
+    <t xml:space="preserve">2.07708477973938</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.07608437538147</t>
   </si>
   <si>
     <t xml:space="preserve">2.11612415313721</t>
   </si>
   <si>
-    <t xml:space="preserve">2.05906701087952</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.14865756034851</t>
+    <t xml:space="preserve">2.0590672492981</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.14865708351135</t>
   </si>
   <si>
     <t xml:space="preserve">2.1741828918457</t>
@@ -1637,28 +1637,28 @@
     <t xml:space="preserve">2.20921754837036</t>
   </si>
   <si>
-    <t xml:space="preserve">2.23624515533447</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.17768597602844</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.16717553138733</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.24074959754944</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.29730629920959</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.22973871231079</t>
+    <t xml:space="preserve">2.23624491691589</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.17768669128418</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.16717529296875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.24074912071228</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.29730606079102</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.22973847389221</t>
   </si>
   <si>
     <t xml:space="preserve">2.39390325546265</t>
   </si>
   <si>
-    <t xml:space="preserve">2.34485411643982</t>
+    <t xml:space="preserve">2.3448543548584</t>
   </si>
   <si>
     <t xml:space="preserve">2.35786747932434</t>
@@ -1667,37 +1667,37 @@
     <t xml:space="preserve">2.32433319091797</t>
   </si>
   <si>
-    <t xml:space="preserve">2.34535479545593</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.35586500167847</t>
+    <t xml:space="preserve">2.34535455703735</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.35586524009705</t>
   </si>
   <si>
     <t xml:space="preserve">2.34685611724854</t>
   </si>
   <si>
-    <t xml:space="preserve">2.34935879707336</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.34034991264343</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.3863959312439</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.39440393447876</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.34785723686218</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.30881834030151</t>
+    <t xml:space="preserve">2.34935927391052</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.34034967422485</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.38639616966248</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.39440417289734</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.3478569984436</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.30881762504578</t>
   </si>
   <si>
     <t xml:space="preserve">2.32483386993408</t>
   </si>
   <si>
-    <t xml:space="preserve">2.35686635971069</t>
+    <t xml:space="preserve">2.35686612129211</t>
   </si>
   <si>
     <t xml:space="preserve">2.3153247833252</t>
@@ -1706,70 +1706,70 @@
     <t xml:space="preserve">2.27228140830994</t>
   </si>
   <si>
-    <t xml:space="preserve">2.31832766532898</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.31582427024841</t>
+    <t xml:space="preserve">2.3183274269104</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.31582474708557</t>
   </si>
   <si>
     <t xml:space="preserve">2.34985852241516</t>
   </si>
   <si>
-    <t xml:space="preserve">2.38289213180542</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.35936856269836</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.39290237426758</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.38189101219177</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.29680562019348</t>
+    <t xml:space="preserve">2.38289260864258</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.35936832427979</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.39290189743042</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.38189148902893</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.29680585861206</t>
   </si>
   <si>
     <t xml:space="preserve">2.29079961776733</t>
   </si>
   <si>
-    <t xml:space="preserve">2.29230093955994</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.31232118606567</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.17568397521973</t>
+    <t xml:space="preserve">2.29230117797852</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.31232166290283</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.17568373680115</t>
   </si>
   <si>
     <t xml:space="preserve">2.1511595249176</t>
   </si>
   <si>
-    <t xml:space="preserve">2.12112903594971</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.0685760974884</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.04905724525452</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.04655456542969</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.00200986862183</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.00251054763794</t>
+    <t xml:space="preserve">2.12112927436829</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.06857633590698</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.04905700683594</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.04655504226685</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.00200963020325</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.00251030921936</t>
   </si>
   <si>
     <t xml:space="preserve">2.04705476760864</t>
   </si>
   <si>
-    <t xml:space="preserve">2.04605412483215</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.03003740310669</t>
+    <t xml:space="preserve">2.04605436325073</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.03003787994385</t>
   </si>
   <si>
     <t xml:space="preserve">2.02503299713135</t>
@@ -1778,16 +1778,16 @@
     <t xml:space="preserve">2.01702547073364</t>
   </si>
   <si>
-    <t xml:space="preserve">1.98449194431305</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.99700474739075</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.9219297170639</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.90140914916992</t>
+    <t xml:space="preserve">1.98449206352234</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.99700450897217</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.92192995548248</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.90140891075134</t>
   </si>
   <si>
     <t xml:space="preserve">1.91041815280914</t>
@@ -1805,10 +1805,10 @@
     <t xml:space="preserve">2.12413215637207</t>
   </si>
   <si>
-    <t xml:space="preserve">2.11362218856812</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.11562347412109</t>
+    <t xml:space="preserve">2.11362242698669</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.11562371253967</t>
   </si>
   <si>
     <t xml:space="preserve">2.10861682891846</t>
@@ -1817,10 +1817,10 @@
     <t xml:space="preserve">2.15716600418091</t>
   </si>
   <si>
-    <t xml:space="preserve">2.18969821929932</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.1691780090332</t>
+    <t xml:space="preserve">2.18969798088074</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.16917777061462</t>
   </si>
   <si>
     <t xml:space="preserve">2.12763643264771</t>
@@ -1832,49 +1832,49 @@
     <t xml:space="preserve">2.17868757247925</t>
   </si>
   <si>
-    <t xml:space="preserve">2.20070910453796</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.99600374698639</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.91742515563965</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.88389146327972</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.85936605930328</t>
+    <t xml:space="preserve">2.20070886611938</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.99600338935852</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.91742479801178</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.88389134407043</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.85936641693115</t>
   </si>
   <si>
     <t xml:space="preserve">1.87087833881378</t>
   </si>
   <si>
-    <t xml:space="preserve">1.83684420585632</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.80631351470947</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.77027678489685</t>
+    <t xml:space="preserve">1.83684408664703</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.80631327629089</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.77027690410614</t>
   </si>
   <si>
     <t xml:space="preserve">1.80881559848785</t>
   </si>
   <si>
-    <t xml:space="preserve">1.77478158473969</t>
+    <t xml:space="preserve">1.77478134632111</t>
   </si>
   <si>
     <t xml:space="preserve">1.78829503059387</t>
   </si>
   <si>
-    <t xml:space="preserve">1.8008074760437</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.78529226779938</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.78779470920563</t>
+    <t xml:space="preserve">1.80080759525299</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.78529250621796</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.78779458999634</t>
   </si>
   <si>
     <t xml:space="preserve">1.74925577640533</t>
@@ -1886,130 +1886,130 @@
     <t xml:space="preserve">1.69169843196869</t>
   </si>
   <si>
-    <t xml:space="preserve">1.65516126155853</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.60811400413513</t>
+    <t xml:space="preserve">1.65516138076782</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.60811412334442</t>
   </si>
   <si>
     <t xml:space="preserve">1.64515161514282</t>
   </si>
   <si>
-    <t xml:space="preserve">1.63263916969299</t>
+    <t xml:space="preserve">1.63263928890228</t>
   </si>
   <si>
     <t xml:space="preserve">1.70471143722534</t>
   </si>
   <si>
-    <t xml:space="preserve">1.69470131397247</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.6806868314743</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.69069719314575</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.75926613807678</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.69870519638062</t>
+    <t xml:space="preserve">1.69470107555389</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.68068695068359</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.69069743156433</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.75926601886749</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.69870507717133</t>
   </si>
   <si>
     <t xml:space="preserve">1.6861926317215</t>
   </si>
   <si>
-    <t xml:space="preserve">1.71672344207764</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.72973656654358</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.7452517747879</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.74775445461273</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.69670343399048</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.71071708202362</t>
+    <t xml:space="preserve">1.71672332286835</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.72973644733429</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.74525213241577</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.74775469303131</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.69670367240906</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.7107173204422</t>
   </si>
   <si>
     <t xml:space="preserve">1.67968654632568</t>
   </si>
   <si>
-    <t xml:space="preserve">1.6952018737793</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.67568242549896</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.73624277114868</t>
+    <t xml:space="preserve">1.69520199298859</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.67568230628967</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.73624265193939</t>
   </si>
   <si>
     <t xml:space="preserve">1.74625313282013</t>
   </si>
   <si>
-    <t xml:space="preserve">1.74725437164307</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.84084808826447</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.77628314495087</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.79229938983917</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.80130803585052</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.88439190387726</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.85235929489136</t>
+    <t xml:space="preserve">1.74725425243378</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.84084820747375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.77628302574158</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.79229927062988</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.8013082742691</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.88439202308655</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.85235953330994</t>
   </si>
   <si>
     <t xml:space="preserve">1.88689422607422</t>
   </si>
   <si>
-    <t xml:space="preserve">1.82683396339417</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.79780471324921</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.76727426052094</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.75025713443756</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.74325037002563</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.71622288227081</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.68268930912018</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.67468106746674</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.70871555805206</t>
+    <t xml:space="preserve">1.82683408260345</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.7978048324585</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.76727414131165</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.75025701522827</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.74325025081635</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.71622276306152</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.68268942832947</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.6746814250946</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.70871531963348</t>
   </si>
   <si>
     <t xml:space="preserve">1.67618227005005</t>
   </si>
   <si>
-    <t xml:space="preserve">1.66366994380951</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.6411474943161</t>
+    <t xml:space="preserve">1.6636700630188</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.64114785194397</t>
   </si>
   <si>
     <t xml:space="preserve">1.68369054794312</t>
@@ -2018,19 +2018,19 @@
     <t xml:space="preserve">1.64965629577637</t>
   </si>
   <si>
-    <t xml:space="preserve">1.63864481449127</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.69369983673096</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.70421099662781</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.66667330265045</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.65966582298279</t>
+    <t xml:space="preserve">1.63864505290985</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.69369995594025</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.70421075820923</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.66667342185974</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.65966594219208</t>
   </si>
   <si>
     <t xml:space="preserve">1.66467106342316</t>
@@ -2042,13 +2042,13 @@
     <t xml:space="preserve">1.57357931137085</t>
   </si>
   <si>
-    <t xml:space="preserve">1.49900484085083</t>
+    <t xml:space="preserve">1.49900472164154</t>
   </si>
   <si>
     <t xml:space="preserve">1.53203785419464</t>
   </si>
   <si>
-    <t xml:space="preserve">1.53804397583008</t>
+    <t xml:space="preserve">1.53804409503937</t>
   </si>
   <si>
     <t xml:space="preserve">1.52903497219086</t>
@@ -2057,10 +2057,10 @@
     <t xml:space="preserve">1.53704285621643</t>
   </si>
   <si>
-    <t xml:space="preserve">1.52853429317474</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.50601172447205</t>
+    <t xml:space="preserve">1.52853417396545</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.50601160526276</t>
   </si>
   <si>
     <t xml:space="preserve">1.51051616668701</t>
@@ -2069,28 +2069,28 @@
     <t xml:space="preserve">1.57658278942108</t>
   </si>
   <si>
-    <t xml:space="preserve">1.55756330490112</t>
+    <t xml:space="preserve">1.5575635433197</t>
   </si>
   <si>
     <t xml:space="preserve">1.56156718730927</t>
   </si>
   <si>
-    <t xml:space="preserve">1.57508099079132</t>
+    <t xml:space="preserve">1.57508087158203</t>
   </si>
   <si>
     <t xml:space="preserve">1.47948551177979</t>
   </si>
   <si>
-    <t xml:space="preserve">1.4839893579483</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.48649227619171</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.48899447917938</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.52402985095978</t>
+    <t xml:space="preserve">1.48398947715759</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.48649215698242</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.48899435997009</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.52402973175049</t>
   </si>
   <si>
     <t xml:space="preserve">1.50851440429688</t>
@@ -2102,127 +2102,127 @@
     <t xml:space="preserve">1.70971667766571</t>
   </si>
   <si>
-    <t xml:space="preserve">1.69219875335693</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.68569207191467</t>
+    <t xml:space="preserve">1.69219899177551</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.68569219112396</t>
   </si>
   <si>
     <t xml:space="preserve">1.76377069950104</t>
   </si>
   <si>
-    <t xml:space="preserve">1.75676417350769</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.74174857139587</t>
+    <t xml:space="preserve">1.75676393508911</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.74174845218658</t>
   </si>
   <si>
     <t xml:space="preserve">1.71372056007385</t>
   </si>
   <si>
-    <t xml:space="preserve">1.73374056816101</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.75125849246979</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.76276934146881</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.81031739711761</t>
+    <t xml:space="preserve">1.73374044895172</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.75125789642334</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.76276957988739</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.8103175163269</t>
   </si>
   <si>
     <t xml:space="preserve">1.8508574962616</t>
   </si>
   <si>
-    <t xml:space="preserve">1.84585297107697</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.83984708786011</t>
+    <t xml:space="preserve">1.84585332870483</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.83984696865082</t>
   </si>
   <si>
     <t xml:space="preserve">1.85486257076263</t>
   </si>
   <si>
-    <t xml:space="preserve">1.80030679702759</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.78178894519806</t>
+    <t xml:space="preserve">1.80030727386475</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.78178906440735</t>
   </si>
   <si>
     <t xml:space="preserve">1.77077746391296</t>
   </si>
   <si>
-    <t xml:space="preserve">1.78128826618195</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.81732392311096</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.85386109352112</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.86787462234497</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.86837518215179</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.85185897350311</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.82633316516876</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.81882560253143</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.80331075191498</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.83183896541595</t>
+    <t xml:space="preserve">1.78128838539124</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.81732439994812</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.8538613319397</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.86787486076355</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.86837553977966</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.85185921192169</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.82633328437805</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.8188259601593</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.80331063270569</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.83183932304382</t>
   </si>
   <si>
     <t xml:space="preserve">1.8243316411972</t>
   </si>
   <si>
-    <t xml:space="preserve">1.82232916355133</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.84735441207886</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.83334076404572</t>
+    <t xml:space="preserve">1.82232940196991</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.84735453128815</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.83334064483643</t>
   </si>
   <si>
     <t xml:space="preserve">1.85135817527771</t>
   </si>
   <si>
-    <t xml:space="preserve">1.85336053371429</t>
+    <t xml:space="preserve">1.853360414505</t>
   </si>
   <si>
     <t xml:space="preserve">1.86937665939331</t>
   </si>
   <si>
-    <t xml:space="preserve">1.8703773021698</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.89990723133087</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.9354430437088</t>
+    <t xml:space="preserve">1.87037765979767</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.89990758895874</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.93544340133667</t>
   </si>
   <si>
     <t xml:space="preserve">1.98649442195892</t>
   </si>
   <si>
-    <t xml:space="preserve">2.02002835273743</t>
+    <t xml:space="preserve">2.02002811431885</t>
   </si>
   <si>
     <t xml:space="preserve">2.07358145713806</t>
   </si>
   <si>
-    <t xml:space="preserve">2.0936017036438</t>
+    <t xml:space="preserve">2.09360218048096</t>
   </si>
   <si>
     <t xml:space="preserve">2.07308077812195</t>
@@ -2231,28 +2231,28 @@
     <t xml:space="preserve">2.05506348609924</t>
   </si>
   <si>
-    <t xml:space="preserve">2.08859658241272</t>
+    <t xml:space="preserve">2.08859705924988</t>
   </si>
   <si>
     <t xml:space="preserve">2.10561418533325</t>
   </si>
   <si>
-    <t xml:space="preserve">2.11161971092224</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.14415264129639</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.1096179485321</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.10311079025269</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.05956768989563</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.04805612564087</t>
+    <t xml:space="preserve">2.11161947250366</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.14415287971497</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.10961771011353</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.10311126708984</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.05956792831421</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.04805588722229</t>
   </si>
   <si>
     <t xml:space="preserve">2.00401210784912</t>
@@ -2267,7 +2267,7 @@
     <t xml:space="preserve">1.96947741508484</t>
   </si>
   <si>
-    <t xml:space="preserve">1.93494248390198</t>
+    <t xml:space="preserve">1.93494260311127</t>
   </si>
   <si>
     <t xml:space="preserve">1.97848665714264</t>
@@ -2276,58 +2276,58 @@
     <t xml:space="preserve">1.92558348178864</t>
   </si>
   <si>
-    <t xml:space="preserve">1.87486898899078</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.83502221107483</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.8107008934021</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.82933056354523</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.780686378479</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.78172075748444</t>
+    <t xml:space="preserve">1.87486910820007</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.83502209186554</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.81070041656494</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.82933032512665</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.78068614006042</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.78172063827515</t>
   </si>
   <si>
     <t xml:space="preserve">1.77240633964539</t>
   </si>
   <si>
-    <t xml:space="preserve">1.75998604297638</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.7511887550354</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.73721623420715</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.76774895191193</t>
+    <t xml:space="preserve">1.75998616218567</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.75118863582611</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.73721635341644</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.76774907112122</t>
   </si>
   <si>
     <t xml:space="preserve">1.73566436767578</t>
   </si>
   <si>
-    <t xml:space="preserve">1.71496486663818</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.71185946464539</t>
+    <t xml:space="preserve">1.71496498584747</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.7118593454361</t>
   </si>
   <si>
     <t xml:space="preserve">1.76567888259888</t>
   </si>
   <si>
-    <t xml:space="preserve">1.78223824501038</t>
+    <t xml:space="preserve">1.78223812580109</t>
   </si>
   <si>
     <t xml:space="preserve">1.76205635070801</t>
   </si>
   <si>
-    <t xml:space="preserve">1.78327322006226</t>
+    <t xml:space="preserve">1.78327333927155</t>
   </si>
   <si>
     <t xml:space="preserve">1.7770631313324</t>
@@ -2339,58 +2339,58 @@
     <t xml:space="preserve">1.83088254928589</t>
   </si>
   <si>
-    <t xml:space="preserve">1.86503732204437</t>
+    <t xml:space="preserve">1.86503744125366</t>
   </si>
   <si>
     <t xml:space="preserve">1.86296713352203</t>
   </si>
   <si>
-    <t xml:space="preserve">1.89453423023224</t>
+    <t xml:space="preserve">1.89453387260437</t>
   </si>
   <si>
     <t xml:space="preserve">1.87383484840393</t>
   </si>
   <si>
-    <t xml:space="preserve">1.87279951572418</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.88366603851318</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.85416972637177</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.84433722496033</t>
+    <t xml:space="preserve">1.8727992773056</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.88366651535034</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.85416984558105</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.84433710575104</t>
   </si>
   <si>
     <t xml:space="preserve">1.88211441040039</t>
   </si>
   <si>
-    <t xml:space="preserve">1.95559787750244</t>
+    <t xml:space="preserve">1.95559811592102</t>
   </si>
   <si>
     <t xml:space="preserve">2.01252198219299</t>
   </si>
   <si>
-    <t xml:space="preserve">2.01666188240051</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.99854946136475</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.99026966094971</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.97371029853821</t>
+    <t xml:space="preserve">2.01666164398193</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.99854958057404</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.99026989936829</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.97371017932892</t>
   </si>
   <si>
     <t xml:space="preserve">1.98250734806061</t>
   </si>
   <si>
-    <t xml:space="preserve">1.96853530406952</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.99647986888885</t>
+    <t xml:space="preserve">1.96853518486023</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.99647974967957</t>
   </si>
   <si>
     <t xml:space="preserve">1.96439528465271</t>
@@ -2399,31 +2399,31 @@
     <t xml:space="preserve">1.93955600261688</t>
   </si>
   <si>
-    <t xml:space="preserve">1.94576525688171</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.93541610240936</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.88625419139862</t>
+    <t xml:space="preserve">1.94576549530029</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.93541646003723</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.8862544298172</t>
   </si>
   <si>
     <t xml:space="preserve">1.87072920799255</t>
   </si>
   <si>
-    <t xml:space="preserve">1.85106515884399</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.82570719718933</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.7542941570282</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.7434264421463</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.79000127315521</t>
+    <t xml:space="preserve">1.85106539726257</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.82570743560791</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.75429439544678</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.74342632293701</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.79000091552734</t>
   </si>
   <si>
     <t xml:space="preserve">1.76257395744324</t>
@@ -2432,37 +2432,37 @@
     <t xml:space="preserve">1.78948354721069</t>
   </si>
   <si>
-    <t xml:space="preserve">1.76464319229126</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.79828059673309</t>
+    <t xml:space="preserve">1.76464331150055</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.79828083515167</t>
   </si>
   <si>
     <t xml:space="preserve">1.65597057342529</t>
   </si>
   <si>
-    <t xml:space="preserve">1.62078130245209</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.6394110918045</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.55868220329285</t>
+    <t xml:space="preserve">1.62078142166138</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.63941144943237</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.55868232250214</t>
   </si>
   <si>
     <t xml:space="preserve">1.59283673763275</t>
   </si>
   <si>
-    <t xml:space="preserve">1.60887956619263</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.55764722824097</t>
+    <t xml:space="preserve">1.60887920856476</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.55764710903168</t>
   </si>
   <si>
     <t xml:space="preserve">1.58455681800842</t>
   </si>
   <si>
-    <t xml:space="preserve">1.59076726436615</t>
+    <t xml:space="preserve">1.59076702594757</t>
   </si>
   <si>
     <t xml:space="preserve">1.57731223106384</t>
@@ -2480,10 +2480,10 @@
     <t xml:space="preserve">1.68132770061493</t>
   </si>
   <si>
-    <t xml:space="preserve">1.66787266731262</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.6714950799942</t>
+    <t xml:space="preserve">1.66787278652191</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.67149531841278</t>
   </si>
   <si>
     <t xml:space="preserve">1.69943988323212</t>
@@ -2492,49 +2492,49 @@
     <t xml:space="preserve">1.71651697158813</t>
   </si>
   <si>
-    <t xml:space="preserve">1.72169196605682</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.72997164726257</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.78844857215881</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.80863034725189</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.79103565216064</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.81846284866333</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.86451995372772</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.87331688404083</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.8122524023056</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.82311999797821</t>
+    <t xml:space="preserve">1.72169184684753</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.72997176647186</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.78844845294952</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.8086302280426</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.79103553295135</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.81846272945404</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.86451971530914</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.87331712245941</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.81225252151489</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.82312023639679</t>
   </si>
   <si>
     <t xml:space="preserve">1.90281403064728</t>
   </si>
   <si>
-    <t xml:space="preserve">1.84588992595673</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.81794500350952</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.79879868030548</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.80966532230377</t>
+    <t xml:space="preserve">1.84589004516602</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.81794512271881</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.79879856109619</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.80966544151306</t>
   </si>
   <si>
     <t xml:space="preserve">1.83295249938965</t>
@@ -2543,40 +2543,40 @@
     <t xml:space="preserve">1.80500793457031</t>
   </si>
   <si>
-    <t xml:space="preserve">1.8158757686615</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.7993152141571</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.80552542209625</t>
+    <t xml:space="preserve">1.81587553024292</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.79931533336639</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.80552554130554</t>
   </si>
   <si>
     <t xml:space="preserve">1.81639313697815</t>
   </si>
   <si>
-    <t xml:space="preserve">1.8826322555542</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.90333127975464</t>
+    <t xml:space="preserve">1.88263165950775</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.90333151817322</t>
   </si>
   <si>
     <t xml:space="preserve">1.94421339035034</t>
   </si>
   <si>
-    <t xml:space="preserve">1.97267484664917</t>
+    <t xml:space="preserve">1.97267496585846</t>
   </si>
   <si>
     <t xml:space="preserve">2.02649426460266</t>
   </si>
   <si>
-    <t xml:space="preserve">2.07927799224854</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.10204815864563</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.12999176979065</t>
+    <t xml:space="preserve">2.07927846908569</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.10204792022705</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.12999200820923</t>
   </si>
   <si>
     <t xml:space="preserve">2.09066295623779</t>
@@ -2585,10 +2585,10 @@
     <t xml:space="preserve">2.08962845802307</t>
   </si>
   <si>
-    <t xml:space="preserve">2.10515260696411</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.10567045211792</t>
+    <t xml:space="preserve">2.10515284538269</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.10566997528076</t>
   </si>
   <si>
     <t xml:space="preserve">2.06582355499268</t>
@@ -2600,28 +2600,28 @@
     <t xml:space="preserve">2.06996321678162</t>
   </si>
   <si>
-    <t xml:space="preserve">2.13671970367432</t>
+    <t xml:space="preserve">2.1367199420929</t>
   </si>
   <si>
     <t xml:space="preserve">2.16155910491943</t>
   </si>
   <si>
-    <t xml:space="preserve">2.17604899406433</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.20761632919312</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.18329358100891</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.21951794624329</t>
+    <t xml:space="preserve">2.17604923248291</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.20761609077454</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.18329334259033</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.21951818466187</t>
   </si>
   <si>
     <t xml:space="preserve">2.23556017875671</t>
   </si>
   <si>
-    <t xml:space="preserve">2.25056791305542</t>
+    <t xml:space="preserve">2.25056767463684</t>
   </si>
   <si>
     <t xml:space="preserve">2.24280548095703</t>
@@ -2636,46 +2636,46 @@
     <t xml:space="preserve">2.35303092002869</t>
   </si>
   <si>
-    <t xml:space="preserve">2.38459825515747</t>
+    <t xml:space="preserve">2.38459801673889</t>
   </si>
   <si>
     <t xml:space="preserve">2.37114334106445</t>
   </si>
   <si>
-    <t xml:space="preserve">2.3142192363739</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.32715654373169</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.32146382331848</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.3007640838623</t>
+    <t xml:space="preserve">2.31421971321106</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.32715630531311</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.32146406173706</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.30076479911804</t>
   </si>
   <si>
     <t xml:space="preserve">2.27074933052063</t>
   </si>
   <si>
-    <t xml:space="preserve">2.27437281608582</t>
+    <t xml:space="preserve">2.27437257766724</t>
   </si>
   <si>
     <t xml:space="preserve">2.2277979850769</t>
   </si>
   <si>
-    <t xml:space="preserve">2.2443573474884</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.27178478240967</t>
+    <t xml:space="preserve">2.24435758590698</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.27178454399109</t>
   </si>
   <si>
     <t xml:space="preserve">2.28368759155273</t>
   </si>
   <si>
-    <t xml:space="preserve">2.30593943595886</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.27851247787476</t>
+    <t xml:space="preserve">2.30593991279602</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.27851223945618</t>
   </si>
   <si>
     <t xml:space="preserve">2.30283403396606</t>
@@ -2687,19 +2687,19 @@
     <t xml:space="preserve">2.33026146888733</t>
   </si>
   <si>
-    <t xml:space="preserve">2.3131844997406</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.34216356277466</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.35975790023804</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.3369882106781</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.33388376235962</t>
+    <t xml:space="preserve">2.31318426132202</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.34216380119324</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.35975813865662</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.33698844909668</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.3338840007782</t>
   </si>
   <si>
     <t xml:space="preserve">2.30490446090698</t>
@@ -2708,7 +2708,7 @@
     <t xml:space="preserve">2.31991124153137</t>
   </si>
   <si>
-    <t xml:space="preserve">2.37787008285522</t>
+    <t xml:space="preserve">2.37787055969238</t>
   </si>
   <si>
     <t xml:space="preserve">2.37631821632385</t>
@@ -2726,7 +2726,7 @@
     <t xml:space="preserve">2.38873815536499</t>
   </si>
   <si>
-    <t xml:space="preserve">2.39080786705017</t>
+    <t xml:space="preserve">2.39080739021301</t>
   </si>
   <si>
     <t xml:space="preserve">2.38045835494995</t>
@@ -2735,7 +2735,7 @@
     <t xml:space="preserve">2.38822054862976</t>
   </si>
   <si>
-    <t xml:space="preserve">2.36700367927551</t>
+    <t xml:space="preserve">2.36700344085693</t>
   </si>
   <si>
     <t xml:space="preserve">2.36079335212708</t>
@@ -2744,34 +2744,34 @@
     <t xml:space="preserve">2.37942314147949</t>
   </si>
   <si>
-    <t xml:space="preserve">2.36493325233459</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.39494752883911</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.30749177932739</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.30800914764404</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.29351949691772</t>
+    <t xml:space="preserve">2.36493301391602</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.39494729042053</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.30749130249023</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.30800938606262</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.29351925849915</t>
   </si>
   <si>
     <t xml:space="preserve">2.34009408950806</t>
   </si>
   <si>
-    <t xml:space="preserve">2.31939339637756</t>
+    <t xml:space="preserve">2.31939363479614</t>
   </si>
   <si>
     <t xml:space="preserve">2.23866581916809</t>
   </si>
   <si>
-    <t xml:space="preserve">2.14758682250977</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.19157361984253</t>
+    <t xml:space="preserve">2.14758658409119</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.19157338142395</t>
   </si>
   <si>
     <t xml:space="preserve">2.24073505401611</t>
@@ -2786,19 +2786,19 @@
     <t xml:space="preserve">2.25263810157776</t>
   </si>
   <si>
-    <t xml:space="preserve">2.2629873752594</t>
+    <t xml:space="preserve">2.26298713684082</t>
   </si>
   <si>
     <t xml:space="preserve">2.3463032245636</t>
   </si>
   <si>
-    <t xml:space="preserve">2.32612156867981</t>
+    <t xml:space="preserve">2.32612133026123</t>
   </si>
   <si>
     <t xml:space="preserve">2.40322709083557</t>
   </si>
   <si>
-    <t xml:space="preserve">2.14292931556702</t>
+    <t xml:space="preserve">2.14292907714844</t>
   </si>
   <si>
     <t xml:space="preserve">2.13568472862244</t>
@@ -2813,28 +2813,28 @@
     <t xml:space="preserve">1.98509442806244</t>
   </si>
   <si>
-    <t xml:space="preserve">1.98716509342194</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.03115177154541</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.95508050918579</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.86244940757751</t>
+    <t xml:space="preserve">1.98716533184052</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.03115153312683</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.9550803899765</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.86244928836823</t>
   </si>
   <si>
     <t xml:space="preserve">1.72065663337708</t>
   </si>
   <si>
-    <t xml:space="preserve">1.67615222930908</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.61508870124817</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.58093464374542</t>
+    <t xml:space="preserve">1.67615246772766</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.61508882045746</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.58093440532684</t>
   </si>
   <si>
     <t xml:space="preserve">1.36617600917816</t>
@@ -2843,7 +2843,7 @@
     <t xml:space="preserve">1.2999370098114</t>
   </si>
   <si>
-    <t xml:space="preserve">1.30304193496704</t>
+    <t xml:space="preserve">1.30304169654846</t>
   </si>
   <si>
     <t xml:space="preserve">1.07172310352325</t>
@@ -2852,7 +2852,7 @@
     <t xml:space="preserve">1.31183910369873</t>
   </si>
   <si>
-    <t xml:space="preserve">1.21144616603851</t>
+    <t xml:space="preserve">1.21144604682922</t>
   </si>
   <si>
     <t xml:space="preserve">1.20730626583099</t>
@@ -2861,25 +2861,25 @@
     <t xml:space="preserve">1.17522144317627</t>
   </si>
   <si>
-    <t xml:space="preserve">1.19333374500275</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.33253848552704</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.51935303211212</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.55712962150574</t>
+    <t xml:space="preserve">1.19333398342133</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.33253860473633</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.51935315132141</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.55712974071503</t>
   </si>
   <si>
     <t xml:space="preserve">1.53280794620514</t>
   </si>
   <si>
-    <t xml:space="preserve">1.50279366970062</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.40602266788483</t>
+    <t xml:space="preserve">1.50279355049133</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.40602290630341</t>
   </si>
   <si>
     <t xml:space="preserve">1.40550529956818</t>
@@ -2888,7 +2888,7 @@
     <t xml:space="preserve">1.44897425174713</t>
   </si>
   <si>
-    <t xml:space="preserve">1.40705728530884</t>
+    <t xml:space="preserve">1.40705716609955</t>
   </si>
   <si>
     <t xml:space="preserve">1.39567267894745</t>
@@ -2897,16 +2897,16 @@
     <t xml:space="preserve">1.38894486427307</t>
   </si>
   <si>
-    <t xml:space="preserve">1.41585469245911</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.41016256809235</t>
+    <t xml:space="preserve">1.41585457324982</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.41016268730164</t>
   </si>
   <si>
     <t xml:space="preserve">1.34081828594208</t>
   </si>
   <si>
-    <t xml:space="preserve">1.35375547409058</t>
+    <t xml:space="preserve">1.35375571250916</t>
   </si>
   <si>
     <t xml:space="preserve">1.29320931434631</t>
@@ -2915,13 +2915,13 @@
     <t xml:space="preserve">1.1979912519455</t>
   </si>
   <si>
-    <t xml:space="preserve">1.1462424993515</t>
+    <t xml:space="preserve">1.14624226093292</t>
   </si>
   <si>
     <t xml:space="preserve">1.15814447402954</t>
   </si>
   <si>
-    <t xml:space="preserve">1.15917956829071</t>
+    <t xml:space="preserve">1.15917944908142</t>
   </si>
   <si>
     <t xml:space="preserve">1.10898280143738</t>
@@ -2933,118 +2933,118 @@
     <t xml:space="preserve">1.14468967914581</t>
   </si>
   <si>
-    <t xml:space="preserve">1.09708082675934</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.12813007831573</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.19902634620667</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.21817326545715</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.16538918018341</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.14054977893829</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.13847959041595</t>
+    <t xml:space="preserve">1.09708070755005</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.12813019752502</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.19902646541595</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.21817314624786</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.16538894176483</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.140549659729</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.13847947120667</t>
   </si>
   <si>
     <t xml:space="preserve">1.12502467632294</t>
   </si>
   <si>
-    <t xml:space="preserve">1.10639572143555</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.09397506713867</t>
+    <t xml:space="preserve">1.10639560222626</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.09397518634796</t>
   </si>
   <si>
     <t xml:space="preserve">1.08673059940338</t>
   </si>
   <si>
-    <t xml:space="preserve">1.05050599575043</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.04222631454468</t>
+    <t xml:space="preserve">1.05050587654114</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.04222643375397</t>
   </si>
   <si>
     <t xml:space="preserve">1.03860402107239</t>
   </si>
   <si>
-    <t xml:space="preserve">1.08031666278839</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.02012348175049</t>
+    <t xml:space="preserve">1.08031630516052</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.0201233625412</t>
   </si>
   <si>
     <t xml:space="preserve">1.0024346113205</t>
   </si>
   <si>
-    <t xml:space="preserve">0.983425796031952</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.98421847820282</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.986858069896698</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.08982074260712</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.12942171096802</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.17483115196228</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.13364672660828</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.16163063049316</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.18275189399719</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.22076845169067</t>
+    <t xml:space="preserve">0.983426034450531</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.984218418598175</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.986858248710632</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.0898209810257</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.12942183017731</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.17483103275299</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.13364660739899</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.16163086891174</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.1827517747879</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.22076857089996</t>
   </si>
   <si>
     <t xml:space="preserve">1.22129654884338</t>
   </si>
   <si>
-    <t xml:space="preserve">1.34010004997253</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.40504539012909</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.3849812746048</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.31528317928314</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.23132908344269</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.20334422588348</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.21443271636963</t>
+    <t xml:space="preserve">1.34010016918182</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.40504550933838</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.38498115539551</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.31528294086456</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.2313289642334</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.2033439874649</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.21443283557892</t>
   </si>
   <si>
     <t xml:space="preserve">1.29416275024414</t>
   </si>
   <si>
-    <t xml:space="preserve">1.26829016208649</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.2334406375885</t>
+    <t xml:space="preserve">1.26829028129578</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.23344075679779</t>
   </si>
   <si>
     <t xml:space="preserve">1.24611365795135</t>
@@ -3053,10 +3053,10 @@
     <t xml:space="preserve">1.19806385040283</t>
   </si>
   <si>
-    <t xml:space="preserve">1.22763311862946</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.16532647609711</t>
+    <t xml:space="preserve">1.22763299942017</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.16532683372498</t>
   </si>
   <si>
     <t xml:space="preserve">1.17430293560028</t>
@@ -3065,10 +3065,10 @@
     <t xml:space="preserve">1.1473742723465</t>
   </si>
   <si>
-    <t xml:space="preserve">1.16796720027924</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.1452624797821</t>
+    <t xml:space="preserve">1.16796731948853</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.14526259899139</t>
   </si>
   <si>
     <t xml:space="preserve">1.15371072292328</t>
@@ -3077,10 +3077,10 @@
     <t xml:space="preserve">1.14843046665192</t>
   </si>
   <si>
-    <t xml:space="preserve">1.18327927589417</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.17007887363434</t>
+    <t xml:space="preserve">1.18327915668488</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.17007875442505</t>
   </si>
   <si>
     <t xml:space="preserve">1.16479957103729</t>
@@ -3089,25 +3089,25 @@
     <t xml:space="preserve">1.13417398929596</t>
   </si>
   <si>
-    <t xml:space="preserve">1.19120001792908</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.31581115722656</t>
+    <t xml:space="preserve">1.19120013713837</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.31581103801727</t>
   </si>
   <si>
     <t xml:space="preserve">1.31686747074127</t>
   </si>
   <si>
-    <t xml:space="preserve">1.32373118400574</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.34115552902222</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.31317150592804</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.35858082771301</t>
+    <t xml:space="preserve">1.32373094558716</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.34115564823151</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.31317114830017</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.35858058929443</t>
   </si>
   <si>
     <t xml:space="preserve">1.34590768814087</t>
@@ -3119,7 +3119,7 @@
     <t xml:space="preserve">1.27990615367889</t>
   </si>
   <si>
-    <t xml:space="preserve">1.22657692432404</t>
+    <t xml:space="preserve">1.22657680511475</t>
   </si>
   <si>
     <t xml:space="preserve">1.23027288913727</t>
@@ -3128,19 +3128,19 @@
     <t xml:space="preserve">1.19067203998566</t>
   </si>
   <si>
-    <t xml:space="preserve">1.17588722705841</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.12572574615479</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.09668552875519</t>
+    <t xml:space="preserve">1.1758873462677</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.12572586536407</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.0966854095459</t>
   </si>
   <si>
     <t xml:space="preserve">1.08242893218994</t>
   </si>
   <si>
-    <t xml:space="preserve">1.14790236949921</t>
+    <t xml:space="preserve">1.14790225028992</t>
   </si>
   <si>
     <t xml:space="preserve">1.23555314540863</t>
@@ -3149,103 +3149,103 @@
     <t xml:space="preserve">1.25139319896698</t>
   </si>
   <si>
-    <t xml:space="preserve">1.25244951248169</t>
+    <t xml:space="preserve">1.2524493932724</t>
   </si>
   <si>
     <t xml:space="preserve">1.2228809595108</t>
   </si>
   <si>
-    <t xml:space="preserve">1.22604882717133</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.23713731765747</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.21707248687744</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.2038722038269</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.24030542373657</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.23977720737457</t>
+    <t xml:space="preserve">1.22604870796204</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.23713743686676</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.21707260608673</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.20387232303619</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.24030530452728</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.23977708816528</t>
   </si>
   <si>
     <t xml:space="preserve">1.23080098628998</t>
   </si>
   <si>
-    <t xml:space="preserve">1.25667357444763</t>
+    <t xml:space="preserve">1.25667345523834</t>
   </si>
   <si>
     <t xml:space="preserve">1.2149600982666</t>
   </si>
   <si>
-    <t xml:space="preserve">1.18222391605377</t>
+    <t xml:space="preserve">1.18222367763519</t>
   </si>
   <si>
     <t xml:space="preserve">1.17905509471893</t>
   </si>
   <si>
-    <t xml:space="preserve">1.14156663417816</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.15265440940857</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.14684689044952</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.11569333076477</t>
+    <t xml:space="preserve">1.14156651496887</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.15265464782715</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.14684700965881</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.11569321155548</t>
   </si>
   <si>
     <t xml:space="preserve">1.13100624084473</t>
   </si>
   <si>
-    <t xml:space="preserve">1.16004729270935</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.1568785905838</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.15635061264038</t>
+    <t xml:space="preserve">1.16004717350006</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.15687847137451</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.15635049343109</t>
   </si>
   <si>
     <t xml:space="preserve">1.14209485054016</t>
   </si>
   <si>
-    <t xml:space="preserve">1.15054285526276</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.14051055908203</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.09404492378235</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.06447660923004</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.06658804416656</t>
+    <t xml:space="preserve">1.15054273605347</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.14051043987274</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.09404504299164</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.06447649002075</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.06658792495728</t>
   </si>
   <si>
     <t xml:space="preserve">1.03490722179413</t>
   </si>
   <si>
-    <t xml:space="preserve">1.03226733207703</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.05919623374939</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.0296276807785</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.04969167709351</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.02857148647308</t>
+    <t xml:space="preserve">1.03226757049561</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.0591961145401</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.02962791919708</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.0496917963028</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.02857160568237</t>
   </si>
   <si>
     <t xml:space="preserve">1.00058650970459</t>
@@ -3254,115 +3254,115 @@
     <t xml:space="preserve">0.926720380783081</t>
   </si>
   <si>
-    <t xml:space="preserve">0.965333759784698</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.924770176410675</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.93335098028183</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.938031375408173</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.914239346981049</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.867435276508331</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.870945572853088</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.866265177726746</t>
+    <t xml:space="preserve">0.965333819389343</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.92477023601532</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.933351039886475</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.938031494617462</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.914239406585693</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.867435216903687</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.870945692062378</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.86626523733139</t>
   </si>
   <si>
     <t xml:space="preserve">0.936471343040466</t>
   </si>
   <si>
-    <t xml:space="preserve">0.9239901304245</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.01408791542053</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.949342370033264</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.925550282001495</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.938811600208282</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.929450631141663</t>
+    <t xml:space="preserve">0.923990070819855</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.01408803462982</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.949342429637909</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.92555034160614</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.938811480998993</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.929450571537018</t>
   </si>
   <si>
     <t xml:space="preserve">0.871335625648499</t>
   </si>
   <si>
-    <t xml:space="preserve">0.808540046215057</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.798399209976196</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.793328762054443</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.822971343994141</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.844033300876617</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.863534927368164</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.844813287258148</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.817510902881622</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.939201533794403</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.931400835514069</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.966503739356995</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.02929925918579</t>
+    <t xml:space="preserve">0.808540225028992</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.798399329185486</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.793328881263733</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.822971403598785</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.844033241271973</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.863534986972809</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.844813227653503</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.817510962486267</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.939201474189758</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.931400775909424</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.966503858566284</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.02929937839508</t>
   </si>
   <si>
     <t xml:space="preserve">1.04139029979706</t>
   </si>
   <si>
-    <t xml:space="preserve">1.10496580600739</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.11198651790619</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.15801048278809</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.18258261680603</t>
+    <t xml:space="preserve">1.10496604442596</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.1119863986969</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.15801060199738</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.18258273601532</t>
   </si>
   <si>
     <t xml:space="preserve">1.1853129863739</t>
   </si>
   <si>
-    <t xml:space="preserve">1.18921327590942</t>
+    <t xml:space="preserve">1.18921315670013</t>
   </si>
   <si>
     <t xml:space="preserve">1.1584005355835</t>
   </si>
   <si>
-    <t xml:space="preserve">1.17868232727051</t>
+    <t xml:space="preserve">1.17868220806122</t>
   </si>
   <si>
     <t xml:space="preserve">1.14279913902283</t>
@@ -3380,31 +3380,31 @@
     <t xml:space="preserve">1.1486496925354</t>
   </si>
   <si>
-    <t xml:space="preserve">1.14240920543671</t>
+    <t xml:space="preserve">1.14240896701813</t>
   </si>
   <si>
     <t xml:space="preserve">1.15020978450775</t>
   </si>
   <si>
-    <t xml:space="preserve">1.18336272239685</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.14435923099518</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.14162921905518</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.15254998207092</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.13694870471954</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.14396929740906</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.13265824317932</t>
+    <t xml:space="preserve">1.18336260318756</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.14435946941376</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.1416289806366</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.15254986286163</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.13694858551025</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.14396941661835</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.13265812397003</t>
   </si>
   <si>
     <t xml:space="preserve">1.08702433109283</t>
@@ -3413,31 +3413,31 @@
     <t xml:space="preserve">1.11159646511078</t>
   </si>
   <si>
-    <t xml:space="preserve">1.15450012683868</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.17010152339935</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.1619108915329</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.14045906066895</t>
+    <t xml:space="preserve">1.15450024604797</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.17010164260864</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.16191077232361</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.14045894145966</t>
   </si>
   <si>
     <t xml:space="preserve">1.14981973171234</t>
   </si>
   <si>
-    <t xml:space="preserve">1.2110550403595</t>
+    <t xml:space="preserve">1.21105515956879</t>
   </si>
   <si>
     <t xml:space="preserve">1.28594160079956</t>
   </si>
   <si>
-    <t xml:space="preserve">1.27151048183441</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.29764258861542</t>
+    <t xml:space="preserve">1.27151036262512</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.29764246940613</t>
   </si>
   <si>
     <t xml:space="preserve">1.29959273338318</t>
@@ -3449,7 +3449,7 @@
     <t xml:space="preserve">1.26331973075867</t>
   </si>
   <si>
-    <t xml:space="preserve">1.25512874126434</t>
+    <t xml:space="preserve">1.25512897968292</t>
   </si>
   <si>
     <t xml:space="preserve">1.28282129764557</t>
@@ -3458,7 +3458,7 @@
     <t xml:space="preserve">1.26448976993561</t>
   </si>
   <si>
-    <t xml:space="preserve">1.28633165359497</t>
+    <t xml:space="preserve">1.28633153438568</t>
   </si>
   <si>
     <t xml:space="preserve">1.26370966434479</t>
@@ -3470,25 +3470,25 @@
     <t xml:space="preserve">1.19194340705872</t>
   </si>
   <si>
-    <t xml:space="preserve">1.2250964641571</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.18882322311401</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.21573543548584</t>
+    <t xml:space="preserve">1.22509634494781</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.18882310390472</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.21573555469513</t>
   </si>
   <si>
     <t xml:space="preserve">1.19584369659424</t>
   </si>
   <si>
-    <t xml:space="preserve">1.20442450046539</t>
+    <t xml:space="preserve">1.20442461967468</t>
   </si>
   <si>
     <t xml:space="preserve">1.32455492019653</t>
   </si>
   <si>
-    <t xml:space="preserve">1.38696026802063</t>
+    <t xml:space="preserve">1.38696038722992</t>
   </si>
   <si>
     <t xml:space="preserve">1.48953926563263</t>
@@ -3500,7 +3500,7 @@
     <t xml:space="preserve">1.48212873935699</t>
   </si>
   <si>
-    <t xml:space="preserve">1.45521628856659</t>
+    <t xml:space="preserve">1.45521605014801</t>
   </si>
   <si>
     <t xml:space="preserve">1.45248603820801</t>
@@ -3509,22 +3509,22 @@
     <t xml:space="preserve">1.46886742115021</t>
   </si>
   <si>
-    <t xml:space="preserve">1.44741559028625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.42089319229126</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.3963211774826</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.45170593261719</t>
+    <t xml:space="preserve">1.44741570949554</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.42089331150055</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.39632105827332</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.45170605182648</t>
   </si>
   <si>
     <t xml:space="preserve">1.43064415454865</t>
   </si>
   <si>
-    <t xml:space="preserve">1.43025422096252</t>
+    <t xml:space="preserve">1.43025410175323</t>
   </si>
   <si>
     <t xml:space="preserve">1.45326614379883</t>
@@ -3533,10 +3533,10 @@
     <t xml:space="preserve">1.41543281078339</t>
   </si>
   <si>
-    <t xml:space="preserve">1.45287597179413</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.43766474723816</t>
+    <t xml:space="preserve">1.45287609100342</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.43766498565674</t>
   </si>
   <si>
     <t xml:space="preserve">1.44624531269073</t>
@@ -3551,16 +3551,16 @@
     <t xml:space="preserve">1.54102373123169</t>
   </si>
   <si>
-    <t xml:space="preserve">1.52815270423889</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.53673326969147</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.51879179477692</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.55233466625214</t>
+    <t xml:space="preserve">1.5281525850296</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.53673350811005</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.51879167556763</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.55233454704285</t>
   </si>
   <si>
     <t xml:space="preserve">1.60069894790649</t>
@@ -3575,10 +3575,10 @@
     <t xml:space="preserve">1.48758912086487</t>
   </si>
   <si>
-    <t xml:space="preserve">1.48602879047394</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.50670063495636</t>
+    <t xml:space="preserve">1.48602890968323</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.50670075416565</t>
   </si>
   <si>
     <t xml:space="preserve">1.4953898191452</t>
@@ -3590,10 +3590,10 @@
     <t xml:space="preserve">1.48056852817535</t>
   </si>
   <si>
-    <t xml:space="preserve">1.48173868656158</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.46379685401917</t>
+    <t xml:space="preserve">1.48173856735229</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.46379697322845</t>
   </si>
   <si>
     <t xml:space="preserve">1.48329865932465</t>
@@ -3602,7 +3602,7 @@
     <t xml:space="preserve">1.48134863376617</t>
   </si>
   <si>
-    <t xml:space="preserve">1.47510814666748</t>
+    <t xml:space="preserve">1.4751079082489</t>
   </si>
   <si>
     <t xml:space="preserve">1.45014584064484</t>
@@ -3611,22 +3611,22 @@
     <t xml:space="preserve">1.45872664451599</t>
   </si>
   <si>
-    <t xml:space="preserve">1.48485887050629</t>
+    <t xml:space="preserve">1.484858751297</t>
   </si>
   <si>
     <t xml:space="preserve">1.46808743476868</t>
   </si>
   <si>
-    <t xml:space="preserve">1.47666811943054</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.4754980802536</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.5219122171402</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.44000494480133</t>
+    <t xml:space="preserve">1.47666823863983</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.47549796104431</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.52191209793091</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.44000482559204</t>
   </si>
   <si>
     <t xml:space="preserve">1.40802216529846</t>
@@ -3635,43 +3635,43 @@
     <t xml:space="preserve">1.41036236286163</t>
   </si>
   <si>
-    <t xml:space="preserve">1.41738307476044</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.46106684207916</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.44507539272308</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.47744822502136</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.46847748756409</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.4622368812561</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.479008436203</t>
+    <t xml:space="preserve">1.41738283634186</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.46106672286987</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.44507527351379</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.47744834423065</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.46847760677338</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.46223700046539</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.47900831699371</t>
   </si>
   <si>
     <t xml:space="preserve">1.50787079334259</t>
   </si>
   <si>
-    <t xml:space="preserve">1.50046014785767</t>
+    <t xml:space="preserve">1.50046026706696</t>
   </si>
   <si>
     <t xml:space="preserve">1.55857527256012</t>
   </si>
   <si>
-    <t xml:space="preserve">1.57261645793915</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.54921436309814</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.56403577327728</t>
+    <t xml:space="preserve">1.57261657714844</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.54921448230743</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.56403565406799</t>
   </si>
   <si>
     <t xml:space="preserve">1.56481575965881</t>
@@ -3683,13 +3683,13 @@
     <t xml:space="preserve">1.54219377040863</t>
   </si>
   <si>
-    <t xml:space="preserve">1.52776265144348</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.55584502220154</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.6557469367981</t>
+    <t xml:space="preserve">1.52776253223419</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.55584514141083</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.65574705600739</t>
   </si>
   <si>
     <t xml:space="preserve">1.6923645734787</t>
@@ -3698,28 +3698,28 @@
     <t xml:space="preserve">1.61116921901703</t>
   </si>
   <si>
-    <t xml:space="preserve">1.63186597824097</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.62151765823364</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.61435329914093</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.61912941932678</t>
+    <t xml:space="preserve">1.63186609745026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.62151753902435</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.6143536567688</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.61912965774536</t>
   </si>
   <si>
     <t xml:space="preserve">1.6270899772644</t>
   </si>
   <si>
-    <t xml:space="preserve">1.61992561817169</t>
+    <t xml:space="preserve">1.61992573738098</t>
   </si>
   <si>
     <t xml:space="preserve">1.60957741737366</t>
   </si>
   <si>
-    <t xml:space="preserve">1.63107025623322</t>
+    <t xml:space="preserve">1.63107001781464</t>
   </si>
   <si>
     <t xml:space="preserve">1.62072169780731</t>
@@ -3737,22 +3737,22 @@
     <t xml:space="preserve">1.62470173835754</t>
   </si>
   <si>
-    <t xml:space="preserve">1.59922885894775</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.57693982124329</t>
+    <t xml:space="preserve">1.59922897815704</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.57693994045258</t>
   </si>
   <si>
     <t xml:space="preserve">1.56539750099182</t>
   </si>
   <si>
-    <t xml:space="preserve">1.52997410297394</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.54470074176788</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.52440178394318</t>
+    <t xml:space="preserve">1.52997398376465</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.54470062255859</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.52440166473389</t>
   </si>
   <si>
     <t xml:space="preserve">1.50410294532776</t>
@@ -3761,13 +3761,13 @@
     <t xml:space="preserve">1.52081966400146</t>
   </si>
   <si>
-    <t xml:space="preserve">1.51405346393585</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.46589350700378</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.45395290851593</t>
+    <t xml:space="preserve">1.51405334472656</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.46589338779449</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.45395278930664</t>
   </si>
   <si>
     <t xml:space="preserve">1.46111714839935</t>
@@ -3779,7 +3779,7 @@
     <t xml:space="preserve">1.4595251083374</t>
   </si>
   <si>
-    <t xml:space="preserve">1.47106766700745</t>
+    <t xml:space="preserve">1.47106754779816</t>
   </si>
   <si>
     <t xml:space="preserve">1.43206202983856</t>
@@ -3791,7 +3791,7 @@
     <t xml:space="preserve">1.37315571308136</t>
   </si>
   <si>
-    <t xml:space="preserve">1.4042010307312</t>
+    <t xml:space="preserve">1.40420091152191</t>
   </si>
   <si>
     <t xml:space="preserve">1.410569190979</t>
@@ -3800,40 +3800,40 @@
     <t xml:space="preserve">1.36240923404694</t>
   </si>
   <si>
-    <t xml:space="preserve">1.35643899440765</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.34529447555542</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.3019106388092</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.23584008216858</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.24579048156738</t>
+    <t xml:space="preserve">1.35643911361694</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.34529459476471</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.30191075801849</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.23584020137787</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.24579060077667</t>
   </si>
   <si>
     <t xml:space="preserve">1.26171112060547</t>
   </si>
   <si>
-    <t xml:space="preserve">1.28400003910065</t>
+    <t xml:space="preserve">1.28399991989136</t>
   </si>
   <si>
     <t xml:space="preserve">1.28519415855408</t>
   </si>
   <si>
-    <t xml:space="preserve">1.30469691753387</t>
+    <t xml:space="preserve">1.30469703674316</t>
   </si>
   <si>
     <t xml:space="preserve">1.28957223892212</t>
   </si>
   <si>
-    <t xml:space="preserve">1.29076623916626</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.29434847831726</t>
+    <t xml:space="preserve">1.29076635837555</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.29434835910797</t>
   </si>
   <si>
     <t xml:space="preserve">1.31066703796387</t>
@@ -3845,25 +3845,25 @@
     <t xml:space="preserve">1.29235827922821</t>
   </si>
   <si>
-    <t xml:space="preserve">1.30071663856506</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.43922638893127</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.43604207038879</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.43046998977661</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.47265958786011</t>
+    <t xml:space="preserve">1.30071675777435</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.43922626972198</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.43604218959808</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.4304701089859</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.4726597070694</t>
   </si>
   <si>
     <t xml:space="preserve">1.46231126785278</t>
   </si>
   <si>
-    <t xml:space="preserve">1.45474910736084</t>
+    <t xml:space="preserve">1.45474898815155</t>
   </si>
   <si>
     <t xml:space="preserve">1.43683815002441</t>
@@ -3875,37 +3875,37 @@
     <t xml:space="preserve">1.42091763019562</t>
   </si>
   <si>
-    <t xml:space="preserve">1.39783263206482</t>
+    <t xml:space="preserve">1.39783275127411</t>
   </si>
   <si>
     <t xml:space="preserve">1.39305651187897</t>
   </si>
   <si>
-    <t xml:space="preserve">1.42290759086609</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.42808198928833</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.45793306827545</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.43882834911346</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.46151518821716</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.44440042972565</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.46668946743011</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.4758437871933</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.4690774679184</t>
+    <t xml:space="preserve">1.42290782928467</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.42808187007904</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.45793318748474</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.43882822990417</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.46151530742645</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.44440054893494</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.46668934822083</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.47584366798401</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.46907758712769</t>
   </si>
   <si>
     <t xml:space="preserve">1.48619222640991</t>
@@ -3914,13 +3914,13 @@
     <t xml:space="preserve">1.44718670845032</t>
   </si>
   <si>
-    <t xml:space="preserve">1.43644022941589</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.45037078857422</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.44201231002808</t>
+    <t xml:space="preserve">1.4364401102066</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.45037066936493</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.44201242923737</t>
   </si>
   <si>
     <t xml:space="preserve">1.44081830978394</t>
@@ -3935,46 +3935,46 @@
     <t xml:space="preserve">1.36519539356232</t>
   </si>
   <si>
-    <t xml:space="preserve">1.40499699115753</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.42449963092804</t>
+    <t xml:space="preserve">1.40499687194824</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.42449975013733</t>
   </si>
   <si>
     <t xml:space="preserve">1.45992314815521</t>
   </si>
   <si>
-    <t xml:space="preserve">1.51604342460632</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.50848114490509</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.54708862304688</t>
+    <t xml:space="preserve">1.51604354381561</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.5084810256958</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.54708874225616</t>
   </si>
   <si>
     <t xml:space="preserve">1.53873026371002</t>
   </si>
   <si>
-    <t xml:space="preserve">1.57574582099915</t>
+    <t xml:space="preserve">1.57574594020844</t>
   </si>
   <si>
     <t xml:space="preserve">1.56261134147644</t>
   </si>
   <si>
-    <t xml:space="preserve">1.61753761768341</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.60002481937408</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.61833369731903</t>
+    <t xml:space="preserve">1.6175377368927</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.60002493858337</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.61833345890045</t>
   </si>
   <si>
     <t xml:space="preserve">1.64380669593811</t>
   </si>
   <si>
-    <t xml:space="preserve">1.64539849758148</t>
+    <t xml:space="preserve">1.64539873600006</t>
   </si>
   <si>
     <t xml:space="preserve">1.63903045654297</t>
@@ -3983,25 +3983,25 @@
     <t xml:space="preserve">1.6398264169693</t>
   </si>
   <si>
-    <t xml:space="preserve">1.64221465587616</t>
+    <t xml:space="preserve">1.64221453666687</t>
   </si>
   <si>
     <t xml:space="preserve">1.65415501594543</t>
   </si>
   <si>
-    <t xml:space="preserve">1.6302741765976</t>
+    <t xml:space="preserve">1.63027405738831</t>
   </si>
   <si>
     <t xml:space="preserve">1.62947809696198</t>
   </si>
   <si>
-    <t xml:space="preserve">1.63345813751221</t>
+    <t xml:space="preserve">1.6334582567215</t>
   </si>
   <si>
     <t xml:space="preserve">1.59365665912628</t>
   </si>
   <si>
-    <t xml:space="preserve">1.61196529865265</t>
+    <t xml:space="preserve">1.61196541786194</t>
   </si>
   <si>
     <t xml:space="preserve">1.50808310508728</t>
@@ -4022,25 +4022,25 @@
     <t xml:space="preserve">1.53196406364441</t>
   </si>
   <si>
-    <t xml:space="preserve">1.52758586406708</t>
+    <t xml:space="preserve">1.52758598327637</t>
   </si>
   <si>
     <t xml:space="preserve">1.52002358436584</t>
   </si>
   <si>
-    <t xml:space="preserve">1.53116798400879</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.52121758460999</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.53315818309784</t>
+    <t xml:space="preserve">1.53116810321808</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.52121770381927</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.53315806388855</t>
   </si>
   <si>
     <t xml:space="preserve">1.51325738430023</t>
   </si>
   <si>
-    <t xml:space="preserve">1.47027146816254</t>
+    <t xml:space="preserve">1.47027158737183</t>
   </si>
   <si>
     <t xml:space="preserve">1.4300719499588</t>
@@ -4061,10 +4061,10 @@
     <t xml:space="preserve">1.34012043476105</t>
   </si>
   <si>
-    <t xml:space="preserve">1.33892631530762</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.37753391265869</t>
+    <t xml:space="preserve">1.33892643451691</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.3775337934494</t>
   </si>
   <si>
     <t xml:space="preserve">1.3643993139267</t>
@@ -4079,13 +4079,13 @@
     <t xml:space="preserve">1.40619099140167</t>
   </si>
   <si>
-    <t xml:space="preserve">1.38191199302673</t>
+    <t xml:space="preserve">1.38191187381744</t>
   </si>
   <si>
     <t xml:space="preserve">1.38907623291016</t>
   </si>
   <si>
-    <t xml:space="preserve">1.37872779369354</t>
+    <t xml:space="preserve">1.37872791290283</t>
   </si>
   <si>
     <t xml:space="preserve">1.47902798652649</t>
@@ -4094,7 +4094,7 @@
     <t xml:space="preserve">1.41614139080048</t>
   </si>
   <si>
-    <t xml:space="preserve">1.41375315189362</t>
+    <t xml:space="preserve">1.41375327110291</t>
   </si>
   <si>
     <t xml:space="preserve">1.37912583351135</t>
@@ -4103,22 +4103,22 @@
     <t xml:space="preserve">1.41494739055634</t>
   </si>
   <si>
-    <t xml:space="preserve">1.40260875225067</t>
+    <t xml:space="preserve">1.40260887145996</t>
   </si>
   <si>
     <t xml:space="preserve">1.42569386959076</t>
   </si>
   <si>
-    <t xml:space="preserve">1.44320642948151</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.45435082912445</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.45116674900055</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.50052094459534</t>
+    <t xml:space="preserve">1.4432065486908</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.45435094833374</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.45116662979126</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.50052070617676</t>
   </si>
   <si>
     <t xml:space="preserve">1.52917790412903</t>
@@ -4127,7 +4127,7 @@
     <t xml:space="preserve">1.52519774436951</t>
   </si>
   <si>
-    <t xml:space="preserve">1.53634214401245</t>
+    <t xml:space="preserve">1.53634226322174</t>
   </si>
   <si>
     <t xml:space="preserve">1.5347501039505</t>
@@ -4148,67 +4148,67 @@
     <t xml:space="preserve">1.49813270568848</t>
   </si>
   <si>
-    <t xml:space="preserve">1.42847979068756</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.42330574989319</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.48818242549896</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.52320778369904</t>
+    <t xml:space="preserve">1.42847990989685</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.4233056306839</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.48818230628967</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.52320766448975</t>
   </si>
   <si>
     <t xml:space="preserve">1.46509730815887</t>
   </si>
   <si>
-    <t xml:space="preserve">1.4762419462204</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.54350662231445</t>
+    <t xml:space="preserve">1.47624182701111</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.54350650310516</t>
   </si>
   <si>
     <t xml:space="preserve">1.57375574111938</t>
   </si>
   <si>
-    <t xml:space="preserve">1.55783522129059</t>
+    <t xml:space="preserve">1.5578351020813</t>
   </si>
   <si>
     <t xml:space="preserve">1.61514949798584</t>
   </si>
   <si>
-    <t xml:space="preserve">1.61276149749756</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.63743817806244</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.57455193996429</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.7186336517334</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.69793665409088</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.60718929767609</t>
+    <t xml:space="preserve">1.61276125907898</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.63743829727173</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.574551820755</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.71863353252411</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.69793677330017</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.60718905925751</t>
   </si>
   <si>
     <t xml:space="preserve">1.56022322177887</t>
   </si>
   <si>
-    <t xml:space="preserve">1.44161438941956</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.46788346767426</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.32260775566101</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.31743335723877</t>
+    <t xml:space="preserve">1.44161427021027</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.46788334846497</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.32260751724243</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.31743323802948</t>
   </si>
   <si>
     <t xml:space="preserve">1.24857664108276</t>
@@ -4217,22 +4217,22 @@
     <t xml:space="preserve">1.11643528938293</t>
   </si>
   <si>
-    <t xml:space="preserve">1.05872285366058</t>
+    <t xml:space="preserve">1.05872297286987</t>
   </si>
   <si>
     <t xml:space="preserve">1.11563920974731</t>
   </si>
   <si>
-    <t xml:space="preserve">1.22708380222321</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.13514196872711</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.12877380847931</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.17494356632233</t>
+    <t xml:space="preserve">1.22708368301392</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.1351420879364</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.12877368927002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.17494344711304</t>
   </si>
   <si>
     <t xml:space="preserve">1.19882464408875</t>
@@ -4247,22 +4247,22 @@
     <t xml:space="preserve">1.2497706413269</t>
   </si>
   <si>
-    <t xml:space="preserve">1.2660893201828</t>
+    <t xml:space="preserve">1.26608943939209</t>
   </si>
   <si>
     <t xml:space="preserve">1.24698448181152</t>
   </si>
   <si>
-    <t xml:space="preserve">1.23464608192444</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.24300420284271</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.25892496109009</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.33295583724976</t>
+    <t xml:space="preserve">1.23464596271515</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.24300444126129</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.25892508029938</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.33295595645905</t>
   </si>
   <si>
     <t xml:space="preserve">1.30668699741364</t>
@@ -4271,10 +4271,10 @@
     <t xml:space="preserve">1.26529335975647</t>
   </si>
   <si>
-    <t xml:space="preserve">1.27922368049622</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.22429752349854</t>
+    <t xml:space="preserve">1.27922379970551</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.22429764270782</t>
   </si>
   <si>
     <t xml:space="preserve">1.22628784179688</t>
@@ -4286,7 +4286,7 @@
     <t xml:space="preserve">1.2728556394577</t>
   </si>
   <si>
-    <t xml:space="preserve">1.23225784301758</t>
+    <t xml:space="preserve">1.23225796222687</t>
   </si>
   <si>
     <t xml:space="preserve">1.23504400253296</t>
@@ -4301,16 +4301,16 @@
     <t xml:space="preserve">1.29753255844116</t>
   </si>
   <si>
-    <t xml:space="preserve">1.30628883838654</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.28758227825165</t>
+    <t xml:space="preserve">1.30628895759583</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.28758203983307</t>
   </si>
   <si>
     <t xml:space="preserve">1.27404952049255</t>
   </si>
   <si>
-    <t xml:space="preserve">1.25932312011719</t>
+    <t xml:space="preserve">1.2593230009079</t>
   </si>
   <si>
     <t xml:space="preserve">1.26847732067108</t>
@@ -4322,19 +4322,19 @@
     <t xml:space="preserve">1.27763175964355</t>
   </si>
   <si>
-    <t xml:space="preserve">1.2692734003067</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.23822820186615</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.21912336349487</t>
+    <t xml:space="preserve">1.26927328109741</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.23822832107544</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.21912324428558</t>
   </si>
   <si>
     <t xml:space="preserve">1.22071540355682</t>
   </si>
   <si>
-    <t xml:space="preserve">1.21116304397583</t>
+    <t xml:space="preserve">1.21116316318512</t>
   </si>
   <si>
     <t xml:space="preserve">1.35325479507446</t>
@@ -4343,7 +4343,7 @@
     <t xml:space="preserve">1.38629019260406</t>
   </si>
   <si>
-    <t xml:space="preserve">1.38668823242188</t>
+    <t xml:space="preserve">1.38668811321259</t>
   </si>
   <si>
     <t xml:space="preserve">1.37395167350769</t>
@@ -4364,7 +4364,7 @@
     <t xml:space="preserve">1.4838342666626</t>
   </si>
   <si>
-    <t xml:space="preserve">1.49949717521667</t>
+    <t xml:space="preserve">1.49949705600739</t>
   </si>
   <si>
     <t xml:space="preserve">1.54153907299042</t>
@@ -4373,22 +4373,22 @@
     <t xml:space="preserve">1.56049907207489</t>
   </si>
   <si>
-    <t xml:space="preserve">1.55390441417694</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.55349206924438</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.57987141609192</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.57616186141968</t>
+    <t xml:space="preserve">1.55390429496765</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.55349218845367</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.57987129688263</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.57616174221039</t>
   </si>
   <si>
     <t xml:space="preserve">1.58976364135742</t>
   </si>
   <si>
-    <t xml:space="preserve">1.53576874732971</t>
+    <t xml:space="preserve">1.53576862812042</t>
   </si>
   <si>
     <t xml:space="preserve">1.59182453155518</t>
@@ -4412,19 +4412,19 @@
     <t xml:space="preserve">1.36430323123932</t>
   </si>
   <si>
-    <t xml:space="preserve">1.41788613796234</t>
+    <t xml:space="preserve">1.41788625717163</t>
   </si>
   <si>
     <t xml:space="preserve">1.35770845413208</t>
   </si>
   <si>
-    <t xml:space="preserve">1.38326334953308</t>
+    <t xml:space="preserve">1.38326323032379</t>
   </si>
   <si>
     <t xml:space="preserve">1.40799391269684</t>
   </si>
   <si>
-    <t xml:space="preserve">1.41458880901337</t>
+    <t xml:space="preserve">1.41458868980408</t>
   </si>
   <si>
     <t xml:space="preserve">1.41252791881561</t>
@@ -4433,13 +4433,13 @@
     <t xml:space="preserve">1.34451878070831</t>
   </si>
   <si>
-    <t xml:space="preserve">1.38820958137512</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.36718857288361</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.36512768268585</t>
+    <t xml:space="preserve">1.38820946216583</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.36718845367432</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.36512756347656</t>
   </si>
   <si>
     <t xml:space="preserve">1.34493100643158</t>
@@ -4448,7 +4448,7 @@
     <t xml:space="preserve">1.2921724319458</t>
   </si>
   <si>
-    <t xml:space="preserve">1.25219130516052</t>
+    <t xml:space="preserve">1.25219142436981</t>
   </si>
   <si>
     <t xml:space="preserve">1.25136709213257</t>
@@ -4457,19 +4457,19 @@
     <t xml:space="preserve">1.18789184093475</t>
   </si>
   <si>
-    <t xml:space="preserve">1.16934382915497</t>
+    <t xml:space="preserve">1.16934394836426</t>
   </si>
   <si>
     <t xml:space="preserve">1.2299337387085</t>
   </si>
   <si>
-    <t xml:space="preserve">1.24477219581604</t>
+    <t xml:space="preserve">1.24477207660675</t>
   </si>
   <si>
     <t xml:space="preserve">1.18830394744873</t>
   </si>
   <si>
-    <t xml:space="preserve">1.1590393781662</t>
+    <t xml:space="preserve">1.15903949737549</t>
   </si>
   <si>
     <t xml:space="preserve">1.128950715065</t>
@@ -4481,7 +4481,7 @@
     <t xml:space="preserve">1.06588768959045</t>
   </si>
   <si>
-    <t xml:space="preserve">1.07990157604218</t>
+    <t xml:space="preserve">1.07990169525146</t>
   </si>
   <si>
     <t xml:space="preserve">1.15326905250549</t>
@@ -4490,19 +4490,19 @@
     <t xml:space="preserve">1.12029492855072</t>
   </si>
   <si>
-    <t xml:space="preserve">1.08526003360748</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.06794857978821</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.09556436538696</t>
+    <t xml:space="preserve">1.08525991439819</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.0679486989975</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.09556448459625</t>
   </si>
   <si>
     <t xml:space="preserve">1.06506335735321</t>
   </si>
   <si>
-    <t xml:space="preserve">1.08567214012146</t>
+    <t xml:space="preserve">1.08567225933075</t>
   </si>
   <si>
     <t xml:space="preserve">1.08814525604248</t>
@@ -4517,19 +4517,19 @@
     <t xml:space="preserve">1.14337682723999</t>
   </si>
   <si>
-    <t xml:space="preserve">1.18912827968597</t>
+    <t xml:space="preserve">1.18912839889526</t>
   </si>
   <si>
     <t xml:space="preserve">1.18129694461823</t>
   </si>
   <si>
-    <t xml:space="preserve">1.29588198661804</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.32720732688904</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.33792412281036</t>
+    <t xml:space="preserve">1.29588210582733</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.32720744609833</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.33792400360107</t>
   </si>
   <si>
     <t xml:space="preserve">1.36842501163483</t>
@@ -4547,19 +4547,19 @@
     <t xml:space="preserve">1.30659854412079</t>
   </si>
   <si>
-    <t xml:space="preserve">1.26290798187256</t>
+    <t xml:space="preserve">1.26290786266327</t>
   </si>
   <si>
     <t xml:space="preserve">1.28063154220581</t>
   </si>
   <si>
-    <t xml:space="preserve">1.28021931648254</t>
+    <t xml:space="preserve">1.28021919727325</t>
   </si>
   <si>
     <t xml:space="preserve">1.26084697246552</t>
   </si>
   <si>
-    <t xml:space="preserve">1.22004151344299</t>
+    <t xml:space="preserve">1.22004163265228</t>
   </si>
   <si>
     <t xml:space="preserve">1.22045373916626</t>
@@ -4568,7 +4568,7 @@
     <t xml:space="preserve">1.24106252193451</t>
   </si>
   <si>
-    <t xml:space="preserve">1.24065041542053</t>
+    <t xml:space="preserve">1.24065029621124</t>
   </si>
   <si>
     <t xml:space="preserve">1.22333908081055</t>
@@ -4589,22 +4589,22 @@
     <t xml:space="preserve">1.23776519298553</t>
   </si>
   <si>
-    <t xml:space="preserve">1.27609741687775</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.33957278728485</t>
+    <t xml:space="preserve">1.27609753608704</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.33957266807556</t>
   </si>
   <si>
     <t xml:space="preserve">1.32597088813782</t>
   </si>
   <si>
-    <t xml:space="preserve">1.3758442401886</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.38120257854462</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.38985812664032</t>
+    <t xml:space="preserve">1.37584435939789</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.38120245933533</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.38985824584961</t>
   </si>
   <si>
     <t xml:space="preserve">1.39686512947083</t>
@@ -4616,7 +4616,7 @@
     <t xml:space="preserve">1.38408768177032</t>
   </si>
   <si>
-    <t xml:space="preserve">1.43025135993958</t>
+    <t xml:space="preserve">1.43025147914886</t>
   </si>
   <si>
     <t xml:space="preserve">1.37337112426758</t>
@@ -4628,31 +4628,31 @@
     <t xml:space="preserve">1.34163355827332</t>
   </si>
   <si>
-    <t xml:space="preserve">1.32020032405853</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.28269243240356</t>
+    <t xml:space="preserve">1.32020044326782</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.28269231319427</t>
   </si>
   <si>
     <t xml:space="preserve">1.30330121517181</t>
   </si>
   <si>
-    <t xml:space="preserve">1.32844400405884</t>
+    <t xml:space="preserve">1.32844388484955</t>
   </si>
   <si>
     <t xml:space="preserve">1.38491201400757</t>
   </si>
   <si>
-    <t xml:space="preserve">1.3589448928833</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.31731534004211</t>
+    <t xml:space="preserve">1.35894501209259</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.31731522083282</t>
   </si>
   <si>
     <t xml:space="preserve">1.33462643623352</t>
   </si>
   <si>
-    <t xml:space="preserve">1.31855165958405</t>
+    <t xml:space="preserve">1.31855154037476</t>
   </si>
   <si>
     <t xml:space="preserve">1.30824732780457</t>
@@ -4673,7 +4673,7 @@
     <t xml:space="preserve">1.41211569309235</t>
   </si>
   <si>
-    <t xml:space="preserve">1.41664958000183</t>
+    <t xml:space="preserve">1.41664969921112</t>
   </si>
   <si>
     <t xml:space="preserve">1.43560981750488</t>
@@ -4682,16 +4682,16 @@
     <t xml:space="preserve">1.4764152765274</t>
   </si>
   <si>
-    <t xml:space="preserve">1.46734738349915</t>
+    <t xml:space="preserve">1.46734726428986</t>
   </si>
   <si>
     <t xml:space="preserve">1.4694082736969</t>
   </si>
   <si>
-    <t xml:space="preserve">1.51103806495667</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.52093017101288</t>
+    <t xml:space="preserve">1.51103794574738</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.52093029022217</t>
   </si>
   <si>
     <t xml:space="preserve">1.54359984397888</t>
@@ -4700,7 +4700,7 @@
     <t xml:space="preserve">1.56214785575867</t>
   </si>
   <si>
-    <t xml:space="preserve">1.58770287036896</t>
+    <t xml:space="preserve">1.58770275115967</t>
   </si>
   <si>
     <t xml:space="preserve">1.58893930912018</t>
@@ -4709,10 +4709,10 @@
     <t xml:space="preserve">1.65942132472992</t>
   </si>
   <si>
-    <t xml:space="preserve">1.68992233276367</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.5600870847702</t>
+    <t xml:space="preserve">1.68992245197296</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.56008696556091</t>
   </si>
   <si>
     <t xml:space="preserve">1.51680850982666</t>
@@ -4724,7 +4724,7 @@
     <t xml:space="preserve">1.52711284160614</t>
   </si>
   <si>
-    <t xml:space="preserve">1.54648506641388</t>
+    <t xml:space="preserve">1.54648518562317</t>
   </si>
   <si>
     <t xml:space="preserve">1.55184352397919</t>
@@ -4736,7 +4736,7 @@
     <t xml:space="preserve">1.57822275161743</t>
   </si>
   <si>
-    <t xml:space="preserve">1.58193230628967</t>
+    <t xml:space="preserve">1.58193242549896</t>
   </si>
   <si>
     <t xml:space="preserve">1.59965598583221</t>
@@ -4748,7 +4748,7 @@
     <t xml:space="preserve">1.62356209754944</t>
   </si>
   <si>
-    <t xml:space="preserve">1.60872387886047</t>
+    <t xml:space="preserve">1.60872375965118</t>
   </si>
   <si>
     <t xml:space="preserve">1.61573076248169</t>
@@ -4757,7 +4757,7 @@
     <t xml:space="preserve">1.62562298774719</t>
   </si>
   <si>
-    <t xml:space="preserve">1.60666298866272</t>
+    <t xml:space="preserve">1.60666286945343</t>
   </si>
   <si>
     <t xml:space="preserve">1.59883153438568</t>
@@ -4766,31 +4766,31 @@
     <t xml:space="preserve">1.59017598628998</t>
   </si>
   <si>
-    <t xml:space="preserve">1.59718298912048</t>
+    <t xml:space="preserve">1.59718286991119</t>
   </si>
   <si>
     <t xml:space="preserve">1.60171675682068</t>
   </si>
   <si>
-    <t xml:space="preserve">1.60954809188843</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.60913586616516</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.61902809143066</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.60707497596741</t>
+    <t xml:space="preserve">1.60954821109772</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.60913598537445</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.61902821063995</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.6070750951767</t>
   </si>
   <si>
     <t xml:space="preserve">1.55101907253265</t>
   </si>
   <si>
-    <t xml:space="preserve">1.54978263378143</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.53782951831818</t>
+    <t xml:space="preserve">1.54978251457214</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.5378292798996</t>
   </si>
   <si>
     <t xml:space="preserve">1.6041898727417</t>
@@ -4799,10 +4799,10 @@
     <t xml:space="preserve">1.60295331478119</t>
   </si>
   <si>
-    <t xml:space="preserve">1.59512186050415</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.5815201997757</t>
+    <t xml:space="preserve">1.59512197971344</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.58152008056641</t>
   </si>
   <si>
     <t xml:space="preserve">1.61531865596771</t>
@@ -4811,19 +4811,19 @@
     <t xml:space="preserve">1.63633954524994</t>
   </si>
   <si>
-    <t xml:space="preserve">1.67920589447021</t>
+    <t xml:space="preserve">1.67920577526093</t>
   </si>
   <si>
     <t xml:space="preserve">1.67343533039093</t>
   </si>
   <si>
-    <t xml:space="preserve">1.71712589263916</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.72536969184875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.73938369750977</t>
+    <t xml:space="preserve">1.71712601184845</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.72536957263947</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.73938357830048</t>
   </si>
   <si>
     <t xml:space="preserve">1.73855924606323</t>
@@ -4832,7 +4832,7 @@
     <t xml:space="preserve">1.74845159053802</t>
   </si>
   <si>
-    <t xml:space="preserve">1.80533182621002</t>
+    <t xml:space="preserve">1.80533170700073</t>
   </si>
   <si>
     <t xml:space="preserve">1.82511639595032</t>
@@ -4850,13 +4850,13 @@
     <t xml:space="preserve">1.89024019241333</t>
   </si>
   <si>
-    <t xml:space="preserve">1.90178108215332</t>
+    <t xml:space="preserve">1.90178084373474</t>
   </si>
   <si>
     <t xml:space="preserve">1.92898464202881</t>
   </si>
   <si>
-    <t xml:space="preserve">1.93310654163361</t>
+    <t xml:space="preserve">1.93310630321503</t>
   </si>
   <si>
     <t xml:space="preserve">1.97349977493286</t>
@@ -4883,13 +4883,13 @@
     <t xml:space="preserve">2.12847781181335</t>
   </si>
   <si>
-    <t xml:space="preserve">2.098801612854</t>
+    <t xml:space="preserve">2.09880137443542</t>
   </si>
   <si>
     <t xml:space="preserve">2.11941027641296</t>
   </si>
   <si>
-    <t xml:space="preserve">2.10457158088684</t>
+    <t xml:space="preserve">2.10457181930542</t>
   </si>
   <si>
     <t xml:space="preserve">2.14991116523743</t>
@@ -4901,13 +4901,13 @@
     <t xml:space="preserve">2.1375458240509</t>
   </si>
   <si>
-    <t xml:space="preserve">2.2043182849884</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.30159211158752</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.26449584960938</t>
+    <t xml:space="preserve">2.20431852340698</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.30159187316895</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.26449608802795</t>
   </si>
   <si>
     <t xml:space="preserve">2.25295519828796</t>
@@ -4931,10 +4931,10 @@
     <t xml:space="preserve">2.19525051116943</t>
   </si>
   <si>
-    <t xml:space="preserve">2.20844006538391</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.22657585144043</t>
+    <t xml:space="preserve">2.20843982696533</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.22657608985901</t>
   </si>
   <si>
     <t xml:space="preserve">2.27026653289795</t>
@@ -4943,34 +4943,34 @@
     <t xml:space="preserve">2.27273964881897</t>
   </si>
   <si>
-    <t xml:space="preserve">2.3304443359375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.32220053672791</t>
+    <t xml:space="preserve">2.33044409751892</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.32220077514648</t>
   </si>
   <si>
     <t xml:space="preserve">2.21833229064941</t>
   </si>
   <si>
-    <t xml:space="preserve">2.00729823112488</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.04027223587036</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.89271306991577</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.89683520793915</t>
+    <t xml:space="preserve">2.0072979927063</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.04027247428894</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.89271330833435</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.89683496952057</t>
   </si>
   <si>
     <t xml:space="preserve">1.84407639503479</t>
   </si>
   <si>
-    <t xml:space="preserve">1.87045574188232</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.96195900440216</t>
+    <t xml:space="preserve">1.87045586109161</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.96195876598358</t>
   </si>
   <si>
     <t xml:space="preserve">1.93393075466156</t>
@@ -4982,16 +4982,16 @@
     <t xml:space="preserve">1.82181882858276</t>
   </si>
   <si>
-    <t xml:space="preserve">1.84325218200684</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.84902238845825</t>
+    <t xml:space="preserve">1.84325206279755</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.84902262687683</t>
   </si>
   <si>
     <t xml:space="preserve">1.89930784702301</t>
   </si>
   <si>
-    <t xml:space="preserve">1.88776707649231</t>
+    <t xml:space="preserve">1.88776683807373</t>
   </si>
   <si>
     <t xml:space="preserve">1.8737530708313</t>
@@ -5003,19 +5003,19 @@
     <t xml:space="preserve">1.9190925359726</t>
   </si>
   <si>
-    <t xml:space="preserve">1.94876933097839</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.94547176361084</t>
+    <t xml:space="preserve">1.94876909255981</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.94547152519226</t>
   </si>
   <si>
     <t xml:space="preserve">1.98339188098907</t>
   </si>
   <si>
-    <t xml:space="preserve">1.97679686546326</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.06912446022034</t>
+    <t xml:space="preserve">1.97679710388184</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.06912469863892</t>
   </si>
   <si>
     <t xml:space="preserve">2.07901692390442</t>
@@ -5027,13 +5027,13 @@
     <t xml:space="preserve">2.20102095603943</t>
   </si>
   <si>
-    <t xml:space="preserve">2.23069787025452</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.26284718513489</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.25377941131592</t>
+    <t xml:space="preserve">2.23069763183594</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.26284742355347</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.25377917289734</t>
   </si>
   <si>
     <t xml:space="preserve">2.1020987033844</t>
@@ -5048,13 +5048,13 @@
     <t xml:space="preserve">2.06500291824341</t>
   </si>
   <si>
-    <t xml:space="preserve">2.10045003890991</t>
+    <t xml:space="preserve">2.10044980049133</t>
   </si>
   <si>
     <t xml:space="preserve">2.0666515827179</t>
   </si>
   <si>
-    <t xml:space="preserve">2.14908671379089</t>
+    <t xml:space="preserve">2.14908695220947</t>
   </si>
   <si>
     <t xml:space="preserve">2.26119875907898</t>
@@ -5069,13 +5069,13 @@
     <t xml:space="preserve">2.24965786933899</t>
   </si>
   <si>
-    <t xml:space="preserve">2.2356436252594</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.23481965065002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.22080564498901</t>
+    <t xml:space="preserve">2.23564386367798</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.23481941223145</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.22080540657043</t>
   </si>
   <si>
     <t xml:space="preserve">2.22575163841248</t>
@@ -5093,10 +5093,10 @@
     <t xml:space="preserve">2.13085508346558</t>
   </si>
   <si>
-    <t xml:space="preserve">2.13516855239868</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.12395358085632</t>
+    <t xml:space="preserve">2.13516879081726</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.12395334243774</t>
   </si>
   <si>
     <t xml:space="preserve">2.0972101688385</t>
@@ -5105,10 +5105,10 @@
     <t xml:space="preserve">2.06183981895447</t>
   </si>
   <si>
-    <t xml:space="preserve">2.11618947982788</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.16363739967346</t>
+    <t xml:space="preserve">2.11618971824646</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.16363763809204</t>
   </si>
   <si>
     <t xml:space="preserve">2.15328526496887</t>
@@ -5117,13 +5117,13 @@
     <t xml:space="preserve">2.15846157073975</t>
   </si>
   <si>
-    <t xml:space="preserve">2.15414786338806</t>
+    <t xml:space="preserve">2.15414810180664</t>
   </si>
   <si>
     <t xml:space="preserve">2.15501046180725</t>
   </si>
   <si>
-    <t xml:space="preserve">2.11273837089539</t>
+    <t xml:space="preserve">2.11273860931396</t>
   </si>
   <si>
     <t xml:space="preserve">2.14465832710266</t>
@@ -5132,7 +5132,7 @@
     <t xml:space="preserve">2.14983439445496</t>
   </si>
   <si>
-    <t xml:space="preserve">2.20073366165161</t>
+    <t xml:space="preserve">2.20073342323303</t>
   </si>
   <si>
     <t xml:space="preserve">2.19814538955688</t>
@@ -5147,13 +5147,13 @@
     <t xml:space="preserve">2.34652876853943</t>
   </si>
   <si>
-    <t xml:space="preserve">2.37931084632874</t>
+    <t xml:space="preserve">2.37931108474731</t>
   </si>
   <si>
     <t xml:space="preserve">2.36809587478638</t>
   </si>
   <si>
-    <t xml:space="preserve">2.31633424758911</t>
+    <t xml:space="preserve">2.31633448600769</t>
   </si>
   <si>
     <t xml:space="preserve">2.28614044189453</t>
@@ -5168,7 +5168,7 @@
     <t xml:space="preserve">2.37672305107117</t>
   </si>
   <si>
-    <t xml:space="preserve">2.40001606941223</t>
+    <t xml:space="preserve">2.40001583099365</t>
   </si>
   <si>
     <t xml:space="preserve">2.42675924301147</t>
@@ -5189,7 +5189,7 @@
     <t xml:space="preserve">2.42072033882141</t>
   </si>
   <si>
-    <t xml:space="preserve">2.44056224822998</t>
+    <t xml:space="preserve">2.44056248664856</t>
   </si>
   <si>
     <t xml:space="preserve">2.47938370704651</t>
@@ -5198,19 +5198,19 @@
     <t xml:space="preserve">2.5337336063385</t>
   </si>
   <si>
-    <t xml:space="preserve">2.51302886009216</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.56133961677551</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.55443787574768</t>
+    <t xml:space="preserve">2.51302909851074</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.56133985519409</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.55443811416626</t>
   </si>
   <si>
     <t xml:space="preserve">2.53200817108154</t>
   </si>
   <si>
-    <t xml:space="preserve">2.58376955986023</t>
+    <t xml:space="preserve">2.58376979827881</t>
   </si>
   <si>
     <t xml:space="preserve">2.60188627243042</t>
@@ -5225,7 +5225,7 @@
     <t xml:space="preserve">2.73819208145142</t>
   </si>
   <si>
-    <t xml:space="preserve">2.69419455528259</t>
+    <t xml:space="preserve">2.69419431686401</t>
   </si>
   <si>
     <t xml:space="preserve">2.70454692840576</t>
@@ -5234,16 +5234,16 @@
     <t xml:space="preserve">2.71489930152893</t>
   </si>
   <si>
-    <t xml:space="preserve">2.66400027275085</t>
+    <t xml:space="preserve">2.66400051116943</t>
   </si>
   <si>
     <t xml:space="preserve">2.59325933456421</t>
   </si>
   <si>
-    <t xml:space="preserve">2.48714780807495</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.44660139083862</t>
+    <t xml:space="preserve">2.48714804649353</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.44660115242004</t>
   </si>
   <si>
     <t xml:space="preserve">2.45264005661011</t>
@@ -5258,7 +5258,7 @@
     <t xml:space="preserve">2.28010106086731</t>
   </si>
   <si>
-    <t xml:space="preserve">2.34048986434937</t>
+    <t xml:space="preserve">2.34049010276794</t>
   </si>
   <si>
     <t xml:space="preserve">2.34911680221558</t>
@@ -5273,28 +5273,28 @@
     <t xml:space="preserve">2.37240958213806</t>
   </si>
   <si>
-    <t xml:space="preserve">2.36895895004272</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.34394073486328</t>
+    <t xml:space="preserve">2.36895871162415</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.3439404964447</t>
   </si>
   <si>
     <t xml:space="preserve">2.39656496047974</t>
   </si>
   <si>
-    <t xml:space="preserve">2.41640710830688</t>
+    <t xml:space="preserve">2.41640734672546</t>
   </si>
   <si>
     <t xml:space="preserve">2.43969988822937</t>
   </si>
   <si>
-    <t xml:space="preserve">2.40519213676453</t>
+    <t xml:space="preserve">2.40519189834595</t>
   </si>
   <si>
     <t xml:space="preserve">2.39138889312744</t>
   </si>
   <si>
-    <t xml:space="preserve">2.36464524269104</t>
+    <t xml:space="preserve">2.36464548110962</t>
   </si>
   <si>
     <t xml:space="preserve">2.26198482513428</t>
@@ -5309,7 +5309,7 @@
     <t xml:space="preserve">2.31115818023682</t>
   </si>
   <si>
-    <t xml:space="preserve">2.38793802261353</t>
+    <t xml:space="preserve">2.3879382610321</t>
   </si>
   <si>
     <t xml:space="preserve">2.41295623779297</t>
@@ -5333,7 +5333,7 @@
     <t xml:space="preserve">2.4388370513916</t>
   </si>
   <si>
-    <t xml:space="preserve">2.41123080253601</t>
+    <t xml:space="preserve">2.41123104095459</t>
   </si>
   <si>
     <t xml:space="preserve">2.49922585487366</t>
@@ -5393,13 +5393,13 @@
     <t xml:space="preserve">2.51389145851135</t>
   </si>
   <si>
-    <t xml:space="preserve">2.52510643005371</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.6476092338562</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.70713496208191</t>
+    <t xml:space="preserve">2.52510666847229</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.64760899543762</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.70713520050049</t>
   </si>
   <si>
     <t xml:space="preserve">2.70972323417664</t>
@@ -5420,7 +5420,7 @@
     <t xml:space="preserve">2.84171533584595</t>
   </si>
   <si>
-    <t xml:space="preserve">3.04444861412048</t>
+    <t xml:space="preserve">3.0444483757019</t>
   </si>
   <si>
     <t xml:space="preserve">3.02546906471252</t>
@@ -5429,7 +5429,7 @@
     <t xml:space="preserve">3.07291746139526</t>
   </si>
   <si>
-    <t xml:space="preserve">2.98751068115234</t>
+    <t xml:space="preserve">2.98751091957092</t>
   </si>
   <si>
     <t xml:space="preserve">3.00562715530396</t>
@@ -5444,13 +5444,13 @@
     <t xml:space="preserve">2.90986824035645</t>
   </si>
   <si>
-    <t xml:space="preserve">2.94696402549744</t>
+    <t xml:space="preserve">2.94696378707886</t>
   </si>
   <si>
     <t xml:space="preserve">2.94782686233521</t>
   </si>
   <si>
-    <t xml:space="preserve">2.9245343208313</t>
+    <t xml:space="preserve">2.92453408241272</t>
   </si>
   <si>
     <t xml:space="preserve">2.8900260925293</t>
@@ -5465,25 +5465,25 @@
     <t xml:space="preserve">2.98837351799011</t>
   </si>
   <si>
-    <t xml:space="preserve">2.9676685333252</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.95214033126831</t>
+    <t xml:space="preserve">2.96766877174377</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.95214009284973</t>
   </si>
   <si>
     <t xml:space="preserve">2.97457027435303</t>
   </si>
   <si>
-    <t xml:space="preserve">2.89347720146179</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.9167697429657</t>
+    <t xml:space="preserve">2.89347696304321</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.91676998138428</t>
   </si>
   <si>
     <t xml:space="preserve">2.8805365562439</t>
   </si>
   <si>
-    <t xml:space="preserve">2.86932158470154</t>
+    <t xml:space="preserve">2.86932134628296</t>
   </si>
   <si>
     <t xml:space="preserve">2.70023369789124</t>
@@ -5492,7 +5492,7 @@
     <t xml:space="preserve">2.64070773124695</t>
   </si>
   <si>
-    <t xml:space="preserve">2.64588379859924</t>
+    <t xml:space="preserve">2.64588356018066</t>
   </si>
   <si>
     <t xml:space="preserve">2.64502096176147</t>
@@ -5519,13 +5519,13 @@
     <t xml:space="preserve">2.77356243133545</t>
   </si>
   <si>
-    <t xml:space="preserve">2.82791256904602</t>
+    <t xml:space="preserve">2.82791233062744</t>
   </si>
   <si>
     <t xml:space="preserve">2.82877492904663</t>
   </si>
   <si>
-    <t xml:space="preserve">2.7200756072998</t>
+    <t xml:space="preserve">2.72007536888123</t>
   </si>
   <si>
     <t xml:space="preserve">2.73215317726135</t>
@@ -5543,7 +5543,7 @@
     <t xml:space="preserve">2.72611451148987</t>
   </si>
   <si>
-    <t xml:space="preserve">2.75285792350769</t>
+    <t xml:space="preserve">2.75285768508911</t>
   </si>
   <si>
     <t xml:space="preserve">2.85034203529358</t>
@@ -5552,13 +5552,13 @@
     <t xml:space="preserve">2.86759614944458</t>
   </si>
   <si>
-    <t xml:space="preserve">2.84861707687378</t>
+    <t xml:space="preserve">2.8486168384552</t>
   </si>
   <si>
     <t xml:space="preserve">2.83826446533203</t>
   </si>
   <si>
-    <t xml:space="preserve">2.88916349411011</t>
+    <t xml:space="preserve">2.88916373252869</t>
   </si>
   <si>
     <t xml:space="preserve">2.81755995750427</t>
@@ -5576,7 +5576,7 @@
     <t xml:space="preserve">2.8943395614624</t>
   </si>
   <si>
-    <t xml:space="preserve">2.8710470199585</t>
+    <t xml:space="preserve">2.87104678153992</t>
   </si>
   <si>
     <t xml:space="preserve">2.92712211608887</t>
@@ -5603,7 +5603,7 @@
     <t xml:space="preserve">3.07981896400452</t>
   </si>
   <si>
-    <t xml:space="preserve">3.0401349067688</t>
+    <t xml:space="preserve">3.04013514518738</t>
   </si>
   <si>
     <t xml:space="preserve">3.03323364257812</t>
@@ -5624,16 +5624,16 @@
     <t xml:space="preserve">3.27910161018372</t>
   </si>
   <si>
-    <t xml:space="preserve">3.23510384559631</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.19973373413086</t>
+    <t xml:space="preserve">3.23510408401489</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.19973349571228</t>
   </si>
   <si>
     <t xml:space="preserve">3.19714546203613</t>
   </si>
   <si>
-    <t xml:space="preserve">3.23941731452942</t>
+    <t xml:space="preserve">3.239417552948</t>
   </si>
   <si>
     <t xml:space="preserve">3.28082680702209</t>
@@ -5654,13 +5654,13 @@
     <t xml:space="preserve">3.34811687469482</t>
   </si>
   <si>
-    <t xml:space="preserve">3.44991493225098</t>
+    <t xml:space="preserve">3.4499146938324</t>
   </si>
   <si>
     <t xml:space="preserve">3.42921018600464</t>
   </si>
   <si>
-    <t xml:space="preserve">3.41972064971924</t>
+    <t xml:space="preserve">3.41972041130066</t>
   </si>
   <si>
     <t xml:space="preserve">3.4671688079834</t>
@@ -5672,7 +5672,7 @@
     <t xml:space="preserve">3.63539433479309</t>
   </si>
   <si>
-    <t xml:space="preserve">3.6707649230957</t>
+    <t xml:space="preserve">3.67076468467712</t>
   </si>
   <si>
     <t xml:space="preserve">3.64574646949768</t>
@@ -5687,13 +5687,13 @@
     <t xml:space="preserve">3.83381366729736</t>
   </si>
   <si>
-    <t xml:space="preserve">3.7440938949585</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.77860140800476</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.76997447013855</t>
+    <t xml:space="preserve">3.74409413337708</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.77860188484192</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.76997423171997</t>
   </si>
   <si>
     <t xml:space="preserve">3.85969471931458</t>
@@ -5705,7 +5705,7 @@
     <t xml:space="preserve">3.78981637954712</t>
   </si>
   <si>
-    <t xml:space="preserve">3.83467698097229</t>
+    <t xml:space="preserve">3.83467650413513</t>
   </si>
   <si>
     <t xml:space="preserve">3.77083706855774</t>
@@ -5714,19 +5714,19 @@
     <t xml:space="preserve">3.83812689781189</t>
   </si>
   <si>
-    <t xml:space="preserve">3.68888092041016</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.68715620040894</t>
+    <t xml:space="preserve">3.68888115882874</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.68715596199036</t>
   </si>
   <si>
     <t xml:space="preserve">3.68197965621948</t>
   </si>
   <si>
-    <t xml:space="preserve">3.63366866111755</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.73460388183594</t>
+    <t xml:space="preserve">3.63366889953613</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.73460412025452</t>
   </si>
   <si>
     <t xml:space="preserve">3.80965852737427</t>
@@ -5738,40 +5738,40 @@
     <t xml:space="preserve">3.89420247077942</t>
   </si>
   <si>
-    <t xml:space="preserve">4.02791976928711</t>
+    <t xml:space="preserve">4.02792024612427</t>
   </si>
   <si>
     <t xml:space="preserve">3.99772572517395</t>
   </si>
   <si>
-    <t xml:space="preserve">4.07450580596924</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.12712955474854</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.15646123886108</t>
+    <t xml:space="preserve">4.0745062828064</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.12713003158569</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.15646171569824</t>
   </si>
   <si>
     <t xml:space="preserve">4.21943807601929</t>
   </si>
   <si>
-    <t xml:space="preserve">4.25394678115845</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.12885522842407</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.17544078826904</t>
+    <t xml:space="preserve">4.25394630432129</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.12885570526123</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.1754412651062</t>
   </si>
   <si>
     <t xml:space="preserve">4.25653457641602</t>
   </si>
   <si>
-    <t xml:space="preserve">4.23237895965576</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.10642576217651</t>
+    <t xml:space="preserve">4.23237943649292</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.10642528533936</t>
   </si>
   <si>
     <t xml:space="preserve">4.09089708328247</t>
@@ -5792,13 +5792,13 @@
     <t xml:space="preserve">4.56710433959961</t>
   </si>
   <si>
-    <t xml:space="preserve">4.46925115585327</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.44730234146118</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.38420104980469</t>
+    <t xml:space="preserve">4.46925067901611</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.44730186462402</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.38420057296753</t>
   </si>
   <si>
     <t xml:space="preserve">4.41072130203247</t>
@@ -5810,7 +5810,7 @@
     <t xml:space="preserve">4.40066146850586</t>
   </si>
   <si>
-    <t xml:space="preserve">4.48205375671387</t>
+    <t xml:space="preserve">4.48205423355103</t>
   </si>
   <si>
     <t xml:space="preserve">4.39425992965698</t>
@@ -5819,19 +5819,19 @@
     <t xml:space="preserve">4.52137804031372</t>
   </si>
   <si>
-    <t xml:space="preserve">4.50949001312256</t>
+    <t xml:space="preserve">4.5094895362854</t>
   </si>
   <si>
     <t xml:space="preserve">4.51772022247314</t>
   </si>
   <si>
-    <t xml:space="preserve">4.37505483627319</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.35310745239258</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.47107934951782</t>
+    <t xml:space="preserve">4.37505531311035</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.35310697555542</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.47107982635498</t>
   </si>
   <si>
     <t xml:space="preserve">4.49760103225708</t>
@@ -5840,7 +5840,7 @@
     <t xml:space="preserve">4.43724250793457</t>
   </si>
   <si>
-    <t xml:space="preserve">4.27720212936401</t>
+    <t xml:space="preserve">4.27720165252686</t>
   </si>
   <si>
     <t xml:space="preserve">4.26805686950684</t>
@@ -5870,13 +5870,13 @@
     <t xml:space="preserve">4.4098072052002</t>
   </si>
   <si>
-    <t xml:space="preserve">4.39243125915527</t>
+    <t xml:space="preserve">4.39243078231812</t>
   </si>
   <si>
     <t xml:space="preserve">4.44181489944458</t>
   </si>
   <si>
-    <t xml:space="preserve">4.38968801498413</t>
+    <t xml:space="preserve">4.38968753814697</t>
   </si>
   <si>
     <t xml:space="preserve">4.3174409866333</t>
@@ -5891,7 +5891,7 @@
     <t xml:space="preserve">4.61283016204834</t>
   </si>
   <si>
-    <t xml:space="preserve">4.70611095428467</t>
+    <t xml:space="preserve">4.70611047744751</t>
   </si>
   <si>
     <t xml:space="preserve">4.64575290679932</t>
@@ -5900,13 +5900,13 @@
     <t xml:space="preserve">4.84145975112915</t>
   </si>
   <si>
-    <t xml:space="preserve">4.799391746521</t>
+    <t xml:space="preserve">4.79939222335815</t>
   </si>
   <si>
     <t xml:space="preserve">4.82134008407593</t>
   </si>
   <si>
-    <t xml:space="preserve">4.75549507141113</t>
+    <t xml:space="preserve">4.75549459457397</t>
   </si>
   <si>
     <t xml:space="preserve">4.7335467338562</t>
@@ -5915,13 +5915,13 @@
     <t xml:space="preserve">4.68782043457031</t>
   </si>
   <si>
-    <t xml:space="preserve">4.7518367767334</t>
+    <t xml:space="preserve">4.75183725357056</t>
   </si>
   <si>
     <t xml:space="preserve">4.77744340896606</t>
   </si>
   <si>
-    <t xml:space="preserve">4.80304956436157</t>
+    <t xml:space="preserve">4.80305004119873</t>
   </si>
   <si>
     <t xml:space="preserve">4.81768226623535</t>
@@ -5930,7 +5930,7 @@
     <t xml:space="preserve">4.98046636581421</t>
   </si>
   <si>
-    <t xml:space="preserve">4.96217584609985</t>
+    <t xml:space="preserve">4.96217632293701</t>
   </si>
   <si>
     <t xml:space="preserve">5.03533744812012</t>
@@ -5960,13 +5960,13 @@
     <t xml:space="preserve">4.27354383468628</t>
   </si>
   <si>
-    <t xml:space="preserve">4.32109832763672</t>
+    <t xml:space="preserve">4.32109880447388</t>
   </si>
   <si>
     <t xml:space="preserve">4.34121799468994</t>
   </si>
   <si>
-    <t xml:space="preserve">4.36956787109375</t>
+    <t xml:space="preserve">4.36956834793091</t>
   </si>
   <si>
     <t xml:space="preserve">4.35767936706543</t>
@@ -5987,7 +5987,7 @@
     <t xml:space="preserve">4.51497650146484</t>
   </si>
   <si>
-    <t xml:space="preserve">4.5305233001709</t>
+    <t xml:space="preserve">4.53052377700806</t>
   </si>
   <si>
     <t xml:space="preserve">4.51040410995483</t>
@@ -5996,28 +5996,28 @@
     <t xml:space="preserve">4.56618976593018</t>
   </si>
   <si>
-    <t xml:space="preserve">4.52686500549316</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.55430126190186</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.53601026535034</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.6274619102478</t>
+    <t xml:space="preserve">4.52686548233032</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.5543007850647</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.5360107421875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.62746238708496</t>
   </si>
   <si>
     <t xml:space="preserve">4.61831712722778</t>
   </si>
   <si>
-    <t xml:space="preserve">4.48662662506104</t>
+    <t xml:space="preserve">4.48662710189819</t>
   </si>
   <si>
     <t xml:space="preserve">4.46559238433838</t>
   </si>
   <si>
-    <t xml:space="preserve">4.49485731124878</t>
+    <t xml:space="preserve">4.49485683441162</t>
   </si>
   <si>
     <t xml:space="preserve">4.39700365066528</t>
@@ -6038,10 +6038,10 @@
     <t xml:space="preserve">4.46284914016724</t>
   </si>
   <si>
-    <t xml:space="preserve">4.53692483901978</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.54972839355469</t>
+    <t xml:space="preserve">4.53692531585693</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.54972791671753</t>
   </si>
   <si>
     <t xml:space="preserve">4.5122332572937</t>
@@ -6065,10 +6065,10 @@
     <t xml:space="preserve">4.4674220085144</t>
   </si>
   <si>
-    <t xml:space="preserve">4.67867517471313</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.77561473846436</t>
+    <t xml:space="preserve">4.67867565155029</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.7756142616272</t>
   </si>
   <si>
     <t xml:space="preserve">4.82499837875366</t>
@@ -6077,16 +6077,16 @@
     <t xml:space="preserve">4.86523723602295</t>
   </si>
   <si>
-    <t xml:space="preserve">5.26579570770264</t>
+    <t xml:space="preserve">5.26579618453979</t>
   </si>
   <si>
     <t xml:space="preserve">5.36639308929443</t>
   </si>
   <si>
-    <t xml:space="preserve">5.33529949188232</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.34078693389893</t>
+    <t xml:space="preserve">5.33529996871948</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.34078645706177</t>
   </si>
   <si>
     <t xml:space="preserve">5.33164167404175</t>
@@ -6098,7 +6098,7 @@
     <t xml:space="preserve">5.35541868209839</t>
   </si>
   <si>
-    <t xml:space="preserve">5.27677011489868</t>
+    <t xml:space="preserve">5.27677059173584</t>
   </si>
   <si>
     <t xml:space="preserve">5.22738647460938</t>
@@ -6140,10 +6140,10 @@
     <t xml:space="preserve">5.46516084671021</t>
   </si>
   <si>
-    <t xml:space="preserve">5.22555732727051</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.36456394195557</t>
+    <t xml:space="preserve">5.22555780410767</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.36456441879272</t>
   </si>
   <si>
     <t xml:space="preserve">5.3682222366333</t>
@@ -6152,13 +6152,13 @@
     <t xml:space="preserve">5.47430658340454</t>
   </si>
   <si>
-    <t xml:space="preserve">5.55112600326538</t>
+    <t xml:space="preserve">5.55112552642822</t>
   </si>
   <si>
     <t xml:space="preserve">5.43223857879639</t>
   </si>
   <si>
-    <t xml:space="preserve">5.55844211578369</t>
+    <t xml:space="preserve">5.55844163894653</t>
   </si>
   <si>
     <t xml:space="preserve">5.44504165649414</t>
@@ -6167,16 +6167,16 @@
     <t xml:space="preserve">5.4395546913147</t>
   </si>
   <si>
-    <t xml:space="preserve">5.42675113677979</t>
+    <t xml:space="preserve">5.42675161361694</t>
   </si>
   <si>
     <t xml:space="preserve">5.34444427490234</t>
   </si>
   <si>
-    <t xml:space="preserve">5.24933481216431</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.19812202453613</t>
+    <t xml:space="preserve">5.24933433532715</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.19812154769897</t>
   </si>
   <si>
     <t xml:space="preserve">5.23287343978882</t>
@@ -6194,7 +6194,7 @@
     <t xml:space="preserve">5.54380941390991</t>
   </si>
   <si>
-    <t xml:space="preserve">5.3865122795105</t>
+    <t xml:space="preserve">5.38651275634766</t>
   </si>
   <si>
     <t xml:space="preserve">5.29323148727417</t>
@@ -6218,19 +6218,19 @@
     <t xml:space="preserve">5.68098735809326</t>
   </si>
   <si>
-    <t xml:space="preserve">5.54929637908936</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.50174188613892</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.48162221908569</t>
+    <t xml:space="preserve">5.54929685592651</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.50174140930176</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.48162269592285</t>
   </si>
   <si>
     <t xml:space="preserve">5.53100633621216</t>
   </si>
   <si>
-    <t xml:space="preserve">5.60965490341187</t>
+    <t xml:space="preserve">5.60965442657471</t>
   </si>
   <si>
     <t xml:space="preserve">5.44687032699585</t>
@@ -6290,7 +6290,7 @@
     <t xml:space="preserve">6.12361431121826</t>
   </si>
   <si>
-    <t xml:space="preserve">6.03947877883911</t>
+    <t xml:space="preserve">6.03947830200195</t>
   </si>
   <si>
     <t xml:space="preserve">6.03033304214478</t>
@@ -6305,13 +6305,13 @@
     <t xml:space="preserve">6.30285978317261</t>
   </si>
   <si>
-    <t xml:space="preserve">5.82548141479492</t>
+    <t xml:space="preserve">5.82548093795776</t>
   </si>
   <si>
     <t xml:space="preserve">5.73220062255859</t>
   </si>
   <si>
-    <t xml:space="preserve">5.8785228729248</t>
+    <t xml:space="preserve">5.87852334976196</t>
   </si>
   <si>
     <t xml:space="preserve">5.90230083465576</t>
@@ -6323,7 +6323,7 @@
     <t xml:space="preserve">5.84742975234985</t>
   </si>
   <si>
-    <t xml:space="preserve">6.04679489135742</t>
+    <t xml:space="preserve">6.04679441452026</t>
   </si>
   <si>
     <t xml:space="preserve">6.13641738891602</t>
@@ -6338,7 +6338,7 @@
     <t xml:space="preserve">6.22055339813232</t>
   </si>
   <si>
-    <t xml:space="preserve">6.36321783065796</t>
+    <t xml:space="preserve">6.36321830749512</t>
   </si>
   <si>
     <t xml:space="preserve">6.48942184448242</t>
@@ -6356,7 +6356,7 @@
     <t xml:space="preserve">6.85157060623169</t>
   </si>
   <si>
-    <t xml:space="preserve">6.56075382232666</t>
+    <t xml:space="preserve">6.5607533454895</t>
   </si>
   <si>
     <t xml:space="preserve">6.77475118637085</t>
@@ -6392,19 +6392,19 @@
     <t xml:space="preserve">6.91375780105591</t>
   </si>
   <si>
-    <t xml:space="preserve">6.95765495300293</t>
+    <t xml:space="preserve">6.95765447616577</t>
   </si>
   <si>
     <t xml:space="preserve">7.01618385314941</t>
   </si>
   <si>
-    <t xml:space="preserve">7.10946464538574</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.0802001953125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.00520992279053</t>
+    <t xml:space="preserve">7.1094651222229</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.08020067214966</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.00520944595337</t>
   </si>
   <si>
     <t xml:space="preserve">6.82413530349731</t>
@@ -6434,13 +6434,13 @@
     <t xml:space="preserve">5.67915821075439</t>
   </si>
   <si>
-    <t xml:space="preserve">5.8876690864563</t>
+    <t xml:space="preserve">5.88766860961914</t>
   </si>
   <si>
     <t xml:space="preserve">6.05959796905518</t>
   </si>
   <si>
-    <t xml:space="preserve">6.16019535064697</t>
+    <t xml:space="preserve">6.16019487380981</t>
   </si>
   <si>
     <t xml:space="preserve">6.06874322891235</t>
@@ -6467,16 +6467,16 @@
     <t xml:space="preserve">6.72902488708496</t>
   </si>
   <si>
-    <t xml:space="preserve">6.7637767791748</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.71622180938721</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.94668102264404</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.17165184020996</t>
+    <t xml:space="preserve">6.76377725601196</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.71622228622437</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.94668054580688</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.17165231704712</t>
   </si>
   <si>
     <t xml:space="preserve">7.17713928222656</t>
@@ -6485,7 +6485,7 @@
     <t xml:space="preserve">7.26859092712402</t>
   </si>
   <si>
-    <t xml:space="preserve">7.28505229949951</t>
+    <t xml:space="preserve">7.28505277633667</t>
   </si>
   <si>
     <t xml:space="preserve">7.20091676712036</t>
@@ -6855,6 +6855,9 @@
   </si>
   <si>
     <t xml:space="preserve">10.0450000762939</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1400003433228</t>
   </si>
 </sst>
 </file>
@@ -72635,7 +72638,7 @@
     </row>
     <row r="2518">
       <c r="A2518" s="1" t="n">
-        <v>45985.6912268518</v>
+        <v>45985.3333333333</v>
       </c>
       <c r="B2518" t="n">
         <v>10978959</v>
@@ -72656,6 +72659,32 @@
         <v>2280</v>
       </c>
       <c r="H2518" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2519">
+      <c r="A2519" s="1" t="n">
+        <v>45986.6933564815</v>
+      </c>
+      <c r="B2519" t="n">
+        <v>8120894</v>
+      </c>
+      <c r="C2519" t="n">
+        <v>10.2349996566772</v>
+      </c>
+      <c r="D2519" t="n">
+        <v>9.96199989318848</v>
+      </c>
+      <c r="E2519" t="n">
+        <v>10.0500001907349</v>
+      </c>
+      <c r="F2519" t="n">
+        <v>10.1400003433228</v>
+      </c>
+      <c r="G2519" t="s">
+        <v>2281</v>
+      </c>
+      <c r="H2519" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/BPE.MI.xlsx
+++ b/data/BPE.MI.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2290" uniqueCount="2290">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2291" uniqueCount="2291">
   <si>
     <t xml:space="preserve">date</t>
   </si>
@@ -44,43 +44,43 @@
     <t xml:space="preserve">BPE.MI</t>
   </si>
   <si>
-    <t xml:space="preserve">3.23759818077087</t>
+    <t xml:space="preserve">3.23759794235229</t>
   </si>
   <si>
     <t xml:space="preserve">3.09375715255737</t>
   </si>
   <si>
-    <t xml:space="preserve">3.02301573753357</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.9546320438385</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.95699048042297</t>
+    <t xml:space="preserve">3.02301597595215</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.95463228225708</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.95699024200439</t>
   </si>
   <si>
     <t xml:space="preserve">2.93340945243835</t>
   </si>
   <si>
-    <t xml:space="preserve">3.07489275932312</t>
+    <t xml:space="preserve">3.07489252090454</t>
   </si>
   <si>
     <t xml:space="preserve">2.91690421104431</t>
   </si>
   <si>
-    <t xml:space="preserve">2.66223454475403</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.65044403076172</t>
+    <t xml:space="preserve">2.66223430633545</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.6504442691803</t>
   </si>
   <si>
     <t xml:space="preserve">2.45708441734314</t>
   </si>
   <si>
-    <t xml:space="preserve">2.72826051712036</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.69760465621948</t>
+    <t xml:space="preserve">2.72825980186462</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.69760489463806</t>
   </si>
   <si>
     <t xml:space="preserve">2.62686395645142</t>
@@ -92,97 +92,97 @@
     <t xml:space="preserve">2.66695046424866</t>
   </si>
   <si>
-    <t xml:space="preserve">2.46651697158813</t>
+    <t xml:space="preserve">2.46651673316956</t>
   </si>
   <si>
     <t xml:space="preserve">2.59385108947754</t>
   </si>
   <si>
-    <t xml:space="preserve">2.53018426895142</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.35804653167725</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.16279983520508</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.17128944396973</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.1260142326355</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.87228870391846</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.83173096179962</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.95812141895294</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.7704211473465</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.97415637969971</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.17411804199219</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.27975916862488</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.33446598052979</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.32031726837158</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.18166470527649</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.40284991264343</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.31182885169983</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.16468644142151</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.21845006942749</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.25995135307312</t>
+    <t xml:space="preserve">2.53018379211426</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.35804629325867</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.16280007362366</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.17128920555115</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.12601447105408</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.87228882312775</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.83173084259033</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.95812153816223</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.77042102813721</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.97415626049042</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.17411875724792</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.2797589302063</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.33446645736694</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.32031774520874</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.18166494369507</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.40284967422485</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.31182861328125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.16468620300293</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.21844983100891</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.25995206832886</t>
   </si>
   <si>
     <t xml:space="preserve">2.22127962112427</t>
   </si>
   <si>
-    <t xml:space="preserve">2.25429177284241</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.36512064933777</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.32409024238586</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.33352255821228</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.21279072761536</t>
+    <t xml:space="preserve">2.25429201126099</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.36512088775635</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.32409071922302</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.33352279663086</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.21279096603394</t>
   </si>
   <si>
     <t xml:space="preserve">2.18072152137756</t>
   </si>
   <si>
-    <t xml:space="preserve">2.20524549484253</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.22505259513855</t>
+    <t xml:space="preserve">2.20524501800537</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.22505235671997</t>
   </si>
   <si>
     <t xml:space="preserve">2.40992331504822</t>
@@ -191,97 +191,97 @@
     <t xml:space="preserve">2.44293642044067</t>
   </si>
   <si>
-    <t xml:space="preserve">2.36276245117188</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.20241498947144</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.22693872451782</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.24674654006958</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.2410876750946</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.20807480812073</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.14770889282227</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.05904603004456</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.03829526901245</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.97321307659149</t>
+    <t xml:space="preserve">2.3627622127533</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.20241522789001</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.2269389629364</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.246746301651</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.24108743667603</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.20807456970215</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.14770841598511</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.05904626846313</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.03829503059387</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.9732129573822</t>
   </si>
   <si>
     <t xml:space="preserve">2.00905585289001</t>
   </si>
   <si>
-    <t xml:space="preserve">1.89492607116699</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.88455033302307</t>
+    <t xml:space="preserve">1.8949259519577</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.88455057144165</t>
   </si>
   <si>
     <t xml:space="preserve">1.77325081825256</t>
   </si>
   <si>
-    <t xml:space="preserve">2.02697658538818</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.12507128715515</t>
+    <t xml:space="preserve">2.0269763469696</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.12507176399231</t>
   </si>
   <si>
     <t xml:space="preserve">2.04018187522888</t>
   </si>
   <si>
-    <t xml:space="preserve">2.27410006523132</t>
+    <t xml:space="preserve">2.2741003036499</t>
   </si>
   <si>
     <t xml:space="preserve">2.37691068649292</t>
   </si>
   <si>
-    <t xml:space="preserve">2.38398480415344</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.30428314208984</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.37219452857971</t>
+    <t xml:space="preserve">2.38398456573486</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.30428266525269</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.37219500541687</t>
   </si>
   <si>
     <t xml:space="preserve">2.44765210151672</t>
   </si>
   <si>
-    <t xml:space="preserve">2.45944237709045</t>
+    <t xml:space="preserve">2.45944166183472</t>
   </si>
   <si>
     <t xml:space="preserve">2.37455272674561</t>
   </si>
   <si>
-    <t xml:space="preserve">2.45236825942993</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.41463971138</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.50896167755127</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.40756511688232</t>
+    <t xml:space="preserve">2.45236802101135</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.41464018821716</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.50896120071411</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.4075653553009</t>
   </si>
   <si>
     <t xml:space="preserve">2.31937408447266</t>
   </si>
   <si>
-    <t xml:space="preserve">2.21750736236572</t>
+    <t xml:space="preserve">2.21750712394714</t>
   </si>
   <si>
     <t xml:space="preserve">2.19298362731934</t>
@@ -296,7 +296,7 @@
     <t xml:space="preserve">2.07036447525024</t>
   </si>
   <si>
-    <t xml:space="preserve">2.06470537185669</t>
+    <t xml:space="preserve">2.06470561027527</t>
   </si>
   <si>
     <t xml:space="preserve">2.0326361656189</t>
@@ -308,76 +308,76 @@
     <t xml:space="preserve">2.06093263626099</t>
   </si>
   <si>
-    <t xml:space="preserve">2.17506194114685</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.07319450378418</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.09960436820984</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.05811405181885</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.22021532058716</t>
+    <t xml:space="preserve">2.17506170272827</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.07319474220276</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.099604845047</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.05811429023743</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.22021555900574</t>
   </si>
   <si>
     <t xml:space="preserve">2.3311779499054</t>
   </si>
   <si>
-    <t xml:space="preserve">2.28582811355591</t>
+    <t xml:space="preserve">2.28582787513733</t>
   </si>
   <si>
     <t xml:space="preserve">2.29161787033081</t>
   </si>
   <si>
-    <t xml:space="preserve">2.31381011009216</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.19416403770447</t>
+    <t xml:space="preserve">2.31381058692932</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.19416427612305</t>
   </si>
   <si>
     <t xml:space="preserve">2.09960460662842</t>
   </si>
   <si>
-    <t xml:space="preserve">2.16618227958679</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.07934165000916</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.06969261169434</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.09670925140381</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.13627004623413</t>
+    <t xml:space="preserve">2.16618204116821</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.07934188842773</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.06969237327576</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.09670901298523</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.13627052307129</t>
   </si>
   <si>
     <t xml:space="preserve">1.99636089801788</t>
   </si>
   <si>
-    <t xml:space="preserve">1.87478411197662</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.82171535491943</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.81592643260956</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.76864612102509</t>
+    <t xml:space="preserve">1.87478387355804</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.82171511650085</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.81592631340027</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.7686460018158</t>
   </si>
   <si>
     <t xml:space="preserve">1.94425702095032</t>
   </si>
   <si>
-    <t xml:space="preserve">2.03206157684326</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.0841658115387</t>
+    <t xml:space="preserve">2.03206181526184</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.08416557312012</t>
   </si>
   <si>
     <t xml:space="preserve">2.07548236846924</t>
@@ -386,58 +386,58 @@
     <t xml:space="preserve">2.23468923568726</t>
   </si>
   <si>
-    <t xml:space="preserve">1.68470084667206</t>
+    <t xml:space="preserve">1.68470096588135</t>
   </si>
   <si>
     <t xml:space="preserve">1.66733288764954</t>
   </si>
   <si>
-    <t xml:space="preserve">1.62777173519135</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.5390020608902</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.5814573764801</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.50523042678833</t>
+    <t xml:space="preserve">1.62777185440063</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.53900194168091</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.58145749568939</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.50523054599762</t>
   </si>
   <si>
     <t xml:space="preserve">1.40391731262207</t>
   </si>
   <si>
-    <t xml:space="preserve">1.40488219261169</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.30453312397003</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.24567484855652</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.44733738899231</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.51487970352173</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.63838601112366</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.55637013912201</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.62294805049896</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.64224553108215</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.65189480781555</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.63645601272583</t>
+    <t xml:space="preserve">1.40488231182098</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.30453336238861</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.24567472934723</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.44733703136444</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.5148800611496</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.63838613033295</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.55637037754059</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.62294816970825</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.64224541187286</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.65189445018768</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.63645565509796</t>
   </si>
   <si>
     <t xml:space="preserve">1.65382421016693</t>
@@ -446,160 +446,160 @@
     <t xml:space="preserve">1.7068932056427</t>
   </si>
   <si>
-    <t xml:space="preserve">1.6943496465683</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.64899957180023</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.6567188501358</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.73294532299042</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.67891144752502</t>
+    <t xml:space="preserve">1.69434952735901</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.64899945259094</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.65671825408936</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.73294544219971</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.67891156673431</t>
   </si>
   <si>
     <t xml:space="preserve">1.77057647705078</t>
   </si>
   <si>
-    <t xml:space="preserve">1.67022728919983</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.46374034881592</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.5225989818573</t>
+    <t xml:space="preserve">1.67022752761841</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.46374011039734</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.52259874343872</t>
   </si>
   <si>
     <t xml:space="preserve">1.53031778335571</t>
   </si>
   <si>
-    <t xml:space="preserve">1.73005104064941</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.69820928573608</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.73198056221008</t>
+    <t xml:space="preserve">1.7300511598587</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.69820916652679</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.73198008537292</t>
   </si>
   <si>
     <t xml:space="preserve">1.72136676311493</t>
   </si>
   <si>
-    <t xml:space="preserve">1.72040200233459</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.69627964496613</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.68373572826385</t>
+    <t xml:space="preserve">1.72040176391602</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.69627976417542</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.68373584747314</t>
   </si>
   <si>
     <t xml:space="preserve">1.62101781368256</t>
   </si>
   <si>
-    <t xml:space="preserve">1.64996480941772</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.55444025993347</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.5650542974472</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.65478909015656</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.69049000740051</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.64128053188324</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.60750925540924</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.65285909175873</t>
+    <t xml:space="preserve">1.64996469020844</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.55444002151489</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.56505453586578</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.65478932857513</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.69048988819122</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.64128041267395</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.60750913619995</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.65285897254944</t>
   </si>
   <si>
     <t xml:space="preserve">1.66443824768066</t>
   </si>
   <si>
-    <t xml:space="preserve">1.69531452655792</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.71847176551819</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.68759572505951</t>
+    <t xml:space="preserve">1.69531440734863</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.71847188472748</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.68759548664093</t>
   </si>
   <si>
     <t xml:space="preserve">1.7445240020752</t>
   </si>
   <si>
-    <t xml:space="preserve">1.74741876125336</t>
+    <t xml:space="preserve">1.74741852283478</t>
   </si>
   <si>
     <t xml:space="preserve">1.71268272399902</t>
   </si>
   <si>
-    <t xml:space="preserve">1.67987608909607</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.63549149036407</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.58049249649048</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.60461485385895</t>
+    <t xml:space="preserve">1.67987632751465</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.63549160957336</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.58049273490906</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.60461449623108</t>
   </si>
   <si>
     <t xml:space="preserve">1.53610777854919</t>
   </si>
   <si>
-    <t xml:space="preserve">1.60847413539886</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.61233365535736</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.5399671792984</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.51584506034851</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.54961633682251</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.55251061916351</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.59786057472229</t>
+    <t xml:space="preserve">1.60847401618958</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.61233377456665</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.53996706008911</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.51584494113922</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.54961597919464</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.55251097679138</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.59786081314087</t>
   </si>
   <si>
     <t xml:space="preserve">1.561194896698</t>
   </si>
   <si>
-    <t xml:space="preserve">1.63452661037445</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.63935089111328</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.61619317531586</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.67408692836761</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.77540099620819</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.81496119499207</t>
+    <t xml:space="preserve">1.63452637195587</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.63935124874115</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.61619329452515</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.67408680915833</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.7754008769989</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.81496143341064</t>
   </si>
   <si>
     <t xml:space="preserve">1.73584008216858</t>
@@ -608,49 +608,49 @@
     <t xml:space="preserve">1.82653975486755</t>
   </si>
   <si>
-    <t xml:space="preserve">1.86513543128967</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.96065986156464</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.05425429344177</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.04943013191223</t>
+    <t xml:space="preserve">1.86513566970825</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.96065998077393</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.05425477027893</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.04942965507507</t>
   </si>
   <si>
     <t xml:space="preserve">2.10153412818909</t>
   </si>
   <si>
-    <t xml:space="preserve">2.01372909545898</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.0465350151062</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.09477996826172</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.08899068832397</t>
+    <t xml:space="preserve">2.01372933387756</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.04653549194336</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.09477972984314</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.08899021148682</t>
   </si>
   <si>
     <t xml:space="preserve">2.06197381019592</t>
   </si>
   <si>
-    <t xml:space="preserve">2.04460549354553</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.92978322505951</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.90566110610962</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.88443338871002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.9500458240509</t>
+    <t xml:space="preserve">2.04460573196411</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.9297833442688</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.90566122531891</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.8844336271286</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.95004594326019</t>
   </si>
   <si>
     <t xml:space="preserve">1.98671185970306</t>
@@ -662,73 +662,73 @@
     <t xml:space="preserve">2.01662373542786</t>
   </si>
   <si>
-    <t xml:space="preserve">1.99539613723755</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.98574662208557</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.9278529882431</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.84583735466003</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.80820727348328</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.80048716068268</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.83715391159058</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.82750499248505</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.83329403400421</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.80531215667725</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.82846975326538</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.97513341903687</t>
+    <t xml:space="preserve">1.99539589881897</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.98574686050415</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.92785334587097</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.84583723545074</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.8082070350647</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.80048727989197</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.83715415000916</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.82750463485718</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.83329379558563</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.80531203746796</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.82847011089325</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.97513318061829</t>
   </si>
   <si>
     <t xml:space="preserve">1.93557286262512</t>
   </si>
   <si>
-    <t xml:space="preserve">2.06679821014404</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.28196859359741</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.31477499008179</t>
+    <t xml:space="preserve">2.06679844856262</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.28196835517883</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.31477475166321</t>
   </si>
   <si>
     <t xml:space="preserve">2.27907419204712</t>
   </si>
   <si>
-    <t xml:space="preserve">2.32152915000916</t>
+    <t xml:space="preserve">2.32152962684631</t>
   </si>
   <si>
     <t xml:space="preserve">2.37073922157288</t>
   </si>
   <si>
-    <t xml:space="preserve">2.33214330673218</t>
+    <t xml:space="preserve">2.3321430683136</t>
   </si>
   <si>
     <t xml:space="preserve">2.39486122131348</t>
   </si>
   <si>
-    <t xml:space="preserve">2.41464138031006</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.39775586128235</t>
+    <t xml:space="preserve">2.41464185714722</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.39775562286377</t>
   </si>
   <si>
     <t xml:space="preserve">2.41222953796387</t>
@@ -737,13 +737,13 @@
     <t xml:space="preserve">2.46529817581177</t>
   </si>
   <si>
-    <t xml:space="preserve">2.48942065238953</t>
+    <t xml:space="preserve">2.48942041397095</t>
   </si>
   <si>
     <t xml:space="preserve">2.496657371521</t>
   </si>
   <si>
-    <t xml:space="preserve">2.44117617607117</t>
+    <t xml:space="preserve">2.44117641448975</t>
   </si>
   <si>
     <t xml:space="preserve">2.54248976707458</t>
@@ -752,19 +752,19 @@
     <t xml:space="preserve">2.63897848129272</t>
   </si>
   <si>
-    <t xml:space="preserve">2.59555888175964</t>
+    <t xml:space="preserve">2.59555840492249</t>
   </si>
   <si>
     <t xml:space="preserve">2.55696272850037</t>
   </si>
   <si>
-    <t xml:space="preserve">2.42911529541016</t>
+    <t xml:space="preserve">2.429114818573</t>
   </si>
   <si>
     <t xml:space="preserve">2.41705322265625</t>
   </si>
   <si>
-    <t xml:space="preserve">2.56178712844849</t>
+    <t xml:space="preserve">2.56178760528564</t>
   </si>
   <si>
     <t xml:space="preserve">2.53766489028931</t>
@@ -773,13 +773,13 @@
     <t xml:space="preserve">2.57867312431335</t>
   </si>
   <si>
-    <t xml:space="preserve">2.58832240104675</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.72823143005371</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.77165126800537</t>
+    <t xml:space="preserve">2.58832192420959</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.72823119163513</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.77165102958679</t>
   </si>
   <si>
     <t xml:space="preserve">2.7065212726593</t>
@@ -788,34 +788,34 @@
     <t xml:space="preserve">2.71375751495361</t>
   </si>
   <si>
-    <t xml:space="preserve">2.74752926826477</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.70410943031311</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.57626104354858</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.52801561355591</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.58590960502625</t>
+    <t xml:space="preserve">2.74752902984619</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.70410895347595</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.57626080513</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.52801609039307</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.58590936660767</t>
   </si>
   <si>
     <t xml:space="preserve">2.59797048568726</t>
   </si>
   <si>
-    <t xml:space="preserve">2.66068887710571</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.50871777534485</t>
+    <t xml:space="preserve">2.66068863868713</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.50871825218201</t>
   </si>
   <si>
     <t xml:space="preserve">2.42187786102295</t>
   </si>
   <si>
-    <t xml:space="preserve">2.45082473754883</t>
+    <t xml:space="preserve">2.45082497596741</t>
   </si>
   <si>
     <t xml:space="preserve">2.2945122718811</t>
@@ -827,28 +827,28 @@
     <t xml:space="preserve">2.38135266304016</t>
   </si>
   <si>
-    <t xml:space="preserve">2.32056450843811</t>
+    <t xml:space="preserve">2.32056427001953</t>
   </si>
   <si>
     <t xml:space="preserve">2.24047803878784</t>
   </si>
   <si>
-    <t xml:space="preserve">2.17100620269775</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.1478488445282</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.14495468139648</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.06293869018555</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.02627277374268</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.99732601642609</t>
+    <t xml:space="preserve">2.17100596427917</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.14784908294678</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.14495444297791</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.06293845176697</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.0262725353241</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.9973258972168</t>
   </si>
   <si>
     <t xml:space="preserve">2.16135740280151</t>
@@ -860,7 +860,7 @@
     <t xml:space="preserve">2.26749563217163</t>
   </si>
   <si>
-    <t xml:space="preserve">2.20574235916138</t>
+    <t xml:space="preserve">2.20574259757996</t>
   </si>
   <si>
     <t xml:space="preserve">2.113112449646</t>
@@ -872,13 +872,13 @@
     <t xml:space="preserve">2.18837428092957</t>
   </si>
   <si>
-    <t xml:space="preserve">2.25977659225464</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.22214555740356</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.16521716117859</t>
+    <t xml:space="preserve">2.25977635383606</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.22214579582214</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.16521692276001</t>
   </si>
   <si>
     <t xml:space="preserve">2.16907644271851</t>
@@ -890,7 +890,7 @@
     <t xml:space="preserve">2.25012731552124</t>
   </si>
   <si>
-    <t xml:space="preserve">2.31766963005066</t>
+    <t xml:space="preserve">2.31767010688782</t>
   </si>
   <si>
     <t xml:space="preserve">2.32635426521301</t>
@@ -899,31 +899,31 @@
     <t xml:space="preserve">2.39196681976318</t>
   </si>
   <si>
-    <t xml:space="preserve">2.36494970321655</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.32249402999878</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.3369677066803</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.29354810714722</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.26267075538635</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.25784611701965</t>
+    <t xml:space="preserve">2.36494946479797</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.3224937915802</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.33696746826172</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.29354786872864</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.26267099380493</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.25784635543823</t>
   </si>
   <si>
     <t xml:space="preserve">2.17872524261475</t>
   </si>
   <si>
-    <t xml:space="preserve">2.19512867927551</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.19319891929626</t>
+    <t xml:space="preserve">2.19512796401978</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.19319868087769</t>
   </si>
   <si>
     <t xml:space="preserve">2.20960187911987</t>
@@ -932,514 +932,514 @@
     <t xml:space="preserve">2.17390131950378</t>
   </si>
   <si>
-    <t xml:space="preserve">2.12179613113403</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.10442900657654</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.21153116226196</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.36398434638977</t>
+    <t xml:space="preserve">2.12179636955261</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.10442924499512</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.21153163909912</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.36398410797119</t>
   </si>
   <si>
     <t xml:space="preserve">2.39872074127197</t>
   </si>
   <si>
-    <t xml:space="preserve">2.34661674499512</t>
+    <t xml:space="preserve">2.34661650657654</t>
   </si>
   <si>
     <t xml:space="preserve">2.41946601867676</t>
   </si>
   <si>
-    <t xml:space="preserve">2.48218393325806</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.51836729049683</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.45564961433411</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.43635153770447</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.29837226867676</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.26170611381531</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.34468626976013</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.30609083175659</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.25302147865295</t>
+    <t xml:space="preserve">2.48218417167664</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.51836776733398</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.45564937591553</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.43635201454163</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.2983717918396</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.26170563697815</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.34468674659729</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.30609107017517</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.25302195549011</t>
   </si>
   <si>
     <t xml:space="preserve">2.22697019577026</t>
   </si>
   <si>
+    <t xml:space="preserve">2.26074123382568</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.2499897480011</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.25096750259399</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.28224396705627</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.27931189537048</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.25292181968689</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.18450331687927</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.18548130989075</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.13074684143066</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.1757071018219</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.14833974838257</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.10924339294434</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.07698893547058</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.08089876174927</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.15811324119568</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.1512713432312</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.10631132125854</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.15909075737</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.13758778572083</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.04082465171814</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.0535306930542</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.00075101852417</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.09067225456238</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.08187580108643</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.13661026954651</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.14931631088257</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.16886520385742</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.15713596343994</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.1336784362793</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.27149271965027</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.34870743751526</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.29201817512512</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.29788303375244</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.29104042053223</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.32231783866882</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.36434698104858</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.41419410705566</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.42103576660156</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.41908144950867</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.4337420463562</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.35457229614258</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.37021040916443</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.30667972564697</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.28126692771912</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.25389885902405</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.2871310710907</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.2988600730896</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.27344727516174</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.26953744888306</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.31352090835571</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.45328998565674</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.42005801200867</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.40246534347534</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.31743097305298</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.39464545249939</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.38389444351196</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.35750389099121</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.32622742652893</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.29690551757812</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.31938481330872</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.3291597366333</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.26856064796448</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.29299569129944</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.31254363059998</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.34382104873657</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.30863404273987</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.27247023582458</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.23337388038635</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.21382570266724</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.27735757827759</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.34773063659668</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.30081462860107</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.2421703338623</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.26269578933716</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.29006338119507</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.33795595169067</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.2861533164978</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.35359477996826</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.42299103736877</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.46306443214417</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.47283887863159</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.51437854766846</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.50704765319824</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.43276453018188</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.3917133808136</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.26171851158142</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.1952543258667</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.14736199378967</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.17081952095032</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.14638495445251</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.14051985740662</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.07210183143616</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.07894325256348</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.09946894645691</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.07601118087769</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.04375743865967</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.05450820922852</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.04473423957825</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.03887033462524</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.11315274238586</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.05939531326294</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.02616381645203</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.98804473876953</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.90105557441711</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.08969521522522</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.06721448898315</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.08578586578369</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.03984761238098</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.08285307884216</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.01345705986023</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.0466890335083</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.01834440231323</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.00661587715149</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.06623721122742</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.16202259063721</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.24607992172241</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.17961668968201</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.2382607460022</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.22653198242188</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.19916415214539</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.27051520347595</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.21773529052734</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.07796597480774</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.03691482543945</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.03105068206787</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.09849238395691</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.08676290512085</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.08871793746948</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.0476667881012</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.0584180355072</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.1151077747345</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.05744004249573</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.03300523757935</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.07307934761047</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.07503366470337</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.11119747161865</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.20600652694702</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.22848653793335</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.20405149459839</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.16104531288147</t>
+  </si>
+  <si>
     <t xml:space="preserve">2.26074147224426</t>
   </si>
   <si>
-    <t xml:space="preserve">2.24998950958252</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.25096702575684</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.28224396705627</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.27931189537048</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.25292181968689</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.18450379371643</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.18548130989075</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.13074684143066</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.17570662498474</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.14833974838257</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.10924315452576</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.07698893547058</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.08089852333069</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.15811347961426</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.15127158164978</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.10631108283997</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.15909099578857</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.13758778572083</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.04082465171814</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.05353093147278</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.00075125694275</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.09067225456238</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.081876039505</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.13661026954651</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.14931631088257</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.16886568069458</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.15713548660278</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.1336784362793</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.27149295806885</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.34870767593384</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.29201793670654</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.29788279533386</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.29104042053223</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.3223180770874</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.36434650421143</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.41419458389282</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.42103576660156</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.41908168792725</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.4337420463562</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.354572057724</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.37021064758301</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.30667948722839</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.28126692771912</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.25389909744263</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.2871310710907</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.29885983467102</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.27344727516174</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.26953768730164</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.31352114677429</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.45329022407532</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.42005801200867</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.40246558189392</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.31743097305298</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.39464545249939</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.38389420509338</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.35750412940979</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.32622766494751</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.29690527915955</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.31938505172729</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.32915949821472</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.2685604095459</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.29299569129944</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.31254363059998</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.34382104873657</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.30863380432129</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.27247047424316</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.23337364196777</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.21382594108582</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.27735757827759</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.3477303981781</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.30081486701965</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.24217009544373</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.26269578933716</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.29006338119507</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.33795642852783</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.28615355491638</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.35359454154968</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.4229907989502</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.46306443214417</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.47283864021301</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.51437830924988</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.50704741477966</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.43276453018188</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.39171361923218</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.26171851158142</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.19525456428528</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.14736175537109</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.1708197593689</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.14638471603394</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.14051985740662</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.072101354599</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.07894325256348</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.09946894645691</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.07601141929626</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.04375743865967</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.05450797080994</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.04473423957825</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.03887009620667</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.11315321922302</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.05939531326294</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.02616357803345</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.98804485797882</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.90105581283569</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.0896954536438</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.06721448898315</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.08578610420227</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.03984785079956</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.08285307884216</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.01345729827881</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.0466890335083</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.01834440231323</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.00661563873291</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.06623697280884</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.16202282905579</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.24608016014099</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.17961668968201</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.2382607460022</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.22653245925903</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.19916415214539</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.27051544189453</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.21773529052734</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.07796573638916</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.03691506385803</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.03105044364929</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.09849214553833</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.08676266670227</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.08871817588806</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.0476667881012</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.05841779708862</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.1151077747345</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.05744028091431</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.03300499916077</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.07307934761047</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.07503414154053</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.11119747161865</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.20600652694702</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.22848677635193</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.20405149459839</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.16104555130005</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.26074171066284</t>
-  </si>
-  <si>
     <t xml:space="preserve">2.35261702537537</t>
   </si>
   <si>
-    <t xml:space="preserve">2.35066270828247</t>
+    <t xml:space="preserve">2.35066246986389</t>
   </si>
   <si>
     <t xml:space="preserve">2.36776733398438</t>
   </si>
   <si>
-    <t xml:space="preserve">2.27686834335327</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.29543900489807</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.27784562110901</t>
+    <t xml:space="preserve">2.27686858177185</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.29543876647949</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.27784538269043</t>
   </si>
   <si>
     <t xml:space="preserve">2.21578025817871</t>
   </si>
   <si>
-    <t xml:space="preserve">2.22408819198608</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.30179262161255</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.25194454193115</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.22213387489319</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.33746767044067</t>
+    <t xml:space="preserve">2.2240879535675</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.30179238319397</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.25194478034973</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.22213363647461</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.33746743202209</t>
   </si>
   <si>
     <t xml:space="preserve">2.34186601638794</t>
@@ -1448,34 +1448,34 @@
     <t xml:space="preserve">2.33209156990051</t>
   </si>
   <si>
-    <t xml:space="preserve">2.33600091934204</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.28957509994507</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.37656450271606</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.37705278396606</t>
+    <t xml:space="preserve">2.3360013961792</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.28957486152649</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.37656426429749</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.37705254554749</t>
   </si>
   <si>
     <t xml:space="preserve">2.38145112991333</t>
   </si>
   <si>
-    <t xml:space="preserve">2.37900733947754</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.40735149383545</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.38731527328491</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.20551824569702</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.29592776298523</t>
+    <t xml:space="preserve">2.37900710105896</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.40735173225403</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.38731503486633</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.20551800727844</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.29592752456665</t>
   </si>
   <si>
     <t xml:space="preserve">2.32720518112183</t>
@@ -1487,109 +1487,109 @@
     <t xml:space="preserve">2.29641675949097</t>
   </si>
   <si>
-    <t xml:space="preserve">2.24461364746094</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.24901175498962</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.27540254592896</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.28322148323059</t>
+    <t xml:space="preserve">2.24461388587952</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.24901223182678</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.2754020690918</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.28322124481201</t>
   </si>
   <si>
     <t xml:space="preserve">2.26758289337158</t>
   </si>
   <si>
-    <t xml:space="preserve">2.22359943389893</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.22995257377625</t>
+    <t xml:space="preserve">2.22359919548035</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.22995281219482</t>
   </si>
   <si>
     <t xml:space="preserve">2.21040511131287</t>
   </si>
   <si>
-    <t xml:space="preserve">2.22555470466614</t>
+    <t xml:space="preserve">2.22555446624756</t>
   </si>
   <si>
     <t xml:space="preserve">2.20698356628418</t>
   </si>
   <si>
-    <t xml:space="preserve">2.20893859863281</t>
+    <t xml:space="preserve">2.20893883705139</t>
   </si>
   <si>
     <t xml:space="preserve">2.29446125030518</t>
   </si>
   <si>
-    <t xml:space="preserve">2.30276966094971</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.3115656375885</t>
+    <t xml:space="preserve">2.30276942253113</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.31156587600708</t>
   </si>
   <si>
     <t xml:space="preserve">2.33502411842346</t>
   </si>
   <si>
-    <t xml:space="preserve">2.3848717212677</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.35652732849121</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.36287999153137</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.38829278945923</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.34479808807373</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.31547570228577</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.33013725280762</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.31889700889587</t>
+    <t xml:space="preserve">2.38487195968628</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.35652756690979</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.36288022994995</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.38829255104065</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.34479784965515</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.31547546386719</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.33013701438904</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.31889724731445</t>
   </si>
   <si>
     <t xml:space="preserve">2.3306257724762</t>
   </si>
   <si>
-    <t xml:space="preserve">2.31303238868713</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.30570220947266</t>
+    <t xml:space="preserve">2.31303262710571</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.30570197105408</t>
   </si>
   <si>
     <t xml:space="preserve">2.3966007232666</t>
   </si>
   <si>
-    <t xml:space="preserve">2.40539717674255</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.45231294631958</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.48749971389771</t>
+    <t xml:space="preserve">2.40539741516113</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.45231318473816</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.48749947547913</t>
   </si>
   <si>
     <t xml:space="preserve">2.51584410667419</t>
   </si>
   <si>
-    <t xml:space="preserve">2.44205021858215</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.44253897666931</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.28028917312622</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.30131053924561</t>
+    <t xml:space="preserve">2.44204998016357</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.44253873825073</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.2802894115448</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.30131030082703</t>
   </si>
   <si>
     <t xml:space="preserve">2.33834743499756</t>
@@ -1598,16 +1598,16 @@
     <t xml:space="preserve">2.36387300491333</t>
   </si>
   <si>
-    <t xml:space="preserve">2.33484387397766</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.28779673576355</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.15416240692139</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.04555344581604</t>
+    <t xml:space="preserve">2.33484411239624</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.28779625892639</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.15416216850281</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.04555368423462</t>
   </si>
   <si>
     <t xml:space="preserve">2.05306100845337</t>
@@ -1616,22 +1616,22 @@
     <t xml:space="preserve">2.0535614490509</t>
   </si>
   <si>
-    <t xml:space="preserve">2.21522378921509</t>
+    <t xml:space="preserve">2.21522402763367</t>
   </si>
   <si>
     <t xml:space="preserve">2.15015840530396</t>
   </si>
   <si>
-    <t xml:space="preserve">2.07708501815796</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.07608437538147</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.11612415313721</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.05906748771667</t>
+    <t xml:space="preserve">2.07708477973938</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.07608461380005</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.11612439155579</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.05906701087952</t>
   </si>
   <si>
     <t xml:space="preserve">2.14865708351135</t>
@@ -1640,31 +1640,31 @@
     <t xml:space="preserve">2.17418313026428</t>
   </si>
   <si>
-    <t xml:space="preserve">2.20921730995178</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.23624515533447</t>
+    <t xml:space="preserve">2.20921778678894</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.23624467849731</t>
   </si>
   <si>
     <t xml:space="preserve">2.17768621444702</t>
   </si>
   <si>
-    <t xml:space="preserve">2.16717576980591</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.24074959754944</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.29730629920959</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.22973871231079</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.39390349388123</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.34485459327698</t>
+    <t xml:space="preserve">2.16717553138733</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.24074935913086</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.29730606079102</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.22973895072937</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.39390325546265</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.3448543548584</t>
   </si>
   <si>
     <t xml:space="preserve">2.35786747932434</t>
@@ -1673,25 +1673,25 @@
     <t xml:space="preserve">2.32433319091797</t>
   </si>
   <si>
-    <t xml:space="preserve">2.34535455703735</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.35586476325989</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.34685587882996</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.34935879707336</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.34034991264343</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.3863959312439</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.39440393447876</t>
+    <t xml:space="preserve">2.34535479545593</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.35586500167847</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.34685611724854</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.34935927391052</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.34034943580627</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.38639569282532</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.39440369606018</t>
   </si>
   <si>
     <t xml:space="preserve">2.3478569984436</t>
@@ -1700,22 +1700,22 @@
     <t xml:space="preserve">2.30881786346436</t>
   </si>
   <si>
-    <t xml:space="preserve">2.32483339309692</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.35686612129211</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.31532502174377</t>
+    <t xml:space="preserve">2.32483386993408</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.35686635971069</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.3153247833252</t>
   </si>
   <si>
     <t xml:space="preserve">2.27228140830994</t>
   </si>
   <si>
-    <t xml:space="preserve">2.31832766532898</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.31582427024841</t>
+    <t xml:space="preserve">2.3183274269104</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.31582450866699</t>
   </si>
   <si>
     <t xml:space="preserve">2.34985852241516</t>
@@ -1727,13 +1727,13 @@
     <t xml:space="preserve">2.35936856269836</t>
   </si>
   <si>
-    <t xml:space="preserve">2.39290237426758</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.38189125061035</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.29680585861206</t>
+    <t xml:space="preserve">2.39290189743042</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.38189101219177</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.29680609703064</t>
   </si>
   <si>
     <t xml:space="preserve">2.29079961776733</t>
@@ -1745,34 +1745,34 @@
     <t xml:space="preserve">2.31232142448425</t>
   </si>
   <si>
-    <t xml:space="preserve">2.17568421363831</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.15115976333618</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.12112927436829</t>
+    <t xml:space="preserve">2.17568445205688</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.15115928649902</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.12112951278687</t>
   </si>
   <si>
     <t xml:space="preserve">2.0685760974884</t>
   </si>
   <si>
-    <t xml:space="preserve">2.04905724525452</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.04655480384827</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.00200963020325</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.00251030921936</t>
+    <t xml:space="preserve">2.04905700683594</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.04655504226685</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.00200986862183</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.0025098323822</t>
   </si>
   <si>
     <t xml:space="preserve">2.04705476760864</t>
   </si>
   <si>
-    <t xml:space="preserve">2.04605460166931</t>
+    <t xml:space="preserve">2.04605412483215</t>
   </si>
   <si>
     <t xml:space="preserve">2.03003764152527</t>
@@ -1781,43 +1781,43 @@
     <t xml:space="preserve">2.02503299713135</t>
   </si>
   <si>
-    <t xml:space="preserve">2.01702547073364</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.9844925403595</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.99700474739075</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.92192947864532</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.90140891075134</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.91041839122772</t>
+    <t xml:space="preserve">2.01702523231506</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.98449230194092</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.99700486660004</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.92192995548248</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.90140914916992</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.91041827201843</t>
   </si>
   <si>
     <t xml:space="preserve">1.98048806190491</t>
   </si>
   <si>
-    <t xml:space="preserve">2.06507277488708</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.06907677650452</t>
+    <t xml:space="preserve">2.06507301330566</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.0690770149231</t>
   </si>
   <si>
     <t xml:space="preserve">2.12413215637207</t>
   </si>
   <si>
-    <t xml:space="preserve">2.11362218856812</t>
+    <t xml:space="preserve">2.11362195014954</t>
   </si>
   <si>
     <t xml:space="preserve">2.11562347412109</t>
   </si>
   <si>
-    <t xml:space="preserve">2.10861682891846</t>
+    <t xml:space="preserve">2.10861706733704</t>
   </si>
   <si>
     <t xml:space="preserve">2.15716576576233</t>
@@ -1826,40 +1826,40 @@
     <t xml:space="preserve">2.18969798088074</t>
   </si>
   <si>
-    <t xml:space="preserve">2.16917777061462</t>
+    <t xml:space="preserve">2.1691780090332</t>
   </si>
   <si>
     <t xml:space="preserve">2.12763643264771</t>
   </si>
   <si>
-    <t xml:space="preserve">2.15216064453125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.17868781089783</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.20070910453796</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.9960036277771</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.91742527484894</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.88389134407043</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.85936641693115</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.87087821960449</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.83684396743774</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.80631351470947</t>
+    <t xml:space="preserve">2.15216040611267</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.17868757247925</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.20070934295654</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.99600338935852</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.91742479801178</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.88389146327972</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.85936617851257</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.87087833881378</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.83684432506561</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.80631339550018</t>
   </si>
   <si>
     <t xml:space="preserve">1.77027702331543</t>
@@ -1868,76 +1868,76 @@
     <t xml:space="preserve">1.80881571769714</t>
   </si>
   <si>
-    <t xml:space="preserve">1.77478122711182</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.78829514980316</t>
+    <t xml:space="preserve">1.7747814655304</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.788294672966</t>
   </si>
   <si>
     <t xml:space="preserve">1.80080771446228</t>
   </si>
   <si>
-    <t xml:space="preserve">1.78529250621796</t>
+    <t xml:space="preserve">1.78529226779938</t>
   </si>
   <si>
     <t xml:space="preserve">1.78779447078705</t>
   </si>
   <si>
-    <t xml:space="preserve">1.7492561340332</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.75576305389404</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.69169855117798</t>
+    <t xml:space="preserve">1.74925577640533</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.75576281547546</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.6916983127594</t>
   </si>
   <si>
     <t xml:space="preserve">1.65516114234924</t>
   </si>
   <si>
-    <t xml:space="preserve">1.60811400413513</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.64515173435211</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.63263916969299</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.70471143722534</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.69470119476318</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.6806868314743</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.69069719314575</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.75926601886749</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.69870507717133</t>
+    <t xml:space="preserve">1.60811412334442</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.64515161514282</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.63263928890228</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.70471155643463</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.69470131397247</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.68068695068359</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.69069731235504</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.75926625728607</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.6987053155899</t>
   </si>
   <si>
     <t xml:space="preserve">1.6861926317215</t>
   </si>
   <si>
-    <t xml:space="preserve">1.71672344207764</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.72973644733429</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.74525201320648</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.74775457382202</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.69670343399048</t>
+    <t xml:space="preserve">1.71672368049622</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.72973668575287</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.74525213241577</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.74775469303131</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.69670355319977</t>
   </si>
   <si>
     <t xml:space="preserve">1.71071708202362</t>
@@ -1949,34 +1949,34 @@
     <t xml:space="preserve">1.69520175457001</t>
   </si>
   <si>
-    <t xml:space="preserve">1.67568230628967</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.73624277114868</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.74625301361084</t>
+    <t xml:space="preserve">1.67568242549896</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.73624265193939</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.74625313282013</t>
   </si>
   <si>
     <t xml:space="preserve">1.74725437164307</t>
   </si>
   <si>
-    <t xml:space="preserve">1.84084808826447</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.77628326416016</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.79229927062988</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.80130815505981</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.88439226150513</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.85235965251923</t>
+    <t xml:space="preserve">1.84084784984589</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.77628302574158</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.79229915142059</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.80130839347839</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.88439214229584</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.85235977172852</t>
   </si>
   <si>
     <t xml:space="preserve">1.88689398765564</t>
@@ -1985,7 +1985,7 @@
     <t xml:space="preserve">1.82683408260345</t>
   </si>
   <si>
-    <t xml:space="preserve">1.7978048324585</t>
+    <t xml:space="preserve">1.79780471324921</t>
   </si>
   <si>
     <t xml:space="preserve">1.76727414131165</t>
@@ -1997,118 +1997,118 @@
     <t xml:space="preserve">1.74325025081635</t>
   </si>
   <si>
-    <t xml:space="preserve">1.71622276306152</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.68268930912018</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.67468106746674</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.70871579647064</t>
+    <t xml:space="preserve">1.71622240543365</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.68268942832947</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.67468118667603</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.70871555805206</t>
   </si>
   <si>
     <t xml:space="preserve">1.67618262767792</t>
   </si>
   <si>
-    <t xml:space="preserve">1.66366994380951</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.64114761352539</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.68369042873383</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.64965641498566</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.63864493370056</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.69369983673096</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.70421075820923</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.66667354106903</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.65966582298279</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.66467118263245</t>
+    <t xml:space="preserve">1.66366982460022</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.64114785194397</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.6836906671524</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.64965629577637</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.63864481449127</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.69370007514954</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.70421063899994</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.66667342185974</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.6596657037735</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.66467094421387</t>
   </si>
   <si>
     <t xml:space="preserve">1.63664329051971</t>
   </si>
   <si>
-    <t xml:space="preserve">1.57357931137085</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.49900460243225</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.53203773498535</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.53804433345795</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.52903521060944</t>
+    <t xml:space="preserve">1.57357943058014</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.49900472164154</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.53203797340393</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.53804421424866</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.52903497219086</t>
   </si>
   <si>
     <t xml:space="preserve">1.53704285621643</t>
   </si>
   <si>
-    <t xml:space="preserve">1.52853429317474</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.50601172447205</t>
+    <t xml:space="preserve">1.52853441238403</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.50601160526276</t>
   </si>
   <si>
     <t xml:space="preserve">1.51051616668701</t>
   </si>
   <si>
-    <t xml:space="preserve">1.57658278942108</t>
+    <t xml:space="preserve">1.57658290863037</t>
   </si>
   <si>
     <t xml:space="preserve">1.55756342411041</t>
   </si>
   <si>
-    <t xml:space="preserve">1.56156718730927</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.57508087158203</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.4794853925705</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.48398947715759</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.48649227619171</t>
+    <t xml:space="preserve">1.56156730651855</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.57508099079132</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.47948551177979</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.48398923873901</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.48649215698242</t>
   </si>
   <si>
     <t xml:space="preserve">1.48899447917938</t>
   </si>
   <si>
-    <t xml:space="preserve">1.52402985095978</t>
+    <t xml:space="preserve">1.52402973175049</t>
   </si>
   <si>
     <t xml:space="preserve">1.50851452350616</t>
   </si>
   <si>
-    <t xml:space="preserve">1.6416482925415</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.709716796875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.69219887256622</t>
+    <t xml:space="preserve">1.64164841175079</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.70971667766571</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.69219899177551</t>
   </si>
   <si>
     <t xml:space="preserve">1.68569207191467</t>
@@ -2117,103 +2117,103 @@
     <t xml:space="preserve">1.76377081871033</t>
   </si>
   <si>
-    <t xml:space="preserve">1.75676393508911</t>
+    <t xml:space="preserve">1.75676369667053</t>
   </si>
   <si>
     <t xml:space="preserve">1.74174857139587</t>
   </si>
   <si>
-    <t xml:space="preserve">1.71372079849243</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.73374056816101</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.75125777721405</t>
+    <t xml:space="preserve">1.71372032165527</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.7337406873703</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.7512583732605</t>
   </si>
   <si>
     <t xml:space="preserve">1.7627694606781</t>
   </si>
   <si>
-    <t xml:space="preserve">1.81031692028046</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.85085761547089</t>
+    <t xml:space="preserve">1.81031727790833</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.85085797309875</t>
   </si>
   <si>
     <t xml:space="preserve">1.84585320949554</t>
   </si>
   <si>
-    <t xml:space="preserve">1.83984684944153</t>
+    <t xml:space="preserve">1.83984696865082</t>
   </si>
   <si>
     <t xml:space="preserve">1.85486245155334</t>
   </si>
   <si>
-    <t xml:space="preserve">1.80030691623688</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.78178906440735</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.77077722549438</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.78128838539124</t>
+    <t xml:space="preserve">1.8003066778183</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.78178894519806</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.77077758312225</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.78128850460052</t>
   </si>
   <si>
     <t xml:space="preserve">1.81732428073883</t>
   </si>
   <si>
-    <t xml:space="preserve">1.85386145114899</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.86787474155426</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.86837565898895</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.8518590927124</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.82633316516876</t>
+    <t xml:space="preserve">1.8538613319397</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.86787462234497</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.86837553977966</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.85185885429382</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.82633304595947</t>
   </si>
   <si>
     <t xml:space="preserve">1.81882572174072</t>
   </si>
   <si>
-    <t xml:space="preserve">1.8033105134964</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.83183884620667</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.8243316411972</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.8223295211792</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.84735429286957</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.833340883255</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.85135805606842</t>
+    <t xml:space="preserve">1.80331063270569</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.83183908462524</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.82433140277863</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.82232940196991</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.84735441207886</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.83334076404572</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.85135853290558</t>
   </si>
   <si>
     <t xml:space="preserve">1.85336065292358</t>
   </si>
   <si>
-    <t xml:space="preserve">1.86937642097473</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.87037777900696</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.89990746974945</t>
+    <t xml:space="preserve">1.86937654018402</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.87037765979767</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.89990735054016</t>
   </si>
   <si>
     <t xml:space="preserve">1.93544352054596</t>
@@ -2228,148 +2228,148 @@
     <t xml:space="preserve">2.07358145713806</t>
   </si>
   <si>
-    <t xml:space="preserve">2.09360194206238</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.07308077812195</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.05506324768066</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.08859705924988</t>
+    <t xml:space="preserve">2.09360218048096</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.07308101654053</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.05506348609924</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.0885968208313</t>
   </si>
   <si>
     <t xml:space="preserve">2.10561394691467</t>
   </si>
   <si>
-    <t xml:space="preserve">2.11161994934082</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.14415264129639</t>
+    <t xml:space="preserve">2.11161947250366</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.14415287971497</t>
   </si>
   <si>
     <t xml:space="preserve">2.1096179485321</t>
   </si>
   <si>
-    <t xml:space="preserve">2.10311126708984</t>
+    <t xml:space="preserve">2.10311102867126</t>
   </si>
   <si>
     <t xml:space="preserve">2.05956792831421</t>
   </si>
   <si>
-    <t xml:space="preserve">2.04805588722229</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.0040123462677</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.98198986053467</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.95195984840393</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.96947765350342</t>
+    <t xml:space="preserve">2.04805612564087</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.00401210784912</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.98198974132538</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.95195960998535</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.96947753429413</t>
   </si>
   <si>
     <t xml:space="preserve">1.93494248390198</t>
   </si>
   <si>
-    <t xml:space="preserve">1.97848689556122</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.92558360099792</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.87486898899078</t>
+    <t xml:space="preserve">1.97848665714264</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.9255838394165</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.87486886978149</t>
   </si>
   <si>
     <t xml:space="preserve">1.83502221107483</t>
   </si>
   <si>
-    <t xml:space="preserve">1.81070041656494</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.82933020591736</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.78068602085114</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.78172087669373</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.77240645885468</t>
+    <t xml:space="preserve">1.81070077419281</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.82933068275452</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.78068614006042</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.78172075748444</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.77240657806396</t>
   </si>
   <si>
     <t xml:space="preserve">1.75998628139496</t>
   </si>
   <si>
-    <t xml:space="preserve">1.75118851661682</t>
+    <t xml:space="preserve">1.7511887550354</t>
   </si>
   <si>
     <t xml:space="preserve">1.73721647262573</t>
   </si>
   <si>
-    <t xml:space="preserve">1.76774919033051</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.73566436767578</t>
+    <t xml:space="preserve">1.76774907112122</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.73566424846649</t>
   </si>
   <si>
     <t xml:space="preserve">1.71496486663818</t>
   </si>
   <si>
-    <t xml:space="preserve">1.7118593454361</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.76567888259888</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.78223824501038</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.76205635070801</t>
+    <t xml:space="preserve">1.71185946464539</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.7656786441803</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.78223836421967</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.76205623149872</t>
   </si>
   <si>
     <t xml:space="preserve">1.78327333927155</t>
   </si>
   <si>
-    <t xml:space="preserve">1.77706289291382</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.79051768779755</t>
+    <t xml:space="preserve">1.77706277370453</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.79051804542542</t>
   </si>
   <si>
     <t xml:space="preserve">1.83088254928589</t>
   </si>
   <si>
-    <t xml:space="preserve">1.86503732204437</t>
+    <t xml:space="preserve">1.86503744125366</t>
   </si>
   <si>
     <t xml:space="preserve">1.86296701431274</t>
   </si>
   <si>
-    <t xml:space="preserve">1.89453399181366</t>
+    <t xml:space="preserve">1.89453387260437</t>
   </si>
   <si>
     <t xml:space="preserve">1.87383460998535</t>
   </si>
   <si>
-    <t xml:space="preserve">1.8727992773056</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.88366627693176</t>
+    <t xml:space="preserve">1.87279963493347</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.88366639614105</t>
   </si>
   <si>
     <t xml:space="preserve">1.85416996479034</t>
   </si>
   <si>
-    <t xml:space="preserve">1.84433734416962</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.88211441040039</t>
+    <t xml:space="preserve">1.84433722496033</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.8821142911911</t>
   </si>
   <si>
     <t xml:space="preserve">1.95559799671173</t>
@@ -2378,31 +2378,31 @@
     <t xml:space="preserve">2.01252174377441</t>
   </si>
   <si>
-    <t xml:space="preserve">2.01666188240051</t>
+    <t xml:space="preserve">2.01666164398193</t>
   </si>
   <si>
     <t xml:space="preserve">1.99854934215546</t>
   </si>
   <si>
-    <t xml:space="preserve">1.98199009895325</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.99026966094971</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.97370994091034</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.98250782489777</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.96853542327881</t>
+    <t xml:space="preserve">1.98198997974396</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.99026954174042</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.97371029853821</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.9825074672699</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.96853530406952</t>
   </si>
   <si>
     <t xml:space="preserve">1.99647998809814</t>
   </si>
   <si>
-    <t xml:space="preserve">1.96439528465271</t>
+    <t xml:space="preserve">1.96439552307129</t>
   </si>
   <si>
     <t xml:space="preserve">1.93955600261688</t>
@@ -2414,169 +2414,169 @@
     <t xml:space="preserve">1.93541634082794</t>
   </si>
   <si>
-    <t xml:space="preserve">1.88625454902649</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.87072932720184</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.8510650396347</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.82570731639862</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.7542941570282</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.74342656135559</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.79000115394592</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.76257383823395</t>
+    <t xml:space="preserve">1.88625419139862</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.87072920799255</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.85106492042542</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.8257075548172</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.75429427623749</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.7434264421463</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.7900013923645</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.76257407665253</t>
   </si>
   <si>
     <t xml:space="preserve">1.78948354721069</t>
   </si>
   <si>
-    <t xml:space="preserve">1.76464343070984</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.79828095436096</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.65597057342529</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.6207811832428</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.63941121101379</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.55868232250214</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.59283661842346</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.60887932777405</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.55764710903168</t>
+    <t xml:space="preserve">1.76464354991913</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.79828071594238</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.65597069263458</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.62078142166138</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.63941133022308</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.55868220329285</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.59283673763275</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.60887944698334</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.55764722824097</t>
   </si>
   <si>
     <t xml:space="preserve">1.58455681800842</t>
   </si>
   <si>
-    <t xml:space="preserve">1.59076690673828</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.57731223106384</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.58817911148071</t>
+    <t xml:space="preserve">1.59076714515686</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.57731211185455</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.58817923069</t>
   </si>
   <si>
     <t xml:space="preserve">1.66011047363281</t>
   </si>
   <si>
-    <t xml:space="preserve">1.64872634410858</t>
+    <t xml:space="preserve">1.64872622489929</t>
   </si>
   <si>
     <t xml:space="preserve">1.68132758140564</t>
   </si>
   <si>
-    <t xml:space="preserve">1.6678729057312</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.67149519920349</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.69943988323212</t>
+    <t xml:space="preserve">1.66787278652191</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.6714950799942</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.69944000244141</t>
   </si>
   <si>
     <t xml:space="preserve">1.71651697158813</t>
   </si>
   <si>
-    <t xml:space="preserve">1.72169172763824</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.72997176647186</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.78844833374023</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.80863034725189</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.79103565216064</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.81846272945404</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.86451983451843</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.87331736087799</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.81225252151489</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.8231201171875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.9028137922287</t>
+    <t xml:space="preserve">1.72169184684753</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.72997164726257</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.7884486913681</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.80863010883331</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.79103541374207</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.81846284866333</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.86451995372772</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.8733172416687</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.8122524023056</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.82312035560608</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.90281414985657</t>
   </si>
   <si>
     <t xml:space="preserve">1.84588980674744</t>
   </si>
   <si>
-    <t xml:space="preserve">1.81794512271881</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.79879856109619</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.80966544151306</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.83295238018036</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.8050080537796</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.81587553024292</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.79931509494781</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.80552566051483</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.81639325618744</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.88263189792633</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.90333139896393</t>
+    <t xml:space="preserve">1.8179452419281</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.7987984418869</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.80966532230377</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.83295261859894</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.80500781536102</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.81587564945221</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.7993152141571</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.80552542209625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.81639289855957</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.88263213634491</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.90333116054535</t>
   </si>
   <si>
     <t xml:space="preserve">1.94421339035034</t>
   </si>
   <si>
-    <t xml:space="preserve">1.97267472743988</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.02649426460266</t>
+    <t xml:space="preserve">1.97267496585846</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.02649402618408</t>
   </si>
   <si>
     <t xml:space="preserve">2.07927823066711</t>
@@ -2585,7 +2585,7 @@
     <t xml:space="preserve">2.10204815864563</t>
   </si>
   <si>
-    <t xml:space="preserve">2.12999224662781</t>
+    <t xml:space="preserve">2.12999176979065</t>
   </si>
   <si>
     <t xml:space="preserve">2.09066295623779</t>
@@ -2594,43 +2594,43 @@
     <t xml:space="preserve">2.08962845802307</t>
   </si>
   <si>
-    <t xml:space="preserve">2.10515284538269</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.10567045211792</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.06582355499268</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.07358551025391</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.06996321678162</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.13671970367432</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.16155862808228</t>
+    <t xml:space="preserve">2.10515260696411</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.1056706905365</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.06582379341125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.07358574867249</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.06996369361877</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.1367199420929</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.16155886650085</t>
   </si>
   <si>
     <t xml:space="preserve">2.17604899406433</t>
   </si>
   <si>
-    <t xml:space="preserve">2.20761632919312</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.18329358100891</t>
+    <t xml:space="preserve">2.20761656761169</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.18329334259033</t>
   </si>
   <si>
     <t xml:space="preserve">2.21951842308044</t>
   </si>
   <si>
-    <t xml:space="preserve">2.23556017875671</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.25056743621826</t>
+    <t xml:space="preserve">2.23555994033813</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.25056791305542</t>
   </si>
   <si>
     <t xml:space="preserve">2.24280548095703</t>
@@ -2639,7 +2639,7 @@
     <t xml:space="preserve">2.25936508178711</t>
   </si>
   <si>
-    <t xml:space="preserve">2.28679203987122</t>
+    <t xml:space="preserve">2.28679227828979</t>
   </si>
   <si>
     <t xml:space="preserve">2.35303115844727</t>
@@ -2648,55 +2648,55 @@
     <t xml:space="preserve">2.38459801673889</t>
   </si>
   <si>
-    <t xml:space="preserve">2.37114334106445</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.31421971321106</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.32715678215027</t>
+    <t xml:space="preserve">2.37114310264587</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.31421947479248</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.32715654373169</t>
   </si>
   <si>
     <t xml:space="preserve">2.32146406173706</t>
   </si>
   <si>
-    <t xml:space="preserve">2.30076479911804</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.27074980735779</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.27437281608582</t>
+    <t xml:space="preserve">2.30076456069946</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.27074933052063</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.27437257766724</t>
   </si>
   <si>
     <t xml:space="preserve">2.2277979850769</t>
   </si>
   <si>
-    <t xml:space="preserve">2.24435758590698</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.27178478240967</t>
+    <t xml:space="preserve">2.2443573474884</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.27178454399109</t>
   </si>
   <si>
     <t xml:space="preserve">2.28368759155273</t>
   </si>
   <si>
-    <t xml:space="preserve">2.30593967437744</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.27851271629333</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.30283403396606</t>
+    <t xml:space="preserve">2.30593943595886</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.27851247787476</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.30283451080322</t>
   </si>
   <si>
     <t xml:space="preserve">2.299729347229</t>
   </si>
   <si>
-    <t xml:space="preserve">2.33026146888733</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.31318426132202</t>
+    <t xml:space="preserve">2.33026123046875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.3131844997406</t>
   </si>
   <si>
     <t xml:space="preserve">2.34216356277466</t>
@@ -2708,16 +2708,16 @@
     <t xml:space="preserve">2.3369882106781</t>
   </si>
   <si>
-    <t xml:space="preserve">2.3338840007782</t>
+    <t xml:space="preserve">2.33388376235962</t>
   </si>
   <si>
     <t xml:space="preserve">2.3049042224884</t>
   </si>
   <si>
-    <t xml:space="preserve">2.31991124153137</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.3778703212738</t>
+    <t xml:space="preserve">2.31991147994995</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.37787008285522</t>
   </si>
   <si>
     <t xml:space="preserve">2.37631821632385</t>
@@ -2726,58 +2726,58 @@
     <t xml:space="preserve">2.32767415046692</t>
   </si>
   <si>
-    <t xml:space="preserve">2.33440136909485</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.35665345191956</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.38873791694641</t>
+    <t xml:space="preserve">2.33440113067627</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.35665321350098</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.38873815536499</t>
   </si>
   <si>
     <t xml:space="preserve">2.39080762863159</t>
   </si>
   <si>
-    <t xml:space="preserve">2.38045835494995</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.38822031021118</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.36700367927551</t>
+    <t xml:space="preserve">2.38045787811279</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.38822054862976</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.36700320243835</t>
   </si>
   <si>
     <t xml:space="preserve">2.36079335212708</t>
   </si>
   <si>
-    <t xml:space="preserve">2.37942314147949</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.36493301391602</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.39494776725769</t>
+    <t xml:space="preserve">2.37942290306091</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.36493325233459</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.39494752883911</t>
   </si>
   <si>
     <t xml:space="preserve">2.30749154090881</t>
   </si>
   <si>
-    <t xml:space="preserve">2.3080096244812</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.29351949691772</t>
+    <t xml:space="preserve">2.30800938606262</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.29351902008057</t>
   </si>
   <si>
     <t xml:space="preserve">2.34009385108948</t>
   </si>
   <si>
-    <t xml:space="preserve">2.31939387321472</t>
+    <t xml:space="preserve">2.31939363479614</t>
   </si>
   <si>
     <t xml:space="preserve">2.23866558074951</t>
   </si>
   <si>
-    <t xml:space="preserve">2.14758658409119</t>
+    <t xml:space="preserve">2.14758682250977</t>
   </si>
   <si>
     <t xml:space="preserve">2.19157338142395</t>
@@ -2789,13 +2789,13 @@
     <t xml:space="preserve">2.26505756378174</t>
   </si>
   <si>
-    <t xml:space="preserve">2.24384045600891</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.25263810157776</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.26298689842224</t>
+    <t xml:space="preserve">2.24384069442749</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.25263786315918</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.2629873752594</t>
   </si>
   <si>
     <t xml:space="preserve">2.34630346298218</t>
@@ -2807,52 +2807,52 @@
     <t xml:space="preserve">2.40322709083557</t>
   </si>
   <si>
-    <t xml:space="preserve">2.14292931556702</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.13568449020386</t>
+    <t xml:space="preserve">2.14292907714844</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.13568496704102</t>
   </si>
   <si>
     <t xml:space="preserve">2.1703565120697</t>
   </si>
   <si>
-    <t xml:space="preserve">2.10722303390503</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.98509466648102</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.98716485500336</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.03115200996399</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.95508027076721</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.86244928836823</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.72065651416779</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.67615222930908</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.61508858203888</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.58093452453613</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.36617600917816</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.29993689060211</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.30304181575775</t>
+    <t xml:space="preserve">2.10722327232361</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.98509442806244</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.98716509342194</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.03115177154541</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.95508003234863</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.8624495267868</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.72065699100494</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.67615234851837</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.61508882045746</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.58093464374542</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.36617588996887</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.29993712902069</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.30304205417633</t>
   </si>
   <si>
     <t xml:space="preserve">1.07172310352325</t>
@@ -2861,19 +2861,19 @@
     <t xml:space="preserve">1.31183910369873</t>
   </si>
   <si>
-    <t xml:space="preserve">1.21144604682922</t>
+    <t xml:space="preserve">1.21144616603851</t>
   </si>
   <si>
     <t xml:space="preserve">1.2073061466217</t>
   </si>
   <si>
-    <t xml:space="preserve">1.17522144317627</t>
+    <t xml:space="preserve">1.17522156238556</t>
   </si>
   <si>
     <t xml:space="preserve">1.19333386421204</t>
   </si>
   <si>
-    <t xml:space="preserve">1.33253860473633</t>
+    <t xml:space="preserve">1.33253872394562</t>
   </si>
   <si>
     <t xml:space="preserve">1.51935303211212</t>
@@ -2891,7 +2891,7 @@
     <t xml:space="preserve">1.40602278709412</t>
   </si>
   <si>
-    <t xml:space="preserve">1.40550518035889</t>
+    <t xml:space="preserve">1.40550529956818</t>
   </si>
   <si>
     <t xml:space="preserve">1.44897437095642</t>
@@ -2900,16 +2900,16 @@
     <t xml:space="preserve">1.40705716609955</t>
   </si>
   <si>
-    <t xml:space="preserve">1.39567279815674</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.38894498348236</t>
+    <t xml:space="preserve">1.39567267894745</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.38894486427307</t>
   </si>
   <si>
     <t xml:space="preserve">1.41585457324982</t>
   </si>
   <si>
-    <t xml:space="preserve">1.41016256809235</t>
+    <t xml:space="preserve">1.41016268730164</t>
   </si>
   <si>
     <t xml:space="preserve">1.34081828594208</t>
@@ -2921,19 +2921,19 @@
     <t xml:space="preserve">1.29320931434631</t>
   </si>
   <si>
-    <t xml:space="preserve">1.1979912519455</t>
+    <t xml:space="preserve">1.19799137115479</t>
   </si>
   <si>
     <t xml:space="preserve">1.14624238014221</t>
   </si>
   <si>
-    <t xml:space="preserve">1.15814459323883</t>
+    <t xml:space="preserve">1.15814447402954</t>
   </si>
   <si>
     <t xml:space="preserve">1.15917956829071</t>
   </si>
   <si>
-    <t xml:space="preserve">1.10898268222809</t>
+    <t xml:space="preserve">1.10898280143738</t>
   </si>
   <si>
     <t xml:space="preserve">1.10742998123169</t>
@@ -2942,22 +2942,22 @@
     <t xml:space="preserve">1.14468967914581</t>
   </si>
   <si>
-    <t xml:space="preserve">1.09708058834076</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.1281304359436</t>
+    <t xml:space="preserve">1.09708070755005</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.12813019752502</t>
   </si>
   <si>
     <t xml:space="preserve">1.19902646541595</t>
   </si>
   <si>
-    <t xml:space="preserve">1.21817302703857</t>
+    <t xml:space="preserve">1.21817326545715</t>
   </si>
   <si>
     <t xml:space="preserve">1.16538906097412</t>
   </si>
   <si>
-    <t xml:space="preserve">1.140549659729</t>
+    <t xml:space="preserve">1.14054989814758</t>
   </si>
   <si>
     <t xml:space="preserve">1.13847947120667</t>
@@ -2969,7 +2969,7 @@
     <t xml:space="preserve">1.10639560222626</t>
   </si>
   <si>
-    <t xml:space="preserve">1.09397518634796</t>
+    <t xml:space="preserve">1.09397506713867</t>
   </si>
   <si>
     <t xml:space="preserve">1.08673048019409</t>
@@ -2981,25 +2981,25 @@
     <t xml:space="preserve">1.04222631454468</t>
   </si>
   <si>
-    <t xml:space="preserve">1.0386039018631</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.08031642436981</t>
+    <t xml:space="preserve">1.03860402107239</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.0803165435791</t>
   </si>
   <si>
     <t xml:space="preserve">1.0201233625412</t>
   </si>
   <si>
-    <t xml:space="preserve">1.0024346113205</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.983425915241241</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.984218299388885</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.986858129501343</t>
+    <t xml:space="preserve">1.00243449211121</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.983425855636597</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.984218418598175</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.986858189105988</t>
   </si>
   <si>
     <t xml:space="preserve">1.0898209810257</t>
@@ -3008,37 +3008,37 @@
     <t xml:space="preserve">1.12942171096802</t>
   </si>
   <si>
-    <t xml:space="preserve">1.17483103275299</t>
+    <t xml:space="preserve">1.17483115196228</t>
   </si>
   <si>
     <t xml:space="preserve">1.13364660739899</t>
   </si>
   <si>
-    <t xml:space="preserve">1.16163086891174</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.1827517747879</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.22076857089996</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.22129654884338</t>
+    <t xml:space="preserve">1.16163074970245</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.18275189399719</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.22076869010925</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.22129666805267</t>
   </si>
   <si>
     <t xml:space="preserve">1.34010016918182</t>
   </si>
   <si>
-    <t xml:space="preserve">1.40504562854767</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.38498115539551</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.31528317928314</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.2313289642334</t>
+    <t xml:space="preserve">1.40504550933838</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.3849812746048</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.31528294086456</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.23132908344269</t>
   </si>
   <si>
     <t xml:space="preserve">1.20334410667419</t>
@@ -3047,43 +3047,43 @@
     <t xml:space="preserve">1.21443283557892</t>
   </si>
   <si>
-    <t xml:space="preserve">1.29416275024414</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.26829016208649</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.2334406375885</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.24611377716064</t>
+    <t xml:space="preserve">1.29416263103485</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.26829028129578</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.23344075679779</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.24611365795135</t>
   </si>
   <si>
     <t xml:space="preserve">1.19806396961212</t>
   </si>
   <si>
-    <t xml:space="preserve">1.22763311862946</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.16532671451569</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.17430293560028</t>
+    <t xml:space="preserve">1.22763323783875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.1653265953064</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.17430305480957</t>
   </si>
   <si>
     <t xml:space="preserve">1.1473742723465</t>
   </si>
   <si>
-    <t xml:space="preserve">1.16796731948853</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.14526271820068</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.15371072292328</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.14843046665192</t>
+    <t xml:space="preserve">1.16796720027924</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.14526259899139</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.15371084213257</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.14843058586121</t>
   </si>
   <si>
     <t xml:space="preserve">1.18327927589417</t>
@@ -3095,25 +3095,25 @@
     <t xml:space="preserve">1.164799451828</t>
   </si>
   <si>
-    <t xml:space="preserve">1.13417387008667</t>
+    <t xml:space="preserve">1.13417410850525</t>
   </si>
   <si>
     <t xml:space="preserve">1.19119989871979</t>
   </si>
   <si>
-    <t xml:space="preserve">1.31581115722656</t>
+    <t xml:space="preserve">1.31581103801727</t>
   </si>
   <si>
     <t xml:space="preserve">1.31686747074127</t>
   </si>
   <si>
-    <t xml:space="preserve">1.32373106479645</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.34115552902222</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.31317126750946</t>
+    <t xml:space="preserve">1.32373118400574</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.34115540981293</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.31317138671875</t>
   </si>
   <si>
     <t xml:space="preserve">1.35858070850372</t>
@@ -3128,10 +3128,10 @@
     <t xml:space="preserve">1.27990615367889</t>
   </si>
   <si>
-    <t xml:space="preserve">1.22657692432404</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.23027288913727</t>
+    <t xml:space="preserve">1.22657680511475</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.23027276992798</t>
   </si>
   <si>
     <t xml:space="preserve">1.19067203998566</t>
@@ -3149,7 +3149,7 @@
     <t xml:space="preserve">1.08242893218994</t>
   </si>
   <si>
-    <t xml:space="preserve">1.14790225028992</t>
+    <t xml:space="preserve">1.14790236949921</t>
   </si>
   <si>
     <t xml:space="preserve">1.23555302619934</t>
@@ -3161,31 +3161,31 @@
     <t xml:space="preserve">1.2524493932724</t>
   </si>
   <si>
-    <t xml:space="preserve">1.2228809595108</t>
+    <t xml:space="preserve">1.22288072109222</t>
   </si>
   <si>
     <t xml:space="preserve">1.22604870796204</t>
   </si>
   <si>
-    <t xml:space="preserve">1.23713743686676</t>
+    <t xml:space="preserve">1.23713731765747</t>
   </si>
   <si>
     <t xml:space="preserve">1.21707260608673</t>
   </si>
   <si>
-    <t xml:space="preserve">1.20387244224548</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.24030530452728</t>
+    <t xml:space="preserve">1.2038722038269</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.24030542373657</t>
   </si>
   <si>
     <t xml:space="preserve">1.23977708816528</t>
   </si>
   <si>
-    <t xml:space="preserve">1.23080098628998</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.25667345523834</t>
+    <t xml:space="preserve">1.23080086708069</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.25667357444763</t>
   </si>
   <si>
     <t xml:space="preserve">1.2149600982666</t>
@@ -3200,22 +3200,22 @@
     <t xml:space="preserve">1.14156663417816</t>
   </si>
   <si>
-    <t xml:space="preserve">1.15265464782715</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.14684700965881</t>
+    <t xml:space="preserve">1.15265440940857</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.14684689044952</t>
   </si>
   <si>
     <t xml:space="preserve">1.11569333076477</t>
   </si>
   <si>
-    <t xml:space="preserve">1.13100600242615</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.16004705429077</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.15687847137451</t>
+    <t xml:space="preserve">1.13100612163544</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.16004729270935</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.1568785905838</t>
   </si>
   <si>
     <t xml:space="preserve">1.15635049343109</t>
@@ -3224,34 +3224,34 @@
     <t xml:space="preserve">1.14209473133087</t>
   </si>
   <si>
-    <t xml:space="preserve">1.15054285526276</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.14051043987274</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.09404504299164</t>
+    <t xml:space="preserve">1.15054297447205</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.14051055908203</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.09404492378235</t>
   </si>
   <si>
     <t xml:space="preserve">1.06447660923004</t>
   </si>
   <si>
-    <t xml:space="preserve">1.06658804416656</t>
+    <t xml:space="preserve">1.06658816337585</t>
   </si>
   <si>
     <t xml:space="preserve">1.03490710258484</t>
   </si>
   <si>
-    <t xml:space="preserve">1.03226745128632</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.0591961145401</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.0296276807785</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.04969191551208</t>
+    <t xml:space="preserve">1.03226757049561</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.05919623374939</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.02962779998779</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.0496917963028</t>
   </si>
   <si>
     <t xml:space="preserve">1.02857148647308</t>
@@ -3269,19 +3269,19 @@
     <t xml:space="preserve">0.92477023601532</t>
   </si>
   <si>
-    <t xml:space="preserve">0.933350801467896</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.938031256198883</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.914239346981049</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.867435276508331</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.870945632457733</t>
+    <t xml:space="preserve">0.933350920677185</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.938031435012817</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.914239406585693</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.867435216903687</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.870945513248444</t>
   </si>
   <si>
     <t xml:space="preserve">0.866265177726746</t>
@@ -3293,7 +3293,7 @@
     <t xml:space="preserve">0.923990190029144</t>
   </si>
   <si>
-    <t xml:space="preserve">1.01408791542053</t>
+    <t xml:space="preserve">1.01408803462982</t>
   </si>
   <si>
     <t xml:space="preserve">0.949342429637909</t>
@@ -3302,22 +3302,22 @@
     <t xml:space="preserve">0.925550222396851</t>
   </si>
   <si>
-    <t xml:space="preserve">0.938811361789703</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.929450571537018</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.871335625648499</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.808540165424347</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.798399269580841</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.793328762054443</t>
+    <t xml:space="preserve">0.938811540603638</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.929450452327728</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.871335566043854</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.808540105819702</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.798399209976196</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.793328881263733</t>
   </si>
   <si>
     <t xml:space="preserve">0.82297146320343</t>
@@ -3329,37 +3329,37 @@
     <t xml:space="preserve">0.863534867763519</t>
   </si>
   <si>
-    <t xml:space="preserve">0.844813287258148</t>
+    <t xml:space="preserve">0.844813346862793</t>
   </si>
   <si>
     <t xml:space="preserve">0.817510902881622</t>
   </si>
   <si>
-    <t xml:space="preserve">0.939201474189758</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.931400895118713</t>
+    <t xml:space="preserve">0.939201414585114</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.931400835514069</t>
   </si>
   <si>
     <t xml:space="preserve">0.966503858566284</t>
   </si>
   <si>
-    <t xml:space="preserve">1.02929925918579</t>
+    <t xml:space="preserve">1.0292991399765</t>
   </si>
   <si>
     <t xml:space="preserve">1.04139041900635</t>
   </si>
   <si>
-    <t xml:space="preserve">1.10496592521667</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.1119863986969</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.15801048278809</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.18258273601532</t>
+    <t xml:space="preserve">1.10496580600739</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.11198651790619</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.15801060199738</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.18258261680603</t>
   </si>
   <si>
     <t xml:space="preserve">1.18531286716461</t>
@@ -3371,16 +3371,16 @@
     <t xml:space="preserve">1.1584005355835</t>
   </si>
   <si>
-    <t xml:space="preserve">1.17868232727051</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.14279925823212</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.15918064117432</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.14669954776764</t>
+    <t xml:space="preserve">1.1786824464798</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.14279913902283</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.15918052196503</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.14669966697693</t>
   </si>
   <si>
     <t xml:space="preserve">1.15723049640656</t>
@@ -3404,19 +3404,19 @@
     <t xml:space="preserve">1.14162909984589</t>
   </si>
   <si>
-    <t xml:space="preserve">1.15254986286163</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.13694858551025</t>
+    <t xml:space="preserve">1.15254998207092</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.13694870471954</t>
   </si>
   <si>
     <t xml:space="preserve">1.14396929740906</t>
   </si>
   <si>
-    <t xml:space="preserve">1.13265824317932</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.08702445030212</t>
+    <t xml:space="preserve">1.13265836238861</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.08702433109283</t>
   </si>
   <si>
     <t xml:space="preserve">1.11159646511078</t>
@@ -3425,25 +3425,25 @@
     <t xml:space="preserve">1.15450024604797</t>
   </si>
   <si>
-    <t xml:space="preserve">1.17010152339935</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.16191077232361</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.14045894145966</t>
+    <t xml:space="preserve">1.17010164260864</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.1619108915329</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.14045906066895</t>
   </si>
   <si>
     <t xml:space="preserve">1.14981973171234</t>
   </si>
   <si>
-    <t xml:space="preserve">1.21105492115021</t>
+    <t xml:space="preserve">1.21105515956879</t>
   </si>
   <si>
     <t xml:space="preserve">1.28594148159027</t>
   </si>
   <si>
-    <t xml:space="preserve">1.27151036262512</t>
+    <t xml:space="preserve">1.27151024341583</t>
   </si>
   <si>
     <t xml:space="preserve">1.29764258861542</t>
@@ -3452,13 +3452,13 @@
     <t xml:space="preserve">1.29959273338318</t>
   </si>
   <si>
-    <t xml:space="preserve">1.2836012840271</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.26331984996796</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.25512897968292</t>
+    <t xml:space="preserve">1.28360140323639</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.26331961154938</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.25512886047363</t>
   </si>
   <si>
     <t xml:space="preserve">1.28282129764557</t>
@@ -3470,61 +3470,61 @@
     <t xml:space="preserve">1.28633165359497</t>
   </si>
   <si>
-    <t xml:space="preserve">1.26370966434479</t>
+    <t xml:space="preserve">1.26370978355408</t>
   </si>
   <si>
     <t xml:space="preserve">1.22899675369263</t>
   </si>
   <si>
-    <t xml:space="preserve">1.19194340705872</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.2250964641571</t>
+    <t xml:space="preserve">1.19194352626801</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.22509634494781</t>
   </si>
   <si>
     <t xml:space="preserve">1.18882322311401</t>
   </si>
   <si>
-    <t xml:space="preserve">1.21573543548584</t>
+    <t xml:space="preserve">1.21573555469513</t>
   </si>
   <si>
     <t xml:space="preserve">1.19584381580353</t>
   </si>
   <si>
-    <t xml:space="preserve">1.20442473888397</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.32455480098724</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.38696038722992</t>
+    <t xml:space="preserve">1.20442450046539</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.32455492019653</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.38696026802063</t>
   </si>
   <si>
     <t xml:space="preserve">1.48953938484192</t>
   </si>
   <si>
-    <t xml:space="preserve">1.45833659172058</t>
+    <t xml:space="preserve">1.45833647251129</t>
   </si>
   <si>
     <t xml:space="preserve">1.48212862014771</t>
   </si>
   <si>
-    <t xml:space="preserve">1.45521628856659</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.45248603820801</t>
+    <t xml:space="preserve">1.4552161693573</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.4524861574173</t>
   </si>
   <si>
     <t xml:space="preserve">1.4688675403595</t>
   </si>
   <si>
-    <t xml:space="preserve">1.44741559028625</t>
+    <t xml:space="preserve">1.44741570949554</t>
   </si>
   <si>
     <t xml:space="preserve">1.42089331150055</t>
   </si>
   <si>
-    <t xml:space="preserve">1.3963211774826</t>
+    <t xml:space="preserve">1.39632105827332</t>
   </si>
   <si>
     <t xml:space="preserve">1.45170593261719</t>
@@ -3533,22 +3533,22 @@
     <t xml:space="preserve">1.43064415454865</t>
   </si>
   <si>
-    <t xml:space="preserve">1.43025410175323</t>
+    <t xml:space="preserve">1.43025422096252</t>
   </si>
   <si>
     <t xml:space="preserve">1.45326602458954</t>
   </si>
   <si>
-    <t xml:space="preserve">1.41543281078339</t>
+    <t xml:space="preserve">1.4154326915741</t>
   </si>
   <si>
     <t xml:space="preserve">1.45287609100342</t>
   </si>
   <si>
-    <t xml:space="preserve">1.43766486644745</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.44624531269073</t>
+    <t xml:space="preserve">1.43766474723816</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.44624543190002</t>
   </si>
   <si>
     <t xml:space="preserve">1.50709080696106</t>
@@ -3557,37 +3557,37 @@
     <t xml:space="preserve">1.54765427112579</t>
   </si>
   <si>
-    <t xml:space="preserve">1.54102385044098</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.52815282344818</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.53673350811005</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.51879179477692</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.55233454704285</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.60069894790649</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.58899784088135</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.52581238746643</t>
+    <t xml:space="preserve">1.54102373123169</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.52815270423889</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.53673338890076</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.51879191398621</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.55233466625214</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.6006988286972</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.58899772167206</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.52581226825714</t>
   </si>
   <si>
     <t xml:space="preserve">1.48758900165558</t>
   </si>
   <si>
-    <t xml:space="preserve">1.48602890968323</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.50670087337494</t>
+    <t xml:space="preserve">1.48602902889252</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.50670075416565</t>
   </si>
   <si>
     <t xml:space="preserve">1.49538969993591</t>
@@ -3596,10 +3596,10 @@
     <t xml:space="preserve">1.49616980552673</t>
   </si>
   <si>
-    <t xml:space="preserve">1.48056840896606</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.48173856735229</t>
+    <t xml:space="preserve">1.48056852817535</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.48173868656158</t>
   </si>
   <si>
     <t xml:space="preserve">1.46379697322845</t>
@@ -3620,7 +3620,7 @@
     <t xml:space="preserve">1.4587265253067</t>
   </si>
   <si>
-    <t xml:space="preserve">1.48485887050629</t>
+    <t xml:space="preserve">1.484858751297</t>
   </si>
   <si>
     <t xml:space="preserve">1.46808743476868</t>
@@ -3632,49 +3632,49 @@
     <t xml:space="preserve">1.47549796104431</t>
   </si>
   <si>
-    <t xml:space="preserve">1.52191209793091</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.44000494480133</t>
+    <t xml:space="preserve">1.52191197872162</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.44000506401062</t>
   </si>
   <si>
     <t xml:space="preserve">1.40802216529846</t>
   </si>
   <si>
-    <t xml:space="preserve">1.41036224365234</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.41738283634186</t>
+    <t xml:space="preserve">1.41036248207092</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.41738307476044</t>
   </si>
   <si>
     <t xml:space="preserve">1.46106684207916</t>
   </si>
   <si>
-    <t xml:space="preserve">1.44507539272308</t>
+    <t xml:space="preserve">1.44507527351379</t>
   </si>
   <si>
     <t xml:space="preserve">1.47744834423065</t>
   </si>
   <si>
-    <t xml:space="preserve">1.46847760677338</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.46223700046539</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.47900831699371</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.50787079334259</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.50046014785767</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.55857527256012</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.57261657714844</t>
+    <t xml:space="preserve">1.46847748756409</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.4622368812561</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.47900819778442</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.50787091255188</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.50046002864838</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.55857515335083</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.57261645793915</t>
   </si>
   <si>
     <t xml:space="preserve">1.54921436309814</t>
@@ -3683,16 +3683,16 @@
     <t xml:space="preserve">1.56403577327728</t>
   </si>
   <si>
-    <t xml:space="preserve">1.56481575965881</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.57183647155762</t>
+    <t xml:space="preserve">1.5648158788681</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.57183635234833</t>
   </si>
   <si>
     <t xml:space="preserve">1.54219365119934</t>
   </si>
   <si>
-    <t xml:space="preserve">1.52776253223419</t>
+    <t xml:space="preserve">1.52776265144348</t>
   </si>
   <si>
     <t xml:space="preserve">1.55584502220154</t>
@@ -3701,7 +3701,7 @@
     <t xml:space="preserve">1.65574705600739</t>
   </si>
   <si>
-    <t xml:space="preserve">1.69236445426941</t>
+    <t xml:space="preserve">1.69236433506012</t>
   </si>
   <si>
     <t xml:space="preserve">1.61116933822632</t>
@@ -3710,34 +3710,34 @@
     <t xml:space="preserve">1.63186609745026</t>
   </si>
   <si>
-    <t xml:space="preserve">1.62151765823364</t>
+    <t xml:space="preserve">1.62151753902435</t>
   </si>
   <si>
     <t xml:space="preserve">1.61435353755951</t>
   </si>
   <si>
-    <t xml:space="preserve">1.61912941932678</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.62708985805511</t>
+    <t xml:space="preserve">1.61912953853607</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.6270899772644</t>
   </si>
   <si>
     <t xml:space="preserve">1.61992561817169</t>
   </si>
   <si>
-    <t xml:space="preserve">1.60957729816437</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.63107025623322</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.62072157859802</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.63425433635712</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.62231385707855</t>
+    <t xml:space="preserve">1.60957717895508</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.63107001781464</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.62072169780731</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.63425421714783</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.62231397628784</t>
   </si>
   <si>
     <t xml:space="preserve">1.6167414188385</t>
@@ -3752,10 +3752,10 @@
     <t xml:space="preserve">1.57693994045258</t>
   </si>
   <si>
-    <t xml:space="preserve">1.56539750099182</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.52997398376465</t>
+    <t xml:space="preserve">1.56539738178253</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.52997410297394</t>
   </si>
   <si>
     <t xml:space="preserve">1.54470062255859</t>
@@ -3767,7 +3767,7 @@
     <t xml:space="preserve">1.50410306453705</t>
   </si>
   <si>
-    <t xml:space="preserve">1.52081978321075</t>
+    <t xml:space="preserve">1.52081966400146</t>
   </si>
   <si>
     <t xml:space="preserve">1.51405334472656</t>
@@ -3776,10 +3776,10 @@
     <t xml:space="preserve">1.46589338779449</t>
   </si>
   <si>
-    <t xml:space="preserve">1.45395278930664</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.46111714839935</t>
+    <t xml:space="preserve">1.45395290851593</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.46111726760864</t>
   </si>
   <si>
     <t xml:space="preserve">1.46987366676331</t>
@@ -3809,16 +3809,16 @@
     <t xml:space="preserve">1.36240923404694</t>
   </si>
   <si>
-    <t xml:space="preserve">1.35643911361694</t>
+    <t xml:space="preserve">1.35643899440765</t>
   </si>
   <si>
     <t xml:space="preserve">1.34529459476471</t>
   </si>
   <si>
-    <t xml:space="preserve">1.30191075801849</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.23583996295929</t>
+    <t xml:space="preserve">1.30191087722778</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.23584008216858</t>
   </si>
   <si>
     <t xml:space="preserve">1.24579060077667</t>
@@ -3827,46 +3827,46 @@
     <t xml:space="preserve">1.26171112060547</t>
   </si>
   <si>
-    <t xml:space="preserve">1.28400003910065</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.28519403934479</t>
+    <t xml:space="preserve">1.28399991989136</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.28519415855408</t>
   </si>
   <si>
     <t xml:space="preserve">1.30469691753387</t>
   </si>
   <si>
-    <t xml:space="preserve">1.28957223892212</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.29076635837555</t>
+    <t xml:space="preserve">1.28957235813141</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.29076623916626</t>
   </si>
   <si>
     <t xml:space="preserve">1.29434847831726</t>
   </si>
   <si>
-    <t xml:space="preserve">1.31066703796387</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.31026923656464</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.2923583984375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.30071663856506</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.4392261505127</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.43604207038879</t>
+    <t xml:space="preserve">1.31066715717316</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.31026911735535</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.29235827922821</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.30071651935577</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.43922626972198</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.43604218959808</t>
   </si>
   <si>
     <t xml:space="preserve">1.43046998977661</t>
   </si>
   <si>
-    <t xml:space="preserve">1.4726597070694</t>
+    <t xml:space="preserve">1.47265982627869</t>
   </si>
   <si>
     <t xml:space="preserve">1.46231114864349</t>
@@ -3875,7 +3875,7 @@
     <t xml:space="preserve">1.45474886894226</t>
   </si>
   <si>
-    <t xml:space="preserve">1.43683815002441</t>
+    <t xml:space="preserve">1.4368382692337</t>
   </si>
   <si>
     <t xml:space="preserve">1.41136515140533</t>
@@ -3887,10 +3887,10 @@
     <t xml:space="preserve">1.39783263206482</t>
   </si>
   <si>
-    <t xml:space="preserve">1.39305639266968</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.42290771007538</t>
+    <t xml:space="preserve">1.39305627346039</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.42290782928467</t>
   </si>
   <si>
     <t xml:space="preserve">1.42808187007904</t>
@@ -3899,7 +3899,7 @@
     <t xml:space="preserve">1.45793306827545</t>
   </si>
   <si>
-    <t xml:space="preserve">1.43882834911346</t>
+    <t xml:space="preserve">1.43882822990417</t>
   </si>
   <si>
     <t xml:space="preserve">1.46151530742645</t>
@@ -3908,10 +3908,10 @@
     <t xml:space="preserve">1.44440054893494</t>
   </si>
   <si>
-    <t xml:space="preserve">1.46668934822083</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.47584366798401</t>
+    <t xml:space="preserve">1.46668922901154</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.4758437871933</t>
   </si>
   <si>
     <t xml:space="preserve">1.46907758712769</t>
@@ -3920,13 +3920,13 @@
     <t xml:space="preserve">1.48619210720062</t>
   </si>
   <si>
-    <t xml:space="preserve">1.44718670845032</t>
+    <t xml:space="preserve">1.44718658924103</t>
   </si>
   <si>
     <t xml:space="preserve">1.4364401102066</t>
   </si>
   <si>
-    <t xml:space="preserve">1.45037078857422</t>
+    <t xml:space="preserve">1.45037066936493</t>
   </si>
   <si>
     <t xml:space="preserve">1.44201231002808</t>
@@ -3935,16 +3935,16 @@
     <t xml:space="preserve">1.44081819057465</t>
   </si>
   <si>
-    <t xml:space="preserve">1.423703789711</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.3476824760437</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.36519539356232</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.40499699115753</t>
+    <t xml:space="preserve">1.42370367050171</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.34768259525299</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.36519527435303</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.40499687194824</t>
   </si>
   <si>
     <t xml:space="preserve">1.42449963092804</t>
@@ -3962,22 +3962,22 @@
     <t xml:space="preserve">1.54708862304688</t>
   </si>
   <si>
-    <t xml:space="preserve">1.53873026371002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.57574594020844</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.56261146068573</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.61753761768341</t>
+    <t xml:space="preserve">1.53873038291931</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.57574582099915</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.56261134147644</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.6175377368927</t>
   </si>
   <si>
     <t xml:space="preserve">1.60002481937408</t>
   </si>
   <si>
-    <t xml:space="preserve">1.61833357810974</t>
+    <t xml:space="preserve">1.61833345890045</t>
   </si>
   <si>
     <t xml:space="preserve">1.64380669593811</t>
@@ -3986,16 +3986,16 @@
     <t xml:space="preserve">1.64539861679077</t>
   </si>
   <si>
-    <t xml:space="preserve">1.63903045654297</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.63982653617859</t>
+    <t xml:space="preserve">1.63903057575226</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.6398264169693</t>
   </si>
   <si>
     <t xml:space="preserve">1.64221441745758</t>
   </si>
   <si>
-    <t xml:space="preserve">1.65415513515472</t>
+    <t xml:space="preserve">1.65415501594543</t>
   </si>
   <si>
     <t xml:space="preserve">1.63027405738831</t>
@@ -4004,7 +4004,7 @@
     <t xml:space="preserve">1.62947797775269</t>
   </si>
   <si>
-    <t xml:space="preserve">1.6334582567215</t>
+    <t xml:space="preserve">1.63345813751221</t>
   </si>
   <si>
     <t xml:space="preserve">1.59365677833557</t>
@@ -4013,7 +4013,7 @@
     <t xml:space="preserve">1.61196541786194</t>
   </si>
   <si>
-    <t xml:space="preserve">1.50808310508728</t>
+    <t xml:space="preserve">1.50808322429657</t>
   </si>
   <si>
     <t xml:space="preserve">1.49932682514191</t>
@@ -4028,7 +4028,7 @@
     <t xml:space="preserve">1.50609302520752</t>
   </si>
   <si>
-    <t xml:space="preserve">1.53196406364441</t>
+    <t xml:space="preserve">1.5319641828537</t>
   </si>
   <si>
     <t xml:space="preserve">1.52758586406708</t>
@@ -4037,13 +4037,13 @@
     <t xml:space="preserve">1.52002370357513</t>
   </si>
   <si>
-    <t xml:space="preserve">1.53116798400879</t>
+    <t xml:space="preserve">1.5311678647995</t>
   </si>
   <si>
     <t xml:space="preserve">1.52121758460999</t>
   </si>
   <si>
-    <t xml:space="preserve">1.53315818309784</t>
+    <t xml:space="preserve">1.53315806388855</t>
   </si>
   <si>
     <t xml:space="preserve">1.51325738430023</t>
@@ -4055,19 +4055,19 @@
     <t xml:space="preserve">1.4300719499588</t>
   </si>
   <si>
-    <t xml:space="preserve">1.43564426898956</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.42887783050537</t>
+    <t xml:space="preserve">1.43564414978027</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.42887771129608</t>
   </si>
   <si>
     <t xml:space="preserve">1.41176319122314</t>
   </si>
   <si>
-    <t xml:space="preserve">1.35086667537689</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.34012043476105</t>
+    <t xml:space="preserve">1.35086679458618</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.34012031555176</t>
   </si>
   <si>
     <t xml:space="preserve">1.33892631530762</t>
@@ -4079,19 +4079,19 @@
     <t xml:space="preserve">1.36439919471741</t>
   </si>
   <si>
-    <t xml:space="preserve">1.35166263580322</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.3942506313324</t>
+    <t xml:space="preserve">1.35166275501251</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.39425051212311</t>
   </si>
   <si>
     <t xml:space="preserve">1.40619099140167</t>
   </si>
   <si>
-    <t xml:space="preserve">1.38191187381744</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.38907623291016</t>
+    <t xml:space="preserve">1.38191199302673</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.38907635211945</t>
   </si>
   <si>
     <t xml:space="preserve">1.37872791290283</t>
@@ -4112,25 +4112,25 @@
     <t xml:space="preserve">1.41494727134705</t>
   </si>
   <si>
-    <t xml:space="preserve">1.40260887145996</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.42569386959076</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.44320642948151</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.45435106754303</t>
+    <t xml:space="preserve">1.40260875225067</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.42569375038147</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.4432065486908</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.45435094833374</t>
   </si>
   <si>
     <t xml:space="preserve">1.45116674900055</t>
   </si>
   <si>
-    <t xml:space="preserve">1.50052082538605</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.52917802333832</t>
+    <t xml:space="preserve">1.50052070617676</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.52917790412903</t>
   </si>
   <si>
     <t xml:space="preserve">1.5251978635788</t>
@@ -4154,16 +4154,16 @@
     <t xml:space="preserve">1.52678978443146</t>
   </si>
   <si>
-    <t xml:space="preserve">1.49813270568848</t>
+    <t xml:space="preserve">1.49813258647919</t>
   </si>
   <si>
     <t xml:space="preserve">1.42847990989685</t>
   </si>
   <si>
-    <t xml:space="preserve">1.42330551147461</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.48818230628967</t>
+    <t xml:space="preserve">1.4233056306839</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.48818218708038</t>
   </si>
   <si>
     <t xml:space="preserve">1.52320766448975</t>
@@ -4172,7 +4172,7 @@
     <t xml:space="preserve">1.46509730815887</t>
   </si>
   <si>
-    <t xml:space="preserve">1.4762419462204</t>
+    <t xml:space="preserve">1.47624182701111</t>
   </si>
   <si>
     <t xml:space="preserve">1.54350650310516</t>
@@ -4181,25 +4181,25 @@
     <t xml:space="preserve">1.5737556219101</t>
   </si>
   <si>
-    <t xml:space="preserve">1.5578351020813</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.61514949798584</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.61276125907898</t>
+    <t xml:space="preserve">1.55783522129059</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.61514961719513</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.61276137828827</t>
   </si>
   <si>
     <t xml:space="preserve">1.63743829727173</t>
   </si>
   <si>
-    <t xml:space="preserve">1.574551820755</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.71863353252411</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.69793677330017</t>
+    <t xml:space="preserve">1.57455193996429</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.71863341331482</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.69793689250946</t>
   </si>
   <si>
     <t xml:space="preserve">1.60718905925751</t>
@@ -4208,7 +4208,7 @@
     <t xml:space="preserve">1.56022322177887</t>
   </si>
   <si>
-    <t xml:space="preserve">1.44161438941956</t>
+    <t xml:space="preserve">1.44161450862885</t>
   </si>
   <si>
     <t xml:space="preserve">1.46788346767426</t>
@@ -4217,16 +4217,16 @@
     <t xml:space="preserve">1.32260763645172</t>
   </si>
   <si>
-    <t xml:space="preserve">1.31743335723877</t>
+    <t xml:space="preserve">1.31743323802948</t>
   </si>
   <si>
     <t xml:space="preserve">1.24857664108276</t>
   </si>
   <si>
-    <t xml:space="preserve">1.11643540859222</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.05872297286987</t>
+    <t xml:space="preserve">1.11643528938293</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.05872285366058</t>
   </si>
   <si>
     <t xml:space="preserve">1.11563920974731</t>
@@ -4235,19 +4235,19 @@
     <t xml:space="preserve">1.22708368301392</t>
   </si>
   <si>
-    <t xml:space="preserve">1.13514196872711</t>
+    <t xml:space="preserve">1.1351420879364</t>
   </si>
   <si>
     <t xml:space="preserve">1.12877368927002</t>
   </si>
   <si>
-    <t xml:space="preserve">1.17494356632233</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.19882464408875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.28678619861603</t>
+    <t xml:space="preserve">1.17494344711304</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.19882452487946</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.28678607940674</t>
   </si>
   <si>
     <t xml:space="preserve">1.25773096084595</t>
@@ -4265,22 +4265,22 @@
     <t xml:space="preserve">1.23464608192444</t>
   </si>
   <si>
-    <t xml:space="preserve">1.24300444126129</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.25892508029938</t>
+    <t xml:space="preserve">1.243004322052</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.25892519950867</t>
   </si>
   <si>
     <t xml:space="preserve">1.33295607566833</t>
   </si>
   <si>
-    <t xml:space="preserve">1.30668699741364</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.26529312133789</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.27922379970551</t>
+    <t xml:space="preserve">1.30668711662292</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.26529324054718</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.27922368049622</t>
   </si>
   <si>
     <t xml:space="preserve">1.22429764270782</t>
@@ -4298,22 +4298,22 @@
     <t xml:space="preserve">1.23225796222687</t>
   </si>
   <si>
-    <t xml:space="preserve">1.23504388332367</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.24778056144714</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.25335276126862</t>
+    <t xml:space="preserve">1.23504400253296</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.24778044223785</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.25335264205933</t>
   </si>
   <si>
     <t xml:space="preserve">1.29753255844116</t>
   </si>
   <si>
-    <t xml:space="preserve">1.30628883838654</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.28758215904236</t>
+    <t xml:space="preserve">1.30628895759583</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.28758203983307</t>
   </si>
   <si>
     <t xml:space="preserve">1.27404952049255</t>
@@ -4343,13 +4343,13 @@
     <t xml:space="preserve">1.22071552276611</t>
   </si>
   <si>
-    <t xml:space="preserve">1.21116304397583</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.35325491428375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.38629019260406</t>
+    <t xml:space="preserve">1.21116316318512</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.35325479507446</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.38629007339478</t>
   </si>
   <si>
     <t xml:space="preserve">1.38668811321259</t>
@@ -4358,13 +4358,13 @@
     <t xml:space="preserve">1.37395167350769</t>
   </si>
   <si>
-    <t xml:space="preserve">1.40539491176605</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.39862859249115</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.4073851108551</t>
+    <t xml:space="preserve">1.40539503097534</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.39862871170044</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.40738499164581</t>
   </si>
   <si>
     <t xml:space="preserve">1.39027035236359</t>
@@ -4379,19 +4379,19 @@
     <t xml:space="preserve">1.54153907299042</t>
   </si>
   <si>
-    <t xml:space="preserve">1.56049907207489</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.55390429496765</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.55349206924438</t>
+    <t xml:space="preserve">1.56049919128418</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.55390441417694</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.55349218845367</t>
   </si>
   <si>
     <t xml:space="preserve">1.57987141609192</t>
   </si>
   <si>
-    <t xml:space="preserve">1.57616174221039</t>
+    <t xml:space="preserve">1.57616186141968</t>
   </si>
   <si>
     <t xml:space="preserve">1.58976364135742</t>
@@ -4403,10 +4403,10 @@
     <t xml:space="preserve">1.59182453155518</t>
   </si>
   <si>
-    <t xml:space="preserve">1.55307996273041</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.59841930866241</t>
+    <t xml:space="preserve">1.55307984352112</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.5984194278717</t>
   </si>
   <si>
     <t xml:space="preserve">1.60831165313721</t>
@@ -4418,43 +4418,43 @@
     <t xml:space="preserve">1.35482323169708</t>
   </si>
   <si>
-    <t xml:space="preserve">1.36430323123932</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.41788625717163</t>
+    <t xml:space="preserve">1.36430335044861</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.41788613796234</t>
   </si>
   <si>
     <t xml:space="preserve">1.35770845413208</t>
   </si>
   <si>
-    <t xml:space="preserve">1.38326323032379</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.40799379348755</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.41458880901337</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.41252791881561</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.34451878070831</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.38820946216583</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.36718857288361</t>
+    <t xml:space="preserve">1.38326334953308</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.40799391269684</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.41458868980408</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.41252779960632</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.3445188999176</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.38820958137512</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.36718845367432</t>
   </si>
   <si>
     <t xml:space="preserve">1.36512756347656</t>
   </si>
   <si>
-    <t xml:space="preserve">1.34493100643158</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.2921724319458</t>
+    <t xml:space="preserve">1.34493112564087</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.29217255115509</t>
   </si>
   <si>
     <t xml:space="preserve">1.25219130516052</t>
@@ -4478,10 +4478,10 @@
     <t xml:space="preserve">1.18830394744873</t>
   </si>
   <si>
-    <t xml:space="preserve">1.1590393781662</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.128950715065</t>
+    <t xml:space="preserve">1.15903949737549</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.12895083427429</t>
   </si>
   <si>
     <t xml:space="preserve">1.05929279327393</t>
@@ -4508,37 +4508,37 @@
     <t xml:space="preserve">1.09556436538696</t>
   </si>
   <si>
-    <t xml:space="preserve">1.06506335735321</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.08567214012146</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.08814537525177</t>
+    <t xml:space="preserve">1.0650634765625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.08567225933075</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.08814525604248</t>
   </si>
   <si>
     <t xml:space="preserve">1.11287581920624</t>
   </si>
   <si>
-    <t xml:space="preserve">1.12482893466949</t>
+    <t xml:space="preserve">1.12482881546021</t>
   </si>
   <si>
     <t xml:space="preserve">1.1433767080307</t>
   </si>
   <si>
-    <t xml:space="preserve">1.18912839889526</t>
+    <t xml:space="preserve">1.18912827968597</t>
   </si>
   <si>
     <t xml:space="preserve">1.18129694461823</t>
   </si>
   <si>
-    <t xml:space="preserve">1.29588210582733</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.32720744609833</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.33792400360107</t>
+    <t xml:space="preserve">1.29588198661804</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.32720732688904</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.33792412281036</t>
   </si>
   <si>
     <t xml:space="preserve">1.36842501163483</t>
@@ -4547,25 +4547,25 @@
     <t xml:space="preserve">1.34987711906433</t>
   </si>
   <si>
-    <t xml:space="preserve">1.35647189617157</t>
+    <t xml:space="preserve">1.35647201538086</t>
   </si>
   <si>
     <t xml:space="preserve">1.35070145130157</t>
   </si>
   <si>
-    <t xml:space="preserve">1.30659866333008</t>
+    <t xml:space="preserve">1.30659854412079</t>
   </si>
   <si>
     <t xml:space="preserve">1.26290786266327</t>
   </si>
   <si>
-    <t xml:space="preserve">1.28063154220581</t>
+    <t xml:space="preserve">1.2806316614151</t>
   </si>
   <si>
     <t xml:space="preserve">1.28021931648254</t>
   </si>
   <si>
-    <t xml:space="preserve">1.26084697246552</t>
+    <t xml:space="preserve">1.2608470916748</t>
   </si>
   <si>
     <t xml:space="preserve">1.22004151344299</t>
@@ -4580,28 +4580,28 @@
     <t xml:space="preserve">1.24065041542053</t>
   </si>
   <si>
-    <t xml:space="preserve">1.22333908081055</t>
+    <t xml:space="preserve">1.22333896160126</t>
   </si>
   <si>
     <t xml:space="preserve">1.25301563739777</t>
   </si>
   <si>
-    <t xml:space="preserve">1.21550762653351</t>
+    <t xml:space="preserve">1.21550750732422</t>
   </si>
   <si>
     <t xml:space="preserve">1.21798074245453</t>
   </si>
   <si>
-    <t xml:space="preserve">1.20066940784454</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.23776519298553</t>
+    <t xml:space="preserve">1.20066928863525</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.23776531219482</t>
   </si>
   <si>
     <t xml:space="preserve">1.27609741687775</t>
   </si>
   <si>
-    <t xml:space="preserve">1.33957266807556</t>
+    <t xml:space="preserve">1.33957278728485</t>
   </si>
   <si>
     <t xml:space="preserve">1.32597088813782</t>
@@ -4622,25 +4622,25 @@
     <t xml:space="preserve">1.3729590177536</t>
   </si>
   <si>
-    <t xml:space="preserve">1.38408768177032</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.43025135993958</t>
+    <t xml:space="preserve">1.38408780097961</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.43025147914886</t>
   </si>
   <si>
     <t xml:space="preserve">1.37337112426758</t>
   </si>
   <si>
-    <t xml:space="preserve">1.3717223405838</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.34163355827332</t>
+    <t xml:space="preserve">1.37172245979309</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.3416336774826</t>
   </si>
   <si>
     <t xml:space="preserve">1.32020044326782</t>
   </si>
   <si>
-    <t xml:space="preserve">1.28269243240356</t>
+    <t xml:space="preserve">1.28269231319427</t>
   </si>
   <si>
     <t xml:space="preserve">1.30330121517181</t>
@@ -4655,10 +4655,10 @@
     <t xml:space="preserve">1.3589448928833</t>
   </si>
   <si>
-    <t xml:space="preserve">1.31731534004211</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.33462643623352</t>
+    <t xml:space="preserve">1.31731522083282</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.33462655544281</t>
   </si>
   <si>
     <t xml:space="preserve">1.31855165958405</t>
@@ -4679,10 +4679,10 @@
     <t xml:space="preserve">1.40181136131287</t>
   </si>
   <si>
-    <t xml:space="preserve">1.41211569309235</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.41664969921112</t>
+    <t xml:space="preserve">1.41211581230164</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.41664958000183</t>
   </si>
   <si>
     <t xml:space="preserve">1.43560981750488</t>
@@ -4691,10 +4691,10 @@
     <t xml:space="preserve">1.4764152765274</t>
   </si>
   <si>
-    <t xml:space="preserve">1.46734726428986</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.46940815448761</t>
+    <t xml:space="preserve">1.46734738349915</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.4694082736969</t>
   </si>
   <si>
     <t xml:space="preserve">1.51103806495667</t>
@@ -4706,7 +4706,7 @@
     <t xml:space="preserve">1.54359984397888</t>
   </si>
   <si>
-    <t xml:space="preserve">1.56214773654938</t>
+    <t xml:space="preserve">1.56214797496796</t>
   </si>
   <si>
     <t xml:space="preserve">1.58770275115967</t>
@@ -4718,10 +4718,10 @@
     <t xml:space="preserve">1.65942132472992</t>
   </si>
   <si>
-    <t xml:space="preserve">1.68992245197296</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.5600870847702</t>
+    <t xml:space="preserve">1.68992233276367</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.56008696556091</t>
   </si>
   <si>
     <t xml:space="preserve">1.51680850982666</t>
@@ -4733,13 +4733,13 @@
     <t xml:space="preserve">1.52711284160614</t>
   </si>
   <si>
-    <t xml:space="preserve">1.54648506641388</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.5518434047699</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.57410085201263</t>
+    <t xml:space="preserve">1.54648518562317</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.55184352397919</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.57410097122192</t>
   </si>
   <si>
     <t xml:space="preserve">1.57822275161743</t>
@@ -4751,7 +4751,7 @@
     <t xml:space="preserve">1.59965598583221</t>
   </si>
   <si>
-    <t xml:space="preserve">1.61284554004669</t>
+    <t xml:space="preserve">1.61284565925598</t>
   </si>
   <si>
     <t xml:space="preserve">1.62356209754944</t>
@@ -4766,7 +4766,7 @@
     <t xml:space="preserve">1.62562298774719</t>
   </si>
   <si>
-    <t xml:space="preserve">1.60666298866272</t>
+    <t xml:space="preserve">1.60666286945343</t>
   </si>
   <si>
     <t xml:space="preserve">1.59883153438568</t>
@@ -4775,22 +4775,22 @@
     <t xml:space="preserve">1.59017586708069</t>
   </si>
   <si>
-    <t xml:space="preserve">1.59718298912048</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.60171663761139</t>
+    <t xml:space="preserve">1.59718286991119</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.60171675682068</t>
   </si>
   <si>
     <t xml:space="preserve">1.60954821109772</t>
   </si>
   <si>
-    <t xml:space="preserve">1.60913598537445</t>
+    <t xml:space="preserve">1.60913586616516</t>
   </si>
   <si>
     <t xml:space="preserve">1.61902809143066</t>
   </si>
   <si>
-    <t xml:space="preserve">1.6070750951767</t>
+    <t xml:space="preserve">1.60707497596741</t>
   </si>
   <si>
     <t xml:space="preserve">1.55101907253265</t>
@@ -4799,7 +4799,7 @@
     <t xml:space="preserve">1.54978263378143</t>
   </si>
   <si>
-    <t xml:space="preserve">1.53782951831818</t>
+    <t xml:space="preserve">1.53782939910889</t>
   </si>
   <si>
     <t xml:space="preserve">1.6041898727417</t>
@@ -4814,7 +4814,7 @@
     <t xml:space="preserve">1.5815201997757</t>
   </si>
   <si>
-    <t xml:space="preserve">1.61531865596771</t>
+    <t xml:space="preserve">1.61531853675842</t>
   </si>
   <si>
     <t xml:space="preserve">1.63633954524994</t>
@@ -4826,7 +4826,7 @@
     <t xml:space="preserve">1.67343533039093</t>
   </si>
   <si>
-    <t xml:space="preserve">1.71712613105774</t>
+    <t xml:space="preserve">1.71712589263916</t>
   </si>
   <si>
     <t xml:space="preserve">1.72536969184875</t>
@@ -4838,19 +4838,19 @@
     <t xml:space="preserve">1.73855924606323</t>
   </si>
   <si>
-    <t xml:space="preserve">1.74845147132874</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.8053320646286</t>
+    <t xml:space="preserve">1.74845159053802</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.80533194541931</t>
   </si>
   <si>
     <t xml:space="preserve">1.82511639595032</t>
   </si>
   <si>
-    <t xml:space="preserve">1.7970883846283</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.85644161701202</t>
+    <t xml:space="preserve">1.79708850383759</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.85644197463989</t>
   </si>
   <si>
     <t xml:space="preserve">1.85479307174683</t>
@@ -4862,7 +4862,7 @@
     <t xml:space="preserve">1.90178108215332</t>
   </si>
   <si>
-    <t xml:space="preserve">1.92898440361023</t>
+    <t xml:space="preserve">1.92898464202881</t>
   </si>
   <si>
     <t xml:space="preserve">1.93310654163361</t>
@@ -4871,7 +4871,7 @@
     <t xml:space="preserve">1.97349977493286</t>
   </si>
   <si>
-    <t xml:space="preserve">2.0040009021759</t>
+    <t xml:space="preserve">2.00400066375732</t>
   </si>
   <si>
     <t xml:space="preserve">2.00317645072937</t>
@@ -4880,13 +4880,13 @@
     <t xml:space="preserve">2.07489490509033</t>
   </si>
   <si>
-    <t xml:space="preserve">2.1433162689209</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.08396291732788</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.09385514259338</t>
+    <t xml:space="preserve">2.14331650733948</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.08396315574646</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.09385538101196</t>
   </si>
   <si>
     <t xml:space="preserve">2.12847781181335</t>
@@ -4895,7 +4895,7 @@
     <t xml:space="preserve">2.09880137443542</t>
   </si>
   <si>
-    <t xml:space="preserve">2.11941003799438</t>
+    <t xml:space="preserve">2.11941027641296</t>
   </si>
   <si>
     <t xml:space="preserve">2.10457158088684</t>
@@ -4904,31 +4904,31 @@
     <t xml:space="preserve">2.14991116523743</t>
   </si>
   <si>
-    <t xml:space="preserve">2.13919448852539</t>
+    <t xml:space="preserve">2.13919472694397</t>
   </si>
   <si>
     <t xml:space="preserve">2.1375458240509</t>
   </si>
   <si>
-    <t xml:space="preserve">2.20431852340698</t>
+    <t xml:space="preserve">2.2043182849884</t>
   </si>
   <si>
     <t xml:space="preserve">2.30159211158752</t>
   </si>
   <si>
-    <t xml:space="preserve">2.26449584960938</t>
+    <t xml:space="preserve">2.26449608802795</t>
   </si>
   <si>
     <t xml:space="preserve">2.25295519828796</t>
   </si>
   <si>
-    <t xml:space="preserve">2.15403294563293</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.17629075050354</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.12600493431091</t>
+    <t xml:space="preserve">2.15403270721436</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.17629051208496</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.12600517272949</t>
   </si>
   <si>
     <t xml:space="preserve">2.18700695037842</t>
@@ -4949,25 +4949,25 @@
     <t xml:space="preserve">2.27026653289795</t>
   </si>
   <si>
-    <t xml:space="preserve">2.27273964881897</t>
+    <t xml:space="preserve">2.27273941040039</t>
   </si>
   <si>
     <t xml:space="preserve">2.3304443359375</t>
   </si>
   <si>
-    <t xml:space="preserve">2.32220077514648</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.21833229064941</t>
+    <t xml:space="preserve">2.32220053672791</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.21833252906799</t>
   </si>
   <si>
     <t xml:space="preserve">2.00729823112488</t>
   </si>
   <si>
-    <t xml:space="preserve">2.04027247428894</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.89271306991577</t>
+    <t xml:space="preserve">2.04027223587036</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.89271330833435</t>
   </si>
   <si>
     <t xml:space="preserve">1.89683520793915</t>
@@ -4976,25 +4976,25 @@
     <t xml:space="preserve">1.84407639503479</t>
   </si>
   <si>
-    <t xml:space="preserve">1.87045574188232</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.96195876598358</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.93393051624298</t>
+    <t xml:space="preserve">1.87045586109161</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.96195900440216</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.93393075466156</t>
   </si>
   <si>
     <t xml:space="preserve">1.89848375320435</t>
   </si>
   <si>
-    <t xml:space="preserve">1.82181906700134</t>
+    <t xml:space="preserve">1.82181882858276</t>
   </si>
   <si>
     <t xml:space="preserve">1.84325218200684</t>
   </si>
   <si>
-    <t xml:space="preserve">1.84902250766754</t>
+    <t xml:space="preserve">1.84902238845825</t>
   </si>
   <si>
     <t xml:space="preserve">1.89930784702301</t>
@@ -5003,10 +5003,10 @@
     <t xml:space="preserve">1.88776683807373</t>
   </si>
   <si>
-    <t xml:space="preserve">1.8737530708313</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.91991674900055</t>
+    <t xml:space="preserve">1.87375295162201</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.91991698741913</t>
   </si>
   <si>
     <t xml:space="preserve">1.9190925359726</t>
@@ -5024,13 +5024,13 @@
     <t xml:space="preserve">1.97679686546326</t>
   </si>
   <si>
-    <t xml:space="preserve">2.06912469863892</t>
+    <t xml:space="preserve">2.06912446022034</t>
   </si>
   <si>
     <t xml:space="preserve">2.07901692390442</t>
   </si>
   <si>
-    <t xml:space="preserve">2.16392517089844</t>
+    <t xml:space="preserve">2.16392493247986</t>
   </si>
   <si>
     <t xml:space="preserve">2.20102095603943</t>
@@ -5042,13 +5042,13 @@
     <t xml:space="preserve">2.26284718513489</t>
   </si>
   <si>
-    <t xml:space="preserve">2.2537796497345</t>
+    <t xml:space="preserve">2.25377917289734</t>
   </si>
   <si>
     <t xml:space="preserve">2.1020987033844</t>
   </si>
   <si>
-    <t xml:space="preserve">2.18618273735046</t>
+    <t xml:space="preserve">2.18618249893188</t>
   </si>
   <si>
     <t xml:space="preserve">2.09797692298889</t>
@@ -5060,25 +5060,25 @@
     <t xml:space="preserve">2.10045003890991</t>
   </si>
   <si>
-    <t xml:space="preserve">2.06665134429932</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.14908671379089</t>
+    <t xml:space="preserve">2.0666515827179</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.14908695220947</t>
   </si>
   <si>
     <t xml:space="preserve">2.26119875907898</t>
   </si>
   <si>
-    <t xml:space="preserve">2.25048232078552</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.2001965045929</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.24965786933899</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.23564386367798</t>
+    <t xml:space="preserve">2.25048208236694</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.20019626617432</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.24965763092041</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.2356436252594</t>
   </si>
   <si>
     <t xml:space="preserve">2.23481965065002</t>
@@ -5102,10 +5102,10 @@
     <t xml:space="preserve">2.13085508346558</t>
   </si>
   <si>
-    <t xml:space="preserve">2.13516879081726</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.12395334243774</t>
+    <t xml:space="preserve">2.13516855239868</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.12395358085632</t>
   </si>
   <si>
     <t xml:space="preserve">2.0972101688385</t>
@@ -5114,10 +5114,10 @@
     <t xml:space="preserve">2.06183981895447</t>
   </si>
   <si>
-    <t xml:space="preserve">2.11618971824646</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.16363763809204</t>
+    <t xml:space="preserve">2.11618947982788</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.16363739967346</t>
   </si>
   <si>
     <t xml:space="preserve">2.15328526496887</t>
@@ -5126,13 +5126,13 @@
     <t xml:space="preserve">2.15846157073975</t>
   </si>
   <si>
-    <t xml:space="preserve">2.15414810180664</t>
+    <t xml:space="preserve">2.15414786338806</t>
   </si>
   <si>
     <t xml:space="preserve">2.15501046180725</t>
   </si>
   <si>
-    <t xml:space="preserve">2.11273860931396</t>
+    <t xml:space="preserve">2.11273837089539</t>
   </si>
   <si>
     <t xml:space="preserve">2.14465832710266</t>
@@ -5141,7 +5141,7 @@
     <t xml:space="preserve">2.14983439445496</t>
   </si>
   <si>
-    <t xml:space="preserve">2.20073342323303</t>
+    <t xml:space="preserve">2.20073366165161</t>
   </si>
   <si>
     <t xml:space="preserve">2.19814538955688</t>
@@ -5156,13 +5156,13 @@
     <t xml:space="preserve">2.34652876853943</t>
   </si>
   <si>
-    <t xml:space="preserve">2.37931108474731</t>
+    <t xml:space="preserve">2.37931084632874</t>
   </si>
   <si>
     <t xml:space="preserve">2.36809587478638</t>
   </si>
   <si>
-    <t xml:space="preserve">2.31633448600769</t>
+    <t xml:space="preserve">2.31633424758911</t>
   </si>
   <si>
     <t xml:space="preserve">2.28614044189453</t>
@@ -5177,7 +5177,7 @@
     <t xml:space="preserve">2.37672305107117</t>
   </si>
   <si>
-    <t xml:space="preserve">2.40001583099365</t>
+    <t xml:space="preserve">2.40001606941223</t>
   </si>
   <si>
     <t xml:space="preserve">2.42675924301147</t>
@@ -5198,7 +5198,7 @@
     <t xml:space="preserve">2.42072033882141</t>
   </si>
   <si>
-    <t xml:space="preserve">2.44056248664856</t>
+    <t xml:space="preserve">2.44056224822998</t>
   </si>
   <si>
     <t xml:space="preserve">2.47938370704651</t>
@@ -5207,19 +5207,19 @@
     <t xml:space="preserve">2.5337336063385</t>
   </si>
   <si>
-    <t xml:space="preserve">2.51302909851074</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.56133985519409</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.55443811416626</t>
+    <t xml:space="preserve">2.51302886009216</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.56133961677551</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.55443787574768</t>
   </si>
   <si>
     <t xml:space="preserve">2.53200817108154</t>
   </si>
   <si>
-    <t xml:space="preserve">2.58376979827881</t>
+    <t xml:space="preserve">2.58376955986023</t>
   </si>
   <si>
     <t xml:space="preserve">2.60188627243042</t>
@@ -5234,7 +5234,7 @@
     <t xml:space="preserve">2.73819208145142</t>
   </si>
   <si>
-    <t xml:space="preserve">2.69419431686401</t>
+    <t xml:space="preserve">2.69419455528259</t>
   </si>
   <si>
     <t xml:space="preserve">2.70454692840576</t>
@@ -5243,16 +5243,16 @@
     <t xml:space="preserve">2.71489930152893</t>
   </si>
   <si>
-    <t xml:space="preserve">2.66400051116943</t>
+    <t xml:space="preserve">2.66400027275085</t>
   </si>
   <si>
     <t xml:space="preserve">2.59325933456421</t>
   </si>
   <si>
-    <t xml:space="preserve">2.48714804649353</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.44660115242004</t>
+    <t xml:space="preserve">2.48714780807495</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.44660139083862</t>
   </si>
   <si>
     <t xml:space="preserve">2.45264005661011</t>
@@ -5267,7 +5267,7 @@
     <t xml:space="preserve">2.28010106086731</t>
   </si>
   <si>
-    <t xml:space="preserve">2.34049010276794</t>
+    <t xml:space="preserve">2.34048986434937</t>
   </si>
   <si>
     <t xml:space="preserve">2.34911680221558</t>
@@ -5282,28 +5282,28 @@
     <t xml:space="preserve">2.37240958213806</t>
   </si>
   <si>
-    <t xml:space="preserve">2.36895871162415</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.3439404964447</t>
+    <t xml:space="preserve">2.36895895004272</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.34394073486328</t>
   </si>
   <si>
     <t xml:space="preserve">2.39656496047974</t>
   </si>
   <si>
-    <t xml:space="preserve">2.41640734672546</t>
+    <t xml:space="preserve">2.41640710830688</t>
   </si>
   <si>
     <t xml:space="preserve">2.43969988822937</t>
   </si>
   <si>
-    <t xml:space="preserve">2.40519189834595</t>
+    <t xml:space="preserve">2.40519213676453</t>
   </si>
   <si>
     <t xml:space="preserve">2.39138889312744</t>
   </si>
   <si>
-    <t xml:space="preserve">2.36464548110962</t>
+    <t xml:space="preserve">2.36464524269104</t>
   </si>
   <si>
     <t xml:space="preserve">2.26198482513428</t>
@@ -5318,7 +5318,7 @@
     <t xml:space="preserve">2.31115818023682</t>
   </si>
   <si>
-    <t xml:space="preserve">2.3879382610321</t>
+    <t xml:space="preserve">2.38793802261353</t>
   </si>
   <si>
     <t xml:space="preserve">2.41295623779297</t>
@@ -5342,7 +5342,7 @@
     <t xml:space="preserve">2.4388370513916</t>
   </si>
   <si>
-    <t xml:space="preserve">2.41123104095459</t>
+    <t xml:space="preserve">2.41123080253601</t>
   </si>
   <si>
     <t xml:space="preserve">2.49922585487366</t>
@@ -5402,13 +5402,13 @@
     <t xml:space="preserve">2.51389145851135</t>
   </si>
   <si>
-    <t xml:space="preserve">2.52510666847229</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.64760899543762</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.70713520050049</t>
+    <t xml:space="preserve">2.52510643005371</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.6476092338562</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.70713496208191</t>
   </si>
   <si>
     <t xml:space="preserve">2.70972323417664</t>
@@ -5429,7 +5429,7 @@
     <t xml:space="preserve">2.84171533584595</t>
   </si>
   <si>
-    <t xml:space="preserve">3.0444483757019</t>
+    <t xml:space="preserve">3.04444861412048</t>
   </si>
   <si>
     <t xml:space="preserve">3.02546906471252</t>
@@ -5438,7 +5438,7 @@
     <t xml:space="preserve">3.07291746139526</t>
   </si>
   <si>
-    <t xml:space="preserve">2.98751091957092</t>
+    <t xml:space="preserve">2.98751068115234</t>
   </si>
   <si>
     <t xml:space="preserve">3.00562715530396</t>
@@ -5453,13 +5453,13 @@
     <t xml:space="preserve">2.90986824035645</t>
   </si>
   <si>
-    <t xml:space="preserve">2.94696378707886</t>
+    <t xml:space="preserve">2.94696402549744</t>
   </si>
   <si>
     <t xml:space="preserve">2.94782686233521</t>
   </si>
   <si>
-    <t xml:space="preserve">2.92453408241272</t>
+    <t xml:space="preserve">2.9245343208313</t>
   </si>
   <si>
     <t xml:space="preserve">2.8900260925293</t>
@@ -5474,25 +5474,25 @@
     <t xml:space="preserve">2.98837351799011</t>
   </si>
   <si>
-    <t xml:space="preserve">2.96766877174377</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.95214009284973</t>
+    <t xml:space="preserve">2.9676685333252</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.95214033126831</t>
   </si>
   <si>
     <t xml:space="preserve">2.97457027435303</t>
   </si>
   <si>
-    <t xml:space="preserve">2.89347696304321</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.91676998138428</t>
+    <t xml:space="preserve">2.89347720146179</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.9167697429657</t>
   </si>
   <si>
     <t xml:space="preserve">2.8805365562439</t>
   </si>
   <si>
-    <t xml:space="preserve">2.86932134628296</t>
+    <t xml:space="preserve">2.86932158470154</t>
   </si>
   <si>
     <t xml:space="preserve">2.70023369789124</t>
@@ -5501,7 +5501,7 @@
     <t xml:space="preserve">2.64070773124695</t>
   </si>
   <si>
-    <t xml:space="preserve">2.64588356018066</t>
+    <t xml:space="preserve">2.64588379859924</t>
   </si>
   <si>
     <t xml:space="preserve">2.64502096176147</t>
@@ -5528,13 +5528,13 @@
     <t xml:space="preserve">2.77356243133545</t>
   </si>
   <si>
-    <t xml:space="preserve">2.82791233062744</t>
+    <t xml:space="preserve">2.82791256904602</t>
   </si>
   <si>
     <t xml:space="preserve">2.82877492904663</t>
   </si>
   <si>
-    <t xml:space="preserve">2.72007536888123</t>
+    <t xml:space="preserve">2.7200756072998</t>
   </si>
   <si>
     <t xml:space="preserve">2.73215317726135</t>
@@ -5552,7 +5552,7 @@
     <t xml:space="preserve">2.72611451148987</t>
   </si>
   <si>
-    <t xml:space="preserve">2.75285768508911</t>
+    <t xml:space="preserve">2.75285792350769</t>
   </si>
   <si>
     <t xml:space="preserve">2.85034203529358</t>
@@ -5561,13 +5561,13 @@
     <t xml:space="preserve">2.86759614944458</t>
   </si>
   <si>
-    <t xml:space="preserve">2.8486168384552</t>
+    <t xml:space="preserve">2.84861707687378</t>
   </si>
   <si>
     <t xml:space="preserve">2.83826446533203</t>
   </si>
   <si>
-    <t xml:space="preserve">2.88916373252869</t>
+    <t xml:space="preserve">2.88916349411011</t>
   </si>
   <si>
     <t xml:space="preserve">2.81755995750427</t>
@@ -5585,7 +5585,7 @@
     <t xml:space="preserve">2.8943395614624</t>
   </si>
   <si>
-    <t xml:space="preserve">2.87104678153992</t>
+    <t xml:space="preserve">2.8710470199585</t>
   </si>
   <si>
     <t xml:space="preserve">2.92712211608887</t>
@@ -5612,7 +5612,7 @@
     <t xml:space="preserve">3.07981896400452</t>
   </si>
   <si>
-    <t xml:space="preserve">3.04013514518738</t>
+    <t xml:space="preserve">3.0401349067688</t>
   </si>
   <si>
     <t xml:space="preserve">3.03323364257812</t>
@@ -5633,16 +5633,16 @@
     <t xml:space="preserve">3.27910161018372</t>
   </si>
   <si>
-    <t xml:space="preserve">3.23510408401489</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.19973349571228</t>
+    <t xml:space="preserve">3.23510384559631</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.19973373413086</t>
   </si>
   <si>
     <t xml:space="preserve">3.19714546203613</t>
   </si>
   <si>
-    <t xml:space="preserve">3.239417552948</t>
+    <t xml:space="preserve">3.23941731452942</t>
   </si>
   <si>
     <t xml:space="preserve">3.28082680702209</t>
@@ -5663,13 +5663,13 @@
     <t xml:space="preserve">3.34811687469482</t>
   </si>
   <si>
-    <t xml:space="preserve">3.4499146938324</t>
+    <t xml:space="preserve">3.44991493225098</t>
   </si>
   <si>
     <t xml:space="preserve">3.42921018600464</t>
   </si>
   <si>
-    <t xml:space="preserve">3.41972041130066</t>
+    <t xml:space="preserve">3.41972064971924</t>
   </si>
   <si>
     <t xml:space="preserve">3.4671688079834</t>
@@ -5681,7 +5681,7 @@
     <t xml:space="preserve">3.63539433479309</t>
   </si>
   <si>
-    <t xml:space="preserve">3.67076468467712</t>
+    <t xml:space="preserve">3.6707649230957</t>
   </si>
   <si>
     <t xml:space="preserve">3.64574646949768</t>
@@ -5696,13 +5696,13 @@
     <t xml:space="preserve">3.83381366729736</t>
   </si>
   <si>
-    <t xml:space="preserve">3.74409413337708</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.77860188484192</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.76997423171997</t>
+    <t xml:space="preserve">3.7440938949585</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.77860140800476</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.76997447013855</t>
   </si>
   <si>
     <t xml:space="preserve">3.85969471931458</t>
@@ -5714,7 +5714,7 @@
     <t xml:space="preserve">3.78981637954712</t>
   </si>
   <si>
-    <t xml:space="preserve">3.83467650413513</t>
+    <t xml:space="preserve">3.83467698097229</t>
   </si>
   <si>
     <t xml:space="preserve">3.77083706855774</t>
@@ -5723,19 +5723,19 @@
     <t xml:space="preserve">3.83812689781189</t>
   </si>
   <si>
-    <t xml:space="preserve">3.68888115882874</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.68715596199036</t>
+    <t xml:space="preserve">3.68888092041016</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.68715620040894</t>
   </si>
   <si>
     <t xml:space="preserve">3.68197965621948</t>
   </si>
   <si>
-    <t xml:space="preserve">3.63366889953613</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.73460412025452</t>
+    <t xml:space="preserve">3.63366866111755</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.73460388183594</t>
   </si>
   <si>
     <t xml:space="preserve">3.80965852737427</t>
@@ -5747,40 +5747,40 @@
     <t xml:space="preserve">3.89420247077942</t>
   </si>
   <si>
-    <t xml:space="preserve">4.02792024612427</t>
+    <t xml:space="preserve">4.02791976928711</t>
   </si>
   <si>
     <t xml:space="preserve">3.99772572517395</t>
   </si>
   <si>
-    <t xml:space="preserve">4.0745062828064</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.12713003158569</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.15646171569824</t>
+    <t xml:space="preserve">4.07450580596924</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.12712955474854</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.15646123886108</t>
   </si>
   <si>
     <t xml:space="preserve">4.21943807601929</t>
   </si>
   <si>
-    <t xml:space="preserve">4.25394630432129</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.12885570526123</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.1754412651062</t>
+    <t xml:space="preserve">4.25394678115845</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.12885522842407</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.17544078826904</t>
   </si>
   <si>
     <t xml:space="preserve">4.25653457641602</t>
   </si>
   <si>
-    <t xml:space="preserve">4.23237943649292</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.10642528533936</t>
+    <t xml:space="preserve">4.23237895965576</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.10642576217651</t>
   </si>
   <si>
     <t xml:space="preserve">4.09089708328247</t>
@@ -5801,13 +5801,13 @@
     <t xml:space="preserve">4.56710433959961</t>
   </si>
   <si>
-    <t xml:space="preserve">4.46925067901611</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.44730186462402</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.38420057296753</t>
+    <t xml:space="preserve">4.46925115585327</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.44730234146118</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.38420104980469</t>
   </si>
   <si>
     <t xml:space="preserve">4.41072130203247</t>
@@ -5819,7 +5819,7 @@
     <t xml:space="preserve">4.40066146850586</t>
   </si>
   <si>
-    <t xml:space="preserve">4.48205423355103</t>
+    <t xml:space="preserve">4.48205375671387</t>
   </si>
   <si>
     <t xml:space="preserve">4.39425992965698</t>
@@ -5828,19 +5828,19 @@
     <t xml:space="preserve">4.52137804031372</t>
   </si>
   <si>
-    <t xml:space="preserve">4.5094895362854</t>
+    <t xml:space="preserve">4.50949001312256</t>
   </si>
   <si>
     <t xml:space="preserve">4.51772022247314</t>
   </si>
   <si>
-    <t xml:space="preserve">4.37505531311035</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.35310697555542</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.47107982635498</t>
+    <t xml:space="preserve">4.37505483627319</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.35310745239258</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.47107934951782</t>
   </si>
   <si>
     <t xml:space="preserve">4.49760103225708</t>
@@ -5849,7 +5849,7 @@
     <t xml:space="preserve">4.43724250793457</t>
   </si>
   <si>
-    <t xml:space="preserve">4.27720165252686</t>
+    <t xml:space="preserve">4.27720212936401</t>
   </si>
   <si>
     <t xml:space="preserve">4.26805686950684</t>
@@ -5879,13 +5879,13 @@
     <t xml:space="preserve">4.4098072052002</t>
   </si>
   <si>
-    <t xml:space="preserve">4.39243078231812</t>
+    <t xml:space="preserve">4.39243125915527</t>
   </si>
   <si>
     <t xml:space="preserve">4.44181489944458</t>
   </si>
   <si>
-    <t xml:space="preserve">4.38968753814697</t>
+    <t xml:space="preserve">4.38968801498413</t>
   </si>
   <si>
     <t xml:space="preserve">4.3174409866333</t>
@@ -5900,7 +5900,7 @@
     <t xml:space="preserve">4.61283016204834</t>
   </si>
   <si>
-    <t xml:space="preserve">4.70611047744751</t>
+    <t xml:space="preserve">4.70611095428467</t>
   </si>
   <si>
     <t xml:space="preserve">4.64575290679932</t>
@@ -5909,13 +5909,13 @@
     <t xml:space="preserve">4.84145975112915</t>
   </si>
   <si>
-    <t xml:space="preserve">4.79939222335815</t>
+    <t xml:space="preserve">4.799391746521</t>
   </si>
   <si>
     <t xml:space="preserve">4.82134008407593</t>
   </si>
   <si>
-    <t xml:space="preserve">4.75549459457397</t>
+    <t xml:space="preserve">4.75549507141113</t>
   </si>
   <si>
     <t xml:space="preserve">4.7335467338562</t>
@@ -5924,13 +5924,13 @@
     <t xml:space="preserve">4.68782043457031</t>
   </si>
   <si>
-    <t xml:space="preserve">4.75183725357056</t>
+    <t xml:space="preserve">4.7518367767334</t>
   </si>
   <si>
     <t xml:space="preserve">4.77744340896606</t>
   </si>
   <si>
-    <t xml:space="preserve">4.80305004119873</t>
+    <t xml:space="preserve">4.80304956436157</t>
   </si>
   <si>
     <t xml:space="preserve">4.81768226623535</t>
@@ -5939,7 +5939,7 @@
     <t xml:space="preserve">4.98046636581421</t>
   </si>
   <si>
-    <t xml:space="preserve">4.96217632293701</t>
+    <t xml:space="preserve">4.96217584609985</t>
   </si>
   <si>
     <t xml:space="preserve">5.03533744812012</t>
@@ -5969,13 +5969,13 @@
     <t xml:space="preserve">4.27354383468628</t>
   </si>
   <si>
-    <t xml:space="preserve">4.32109880447388</t>
+    <t xml:space="preserve">4.32109832763672</t>
   </si>
   <si>
     <t xml:space="preserve">4.34121799468994</t>
   </si>
   <si>
-    <t xml:space="preserve">4.36956834793091</t>
+    <t xml:space="preserve">4.36956787109375</t>
   </si>
   <si>
     <t xml:space="preserve">4.35767936706543</t>
@@ -5996,7 +5996,7 @@
     <t xml:space="preserve">4.51497650146484</t>
   </si>
   <si>
-    <t xml:space="preserve">4.53052377700806</t>
+    <t xml:space="preserve">4.5305233001709</t>
   </si>
   <si>
     <t xml:space="preserve">4.51040410995483</t>
@@ -6005,28 +6005,28 @@
     <t xml:space="preserve">4.56618976593018</t>
   </si>
   <si>
-    <t xml:space="preserve">4.52686548233032</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.5543007850647</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.5360107421875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.62746238708496</t>
+    <t xml:space="preserve">4.52686500549316</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.55430126190186</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.53601026535034</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.6274619102478</t>
   </si>
   <si>
     <t xml:space="preserve">4.61831712722778</t>
   </si>
   <si>
-    <t xml:space="preserve">4.48662710189819</t>
+    <t xml:space="preserve">4.48662662506104</t>
   </si>
   <si>
     <t xml:space="preserve">4.46559238433838</t>
   </si>
   <si>
-    <t xml:space="preserve">4.49485683441162</t>
+    <t xml:space="preserve">4.49485731124878</t>
   </si>
   <si>
     <t xml:space="preserve">4.39700365066528</t>
@@ -6047,10 +6047,10 @@
     <t xml:space="preserve">4.46284914016724</t>
   </si>
   <si>
-    <t xml:space="preserve">4.53692531585693</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.54972791671753</t>
+    <t xml:space="preserve">4.53692483901978</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.54972839355469</t>
   </si>
   <si>
     <t xml:space="preserve">4.5122332572937</t>
@@ -6074,10 +6074,10 @@
     <t xml:space="preserve">4.4674220085144</t>
   </si>
   <si>
-    <t xml:space="preserve">4.67867565155029</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.7756142616272</t>
+    <t xml:space="preserve">4.67867517471313</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.77561473846436</t>
   </si>
   <si>
     <t xml:space="preserve">4.82499837875366</t>
@@ -6086,16 +6086,16 @@
     <t xml:space="preserve">4.86523723602295</t>
   </si>
   <si>
-    <t xml:space="preserve">5.26579618453979</t>
+    <t xml:space="preserve">5.26579570770264</t>
   </si>
   <si>
     <t xml:space="preserve">5.36639308929443</t>
   </si>
   <si>
-    <t xml:space="preserve">5.33529996871948</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.34078645706177</t>
+    <t xml:space="preserve">5.33529949188232</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.34078693389893</t>
   </si>
   <si>
     <t xml:space="preserve">5.33164167404175</t>
@@ -6107,7 +6107,7 @@
     <t xml:space="preserve">5.35541868209839</t>
   </si>
   <si>
-    <t xml:space="preserve">5.27677059173584</t>
+    <t xml:space="preserve">5.27677011489868</t>
   </si>
   <si>
     <t xml:space="preserve">5.22738647460938</t>
@@ -6149,10 +6149,10 @@
     <t xml:space="preserve">5.46516084671021</t>
   </si>
   <si>
-    <t xml:space="preserve">5.22555780410767</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.36456441879272</t>
+    <t xml:space="preserve">5.22555732727051</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.36456394195557</t>
   </si>
   <si>
     <t xml:space="preserve">5.3682222366333</t>
@@ -6161,13 +6161,13 @@
     <t xml:space="preserve">5.47430658340454</t>
   </si>
   <si>
-    <t xml:space="preserve">5.55112552642822</t>
+    <t xml:space="preserve">5.55112600326538</t>
   </si>
   <si>
     <t xml:space="preserve">5.43223857879639</t>
   </si>
   <si>
-    <t xml:space="preserve">5.55844163894653</t>
+    <t xml:space="preserve">5.55844211578369</t>
   </si>
   <si>
     <t xml:space="preserve">5.44504165649414</t>
@@ -6176,16 +6176,16 @@
     <t xml:space="preserve">5.4395546913147</t>
   </si>
   <si>
-    <t xml:space="preserve">5.42675161361694</t>
+    <t xml:space="preserve">5.42675113677979</t>
   </si>
   <si>
     <t xml:space="preserve">5.34444427490234</t>
   </si>
   <si>
-    <t xml:space="preserve">5.24933433532715</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.19812154769897</t>
+    <t xml:space="preserve">5.24933481216431</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.19812202453613</t>
   </si>
   <si>
     <t xml:space="preserve">5.23287343978882</t>
@@ -6203,7 +6203,7 @@
     <t xml:space="preserve">5.54380941390991</t>
   </si>
   <si>
-    <t xml:space="preserve">5.38651275634766</t>
+    <t xml:space="preserve">5.3865122795105</t>
   </si>
   <si>
     <t xml:space="preserve">5.29323148727417</t>
@@ -6227,19 +6227,19 @@
     <t xml:space="preserve">5.68098735809326</t>
   </si>
   <si>
-    <t xml:space="preserve">5.54929685592651</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.50174140930176</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.48162269592285</t>
+    <t xml:space="preserve">5.54929637908936</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.50174188613892</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.48162221908569</t>
   </si>
   <si>
     <t xml:space="preserve">5.53100633621216</t>
   </si>
   <si>
-    <t xml:space="preserve">5.60965442657471</t>
+    <t xml:space="preserve">5.60965490341187</t>
   </si>
   <si>
     <t xml:space="preserve">5.44687032699585</t>
@@ -6299,7 +6299,7 @@
     <t xml:space="preserve">6.12361431121826</t>
   </si>
   <si>
-    <t xml:space="preserve">6.03947830200195</t>
+    <t xml:space="preserve">6.03947877883911</t>
   </si>
   <si>
     <t xml:space="preserve">6.03033304214478</t>
@@ -6314,13 +6314,13 @@
     <t xml:space="preserve">6.30285978317261</t>
   </si>
   <si>
-    <t xml:space="preserve">5.82548093795776</t>
+    <t xml:space="preserve">5.82548141479492</t>
   </si>
   <si>
     <t xml:space="preserve">5.73220062255859</t>
   </si>
   <si>
-    <t xml:space="preserve">5.87852334976196</t>
+    <t xml:space="preserve">5.8785228729248</t>
   </si>
   <si>
     <t xml:space="preserve">5.90230083465576</t>
@@ -6332,7 +6332,7 @@
     <t xml:space="preserve">5.84742975234985</t>
   </si>
   <si>
-    <t xml:space="preserve">6.04679441452026</t>
+    <t xml:space="preserve">6.04679489135742</t>
   </si>
   <si>
     <t xml:space="preserve">6.13641738891602</t>
@@ -6347,7 +6347,7 @@
     <t xml:space="preserve">6.22055339813232</t>
   </si>
   <si>
-    <t xml:space="preserve">6.36321830749512</t>
+    <t xml:space="preserve">6.36321783065796</t>
   </si>
   <si>
     <t xml:space="preserve">6.48942184448242</t>
@@ -6365,7 +6365,7 @@
     <t xml:space="preserve">6.85157060623169</t>
   </si>
   <si>
-    <t xml:space="preserve">6.5607533454895</t>
+    <t xml:space="preserve">6.56075382232666</t>
   </si>
   <si>
     <t xml:space="preserve">6.77475118637085</t>
@@ -6401,19 +6401,19 @@
     <t xml:space="preserve">6.91375780105591</t>
   </si>
   <si>
-    <t xml:space="preserve">6.95765447616577</t>
+    <t xml:space="preserve">6.95765495300293</t>
   </si>
   <si>
     <t xml:space="preserve">7.01618385314941</t>
   </si>
   <si>
-    <t xml:space="preserve">7.1094651222229</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.08020067214966</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.00520944595337</t>
+    <t xml:space="preserve">7.10946464538574</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.0802001953125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.00520992279053</t>
   </si>
   <si>
     <t xml:space="preserve">6.82413530349731</t>
@@ -6443,13 +6443,13 @@
     <t xml:space="preserve">5.67915821075439</t>
   </si>
   <si>
-    <t xml:space="preserve">5.88766860961914</t>
+    <t xml:space="preserve">5.8876690864563</t>
   </si>
   <si>
     <t xml:space="preserve">6.05959796905518</t>
   </si>
   <si>
-    <t xml:space="preserve">6.16019487380981</t>
+    <t xml:space="preserve">6.16019535064697</t>
   </si>
   <si>
     <t xml:space="preserve">6.06874322891235</t>
@@ -6476,16 +6476,16 @@
     <t xml:space="preserve">6.72902488708496</t>
   </si>
   <si>
-    <t xml:space="preserve">6.76377725601196</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.71622228622437</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.94668054580688</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.17165231704712</t>
+    <t xml:space="preserve">6.7637767791748</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.71622180938721</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.94668102264404</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.17165184020996</t>
   </si>
   <si>
     <t xml:space="preserve">7.17713928222656</t>
@@ -6494,7 +6494,7 @@
     <t xml:space="preserve">7.26859092712402</t>
   </si>
   <si>
-    <t xml:space="preserve">7.28505277633667</t>
+    <t xml:space="preserve">7.28505229949951</t>
   </si>
   <si>
     <t xml:space="preserve">7.20091676712036</t>
@@ -6882,6 +6882,9 @@
   </si>
   <si>
     <t xml:space="preserve">10.6000003814697</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4899997711182</t>
   </si>
 </sst>
 </file>
@@ -72818,7 +72821,7 @@
     </row>
     <row r="2524">
       <c r="A2524" s="1" t="n">
-        <v>45993.6910069444</v>
+        <v>45993.3333333333</v>
       </c>
       <c r="B2524" t="n">
         <v>11457314</v>
@@ -72839,6 +72842,32 @@
         <v>2289</v>
       </c>
       <c r="H2524" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2525">
+      <c r="A2525" s="1" t="n">
+        <v>45994.6912037037</v>
+      </c>
+      <c r="B2525" t="n">
+        <v>7844184</v>
+      </c>
+      <c r="C2525" t="n">
+        <v>10.7049999237061</v>
+      </c>
+      <c r="D2525" t="n">
+        <v>10.4899997711182</v>
+      </c>
+      <c r="E2525" t="n">
+        <v>10.6899995803833</v>
+      </c>
+      <c r="F2525" t="n">
+        <v>10.4899997711182</v>
+      </c>
+      <c r="G2525" t="s">
+        <v>2290</v>
+      </c>
+      <c r="H2525" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/BPE.MI.xlsx
+++ b/data/BPE.MI.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2290" uniqueCount="2290">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2291" uniqueCount="2291">
   <si>
     <t xml:space="preserve">date</t>
   </si>
@@ -50,28 +50,28 @@
     <t xml:space="preserve">3.09375739097595</t>
   </si>
   <si>
-    <t xml:space="preserve">3.02301597595215</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.9546320438385</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.95699024200439</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.9334089756012</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.07489228248596</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.91690421104431</t>
+    <t xml:space="preserve">3.02301549911499</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.95463180541992</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.95699048042297</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.93340921401978</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.07489252090454</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.91690397262573</t>
   </si>
   <si>
     <t xml:space="preserve">2.66223454475403</t>
   </si>
   <si>
-    <t xml:space="preserve">2.65044403076172</t>
+    <t xml:space="preserve">2.6504442691803</t>
   </si>
   <si>
     <t xml:space="preserve">2.45708417892456</t>
@@ -83,91 +83,91 @@
     <t xml:space="preserve">2.69760513305664</t>
   </si>
   <si>
-    <t xml:space="preserve">2.62686395645142</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.78013730049133</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.66695070266724</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.46651649475098</t>
+    <t xml:space="preserve">2.62686371803284</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.78013682365417</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.66695094108582</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.46651673316956</t>
   </si>
   <si>
     <t xml:space="preserve">2.59385085105896</t>
   </si>
   <si>
-    <t xml:space="preserve">2.53018403053284</t>
+    <t xml:space="preserve">2.53018426895142</t>
   </si>
   <si>
     <t xml:space="preserve">2.35804677009583</t>
   </si>
   <si>
-    <t xml:space="preserve">2.16279983520508</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.17128920555115</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.1260142326355</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.87228894233704</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.83173036575317</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.95812141895294</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.7704211473465</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.97415626049042</t>
+    <t xml:space="preserve">2.16280007362366</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.17128896713257</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.12601447105408</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.87228906154633</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.83173072338104</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.95812177658081</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.77042138576508</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.97415661811829</t>
   </si>
   <si>
     <t xml:space="preserve">2.17411875724792</t>
   </si>
   <si>
-    <t xml:space="preserve">2.2797589302063</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.33446621894836</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.32031798362732</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.18166518211365</t>
+    <t xml:space="preserve">2.27975916862488</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.33446645736694</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.32031750679016</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.18166494369507</t>
   </si>
   <si>
     <t xml:space="preserve">2.40284991264343</t>
   </si>
   <si>
-    <t xml:space="preserve">2.31182909011841</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.16468644142151</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.21844983100891</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.25995206832886</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.22127985954285</t>
+    <t xml:space="preserve">2.31182861328125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.16468667984009</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.21844959259033</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.2599515914917</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.22127962112427</t>
   </si>
   <si>
     <t xml:space="preserve">2.25429201126099</t>
   </si>
   <si>
-    <t xml:space="preserve">2.36512088775635</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.32409071922302</t>
+    <t xml:space="preserve">2.36512064933777</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.32409024238586</t>
   </si>
   <si>
     <t xml:space="preserve">2.33352279663086</t>
@@ -176,22 +176,22 @@
     <t xml:space="preserve">2.21279072761536</t>
   </si>
   <si>
-    <t xml:space="preserve">2.18072128295898</t>
+    <t xml:space="preserve">2.18072152137756</t>
   </si>
   <si>
     <t xml:space="preserve">2.20524501800537</t>
   </si>
   <si>
-    <t xml:space="preserve">2.22505283355713</t>
+    <t xml:space="preserve">2.22505259513855</t>
   </si>
   <si>
     <t xml:space="preserve">2.4099235534668</t>
   </si>
   <si>
-    <t xml:space="preserve">2.44293642044067</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.36276245117188</t>
+    <t xml:space="preserve">2.44293618202209</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.3627622127533</t>
   </si>
   <si>
     <t xml:space="preserve">2.20241498947144</t>
@@ -203,43 +203,43 @@
     <t xml:space="preserve">2.246746301651</t>
   </si>
   <si>
-    <t xml:space="preserve">2.24108719825745</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.20807480812073</t>
+    <t xml:space="preserve">2.2410876750946</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.20807409286499</t>
   </si>
   <si>
     <t xml:space="preserve">2.14770865440369</t>
   </si>
   <si>
-    <t xml:space="preserve">2.05904626846313</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.03829503059387</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.97321283817291</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.00905585289001</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.89492619037628</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.88455033302307</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.77325093746185</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.0269763469696</t>
+    <t xml:space="preserve">2.05904603004456</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.03829479217529</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.9732129573822</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.00905561447144</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.8949259519577</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.88455021381378</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.77325069904327</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.02697658538818</t>
   </si>
   <si>
     <t xml:space="preserve">2.12507224082947</t>
   </si>
   <si>
-    <t xml:space="preserve">2.04018187522888</t>
+    <t xml:space="preserve">2.0401816368103</t>
   </si>
   <si>
     <t xml:space="preserve">2.2741003036499</t>
@@ -248,31 +248,31 @@
     <t xml:space="preserve">2.37691068649292</t>
   </si>
   <si>
-    <t xml:space="preserve">2.38398504257202</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.30428314208984</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.37219476699829</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.44765186309814</t>
+    <t xml:space="preserve">2.38398480415344</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.30428290367126</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.37219452857971</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.44765210151672</t>
   </si>
   <si>
     <t xml:space="preserve">2.45944213867188</t>
   </si>
   <si>
-    <t xml:space="preserve">2.37455320358276</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.45236849784851</t>
+    <t xml:space="preserve">2.37455296516418</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.45236802101135</t>
   </si>
   <si>
     <t xml:space="preserve">2.41463994979858</t>
   </si>
   <si>
-    <t xml:space="preserve">2.50896143913269</t>
+    <t xml:space="preserve">2.50896191596985</t>
   </si>
   <si>
     <t xml:space="preserve">2.4075653553009</t>
@@ -281,142 +281,142 @@
     <t xml:space="preserve">2.31937408447266</t>
   </si>
   <si>
-    <t xml:space="preserve">2.21750688552856</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.1929829120636</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.13167405128479</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.0760235786438</t>
+    <t xml:space="preserve">2.21750736236572</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.19298362731934</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.13167381286621</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.07602405548096</t>
   </si>
   <si>
     <t xml:space="preserve">2.07036447525024</t>
   </si>
   <si>
-    <t xml:space="preserve">2.06470584869385</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.03263640403748</t>
+    <t xml:space="preserve">2.06470537185669</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.03263592720032</t>
   </si>
   <si>
     <t xml:space="preserve">2.02980589866638</t>
   </si>
   <si>
-    <t xml:space="preserve">2.06093311309814</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.17506170272827</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.07319474220276</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.09960412979126</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.05811429023743</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.22021555900574</t>
+    <t xml:space="preserve">2.06093239784241</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.17506194114685</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.07319450378418</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.09960436820984</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.05811405181885</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.22021532058716</t>
   </si>
   <si>
     <t xml:space="preserve">2.3311779499054</t>
   </si>
   <si>
-    <t xml:space="preserve">2.28582811355591</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.29161787033081</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.31381034851074</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.19416356086731</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.16618204116821</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.07934188842773</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.06969261169434</t>
+    <t xml:space="preserve">2.28582835197449</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.29161763191223</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.31381058692932</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.19416403770447</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.16618227958679</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.07934165000916</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.06969237327576</t>
   </si>
   <si>
     <t xml:space="preserve">2.09670925140381</t>
   </si>
   <si>
-    <t xml:space="preserve">2.13627028465271</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.99636113643646</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.87478423118591</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.82171535491943</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.81592631340027</t>
+    <t xml:space="preserve">2.13627052307129</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.99636077880859</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.87478411197662</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.82171499729156</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.81592607498169</t>
   </si>
   <si>
     <t xml:space="preserve">1.76864624023438</t>
   </si>
   <si>
-    <t xml:space="preserve">1.94425702095032</t>
+    <t xml:space="preserve">1.94425678253174</t>
   </si>
   <si>
     <t xml:space="preserve">2.03206157684326</t>
   </si>
   <si>
-    <t xml:space="preserve">2.08416533470154</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.07548236846924</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.23468899726868</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.68470096588135</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.66733300685883</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.62777173519135</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.5390020608902</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.5814573764801</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.50523066520691</t>
+    <t xml:space="preserve">2.0841658115387</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.07548213005066</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.23468923568726</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.68470084667206</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.66733288764954</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.62777185440063</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.53900182247162</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.58145749568939</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.50523054599762</t>
   </si>
   <si>
     <t xml:space="preserve">1.40391731262207</t>
   </si>
   <si>
-    <t xml:space="preserve">1.40488255023956</t>
+    <t xml:space="preserve">1.40488243103027</t>
   </si>
   <si>
     <t xml:space="preserve">1.30453336238861</t>
   </si>
   <si>
-    <t xml:space="preserve">1.24567461013794</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.44733703136444</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.51487970352173</t>
+    <t xml:space="preserve">1.24567449092865</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.44733715057373</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.51487994194031</t>
   </si>
   <si>
     <t xml:space="preserve">1.63838613033295</t>
@@ -425,64 +425,64 @@
     <t xml:space="preserve">1.5563702583313</t>
   </si>
   <si>
-    <t xml:space="preserve">1.62294793128967</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.64224541187286</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.65189468860626</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.63645577430725</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.65382432937622</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.70689308643341</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.69434940814972</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.64899957180023</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.65671837329865</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.73294532299042</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.67891144752502</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.7705762386322</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.67022752761841</t>
+    <t xml:space="preserve">1.62294805049896</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.64224553108215</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.65189492702484</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.63645601272583</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.65382409095764</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.70689284801483</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.69434952735901</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.6489999294281</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.65671849250793</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.73294544219971</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.67891156673431</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.77057635784149</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.67022740840912</t>
   </si>
   <si>
     <t xml:space="preserve">1.46374022960663</t>
   </si>
   <si>
-    <t xml:space="preserve">1.52259886264801</t>
+    <t xml:space="preserve">1.52259862422943</t>
   </si>
   <si>
     <t xml:space="preserve">1.53031778335571</t>
   </si>
   <si>
-    <t xml:space="preserve">1.73005080223083</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.69820892810822</t>
+    <t xml:space="preserve">1.73005104064941</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.69820916652679</t>
   </si>
   <si>
     <t xml:space="preserve">1.73198044300079</t>
   </si>
   <si>
-    <t xml:space="preserve">1.72136688232422</t>
+    <t xml:space="preserve">1.72136700153351</t>
   </si>
   <si>
     <t xml:space="preserve">1.72040188312531</t>
@@ -494,10 +494,10 @@
     <t xml:space="preserve">1.68373608589172</t>
   </si>
   <si>
-    <t xml:space="preserve">1.62101781368256</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.64996469020844</t>
+    <t xml:space="preserve">1.62101769447327</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.64996457099915</t>
   </si>
   <si>
     <t xml:space="preserve">1.55444025993347</t>
@@ -509,7 +509,7 @@
     <t xml:space="preserve">1.65478932857513</t>
   </si>
   <si>
-    <t xml:space="preserve">1.6904901266098</t>
+    <t xml:space="preserve">1.69048988819122</t>
   </si>
   <si>
     <t xml:space="preserve">1.64128041267395</t>
@@ -518,31 +518,31 @@
     <t xml:space="preserve">1.60750913619995</t>
   </si>
   <si>
-    <t xml:space="preserve">1.65285909175873</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.66443824768066</t>
+    <t xml:space="preserve">1.65285921096802</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.66443836688995</t>
   </si>
   <si>
     <t xml:space="preserve">1.69531464576721</t>
   </si>
   <si>
-    <t xml:space="preserve">1.7184716463089</t>
+    <t xml:space="preserve">1.71847188472748</t>
   </si>
   <si>
     <t xml:space="preserve">1.68759536743164</t>
   </si>
   <si>
-    <t xml:space="preserve">1.74452412128448</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.7474182844162</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.71268272399902</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.67987644672394</t>
+    <t xml:space="preserve">1.74452388286591</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.74741864204407</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.71268260478973</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.67987620830536</t>
   </si>
   <si>
     <t xml:space="preserve">1.63549149036407</t>
@@ -551,16 +551,16 @@
     <t xml:space="preserve">1.58049249649048</t>
   </si>
   <si>
-    <t xml:space="preserve">1.60461473464966</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.5361076593399</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.60847425460815</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.61233389377594</t>
+    <t xml:space="preserve">1.60461461544037</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.53610742092133</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.60847413539886</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.61233365535736</t>
   </si>
   <si>
     <t xml:space="preserve">1.53996706008911</t>
@@ -569,142 +569,142 @@
     <t xml:space="preserve">1.51584494113922</t>
   </si>
   <si>
-    <t xml:space="preserve">1.54961609840393</t>
+    <t xml:space="preserve">1.54961621761322</t>
   </si>
   <si>
     <t xml:space="preserve">1.5525107383728</t>
   </si>
   <si>
-    <t xml:space="preserve">1.59786069393158</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.56119477748871</t>
+    <t xml:space="preserve">1.597860455513</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.56119501590729</t>
   </si>
   <si>
     <t xml:space="preserve">1.63452649116516</t>
   </si>
   <si>
-    <t xml:space="preserve">1.63935089111328</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.61619329452515</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.6740870475769</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.77540075778961</t>
+    <t xml:space="preserve">1.63935101032257</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.61619317531586</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.67408668994904</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.7754008769989</t>
   </si>
   <si>
     <t xml:space="preserve">1.81496119499207</t>
   </si>
   <si>
-    <t xml:space="preserve">1.73583984375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.82653987407684</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.86513590812683</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.96066045761108</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.05425453186035</t>
+    <t xml:space="preserve">1.73583960533142</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.82653951644897</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.86513566970825</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.96065998077393</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.05425429344177</t>
   </si>
   <si>
     <t xml:space="preserve">2.04943013191223</t>
   </si>
   <si>
-    <t xml:space="preserve">2.10153388977051</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.01372933387756</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.04653525352478</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.09477949142456</t>
+    <t xml:space="preserve">2.10153365135193</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.01372909545898</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.04653549194336</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.09477996826172</t>
   </si>
   <si>
     <t xml:space="preserve">2.08899021148682</t>
   </si>
   <si>
-    <t xml:space="preserve">2.06197333335876</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.04460525512695</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.92978322505951</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.9056613445282</t>
+    <t xml:space="preserve">2.06197357177734</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.04460501670837</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.92978346347809</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.90566122531891</t>
   </si>
   <si>
     <t xml:space="preserve">1.88443374633789</t>
   </si>
   <si>
-    <t xml:space="preserve">1.95004606246948</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.98671162128448</t>
+    <t xml:space="preserve">1.95004570484161</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.98671185970306</t>
   </si>
   <si>
     <t xml:space="preserve">2.01565837860107</t>
   </si>
   <si>
-    <t xml:space="preserve">2.0166232585907</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.99539613723755</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.98574674129486</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.92785322666168</t>
+    <t xml:space="preserve">2.01662373542786</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.99539601802826</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.98574662208557</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.92785334587097</t>
   </si>
   <si>
     <t xml:space="preserve">1.84583723545074</t>
   </si>
   <si>
-    <t xml:space="preserve">1.80820727348328</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.80048739910126</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.83715391159058</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.82750487327576</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.83329379558563</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.80531191825867</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.82846975326538</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.975133061409</t>
+    <t xml:space="preserve">1.8082070350647</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.80048763751984</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.83715403079987</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.82750475406647</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.83329391479492</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.80531203746796</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.82846999168396</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.97513329982758</t>
   </si>
   <si>
     <t xml:space="preserve">1.93557286262512</t>
   </si>
   <si>
-    <t xml:space="preserve">2.06679844856262</t>
+    <t xml:space="preserve">2.06679797172546</t>
   </si>
   <si>
     <t xml:space="preserve">2.28196859359741</t>
   </si>
   <si>
-    <t xml:space="preserve">2.31477499008179</t>
+    <t xml:space="preserve">2.31477475166321</t>
   </si>
   <si>
     <t xml:space="preserve">2.27907395362854</t>
@@ -713,19 +713,19 @@
     <t xml:space="preserve">2.32152938842773</t>
   </si>
   <si>
-    <t xml:space="preserve">2.37073874473572</t>
+    <t xml:space="preserve">2.37073922157288</t>
   </si>
   <si>
     <t xml:space="preserve">2.33214282989502</t>
   </si>
   <si>
-    <t xml:space="preserve">2.39486122131348</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.41464161872864</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.39775586128235</t>
+    <t xml:space="preserve">2.3948609828949</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.41464185714722</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.39775562286377</t>
   </si>
   <si>
     <t xml:space="preserve">2.41222929954529</t>
@@ -734,55 +734,55 @@
     <t xml:space="preserve">2.46529841423035</t>
   </si>
   <si>
-    <t xml:space="preserve">2.48942089080811</t>
+    <t xml:space="preserve">2.48942065238953</t>
   </si>
   <si>
     <t xml:space="preserve">2.49665713310242</t>
   </si>
   <si>
-    <t xml:space="preserve">2.44117593765259</t>
+    <t xml:space="preserve">2.44117641448975</t>
   </si>
   <si>
     <t xml:space="preserve">2.54248952865601</t>
   </si>
   <si>
-    <t xml:space="preserve">2.63897848129272</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.59555912017822</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.55696272850037</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.42911505699158</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.41705346107483</t>
+    <t xml:space="preserve">2.6389787197113</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.59555864334106</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.55696249008179</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.42911529541016</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.41705322265625</t>
   </si>
   <si>
     <t xml:space="preserve">2.56178760528564</t>
   </si>
   <si>
-    <t xml:space="preserve">2.53766512870789</t>
+    <t xml:space="preserve">2.53766489028931</t>
   </si>
   <si>
     <t xml:space="preserve">2.57867312431335</t>
   </si>
   <si>
-    <t xml:space="preserve">2.58832216262817</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.72823119163513</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.77165102958679</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.7065212726593</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.71375751495361</t>
+    <t xml:space="preserve">2.58832192420959</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.72823143005371</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.77165126800537</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.70652103424072</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.71375775337219</t>
   </si>
   <si>
     <t xml:space="preserve">2.74752879142761</t>
@@ -800,13 +800,13 @@
     <t xml:space="preserve">2.58590936660767</t>
   </si>
   <si>
-    <t xml:space="preserve">2.59797048568726</t>
+    <t xml:space="preserve">2.59797024726868</t>
   </si>
   <si>
     <t xml:space="preserve">2.66068863868713</t>
   </si>
   <si>
-    <t xml:space="preserve">2.50871849060059</t>
+    <t xml:space="preserve">2.50871801376343</t>
   </si>
   <si>
     <t xml:space="preserve">2.42187786102295</t>
@@ -815,13 +815,13 @@
     <t xml:space="preserve">2.45082497596741</t>
   </si>
   <si>
-    <t xml:space="preserve">2.29451203346252</t>
+    <t xml:space="preserve">2.2945122718811</t>
   </si>
   <si>
     <t xml:space="preserve">2.3022313117981</t>
   </si>
   <si>
-    <t xml:space="preserve">2.38135290145874</t>
+    <t xml:space="preserve">2.38135266304016</t>
   </si>
   <si>
     <t xml:space="preserve">2.32056474685669</t>
@@ -833,82 +833,82 @@
     <t xml:space="preserve">2.17100596427917</t>
   </si>
   <si>
-    <t xml:space="preserve">2.14784860610962</t>
+    <t xml:space="preserve">2.1478488445282</t>
   </si>
   <si>
     <t xml:space="preserve">2.14495444297791</t>
   </si>
   <si>
-    <t xml:space="preserve">2.06293892860413</t>
+    <t xml:space="preserve">2.06293869018555</t>
   </si>
   <si>
     <t xml:space="preserve">2.02627277374268</t>
   </si>
   <si>
-    <t xml:space="preserve">1.99732601642609</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.16135740280151</t>
+    <t xml:space="preserve">1.9973258972168</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.16135764122009</t>
   </si>
   <si>
     <t xml:space="preserve">2.17004179954529</t>
   </si>
   <si>
-    <t xml:space="preserve">2.26749587059021</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.20574235916138</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.113112449646</t>
+    <t xml:space="preserve">2.26749539375305</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.20574283599854</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.11311268806458</t>
   </si>
   <si>
     <t xml:space="preserve">2.11793684959412</t>
   </si>
   <si>
-    <t xml:space="preserve">2.18837404251099</t>
+    <t xml:space="preserve">2.18837428092957</t>
   </si>
   <si>
     <t xml:space="preserve">2.25977635383606</t>
   </si>
   <si>
-    <t xml:space="preserve">2.22214531898499</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.16521692276001</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.16907668113708</t>
+    <t xml:space="preserve">2.22214579582214</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.16521668434143</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.16907644271851</t>
   </si>
   <si>
     <t xml:space="preserve">2.27714490890503</t>
   </si>
   <si>
-    <t xml:space="preserve">2.25012731552124</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.31767010688782</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.32635402679443</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.39196634292603</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.36494970321655</t>
+    <t xml:space="preserve">2.25012755393982</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.31766986846924</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.32635426521301</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.39196705818176</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.36494946479797</t>
   </si>
   <si>
     <t xml:space="preserve">2.3224937915802</t>
   </si>
   <si>
-    <t xml:space="preserve">2.3369677066803</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.29354810714722</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.26267075538635</t>
+    <t xml:space="preserve">2.33696746826172</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.2935483455658</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.26267099380493</t>
   </si>
   <si>
     <t xml:space="preserve">2.25784659385681</t>
@@ -917,37 +917,37 @@
     <t xml:space="preserve">2.17872500419617</t>
   </si>
   <si>
-    <t xml:space="preserve">2.19512820243835</t>
+    <t xml:space="preserve">2.19512796401978</t>
   </si>
   <si>
     <t xml:space="preserve">2.19319891929626</t>
   </si>
   <si>
-    <t xml:space="preserve">2.20960211753845</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.17390155792236</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.12179613113403</t>
+    <t xml:space="preserve">2.20960187911987</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.17390108108521</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.12179684638977</t>
   </si>
   <si>
     <t xml:space="preserve">2.10442900657654</t>
   </si>
   <si>
-    <t xml:space="preserve">2.21153140068054</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.36398410797119</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.39872074127197</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.34661674499512</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.41946601867676</t>
+    <t xml:space="preserve">2.21153163909912</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.36398434638977</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.39872050285339</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.3466169834137</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.41946625709534</t>
   </si>
   <si>
     <t xml:space="preserve">2.48218441009521</t>
@@ -956,49 +956,49 @@
     <t xml:space="preserve">2.51836729049683</t>
   </si>
   <si>
-    <t xml:space="preserve">2.45564961433411</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.43635177612305</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.29837155342102</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.26170587539673</t>
+    <t xml:space="preserve">2.45564913749695</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.43635129928589</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.29837203025818</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.26170563697815</t>
   </si>
   <si>
     <t xml:space="preserve">2.34468650817871</t>
   </si>
   <si>
-    <t xml:space="preserve">2.30609035491943</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.25302147865295</t>
+    <t xml:space="preserve">2.30609059333801</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.25302219390869</t>
   </si>
   <si>
     <t xml:space="preserve">2.22697019577026</t>
   </si>
   <si>
-    <t xml:space="preserve">2.26074147224426</t>
+    <t xml:space="preserve">2.26074171066284</t>
   </si>
   <si>
     <t xml:space="preserve">2.24998950958252</t>
   </si>
   <si>
-    <t xml:space="preserve">2.25096702575684</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.28224349021912</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.27931189537048</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.25292158126831</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.18450331687927</t>
+    <t xml:space="preserve">2.25096750259399</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.28224396705627</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.27931213378906</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.25292181968689</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.18450379371643</t>
   </si>
   <si>
     <t xml:space="preserve">2.18548130989075</t>
@@ -1007,31 +1007,31 @@
     <t xml:space="preserve">2.13074636459351</t>
   </si>
   <si>
-    <t xml:space="preserve">2.17570638656616</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.14833998680115</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.10924315452576</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.07698917388916</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.08089852333069</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.15811347961426</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.1512713432312</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.10631132125854</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.15909123420715</t>
+    <t xml:space="preserve">2.1757071018219</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.14833950996399</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.10924339294434</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.07698893547058</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.08089828491211</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.15811324119568</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.15127158164978</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.10631108283997</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.15909099578857</t>
   </si>
   <si>
     <t xml:space="preserve">2.13758778572083</t>
@@ -1040,7 +1040,7 @@
     <t xml:space="preserve">2.04082465171814</t>
   </si>
   <si>
-    <t xml:space="preserve">2.05353093147278</t>
+    <t xml:space="preserve">2.0535306930542</t>
   </si>
   <si>
     <t xml:space="preserve">2.00075101852417</t>
@@ -1049,16 +1049,16 @@
     <t xml:space="preserve">2.09067225456238</t>
   </si>
   <si>
-    <t xml:space="preserve">2.08187627792358</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.13661026954651</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.14931631088257</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.16886568069458</t>
+    <t xml:space="preserve">2.081876039505</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.13661050796509</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.14931678771973</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.168865442276</t>
   </si>
   <si>
     <t xml:space="preserve">2.15713596343994</t>
@@ -1067,19 +1067,19 @@
     <t xml:space="preserve">2.13367819786072</t>
   </si>
   <si>
-    <t xml:space="preserve">2.27149295806885</t>
+    <t xml:space="preserve">2.27149248123169</t>
   </si>
   <si>
     <t xml:space="preserve">2.34870719909668</t>
   </si>
   <si>
-    <t xml:space="preserve">2.29201769828796</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.29788255691528</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.29104065895081</t>
+    <t xml:space="preserve">2.29201817512512</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.29788303375244</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.29104018211365</t>
   </si>
   <si>
     <t xml:space="preserve">2.32231783866882</t>
@@ -1088,25 +1088,25 @@
     <t xml:space="preserve">2.36434650421143</t>
   </si>
   <si>
-    <t xml:space="preserve">2.41419458389282</t>
+    <t xml:space="preserve">2.41419434547424</t>
   </si>
   <si>
     <t xml:space="preserve">2.42103576660156</t>
   </si>
   <si>
-    <t xml:space="preserve">2.41908121109009</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.43374228477478</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.35457229614258</t>
+    <t xml:space="preserve">2.41908144950867</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.43374180793762</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.354572057724</t>
   </si>
   <si>
     <t xml:space="preserve">2.37021040916443</t>
   </si>
   <si>
-    <t xml:space="preserve">2.30667996406555</t>
+    <t xml:space="preserve">2.30667972564697</t>
   </si>
   <si>
     <t xml:space="preserve">2.28126692771912</t>
@@ -1115,37 +1115,37 @@
     <t xml:space="preserve">2.25389933586121</t>
   </si>
   <si>
-    <t xml:space="preserve">2.2871310710907</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.29885983467102</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.27344727516174</t>
+    <t xml:space="preserve">2.28713130950928</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.29885959625244</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.27344751358032</t>
   </si>
   <si>
     <t xml:space="preserve">2.26953744888306</t>
   </si>
   <si>
-    <t xml:space="preserve">2.31352114677429</t>
+    <t xml:space="preserve">2.31352090835571</t>
   </si>
   <si>
     <t xml:space="preserve">2.45328998565674</t>
   </si>
   <si>
-    <t xml:space="preserve">2.42005848884583</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.40246558189392</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.3174307346344</t>
+    <t xml:space="preserve">2.42005801200867</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.40246534347534</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.31743121147156</t>
   </si>
   <si>
     <t xml:space="preserve">2.39464545249939</t>
   </si>
   <si>
-    <t xml:space="preserve">2.38389420509338</t>
+    <t xml:space="preserve">2.38389444351196</t>
   </si>
   <si>
     <t xml:space="preserve">2.35750436782837</t>
@@ -1154,13 +1154,13 @@
     <t xml:space="preserve">2.32622742652893</t>
   </si>
   <si>
-    <t xml:space="preserve">2.2969057559967</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.31938529014587</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.3291597366333</t>
+    <t xml:space="preserve">2.29690527915955</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.31938505172729</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.32915949821472</t>
   </si>
   <si>
     <t xml:space="preserve">2.2685604095459</t>
@@ -1169,25 +1169,25 @@
     <t xml:space="preserve">2.29299569129944</t>
   </si>
   <si>
-    <t xml:space="preserve">2.3125433921814</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.34382081031799</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.30863380432129</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.27246999740601</t>
+    <t xml:space="preserve">2.31254363059998</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.34382104873657</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.30863428115845</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.27247023582458</t>
   </si>
   <si>
     <t xml:space="preserve">2.23337364196777</t>
   </si>
   <si>
-    <t xml:space="preserve">2.21382570266724</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.27735757827759</t>
+    <t xml:space="preserve">2.21382546424866</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.27735733985901</t>
   </si>
   <si>
     <t xml:space="preserve">2.34773063659668</t>
@@ -1196,10 +1196,10 @@
     <t xml:space="preserve">2.30081510543823</t>
   </si>
   <si>
-    <t xml:space="preserve">2.2421703338623</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.26269578933716</t>
+    <t xml:space="preserve">2.24217009544373</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.26269602775574</t>
   </si>
   <si>
     <t xml:space="preserve">2.29006361961365</t>
@@ -1214,28 +1214,28 @@
     <t xml:space="preserve">2.35359477996826</t>
   </si>
   <si>
-    <t xml:space="preserve">2.42299056053162</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.46306419372559</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.47283840179443</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.51437854766846</t>
+    <t xml:space="preserve">2.42299103736877</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.46306443214417</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.47283887863159</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.51437878608704</t>
   </si>
   <si>
     <t xml:space="preserve">2.50704741477966</t>
   </si>
   <si>
-    <t xml:space="preserve">2.43276453018188</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.39171361923218</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.26171851158142</t>
+    <t xml:space="preserve">2.43276429176331</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.39171385765076</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.26171803474426</t>
   </si>
   <si>
     <t xml:space="preserve">2.19525480270386</t>
@@ -1244,22 +1244,22 @@
     <t xml:space="preserve">2.14736199378967</t>
   </si>
   <si>
-    <t xml:space="preserve">2.1708197593689</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.14638447761536</t>
+    <t xml:space="preserve">2.17081928253174</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.14638495445251</t>
   </si>
   <si>
     <t xml:space="preserve">2.1405200958252</t>
   </si>
   <si>
-    <t xml:space="preserve">2.07210206985474</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.07894349098206</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.09946894645691</t>
+    <t xml:space="preserve">2.07210159301758</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.07894325256348</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.09946870803833</t>
   </si>
   <si>
     <t xml:space="preserve">2.07601141929626</t>
@@ -1268,58 +1268,58 @@
     <t xml:space="preserve">2.04375743865967</t>
   </si>
   <si>
-    <t xml:space="preserve">2.05450820922852</t>
+    <t xml:space="preserve">2.05450844764709</t>
   </si>
   <si>
     <t xml:space="preserve">2.04473400115967</t>
   </si>
   <si>
-    <t xml:space="preserve">2.03886985778809</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.11315274238586</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.0593957901001</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.02616381645203</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.98804473876953</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.9010556936264</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.08969569206238</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.06721472740173</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.08578586578369</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.03984761238098</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.08285284042358</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.01345729827881</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.04668879508972</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.01834464073181</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.00661540031433</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.06623697280884</t>
+    <t xml:space="preserve">2.03887009620667</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.11315298080444</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.05939507484436</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.02616357803345</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.98804461956024</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.90105581283569</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.0896954536438</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.06721496582031</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.08578562736511</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.0398473739624</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.08285307884216</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.01345705986023</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.04668951034546</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.01834440231323</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.00661587715149</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.06623721122742</t>
   </si>
   <si>
     <t xml:space="preserve">2.16202282905579</t>
@@ -1328,13 +1328,13 @@
     <t xml:space="preserve">2.24607992172241</t>
   </si>
   <si>
-    <t xml:space="preserve">2.17961621284485</t>
+    <t xml:space="preserve">2.17961668968201</t>
   </si>
   <si>
     <t xml:space="preserve">2.23826098442078</t>
   </si>
   <si>
-    <t xml:space="preserve">2.22653222084045</t>
+    <t xml:space="preserve">2.22653198242188</t>
   </si>
   <si>
     <t xml:space="preserve">2.19916439056396</t>
@@ -1346,37 +1346,37 @@
     <t xml:space="preserve">2.21773552894592</t>
   </si>
   <si>
-    <t xml:space="preserve">2.07796573638916</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.03691458702087</t>
+    <t xml:space="preserve">2.07796549797058</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.03691482543945</t>
   </si>
   <si>
     <t xml:space="preserve">2.03105115890503</t>
   </si>
   <si>
-    <t xml:space="preserve">2.09849214553833</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.08676266670227</t>
+    <t xml:space="preserve">2.09849190711975</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.08676314353943</t>
   </si>
   <si>
     <t xml:space="preserve">2.0887176990509</t>
   </si>
   <si>
-    <t xml:space="preserve">2.04766654968262</t>
+    <t xml:space="preserve">2.0476667881012</t>
   </si>
   <si>
     <t xml:space="preserve">2.05841755867004</t>
   </si>
   <si>
-    <t xml:space="preserve">2.1151077747345</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.05744028091431</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.03300499916077</t>
+    <t xml:space="preserve">2.11510801315308</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.05744051933289</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.03300523757935</t>
   </si>
   <si>
     <t xml:space="preserve">2.07307934761047</t>
@@ -1385,34 +1385,34 @@
     <t xml:space="preserve">2.07503366470337</t>
   </si>
   <si>
-    <t xml:space="preserve">2.11119747161865</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.20600628852844</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.22848653793335</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.20405125617981</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.16104578971863</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.35261702537537</t>
+    <t xml:space="preserve">2.11119771003723</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.20600652694702</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.22848677635193</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.20405149459839</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.16104531288147</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.35261726379395</t>
   </si>
   <si>
     <t xml:space="preserve">2.35066270828247</t>
   </si>
   <si>
-    <t xml:space="preserve">2.3677670955658</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.27686834335327</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.29543900489807</t>
+    <t xml:space="preserve">2.36776733398438</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.27686858177185</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.29543876647949</t>
   </si>
   <si>
     <t xml:space="preserve">2.27784562110901</t>
@@ -1427,13 +1427,13 @@
     <t xml:space="preserve">2.30179214477539</t>
   </si>
   <si>
-    <t xml:space="preserve">2.25194454193115</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.22213339805603</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.33746743202209</t>
+    <t xml:space="preserve">2.25194501876831</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.22213363647461</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.33746767044067</t>
   </si>
   <si>
     <t xml:space="preserve">2.34186625480652</t>
@@ -1442,34 +1442,34 @@
     <t xml:space="preserve">2.33209156990051</t>
   </si>
   <si>
-    <t xml:space="preserve">2.33600091934204</t>
+    <t xml:space="preserve">2.33600115776062</t>
   </si>
   <si>
     <t xml:space="preserve">2.28957486152649</t>
   </si>
   <si>
-    <t xml:space="preserve">2.37656402587891</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.37705254554749</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.38145112991333</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.37900710105896</t>
+    <t xml:space="preserve">2.37656426429749</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.37705278396606</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.38145136833191</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.37900733947754</t>
   </si>
   <si>
     <t xml:space="preserve">2.40735173225403</t>
   </si>
   <si>
-    <t xml:space="preserve">2.38731527328491</t>
+    <t xml:space="preserve">2.38731503486633</t>
   </si>
   <si>
     <t xml:space="preserve">2.20551776885986</t>
   </si>
   <si>
-    <t xml:space="preserve">2.29592776298523</t>
+    <t xml:space="preserve">2.29592752456665</t>
   </si>
   <si>
     <t xml:space="preserve">2.32720518112183</t>
@@ -1478,7 +1478,7 @@
     <t xml:space="preserve">2.25438809394836</t>
   </si>
   <si>
-    <t xml:space="preserve">2.29641652107239</t>
+    <t xml:space="preserve">2.29641675949097</t>
   </si>
   <si>
     <t xml:space="preserve">2.24461388587952</t>
@@ -1493,7 +1493,7 @@
     <t xml:space="preserve">2.28322148323059</t>
   </si>
   <si>
-    <t xml:space="preserve">2.26758313179016</t>
+    <t xml:space="preserve">2.26758289337158</t>
   </si>
   <si>
     <t xml:space="preserve">2.22359943389893</t>
@@ -1502,16 +1502,16 @@
     <t xml:space="preserve">2.22995281219482</t>
   </si>
   <si>
-    <t xml:space="preserve">2.21040487289429</t>
+    <t xml:space="preserve">2.21040511131287</t>
   </si>
   <si>
     <t xml:space="preserve">2.22555470466614</t>
   </si>
   <si>
-    <t xml:space="preserve">2.20698356628418</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.20893883705139</t>
+    <t xml:space="preserve">2.2069833278656</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.20893907546997</t>
   </si>
   <si>
     <t xml:space="preserve">2.29446148872375</t>
@@ -1523,7 +1523,7 @@
     <t xml:space="preserve">2.31156611442566</t>
   </si>
   <si>
-    <t xml:space="preserve">2.33502435684204</t>
+    <t xml:space="preserve">2.33502388000488</t>
   </si>
   <si>
     <t xml:space="preserve">2.3848717212677</t>
@@ -1538,43 +1538,43 @@
     <t xml:space="preserve">2.38829278945923</t>
   </si>
   <si>
-    <t xml:space="preserve">2.34479808807373</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.31547570228577</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.33013677597046</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.31889700889587</t>
+    <t xml:space="preserve">2.34479761123657</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.31547546386719</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.33013725280762</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.31889724731445</t>
   </si>
   <si>
     <t xml:space="preserve">2.3306257724762</t>
   </si>
   <si>
-    <t xml:space="preserve">2.31303238868713</t>
+    <t xml:space="preserve">2.31303286552429</t>
   </si>
   <si>
     <t xml:space="preserve">2.30570220947266</t>
   </si>
   <si>
-    <t xml:space="preserve">2.39660048484802</t>
+    <t xml:space="preserve">2.3966007232666</t>
   </si>
   <si>
     <t xml:space="preserve">2.40539741516113</t>
   </si>
   <si>
-    <t xml:space="preserve">2.45231342315674</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.48749971389771</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.51584410667419</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.44205021858215</t>
+    <t xml:space="preserve">2.45231318473816</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.48749947547913</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.51584386825562</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.44204998016357</t>
   </si>
   <si>
     <t xml:space="preserve">2.44253897666931</t>
@@ -1586,46 +1586,46 @@
     <t xml:space="preserve">2.30131053924561</t>
   </si>
   <si>
-    <t xml:space="preserve">2.33834767341614</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.36387276649475</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.33484363555908</t>
+    <t xml:space="preserve">2.33834743499756</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.36387300491333</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.33484387397766</t>
   </si>
   <si>
     <t xml:space="preserve">2.28779673576355</t>
   </si>
   <si>
-    <t xml:space="preserve">2.15416240692139</t>
+    <t xml:space="preserve">2.15416216850281</t>
   </si>
   <si>
     <t xml:space="preserve">2.04555368423462</t>
   </si>
   <si>
-    <t xml:space="preserve">2.05306100845337</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.0535614490509</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.21522378921509</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.15015840530396</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.07708477973938</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.07608437538147</t>
+    <t xml:space="preserve">2.05306077003479</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.05356168746948</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.21522402763367</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.15015816688538</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.07708501815796</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.07608413696289</t>
   </si>
   <si>
     <t xml:space="preserve">2.11612415313721</t>
   </si>
   <si>
-    <t xml:space="preserve">2.05906748771667</t>
+    <t xml:space="preserve">2.0590672492981</t>
   </si>
   <si>
     <t xml:space="preserve">2.14865732192993</t>
@@ -1637,22 +1637,22 @@
     <t xml:space="preserve">2.20921778678894</t>
   </si>
   <si>
-    <t xml:space="preserve">2.23624467849731</t>
+    <t xml:space="preserve">2.23624491691589</t>
   </si>
   <si>
     <t xml:space="preserve">2.1776864528656</t>
   </si>
   <si>
-    <t xml:space="preserve">2.16717553138733</t>
+    <t xml:space="preserve">2.16717529296875</t>
   </si>
   <si>
     <t xml:space="preserve">2.24074959754944</t>
   </si>
   <si>
-    <t xml:space="preserve">2.29730653762817</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.22973895072937</t>
+    <t xml:space="preserve">2.29730629920959</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.22973847389221</t>
   </si>
   <si>
     <t xml:space="preserve">2.39390325546265</t>
@@ -1664,13 +1664,13 @@
     <t xml:space="preserve">2.35786747932434</t>
   </si>
   <si>
-    <t xml:space="preserve">2.32433342933655</t>
+    <t xml:space="preserve">2.32433319091797</t>
   </si>
   <si>
     <t xml:space="preserve">2.34535479545593</t>
   </si>
   <si>
-    <t xml:space="preserve">2.35586500167847</t>
+    <t xml:space="preserve">2.35586524009705</t>
   </si>
   <si>
     <t xml:space="preserve">2.34685587882996</t>
@@ -1679,58 +1679,58 @@
     <t xml:space="preserve">2.34935879707336</t>
   </si>
   <si>
-    <t xml:space="preserve">2.34034991264343</t>
+    <t xml:space="preserve">2.34034967422485</t>
   </si>
   <si>
     <t xml:space="preserve">2.3863959312439</t>
   </si>
   <si>
-    <t xml:space="preserve">2.39440393447876</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.34785723686218</t>
+    <t xml:space="preserve">2.39440369606018</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.3478569984436</t>
   </si>
   <si>
     <t xml:space="preserve">2.30881786346436</t>
   </si>
   <si>
-    <t xml:space="preserve">2.32483386993408</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.35686612129211</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.31532502174377</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.27228164672852</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.31832718849182</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.31582450866699</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.34985852241516</t>
+    <t xml:space="preserve">2.3248336315155</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.35686588287354</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.3153247833252</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.27228140830994</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.31832766532898</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.31582474708557</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.34985899925232</t>
   </si>
   <si>
     <t xml:space="preserve">2.382892370224</t>
   </si>
   <si>
-    <t xml:space="preserve">2.35936880111694</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.392902135849</t>
+    <t xml:space="preserve">2.35936832427979</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.39290189743042</t>
   </si>
   <si>
     <t xml:space="preserve">2.38189125061035</t>
   </si>
   <si>
-    <t xml:space="preserve">2.29680585861206</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.29079937934875</t>
+    <t xml:space="preserve">2.29680609703064</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.29079961776733</t>
   </si>
   <si>
     <t xml:space="preserve">2.29230141639709</t>
@@ -1739,7 +1739,7 @@
     <t xml:space="preserve">2.31232118606567</t>
   </si>
   <si>
-    <t xml:space="preserve">2.17568397521973</t>
+    <t xml:space="preserve">2.17568421363831</t>
   </si>
   <si>
     <t xml:space="preserve">2.1511595249176</t>
@@ -1748,13 +1748,13 @@
     <t xml:space="preserve">2.12112927436829</t>
   </si>
   <si>
-    <t xml:space="preserve">2.0685760974884</t>
+    <t xml:space="preserve">2.06857633590698</t>
   </si>
   <si>
     <t xml:space="preserve">2.04905700683594</t>
   </si>
   <si>
-    <t xml:space="preserve">2.04655504226685</t>
+    <t xml:space="preserve">2.04655456542969</t>
   </si>
   <si>
     <t xml:space="preserve">2.00200963020325</t>
@@ -1763,7 +1763,7 @@
     <t xml:space="preserve">2.00251030921936</t>
   </si>
   <si>
-    <t xml:space="preserve">2.04705476760864</t>
+    <t xml:space="preserve">2.04705500602722</t>
   </si>
   <si>
     <t xml:space="preserve">2.04605460166931</t>
@@ -1775,28 +1775,28 @@
     <t xml:space="preserve">2.02503323554993</t>
   </si>
   <si>
-    <t xml:space="preserve">2.01702547073364</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.98449230194092</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.99700450897217</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.92192983627319</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.90140926837921</t>
+    <t xml:space="preserve">2.01702523231506</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.98449218273163</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.99700486660004</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.9219297170639</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.90140891075134</t>
   </si>
   <si>
     <t xml:space="preserve">1.91041803359985</t>
   </si>
   <si>
-    <t xml:space="preserve">1.98048830032349</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.06507325172424</t>
+    <t xml:space="preserve">1.9804881811142</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.06507277488708</t>
   </si>
   <si>
     <t xml:space="preserve">2.0690770149231</t>
@@ -1805,13 +1805,13 @@
     <t xml:space="preserve">2.12413215637207</t>
   </si>
   <si>
-    <t xml:space="preserve">2.11362218856812</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.11562371253967</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.10861682891846</t>
+    <t xml:space="preserve">2.11362171173096</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.11562347412109</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.10861706733704</t>
   </si>
   <si>
     <t xml:space="preserve">2.15716576576233</t>
@@ -1820,79 +1820,79 @@
     <t xml:space="preserve">2.18969821929932</t>
   </si>
   <si>
-    <t xml:space="preserve">2.16917753219604</t>
+    <t xml:space="preserve">2.16917777061462</t>
   </si>
   <si>
     <t xml:space="preserve">2.12763643264771</t>
   </si>
   <si>
-    <t xml:space="preserve">2.15216088294983</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.17868781089783</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.20070886611938</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.99600338935852</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.91742503643036</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.88389158248901</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.85936617851257</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.87087833881378</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.83684408664703</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.80631327629089</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.77027690410614</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.80881547927856</t>
+    <t xml:space="preserve">2.15216064453125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.17868733406067</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.20070910453796</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.99600386619568</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.91742515563965</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.88389134407043</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.85936629772186</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.87087798118591</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.83684420585632</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.80631351470947</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.77027702331543</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.80881583690643</t>
   </si>
   <si>
     <t xml:space="preserve">1.77478134632111</t>
   </si>
   <si>
-    <t xml:space="preserve">1.78829514980316</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.80080759525299</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.78529250621796</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.78779447078705</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.74925589561462</t>
+    <t xml:space="preserve">1.78829503059387</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.80080735683441</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.78529238700867</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.78779435157776</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.74925601482391</t>
   </si>
   <si>
     <t xml:space="preserve">1.75576281547546</t>
   </si>
   <si>
-    <t xml:space="preserve">1.69169855117798</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.65516138076782</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.60811412334442</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.64515173435211</t>
+    <t xml:space="preserve">1.69169843196869</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.65516114234924</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.60811400413513</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.64515161514282</t>
   </si>
   <si>
     <t xml:space="preserve">1.6326390504837</t>
@@ -1901,55 +1901,55 @@
     <t xml:space="preserve">1.70471143722534</t>
   </si>
   <si>
-    <t xml:space="preserve">1.69470119476318</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.68068695068359</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.69069731235504</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.75926601886749</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.69870519638062</t>
+    <t xml:space="preserve">1.69470131397247</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.68068718910217</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.69069707393646</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.75926578044891</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.69870495796204</t>
   </si>
   <si>
     <t xml:space="preserve">1.68619251251221</t>
   </si>
   <si>
-    <t xml:space="preserve">1.71672368049622</t>
+    <t xml:space="preserve">1.71672344207764</t>
   </si>
   <si>
     <t xml:space="preserve">1.72973656654358</t>
   </si>
   <si>
-    <t xml:space="preserve">1.74525189399719</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.74775469303131</t>
+    <t xml:space="preserve">1.74525213241577</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.74775457382202</t>
   </si>
   <si>
     <t xml:space="preserve">1.69670343399048</t>
   </si>
   <si>
-    <t xml:space="preserve">1.71071720123291</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.67968642711639</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.69520199298859</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.67568242549896</t>
+    <t xml:space="preserve">1.71071743965149</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.6796863079071</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.6952018737793</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.67568230628967</t>
   </si>
   <si>
     <t xml:space="preserve">1.73624265193939</t>
   </si>
   <si>
-    <t xml:space="preserve">1.74625313282013</t>
+    <t xml:space="preserve">1.74625289440155</t>
   </si>
   <si>
     <t xml:space="preserve">1.74725425243378</t>
@@ -1961,31 +1961,31 @@
     <t xml:space="preserve">1.77628314495087</t>
   </si>
   <si>
-    <t xml:space="preserve">1.79229950904846</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.80130815505981</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.88439226150513</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.85235965251923</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.88689434528351</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.82683408260345</t>
+    <t xml:space="preserve">1.79229938983917</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.8013082742691</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.88439214229584</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.85235929489136</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.88689422607422</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.82683396339417</t>
   </si>
   <si>
     <t xml:space="preserve">1.79780471324921</t>
   </si>
   <si>
-    <t xml:space="preserve">1.76727414131165</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.75025713443756</t>
+    <t xml:space="preserve">1.76727402210236</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.75025689601898</t>
   </si>
   <si>
     <t xml:space="preserve">1.74325037002563</t>
@@ -1994,34 +1994,34 @@
     <t xml:space="preserve">1.71622264385223</t>
   </si>
   <si>
-    <t xml:space="preserve">1.68268942832947</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.67468130588531</t>
+    <t xml:space="preserve">1.6826890707016</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.67468166351318</t>
   </si>
   <si>
     <t xml:space="preserve">1.70871555805206</t>
   </si>
   <si>
-    <t xml:space="preserve">1.67618238925934</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.66366982460022</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.64114761352539</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.68369054794312</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.64965617656708</t>
+    <t xml:space="preserve">1.67618250846863</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.66366994380951</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.64114773273468</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.6836906671524</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.64965641498566</t>
   </si>
   <si>
     <t xml:space="preserve">1.63864505290985</t>
   </si>
   <si>
-    <t xml:space="preserve">1.69370007514954</t>
+    <t xml:space="preserve">1.69370019435883</t>
   </si>
   <si>
     <t xml:space="preserve">1.70421099662781</t>
@@ -2030,19 +2030,19 @@
     <t xml:space="preserve">1.66667342185974</t>
   </si>
   <si>
-    <t xml:space="preserve">1.65966582298279</t>
+    <t xml:space="preserve">1.65966558456421</t>
   </si>
   <si>
     <t xml:space="preserve">1.66467106342316</t>
   </si>
   <si>
-    <t xml:space="preserve">1.63664305210114</t>
+    <t xml:space="preserve">1.63664329051971</t>
   </si>
   <si>
     <t xml:space="preserve">1.57357931137085</t>
   </si>
   <si>
-    <t xml:space="preserve">1.49900460243225</t>
+    <t xml:space="preserve">1.49900472164154</t>
   </si>
   <si>
     <t xml:space="preserve">1.53203785419464</t>
@@ -2051,40 +2051,40 @@
     <t xml:space="preserve">1.53804421424866</t>
   </si>
   <si>
-    <t xml:space="preserve">1.52903485298157</t>
+    <t xml:space="preserve">1.52903509140015</t>
   </si>
   <si>
     <t xml:space="preserve">1.53704285621643</t>
   </si>
   <si>
-    <t xml:space="preserve">1.52853429317474</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.50601172447205</t>
+    <t xml:space="preserve">1.52853453159332</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.50601160526276</t>
   </si>
   <si>
     <t xml:space="preserve">1.51051616668701</t>
   </si>
   <si>
-    <t xml:space="preserve">1.5765825510025</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.55756342411041</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.56156730651855</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.57508087158203</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.47948551177979</t>
+    <t xml:space="preserve">1.57658278942108</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.55756330490112</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.56156718730927</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.57508099079132</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.47948527336121</t>
   </si>
   <si>
     <t xml:space="preserve">1.48398947715759</t>
   </si>
   <si>
-    <t xml:space="preserve">1.48649203777313</t>
+    <t xml:space="preserve">1.48649227619171</t>
   </si>
   <si>
     <t xml:space="preserve">1.48899447917938</t>
@@ -2096,67 +2096,67 @@
     <t xml:space="preserve">1.50851440429688</t>
   </si>
   <si>
-    <t xml:space="preserve">1.64164817333221</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.70971655845642</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.69219899177551</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.68569231033325</t>
+    <t xml:space="preserve">1.64164841175079</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.70971667766571</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.69219875335693</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.68569219112396</t>
   </si>
   <si>
     <t xml:space="preserve">1.76377069950104</t>
   </si>
   <si>
-    <t xml:space="preserve">1.75676417350769</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.74174857139587</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.71372056007385</t>
+    <t xml:space="preserve">1.75676381587982</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.74174845218658</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.71372079849243</t>
   </si>
   <si>
     <t xml:space="preserve">1.73374044895172</t>
   </si>
   <si>
-    <t xml:space="preserve">1.75125825405121</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.76276957988739</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.81031739711761</t>
+    <t xml:space="preserve">1.75125849246979</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.7627694606781</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.81031727790833</t>
   </si>
   <si>
     <t xml:space="preserve">1.85085761547089</t>
   </si>
   <si>
-    <t xml:space="preserve">1.84585332870483</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.83984696865082</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.85486245155334</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.80030691623688</t>
+    <t xml:space="preserve">1.84585309028625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.83984684944153</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.85486257076263</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.80030679702759</t>
   </si>
   <si>
     <t xml:space="preserve">1.78178894519806</t>
   </si>
   <si>
-    <t xml:space="preserve">1.77077758312225</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.78128850460052</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.81732416152954</t>
+    <t xml:space="preserve">1.77077746391296</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.78128862380981</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.81732439994812</t>
   </si>
   <si>
     <t xml:space="preserve">1.8538613319397</t>
@@ -2165,55 +2165,55 @@
     <t xml:space="preserve">1.86787474155426</t>
   </si>
   <si>
-    <t xml:space="preserve">1.86837542057037</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.85185897350311</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.82633340358734</t>
+    <t xml:space="preserve">1.86837518215179</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.8518590927124</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.82633316516876</t>
   </si>
   <si>
     <t xml:space="preserve">1.8188259601593</t>
   </si>
   <si>
-    <t xml:space="preserve">1.8033105134964</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.83183896541595</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.82433152198792</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.8223295211792</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.84735429286957</t>
+    <t xml:space="preserve">1.80331039428711</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.83183908462524</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.82433176040649</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.82232916355133</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.84735453128815</t>
   </si>
   <si>
     <t xml:space="preserve">1.83334064483643</t>
   </si>
   <si>
-    <t xml:space="preserve">1.851358294487</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.85336053371429</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.8693767786026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.87037777900696</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.89990758895874</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.93544328212738</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.9864946603775</t>
+    <t xml:space="preserve">1.85135853290558</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.85336089134216</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.86937654018402</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.87037801742554</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.89990735054016</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.93544316291809</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.98649477958679</t>
   </si>
   <si>
     <t xml:space="preserve">2.02002811431885</t>
@@ -2222,55 +2222,55 @@
     <t xml:space="preserve">2.07358145713806</t>
   </si>
   <si>
-    <t xml:space="preserve">2.09360194206238</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.07308101654053</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.05506324768066</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.08859729766846</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.10561370849609</t>
+    <t xml:space="preserve">2.09360218048096</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.07308077812195</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.05506348609924</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.08859658241272</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.10561418533325</t>
   </si>
   <si>
     <t xml:space="preserve">2.11161971092224</t>
   </si>
   <si>
-    <t xml:space="preserve">2.14415311813354</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.10961771011353</t>
+    <t xml:space="preserve">2.14415240287781</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.1096179485321</t>
   </si>
   <si>
     <t xml:space="preserve">2.10311102867126</t>
   </si>
   <si>
-    <t xml:space="preserve">2.05956816673279</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.04805612564087</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.0040123462677</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.98199009895325</t>
+    <t xml:space="preserve">2.05956768989563</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.04805588722229</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.00401210784912</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.98198997974396</t>
   </si>
   <si>
     <t xml:space="preserve">1.95195984840393</t>
   </si>
   <si>
-    <t xml:space="preserve">1.96947741508484</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.93494284152985</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.97848665714264</t>
+    <t xml:space="preserve">1.96947729587555</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.93494248390198</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.97848653793335</t>
   </si>
   <si>
     <t xml:space="preserve">1.92558372020721</t>
@@ -2279,34 +2279,34 @@
     <t xml:space="preserve">1.87486886978149</t>
   </si>
   <si>
-    <t xml:space="preserve">1.83502221107483</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.81070065498352</t>
+    <t xml:space="preserve">1.83502209186554</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.8107008934021</t>
   </si>
   <si>
     <t xml:space="preserve">1.82933044433594</t>
   </si>
   <si>
-    <t xml:space="preserve">1.78068614006042</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.78172063827515</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.77240645885468</t>
+    <t xml:space="preserve">1.78068625926971</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.78172075748444</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.77240633964539</t>
   </si>
   <si>
     <t xml:space="preserve">1.75998616218567</t>
   </si>
   <si>
-    <t xml:space="preserve">1.75118863582611</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.73721611499786</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.76774883270264</t>
+    <t xml:space="preserve">1.75118887424469</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.73721623420715</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.76774907112122</t>
   </si>
   <si>
     <t xml:space="preserve">1.73566436767578</t>
@@ -2318,19 +2318,19 @@
     <t xml:space="preserve">1.71185946464539</t>
   </si>
   <si>
-    <t xml:space="preserve">1.76567888259888</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.78223848342896</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.76205658912659</t>
+    <t xml:space="preserve">1.7656786441803</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.78223836421967</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.7620564699173</t>
   </si>
   <si>
     <t xml:space="preserve">1.78327322006226</t>
   </si>
   <si>
-    <t xml:space="preserve">1.77706301212311</t>
+    <t xml:space="preserve">1.77706289291382</t>
   </si>
   <si>
     <t xml:space="preserve">1.79051780700684</t>
@@ -2339,22 +2339,22 @@
     <t xml:space="preserve">1.8308824300766</t>
   </si>
   <si>
-    <t xml:space="preserve">1.86503756046295</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.86296713352203</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.89453411102295</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.87383484840393</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.87279939651489</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.88366651535034</t>
+    <t xml:space="preserve">1.86503720283508</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.86296701431274</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.89453387260437</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.87383449077606</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.87279951572418</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.88366639614105</t>
   </si>
   <si>
     <t xml:space="preserve">1.85416972637177</t>
@@ -2363,145 +2363,145 @@
     <t xml:space="preserve">1.84433746337891</t>
   </si>
   <si>
-    <t xml:space="preserve">1.88211441040039</t>
+    <t xml:space="preserve">1.88211464881897</t>
   </si>
   <si>
     <t xml:space="preserve">1.95559799671173</t>
   </si>
   <si>
-    <t xml:space="preserve">2.01252198219299</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.01666164398193</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.99854934215546</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.99026989936829</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.97370994091034</t>
+    <t xml:space="preserve">2.01252150535583</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.01666188240051</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.99854922294617</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.990269780159</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.97371029853821</t>
   </si>
   <si>
     <t xml:space="preserve">1.98250758647919</t>
   </si>
   <si>
-    <t xml:space="preserve">1.96853542327881</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.99647998809814</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.96439552307129</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.93955600261688</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.94576549530029</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.93541598320007</t>
+    <t xml:space="preserve">1.96853482723236</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.99647974967957</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.96439504623413</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.93955612182617</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.94576561450958</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.93541634082794</t>
   </si>
   <si>
     <t xml:space="preserve">1.88625431060791</t>
   </si>
   <si>
-    <t xml:space="preserve">1.87072932720184</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.85106515884399</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.82570707798004</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.7542941570282</t>
+    <t xml:space="preserve">1.87072920799255</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.8510650396347</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.82570743560791</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.75429403781891</t>
   </si>
   <si>
     <t xml:space="preserve">1.7434264421463</t>
   </si>
   <si>
-    <t xml:space="preserve">1.79000115394592</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.76257383823395</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.78948354721069</t>
+    <t xml:space="preserve">1.79000103473663</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.76257395744324</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.78948366641998</t>
   </si>
   <si>
     <t xml:space="preserve">1.76464343070984</t>
   </si>
   <si>
-    <t xml:space="preserve">1.79828083515167</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.65597069263458</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.62078142166138</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.63941121101379</t>
+    <t xml:space="preserve">1.79828071594238</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.65597081184387</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.62078130245209</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.63941133022308</t>
   </si>
   <si>
     <t xml:space="preserve">1.55868220329285</t>
   </si>
   <si>
-    <t xml:space="preserve">1.59283673763275</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.60887944698334</t>
+    <t xml:space="preserve">1.59283661842346</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.60887932777405</t>
   </si>
   <si>
     <t xml:space="preserve">1.55764722824097</t>
   </si>
   <si>
-    <t xml:space="preserve">1.58455681800842</t>
+    <t xml:space="preserve">1.58455669879913</t>
   </si>
   <si>
     <t xml:space="preserve">1.59076702594757</t>
   </si>
   <si>
-    <t xml:space="preserve">1.57731199264526</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.58817923069</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.66011047363281</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.64872610569</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.68132758140564</t>
+    <t xml:space="preserve">1.57731223106384</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.58817911148071</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.6601105928421</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.64872634410858</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.68132781982422</t>
   </si>
   <si>
     <t xml:space="preserve">1.66787278652191</t>
   </si>
   <si>
-    <t xml:space="preserve">1.67149531841278</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.69943988323212</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.71651697158813</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.72169196605682</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.72997188568115</t>
+    <t xml:space="preserve">1.6714950799942</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.69943976402283</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.71651709079742</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.72169208526611</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.72997200489044</t>
   </si>
   <si>
     <t xml:space="preserve">1.7884486913681</t>
   </si>
   <si>
-    <t xml:space="preserve">1.8086302280426</t>
+    <t xml:space="preserve">1.80863046646118</t>
   </si>
   <si>
     <t xml:space="preserve">1.79103577136993</t>
@@ -2510,13 +2510,13 @@
     <t xml:space="preserve">1.81846272945404</t>
   </si>
   <si>
-    <t xml:space="preserve">1.86451971530914</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.87331712245941</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.81225228309631</t>
+    <t xml:space="preserve">1.86451959609985</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.87331700325012</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.8122524023056</t>
   </si>
   <si>
     <t xml:space="preserve">1.8231201171875</t>
@@ -2528,52 +2528,52 @@
     <t xml:space="preserve">1.84589004516602</t>
   </si>
   <si>
-    <t xml:space="preserve">1.8179452419281</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.79879856109619</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.80966556072235</t>
+    <t xml:space="preserve">1.81794488430023</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.7987984418869</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.80966532230377</t>
   </si>
   <si>
     <t xml:space="preserve">1.83295261859894</t>
   </si>
   <si>
-    <t xml:space="preserve">1.80500793457031</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.81587553024292</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.79931509494781</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.80552554130554</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.81639349460602</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.88263201713562</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.90333151817322</t>
+    <t xml:space="preserve">1.80500781536102</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.81587541103363</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.7993152141571</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.80552542209625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.81639325618744</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.88263189792633</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.90333139896393</t>
   </si>
   <si>
     <t xml:space="preserve">1.94421327114105</t>
   </si>
   <si>
-    <t xml:space="preserve">1.97267520427704</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.02649426460266</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.07927846908569</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.10204815864563</t>
+    <t xml:space="preserve">1.97267508506775</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.02649450302124</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.07927823066711</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.10204792022705</t>
   </si>
   <si>
     <t xml:space="preserve">2.12999224662781</t>
@@ -2585,22 +2585,22 @@
     <t xml:space="preserve">2.08962845802307</t>
   </si>
   <si>
-    <t xml:space="preserve">2.10515284538269</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.10567021369934</t>
+    <t xml:space="preserve">2.10515260696411</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.10567045211792</t>
   </si>
   <si>
     <t xml:space="preserve">2.06582355499268</t>
   </si>
   <si>
-    <t xml:space="preserve">2.07358551025391</t>
+    <t xml:space="preserve">2.07358574867249</t>
   </si>
   <si>
     <t xml:space="preserve">2.06996321678162</t>
   </si>
   <si>
-    <t xml:space="preserve">2.1367199420929</t>
+    <t xml:space="preserve">2.13671970367432</t>
   </si>
   <si>
     <t xml:space="preserve">2.16155910491943</t>
@@ -2609,13 +2609,13 @@
     <t xml:space="preserve">2.17604899406433</t>
   </si>
   <si>
-    <t xml:space="preserve">2.20761609077454</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.18329334259033</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.21951818466187</t>
+    <t xml:space="preserve">2.20761632919312</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.18329381942749</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.21951794624329</t>
   </si>
   <si>
     <t xml:space="preserve">2.23556017875671</t>
@@ -2630,25 +2630,25 @@
     <t xml:space="preserve">2.25936508178711</t>
   </si>
   <si>
-    <t xml:space="preserve">2.28679203987122</t>
+    <t xml:space="preserve">2.28679227828979</t>
   </si>
   <si>
     <t xml:space="preserve">2.35303115844727</t>
   </si>
   <si>
-    <t xml:space="preserve">2.38459777832031</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.37114310264587</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.31421971321106</t>
+    <t xml:space="preserve">2.38459825515747</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.37114334106445</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.31421947479248</t>
   </si>
   <si>
     <t xml:space="preserve">2.32715654373169</t>
   </si>
   <si>
-    <t xml:space="preserve">2.32146406173706</t>
+    <t xml:space="preserve">2.32146430015564</t>
   </si>
   <si>
     <t xml:space="preserve">2.30076456069946</t>
@@ -2657,7 +2657,7 @@
     <t xml:space="preserve">2.27074956893921</t>
   </si>
   <si>
-    <t xml:space="preserve">2.27437305450439</t>
+    <t xml:space="preserve">2.27437281608582</t>
   </si>
   <si>
     <t xml:space="preserve">2.2277979850769</t>
@@ -2669,10 +2669,10 @@
     <t xml:space="preserve">2.27178454399109</t>
   </si>
   <si>
-    <t xml:space="preserve">2.28368759155273</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.30593943595886</t>
+    <t xml:space="preserve">2.28368711471558</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.30593967437744</t>
   </si>
   <si>
     <t xml:space="preserve">2.27851247787476</t>
@@ -2684,76 +2684,76 @@
     <t xml:space="preserve">2.299729347229</t>
   </si>
   <si>
-    <t xml:space="preserve">2.33026123046875</t>
+    <t xml:space="preserve">2.33026146888733</t>
   </si>
   <si>
     <t xml:space="preserve">2.31318426132202</t>
   </si>
   <si>
-    <t xml:space="preserve">2.34216356277466</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.3597583770752</t>
+    <t xml:space="preserve">2.34216380119324</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.35975813865662</t>
   </si>
   <si>
     <t xml:space="preserve">2.33698844909668</t>
   </si>
   <si>
-    <t xml:space="preserve">2.33388352394104</t>
+    <t xml:space="preserve">2.33388376235962</t>
   </si>
   <si>
     <t xml:space="preserve">2.30490446090698</t>
   </si>
   <si>
-    <t xml:space="preserve">2.31991100311279</t>
+    <t xml:space="preserve">2.31991124153137</t>
   </si>
   <si>
     <t xml:space="preserve">2.3778703212738</t>
   </si>
   <si>
-    <t xml:space="preserve">2.37631821632385</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.3276743888855</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.33440089225769</t>
+    <t xml:space="preserve">2.37631869316101</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.32767391204834</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.33440113067627</t>
   </si>
   <si>
     <t xml:space="preserve">2.35665345191956</t>
   </si>
   <si>
-    <t xml:space="preserve">2.38873767852783</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.39080739021301</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.38045859336853</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.38822031021118</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.36700367927551</t>
+    <t xml:space="preserve">2.38873815536499</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.39080762863159</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.38045811653137</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.38822054862976</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.36700320243835</t>
   </si>
   <si>
     <t xml:space="preserve">2.36079335212708</t>
   </si>
   <si>
-    <t xml:space="preserve">2.37942314147949</t>
+    <t xml:space="preserve">2.37942337989807</t>
   </si>
   <si>
     <t xml:space="preserve">2.36493301391602</t>
   </si>
   <si>
-    <t xml:space="preserve">2.39494776725769</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.30749154090881</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.30800914764404</t>
+    <t xml:space="preserve">2.39494705200195</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.30749177932739</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.3080096244812</t>
   </si>
   <si>
     <t xml:space="preserve">2.29351925849915</t>
@@ -2774,52 +2774,52 @@
     <t xml:space="preserve">2.19157338142395</t>
   </si>
   <si>
-    <t xml:space="preserve">2.24073529243469</t>
+    <t xml:space="preserve">2.24073505401611</t>
   </si>
   <si>
     <t xml:space="preserve">2.26505756378174</t>
   </si>
   <si>
-    <t xml:space="preserve">2.24384069442749</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.25263810157776</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.26298713684082</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.3463032245636</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.32612156867981</t>
+    <t xml:space="preserve">2.24384021759033</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.25263786315918</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.2629873752594</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.34630346298218</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.32612180709839</t>
   </si>
   <si>
     <t xml:space="preserve">2.40322709083557</t>
   </si>
   <si>
-    <t xml:space="preserve">2.14292907714844</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.13568472862244</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.17035627365112</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.10722351074219</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.98509442806244</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.98716533184052</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.03115153312683</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.95508050918579</t>
+    <t xml:space="preserve">2.14292931556702</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.13568449020386</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.1703565120697</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.10722327232361</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.98509454727173</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.98716521263123</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.03115177154541</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.9550803899765</t>
   </si>
   <si>
     <t xml:space="preserve">1.86244940757751</t>
@@ -2828,34 +2828,34 @@
     <t xml:space="preserve">1.72065675258636</t>
   </si>
   <si>
-    <t xml:space="preserve">1.67615246772766</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.61508882045746</t>
+    <t xml:space="preserve">1.67615234851837</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.61508870124817</t>
   </si>
   <si>
     <t xml:space="preserve">1.58093452453613</t>
   </si>
   <si>
-    <t xml:space="preserve">1.36617600917816</t>
+    <t xml:space="preserve">1.36617588996887</t>
   </si>
   <si>
     <t xml:space="preserve">1.2999370098114</t>
   </si>
   <si>
-    <t xml:space="preserve">1.30304181575775</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.07172310352325</t>
+    <t xml:space="preserve">1.30304193496704</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.07172298431396</t>
   </si>
   <si>
     <t xml:space="preserve">1.31183922290802</t>
   </si>
   <si>
-    <t xml:space="preserve">1.21144604682922</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.2073061466217</t>
+    <t xml:space="preserve">1.21144616603851</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.20730626583099</t>
   </si>
   <si>
     <t xml:space="preserve">1.17522144317627</t>
@@ -2864,28 +2864,28 @@
     <t xml:space="preserve">1.19333386421204</t>
   </si>
   <si>
-    <t xml:space="preserve">1.33253848552704</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.51935303211212</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.55712974071503</t>
+    <t xml:space="preserve">1.33253860473633</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.51935315132141</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.55712962150574</t>
   </si>
   <si>
     <t xml:space="preserve">1.53280782699585</t>
   </si>
   <si>
-    <t xml:space="preserve">1.50279355049133</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.40602290630341</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.40550529956818</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.44897425174713</t>
+    <t xml:space="preserve">1.50279343128204</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.40602278709412</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.40550518035889</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.44897437095642</t>
   </si>
   <si>
     <t xml:space="preserve">1.40705740451813</t>
@@ -2894,7 +2894,7 @@
     <t xml:space="preserve">1.39567267894745</t>
   </si>
   <si>
-    <t xml:space="preserve">1.38894486427307</t>
+    <t xml:space="preserve">1.38894474506378</t>
   </si>
   <si>
     <t xml:space="preserve">1.41585457324982</t>
@@ -2903,40 +2903,40 @@
     <t xml:space="preserve">1.41016268730164</t>
   </si>
   <si>
-    <t xml:space="preserve">1.34081840515137</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.35375559329987</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.29320919513702</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.1979912519455</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.1462424993515</t>
+    <t xml:space="preserve">1.34081828594208</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.35375547409058</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.29320931434631</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.19799137115479</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.14624238014221</t>
   </si>
   <si>
     <t xml:space="preserve">1.15814447402954</t>
   </si>
   <si>
-    <t xml:space="preserve">1.15917956829071</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.10898280143738</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.10743010044098</t>
+    <t xml:space="preserve">1.15917944908142</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.10898268222809</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.10742998123169</t>
   </si>
   <si>
     <t xml:space="preserve">1.14468967914581</t>
   </si>
   <si>
-    <t xml:space="preserve">1.09708070755005</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.12813019752502</t>
+    <t xml:space="preserve">1.09708058834076</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.12813031673431</t>
   </si>
   <si>
     <t xml:space="preserve">1.19902646541595</t>
@@ -2951,13 +2951,13 @@
     <t xml:space="preserve">1.140549659729</t>
   </si>
   <si>
-    <t xml:space="preserve">1.13847935199738</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.12502467632294</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.10639560222626</t>
+    <t xml:space="preserve">1.13847947120667</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.12502479553223</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.10639572143555</t>
   </si>
   <si>
     <t xml:space="preserve">1.09397506713867</t>
@@ -2969,28 +2969,28 @@
     <t xml:space="preserve">1.05050599575043</t>
   </si>
   <si>
-    <t xml:space="preserve">1.04222631454468</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.03860402107239</t>
+    <t xml:space="preserve">1.04222619533539</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.0386039018631</t>
   </si>
   <si>
     <t xml:space="preserve">1.0803165435791</t>
   </si>
   <si>
-    <t xml:space="preserve">1.02012324333191</t>
+    <t xml:space="preserve">1.02012348175049</t>
   </si>
   <si>
     <t xml:space="preserve">1.0024346113205</t>
   </si>
   <si>
-    <t xml:space="preserve">0.983425796031952</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.984218418598175</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.986858129501343</t>
+    <t xml:space="preserve">0.983425855636597</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.984218299388885</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.986858189105988</t>
   </si>
   <si>
     <t xml:space="preserve">1.08982086181641</t>
@@ -2999,7 +2999,7 @@
     <t xml:space="preserve">1.12942171096802</t>
   </si>
   <si>
-    <t xml:space="preserve">1.17483103275299</t>
+    <t xml:space="preserve">1.17483115196228</t>
   </si>
   <si>
     <t xml:space="preserve">1.13364672660828</t>
@@ -3008,22 +3008,22 @@
     <t xml:space="preserve">1.16163086891174</t>
   </si>
   <si>
-    <t xml:space="preserve">1.1827517747879</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.22076845169067</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.22129666805267</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.34010004997253</t>
+    <t xml:space="preserve">1.18275189399719</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.22076857089996</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.22129654884338</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.34010016918182</t>
   </si>
   <si>
     <t xml:space="preserve">1.40504550933838</t>
   </si>
   <si>
-    <t xml:space="preserve">1.38498139381409</t>
+    <t xml:space="preserve">1.3849812746048</t>
   </si>
   <si>
     <t xml:space="preserve">1.31528294086456</t>
@@ -3032,13 +3032,13 @@
     <t xml:space="preserve">1.23132908344269</t>
   </si>
   <si>
-    <t xml:space="preserve">1.20334410667419</t>
+    <t xml:space="preserve">1.20334422588348</t>
   </si>
   <si>
     <t xml:space="preserve">1.21443283557892</t>
   </si>
   <si>
-    <t xml:space="preserve">1.29416286945343</t>
+    <t xml:space="preserve">1.29416263103485</t>
   </si>
   <si>
     <t xml:space="preserve">1.26829016208649</t>
@@ -3047,13 +3047,13 @@
     <t xml:space="preserve">1.2334406375885</t>
   </si>
   <si>
-    <t xml:space="preserve">1.24611377716064</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.19806396961212</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.22763311862946</t>
+    <t xml:space="preserve">1.24611365795135</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.19806373119354</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.22763323783875</t>
   </si>
   <si>
     <t xml:space="preserve">1.16532671451569</t>
@@ -3062,31 +3062,31 @@
     <t xml:space="preserve">1.17430293560028</t>
   </si>
   <si>
-    <t xml:space="preserve">1.14737415313721</t>
+    <t xml:space="preserve">1.1473742723465</t>
   </si>
   <si>
     <t xml:space="preserve">1.16796731948853</t>
   </si>
   <si>
-    <t xml:space="preserve">1.14526271820068</t>
+    <t xml:space="preserve">1.14526259899139</t>
   </si>
   <si>
     <t xml:space="preserve">1.15371084213257</t>
   </si>
   <si>
-    <t xml:space="preserve">1.14843046665192</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.18327915668488</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.17007887363434</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.164799451828</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.13417387008667</t>
+    <t xml:space="preserve">1.14843034744263</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.18327927589417</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.17007899284363</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.16479957103729</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.13417398929596</t>
   </si>
   <si>
     <t xml:space="preserve">1.19120001792908</t>
@@ -3095,46 +3095,46 @@
     <t xml:space="preserve">1.31581115722656</t>
   </si>
   <si>
-    <t xml:space="preserve">1.31686735153198</t>
+    <t xml:space="preserve">1.31686747074127</t>
   </si>
   <si>
     <t xml:space="preserve">1.32373118400574</t>
   </si>
   <si>
-    <t xml:space="preserve">1.34115564823151</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.31317126750946</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.35858070850372</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.34590768814087</t>
+    <t xml:space="preserve">1.34115552902222</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.31317138671875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.35858082771301</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.34590780735016</t>
   </si>
   <si>
     <t xml:space="preserve">1.29944288730621</t>
   </si>
   <si>
-    <t xml:space="preserve">1.27990627288818</t>
+    <t xml:space="preserve">1.27990639209747</t>
   </si>
   <si>
     <t xml:space="preserve">1.22657680511475</t>
   </si>
   <si>
-    <t xml:space="preserve">1.23027300834656</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.19067203998566</t>
+    <t xml:space="preserve">1.23027276992798</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.19067180156708</t>
   </si>
   <si>
     <t xml:space="preserve">1.1758873462677</t>
   </si>
   <si>
-    <t xml:space="preserve">1.12572598457336</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.0966854095459</t>
+    <t xml:space="preserve">1.12572586536407</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.09668552875519</t>
   </si>
   <si>
     <t xml:space="preserve">1.08242893218994</t>
@@ -3146,7 +3146,7 @@
     <t xml:space="preserve">1.23555314540863</t>
   </si>
   <si>
-    <t xml:space="preserve">1.25139307975769</t>
+    <t xml:space="preserve">1.25139319896698</t>
   </si>
   <si>
     <t xml:space="preserve">1.2524493932724</t>
@@ -3155,10 +3155,10 @@
     <t xml:space="preserve">1.22288084030151</t>
   </si>
   <si>
-    <t xml:space="preserve">1.22604870796204</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.23713743686676</t>
+    <t xml:space="preserve">1.22604858875275</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.23713731765747</t>
   </si>
   <si>
     <t xml:space="preserve">1.21707248687744</t>
@@ -3170,7 +3170,7 @@
     <t xml:space="preserve">1.24030530452728</t>
   </si>
   <si>
-    <t xml:space="preserve">1.23977708816528</t>
+    <t xml:space="preserve">1.23977720737457</t>
   </si>
   <si>
     <t xml:space="preserve">1.23080098628998</t>
@@ -3179,13 +3179,13 @@
     <t xml:space="preserve">1.25667345523834</t>
   </si>
   <si>
-    <t xml:space="preserve">1.21495997905731</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.18222379684448</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.17905497550964</t>
+    <t xml:space="preserve">1.21496021747589</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.18222367763519</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.17905509471893</t>
   </si>
   <si>
     <t xml:space="preserve">1.14156675338745</t>
@@ -3194,106 +3194,106 @@
     <t xml:space="preserve">1.15265452861786</t>
   </si>
   <si>
-    <t xml:space="preserve">1.1468471288681</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.11569321155548</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.13100624084473</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.16004705429077</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.15687847137451</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.15635049343109</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.14209473133087</t>
+    <t xml:space="preserve">1.14684689044952</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.11569333076477</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.13100612163544</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.16004717350006</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.1568785905838</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.15635061264038</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.14209461212158</t>
   </si>
   <si>
     <t xml:space="preserve">1.15054285526276</t>
   </si>
   <si>
-    <t xml:space="preserve">1.14051043987274</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.09404504299164</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.06447649002075</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.06658804416656</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.03490722179413</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.03226733207703</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.0591961145401</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.02962791919708</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.04969191551208</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.02857136726379</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.00058650970459</t>
+    <t xml:space="preserve">1.14051055908203</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.09404516220093</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.06447660923004</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.06658828258514</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.03490734100342</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.03226745128632</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.05919623374939</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.0296276807785</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.0496917963028</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.02857160568237</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.00058662891388</t>
   </si>
   <si>
     <t xml:space="preserve">0.926720380783081</t>
   </si>
   <si>
-    <t xml:space="preserve">0.965333759784698</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.924770295619965</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.933351039886475</t>
+    <t xml:space="preserve">0.965333700180054</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.92477023601532</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.933350920677185</t>
   </si>
   <si>
     <t xml:space="preserve">0.938031435012817</t>
   </si>
   <si>
-    <t xml:space="preserve">0.914239287376404</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.867435276508331</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.870945632457733</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.866265177726746</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.936471223831177</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.923990190029144</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.01408791542053</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.949342489242554</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.925550282001495</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.938811480998993</t>
+    <t xml:space="preserve">0.914239346981049</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.867435336112976</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.870945453643799</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.866265118122101</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.936471283435822</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.923990249633789</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.01408803462982</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.949342310428619</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.925550401210785</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.938811540603638</t>
   </si>
   <si>
     <t xml:space="preserve">0.929450631141663</t>
@@ -3302,16 +3302,16 @@
     <t xml:space="preserve">0.871335566043854</t>
   </si>
   <si>
-    <t xml:space="preserve">0.808540165424347</t>
+    <t xml:space="preserve">0.808540046215057</t>
   </si>
   <si>
     <t xml:space="preserve">0.798399269580841</t>
   </si>
   <si>
-    <t xml:space="preserve">0.793328881263733</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.822971403598785</t>
+    <t xml:space="preserve">0.793328762054443</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.82297146320343</t>
   </si>
   <si>
     <t xml:space="preserve">0.844033241271973</t>
@@ -3320,28 +3320,28 @@
     <t xml:space="preserve">0.863534927368164</t>
   </si>
   <si>
-    <t xml:space="preserve">0.844813287258148</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.817510962486267</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.939201593399048</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.931400895118713</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.966503858566284</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.02929925918579</t>
+    <t xml:space="preserve">0.844813227653503</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.817510843276978</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.939201474189758</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.931400775909424</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.966503798961639</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.02929937839508</t>
   </si>
   <si>
     <t xml:space="preserve">1.04139041900635</t>
   </si>
   <si>
-    <t xml:space="preserve">1.10496580600739</t>
+    <t xml:space="preserve">1.10496592521667</t>
   </si>
   <si>
     <t xml:space="preserve">1.11198651790619</t>
@@ -3350,13 +3350,13 @@
     <t xml:space="preserve">1.15801048278809</t>
   </si>
   <si>
-    <t xml:space="preserve">1.18258285522461</t>
+    <t xml:space="preserve">1.18258261680603</t>
   </si>
   <si>
     <t xml:space="preserve">1.18531286716461</t>
   </si>
   <si>
-    <t xml:space="preserve">1.18921315670013</t>
+    <t xml:space="preserve">1.18921303749084</t>
   </si>
   <si>
     <t xml:space="preserve">1.1584005355835</t>
@@ -3365,7 +3365,7 @@
     <t xml:space="preserve">1.17868220806122</t>
   </si>
   <si>
-    <t xml:space="preserve">1.14279913902283</t>
+    <t xml:space="preserve">1.14279925823212</t>
   </si>
   <si>
     <t xml:space="preserve">1.15918052196503</t>
@@ -3374,28 +3374,28 @@
     <t xml:space="preserve">1.14669942855835</t>
   </si>
   <si>
-    <t xml:space="preserve">1.15723049640656</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.14864957332611</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.14240920543671</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.15020966529846</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.18336260318756</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.14435946941376</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.1416289806366</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.15254998207092</t>
+    <t xml:space="preserve">1.15723037719727</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.1486496925354</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.14240896701813</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.15020978450775</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.18336248397827</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.14435935020447</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.14162909984589</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.15254986286163</t>
   </si>
   <si>
     <t xml:space="preserve">1.13694870471954</t>
@@ -3413,19 +3413,19 @@
     <t xml:space="preserve">1.11159634590149</t>
   </si>
   <si>
-    <t xml:space="preserve">1.15450024604797</t>
+    <t xml:space="preserve">1.15450012683868</t>
   </si>
   <si>
     <t xml:space="preserve">1.17010140419006</t>
   </si>
   <si>
-    <t xml:space="preserve">1.16191077232361</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.14045882225037</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.14981973171234</t>
+    <t xml:space="preserve">1.16191101074219</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.14045906066895</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.14981985092163</t>
   </si>
   <si>
     <t xml:space="preserve">1.2110550403595</t>
@@ -3434,10 +3434,10 @@
     <t xml:space="preserve">1.28594160079956</t>
   </si>
   <si>
-    <t xml:space="preserve">1.27151024341583</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.29764246940613</t>
+    <t xml:space="preserve">1.27151048183441</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.29764270782471</t>
   </si>
   <si>
     <t xml:space="preserve">1.29959273338318</t>
@@ -3446,13 +3446,13 @@
     <t xml:space="preserve">1.28360140323639</t>
   </si>
   <si>
-    <t xml:space="preserve">1.26331973075867</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.25512897968292</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.28282129764557</t>
+    <t xml:space="preserve">1.26331961154938</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.25512886047363</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.28282117843628</t>
   </si>
   <si>
     <t xml:space="preserve">1.26448976993561</t>
@@ -3461,10 +3461,10 @@
     <t xml:space="preserve">1.28633165359497</t>
   </si>
   <si>
-    <t xml:space="preserve">1.26370966434479</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.22899651527405</t>
+    <t xml:space="preserve">1.2637095451355</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.22899663448334</t>
   </si>
   <si>
     <t xml:space="preserve">1.19194340705872</t>
@@ -3476,34 +3476,34 @@
     <t xml:space="preserve">1.18882322311401</t>
   </si>
   <si>
-    <t xml:space="preserve">1.21573567390442</t>
+    <t xml:space="preserve">1.21573543548584</t>
   </si>
   <si>
     <t xml:space="preserve">1.19584369659424</t>
   </si>
   <si>
-    <t xml:space="preserve">1.20442461967468</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.32455492019653</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.38696038722992</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.48953938484192</t>
+    <t xml:space="preserve">1.20442450046539</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.32455480098724</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.38696026802063</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.48953926563263</t>
   </si>
   <si>
     <t xml:space="preserve">1.45833659172058</t>
   </si>
   <si>
-    <t xml:space="preserve">1.48212862014771</t>
+    <t xml:space="preserve">1.48212850093842</t>
   </si>
   <si>
     <t xml:space="preserve">1.45521628856659</t>
   </si>
   <si>
-    <t xml:space="preserve">1.45248603820801</t>
+    <t xml:space="preserve">1.4524861574173</t>
   </si>
   <si>
     <t xml:space="preserve">1.46886742115021</t>
@@ -3512,7 +3512,7 @@
     <t xml:space="preserve">1.44741559028625</t>
   </si>
   <si>
-    <t xml:space="preserve">1.42089319229126</t>
+    <t xml:space="preserve">1.42089331150055</t>
   </si>
   <si>
     <t xml:space="preserve">1.39632105827332</t>
@@ -3521,7 +3521,7 @@
     <t xml:space="preserve">1.45170593261719</t>
   </si>
   <si>
-    <t xml:space="preserve">1.43064427375793</t>
+    <t xml:space="preserve">1.43064403533936</t>
   </si>
   <si>
     <t xml:space="preserve">1.43025410175323</t>
@@ -3530,46 +3530,46 @@
     <t xml:space="preserve">1.45326614379883</t>
   </si>
   <si>
-    <t xml:space="preserve">1.41543281078339</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.45287597179413</t>
+    <t xml:space="preserve">1.41543292999268</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.45287609100342</t>
   </si>
   <si>
     <t xml:space="preserve">1.43766486644745</t>
   </si>
   <si>
-    <t xml:space="preserve">1.44624543190002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.50709092617035</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.54765439033508</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.5410236120224</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.52815270423889</t>
+    <t xml:space="preserve">1.44624555110931</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.50709080696106</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.54765427112579</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.54102373123169</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.5281525850296</t>
   </si>
   <si>
     <t xml:space="preserve">1.53673350811005</t>
   </si>
   <si>
-    <t xml:space="preserve">1.51879191398621</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.55233466625214</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.6006988286972</t>
+    <t xml:space="preserve">1.51879179477692</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.55233478546143</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.60069894790649</t>
   </si>
   <si>
     <t xml:space="preserve">1.58899784088135</t>
   </si>
   <si>
-    <t xml:space="preserve">1.52581250667572</t>
+    <t xml:space="preserve">1.52581238746643</t>
   </si>
   <si>
     <t xml:space="preserve">1.48758912086487</t>
@@ -3581,28 +3581,28 @@
     <t xml:space="preserve">1.50670075416565</t>
   </si>
   <si>
-    <t xml:space="preserve">1.49538969993591</t>
+    <t xml:space="preserve">1.4953898191452</t>
   </si>
   <si>
     <t xml:space="preserve">1.49616992473602</t>
   </si>
   <si>
-    <t xml:space="preserve">1.48056840896606</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.48173856735229</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.46379709243774</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.48329854011536</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.48134851455688</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.47510814666748</t>
+    <t xml:space="preserve">1.48056852817535</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.48173844814301</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.46379721164703</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.48329889774323</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.48134863376617</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.47510802745819</t>
   </si>
   <si>
     <t xml:space="preserve">1.45014572143555</t>
@@ -3620,10 +3620,10 @@
     <t xml:space="preserve">1.47666811943054</t>
   </si>
   <si>
-    <t xml:space="preserve">1.4754980802536</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.52191197872162</t>
+    <t xml:space="preserve">1.47549796104431</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.5219122171402</t>
   </si>
   <si>
     <t xml:space="preserve">1.44000482559204</t>
@@ -3632,34 +3632,34 @@
     <t xml:space="preserve">1.40802216529846</t>
   </si>
   <si>
-    <t xml:space="preserve">1.41036224365234</t>
+    <t xml:space="preserve">1.41036236286163</t>
   </si>
   <si>
     <t xml:space="preserve">1.41738295555115</t>
   </si>
   <si>
-    <t xml:space="preserve">1.46106672286987</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.44507539272308</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.47744834423065</t>
+    <t xml:space="preserve">1.46106684207916</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.44507527351379</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.47744822502136</t>
   </si>
   <si>
     <t xml:space="preserve">1.46847748756409</t>
   </si>
   <si>
-    <t xml:space="preserve">1.4622368812561</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.479008436203</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.50787079334259</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.50046014785767</t>
+    <t xml:space="preserve">1.46223676204681</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.47900855541229</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.5078706741333</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.50046026706696</t>
   </si>
   <si>
     <t xml:space="preserve">1.55857539176941</t>
@@ -3668,49 +3668,49 @@
     <t xml:space="preserve">1.57261645793915</t>
   </si>
   <si>
-    <t xml:space="preserve">1.54921436309814</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.56403565406799</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.56481575965881</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.57183647155762</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.54219365119934</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.52776265144348</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.55584514141083</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.6557469367981</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.69236445426941</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.61116909980774</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.63186621665955</t>
+    <t xml:space="preserve">1.54921424388885</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.56403589248657</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.5648158788681</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.57183659076691</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.54219388961792</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.52776253223419</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.55584502220154</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.65574717521667</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.6923645734787</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.61116933822632</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.63186585903168</t>
   </si>
   <si>
     <t xml:space="preserve">1.62151765823364</t>
   </si>
   <si>
-    <t xml:space="preserve">1.61435353755951</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.61912965774536</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.62708985805511</t>
+    <t xml:space="preserve">1.61435341835022</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.61912953853607</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.6270899772644</t>
   </si>
   <si>
     <t xml:space="preserve">1.61992573738098</t>
@@ -3719,7 +3719,7 @@
     <t xml:space="preserve">1.60957741737366</t>
   </si>
   <si>
-    <t xml:space="preserve">1.63107013702393</t>
+    <t xml:space="preserve">1.63107025623322</t>
   </si>
   <si>
     <t xml:space="preserve">1.62072169780731</t>
@@ -3743,13 +3743,13 @@
     <t xml:space="preserve">1.57693994045258</t>
   </si>
   <si>
-    <t xml:space="preserve">1.56539750099182</t>
+    <t xml:space="preserve">1.56539726257324</t>
   </si>
   <si>
     <t xml:space="preserve">1.52997398376465</t>
   </si>
   <si>
-    <t xml:space="preserve">1.5447005033493</t>
+    <t xml:space="preserve">1.54470074176788</t>
   </si>
   <si>
     <t xml:space="preserve">1.52440178394318</t>
@@ -3758,16 +3758,16 @@
     <t xml:space="preserve">1.50410294532776</t>
   </si>
   <si>
-    <t xml:space="preserve">1.52081966400146</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.51405322551727</t>
+    <t xml:space="preserve">1.52081954479218</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.51405334472656</t>
   </si>
   <si>
     <t xml:space="preserve">1.46589338779449</t>
   </si>
   <si>
-    <t xml:space="preserve">1.45395302772522</t>
+    <t xml:space="preserve">1.45395290851593</t>
   </si>
   <si>
     <t xml:space="preserve">1.46111714839935</t>
@@ -3779,10 +3779,10 @@
     <t xml:space="preserve">1.4595251083374</t>
   </si>
   <si>
-    <t xml:space="preserve">1.47106754779816</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.43206191062927</t>
+    <t xml:space="preserve">1.47106766700745</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.43206202983856</t>
   </si>
   <si>
     <t xml:space="preserve">1.41932547092438</t>
@@ -3791,7 +3791,7 @@
     <t xml:space="preserve">1.37315571308136</t>
   </si>
   <si>
-    <t xml:space="preserve">1.4042010307312</t>
+    <t xml:space="preserve">1.40420091152191</t>
   </si>
   <si>
     <t xml:space="preserve">1.41056907176971</t>
@@ -3806,19 +3806,19 @@
     <t xml:space="preserve">1.34529447555542</t>
   </si>
   <si>
-    <t xml:space="preserve">1.30191075801849</t>
+    <t xml:space="preserve">1.3019106388092</t>
   </si>
   <si>
     <t xml:space="preserve">1.23584008216858</t>
   </si>
   <si>
-    <t xml:space="preserve">1.24579048156738</t>
+    <t xml:space="preserve">1.24579060077667</t>
   </si>
   <si>
     <t xml:space="preserve">1.26171112060547</t>
   </si>
   <si>
-    <t xml:space="preserve">1.28400003910065</t>
+    <t xml:space="preserve">1.28400015830994</t>
   </si>
   <si>
     <t xml:space="preserve">1.28519415855408</t>
@@ -3827,52 +3827,52 @@
     <t xml:space="preserve">1.30469691753387</t>
   </si>
   <si>
-    <t xml:space="preserve">1.28957223892212</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.29076635837555</t>
+    <t xml:space="preserve">1.28957211971283</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.29076623916626</t>
   </si>
   <si>
     <t xml:space="preserve">1.29434847831726</t>
   </si>
   <si>
-    <t xml:space="preserve">1.31066727638245</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.31026911735535</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.29235851764679</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.30071663856506</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.4392261505127</t>
+    <t xml:space="preserve">1.31066715717316</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.31026899814606</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.29235827922821</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.30071675777435</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.43922626972198</t>
   </si>
   <si>
     <t xml:space="preserve">1.43604230880737</t>
   </si>
   <si>
-    <t xml:space="preserve">1.43046998977661</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.4726597070694</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.46231114864349</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.45474886894226</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.43683815002441</t>
+    <t xml:space="preserve">1.4304701089859</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.47265982627869</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.46231126785278</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.45474898815155</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.4368382692337</t>
   </si>
   <si>
     <t xml:space="preserve">1.41136515140533</t>
   </si>
   <si>
-    <t xml:space="preserve">1.42091739177704</t>
+    <t xml:space="preserve">1.42091763019562</t>
   </si>
   <si>
     <t xml:space="preserve">1.39783263206482</t>
@@ -3881,19 +3881,19 @@
     <t xml:space="preserve">1.39305651187897</t>
   </si>
   <si>
-    <t xml:space="preserve">1.42290771007538</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.42808187007904</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.45793306827545</t>
+    <t xml:space="preserve">1.42290759086609</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.42808175086975</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.45793318748474</t>
   </si>
   <si>
     <t xml:space="preserve">1.43882834911346</t>
   </si>
   <si>
-    <t xml:space="preserve">1.46151506900787</t>
+    <t xml:space="preserve">1.46151518821716</t>
   </si>
   <si>
     <t xml:space="preserve">1.44440054893494</t>
@@ -3908,46 +3908,46 @@
     <t xml:space="preserve">1.4690774679184</t>
   </si>
   <si>
-    <t xml:space="preserve">1.4861923456192</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.44718647003174</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.43644022941589</t>
+    <t xml:space="preserve">1.48619222640991</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.44718658924103</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.4364401102066</t>
   </si>
   <si>
     <t xml:space="preserve">1.45037078857422</t>
   </si>
   <si>
-    <t xml:space="preserve">1.44201242923737</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.44081830978394</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.42370355129242</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.3476824760437</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.36519527435303</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.40499699115753</t>
+    <t xml:space="preserve">1.44201231002808</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.44081842899323</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.42370367050171</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.34768259525299</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.36519539356232</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.40499687194824</t>
   </si>
   <si>
     <t xml:space="preserve">1.42449975013733</t>
   </si>
   <si>
-    <t xml:space="preserve">1.4599232673645</t>
+    <t xml:space="preserve">1.45992302894592</t>
   </si>
   <si>
     <t xml:space="preserve">1.51604354381561</t>
   </si>
   <si>
-    <t xml:space="preserve">1.50848114490509</t>
+    <t xml:space="preserve">1.5084810256958</t>
   </si>
   <si>
     <t xml:space="preserve">1.54708874225616</t>
@@ -3974,22 +3974,22 @@
     <t xml:space="preserve">1.64380669593811</t>
   </si>
   <si>
-    <t xml:space="preserve">1.64539861679077</t>
+    <t xml:space="preserve">1.64539849758148</t>
   </si>
   <si>
     <t xml:space="preserve">1.63903045654297</t>
   </si>
   <si>
-    <t xml:space="preserve">1.6398264169693</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.64221453666687</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.65415513515472</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.63027405738831</t>
+    <t xml:space="preserve">1.63982653617859</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.64221465587616</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.65415501594543</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.6302741765976</t>
   </si>
   <si>
     <t xml:space="preserve">1.62947797775269</t>
@@ -3998,7 +3998,7 @@
     <t xml:space="preserve">1.63345813751221</t>
   </si>
   <si>
-    <t xml:space="preserve">1.59365653991699</t>
+    <t xml:space="preserve">1.59365665912628</t>
   </si>
   <si>
     <t xml:space="preserve">1.61196541786194</t>
@@ -4010,52 +4010,52 @@
     <t xml:space="preserve">1.49932670593262</t>
   </si>
   <si>
-    <t xml:space="preserve">1.52639198303223</t>
+    <t xml:space="preserve">1.52639186382294</t>
   </si>
   <si>
     <t xml:space="preserve">1.52400374412537</t>
   </si>
   <si>
-    <t xml:space="preserve">1.50609290599823</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.53196394443512</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.52758610248566</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.52002370357513</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.53116798400879</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.5212174654007</t>
+    <t xml:space="preserve">1.50609302520752</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.53196406364441</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.52758586406708</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.52002358436584</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.53116810321808</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.52121770381927</t>
   </si>
   <si>
     <t xml:space="preserve">1.53315806388855</t>
   </si>
   <si>
-    <t xml:space="preserve">1.51325726509094</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.47027158737183</t>
+    <t xml:space="preserve">1.51325738430023</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.47027146816254</t>
   </si>
   <si>
     <t xml:space="preserve">1.4300719499588</t>
   </si>
   <si>
-    <t xml:space="preserve">1.43564414978027</t>
+    <t xml:space="preserve">1.43564426898956</t>
   </si>
   <si>
     <t xml:space="preserve">1.42887783050537</t>
   </si>
   <si>
-    <t xml:space="preserve">1.41176319122314</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.35086691379547</t>
+    <t xml:space="preserve">1.41176307201385</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.35086667537689</t>
   </si>
   <si>
     <t xml:space="preserve">1.34012031555176</t>
@@ -4064,7 +4064,7 @@
     <t xml:space="preserve">1.33892619609833</t>
   </si>
   <si>
-    <t xml:space="preserve">1.3775337934494</t>
+    <t xml:space="preserve">1.37753391265869</t>
   </si>
   <si>
     <t xml:space="preserve">1.36439919471741</t>
@@ -4076,10 +4076,10 @@
     <t xml:space="preserve">1.39425051212311</t>
   </si>
   <si>
-    <t xml:space="preserve">1.40619099140167</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.38191199302673</t>
+    <t xml:space="preserve">1.40619111061096</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.38191187381744</t>
   </si>
   <si>
     <t xml:space="preserve">1.38907623291016</t>
@@ -4091,28 +4091,28 @@
     <t xml:space="preserve">1.47902798652649</t>
   </si>
   <si>
-    <t xml:space="preserve">1.41614151000977</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.41375339031219</t>
+    <t xml:space="preserve">1.41614139080048</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.41375327110291</t>
   </si>
   <si>
     <t xml:space="preserve">1.37912583351135</t>
   </si>
   <si>
-    <t xml:space="preserve">1.41494750976562</t>
+    <t xml:space="preserve">1.41494739055634</t>
   </si>
   <si>
     <t xml:space="preserve">1.40260875225067</t>
   </si>
   <si>
-    <t xml:space="preserve">1.42569375038147</t>
+    <t xml:space="preserve">1.42569386959076</t>
   </si>
   <si>
     <t xml:space="preserve">1.44320642948151</t>
   </si>
   <si>
-    <t xml:space="preserve">1.45435094833374</t>
+    <t xml:space="preserve">1.45435106754303</t>
   </si>
   <si>
     <t xml:space="preserve">1.45116674900055</t>
@@ -4124,19 +4124,19 @@
     <t xml:space="preserve">1.52917790412903</t>
   </si>
   <si>
-    <t xml:space="preserve">1.5251978635788</t>
+    <t xml:space="preserve">1.52519774436951</t>
   </si>
   <si>
     <t xml:space="preserve">1.53634226322174</t>
   </si>
   <si>
-    <t xml:space="preserve">1.5347501039505</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.56181526184082</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.55624306201935</t>
+    <t xml:space="preserve">1.53475022315979</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.56181538105011</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.55624294281006</t>
   </si>
   <si>
     <t xml:space="preserve">1.54111838340759</t>
@@ -4148,40 +4148,40 @@
     <t xml:space="preserve">1.49813270568848</t>
   </si>
   <si>
-    <t xml:space="preserve">1.42847990989685</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.42330574989319</t>
+    <t xml:space="preserve">1.42847979068756</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.4233056306839</t>
   </si>
   <si>
     <t xml:space="preserve">1.48818230628967</t>
   </si>
   <si>
-    <t xml:space="preserve">1.52320766448975</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.46509742736816</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.4762419462204</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.54350638389587</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.5737556219101</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.55783522129059</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.61514937877655</t>
+    <t xml:space="preserve">1.52320754528046</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.46509730815887</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.47624182701111</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.54350650310516</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.57375574111938</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.5578351020813</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.61514949798584</t>
   </si>
   <si>
     <t xml:space="preserve">1.61276137828827</t>
   </si>
   <si>
-    <t xml:space="preserve">1.63743817806244</t>
+    <t xml:space="preserve">1.63743829727173</t>
   </si>
   <si>
     <t xml:space="preserve">1.574551820755</t>
@@ -4190,13 +4190,13 @@
     <t xml:space="preserve">1.7186336517334</t>
   </si>
   <si>
-    <t xml:space="preserve">1.69793653488159</t>
+    <t xml:space="preserve">1.69793665409088</t>
   </si>
   <si>
     <t xml:space="preserve">1.6071891784668</t>
   </si>
   <si>
-    <t xml:space="preserve">1.56022334098816</t>
+    <t xml:space="preserve">1.56022322177887</t>
   </si>
   <si>
     <t xml:space="preserve">1.44161438941956</t>
@@ -4205,13 +4205,13 @@
     <t xml:space="preserve">1.46788358688354</t>
   </si>
   <si>
-    <t xml:space="preserve">1.32260763645172</t>
+    <t xml:space="preserve">1.32260751724243</t>
   </si>
   <si>
     <t xml:space="preserve">1.31743335723877</t>
   </si>
   <si>
-    <t xml:space="preserve">1.24857664108276</t>
+    <t xml:space="preserve">1.24857652187347</t>
   </si>
   <si>
     <t xml:space="preserve">1.11643540859222</t>
@@ -4223,31 +4223,31 @@
     <t xml:space="preserve">1.11563920974731</t>
   </si>
   <si>
-    <t xml:space="preserve">1.22708368301392</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.1351420879364</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.12877368927002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.17494344711304</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.19882464408875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.28678596019745</t>
+    <t xml:space="preserve">1.22708356380463</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.13514196872711</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.12877380847931</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.17494356632233</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.19882452487946</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.28678607940674</t>
   </si>
   <si>
     <t xml:space="preserve">1.25773096084595</t>
   </si>
   <si>
-    <t xml:space="preserve">1.24977076053619</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.2660893201828</t>
+    <t xml:space="preserve">1.2497706413269</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.26608943939209</t>
   </si>
   <si>
     <t xml:space="preserve">1.24698448181152</t>
@@ -4262,10 +4262,10 @@
     <t xml:space="preserve">1.25892508029938</t>
   </si>
   <si>
-    <t xml:space="preserve">1.33295607566833</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.30668687820435</t>
+    <t xml:space="preserve">1.33295595645905</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.30668699741364</t>
   </si>
   <si>
     <t xml:space="preserve">1.26529324054718</t>
@@ -4277,7 +4277,7 @@
     <t xml:space="preserve">1.22429764270782</t>
   </si>
   <si>
-    <t xml:space="preserve">1.2262876033783</t>
+    <t xml:space="preserve">1.22628772258759</t>
   </si>
   <si>
     <t xml:space="preserve">1.27484571933746</t>
@@ -4292,13 +4292,13 @@
     <t xml:space="preserve">1.23504400253296</t>
   </si>
   <si>
-    <t xml:space="preserve">1.24778068065643</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.25335276126862</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.29753243923187</t>
+    <t xml:space="preserve">1.24778056144714</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.25335264205933</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.29753267765045</t>
   </si>
   <si>
     <t xml:space="preserve">1.30628895759583</t>
@@ -4310,82 +4310,82 @@
     <t xml:space="preserve">1.27404963970184</t>
   </si>
   <si>
-    <t xml:space="preserve">1.25932323932648</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.26847743988037</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.26011896133423</t>
+    <t xml:space="preserve">1.25932312011719</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.26847732067108</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.26011908054352</t>
   </si>
   <si>
     <t xml:space="preserve">1.27763175964355</t>
   </si>
   <si>
-    <t xml:space="preserve">1.26927351951599</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.23822832107544</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.21912336349487</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.22071552276611</t>
+    <t xml:space="preserve">1.2692734003067</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.23822820186615</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.21912348270416</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.22071540355682</t>
   </si>
   <si>
     <t xml:space="preserve">1.21116304397583</t>
   </si>
   <si>
-    <t xml:space="preserve">1.35325479507446</t>
+    <t xml:space="preserve">1.35325491428375</t>
   </si>
   <si>
     <t xml:space="preserve">1.38629019260406</t>
   </si>
   <si>
-    <t xml:space="preserve">1.38668811321259</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.37395167350769</t>
+    <t xml:space="preserve">1.38668823242188</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.3739515542984</t>
   </si>
   <si>
     <t xml:space="preserve">1.40539479255676</t>
   </si>
   <si>
-    <t xml:space="preserve">1.39862859249115</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.40738499164581</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.3902702331543</t>
+    <t xml:space="preserve">1.39862871170044</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.4073851108551</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.39027035236359</t>
   </si>
   <si>
     <t xml:space="preserve">1.48383438587189</t>
   </si>
   <si>
-    <t xml:space="preserve">1.49949705600739</t>
+    <t xml:space="preserve">1.49949717521667</t>
   </si>
   <si>
     <t xml:space="preserve">1.54153895378113</t>
   </si>
   <si>
-    <t xml:space="preserve">1.56049907207489</t>
+    <t xml:space="preserve">1.56049919128418</t>
   </si>
   <si>
     <t xml:space="preserve">1.55390441417694</t>
   </si>
   <si>
-    <t xml:space="preserve">1.55349218845367</t>
+    <t xml:space="preserve">1.55349206924438</t>
   </si>
   <si>
     <t xml:space="preserve">1.57987141609192</t>
   </si>
   <si>
-    <t xml:space="preserve">1.57616186141968</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.58976376056671</t>
+    <t xml:space="preserve">1.57616174221039</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.58976364135742</t>
   </si>
   <si>
     <t xml:space="preserve">1.53576862812042</t>
@@ -4400,13 +4400,13 @@
     <t xml:space="preserve">1.59841930866241</t>
   </si>
   <si>
-    <t xml:space="preserve">1.60831153392792</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.40057468414307</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.35482323169708</t>
+    <t xml:space="preserve">1.60831165313721</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.40057480335236</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.35482311248779</t>
   </si>
   <si>
     <t xml:space="preserve">1.36430323123932</t>
@@ -4418,7 +4418,7 @@
     <t xml:space="preserve">1.35770845413208</t>
   </si>
   <si>
-    <t xml:space="preserve">1.38326346874237</t>
+    <t xml:space="preserve">1.38326334953308</t>
   </si>
   <si>
     <t xml:space="preserve">1.40799391269684</t>
@@ -4430,10 +4430,10 @@
     <t xml:space="preserve">1.41252779960632</t>
   </si>
   <si>
-    <t xml:space="preserve">1.34451878070831</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.38820958137512</t>
+    <t xml:space="preserve">1.3445188999176</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.38820946216583</t>
   </si>
   <si>
     <t xml:space="preserve">1.36718845367432</t>
@@ -4448,13 +4448,13 @@
     <t xml:space="preserve">1.2921724319458</t>
   </si>
   <si>
-    <t xml:space="preserve">1.2521915435791</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.25136697292328</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.18789184093475</t>
+    <t xml:space="preserve">1.25219130516052</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.25136709213257</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.18789196014404</t>
   </si>
   <si>
     <t xml:space="preserve">1.16934394836426</t>
@@ -4475,46 +4475,46 @@
     <t xml:space="preserve">1.128950715065</t>
   </si>
   <si>
-    <t xml:space="preserve">1.05929291248322</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.06588757038116</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.07990169525146</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.15326905250549</t>
+    <t xml:space="preserve">1.05929279327393</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.06588768959045</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.07990157604218</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.15326917171478</t>
   </si>
   <si>
     <t xml:space="preserve">1.12029492855072</t>
   </si>
   <si>
-    <t xml:space="preserve">1.08525991439819</t>
+    <t xml:space="preserve">1.08526003360748</t>
   </si>
   <si>
     <t xml:space="preserve">1.06794857978821</t>
   </si>
   <si>
-    <t xml:space="preserve">1.09556448459625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.06506335735321</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.08567214012146</t>
+    <t xml:space="preserve">1.09556436538696</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.0650634765625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.08567225933075</t>
   </si>
   <si>
     <t xml:space="preserve">1.08814525604248</t>
   </si>
   <si>
-    <t xml:space="preserve">1.11287569999695</t>
+    <t xml:space="preserve">1.11287581920624</t>
   </si>
   <si>
     <t xml:space="preserve">1.12482893466949</t>
   </si>
   <si>
-    <t xml:space="preserve">1.14337682723999</t>
+    <t xml:space="preserve">1.1433767080307</t>
   </si>
   <si>
     <t xml:space="preserve">1.18912839889526</t>
@@ -4526,7 +4526,7 @@
     <t xml:space="preserve">1.29588210582733</t>
   </si>
   <si>
-    <t xml:space="preserve">1.32720744609833</t>
+    <t xml:space="preserve">1.32720732688904</t>
   </si>
   <si>
     <t xml:space="preserve">1.33792412281036</t>
@@ -4541,7 +4541,7 @@
     <t xml:space="preserve">1.35647189617157</t>
   </si>
   <si>
-    <t xml:space="preserve">1.35070133209229</t>
+    <t xml:space="preserve">1.35070145130157</t>
   </si>
   <si>
     <t xml:space="preserve">1.30659854412079</t>
@@ -4550,34 +4550,34 @@
     <t xml:space="preserve">1.26290786266327</t>
   </si>
   <si>
-    <t xml:space="preserve">1.28063142299652</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.28021931648254</t>
+    <t xml:space="preserve">1.28063154220581</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.28021943569183</t>
   </si>
   <si>
     <t xml:space="preserve">1.2608470916748</t>
   </si>
   <si>
-    <t xml:space="preserve">1.22004163265228</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.22045385837555</t>
+    <t xml:space="preserve">1.22004151344299</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.22045373916626</t>
   </si>
   <si>
     <t xml:space="preserve">1.24106252193451</t>
   </si>
   <si>
-    <t xml:space="preserve">1.24065041542053</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.22333896160126</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.25301563739777</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.21550762653351</t>
+    <t xml:space="preserve">1.24065029621124</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.22333908081055</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.25301575660706</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.21550750732422</t>
   </si>
   <si>
     <t xml:space="preserve">1.21798062324524</t>
@@ -4607,7 +4607,7 @@
     <t xml:space="preserve">1.38985824584961</t>
   </si>
   <si>
-    <t xml:space="preserve">1.39686512947083</t>
+    <t xml:space="preserve">1.39686524868011</t>
   </si>
   <si>
     <t xml:space="preserve">1.3729590177536</t>
@@ -4616,10 +4616,10 @@
     <t xml:space="preserve">1.38408780097961</t>
   </si>
   <si>
-    <t xml:space="preserve">1.43025159835815</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.37337112426758</t>
+    <t xml:space="preserve">1.43025147914886</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.37337124347687</t>
   </si>
   <si>
     <t xml:space="preserve">1.37172245979309</t>
@@ -4628,7 +4628,7 @@
     <t xml:space="preserve">1.34163355827332</t>
   </si>
   <si>
-    <t xml:space="preserve">1.32020056247711</t>
+    <t xml:space="preserve">1.32020044326782</t>
   </si>
   <si>
     <t xml:space="preserve">1.28269231319427</t>
@@ -4637,16 +4637,16 @@
     <t xml:space="preserve">1.30330121517181</t>
   </si>
   <si>
-    <t xml:space="preserve">1.32844388484955</t>
+    <t xml:space="preserve">1.32844400405884</t>
   </si>
   <si>
     <t xml:space="preserve">1.38491201400757</t>
   </si>
   <si>
-    <t xml:space="preserve">1.35894501209259</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.31731534004211</t>
+    <t xml:space="preserve">1.3589448928833</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.31731522083282</t>
   </si>
   <si>
     <t xml:space="preserve">1.33462655544281</t>
@@ -4658,25 +4658,25 @@
     <t xml:space="preserve">1.30824732780457</t>
   </si>
   <si>
-    <t xml:space="preserve">1.34080934524536</t>
+    <t xml:space="preserve">1.34080910682678</t>
   </si>
   <si>
     <t xml:space="preserve">1.36347889900208</t>
   </si>
   <si>
-    <t xml:space="preserve">1.39274346828461</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.40181124210358</t>
+    <t xml:space="preserve">1.39274334907532</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.40181136131287</t>
   </si>
   <si>
     <t xml:space="preserve">1.41211581230164</t>
   </si>
   <si>
-    <t xml:space="preserve">1.41664958000183</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.43560969829559</t>
+    <t xml:space="preserve">1.41664969921112</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.43560981750488</t>
   </si>
   <si>
     <t xml:space="preserve">1.47641515731812</t>
@@ -4685,10 +4685,10 @@
     <t xml:space="preserve">1.46734726428986</t>
   </si>
   <si>
-    <t xml:space="preserve">1.4694082736969</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.51103794574738</t>
+    <t xml:space="preserve">1.46940815448761</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.51103806495667</t>
   </si>
   <si>
     <t xml:space="preserve">1.52093029022217</t>
@@ -4700,7 +4700,7 @@
     <t xml:space="preserve">1.56214785575867</t>
   </si>
   <si>
-    <t xml:space="preserve">1.58770275115967</t>
+    <t xml:space="preserve">1.58770287036896</t>
   </si>
   <si>
     <t xml:space="preserve">1.58893930912018</t>
@@ -4709,10 +4709,10 @@
     <t xml:space="preserve">1.65942144393921</t>
   </si>
   <si>
-    <t xml:space="preserve">1.68992257118225</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.5600870847702</t>
+    <t xml:space="preserve">1.68992245197296</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.56008696556091</t>
   </si>
   <si>
     <t xml:space="preserve">1.51680839061737</t>
@@ -4727,22 +4727,22 @@
     <t xml:space="preserve">1.54648518562317</t>
   </si>
   <si>
-    <t xml:space="preserve">1.55184352397919</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.57410109043121</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.57822275161743</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.58193242549896</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.59965586662292</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.61284554004669</t>
+    <t xml:space="preserve">1.55184364318848</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.57410097122192</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.57822263240814</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.58193230628967</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.59965598583221</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.61284565925598</t>
   </si>
   <si>
     <t xml:space="preserve">1.62356197834015</t>
@@ -4751,10 +4751,10 @@
     <t xml:space="preserve">1.60872387886047</t>
   </si>
   <si>
-    <t xml:space="preserve">1.61573088169098</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.62562298774719</t>
+    <t xml:space="preserve">1.61573076248169</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.6256228685379</t>
   </si>
   <si>
     <t xml:space="preserve">1.60666286945343</t>
@@ -4775,37 +4775,37 @@
     <t xml:space="preserve">1.60954809188843</t>
   </si>
   <si>
-    <t xml:space="preserve">1.60913598537445</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.61902821063995</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.6070750951767</t>
+    <t xml:space="preserve">1.60913586616516</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.61902809143066</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.60707497596741</t>
   </si>
   <si>
     <t xml:space="preserve">1.55101907253265</t>
   </si>
   <si>
-    <t xml:space="preserve">1.54978251457214</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.53782951831818</t>
+    <t xml:space="preserve">1.54978263378143</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.53782939910889</t>
   </si>
   <si>
     <t xml:space="preserve">1.6041898727417</t>
   </si>
   <si>
-    <t xml:space="preserve">1.60295331478119</t>
+    <t xml:space="preserve">1.6029531955719</t>
   </si>
   <si>
     <t xml:space="preserve">1.59512197971344</t>
   </si>
   <si>
-    <t xml:space="preserve">1.58151996135712</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.61531841754913</t>
+    <t xml:space="preserve">1.58152008056641</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.61531865596771</t>
   </si>
   <si>
     <t xml:space="preserve">1.63633954524994</t>
@@ -4817,49 +4817,49 @@
     <t xml:space="preserve">1.67343533039093</t>
   </si>
   <si>
-    <t xml:space="preserve">1.71712613105774</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.72536957263947</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.73938345909119</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.73855924606323</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.74845147132874</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.80533182621002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.82511615753174</t>
+    <t xml:space="preserve">1.71712601184845</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.72536969184875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.73938369750977</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.73855936527252</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.74845159053802</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.80533194541931</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.82511639595032</t>
   </si>
   <si>
     <t xml:space="preserve">1.79708826541901</t>
   </si>
   <si>
-    <t xml:space="preserve">1.85644173622131</t>
+    <t xml:space="preserve">1.85644161701202</t>
   </si>
   <si>
     <t xml:space="preserve">1.85479295253754</t>
   </si>
   <si>
-    <t xml:space="preserve">1.89024007320404</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.90178084373474</t>
+    <t xml:space="preserve">1.89023995399475</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.90178096294403</t>
   </si>
   <si>
     <t xml:space="preserve">1.92898464202881</t>
   </si>
   <si>
-    <t xml:space="preserve">1.93310654163361</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.97349965572357</t>
+    <t xml:space="preserve">1.93310642242432</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.97349977493286</t>
   </si>
   <si>
     <t xml:space="preserve">2.00400066375732</t>
@@ -4868,28 +4868,28 @@
     <t xml:space="preserve">2.00317668914795</t>
   </si>
   <si>
-    <t xml:space="preserve">2.07489514350891</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.14331603050232</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.08396315574646</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.0938549041748</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.12847805023193</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.09880137443542</t>
+    <t xml:space="preserve">2.07489490509033</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.1433162689209</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.08396291732788</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.09385538101196</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.12847781181335</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.098801612854</t>
   </si>
   <si>
     <t xml:space="preserve">2.11941003799438</t>
   </si>
   <si>
-    <t xml:space="preserve">2.10457181930542</t>
+    <t xml:space="preserve">2.10457158088684</t>
   </si>
   <si>
     <t xml:space="preserve">2.14991116523743</t>
@@ -4907,7 +4907,7 @@
     <t xml:space="preserve">2.30159187316895</t>
   </si>
   <si>
-    <t xml:space="preserve">2.26449632644653</t>
+    <t xml:space="preserve">2.26449608802795</t>
   </si>
   <si>
     <t xml:space="preserve">2.25295543670654</t>
@@ -4925,28 +4925,28 @@
     <t xml:space="preserve">2.18700695037842</t>
   </si>
   <si>
-    <t xml:space="preserve">2.21503520011902</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.19525027275085</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.20844030380249</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.22657608985901</t>
+    <t xml:space="preserve">2.21503496170044</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.19525051116943</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.20843982696533</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.22657585144043</t>
   </si>
   <si>
     <t xml:space="preserve">2.27026653289795</t>
   </si>
   <si>
-    <t xml:space="preserve">2.27273964881897</t>
+    <t xml:space="preserve">2.27273941040039</t>
   </si>
   <si>
     <t xml:space="preserve">2.3304443359375</t>
   </si>
   <si>
-    <t xml:space="preserve">2.32220077514648</t>
+    <t xml:space="preserve">2.32220053672791</t>
   </si>
   <si>
     <t xml:space="preserve">2.21833229064941</t>
@@ -4958,28 +4958,28 @@
     <t xml:space="preserve">2.04027223587036</t>
   </si>
   <si>
-    <t xml:space="preserve">1.89271330833435</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.89683520793915</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.8440762758255</t>
+    <t xml:space="preserve">1.89271318912506</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.89683496952057</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.84407663345337</t>
   </si>
   <si>
     <t xml:space="preserve">1.87045562267303</t>
   </si>
   <si>
-    <t xml:space="preserve">1.96195888519287</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.93393075466156</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.89848351478577</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.82181906700134</t>
+    <t xml:space="preserve">1.96195900440216</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.93393087387085</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.89848387241364</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.82181882858276</t>
   </si>
   <si>
     <t xml:space="preserve">1.84325206279755</t>
@@ -4988,58 +4988,58 @@
     <t xml:space="preserve">1.84902250766754</t>
   </si>
   <si>
-    <t xml:space="preserve">1.8993079662323</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.88776707649231</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.87375319004059</t>
+    <t xml:space="preserve">1.89930772781372</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.88776695728302</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.8737530708313</t>
   </si>
   <si>
     <t xml:space="preserve">1.91991686820984</t>
   </si>
   <si>
-    <t xml:space="preserve">1.91909241676331</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.94876945018768</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.94547152519226</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.98339188098907</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.97679710388184</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.06912469863892</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.079017162323</t>
+    <t xml:space="preserve">1.91909265518188</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.9487692117691</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.94547176361084</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.98339200019836</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.97679698467255</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.06912446022034</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.07901668548584</t>
   </si>
   <si>
     <t xml:space="preserve">2.16392493247986</t>
   </si>
   <si>
-    <t xml:space="preserve">2.20102119445801</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.23069763183594</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.26284742355347</t>
+    <t xml:space="preserve">2.20102095603943</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.23069787025452</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.26284718513489</t>
   </si>
   <si>
     <t xml:space="preserve">2.25377941131592</t>
   </si>
   <si>
-    <t xml:space="preserve">2.1020987033844</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.18618273735046</t>
+    <t xml:space="preserve">2.10209846496582</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.18618249893188</t>
   </si>
   <si>
     <t xml:space="preserve">2.09797692298889</t>
@@ -5069,19 +5069,19 @@
     <t xml:space="preserve">2.24965786933899</t>
   </si>
   <si>
-    <t xml:space="preserve">2.23564338684082</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.23481965065002</t>
+    <t xml:space="preserve">2.2356436252594</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.23481941223145</t>
   </si>
   <si>
     <t xml:space="preserve">2.22080564498901</t>
   </si>
   <si>
-    <t xml:space="preserve">2.2257513999939</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.25335764884949</t>
+    <t xml:space="preserve">2.22575163841248</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.25335788726807</t>
   </si>
   <si>
     <t xml:space="preserve">2.23179030418396</t>
@@ -5090,7 +5090,7 @@
     <t xml:space="preserve">2.13603138923645</t>
   </si>
   <si>
-    <t xml:space="preserve">2.13085532188416</t>
+    <t xml:space="preserve">2.13085508346558</t>
   </si>
   <si>
     <t xml:space="preserve">2.13516855239868</t>
@@ -5099,13 +5099,13 @@
     <t xml:space="preserve">2.12395358085632</t>
   </si>
   <si>
-    <t xml:space="preserve">2.0972101688385</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.06183981895447</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.11618947982788</t>
+    <t xml:space="preserve">2.09720993041992</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.06183958053589</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.1161892414093</t>
   </si>
   <si>
     <t xml:space="preserve">2.16363739967346</t>
@@ -5114,7 +5114,7 @@
     <t xml:space="preserve">2.15328526496887</t>
   </si>
   <si>
-    <t xml:space="preserve">2.15846133232117</t>
+    <t xml:space="preserve">2.15846157073975</t>
   </si>
   <si>
     <t xml:space="preserve">2.15414786338806</t>
@@ -5129,40 +5129,40 @@
     <t xml:space="preserve">2.14465832710266</t>
   </si>
   <si>
-    <t xml:space="preserve">2.14983439445496</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.20073342323303</t>
+    <t xml:space="preserve">2.14983463287354</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.20073366165161</t>
   </si>
   <si>
     <t xml:space="preserve">2.19814538955688</t>
   </si>
   <si>
-    <t xml:space="preserve">2.24559354782104</t>
+    <t xml:space="preserve">2.24559330940247</t>
   </si>
   <si>
     <t xml:space="preserve">2.31288361549377</t>
   </si>
   <si>
-    <t xml:space="preserve">2.34652900695801</t>
+    <t xml:space="preserve">2.34652876853943</t>
   </si>
   <si>
     <t xml:space="preserve">2.37931108474731</t>
   </si>
   <si>
-    <t xml:space="preserve">2.36809611320496</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.31633472442627</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.28613996505737</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.32927465438843</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.34566617012024</t>
+    <t xml:space="preserve">2.36809587478638</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.31633424758911</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.28614044189453</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.32927489280701</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.34566593170166</t>
   </si>
   <si>
     <t xml:space="preserve">2.37672328948975</t>
@@ -5192,7 +5192,7 @@
     <t xml:space="preserve">2.44056248664856</t>
   </si>
   <si>
-    <t xml:space="preserve">2.47938346862793</t>
+    <t xml:space="preserve">2.47938370704651</t>
   </si>
   <si>
     <t xml:space="preserve">2.53373336791992</t>
@@ -5201,22 +5201,22 @@
     <t xml:space="preserve">2.51302886009216</t>
   </si>
   <si>
-    <t xml:space="preserve">2.56133985519409</t>
+    <t xml:space="preserve">2.56133961677551</t>
   </si>
   <si>
     <t xml:space="preserve">2.55443811416626</t>
   </si>
   <si>
-    <t xml:space="preserve">2.53200817108154</t>
+    <t xml:space="preserve">2.53200793266296</t>
   </si>
   <si>
     <t xml:space="preserve">2.58376955986023</t>
   </si>
   <si>
-    <t xml:space="preserve">2.601886510849</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.62086582183838</t>
+    <t xml:space="preserve">2.60188627243042</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.6208655834198</t>
   </si>
   <si>
     <t xml:space="preserve">2.63553142547607</t>
@@ -5225,7 +5225,7 @@
     <t xml:space="preserve">2.73819208145142</t>
   </si>
   <si>
-    <t xml:space="preserve">2.69419479370117</t>
+    <t xml:space="preserve">2.69419455528259</t>
   </si>
   <si>
     <t xml:space="preserve">2.70454692840576</t>
@@ -5243,55 +5243,55 @@
     <t xml:space="preserve">2.48714780807495</t>
   </si>
   <si>
-    <t xml:space="preserve">2.44660115242004</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.45264029502869</t>
+    <t xml:space="preserve">2.44660139083862</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.45264005661011</t>
   </si>
   <si>
     <t xml:space="preserve">2.18434238433838</t>
   </si>
   <si>
-    <t xml:space="preserve">2.23265337944031</t>
+    <t xml:space="preserve">2.23265314102173</t>
   </si>
   <si>
     <t xml:space="preserve">2.28010129928589</t>
   </si>
   <si>
-    <t xml:space="preserve">2.34048986434937</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.34911704063416</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.31547164916992</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.38276195526123</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.37240958213806</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.36895895004272</t>
+    <t xml:space="preserve">2.34049010276794</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.34911680221558</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.3154718875885</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.38276171684265</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.37240982055664</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.36895871162415</t>
   </si>
   <si>
     <t xml:space="preserve">2.34394073486328</t>
   </si>
   <si>
-    <t xml:space="preserve">2.39656519889832</t>
+    <t xml:space="preserve">2.39656496047974</t>
   </si>
   <si>
     <t xml:space="preserve">2.41640710830688</t>
   </si>
   <si>
-    <t xml:space="preserve">2.43969988822937</t>
+    <t xml:space="preserve">2.43969964981079</t>
   </si>
   <si>
     <t xml:space="preserve">2.40519213676453</t>
   </si>
   <si>
-    <t xml:space="preserve">2.39138889312744</t>
+    <t xml:space="preserve">2.39138913154602</t>
   </si>
   <si>
     <t xml:space="preserve">2.36464524269104</t>
@@ -5306,13 +5306,13 @@
     <t xml:space="preserve">2.24904441833496</t>
   </si>
   <si>
-    <t xml:space="preserve">2.3111584186554</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.38793802261353</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.41295623779297</t>
+    <t xml:space="preserve">2.31115794181824</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.38793778419495</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.41295599937439</t>
   </si>
   <si>
     <t xml:space="preserve">2.42589664459229</t>
@@ -5321,13 +5321,13 @@
     <t xml:space="preserve">2.46989393234253</t>
   </si>
   <si>
-    <t xml:space="preserve">2.57773089408875</t>
+    <t xml:space="preserve">2.57773065567017</t>
   </si>
   <si>
     <t xml:space="preserve">2.57428002357483</t>
   </si>
   <si>
-    <t xml:space="preserve">2.5527126789093</t>
+    <t xml:space="preserve">2.55271291732788</t>
   </si>
   <si>
     <t xml:space="preserve">2.4388370513916</t>
@@ -5336,7 +5336,7 @@
     <t xml:space="preserve">2.41123080253601</t>
   </si>
   <si>
-    <t xml:space="preserve">2.49922585487366</t>
+    <t xml:space="preserve">2.49922561645508</t>
   </si>
   <si>
     <t xml:space="preserve">2.46644330024719</t>
@@ -5351,13 +5351,13 @@
     <t xml:space="preserve">2.44142508506775</t>
   </si>
   <si>
-    <t xml:space="preserve">2.51475405693054</t>
+    <t xml:space="preserve">2.51475429534912</t>
   </si>
   <si>
     <t xml:space="preserve">2.3974277973175</t>
   </si>
   <si>
-    <t xml:space="preserve">2.48628520965576</t>
+    <t xml:space="preserve">2.48628544807434</t>
   </si>
   <si>
     <t xml:space="preserve">2.55530071258545</t>
@@ -5366,13 +5366,13 @@
     <t xml:space="preserve">2.53632140159607</t>
   </si>
   <si>
-    <t xml:space="preserve">2.55357551574707</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.61310148239136</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.6381196975708</t>
+    <t xml:space="preserve">2.55357527732849</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.61310124397278</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.63811945915222</t>
   </si>
   <si>
     <t xml:space="preserve">2.60274910926819</t>
@@ -5381,13 +5381,13 @@
     <t xml:space="preserve">2.46730589866638</t>
   </si>
   <si>
-    <t xml:space="preserve">2.5716917514801</t>
+    <t xml:space="preserve">2.57169198989868</t>
   </si>
   <si>
     <t xml:space="preserve">2.50440192222595</t>
   </si>
   <si>
-    <t xml:space="preserve">2.52683186531067</t>
+    <t xml:space="preserve">2.52683162689209</t>
   </si>
   <si>
     <t xml:space="preserve">2.51389145851135</t>
@@ -5408,13 +5408,13 @@
     <t xml:space="preserve">2.72180080413818</t>
   </si>
   <si>
-    <t xml:space="preserve">2.75458335876465</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.73301577568054</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.83136320114136</t>
+    <t xml:space="preserve">2.75458312034607</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.73301601409912</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.83136296272278</t>
   </si>
   <si>
     <t xml:space="preserve">2.84171533584595</t>
@@ -5423,16 +5423,16 @@
     <t xml:space="preserve">3.04444861412048</t>
   </si>
   <si>
-    <t xml:space="preserve">3.02546906471252</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.07291769981384</t>
+    <t xml:space="preserve">3.0254693031311</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.07291722297668</t>
   </si>
   <si>
     <t xml:space="preserve">2.98751068115234</t>
   </si>
   <si>
-    <t xml:space="preserve">3.00562715530396</t>
+    <t xml:space="preserve">3.00562739372253</t>
   </si>
   <si>
     <t xml:space="preserve">3.05480074882507</t>
@@ -5453,13 +5453,13 @@
     <t xml:space="preserve">2.92453408241272</t>
   </si>
   <si>
-    <t xml:space="preserve">2.89002633094788</t>
+    <t xml:space="preserve">2.8900260925293</t>
   </si>
   <si>
     <t xml:space="preserve">2.98319721221924</t>
   </si>
   <si>
-    <t xml:space="preserve">2.95904183387756</t>
+    <t xml:space="preserve">2.95904159545898</t>
   </si>
   <si>
     <t xml:space="preserve">2.98837351799011</t>
@@ -5468,13 +5468,13 @@
     <t xml:space="preserve">2.96766877174377</t>
   </si>
   <si>
-    <t xml:space="preserve">2.95214033126831</t>
+    <t xml:space="preserve">2.95214009284973</t>
   </si>
   <si>
     <t xml:space="preserve">2.97457027435303</t>
   </si>
   <si>
-    <t xml:space="preserve">2.89347696304321</t>
+    <t xml:space="preserve">2.89347720146179</t>
   </si>
   <si>
     <t xml:space="preserve">2.9167697429657</t>
@@ -5486,13 +5486,13 @@
     <t xml:space="preserve">2.86932158470154</t>
   </si>
   <si>
-    <t xml:space="preserve">2.70023345947266</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.64070773124695</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.64588379859924</t>
+    <t xml:space="preserve">2.70023369789124</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.64070749282837</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.64588356018066</t>
   </si>
   <si>
     <t xml:space="preserve">2.64502096176147</t>
@@ -5504,13 +5504,13 @@
     <t xml:space="preserve">2.62690448760986</t>
   </si>
   <si>
-    <t xml:space="preserve">2.63035535812378</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.60965061187744</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.61051344871521</t>
+    <t xml:space="preserve">2.6303551197052</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.60965085029602</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.61051321029663</t>
   </si>
   <si>
     <t xml:space="preserve">2.68901872634888</t>
@@ -5528,10 +5528,10 @@
     <t xml:space="preserve">2.7200756072998</t>
   </si>
   <si>
-    <t xml:space="preserve">2.73215341567993</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.67952871322632</t>
+    <t xml:space="preserve">2.73215317726135</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.6795289516449</t>
   </si>
   <si>
     <t xml:space="preserve">2.74681901931763</t>
@@ -5540,7 +5540,7 @@
     <t xml:space="preserve">2.73905467987061</t>
   </si>
   <si>
-    <t xml:space="preserve">2.72611427307129</t>
+    <t xml:space="preserve">2.72611451148987</t>
   </si>
   <si>
     <t xml:space="preserve">2.75285792350769</t>
@@ -5552,10 +5552,10 @@
     <t xml:space="preserve">2.86759614944458</t>
   </si>
   <si>
-    <t xml:space="preserve">2.8486168384552</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.83826470375061</t>
+    <t xml:space="preserve">2.84861707687378</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.83826446533203</t>
   </si>
   <si>
     <t xml:space="preserve">2.88916349411011</t>
@@ -5564,10 +5564,10 @@
     <t xml:space="preserve">2.81755995750427</t>
   </si>
   <si>
-    <t xml:space="preserve">2.79858064651489</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.78564023971558</t>
+    <t xml:space="preserve">2.79858040809631</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.78564047813416</t>
   </si>
   <si>
     <t xml:space="preserve">2.86414527893066</t>
@@ -5582,7 +5582,7 @@
     <t xml:space="preserve">2.92712187767029</t>
   </si>
   <si>
-    <t xml:space="preserve">2.99872589111328</t>
+    <t xml:space="preserve">2.9987256526947</t>
   </si>
   <si>
     <t xml:space="preserve">3.021155834198</t>
@@ -5594,7 +5594,7 @@
     <t xml:space="preserve">3.04531121253967</t>
   </si>
   <si>
-    <t xml:space="preserve">3.03150820732117</t>
+    <t xml:space="preserve">3.03150796890259</t>
   </si>
   <si>
     <t xml:space="preserve">3.06515336036682</t>
@@ -5609,13 +5609,13 @@
     <t xml:space="preserve">3.03323340415955</t>
   </si>
   <si>
-    <t xml:space="preserve">2.9624924659729</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.07895612716675</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.11432647705078</t>
+    <t xml:space="preserve">2.96249270439148</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.07895636558533</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.11432671546936</t>
   </si>
   <si>
     <t xml:space="preserve">3.18161702156067</t>
@@ -5630,7 +5630,7 @@
     <t xml:space="preserve">3.19973373413086</t>
   </si>
   <si>
-    <t xml:space="preserve">3.19714570045471</t>
+    <t xml:space="preserve">3.19714546203613</t>
   </si>
   <si>
     <t xml:space="preserve">3.239417552948</t>
@@ -5639,19 +5639,19 @@
     <t xml:space="preserve">3.28082680702209</t>
   </si>
   <si>
-    <t xml:space="preserve">3.30239415168762</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.30929565429688</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.26788663864136</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.27823877334595</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.34811687469482</t>
+    <t xml:space="preserve">3.3023943901062</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.30929589271545</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.26788640022278</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.27823853492737</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.3481171131134</t>
   </si>
   <si>
     <t xml:space="preserve">3.44991493225098</t>
@@ -5663,7 +5663,7 @@
     <t xml:space="preserve">3.41972064971924</t>
   </si>
   <si>
-    <t xml:space="preserve">3.4671688079834</t>
+    <t xml:space="preserve">3.46716904640198</t>
   </si>
   <si>
     <t xml:space="preserve">3.53618431091309</t>
@@ -5672,7 +5672,7 @@
     <t xml:space="preserve">3.63539433479309</t>
   </si>
   <si>
-    <t xml:space="preserve">3.67076444625854</t>
+    <t xml:space="preserve">3.6707649230957</t>
   </si>
   <si>
     <t xml:space="preserve">3.64574646949768</t>
@@ -5684,7 +5684,7 @@
     <t xml:space="preserve">3.72856497764587</t>
   </si>
   <si>
-    <t xml:space="preserve">3.83381390571594</t>
+    <t xml:space="preserve">3.83381366729736</t>
   </si>
   <si>
     <t xml:space="preserve">3.7440938949585</t>
@@ -5696,7 +5696,7 @@
     <t xml:space="preserve">3.76997447013855</t>
   </si>
   <si>
-    <t xml:space="preserve">3.85969471931458</t>
+    <t xml:space="preserve">3.85969519615173</t>
   </si>
   <si>
     <t xml:space="preserve">3.83122587203979</t>
@@ -5708,19 +5708,19 @@
     <t xml:space="preserve">3.83467674255371</t>
   </si>
   <si>
-    <t xml:space="preserve">3.77083706855774</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.83812713623047</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.68888139724731</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.68715596199036</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.68198013305664</t>
+    <t xml:space="preserve">3.77083683013916</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.83812737464905</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.68888092041016</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.68715620040894</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.68197965621948</t>
   </si>
   <si>
     <t xml:space="preserve">3.63366866111755</t>
@@ -5729,10 +5729,10 @@
     <t xml:space="preserve">3.73460388183594</t>
   </si>
   <si>
-    <t xml:space="preserve">3.80965828895569</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.805344581604</t>
+    <t xml:space="preserve">3.80965852737427</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.80534482002258</t>
   </si>
   <si>
     <t xml:space="preserve">3.894202709198</t>
@@ -5741,34 +5741,34 @@
     <t xml:space="preserve">4.02792024612427</t>
   </si>
   <si>
-    <t xml:space="preserve">3.99772596359253</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.07450532913208</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.12712955474854</t>
+    <t xml:space="preserve">3.99772572517395</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.07450580596924</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.12713003158569</t>
   </si>
   <si>
     <t xml:space="preserve">4.15646123886108</t>
   </si>
   <si>
-    <t xml:space="preserve">4.21943807601929</t>
+    <t xml:space="preserve">4.21943759918213</t>
   </si>
   <si>
     <t xml:space="preserve">4.25394630432129</t>
   </si>
   <si>
-    <t xml:space="preserve">4.12885522842407</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.1754412651062</t>
+    <t xml:space="preserve">4.12885475158691</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.17544078826904</t>
   </si>
   <si>
     <t xml:space="preserve">4.25653409957886</t>
   </si>
   <si>
-    <t xml:space="preserve">4.23237895965576</t>
+    <t xml:space="preserve">4.2323784828186</t>
   </si>
   <si>
     <t xml:space="preserve">4.10642576217651</t>
@@ -5786,19 +5786,19 @@
     <t xml:space="preserve">4.32382440567017</t>
   </si>
   <si>
-    <t xml:space="preserve">4.46013021469116</t>
+    <t xml:space="preserve">4.460129737854</t>
   </si>
   <si>
     <t xml:space="preserve">4.56710433959961</t>
   </si>
   <si>
-    <t xml:space="preserve">4.46925067901611</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.44730186462402</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.38420057296753</t>
+    <t xml:space="preserve">4.46925115585327</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.44730234146118</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.38420104980469</t>
   </si>
   <si>
     <t xml:space="preserve">4.41072130203247</t>
@@ -5810,7 +5810,7 @@
     <t xml:space="preserve">4.40066146850586</t>
   </si>
   <si>
-    <t xml:space="preserve">4.48205423355103</t>
+    <t xml:space="preserve">4.48205375671387</t>
   </si>
   <si>
     <t xml:space="preserve">4.39425992965698</t>
@@ -5819,19 +5819,19 @@
     <t xml:space="preserve">4.52137804031372</t>
   </si>
   <si>
-    <t xml:space="preserve">4.5094895362854</t>
+    <t xml:space="preserve">4.50949001312256</t>
   </si>
   <si>
     <t xml:space="preserve">4.51772022247314</t>
   </si>
   <si>
-    <t xml:space="preserve">4.37505531311035</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.35310697555542</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.47107982635498</t>
+    <t xml:space="preserve">4.37505483627319</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.35310745239258</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.47107934951782</t>
   </si>
   <si>
     <t xml:space="preserve">4.49760103225708</t>
@@ -5840,7 +5840,7 @@
     <t xml:space="preserve">4.43724250793457</t>
   </si>
   <si>
-    <t xml:space="preserve">4.27720165252686</t>
+    <t xml:space="preserve">4.27720212936401</t>
   </si>
   <si>
     <t xml:space="preserve">4.26805686950684</t>
@@ -5870,13 +5870,13 @@
     <t xml:space="preserve">4.4098072052002</t>
   </si>
   <si>
-    <t xml:space="preserve">4.39243078231812</t>
+    <t xml:space="preserve">4.39243125915527</t>
   </si>
   <si>
     <t xml:space="preserve">4.44181489944458</t>
   </si>
   <si>
-    <t xml:space="preserve">4.38968753814697</t>
+    <t xml:space="preserve">4.38968801498413</t>
   </si>
   <si>
     <t xml:space="preserve">4.3174409866333</t>
@@ -5891,7 +5891,7 @@
     <t xml:space="preserve">4.61283016204834</t>
   </si>
   <si>
-    <t xml:space="preserve">4.70611047744751</t>
+    <t xml:space="preserve">4.70611095428467</t>
   </si>
   <si>
     <t xml:space="preserve">4.64575290679932</t>
@@ -5900,13 +5900,13 @@
     <t xml:space="preserve">4.84145975112915</t>
   </si>
   <si>
-    <t xml:space="preserve">4.79939222335815</t>
+    <t xml:space="preserve">4.799391746521</t>
   </si>
   <si>
     <t xml:space="preserve">4.82134008407593</t>
   </si>
   <si>
-    <t xml:space="preserve">4.75549459457397</t>
+    <t xml:space="preserve">4.75549507141113</t>
   </si>
   <si>
     <t xml:space="preserve">4.7335467338562</t>
@@ -5915,13 +5915,13 @@
     <t xml:space="preserve">4.68782043457031</t>
   </si>
   <si>
-    <t xml:space="preserve">4.75183725357056</t>
+    <t xml:space="preserve">4.7518367767334</t>
   </si>
   <si>
     <t xml:space="preserve">4.77744340896606</t>
   </si>
   <si>
-    <t xml:space="preserve">4.80305004119873</t>
+    <t xml:space="preserve">4.80304956436157</t>
   </si>
   <si>
     <t xml:space="preserve">4.81768226623535</t>
@@ -5930,7 +5930,7 @@
     <t xml:space="preserve">4.98046636581421</t>
   </si>
   <si>
-    <t xml:space="preserve">4.96217632293701</t>
+    <t xml:space="preserve">4.96217584609985</t>
   </si>
   <si>
     <t xml:space="preserve">5.03533744812012</t>
@@ -5960,13 +5960,13 @@
     <t xml:space="preserve">4.27354383468628</t>
   </si>
   <si>
-    <t xml:space="preserve">4.32109880447388</t>
+    <t xml:space="preserve">4.32109832763672</t>
   </si>
   <si>
     <t xml:space="preserve">4.34121799468994</t>
   </si>
   <si>
-    <t xml:space="preserve">4.36956834793091</t>
+    <t xml:space="preserve">4.36956787109375</t>
   </si>
   <si>
     <t xml:space="preserve">4.35767936706543</t>
@@ -5987,7 +5987,7 @@
     <t xml:space="preserve">4.51497650146484</t>
   </si>
   <si>
-    <t xml:space="preserve">4.53052377700806</t>
+    <t xml:space="preserve">4.5305233001709</t>
   </si>
   <si>
     <t xml:space="preserve">4.51040410995483</t>
@@ -5996,28 +5996,28 @@
     <t xml:space="preserve">4.56618976593018</t>
   </si>
   <si>
-    <t xml:space="preserve">4.52686548233032</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.5543007850647</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.5360107421875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.62746238708496</t>
+    <t xml:space="preserve">4.52686500549316</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.55430126190186</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.53601026535034</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.6274619102478</t>
   </si>
   <si>
     <t xml:space="preserve">4.61831712722778</t>
   </si>
   <si>
-    <t xml:space="preserve">4.48662710189819</t>
+    <t xml:space="preserve">4.48662662506104</t>
   </si>
   <si>
     <t xml:space="preserve">4.46559238433838</t>
   </si>
   <si>
-    <t xml:space="preserve">4.49485683441162</t>
+    <t xml:space="preserve">4.49485731124878</t>
   </si>
   <si>
     <t xml:space="preserve">4.39700365066528</t>
@@ -6038,10 +6038,10 @@
     <t xml:space="preserve">4.46284914016724</t>
   </si>
   <si>
-    <t xml:space="preserve">4.53692531585693</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.54972791671753</t>
+    <t xml:space="preserve">4.53692483901978</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.54972839355469</t>
   </si>
   <si>
     <t xml:space="preserve">4.5122332572937</t>
@@ -6065,10 +6065,10 @@
     <t xml:space="preserve">4.4674220085144</t>
   </si>
   <si>
-    <t xml:space="preserve">4.67867565155029</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.7756142616272</t>
+    <t xml:space="preserve">4.67867517471313</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.77561473846436</t>
   </si>
   <si>
     <t xml:space="preserve">4.82499837875366</t>
@@ -6077,16 +6077,16 @@
     <t xml:space="preserve">4.86523723602295</t>
   </si>
   <si>
-    <t xml:space="preserve">5.26579618453979</t>
+    <t xml:space="preserve">5.26579570770264</t>
   </si>
   <si>
     <t xml:space="preserve">5.36639308929443</t>
   </si>
   <si>
-    <t xml:space="preserve">5.33529996871948</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.34078645706177</t>
+    <t xml:space="preserve">5.33529949188232</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.34078693389893</t>
   </si>
   <si>
     <t xml:space="preserve">5.33164167404175</t>
@@ -6098,7 +6098,7 @@
     <t xml:space="preserve">5.35541868209839</t>
   </si>
   <si>
-    <t xml:space="preserve">5.27677059173584</t>
+    <t xml:space="preserve">5.27677011489868</t>
   </si>
   <si>
     <t xml:space="preserve">5.22738647460938</t>
@@ -6140,10 +6140,10 @@
     <t xml:space="preserve">5.46516084671021</t>
   </si>
   <si>
-    <t xml:space="preserve">5.22555780410767</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.36456441879272</t>
+    <t xml:space="preserve">5.22555732727051</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.36456394195557</t>
   </si>
   <si>
     <t xml:space="preserve">5.3682222366333</t>
@@ -6152,13 +6152,13 @@
     <t xml:space="preserve">5.47430658340454</t>
   </si>
   <si>
-    <t xml:space="preserve">5.55112552642822</t>
+    <t xml:space="preserve">5.55112600326538</t>
   </si>
   <si>
     <t xml:space="preserve">5.43223857879639</t>
   </si>
   <si>
-    <t xml:space="preserve">5.55844163894653</t>
+    <t xml:space="preserve">5.55844211578369</t>
   </si>
   <si>
     <t xml:space="preserve">5.44504165649414</t>
@@ -6167,16 +6167,16 @@
     <t xml:space="preserve">5.4395546913147</t>
   </si>
   <si>
-    <t xml:space="preserve">5.42675161361694</t>
+    <t xml:space="preserve">5.42675113677979</t>
   </si>
   <si>
     <t xml:space="preserve">5.34444427490234</t>
   </si>
   <si>
-    <t xml:space="preserve">5.24933433532715</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.19812154769897</t>
+    <t xml:space="preserve">5.24933481216431</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.19812202453613</t>
   </si>
   <si>
     <t xml:space="preserve">5.23287343978882</t>
@@ -6194,7 +6194,7 @@
     <t xml:space="preserve">5.54380941390991</t>
   </si>
   <si>
-    <t xml:space="preserve">5.38651275634766</t>
+    <t xml:space="preserve">5.3865122795105</t>
   </si>
   <si>
     <t xml:space="preserve">5.29323148727417</t>
@@ -6218,19 +6218,19 @@
     <t xml:space="preserve">5.68098735809326</t>
   </si>
   <si>
-    <t xml:space="preserve">5.54929685592651</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.50174140930176</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.48162269592285</t>
+    <t xml:space="preserve">5.54929637908936</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.50174188613892</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.48162221908569</t>
   </si>
   <si>
     <t xml:space="preserve">5.53100633621216</t>
   </si>
   <si>
-    <t xml:space="preserve">5.60965442657471</t>
+    <t xml:space="preserve">5.60965490341187</t>
   </si>
   <si>
     <t xml:space="preserve">5.44687032699585</t>
@@ -6290,7 +6290,7 @@
     <t xml:space="preserve">6.12361431121826</t>
   </si>
   <si>
-    <t xml:space="preserve">6.03947830200195</t>
+    <t xml:space="preserve">6.03947877883911</t>
   </si>
   <si>
     <t xml:space="preserve">6.03033304214478</t>
@@ -6305,13 +6305,13 @@
     <t xml:space="preserve">6.30285978317261</t>
   </si>
   <si>
-    <t xml:space="preserve">5.82548093795776</t>
+    <t xml:space="preserve">5.82548141479492</t>
   </si>
   <si>
     <t xml:space="preserve">5.73220062255859</t>
   </si>
   <si>
-    <t xml:space="preserve">5.87852334976196</t>
+    <t xml:space="preserve">5.8785228729248</t>
   </si>
   <si>
     <t xml:space="preserve">5.90230083465576</t>
@@ -6323,7 +6323,7 @@
     <t xml:space="preserve">5.84742975234985</t>
   </si>
   <si>
-    <t xml:space="preserve">6.04679441452026</t>
+    <t xml:space="preserve">6.04679489135742</t>
   </si>
   <si>
     <t xml:space="preserve">6.13641738891602</t>
@@ -6338,7 +6338,7 @@
     <t xml:space="preserve">6.22055339813232</t>
   </si>
   <si>
-    <t xml:space="preserve">6.36321830749512</t>
+    <t xml:space="preserve">6.36321783065796</t>
   </si>
   <si>
     <t xml:space="preserve">6.48942184448242</t>
@@ -6356,7 +6356,7 @@
     <t xml:space="preserve">6.85157060623169</t>
   </si>
   <si>
-    <t xml:space="preserve">6.5607533454895</t>
+    <t xml:space="preserve">6.56075382232666</t>
   </si>
   <si>
     <t xml:space="preserve">6.77475118637085</t>
@@ -6392,19 +6392,19 @@
     <t xml:space="preserve">6.91375780105591</t>
   </si>
   <si>
-    <t xml:space="preserve">6.95765447616577</t>
+    <t xml:space="preserve">6.95765495300293</t>
   </si>
   <si>
     <t xml:space="preserve">7.01618385314941</t>
   </si>
   <si>
-    <t xml:space="preserve">7.1094651222229</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.08020067214966</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.00520944595337</t>
+    <t xml:space="preserve">7.10946464538574</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.0802001953125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.00520992279053</t>
   </si>
   <si>
     <t xml:space="preserve">6.82413530349731</t>
@@ -6434,13 +6434,13 @@
     <t xml:space="preserve">5.67915821075439</t>
   </si>
   <si>
-    <t xml:space="preserve">5.88766860961914</t>
+    <t xml:space="preserve">5.8876690864563</t>
   </si>
   <si>
     <t xml:space="preserve">6.05959796905518</t>
   </si>
   <si>
-    <t xml:space="preserve">6.16019487380981</t>
+    <t xml:space="preserve">6.16019535064697</t>
   </si>
   <si>
     <t xml:space="preserve">6.06874322891235</t>
@@ -6467,16 +6467,16 @@
     <t xml:space="preserve">6.72902488708496</t>
   </si>
   <si>
-    <t xml:space="preserve">6.76377725601196</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.71622228622437</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.94668054580688</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.17165231704712</t>
+    <t xml:space="preserve">6.7637767791748</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.71622180938721</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.94668102264404</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.17165184020996</t>
   </si>
   <si>
     <t xml:space="preserve">7.17713928222656</t>
@@ -6485,7 +6485,7 @@
     <t xml:space="preserve">7.26859092712402</t>
   </si>
   <si>
-    <t xml:space="preserve">7.28505277633667</t>
+    <t xml:space="preserve">7.28505229949951</t>
   </si>
   <si>
     <t xml:space="preserve">7.20091676712036</t>
@@ -6882,6 +6882,9 @@
   </si>
   <si>
     <t xml:space="preserve">10.4700002670288</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6199998855591</t>
   </si>
 </sst>
 </file>
@@ -72922,7 +72925,7 @@
     </row>
     <row r="2528">
       <c r="A2528" s="1" t="n">
-        <v>45999.6916435185</v>
+        <v>45999.3333333333</v>
       </c>
       <c r="B2528" t="n">
         <v>5017212</v>
@@ -72943,6 +72946,32 @@
         <v>2289</v>
       </c>
       <c r="H2528" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2529">
+      <c r="A2529" s="1" t="n">
+        <v>46000.6929398148</v>
+      </c>
+      <c r="B2529" t="n">
+        <v>7014100</v>
+      </c>
+      <c r="C2529" t="n">
+        <v>10.6899995803833</v>
+      </c>
+      <c r="D2529" t="n">
+        <v>10.4849996566772</v>
+      </c>
+      <c r="E2529" t="n">
+        <v>10.5200004577637</v>
+      </c>
+      <c r="F2529" t="n">
+        <v>10.6199998855591</v>
+      </c>
+      <c r="G2529" t="s">
+        <v>2290</v>
+      </c>
+      <c r="H2529" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/BPE.MI.xlsx
+++ b/data/BPE.MI.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2296" uniqueCount="2296">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2297" uniqueCount="2297">
   <si>
     <t xml:space="preserve">date</t>
   </si>
@@ -38,43 +38,43 @@
     <t xml:space="preserve">ticker</t>
   </si>
   <si>
-    <t xml:space="preserve">3.1975109577179</t>
+    <t xml:space="preserve">3.19751071929932</t>
   </si>
   <si>
     <t xml:space="preserve">BPE.MI</t>
   </si>
   <si>
-    <t xml:space="preserve">3.23759794235229</t>
+    <t xml:space="preserve">3.23759818077087</t>
   </si>
   <si>
     <t xml:space="preserve">3.09375762939453</t>
   </si>
   <si>
-    <t xml:space="preserve">3.02301597595215</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.95463156700134</t>
+    <t xml:space="preserve">3.02301573753357</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.9546320438385</t>
   </si>
   <si>
     <t xml:space="preserve">2.95699024200439</t>
   </si>
   <si>
-    <t xml:space="preserve">2.93340921401978</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.07489228248596</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.91690373420715</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.66223454475403</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.6504442691803</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.45708417892456</t>
+    <t xml:space="preserve">2.93340945243835</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.07489204406738</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.91690397262573</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.66223430633545</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.65044450759888</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.45708441734314</t>
   </si>
   <si>
     <t xml:space="preserve">2.7282600402832</t>
@@ -92,19 +92,19 @@
     <t xml:space="preserve">2.66695094108582</t>
   </si>
   <si>
-    <t xml:space="preserve">2.46651673316956</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.59385085105896</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.53018426895142</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.3580470085144</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.16280007362366</t>
+    <t xml:space="preserve">2.46651697158813</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.59385108947754</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.53018355369568</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.35804677009583</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.1627995967865</t>
   </si>
   <si>
     <t xml:space="preserve">2.17128896713257</t>
@@ -113,31 +113,31 @@
     <t xml:space="preserve">2.1260142326355</t>
   </si>
   <si>
-    <t xml:space="preserve">1.87228918075562</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.83173072338104</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.95812165737152</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.7704211473465</t>
+    <t xml:space="preserve">1.87228906154633</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.83173060417175</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.95812106132507</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.77042126655579</t>
   </si>
   <si>
     <t xml:space="preserve">1.974156498909</t>
   </si>
   <si>
-    <t xml:space="preserve">2.17411875724792</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.27975916862488</t>
+    <t xml:space="preserve">2.17411851882935</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.2797589302063</t>
   </si>
   <si>
     <t xml:space="preserve">2.33446645736694</t>
   </si>
   <si>
-    <t xml:space="preserve">2.32031726837158</t>
+    <t xml:space="preserve">2.32031750679016</t>
   </si>
   <si>
     <t xml:space="preserve">2.18166470527649</t>
@@ -146,112 +146,112 @@
     <t xml:space="preserve">2.40284967422485</t>
   </si>
   <si>
-    <t xml:space="preserve">2.31182861328125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.16468644142151</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.21845006942749</t>
+    <t xml:space="preserve">2.31182932853699</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.16468691825867</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.21844983100891</t>
   </si>
   <si>
     <t xml:space="preserve">2.25995135307312</t>
   </si>
   <si>
-    <t xml:space="preserve">2.22127985954285</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.25429177284241</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.36512064933777</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.32409048080444</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.33352303504944</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.21279072761536</t>
+    <t xml:space="preserve">2.22128009796143</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.25429201126099</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.36512088775635</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.32409071922302</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.33352255821228</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.21279048919678</t>
   </si>
   <si>
     <t xml:space="preserve">2.18072152137756</t>
   </si>
   <si>
-    <t xml:space="preserve">2.20524525642395</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.22505235671997</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.40992379188538</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.44293642044067</t>
+    <t xml:space="preserve">2.20524501800537</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.22505283355713</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.4099235534668</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.44293618202209</t>
   </si>
   <si>
     <t xml:space="preserve">2.3627622127533</t>
   </si>
   <si>
-    <t xml:space="preserve">2.20241498947144</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.22693872451782</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.246746301651</t>
+    <t xml:space="preserve">2.20241475105286</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.22693848609924</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.24674654006958</t>
   </si>
   <si>
     <t xml:space="preserve">2.24108719825745</t>
   </si>
   <si>
-    <t xml:space="preserve">2.20807504653931</t>
+    <t xml:space="preserve">2.20807456970215</t>
   </si>
   <si>
     <t xml:space="preserve">2.14770889282227</t>
   </si>
   <si>
-    <t xml:space="preserve">2.05904626846313</t>
+    <t xml:space="preserve">2.05904603004456</t>
   </si>
   <si>
     <t xml:space="preserve">2.03829503059387</t>
   </si>
   <si>
-    <t xml:space="preserve">1.97321271896362</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.00905585289001</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.89492619037628</t>
+    <t xml:space="preserve">1.97321307659149</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.00905609130859</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.89492607116699</t>
   </si>
   <si>
     <t xml:space="preserve">1.88455057144165</t>
   </si>
   <si>
-    <t xml:space="preserve">1.77325057983398</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.02697658538818</t>
+    <t xml:space="preserve">1.77325046062469</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.02697682380676</t>
   </si>
   <si>
     <t xml:space="preserve">2.12507176399231</t>
   </si>
   <si>
-    <t xml:space="preserve">2.04018211364746</t>
+    <t xml:space="preserve">2.0401816368103</t>
   </si>
   <si>
     <t xml:space="preserve">2.2741003036499</t>
   </si>
   <si>
-    <t xml:space="preserve">2.3769109249115</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.38398504257202</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.30428314208984</t>
+    <t xml:space="preserve">2.37691068649292</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.38398456573486</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.30428290367126</t>
   </si>
   <si>
     <t xml:space="preserve">2.37219476699829</t>
@@ -260,94 +260,94 @@
     <t xml:space="preserve">2.44765186309814</t>
   </si>
   <si>
-    <t xml:space="preserve">2.45944213867188</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.37455296516418</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.45236778259277</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.41464018821716</t>
+    <t xml:space="preserve">2.4594419002533</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.37455272674561</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.45236802101135</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.41464042663574</t>
   </si>
   <si>
     <t xml:space="preserve">2.50896143913269</t>
   </si>
   <si>
-    <t xml:space="preserve">2.40756511688232</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.31937384605408</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.2175076007843</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.19298338890076</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.13167381286621</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.07602429389954</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.07036447525024</t>
+    <t xml:space="preserve">2.4075653553009</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.31937408447266</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.21750712394714</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.19298362731934</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.13167405128479</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.07602453231812</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.07036471366882</t>
   </si>
   <si>
     <t xml:space="preserve">2.06470584869385</t>
   </si>
   <si>
-    <t xml:space="preserve">2.0326361656189</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.02980589866638</t>
+    <t xml:space="preserve">2.03263640403748</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.02980637550354</t>
   </si>
   <si>
     <t xml:space="preserve">2.06093263626099</t>
   </si>
   <si>
-    <t xml:space="preserve">2.17506146430969</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.07319498062134</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.09960412979126</t>
+    <t xml:space="preserve">2.17506217956543</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.07319450378418</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.09960460662842</t>
   </si>
   <si>
     <t xml:space="preserve">2.05811405181885</t>
   </si>
   <si>
-    <t xml:space="preserve">2.22021555900574</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.3311779499054</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.28582787513733</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.29161810874939</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.3138108253479</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.19416356086731</t>
+    <t xml:space="preserve">2.22021532058716</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.33117771148682</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.28582835197449</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.29161787033081</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.31381034851074</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.19416379928589</t>
   </si>
   <si>
     <t xml:space="preserve">2.16618204116821</t>
   </si>
   <si>
-    <t xml:space="preserve">2.07934165000916</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.06969285011292</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.09670901298523</t>
+    <t xml:space="preserve">2.07934141159058</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.06969261169434</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.09670925140381</t>
   </si>
   <si>
     <t xml:space="preserve">2.13627004623413</t>
@@ -356,25 +356,25 @@
     <t xml:space="preserve">1.99636089801788</t>
   </si>
   <si>
-    <t xml:space="preserve">1.87478411197662</t>
+    <t xml:space="preserve">1.87478399276733</t>
   </si>
   <si>
     <t xml:space="preserve">1.82171511650085</t>
   </si>
   <si>
-    <t xml:space="preserve">1.81592643260956</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.76864624023438</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.9442572593689</t>
+    <t xml:space="preserve">1.81592655181885</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.76864612102509</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.94425702095032</t>
   </si>
   <si>
     <t xml:space="preserve">2.03206157684326</t>
   </si>
   <si>
-    <t xml:space="preserve">2.08416533470154</t>
+    <t xml:space="preserve">2.08416557312012</t>
   </si>
   <si>
     <t xml:space="preserve">2.07548236846924</t>
@@ -383,127 +383,127 @@
     <t xml:space="preserve">2.23468899726868</t>
   </si>
   <si>
-    <t xml:space="preserve">1.68470084667206</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.66733312606812</t>
+    <t xml:space="preserve">1.68470108509064</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.66733288764954</t>
   </si>
   <si>
     <t xml:space="preserve">1.62777173519135</t>
   </si>
   <si>
-    <t xml:space="preserve">1.53900170326233</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.58145773410797</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.50523042678833</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.40391719341278</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.40488231182098</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.30453324317932</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.24567449092865</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.44733703136444</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.51487970352173</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.63838601112366</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.5563702583313</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.62294816970825</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.64224541187286</t>
+    <t xml:space="preserve">1.53900194168091</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.58145749568939</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.50523066520691</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.40391731262207</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.40488243103027</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.30453312397003</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.24567484855652</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.44733715057373</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.5148800611496</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.63838613033295</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.55637001991272</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.62294805049896</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.64224553108215</t>
   </si>
   <si>
     <t xml:space="preserve">1.65189468860626</t>
   </si>
   <si>
-    <t xml:space="preserve">1.63645589351654</t>
+    <t xml:space="preserve">1.63645601272583</t>
   </si>
   <si>
     <t xml:space="preserve">1.65382409095764</t>
   </si>
   <si>
-    <t xml:space="preserve">1.70689308643341</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.69434940814972</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.64899957180023</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.65671849250793</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.73294532299042</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.67891144752502</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.77057671546936</t>
+    <t xml:space="preserve">1.7068932056427</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.6943496465683</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.64899969100952</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.65671861171722</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.73294544219971</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.67891132831573</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.77057635784149</t>
   </si>
   <si>
     <t xml:space="preserve">1.67022740840912</t>
   </si>
   <si>
-    <t xml:space="preserve">1.46374022960663</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.52259886264801</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.53031778335571</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.73005068302155</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.69820916652679</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.7319803237915</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.72136700153351</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.72040200233459</t>
+    <t xml:space="preserve">1.46374034881592</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.5225989818573</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.530317902565</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.7300511598587</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.6982090473175</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.73198056221008</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.72136676311493</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.72040188312531</t>
   </si>
   <si>
     <t xml:space="preserve">1.69627976417542</t>
   </si>
   <si>
-    <t xml:space="preserve">1.68373608589172</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.62101769447327</t>
+    <t xml:space="preserve">1.68373596668243</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.62101745605469</t>
   </si>
   <si>
     <t xml:space="preserve">1.64996469020844</t>
   </si>
   <si>
-    <t xml:space="preserve">1.55444025993347</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.5650542974472</t>
+    <t xml:space="preserve">1.55444037914276</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.56505441665649</t>
   </si>
   <si>
     <t xml:space="preserve">1.65478944778442</t>
@@ -512,58 +512,58 @@
     <t xml:space="preserve">1.69048988819122</t>
   </si>
   <si>
-    <t xml:space="preserve">1.64128077030182</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.60750913619995</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.65285921096802</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.66443800926208</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.69531452655792</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.7184716463089</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.68759536743164</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.7445240020752</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.74741840362549</t>
+    <t xml:space="preserve">1.64128041267395</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.60750901699066</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.65285909175873</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.66443824768066</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.69531464576721</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.71847188472748</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.68759560585022</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.74452388286591</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.74741864204407</t>
   </si>
   <si>
     <t xml:space="preserve">1.7126829624176</t>
   </si>
   <si>
-    <t xml:space="preserve">1.67987620830536</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.63549160957336</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.5804922580719</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.60461485385895</t>
+    <t xml:space="preserve">1.67987632751465</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.63549172878265</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.58049261569977</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.60461449623108</t>
   </si>
   <si>
     <t xml:space="preserve">1.53610754013062</t>
   </si>
   <si>
-    <t xml:space="preserve">1.60847413539886</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.61233389377594</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.5399671792984</t>
+    <t xml:space="preserve">1.60847425460815</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.61233365535736</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.53996706008911</t>
   </si>
   <si>
     <t xml:space="preserve">1.51584494113922</t>
@@ -572,7 +572,7 @@
     <t xml:space="preserve">1.54961609840393</t>
   </si>
   <si>
-    <t xml:space="preserve">1.55251097679138</t>
+    <t xml:space="preserve">1.5525107383728</t>
   </si>
   <si>
     <t xml:space="preserve">1.59786081314087</t>
@@ -581,169 +581,169 @@
     <t xml:space="preserve">1.561194896698</t>
   </si>
   <si>
-    <t xml:space="preserve">1.63452649116516</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.63935077190399</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.61619305610657</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.67408668994904</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.77540063858032</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.81496119499207</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.73583984375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.82653963565826</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.86513555049896</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.9606602191925</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.05425453186035</t>
+    <t xml:space="preserve">1.63452637195587</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.63935101032257</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.61619317531586</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.6740870475769</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.7754008769989</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.8149608373642</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.73583996295929</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.82653951644897</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.86513578891754</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.96065998077393</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.05425429344177</t>
   </si>
   <si>
     <t xml:space="preserve">2.04942965507507</t>
   </si>
   <si>
-    <t xml:space="preserve">2.10153365135193</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.01372933387756</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.04653573036194</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.09477949142456</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.08899021148682</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.0619740486145</t>
+    <t xml:space="preserve">2.10153388977051</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.01372909545898</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.04653549194336</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.09477972984314</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.0889904499054</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.06197381019592</t>
   </si>
   <si>
     <t xml:space="preserve">2.04460549354553</t>
   </si>
   <si>
-    <t xml:space="preserve">1.92978322505951</t>
+    <t xml:space="preserve">1.92978346347809</t>
   </si>
   <si>
     <t xml:space="preserve">1.90566098690033</t>
   </si>
   <si>
-    <t xml:space="preserve">1.88443350791931</t>
+    <t xml:space="preserve">1.88443374633789</t>
   </si>
   <si>
     <t xml:space="preserve">1.95004606246948</t>
   </si>
   <si>
-    <t xml:space="preserve">1.9867115020752</t>
+    <t xml:space="preserve">1.98671185970306</t>
   </si>
   <si>
     <t xml:space="preserve">2.01565861701965</t>
   </si>
   <si>
-    <t xml:space="preserve">2.01662349700928</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.99539589881897</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.98574662208557</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.92785310745239</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.84583735466003</t>
+    <t xml:space="preserve">2.01662373542786</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.99539613723755</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.98574686050415</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.92785322666168</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.84583747386932</t>
   </si>
   <si>
     <t xml:space="preserve">1.80820715427399</t>
   </si>
   <si>
-    <t xml:space="preserve">1.80048727989197</t>
+    <t xml:space="preserve">1.80048751831055</t>
   </si>
   <si>
     <t xml:space="preserve">1.83715415000916</t>
   </si>
   <si>
-    <t xml:space="preserve">1.82750487327576</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.83329379558563</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.80531203746796</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.82847023010254</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.97513341903687</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.93557286262512</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.06679821014404</t>
+    <t xml:space="preserve">1.82750499248505</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.83329403400421</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.80531191825867</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.82846975326538</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.97513318061829</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.9355731010437</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.06679797172546</t>
   </si>
   <si>
     <t xml:space="preserve">2.28196859359741</t>
   </si>
   <si>
-    <t xml:space="preserve">2.31477499008179</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.27907371520996</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.32152938842773</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.37073874473572</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.3321430683136</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.3948609828949</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.41464138031006</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.39775586128235</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.41222929954529</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.46529865264893</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.48942041397095</t>
+    <t xml:space="preserve">2.31477522850037</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.27907395362854</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.32153010368347</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.3707389831543</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.33214282989502</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.39486122131348</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.41464161872864</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.39775562286377</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.41222977638245</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.46529817581177</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.48942089080811</t>
   </si>
   <si>
     <t xml:space="preserve">2.49665713310242</t>
   </si>
   <si>
-    <t xml:space="preserve">2.44117641448975</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.54248952865601</t>
+    <t xml:space="preserve">2.44117617607117</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.54249000549316</t>
   </si>
   <si>
     <t xml:space="preserve">2.63897848129272</t>
@@ -752,7 +752,7 @@
     <t xml:space="preserve">2.59555864334106</t>
   </si>
   <si>
-    <t xml:space="preserve">2.55696272850037</t>
+    <t xml:space="preserve">2.55696225166321</t>
   </si>
   <si>
     <t xml:space="preserve">2.42911505699158</t>
@@ -764,16 +764,16 @@
     <t xml:space="preserve">2.56178736686707</t>
   </si>
   <si>
-    <t xml:space="preserve">2.53766489028931</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.57867288589478</t>
+    <t xml:space="preserve">2.53766465187073</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.57867312431335</t>
   </si>
   <si>
     <t xml:space="preserve">2.58832216262817</t>
   </si>
   <si>
-    <t xml:space="preserve">2.72823166847229</t>
+    <t xml:space="preserve">2.72823119163513</t>
   </si>
   <si>
     <t xml:space="preserve">2.77165126800537</t>
@@ -782,28 +782,28 @@
     <t xml:space="preserve">2.7065212726593</t>
   </si>
   <si>
-    <t xml:space="preserve">2.71375727653503</t>
+    <t xml:space="preserve">2.71375751495361</t>
   </si>
   <si>
     <t xml:space="preserve">2.74752902984619</t>
   </si>
   <si>
-    <t xml:space="preserve">2.70410943031311</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.57626128196716</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.52801585197449</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.58590960502625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.59797024726868</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.66068840026855</t>
+    <t xml:space="preserve">2.70410919189453</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.57626080513</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.52801609039307</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.58590936660767</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.5979700088501</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.66068887710571</t>
   </si>
   <si>
     <t xml:space="preserve">2.50871849060059</t>
@@ -812,73 +812,73 @@
     <t xml:space="preserve">2.42187786102295</t>
   </si>
   <si>
-    <t xml:space="preserve">2.45082497596741</t>
+    <t xml:space="preserve">2.45082473754883</t>
   </si>
   <si>
     <t xml:space="preserve">2.2945122718811</t>
   </si>
   <si>
-    <t xml:space="preserve">2.30223107337952</t>
+    <t xml:space="preserve">2.3022313117981</t>
   </si>
   <si>
     <t xml:space="preserve">2.38135266304016</t>
   </si>
   <si>
-    <t xml:space="preserve">2.32056427001953</t>
+    <t xml:space="preserve">2.32056450843811</t>
   </si>
   <si>
     <t xml:space="preserve">2.24047803878784</t>
   </si>
   <si>
-    <t xml:space="preserve">2.17100596427917</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.1478488445282</t>
+    <t xml:space="preserve">2.17100644111633</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.14784860610962</t>
   </si>
   <si>
     <t xml:space="preserve">2.14495444297791</t>
   </si>
   <si>
-    <t xml:space="preserve">2.06293892860413</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.02627277374268</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.99732601642609</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.16135740280151</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.17004179954529</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.26749563217163</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.20574235916138</t>
+    <t xml:space="preserve">2.06293845176697</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.0262725353241</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.9973258972168</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.16135716438293</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.17004156112671</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.26749539375305</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.20574283599854</t>
   </si>
   <si>
     <t xml:space="preserve">2.113112449646</t>
   </si>
   <si>
-    <t xml:space="preserve">2.11793684959412</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.18837451934814</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.25977635383606</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.22214579582214</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.16521739959717</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.16907620429993</t>
+    <t xml:space="preserve">2.11793732643127</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.18837404251099</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.25977611541748</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.22214555740356</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.16521716117859</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.16907644271851</t>
   </si>
   <si>
     <t xml:space="preserve">2.27714467048645</t>
@@ -887,7 +887,7 @@
     <t xml:space="preserve">2.25012731552124</t>
   </si>
   <si>
-    <t xml:space="preserve">2.31767010688782</t>
+    <t xml:space="preserve">2.3176703453064</t>
   </si>
   <si>
     <t xml:space="preserve">2.32635402679443</t>
@@ -896,61 +896,61 @@
     <t xml:space="preserve">2.39196681976318</t>
   </si>
   <si>
-    <t xml:space="preserve">2.36494922637939</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.32249402999878</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.33696722984314</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.29354763031006</t>
+    <t xml:space="preserve">2.36494946479797</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.3224937915802</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.33696794509888</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.29354786872864</t>
   </si>
   <si>
     <t xml:space="preserve">2.26267075538635</t>
   </si>
   <si>
-    <t xml:space="preserve">2.25784635543823</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.17872524261475</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.1951277256012</t>
+    <t xml:space="preserve">2.25784659385681</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.17872500419617</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.19512796401978</t>
   </si>
   <si>
     <t xml:space="preserve">2.19319891929626</t>
   </si>
   <si>
-    <t xml:space="preserve">2.20960187911987</t>
+    <t xml:space="preserve">2.20960235595703</t>
   </si>
   <si>
     <t xml:space="preserve">2.17390131950378</t>
   </si>
   <si>
-    <t xml:space="preserve">2.12179636955261</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.1044294834137</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.21153116226196</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.36398458480835</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.39872050285339</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.34661674499512</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.41946578025818</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.48218393325806</t>
+    <t xml:space="preserve">2.12179660797119</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.10442876815796</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.21153163909912</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.36398434638977</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.39872097969055</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.3466169834137</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.41946601867676</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.48218417167664</t>
   </si>
   <si>
     <t xml:space="preserve">2.51836752891541</t>
@@ -959,10 +959,10 @@
     <t xml:space="preserve">2.45564937591553</t>
   </si>
   <si>
-    <t xml:space="preserve">2.43635177612305</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.29837155342102</t>
+    <t xml:space="preserve">2.43635201454163</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.2983717918396</t>
   </si>
   <si>
     <t xml:space="preserve">2.26170587539673</t>
@@ -971,34 +971,34 @@
     <t xml:space="preserve">2.34468650817871</t>
   </si>
   <si>
-    <t xml:space="preserve">2.30609059333801</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.25302147865295</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.22696995735168</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.26074171066284</t>
+    <t xml:space="preserve">2.30609083175659</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.25302195549011</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.22697043418884</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.26074147224426</t>
   </si>
   <si>
     <t xml:space="preserve">2.24998950958252</t>
   </si>
   <si>
-    <t xml:space="preserve">2.25096702575684</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.2822437286377</t>
+    <t xml:space="preserve">2.25096726417542</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.28224396705627</t>
   </si>
   <si>
     <t xml:space="preserve">2.27931189537048</t>
   </si>
   <si>
-    <t xml:space="preserve">2.25292158126831</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.18450379371643</t>
+    <t xml:space="preserve">2.25292181968689</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.18450355529785</t>
   </si>
   <si>
     <t xml:space="preserve">2.18548107147217</t>
@@ -1007,28 +1007,28 @@
     <t xml:space="preserve">2.13074636459351</t>
   </si>
   <si>
-    <t xml:space="preserve">2.17570686340332</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.14833974838257</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.10924315452576</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.07698917388916</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.08089876174927</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.15811324119568</t>
+    <t xml:space="preserve">2.17570662498474</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.14833998680115</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.10924339294434</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.07698893547058</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.08089828491211</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.15811347961426</t>
   </si>
   <si>
     <t xml:space="preserve">2.15127182006836</t>
   </si>
   <si>
-    <t xml:space="preserve">2.10631132125854</t>
+    <t xml:space="preserve">2.10631084442139</t>
   </si>
   <si>
     <t xml:space="preserve">2.15909099578857</t>
@@ -1037,46 +1037,46 @@
     <t xml:space="preserve">2.13758778572083</t>
   </si>
   <si>
-    <t xml:space="preserve">2.04082465171814</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.05353045463562</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.00075149536133</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.0906720161438</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.081876039505</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.13661003112793</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.14931631088257</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.16886520385742</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.15713596343994</t>
+    <t xml:space="preserve">2.04082441329956</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.05353093147278</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.00075101852417</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.09067225456238</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.08187627792358</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.13661050796509</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.14931654930115</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.168865442276</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.15713572502136</t>
   </si>
   <si>
     <t xml:space="preserve">2.13367819786072</t>
   </si>
   <si>
-    <t xml:space="preserve">2.27149271965027</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.34870767593384</t>
+    <t xml:space="preserve">2.27149295806885</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.34870743751526</t>
   </si>
   <si>
     <t xml:space="preserve">2.29201793670654</t>
   </si>
   <si>
-    <t xml:space="preserve">2.29788279533386</t>
+    <t xml:space="preserve">2.29788327217102</t>
   </si>
   <si>
     <t xml:space="preserve">2.29104065895081</t>
@@ -1085,7 +1085,7 @@
     <t xml:space="preserve">2.3223180770874</t>
   </si>
   <si>
-    <t xml:space="preserve">2.36434674263</t>
+    <t xml:space="preserve">2.36434650421143</t>
   </si>
   <si>
     <t xml:space="preserve">2.41419434547424</t>
@@ -1097,13 +1097,13 @@
     <t xml:space="preserve">2.41908144950867</t>
   </si>
   <si>
-    <t xml:space="preserve">2.4337420463562</t>
+    <t xml:space="preserve">2.43374180793762</t>
   </si>
   <si>
     <t xml:space="preserve">2.354572057724</t>
   </si>
   <si>
-    <t xml:space="preserve">2.37021040916443</t>
+    <t xml:space="preserve">2.37021064758301</t>
   </si>
   <si>
     <t xml:space="preserve">2.30667948722839</t>
@@ -1112,28 +1112,28 @@
     <t xml:space="preserve">2.28126692771912</t>
   </si>
   <si>
-    <t xml:space="preserve">2.25389933586121</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.28713083267212</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.29885983467102</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.27344703674316</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.26953721046448</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.31352090835571</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.45329022407532</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.42005801200867</t>
+    <t xml:space="preserve">2.25389909744263</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.28713130950928</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.29885959625244</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.27344751358032</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.26953744888306</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.31352114677429</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.45328998565674</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.42005825042725</t>
   </si>
   <si>
     <t xml:space="preserve">2.40246534347534</t>
@@ -1148,91 +1148,91 @@
     <t xml:space="preserve">2.38389444351196</t>
   </si>
   <si>
-    <t xml:space="preserve">2.35750436782837</t>
+    <t xml:space="preserve">2.35750412940979</t>
   </si>
   <si>
     <t xml:space="preserve">2.32622766494751</t>
   </si>
   <si>
-    <t xml:space="preserve">2.29690551757812</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.31938481330872</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.3291597366333</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.2685604095459</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.29299569129944</t>
+    <t xml:space="preserve">2.29690527915955</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.31938505172729</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.32915997505188</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.26856064796448</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.29299545288086</t>
   </si>
   <si>
     <t xml:space="preserve">2.31254386901855</t>
   </si>
   <si>
-    <t xml:space="preserve">2.34382104873657</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.30863404273987</t>
+    <t xml:space="preserve">2.34382081031799</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.30863380432129</t>
   </si>
   <si>
     <t xml:space="preserve">2.27247023582458</t>
   </si>
   <si>
-    <t xml:space="preserve">2.23337364196777</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.21382594108582</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.27735733985901</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.34773063659668</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.30081462860107</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.2421703338623</t>
+    <t xml:space="preserve">2.23337388038635</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.21382570266724</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.27735710144043</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.34773087501526</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.30081510543823</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.24217009544373</t>
   </si>
   <si>
     <t xml:space="preserve">2.26269602775574</t>
   </si>
   <si>
-    <t xml:space="preserve">2.29006385803223</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.33795595169067</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.2861533164978</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.35359454154968</t>
+    <t xml:space="preserve">2.29006361961365</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.33795642852783</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.28615307807922</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.35359477996826</t>
   </si>
   <si>
     <t xml:space="preserve">2.42299103736877</t>
   </si>
   <si>
-    <t xml:space="preserve">2.46306467056274</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.47283887863159</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.51437878608704</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.50704741477966</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.43276429176331</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.39171361923218</t>
+    <t xml:space="preserve">2.46306419372559</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.47283864021301</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.51437854766846</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.50704717636108</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.43276453018188</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.39171385765076</t>
   </si>
   <si>
     <t xml:space="preserve">2.26171851158142</t>
@@ -1241,13 +1241,13 @@
     <t xml:space="preserve">2.19525480270386</t>
   </si>
   <si>
-    <t xml:space="preserve">2.14736223220825</t>
+    <t xml:space="preserve">2.14736175537109</t>
   </si>
   <si>
     <t xml:space="preserve">2.17081952095032</t>
   </si>
   <si>
-    <t xml:space="preserve">2.14638471603394</t>
+    <t xml:space="preserve">2.14638447761536</t>
   </si>
   <si>
     <t xml:space="preserve">2.14051985740662</t>
@@ -1256,40 +1256,40 @@
     <t xml:space="preserve">2.07210183143616</t>
   </si>
   <si>
-    <t xml:space="preserve">2.0789430141449</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.09946894645691</t>
+    <t xml:space="preserve">2.07894325256348</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.09946870803833</t>
   </si>
   <si>
     <t xml:space="preserve">2.07601118087769</t>
   </si>
   <si>
-    <t xml:space="preserve">2.04375720024109</t>
+    <t xml:space="preserve">2.04375743865967</t>
   </si>
   <si>
     <t xml:space="preserve">2.05450820922852</t>
   </si>
   <si>
-    <t xml:space="preserve">2.04473400115967</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.03886985778809</t>
+    <t xml:space="preserve">2.04473423957825</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.03887009620667</t>
   </si>
   <si>
     <t xml:space="preserve">2.11315298080444</t>
   </si>
   <si>
-    <t xml:space="preserve">2.05939555168152</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.02616381645203</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.98804450035095</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.90105581283569</t>
+    <t xml:space="preserve">2.05939531326294</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.02616357803345</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.98804461956024</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.90105557441711</t>
   </si>
   <si>
     <t xml:space="preserve">2.08969521522522</t>
@@ -1298,49 +1298,49 @@
     <t xml:space="preserve">2.06721472740173</t>
   </si>
   <si>
-    <t xml:space="preserve">2.08578562736511</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.03984761238098</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.08285307884216</t>
+    <t xml:space="preserve">2.08578586578369</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.0398473739624</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.08285284042358</t>
   </si>
   <si>
     <t xml:space="preserve">2.01345705986023</t>
   </si>
   <si>
-    <t xml:space="preserve">2.0466890335083</t>
+    <t xml:space="preserve">2.04668927192688</t>
   </si>
   <si>
     <t xml:space="preserve">2.01834487915039</t>
   </si>
   <si>
-    <t xml:space="preserve">2.00661563873291</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.06623721122742</t>
+    <t xml:space="preserve">2.00661540031433</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.06623697280884</t>
   </si>
   <si>
     <t xml:space="preserve">2.16202306747437</t>
   </si>
   <si>
-    <t xml:space="preserve">2.24607968330383</t>
+    <t xml:space="preserve">2.24608016014099</t>
   </si>
   <si>
     <t xml:space="preserve">2.17961668968201</t>
   </si>
   <si>
-    <t xml:space="preserve">2.2382607460022</t>
+    <t xml:space="preserve">2.23826122283936</t>
   </si>
   <si>
     <t xml:space="preserve">2.22653222084045</t>
   </si>
   <si>
-    <t xml:space="preserve">2.19916439056396</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.27051520347595</t>
+    <t xml:space="preserve">2.19916462898254</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.27051472663879</t>
   </si>
   <si>
     <t xml:space="preserve">2.21773552894592</t>
@@ -1349,16 +1349,16 @@
     <t xml:space="preserve">2.07796597480774</t>
   </si>
   <si>
-    <t xml:space="preserve">2.03691506385803</t>
+    <t xml:space="preserve">2.03691458702087</t>
   </si>
   <si>
     <t xml:space="preserve">2.03105068206787</t>
   </si>
   <si>
-    <t xml:space="preserve">2.09849214553833</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.08676242828369</t>
+    <t xml:space="preserve">2.09849190711975</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.08676218986511</t>
   </si>
   <si>
     <t xml:space="preserve">2.08871793746948</t>
@@ -1373,55 +1373,55 @@
     <t xml:space="preserve">2.11510801315308</t>
   </si>
   <si>
-    <t xml:space="preserve">2.05744004249573</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.03300547599792</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.07307958602905</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.07503390312195</t>
+    <t xml:space="preserve">2.05744051933289</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.03300499916077</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.07307934761047</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.07503414154053</t>
   </si>
   <si>
     <t xml:space="preserve">2.11119747161865</t>
   </si>
   <si>
-    <t xml:space="preserve">2.20600652694702</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.22848653793335</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.20405125617981</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.16104531288147</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.26074147224426</t>
+    <t xml:space="preserve">2.20600700378418</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.22848677635193</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.20405173301697</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.16104555130005</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.26074123382568</t>
   </si>
   <si>
     <t xml:space="preserve">2.35261702537537</t>
   </si>
   <si>
-    <t xml:space="preserve">2.35066246986389</t>
+    <t xml:space="preserve">2.35066270828247</t>
   </si>
   <si>
     <t xml:space="preserve">2.36776733398438</t>
   </si>
   <si>
-    <t xml:space="preserve">2.27686834335327</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.29543876647949</t>
+    <t xml:space="preserve">2.27686858177185</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.29543900489807</t>
   </si>
   <si>
     <t xml:space="preserve">2.27784538269043</t>
   </si>
   <si>
-    <t xml:space="preserve">2.21578049659729</t>
+    <t xml:space="preserve">2.21578001976013</t>
   </si>
   <si>
     <t xml:space="preserve">2.22408819198608</t>
@@ -1430,22 +1430,22 @@
     <t xml:space="preserve">2.30179238319397</t>
   </si>
   <si>
-    <t xml:space="preserve">2.25194478034973</t>
+    <t xml:space="preserve">2.25194501876831</t>
   </si>
   <si>
     <t xml:space="preserve">2.22213387489319</t>
   </si>
   <si>
-    <t xml:space="preserve">2.33746743202209</t>
+    <t xml:space="preserve">2.33746767044067</t>
   </si>
   <si>
     <t xml:space="preserve">2.34186601638794</t>
   </si>
   <si>
-    <t xml:space="preserve">2.33209133148193</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.33600091934204</t>
+    <t xml:space="preserve">2.33209156990051</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.33600115776062</t>
   </si>
   <si>
     <t xml:space="preserve">2.28957509994507</t>
@@ -1460,13 +1460,13 @@
     <t xml:space="preserve">2.38145136833191</t>
   </si>
   <si>
-    <t xml:space="preserve">2.37900710105896</t>
+    <t xml:space="preserve">2.37900733947754</t>
   </si>
   <si>
     <t xml:space="preserve">2.40735220909119</t>
   </si>
   <si>
-    <t xml:space="preserve">2.38731527328491</t>
+    <t xml:space="preserve">2.38731503486633</t>
   </si>
   <si>
     <t xml:space="preserve">2.20551776885986</t>
@@ -1475,19 +1475,19 @@
     <t xml:space="preserve">2.29592776298523</t>
   </si>
   <si>
-    <t xml:space="preserve">2.32720518112183</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.25438785552979</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.29641652107239</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.24461388587952</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.24901223182678</t>
+    <t xml:space="preserve">2.32720494270325</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.25438809394836</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.29641675949097</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.24461364746094</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.2490119934082</t>
   </si>
   <si>
     <t xml:space="preserve">2.27540254592896</t>
@@ -1496,19 +1496,19 @@
     <t xml:space="preserve">2.28322124481201</t>
   </si>
   <si>
-    <t xml:space="preserve">2.26758313179016</t>
+    <t xml:space="preserve">2.26758289337158</t>
   </si>
   <si>
     <t xml:space="preserve">2.22359919548035</t>
   </si>
   <si>
-    <t xml:space="preserve">2.22995281219482</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.21040487289429</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.22555446624756</t>
+    <t xml:space="preserve">2.2299530506134</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.21040511131287</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.22555422782898</t>
   </si>
   <si>
     <t xml:space="preserve">2.2069833278656</t>
@@ -1517,10 +1517,10 @@
     <t xml:space="preserve">2.20893859863281</t>
   </si>
   <si>
-    <t xml:space="preserve">2.29446148872375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.30276942253113</t>
+    <t xml:space="preserve">2.29446125030518</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.30276918411255</t>
   </si>
   <si>
     <t xml:space="preserve">2.31156611442566</t>
@@ -1535,31 +1535,31 @@
     <t xml:space="preserve">2.35652732849121</t>
   </si>
   <si>
-    <t xml:space="preserve">2.36287999153137</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.38829255104065</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.34479784965515</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.31547546386719</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.33013725280762</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.31889724731445</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.33062601089478</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.31303215026855</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.3057017326355</t>
+    <t xml:space="preserve">2.36288022994995</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.38829302787781</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.34479832649231</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.31547594070435</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.33013701438904</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.31889700889587</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.33062624931335</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.31303262710571</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.30570197105408</t>
   </si>
   <si>
     <t xml:space="preserve">2.3966007232666</t>
@@ -1577,91 +1577,91 @@
     <t xml:space="preserve">2.51584410667419</t>
   </si>
   <si>
-    <t xml:space="preserve">2.44204998016357</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.44253897666931</t>
+    <t xml:space="preserve">2.44205021858215</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.44253921508789</t>
   </si>
   <si>
     <t xml:space="preserve">2.28028964996338</t>
   </si>
   <si>
-    <t xml:space="preserve">2.30131053924561</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.33834767341614</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.36387276649475</t>
+    <t xml:space="preserve">2.30131030082703</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.33834743499756</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.36387324333191</t>
   </si>
   <si>
     <t xml:space="preserve">2.33484387397766</t>
   </si>
   <si>
-    <t xml:space="preserve">2.28779649734497</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.15416240692139</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.0455539226532</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.05306124687195</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.0535614490509</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.21522378921509</t>
+    <t xml:space="preserve">2.28779673576355</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.15416216850281</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.04555368423462</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.05306077003479</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.05356168746948</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.21522402763367</t>
   </si>
   <si>
     <t xml:space="preserve">2.15015840530396</t>
   </si>
   <si>
-    <t xml:space="preserve">2.07708501815796</t>
+    <t xml:space="preserve">2.07708477973938</t>
   </si>
   <si>
     <t xml:space="preserve">2.07608461380005</t>
   </si>
   <si>
-    <t xml:space="preserve">2.11612415313721</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.05906748771667</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.14865732192993</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.17418313026428</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.20921754837036</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.23624515533447</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.17768621444702</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.16717553138733</t>
+    <t xml:space="preserve">2.11612391471863</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.05906701087952</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.14865756034851</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.1741828918457</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.20921778678894</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.23624491691589</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.1776864528656</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.16717529296875</t>
   </si>
   <si>
     <t xml:space="preserve">2.24074959754944</t>
   </si>
   <si>
-    <t xml:space="preserve">2.29730629920959</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.22973871231079</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.39390301704407</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.34485459327698</t>
+    <t xml:space="preserve">2.29730653762817</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.22973895072937</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.39390325546265</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.3448543548584</t>
   </si>
   <si>
     <t xml:space="preserve">2.35786747932434</t>
@@ -1673,13 +1673,13 @@
     <t xml:space="preserve">2.34535479545593</t>
   </si>
   <si>
-    <t xml:space="preserve">2.35586524009705</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.34685587882996</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.34935903549194</t>
+    <t xml:space="preserve">2.35586500167847</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.34685611724854</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.34935879707336</t>
   </si>
   <si>
     <t xml:space="preserve">2.34034991264343</t>
@@ -1688,10 +1688,10 @@
     <t xml:space="preserve">2.3863959312439</t>
   </si>
   <si>
-    <t xml:space="preserve">2.39440369606018</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.34785723686218</t>
+    <t xml:space="preserve">2.39440393447876</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.3478569984436</t>
   </si>
   <si>
     <t xml:space="preserve">2.30881786346436</t>
@@ -1703,22 +1703,22 @@
     <t xml:space="preserve">2.35686635971069</t>
   </si>
   <si>
-    <t xml:space="preserve">2.3153247833252</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.27228140830994</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.3183274269104</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.31582450866699</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.34985852241516</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.382892370224</t>
+    <t xml:space="preserve">2.31532454490662</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.27228164672852</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.31832718849182</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.31582474708557</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.34985876083374</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.38289260864258</t>
   </si>
   <si>
     <t xml:space="preserve">2.35936832427979</t>
@@ -1727,13 +1727,13 @@
     <t xml:space="preserve">2.392902135849</t>
   </si>
   <si>
-    <t xml:space="preserve">2.38189101219177</t>
+    <t xml:space="preserve">2.38189148902893</t>
   </si>
   <si>
     <t xml:space="preserve">2.29680585861206</t>
   </si>
   <si>
-    <t xml:space="preserve">2.29079937934875</t>
+    <t xml:space="preserve">2.29079961776733</t>
   </si>
   <si>
     <t xml:space="preserve">2.29230117797852</t>
@@ -1742,7 +1742,7 @@
     <t xml:space="preserve">2.31232118606567</t>
   </si>
   <si>
-    <t xml:space="preserve">2.17568373680115</t>
+    <t xml:space="preserve">2.17568397521973</t>
   </si>
   <si>
     <t xml:space="preserve">2.15115928649902</t>
@@ -1754,10 +1754,10 @@
     <t xml:space="preserve">2.0685760974884</t>
   </si>
   <si>
-    <t xml:space="preserve">2.04905700683594</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.04655504226685</t>
+    <t xml:space="preserve">2.04905676841736</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.04655456542969</t>
   </si>
   <si>
     <t xml:space="preserve">2.00200963020325</t>
@@ -1766,28 +1766,28 @@
     <t xml:space="preserve">2.00251030921936</t>
   </si>
   <si>
-    <t xml:space="preserve">2.04705500602722</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.04605412483215</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.03003787994385</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.02503299713135</t>
+    <t xml:space="preserve">2.04705452919006</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.04605436325073</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.03003740310669</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.02503323554993</t>
   </si>
   <si>
     <t xml:space="preserve">2.01702523231506</t>
   </si>
   <si>
-    <t xml:space="preserve">1.98449206352234</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.99700438976288</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.9219297170639</t>
+    <t xml:space="preserve">1.98449230194092</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.99700462818146</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.92192959785461</t>
   </si>
   <si>
     <t xml:space="preserve">1.90140891075134</t>
@@ -1796,49 +1796,49 @@
     <t xml:space="preserve">1.91041827201843</t>
   </si>
   <si>
-    <t xml:space="preserve">1.98048806190491</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.06507349014282</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.0690770149231</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.12413191795349</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.11362195014954</t>
+    <t xml:space="preserve">1.98048782348633</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.06507301330566</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.06907725334167</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.12413239479065</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.11362171173096</t>
   </si>
   <si>
     <t xml:space="preserve">2.11562371253967</t>
   </si>
   <si>
-    <t xml:space="preserve">2.10861659049988</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.15716576576233</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.18969798088074</t>
+    <t xml:space="preserve">2.10861706733704</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.15716600418091</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.18969821929932</t>
   </si>
   <si>
     <t xml:space="preserve">2.16917777061462</t>
   </si>
   <si>
-    <t xml:space="preserve">2.12763643264771</t>
+    <t xml:space="preserve">2.12763619422913</t>
   </si>
   <si>
     <t xml:space="preserve">2.15216088294983</t>
   </si>
   <si>
-    <t xml:space="preserve">2.17868757247925</t>
+    <t xml:space="preserve">2.17868733406067</t>
   </si>
   <si>
     <t xml:space="preserve">2.20070910453796</t>
   </si>
   <si>
-    <t xml:space="preserve">1.99600374698639</t>
+    <t xml:space="preserve">1.99600338935852</t>
   </si>
   <si>
     <t xml:space="preserve">1.91742503643036</t>
@@ -1850,136 +1850,136 @@
     <t xml:space="preserve">1.85936617851257</t>
   </si>
   <si>
-    <t xml:space="preserve">1.87087821960449</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.83684420585632</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.80631327629089</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.77027666568756</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.80881571769714</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.77478158473969</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.78829491138458</t>
+    <t xml:space="preserve">1.87087798118591</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.83684408664703</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.80631339550018</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.77027702331543</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.80881559848785</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.77478098869324</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.78829503059387</t>
   </si>
   <si>
     <t xml:space="preserve">1.8008074760437</t>
   </si>
   <si>
-    <t xml:space="preserve">1.78529214859009</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.78779447078705</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.74925601482391</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.75576269626617</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.69169819355011</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.65516138076782</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.60811412334442</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.64515173435211</t>
+    <t xml:space="preserve">1.78529238700867</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.78779470920563</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.74925589561462</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.75576293468475</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.69169867038727</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.65516114234924</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.60811424255371</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.6451518535614</t>
   </si>
   <si>
     <t xml:space="preserve">1.63263916969299</t>
   </si>
   <si>
-    <t xml:space="preserve">1.70471167564392</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.69470107555389</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.68068695068359</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.69069719314575</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.75926625728607</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.69870519638062</t>
+    <t xml:space="preserve">1.70471143722534</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.69470143318176</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.68068706989288</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.69069743156433</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.75926613807678</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.6987053155899</t>
   </si>
   <si>
     <t xml:space="preserve">1.6861926317215</t>
   </si>
   <si>
-    <t xml:space="preserve">1.71672356128693</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.72973656654358</t>
+    <t xml:space="preserve">1.71672368049622</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.72973668575287</t>
   </si>
   <si>
     <t xml:space="preserve">1.74525201320648</t>
   </si>
   <si>
-    <t xml:space="preserve">1.74775457382202</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.69670355319977</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.71071696281433</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.6796863079071</t>
+    <t xml:space="preserve">1.74775505065918</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.69670343399048</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.71071708202362</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.67968654632568</t>
   </si>
   <si>
     <t xml:space="preserve">1.6952018737793</t>
   </si>
   <si>
-    <t xml:space="preserve">1.67568254470825</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.73624265193939</t>
+    <t xml:space="preserve">1.67568230628967</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.73624277114868</t>
   </si>
   <si>
     <t xml:space="preserve">1.74625301361084</t>
   </si>
   <si>
-    <t xml:space="preserve">1.74725425243378</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.84084796905518</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.77628326416016</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.79229927062988</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.80130839347839</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.88439202308655</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.85235953330994</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.88689398765564</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.82683408260345</t>
+    <t xml:space="preserve">1.7472540140152</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.84084820747375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.77628290653229</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.79229938983917</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.8013082742691</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.88439238071442</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.85235941410065</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.8868944644928</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.82683396339417</t>
   </si>
   <si>
     <t xml:space="preserve">1.79780471324921</t>
@@ -1988,34 +1988,34 @@
     <t xml:space="preserve">1.76727414131165</t>
   </si>
   <si>
-    <t xml:space="preserve">1.75025713443756</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.74325025081635</t>
+    <t xml:space="preserve">1.75025701522827</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.74325037002563</t>
   </si>
   <si>
     <t xml:space="preserve">1.71622276306152</t>
   </si>
   <si>
-    <t xml:space="preserve">1.68268942832947</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.6746814250946</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.70871543884277</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.67618250846863</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.66366982460022</t>
+    <t xml:space="preserve">1.68268930912018</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.67468130588531</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.70871555805206</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.67618238925934</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.66366970539093</t>
   </si>
   <si>
     <t xml:space="preserve">1.64114773273468</t>
   </si>
   <si>
-    <t xml:space="preserve">1.6836906671524</t>
+    <t xml:space="preserve">1.68369042873383</t>
   </si>
   <si>
     <t xml:space="preserve">1.64965605735779</t>
@@ -2027,148 +2027,148 @@
     <t xml:space="preserve">1.69370007514954</t>
   </si>
   <si>
-    <t xml:space="preserve">1.70421099662781</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.66667330265045</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.65966594219208</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.66467106342316</t>
+    <t xml:space="preserve">1.7042111158371</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.66667342185974</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.6596657037735</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.66467082500458</t>
   </si>
   <si>
     <t xml:space="preserve">1.63664329051971</t>
   </si>
   <si>
-    <t xml:space="preserve">1.57357943058014</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.49900472164154</t>
+    <t xml:space="preserve">1.57357931137085</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.49900484085083</t>
   </si>
   <si>
     <t xml:space="preserve">1.53203785419464</t>
   </si>
   <si>
-    <t xml:space="preserve">1.53804421424866</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.52903509140015</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.53704297542572</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.52853417396545</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.50601160526276</t>
+    <t xml:space="preserve">1.53804409503937</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.52903497219086</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.53704309463501</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.52853465080261</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.50601172447205</t>
   </si>
   <si>
     <t xml:space="preserve">1.51051604747772</t>
   </si>
   <si>
-    <t xml:space="preserve">1.57658278942108</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.55756330490112</t>
+    <t xml:space="preserve">1.57658290863037</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.55756342411041</t>
   </si>
   <si>
     <t xml:space="preserve">1.56156718730927</t>
   </si>
   <si>
-    <t xml:space="preserve">1.57508099079132</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.47948551177979</t>
+    <t xml:space="preserve">1.57508111000061</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.47948527336121</t>
   </si>
   <si>
     <t xml:space="preserve">1.4839893579483</t>
   </si>
   <si>
-    <t xml:space="preserve">1.48649215698242</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.48899435997009</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.52402973175049</t>
+    <t xml:space="preserve">1.48649203777313</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.48899447917938</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.5240296125412</t>
   </si>
   <si>
     <t xml:space="preserve">1.50851452350616</t>
   </si>
   <si>
-    <t xml:space="preserve">1.64164853096008</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.709716796875</t>
+    <t xml:space="preserve">1.64164841175079</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.70971667766571</t>
   </si>
   <si>
     <t xml:space="preserve">1.69219875335693</t>
   </si>
   <si>
-    <t xml:space="preserve">1.68569195270538</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.76377081871033</t>
+    <t xml:space="preserve">1.68569219112396</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.76377046108246</t>
   </si>
   <si>
     <t xml:space="preserve">1.75676393508911</t>
   </si>
   <si>
-    <t xml:space="preserve">1.74174845218658</t>
+    <t xml:space="preserve">1.74174833297729</t>
   </si>
   <si>
     <t xml:space="preserve">1.71372067928314</t>
   </si>
   <si>
-    <t xml:space="preserve">1.73374056816101</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.75125813484192</t>
+    <t xml:space="preserve">1.73374080657959</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.75125801563263</t>
   </si>
   <si>
     <t xml:space="preserve">1.76276957988739</t>
   </si>
   <si>
-    <t xml:space="preserve">1.81031739711761</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.85085773468018</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.84585320949554</t>
+    <t xml:space="preserve">1.81031727790833</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.85085785388947</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.84585297107697</t>
   </si>
   <si>
     <t xml:space="preserve">1.83984696865082</t>
   </si>
   <si>
-    <t xml:space="preserve">1.85486245155334</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.80030679702759</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.78178906440735</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.77077734470367</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.78128814697266</t>
+    <t xml:space="preserve">1.85486257076263</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.80030715465546</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.78178894519806</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.77077722549438</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.78128850460052</t>
   </si>
   <si>
     <t xml:space="preserve">1.81732416152954</t>
   </si>
   <si>
-    <t xml:space="preserve">1.85386157035828</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.86787474155426</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.86837530136108</t>
+    <t xml:space="preserve">1.8538613319397</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.86787486076355</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.8683750629425</t>
   </si>
   <si>
     <t xml:space="preserve">1.85185897350311</t>
@@ -2177,7 +2177,7 @@
     <t xml:space="preserve">1.82633328437805</t>
   </si>
   <si>
-    <t xml:space="preserve">1.8188259601593</t>
+    <t xml:space="preserve">1.81882584095001</t>
   </si>
   <si>
     <t xml:space="preserve">1.80331063270569</t>
@@ -2186,49 +2186,49 @@
     <t xml:space="preserve">1.83183908462524</t>
   </si>
   <si>
-    <t xml:space="preserve">1.82433176040649</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.8223295211792</t>
+    <t xml:space="preserve">1.8243316411972</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.82232928276062</t>
   </si>
   <si>
     <t xml:space="preserve">1.84735429286957</t>
   </si>
   <si>
-    <t xml:space="preserve">1.83334064483643</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.85135841369629</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.85336053371429</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.86937665939331</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.87037765979767</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.89990723133087</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.93544352054596</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.98649442195892</t>
+    <t xml:space="preserve">1.83334076404572</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.85135853290558</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.85336065292358</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.86937654018402</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.87037789821625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.89990746974945</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.93544340133667</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.98649454116821</t>
   </si>
   <si>
     <t xml:space="preserve">2.02002811431885</t>
   </si>
   <si>
-    <t xml:space="preserve">2.07358121871948</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.09360218048096</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.07308125495911</t>
+    <t xml:space="preserve">2.07358169555664</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.09360194206238</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.07308077812195</t>
   </si>
   <si>
     <t xml:space="preserve">2.05506324768066</t>
@@ -2243,121 +2243,121 @@
     <t xml:space="preserve">2.11161971092224</t>
   </si>
   <si>
-    <t xml:space="preserve">2.14415287971497</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.1096179485321</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.10311079025269</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.05956792831421</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.04805636405945</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.00401210784912</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.98198997974396</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.95195960998535</t>
+    <t xml:space="preserve">2.14415264129639</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.10961818695068</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.10311102867126</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.05956840515137</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.04805588722229</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.00401186943054</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.98198986053467</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.95195972919464</t>
   </si>
   <si>
     <t xml:space="preserve">1.96947729587555</t>
   </si>
   <si>
-    <t xml:space="preserve">1.93494260311127</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.97848641872406</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.9255838394165</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.8748687505722</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.83502209186554</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.81070053577423</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.82933056354523</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.78068625926971</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.78172063827515</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.77240633964539</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.75998604297638</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.75118887424469</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.73721647262573</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.76774930953979</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.73566460609436</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.71496510505676</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.7118593454361</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.76567876338959</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.78223824501038</t>
+    <t xml:space="preserve">1.93494248390198</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.97848653793335</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.92558360099792</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.87486886978149</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.83502185344696</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.81070041656494</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.82933044433594</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.78068602085114</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.78172051906586</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.77240645885468</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.75998628139496</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.7511887550354</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.73721611499786</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.76774907112122</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.73566424846649</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.71496498584747</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.71185946464539</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.7656786441803</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.78223836421967</t>
   </si>
   <si>
     <t xml:space="preserve">1.76205658912659</t>
   </si>
   <si>
-    <t xml:space="preserve">1.78327345848083</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.77706289291382</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.79051768779755</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.83088254928589</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.86503720283508</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.86296701431274</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.89453411102295</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.87383484840393</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.87279939651489</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.88366639614105</t>
+    <t xml:space="preserve">1.78327322006226</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.77706301212311</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.79051792621613</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.83088219165802</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.86503732204437</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.8629674911499</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.89453399181366</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.87383460998535</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.87279963493347</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.88366627693176</t>
   </si>
   <si>
     <t xml:space="preserve">1.85417008399963</t>
@@ -2369,58 +2369,58 @@
     <t xml:space="preserve">1.88211452960968</t>
   </si>
   <si>
-    <t xml:space="preserve">1.95559799671173</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.01252174377441</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.01666188240051</t>
+    <t xml:space="preserve">1.95559775829315</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.01252150535583</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.01666164398193</t>
   </si>
   <si>
     <t xml:space="preserve">1.99854958057404</t>
   </si>
   <si>
-    <t xml:space="preserve">1.990269780159</t>
+    <t xml:space="preserve">1.99026954174042</t>
   </si>
   <si>
     <t xml:space="preserve">1.97371029853821</t>
   </si>
   <si>
-    <t xml:space="preserve">1.9825074672699</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.96853506565094</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.99647998809814</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.96439528465271</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.9395557641983</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.94576549530029</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.93541634082794</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.8862544298172</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.87072920799255</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.85106515884399</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.82570731639862</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.75429439544678</t>
+    <t xml:space="preserve">1.98250758647919</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.96853542327881</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.9964793920517</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.964395403862</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.93955612182617</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.94576561450958</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.93541598320007</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.88625431060791</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.87072908878326</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.8510650396347</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.82570767402649</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.75429403781891</t>
   </si>
   <si>
     <t xml:space="preserve">1.74342656135559</t>
@@ -2429,34 +2429,34 @@
     <t xml:space="preserve">1.79000115394592</t>
   </si>
   <si>
-    <t xml:space="preserve">1.76257383823395</t>
+    <t xml:space="preserve">1.76257395744324</t>
   </si>
   <si>
     <t xml:space="preserve">1.78948354721069</t>
   </si>
   <si>
-    <t xml:space="preserve">1.76464354991913</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.79828083515167</t>
+    <t xml:space="preserve">1.76464319229126</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.79828071594238</t>
   </si>
   <si>
     <t xml:space="preserve">1.65597069263458</t>
   </si>
   <si>
-    <t xml:space="preserve">1.6207811832428</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.63941133022308</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.55868244171143</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.59283649921417</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.60887932777405</t>
+    <t xml:space="preserve">1.62078142166138</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.63941121101379</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.55868220329285</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.59283661842346</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.60887944698334</t>
   </si>
   <si>
     <t xml:space="preserve">1.55764722824097</t>
@@ -2465,7 +2465,7 @@
     <t xml:space="preserve">1.58455681800842</t>
   </si>
   <si>
-    <t xml:space="preserve">1.59076714515686</t>
+    <t xml:space="preserve">1.59076702594757</t>
   </si>
   <si>
     <t xml:space="preserve">1.57731223106384</t>
@@ -2474,106 +2474,106 @@
     <t xml:space="preserve">1.58817911148071</t>
   </si>
   <si>
-    <t xml:space="preserve">1.66011047363281</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.64872634410858</t>
+    <t xml:space="preserve">1.6601105928421</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.64872622489929</t>
   </si>
   <si>
     <t xml:space="preserve">1.68132758140564</t>
   </si>
   <si>
-    <t xml:space="preserve">1.6678729057312</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.6714950799942</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.69943976402283</t>
+    <t xml:space="preserve">1.66787266731262</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.67149496078491</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.69944000244141</t>
   </si>
   <si>
     <t xml:space="preserve">1.71651697158813</t>
   </si>
   <si>
-    <t xml:space="preserve">1.72169172763824</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.72997200489044</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.78844845294952</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.8086302280426</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.79103541374207</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.81846261024475</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.86451971530914</t>
+    <t xml:space="preserve">1.7216922044754</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.72997176647186</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.78844857215881</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.80863034725189</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.79103553295135</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.81846296787262</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.86451983451843</t>
   </si>
   <si>
     <t xml:space="preserve">1.87331712245941</t>
   </si>
   <si>
-    <t xml:space="preserve">1.81225264072418</t>
+    <t xml:space="preserve">1.81225228309631</t>
   </si>
   <si>
     <t xml:space="preserve">1.82312023639679</t>
   </si>
   <si>
-    <t xml:space="preserve">1.90281367301941</t>
+    <t xml:space="preserve">1.9028137922287</t>
   </si>
   <si>
     <t xml:space="preserve">1.84588992595673</t>
   </si>
   <si>
-    <t xml:space="preserve">1.8179452419281</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.79879879951477</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.80966532230377</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.83295238018036</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.80500793457031</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.81587564945221</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.79931545257568</t>
+    <t xml:space="preserve">1.81794488430023</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.79879856109619</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.80966544151306</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.83295261859894</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.80500781536102</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.81587553024292</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.7993152141571</t>
   </si>
   <si>
     <t xml:space="preserve">1.80552554130554</t>
   </si>
   <si>
-    <t xml:space="preserve">1.81639313697815</t>
+    <t xml:space="preserve">1.81639325618744</t>
   </si>
   <si>
     <t xml:space="preserve">1.88263201713562</t>
   </si>
   <si>
-    <t xml:space="preserve">1.90333139896393</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.94421339035034</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.97267496585846</t>
+    <t xml:space="preserve">1.90333151817322</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.94421315193176</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.97267472743988</t>
   </si>
   <si>
     <t xml:space="preserve">2.02649426460266</t>
   </si>
   <si>
-    <t xml:space="preserve">2.07927846908569</t>
+    <t xml:space="preserve">2.07927823066711</t>
   </si>
   <si>
     <t xml:space="preserve">2.10204815864563</t>
@@ -2585,7 +2585,7 @@
     <t xml:space="preserve">2.09066271781921</t>
   </si>
   <si>
-    <t xml:space="preserve">2.08962869644165</t>
+    <t xml:space="preserve">2.08962845802307</t>
   </si>
   <si>
     <t xml:space="preserve">2.10515260696411</t>
@@ -2594,16 +2594,16 @@
     <t xml:space="preserve">2.10567021369934</t>
   </si>
   <si>
-    <t xml:space="preserve">2.0658233165741</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.07358574867249</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.06996369361877</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.1367199420929</t>
+    <t xml:space="preserve">2.06582355499268</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.07358551025391</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.06996321678162</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.13672018051147</t>
   </si>
   <si>
     <t xml:space="preserve">2.16155910491943</t>
@@ -2621,28 +2621,28 @@
     <t xml:space="preserve">2.21951818466187</t>
   </si>
   <si>
-    <t xml:space="preserve">2.23556041717529</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.25056767463684</t>
+    <t xml:space="preserve">2.23556017875671</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.25056791305542</t>
   </si>
   <si>
     <t xml:space="preserve">2.24280548095703</t>
   </si>
   <si>
-    <t xml:space="preserve">2.25936484336853</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.28679227828979</t>
+    <t xml:space="preserve">2.25936508178711</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.28679251670837</t>
   </si>
   <si>
     <t xml:space="preserve">2.35303115844727</t>
   </si>
   <si>
-    <t xml:space="preserve">2.38459801673889</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.37114334106445</t>
+    <t xml:space="preserve">2.38459825515747</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.37114310264587</t>
   </si>
   <si>
     <t xml:space="preserve">2.31421947479248</t>
@@ -2660,10 +2660,10 @@
     <t xml:space="preserve">2.27074980735779</t>
   </si>
   <si>
-    <t xml:space="preserve">2.27437257766724</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.22779774665833</t>
+    <t xml:space="preserve">2.27437281608582</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.2277979850769</t>
   </si>
   <si>
     <t xml:space="preserve">2.24435710906982</t>
@@ -2675,13 +2675,13 @@
     <t xml:space="preserve">2.28368759155273</t>
   </si>
   <si>
-    <t xml:space="preserve">2.30593967437744</t>
+    <t xml:space="preserve">2.30593943595886</t>
   </si>
   <si>
     <t xml:space="preserve">2.27851247787476</t>
   </si>
   <si>
-    <t xml:space="preserve">2.30283427238464</t>
+    <t xml:space="preserve">2.30283403396606</t>
   </si>
   <si>
     <t xml:space="preserve">2.29972958564758</t>
@@ -2690,31 +2690,31 @@
     <t xml:space="preserve">2.33026146888733</t>
   </si>
   <si>
-    <t xml:space="preserve">2.3131844997406</t>
+    <t xml:space="preserve">2.31318402290344</t>
   </si>
   <si>
     <t xml:space="preserve">2.34216356277466</t>
   </si>
   <si>
-    <t xml:space="preserve">2.3597583770752</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.3369882106781</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.33388376235962</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.30490446090698</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.31991124153137</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.37787008285522</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.37631845474243</t>
+    <t xml:space="preserve">2.35975813865662</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.33698844909668</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.3338840007782</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.3049042224884</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.31991100311279</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.3778703212738</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.37631821632385</t>
   </si>
   <si>
     <t xml:space="preserve">2.32767415046692</t>
@@ -2726,37 +2726,37 @@
     <t xml:space="preserve">2.35665345191956</t>
   </si>
   <si>
-    <t xml:space="preserve">2.38873791694641</t>
+    <t xml:space="preserve">2.38873815536499</t>
   </si>
   <si>
     <t xml:space="preserve">2.39080762863159</t>
   </si>
   <si>
-    <t xml:space="preserve">2.38045835494995</t>
+    <t xml:space="preserve">2.38045859336853</t>
   </si>
   <si>
     <t xml:space="preserve">2.38822031021118</t>
   </si>
   <si>
-    <t xml:space="preserve">2.36700344085693</t>
+    <t xml:space="preserve">2.36700391769409</t>
   </si>
   <si>
     <t xml:space="preserve">2.36079335212708</t>
   </si>
   <si>
-    <t xml:space="preserve">2.37942337989807</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.36493325233459</t>
+    <t xml:space="preserve">2.37942290306091</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.36493301391602</t>
   </si>
   <si>
     <t xml:space="preserve">2.39494752883911</t>
   </si>
   <si>
-    <t xml:space="preserve">2.30749177932739</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.30800914764404</t>
+    <t xml:space="preserve">2.30749154090881</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.30800938606262</t>
   </si>
   <si>
     <t xml:space="preserve">2.29351925849915</t>
@@ -2768,49 +2768,49 @@
     <t xml:space="preserve">2.31939363479614</t>
   </si>
   <si>
-    <t xml:space="preserve">2.23866558074951</t>
+    <t xml:space="preserve">2.23866581916809</t>
   </si>
   <si>
     <t xml:space="preserve">2.14758658409119</t>
   </si>
   <si>
-    <t xml:space="preserve">2.19157361984253</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.24073529243469</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.26505780220032</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.24384069442749</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.25263810157776</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.2629873752594</t>
+    <t xml:space="preserve">2.19157314300537</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.24073505401611</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.26505756378174</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.24384093284607</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.25263786315918</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.26298713684082</t>
   </si>
   <si>
     <t xml:space="preserve">2.3463032245636</t>
   </si>
   <si>
-    <t xml:space="preserve">2.32612133026123</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.40322709083557</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.14292907714844</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.13568472862244</t>
+    <t xml:space="preserve">2.32612156867981</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.40322732925415</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.14292931556702</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.13568449020386</t>
   </si>
   <si>
     <t xml:space="preserve">2.1703565120697</t>
   </si>
   <si>
-    <t xml:space="preserve">2.10722303390503</t>
+    <t xml:space="preserve">2.10722327232361</t>
   </si>
   <si>
     <t xml:space="preserve">1.98509442806244</t>
@@ -2819,25 +2819,25 @@
     <t xml:space="preserve">1.98716497421265</t>
   </si>
   <si>
-    <t xml:space="preserve">2.03115177154541</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.95508003234863</t>
+    <t xml:space="preserve">2.03115153312683</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.95508050918579</t>
   </si>
   <si>
     <t xml:space="preserve">1.8624495267868</t>
   </si>
   <si>
-    <t xml:space="preserve">1.72065675258636</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.67615222930908</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.61508858203888</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.58093464374542</t>
+    <t xml:space="preserve">1.72065687179565</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.67615246772766</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.61508882045746</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.58093452453613</t>
   </si>
   <si>
     <t xml:space="preserve">1.36617600917816</t>
@@ -2852,37 +2852,37 @@
     <t xml:space="preserve">1.07172298431396</t>
   </si>
   <si>
-    <t xml:space="preserve">1.31183922290802</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.21144604682922</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.2073061466217</t>
+    <t xml:space="preserve">1.31183910369873</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.21144616603851</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.20730638504028</t>
   </si>
   <si>
     <t xml:space="preserve">1.17522144317627</t>
   </si>
   <si>
-    <t xml:space="preserve">1.19333398342133</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.33253872394562</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.51935315132141</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.55712950229645</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.53280782699585</t>
+    <t xml:space="preserve">1.19333374500275</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.33253860473633</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.51935303211212</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.55712974071503</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.53280794620514</t>
   </si>
   <si>
     <t xml:space="preserve">1.50279355049133</t>
   </si>
   <si>
-    <t xml:space="preserve">1.40602278709412</t>
+    <t xml:space="preserve">1.40602290630341</t>
   </si>
   <si>
     <t xml:space="preserve">1.40550529956818</t>
@@ -2891,7 +2891,7 @@
     <t xml:space="preserve">1.44897425174713</t>
   </si>
   <si>
-    <t xml:space="preserve">1.40705716609955</t>
+    <t xml:space="preserve">1.40705728530884</t>
   </si>
   <si>
     <t xml:space="preserve">1.39567267894745</t>
@@ -2903,19 +2903,19 @@
     <t xml:space="preserve">1.41585457324982</t>
   </si>
   <si>
-    <t xml:space="preserve">1.41016256809235</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.34081840515137</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.35375559329987</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.29320931434631</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.1979912519455</t>
+    <t xml:space="preserve">1.41016268730164</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.34081828594208</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.35375547409058</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.2932094335556</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.19799137115479</t>
   </si>
   <si>
     <t xml:space="preserve">1.14624238014221</t>
@@ -2924,10 +2924,10 @@
     <t xml:space="preserve">1.15814447402954</t>
   </si>
   <si>
-    <t xml:space="preserve">1.1591796875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.10898280143738</t>
+    <t xml:space="preserve">1.15917956829071</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.10898268222809</t>
   </si>
   <si>
     <t xml:space="preserve">1.10743010044098</t>
@@ -2936,7 +2936,7 @@
     <t xml:space="preserve">1.14468967914581</t>
   </si>
   <si>
-    <t xml:space="preserve">1.09708058834076</t>
+    <t xml:space="preserve">1.09708070755005</t>
   </si>
   <si>
     <t xml:space="preserve">1.12813007831573</t>
@@ -2945,10 +2945,10 @@
     <t xml:space="preserve">1.19902634620667</t>
   </si>
   <si>
-    <t xml:space="preserve">1.21817314624786</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.16538918018341</t>
+    <t xml:space="preserve">1.21817326545715</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.16538906097412</t>
   </si>
   <si>
     <t xml:space="preserve">1.14054977893829</t>
@@ -2957,10 +2957,10 @@
     <t xml:space="preserve">1.13847947120667</t>
   </si>
   <si>
-    <t xml:space="preserve">1.12502467632294</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.10639560222626</t>
+    <t xml:space="preserve">1.12502455711365</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.10639548301697</t>
   </si>
   <si>
     <t xml:space="preserve">1.09397506713867</t>
@@ -2975,28 +2975,28 @@
     <t xml:space="preserve">1.04222619533539</t>
   </si>
   <si>
-    <t xml:space="preserve">1.0386039018631</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.08031666278839</t>
+    <t xml:space="preserve">1.03860402107239</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.0803165435791</t>
   </si>
   <si>
     <t xml:space="preserve">1.02012348175049</t>
   </si>
   <si>
-    <t xml:space="preserve">1.00243449211121</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.983425855636597</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.984218418598175</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.986858189105988</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.08982086181641</t>
+    <t xml:space="preserve">1.0024346113205</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.983425974845886</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.98421835899353</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.986858010292053</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.0898209810257</t>
   </si>
   <si>
     <t xml:space="preserve">1.12942171096802</t>
@@ -3008,13 +3008,13 @@
     <t xml:space="preserve">1.13364660739899</t>
   </si>
   <si>
-    <t xml:space="preserve">1.16163086891174</t>
+    <t xml:space="preserve">1.16163063049316</t>
   </si>
   <si>
     <t xml:space="preserve">1.18275189399719</t>
   </si>
   <si>
-    <t xml:space="preserve">1.22076857089996</t>
+    <t xml:space="preserve">1.22076845169067</t>
   </si>
   <si>
     <t xml:space="preserve">1.22129666805267</t>
@@ -3023,19 +3023,19 @@
     <t xml:space="preserve">1.34010016918182</t>
   </si>
   <si>
-    <t xml:space="preserve">1.40504550933838</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.3849812746048</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.31528306007385</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.2313289642334</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.20334410667419</t>
+    <t xml:space="preserve">1.40504539012909</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.38498115539551</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.31528294086456</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.23132908344269</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.20334422588348</t>
   </si>
   <si>
     <t xml:space="preserve">1.21443283557892</t>
@@ -3047,7 +3047,7 @@
     <t xml:space="preserve">1.26829016208649</t>
   </si>
   <si>
-    <t xml:space="preserve">1.23344075679779</t>
+    <t xml:space="preserve">1.2334406375885</t>
   </si>
   <si>
     <t xml:space="preserve">1.24611365795135</t>
@@ -3056,10 +3056,10 @@
     <t xml:space="preserve">1.19806385040283</t>
   </si>
   <si>
-    <t xml:space="preserve">1.22763323783875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.16532671451569</t>
+    <t xml:space="preserve">1.22763311862946</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.1653265953064</t>
   </si>
   <si>
     <t xml:space="preserve">1.17430293560028</t>
@@ -3083,46 +3083,46 @@
     <t xml:space="preserve">1.18327927589417</t>
   </si>
   <si>
-    <t xml:space="preserve">1.17007887363434</t>
+    <t xml:space="preserve">1.17007875442505</t>
   </si>
   <si>
     <t xml:space="preserve">1.164799451828</t>
   </si>
   <si>
-    <t xml:space="preserve">1.13417398929596</t>
+    <t xml:space="preserve">1.13417387008667</t>
   </si>
   <si>
     <t xml:space="preserve">1.19119989871979</t>
   </si>
   <si>
-    <t xml:space="preserve">1.31581103801727</t>
+    <t xml:space="preserve">1.31581127643585</t>
   </si>
   <si>
     <t xml:space="preserve">1.31686747074127</t>
   </si>
   <si>
-    <t xml:space="preserve">1.32373118400574</t>
+    <t xml:space="preserve">1.32373106479645</t>
   </si>
   <si>
     <t xml:space="preserve">1.34115552902222</t>
   </si>
   <si>
-    <t xml:space="preserve">1.31317138671875</t>
+    <t xml:space="preserve">1.31317126750946</t>
   </si>
   <si>
     <t xml:space="preserve">1.35858070850372</t>
   </si>
   <si>
-    <t xml:space="preserve">1.34590792655945</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.29944288730621</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.27990615367889</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.22657692432404</t>
+    <t xml:space="preserve">1.34590768814087</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.2994430065155</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.27990627288818</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.22657668590546</t>
   </si>
   <si>
     <t xml:space="preserve">1.23027276992798</t>
@@ -3134,22 +3134,22 @@
     <t xml:space="preserve">1.1758873462677</t>
   </si>
   <si>
-    <t xml:space="preserve">1.12572574615479</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.09668552875519</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.08242893218994</t>
+    <t xml:space="preserve">1.12572586536407</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.0966854095459</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.08242881298065</t>
   </si>
   <si>
     <t xml:space="preserve">1.14790236949921</t>
   </si>
   <si>
-    <t xml:space="preserve">1.23555302619934</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.25139319896698</t>
+    <t xml:space="preserve">1.23555314540863</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.25139307975769</t>
   </si>
   <si>
     <t xml:space="preserve">1.2524493932724</t>
@@ -3158,28 +3158,28 @@
     <t xml:space="preserve">1.22288084030151</t>
   </si>
   <si>
-    <t xml:space="preserve">1.22604870796204</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.23713743686676</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.21707260608673</t>
+    <t xml:space="preserve">1.22604894638062</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.23713755607605</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.21707248687744</t>
   </si>
   <si>
     <t xml:space="preserve">1.2038722038269</t>
   </si>
   <si>
-    <t xml:space="preserve">1.24030518531799</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.23977708816528</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.23080086708069</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.25667357444763</t>
+    <t xml:space="preserve">1.24030530452728</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.23977720737457</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.23080098628998</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.25667345523834</t>
   </si>
   <si>
     <t xml:space="preserve">1.2149600982666</t>
@@ -3188,16 +3188,16 @@
     <t xml:space="preserve">1.18222391605377</t>
   </si>
   <si>
-    <t xml:space="preserve">1.17905497550964</t>
+    <t xml:space="preserve">1.17905509471893</t>
   </si>
   <si>
     <t xml:space="preserve">1.14156663417816</t>
   </si>
   <si>
-    <t xml:space="preserve">1.15265440940857</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.14684689044952</t>
+    <t xml:space="preserve">1.15265452861786</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.14684700965881</t>
   </si>
   <si>
     <t xml:space="preserve">1.11569333076477</t>
@@ -3206,7 +3206,7 @@
     <t xml:space="preserve">1.13100612163544</t>
   </si>
   <si>
-    <t xml:space="preserve">1.16004729270935</t>
+    <t xml:space="preserve">1.16004705429077</t>
   </si>
   <si>
     <t xml:space="preserve">1.15687847137451</t>
@@ -3215,25 +3215,25 @@
     <t xml:space="preserve">1.15635049343109</t>
   </si>
   <si>
-    <t xml:space="preserve">1.14209473133087</t>
+    <t xml:space="preserve">1.14209485054016</t>
   </si>
   <si>
     <t xml:space="preserve">1.15054285526276</t>
   </si>
   <si>
-    <t xml:space="preserve">1.14051055908203</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.09404504299164</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.06447660923004</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.06658792495728</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.03490710258484</t>
+    <t xml:space="preserve">1.14051043987274</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.09404492378235</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.06447649002075</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.06658804416656</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.03490722179413</t>
   </si>
   <si>
     <t xml:space="preserve">1.03226757049561</t>
@@ -3242,13 +3242,13 @@
     <t xml:space="preserve">1.05919623374939</t>
   </si>
   <si>
-    <t xml:space="preserve">1.0296276807785</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.0496917963028</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.02857136726379</t>
+    <t xml:space="preserve">1.02962779998779</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.04969191551208</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.02857148647308</t>
   </si>
   <si>
     <t xml:space="preserve">1.00058650970459</t>
@@ -3257,100 +3257,100 @@
     <t xml:space="preserve">0.926720380783081</t>
   </si>
   <si>
-    <t xml:space="preserve">0.965333819389343</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.924770295619965</t>
+    <t xml:space="preserve">0.965333700180054</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.924770176410675</t>
   </si>
   <si>
     <t xml:space="preserve">0.933350920677185</t>
   </si>
   <si>
-    <t xml:space="preserve">0.938031256198883</t>
+    <t xml:space="preserve">0.938031375408173</t>
   </si>
   <si>
     <t xml:space="preserve">0.914239346981049</t>
   </si>
   <si>
-    <t xml:space="preserve">0.867435216903687</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.870945513248444</t>
+    <t xml:space="preserve">0.867435276508331</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.870945572853088</t>
   </si>
   <si>
     <t xml:space="preserve">0.866265118122101</t>
   </si>
   <si>
-    <t xml:space="preserve">0.936471343040466</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.923990249633789</t>
+    <t xml:space="preserve">0.936471164226532</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.9239901304245</t>
   </si>
   <si>
     <t xml:space="preserve">1.01408791542053</t>
   </si>
   <si>
-    <t xml:space="preserve">0.949342310428619</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.925550162792206</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.938811480998993</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.929450452327728</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.871335625648499</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.808540105819702</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.798399209976196</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.793328821659088</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.82297146320343</t>
+    <t xml:space="preserve">0.949342429637909</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.92555034160614</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.938811540603638</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.929450631141663</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.871335506439209</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.808540165424347</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.798399269580841</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.793328762054443</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.822971403598785</t>
   </si>
   <si>
     <t xml:space="preserve">0.844033300876617</t>
   </si>
   <si>
-    <t xml:space="preserve">0.863534927368164</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.844813287258148</t>
+    <t xml:space="preserve">0.863534867763519</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.844813227653503</t>
   </si>
   <si>
     <t xml:space="preserve">0.817510902881622</t>
   </si>
   <si>
-    <t xml:space="preserve">0.939201474189758</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.931400895118713</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.966503858566284</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.02929937839508</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.04139029979706</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.10496592521667</t>
+    <t xml:space="preserve">0.939201533794403</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.931400716304779</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.966503918170929</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.0292991399765</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.04139041900635</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.10496580600739</t>
   </si>
   <si>
     <t xml:space="preserve">1.11198651790619</t>
   </si>
   <si>
-    <t xml:space="preserve">1.15801048278809</t>
+    <t xml:space="preserve">1.15801060199738</t>
   </si>
   <si>
     <t xml:space="preserve">1.18258273601532</t>
@@ -3359,7 +3359,7 @@
     <t xml:space="preserve">1.18531286716461</t>
   </si>
   <si>
-    <t xml:space="preserve">1.18921315670013</t>
+    <t xml:space="preserve">1.18921327590942</t>
   </si>
   <si>
     <t xml:space="preserve">1.1584005355835</t>
@@ -3368,13 +3368,13 @@
     <t xml:space="preserve">1.17868232727051</t>
   </si>
   <si>
-    <t xml:space="preserve">1.14279925823212</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.15918052196503</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.14669966697693</t>
+    <t xml:space="preserve">1.14279913902283</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.15918064117432</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.14669954776764</t>
   </si>
   <si>
     <t xml:space="preserve">1.15723037719727</t>
@@ -3383,22 +3383,22 @@
     <t xml:space="preserve">1.1486496925354</t>
   </si>
   <si>
-    <t xml:space="preserve">1.14240920543671</t>
+    <t xml:space="preserve">1.14240908622742</t>
   </si>
   <si>
     <t xml:space="preserve">1.15020978450775</t>
   </si>
   <si>
-    <t xml:space="preserve">1.18336272239685</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.14435923099518</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.14162909984589</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.15254998207092</t>
+    <t xml:space="preserve">1.18336260318756</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.14435935020447</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.1416289806366</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.15255010128021</t>
   </si>
   <si>
     <t xml:space="preserve">1.13694870471954</t>
@@ -3407,16 +3407,16 @@
     <t xml:space="preserve">1.14396929740906</t>
   </si>
   <si>
-    <t xml:space="preserve">1.13265836238861</t>
+    <t xml:space="preserve">1.13265824317932</t>
   </si>
   <si>
     <t xml:space="preserve">1.08702433109283</t>
   </si>
   <si>
-    <t xml:space="preserve">1.11159646511078</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.15450012683868</t>
+    <t xml:space="preserve">1.11159634590149</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.15450024604797</t>
   </si>
   <si>
     <t xml:space="preserve">1.17010152339935</t>
@@ -3425,61 +3425,61 @@
     <t xml:space="preserve">1.1619108915329</t>
   </si>
   <si>
-    <t xml:space="preserve">1.14045906066895</t>
+    <t xml:space="preserve">1.14045882225037</t>
   </si>
   <si>
     <t xml:space="preserve">1.14981973171234</t>
   </si>
   <si>
-    <t xml:space="preserve">1.21105515956879</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.28594160079956</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.27151024341583</t>
+    <t xml:space="preserve">1.2110550403595</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.28594172000885</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.27151036262512</t>
   </si>
   <si>
     <t xml:space="preserve">1.29764258861542</t>
   </si>
   <si>
-    <t xml:space="preserve">1.29959285259247</t>
+    <t xml:space="preserve">1.29959273338318</t>
   </si>
   <si>
     <t xml:space="preserve">1.2836012840271</t>
   </si>
   <si>
-    <t xml:space="preserve">1.26331961154938</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.25512886047363</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.28282129764557</t>
+    <t xml:space="preserve">1.26331949234009</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.25512897968292</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.28282117843628</t>
   </si>
   <si>
     <t xml:space="preserve">1.26448976993561</t>
   </si>
   <si>
-    <t xml:space="preserve">1.28633153438568</t>
+    <t xml:space="preserve">1.28633165359497</t>
   </si>
   <si>
     <t xml:space="preserve">1.26370966434479</t>
   </si>
   <si>
-    <t xml:space="preserve">1.22899675369263</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.19194352626801</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.22509622573853</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.1888233423233</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.21573555469513</t>
+    <t xml:space="preserve">1.22899663448334</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.19194328784943</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.22509634494781</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.18882322311401</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.21573567390442</t>
   </si>
   <si>
     <t xml:space="preserve">1.19584369659424</t>
@@ -3497,7 +3497,7 @@
     <t xml:space="preserve">1.48953926563263</t>
   </si>
   <si>
-    <t xml:space="preserve">1.45833659172058</t>
+    <t xml:space="preserve">1.45833671092987</t>
   </si>
   <si>
     <t xml:space="preserve">1.48212862014771</t>
@@ -3506,13 +3506,13 @@
     <t xml:space="preserve">1.45521628856659</t>
   </si>
   <si>
-    <t xml:space="preserve">1.45248603820801</t>
+    <t xml:space="preserve">1.4524861574173</t>
   </si>
   <si>
     <t xml:space="preserve">1.46886742115021</t>
   </si>
   <si>
-    <t xml:space="preserve">1.44741559028625</t>
+    <t xml:space="preserve">1.44741547107697</t>
   </si>
   <si>
     <t xml:space="preserve">1.42089331150055</t>
@@ -3521,31 +3521,31 @@
     <t xml:space="preserve">1.3963211774826</t>
   </si>
   <si>
-    <t xml:space="preserve">1.45170593261719</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.43064415454865</t>
+    <t xml:space="preserve">1.45170605182648</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.43064427375793</t>
   </si>
   <si>
     <t xml:space="preserve">1.43025410175323</t>
   </si>
   <si>
-    <t xml:space="preserve">1.45326614379883</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.4154326915741</t>
+    <t xml:space="preserve">1.45326602458954</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.41543281078339</t>
   </si>
   <si>
     <t xml:space="preserve">1.45287609100342</t>
   </si>
   <si>
-    <t xml:space="preserve">1.43766486644745</t>
+    <t xml:space="preserve">1.43766462802887</t>
   </si>
   <si>
     <t xml:space="preserve">1.44624543190002</t>
   </si>
   <si>
-    <t xml:space="preserve">1.50709080696106</t>
+    <t xml:space="preserve">1.50709092617035</t>
   </si>
   <si>
     <t xml:space="preserve">1.54765427112579</t>
@@ -3560,31 +3560,31 @@
     <t xml:space="preserve">1.53673338890076</t>
   </si>
   <si>
-    <t xml:space="preserve">1.51879179477692</t>
+    <t xml:space="preserve">1.51879167556763</t>
   </si>
   <si>
     <t xml:space="preserve">1.55233478546143</t>
   </si>
   <si>
-    <t xml:space="preserve">1.6006988286972</t>
+    <t xml:space="preserve">1.60069894790649</t>
   </si>
   <si>
     <t xml:space="preserve">1.58899784088135</t>
   </si>
   <si>
-    <t xml:space="preserve">1.52581226825714</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.48758900165558</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.48602902889252</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.50670087337494</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.49538969993591</t>
+    <t xml:space="preserve">1.52581238746643</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.48758912086487</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.48602890968323</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.50670075416565</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.4953898191452</t>
   </si>
   <si>
     <t xml:space="preserve">1.49616980552673</t>
@@ -3593,10 +3593,10 @@
     <t xml:space="preserve">1.48056840896606</t>
   </si>
   <si>
-    <t xml:space="preserve">1.48173868656158</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.46379697322845</t>
+    <t xml:space="preserve">1.48173856735229</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.46379709243774</t>
   </si>
   <si>
     <t xml:space="preserve">1.48329865932465</t>
@@ -3605,7 +3605,7 @@
     <t xml:space="preserve">1.48134863376617</t>
   </si>
   <si>
-    <t xml:space="preserve">1.4751079082489</t>
+    <t xml:space="preserve">1.47510814666748</t>
   </si>
   <si>
     <t xml:space="preserve">1.45014572143555</t>
@@ -3614,19 +3614,19 @@
     <t xml:space="preserve">1.4587265253067</t>
   </si>
   <si>
-    <t xml:space="preserve">1.48485887050629</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.46808731555939</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.47666823863983</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.4754980802536</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.52191209793091</t>
+    <t xml:space="preserve">1.48485898971558</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.46808743476868</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.47666811943054</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.47549796104431</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.52191197872162</t>
   </si>
   <si>
     <t xml:space="preserve">1.44000494480133</t>
@@ -3638,25 +3638,25 @@
     <t xml:space="preserve">1.41036236286163</t>
   </si>
   <si>
-    <t xml:space="preserve">1.41738307476044</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.46106684207916</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.44507527351379</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.47744834423065</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.46847748756409</t>
+    <t xml:space="preserve">1.41738295555115</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.46106672286987</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.44507539272308</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.47744822502136</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.46847724914551</t>
   </si>
   <si>
     <t xml:space="preserve">1.4622368812561</t>
   </si>
   <si>
-    <t xml:space="preserve">1.47900831699371</t>
+    <t xml:space="preserve">1.479008436203</t>
   </si>
   <si>
     <t xml:space="preserve">1.50787079334259</t>
@@ -3665,22 +3665,22 @@
     <t xml:space="preserve">1.50046014785767</t>
   </si>
   <si>
-    <t xml:space="preserve">1.55857515335083</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.57261657714844</t>
+    <t xml:space="preserve">1.55857527256012</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.57261645793915</t>
   </si>
   <si>
     <t xml:space="preserve">1.54921436309814</t>
   </si>
   <si>
-    <t xml:space="preserve">1.56403565406799</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.56481575965881</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.57183647155762</t>
+    <t xml:space="preserve">1.56403589248657</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.5648158788681</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.57183659076691</t>
   </si>
   <si>
     <t xml:space="preserve">1.54219365119934</t>
@@ -3689,19 +3689,19 @@
     <t xml:space="preserve">1.52776265144348</t>
   </si>
   <si>
-    <t xml:space="preserve">1.55584490299225</t>
+    <t xml:space="preserve">1.55584502220154</t>
   </si>
   <si>
     <t xml:space="preserve">1.65574705600739</t>
   </si>
   <si>
-    <t xml:space="preserve">1.69236445426941</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.61116933822632</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.63186597824097</t>
+    <t xml:space="preserve">1.6923645734787</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.61116909980774</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.63186609745026</t>
   </si>
   <si>
     <t xml:space="preserve">1.62151765823364</t>
@@ -3710,25 +3710,25 @@
     <t xml:space="preserve">1.61435353755951</t>
   </si>
   <si>
-    <t xml:space="preserve">1.61912953853607</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.6270899772644</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.61992561817169</t>
+    <t xml:space="preserve">1.61912965774536</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.62708985805511</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.61992573738098</t>
   </si>
   <si>
     <t xml:space="preserve">1.60957729816437</t>
   </si>
   <si>
-    <t xml:space="preserve">1.63107013702393</t>
+    <t xml:space="preserve">1.63107001781464</t>
   </si>
   <si>
     <t xml:space="preserve">1.62072169780731</t>
   </si>
   <si>
-    <t xml:space="preserve">1.63425433635712</t>
+    <t xml:space="preserve">1.63425421714783</t>
   </si>
   <si>
     <t xml:space="preserve">1.62231385707855</t>
@@ -3737,16 +3737,16 @@
     <t xml:space="preserve">1.6167414188385</t>
   </si>
   <si>
-    <t xml:space="preserve">1.62470161914825</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.59922873973846</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.57693994045258</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.56539738178253</t>
+    <t xml:space="preserve">1.62470173835754</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.59922885894775</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.57693982124329</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.56539762020111</t>
   </si>
   <si>
     <t xml:space="preserve">1.52997410297394</t>
@@ -3758,10 +3758,10 @@
     <t xml:space="preserve">1.52440166473389</t>
   </si>
   <si>
-    <t xml:space="preserve">1.50410306453705</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.52081966400146</t>
+    <t xml:space="preserve">1.50410294532776</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.52081954479218</t>
   </si>
   <si>
     <t xml:space="preserve">1.51405334472656</t>
@@ -3773,25 +3773,25 @@
     <t xml:space="preserve">1.45395290851593</t>
   </si>
   <si>
-    <t xml:space="preserve">1.46111714839935</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.46987366676331</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.4595251083374</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.47106766700745</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.43206202983856</t>
+    <t xml:space="preserve">1.46111726760864</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.4698737859726</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.45952522754669</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.47106754779816</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.43206214904785</t>
   </si>
   <si>
     <t xml:space="preserve">1.41932547092438</t>
   </si>
   <si>
-    <t xml:space="preserve">1.37315571308136</t>
+    <t xml:space="preserve">1.37315559387207</t>
   </si>
   <si>
     <t xml:space="preserve">1.40420091152191</t>
@@ -3818,31 +3818,31 @@
     <t xml:space="preserve">1.24579060077667</t>
   </si>
   <si>
-    <t xml:space="preserve">1.26171112060547</t>
+    <t xml:space="preserve">1.26171123981476</t>
   </si>
   <si>
     <t xml:space="preserve">1.28400003910065</t>
   </si>
   <si>
-    <t xml:space="preserve">1.28519403934479</t>
+    <t xml:space="preserve">1.28519415855408</t>
   </si>
   <si>
     <t xml:space="preserve">1.30469691753387</t>
   </si>
   <si>
-    <t xml:space="preserve">1.28957223892212</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.29076623916626</t>
+    <t xml:space="preserve">1.28957235813141</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.29076635837555</t>
   </si>
   <si>
     <t xml:space="preserve">1.29434847831726</t>
   </si>
   <si>
-    <t xml:space="preserve">1.31066703796387</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.31026923656464</t>
+    <t xml:space="preserve">1.31066715717316</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.31026911735535</t>
   </si>
   <si>
     <t xml:space="preserve">1.29235827922821</t>
@@ -3851,7 +3851,7 @@
     <t xml:space="preserve">1.30071663856506</t>
   </si>
   <si>
-    <t xml:space="preserve">1.4392261505127</t>
+    <t xml:space="preserve">1.43922626972198</t>
   </si>
   <si>
     <t xml:space="preserve">1.43604218959808</t>
@@ -3863,28 +3863,28 @@
     <t xml:space="preserve">1.4726597070694</t>
   </si>
   <si>
-    <t xml:space="preserve">1.46231114864349</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.45474886894226</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.43683815002441</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.41136515140533</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.42091763019562</t>
+    <t xml:space="preserve">1.46231126785278</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.45474898815155</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.4368382692337</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.41136527061462</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.42091751098633</t>
   </si>
   <si>
     <t xml:space="preserve">1.39783263206482</t>
   </si>
   <si>
-    <t xml:space="preserve">1.39305639266968</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.42290782928467</t>
+    <t xml:space="preserve">1.39305651187897</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.42290759086609</t>
   </si>
   <si>
     <t xml:space="preserve">1.42808187007904</t>
@@ -3896,10 +3896,10 @@
     <t xml:space="preserve">1.43882834911346</t>
   </si>
   <si>
-    <t xml:space="preserve">1.46151530742645</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.44440042972565</t>
+    <t xml:space="preserve">1.46151518821716</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.44440054893494</t>
   </si>
   <si>
     <t xml:space="preserve">1.46668934822083</t>
@@ -3908,28 +3908,28 @@
     <t xml:space="preserve">1.4758437871933</t>
   </si>
   <si>
-    <t xml:space="preserve">1.46907758712769</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.48619222640991</t>
+    <t xml:space="preserve">1.4690774679184</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.4861923456192</t>
   </si>
   <si>
     <t xml:space="preserve">1.44718658924103</t>
   </si>
   <si>
-    <t xml:space="preserve">1.4364401102066</t>
+    <t xml:space="preserve">1.43644022941589</t>
   </si>
   <si>
     <t xml:space="preserve">1.45037078857422</t>
   </si>
   <si>
-    <t xml:space="preserve">1.44201231002808</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.44081830978394</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.42370367050171</t>
+    <t xml:space="preserve">1.44201242923737</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.44081819057465</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.423703789711</t>
   </si>
   <si>
     <t xml:space="preserve">1.3476824760437</t>
@@ -3938,7 +3938,7 @@
     <t xml:space="preserve">1.36519527435303</t>
   </si>
   <si>
-    <t xml:space="preserve">1.40499687194824</t>
+    <t xml:space="preserve">1.40499699115753</t>
   </si>
   <si>
     <t xml:space="preserve">1.42449963092804</t>
@@ -3947,52 +3947,52 @@
     <t xml:space="preserve">1.4599232673645</t>
   </si>
   <si>
-    <t xml:space="preserve">1.51604342460632</t>
+    <t xml:space="preserve">1.51604330539703</t>
   </si>
   <si>
     <t xml:space="preserve">1.50848114490509</t>
   </si>
   <si>
-    <t xml:space="preserve">1.54708874225616</t>
+    <t xml:space="preserve">1.54708886146545</t>
   </si>
   <si>
     <t xml:space="preserve">1.53873026371002</t>
   </si>
   <si>
-    <t xml:space="preserve">1.57574582099915</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.56261146068573</t>
+    <t xml:space="preserve">1.57574594020844</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.56261122226715</t>
   </si>
   <si>
     <t xml:space="preserve">1.61753761768341</t>
   </si>
   <si>
-    <t xml:space="preserve">1.60002481937408</t>
+    <t xml:space="preserve">1.60002470016479</t>
   </si>
   <si>
     <t xml:space="preserve">1.61833357810974</t>
   </si>
   <si>
-    <t xml:space="preserve">1.64380669593811</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.64539861679077</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.63903045654297</t>
+    <t xml:space="preserve">1.64380657672882</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.64539873600006</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.63903033733368</t>
   </si>
   <si>
     <t xml:space="preserve">1.6398264169693</t>
   </si>
   <si>
-    <t xml:space="preserve">1.64221441745758</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.65415513515472</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.63027405738831</t>
+    <t xml:space="preserve">1.64221453666687</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.65415501594543</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.6302741765976</t>
   </si>
   <si>
     <t xml:space="preserve">1.62947797775269</t>
@@ -4001,37 +4001,37 @@
     <t xml:space="preserve">1.63345813751221</t>
   </si>
   <si>
-    <t xml:space="preserve">1.59365677833557</t>
+    <t xml:space="preserve">1.59365665912628</t>
   </si>
   <si>
     <t xml:space="preserve">1.61196541786194</t>
   </si>
   <si>
-    <t xml:space="preserve">1.50808322429657</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.49932682514191</t>
+    <t xml:space="preserve">1.50808310508728</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.49932670593262</t>
   </si>
   <si>
     <t xml:space="preserve">1.52639186382294</t>
   </si>
   <si>
-    <t xml:space="preserve">1.52400374412537</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.50609302520752</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.53196406364441</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.52758586406708</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.52002358436584</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.53116798400879</t>
+    <t xml:space="preserve">1.52400386333466</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.50609290599823</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.5319641828537</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.52758598327637</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.52002370357513</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.5311678647995</t>
   </si>
   <si>
     <t xml:space="preserve">1.52121758460999</t>
@@ -4040,10 +4040,10 @@
     <t xml:space="preserve">1.53315806388855</t>
   </si>
   <si>
-    <t xml:space="preserve">1.51325738430023</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.47027158737183</t>
+    <t xml:space="preserve">1.51325726509094</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.47027170658112</t>
   </si>
   <si>
     <t xml:space="preserve">1.4300719499588</t>
@@ -4052,7 +4052,7 @@
     <t xml:space="preserve">1.43564414978027</t>
   </si>
   <si>
-    <t xml:space="preserve">1.42887783050537</t>
+    <t xml:space="preserve">1.42887794971466</t>
   </si>
   <si>
     <t xml:space="preserve">1.41176319122314</t>
@@ -4070,19 +4070,19 @@
     <t xml:space="preserve">1.3775337934494</t>
   </si>
   <si>
-    <t xml:space="preserve">1.36439907550812</t>
+    <t xml:space="preserve">1.36439919471741</t>
   </si>
   <si>
     <t xml:space="preserve">1.35166275501251</t>
   </si>
   <si>
-    <t xml:space="preserve">1.39425051212311</t>
+    <t xml:space="preserve">1.39425039291382</t>
   </si>
   <si>
     <t xml:space="preserve">1.40619099140167</t>
   </si>
   <si>
-    <t xml:space="preserve">1.38191187381744</t>
+    <t xml:space="preserve">1.38191211223602</t>
   </si>
   <si>
     <t xml:space="preserve">1.38907623291016</t>
@@ -4091,28 +4091,28 @@
     <t xml:space="preserve">1.37872791290283</t>
   </si>
   <si>
-    <t xml:space="preserve">1.47902798652649</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.41614139080048</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.41375327110291</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.37912583351135</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.41494727134705</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.40260887145996</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.42569386959076</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.4432065486908</t>
+    <t xml:space="preserve">1.4790278673172</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.41614151000977</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.41375339031219</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.37912571430206</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.41494739055634</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.40260875225067</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.42569375038147</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.44320642948151</t>
   </si>
   <si>
     <t xml:space="preserve">1.45435094833374</t>
@@ -4124,7 +4124,7 @@
     <t xml:space="preserve">1.50052082538605</t>
   </si>
   <si>
-    <t xml:space="preserve">1.52917802333832</t>
+    <t xml:space="preserve">1.52917790412903</t>
   </si>
   <si>
     <t xml:space="preserve">1.5251978635788</t>
@@ -4139,7 +4139,7 @@
     <t xml:space="preserve">1.56181526184082</t>
   </si>
   <si>
-    <t xml:space="preserve">1.55624306201935</t>
+    <t xml:space="preserve">1.55624294281006</t>
   </si>
   <si>
     <t xml:space="preserve">1.54111838340759</t>
@@ -4148,40 +4148,40 @@
     <t xml:space="preserve">1.52678990364075</t>
   </si>
   <si>
-    <t xml:space="preserve">1.49813258647919</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.42847990989685</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.42330551147461</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.48818230628967</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.52320766448975</t>
+    <t xml:space="preserve">1.49813270568848</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.42848002910614</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.4233056306839</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.48818242549896</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.52320754528046</t>
   </si>
   <si>
     <t xml:space="preserve">1.46509742736816</t>
   </si>
   <si>
-    <t xml:space="preserve">1.47624182701111</t>
+    <t xml:space="preserve">1.4762419462204</t>
   </si>
   <si>
     <t xml:space="preserve">1.54350650310516</t>
   </si>
   <si>
-    <t xml:space="preserve">1.5737556219101</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.5578351020813</t>
+    <t xml:space="preserve">1.57375574111938</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.55783522129059</t>
   </si>
   <si>
     <t xml:space="preserve">1.61514949798584</t>
   </si>
   <si>
-    <t xml:space="preserve">1.61276125907898</t>
+    <t xml:space="preserve">1.61276137828827</t>
   </si>
   <si>
     <t xml:space="preserve">1.63743829727173</t>
@@ -4190,19 +4190,19 @@
     <t xml:space="preserve">1.574551820755</t>
   </si>
   <si>
-    <t xml:space="preserve">1.71863353252411</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.69793677330017</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.60718905925751</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.56022322177887</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.44161450862885</t>
+    <t xml:space="preserve">1.7186336517334</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.69793665409088</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.60718929767609</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.56022334098816</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.44161438941956</t>
   </si>
   <si>
     <t xml:space="preserve">1.46788346767426</t>
@@ -4211,10 +4211,10 @@
     <t xml:space="preserve">1.32260763645172</t>
   </si>
   <si>
-    <t xml:space="preserve">1.31743335723877</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.24857664108276</t>
+    <t xml:space="preserve">1.31743347644806</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.24857652187347</t>
   </si>
   <si>
     <t xml:space="preserve">1.11643528938293</t>
@@ -4223,28 +4223,28 @@
     <t xml:space="preserve">1.05872297286987</t>
   </si>
   <si>
-    <t xml:space="preserve">1.11563920974731</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.22708380222321</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.13514196872711</t>
+    <t xml:space="preserve">1.11563909053802</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.22708368301392</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.1351420879364</t>
   </si>
   <si>
     <t xml:space="preserve">1.12877357006073</t>
   </si>
   <si>
-    <t xml:space="preserve">1.17494344711304</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.19882464408875</t>
+    <t xml:space="preserve">1.17494356632233</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.19882452487946</t>
   </si>
   <si>
     <t xml:space="preserve">1.28678619861603</t>
   </si>
   <si>
-    <t xml:space="preserve">1.25773108005524</t>
+    <t xml:space="preserve">1.25773096084595</t>
   </si>
   <si>
     <t xml:space="preserve">1.2497706413269</t>
@@ -4253,37 +4253,37 @@
     <t xml:space="preserve">1.2660893201828</t>
   </si>
   <si>
-    <t xml:space="preserve">1.24698460102081</t>
+    <t xml:space="preserve">1.24698448181152</t>
   </si>
   <si>
     <t xml:space="preserve">1.23464608192444</t>
   </si>
   <si>
-    <t xml:space="preserve">1.243004322052</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.25892508029938</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.33295595645905</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.30668699741364</t>
+    <t xml:space="preserve">1.24300444126129</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.25892496109009</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.33295607566833</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.30668687820435</t>
   </si>
   <si>
     <t xml:space="preserve">1.26529312133789</t>
   </si>
   <si>
-    <t xml:space="preserve">1.27922368049622</t>
+    <t xml:space="preserve">1.27922379970551</t>
   </si>
   <si>
     <t xml:space="preserve">1.22429764270782</t>
   </si>
   <si>
-    <t xml:space="preserve">1.2262876033783</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.27484560012817</t>
+    <t xml:space="preserve">1.22628772258759</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.27484571933746</t>
   </si>
   <si>
     <t xml:space="preserve">1.27285552024841</t>
@@ -4292,31 +4292,31 @@
     <t xml:space="preserve">1.23225796222687</t>
   </si>
   <si>
-    <t xml:space="preserve">1.23504400253296</t>
+    <t xml:space="preserve">1.23504412174225</t>
   </si>
   <si>
     <t xml:space="preserve">1.24778056144714</t>
   </si>
   <si>
-    <t xml:space="preserve">1.25335276126862</t>
+    <t xml:space="preserve">1.25335288047791</t>
   </si>
   <si>
     <t xml:space="preserve">1.29753255844116</t>
   </si>
   <si>
-    <t xml:space="preserve">1.30628883838654</t>
+    <t xml:space="preserve">1.30628895759583</t>
   </si>
   <si>
     <t xml:space="preserve">1.28758203983307</t>
   </si>
   <si>
-    <t xml:space="preserve">1.27404952049255</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.2593230009079</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.26847732067108</t>
+    <t xml:space="preserve">1.27404963970184</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.25932312011719</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.26847743988037</t>
   </si>
   <si>
     <t xml:space="preserve">1.26011896133423</t>
@@ -4334,13 +4334,13 @@
     <t xml:space="preserve">1.21912336349487</t>
   </si>
   <si>
-    <t xml:space="preserve">1.22071552276611</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.21116316318512</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.35325491428375</t>
+    <t xml:space="preserve">1.22071540355682</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.21116292476654</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.35325479507446</t>
   </si>
   <si>
     <t xml:space="preserve">1.38629019260406</t>
@@ -4349,49 +4349,49 @@
     <t xml:space="preserve">1.38668811321259</t>
   </si>
   <si>
-    <t xml:space="preserve">1.37395167350769</t>
+    <t xml:space="preserve">1.3739515542984</t>
   </si>
   <si>
     <t xml:space="preserve">1.40539503097534</t>
   </si>
   <si>
-    <t xml:space="preserve">1.39862859249115</t>
+    <t xml:space="preserve">1.39862883090973</t>
   </si>
   <si>
     <t xml:space="preserve">1.40738499164581</t>
   </si>
   <si>
-    <t xml:space="preserve">1.39027035236359</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.4838342666626</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.49949717521667</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.54153907299042</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.56049907207489</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.55390441417694</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.55349206924438</t>
+    <t xml:space="preserve">1.39027047157288</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.48383438587189</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.49949705600739</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.54153895378113</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.56049919128418</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.55390429496765</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.55349218845367</t>
   </si>
   <si>
     <t xml:space="preserve">1.57987141609192</t>
   </si>
   <si>
-    <t xml:space="preserve">1.57616186141968</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.58976364135742</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.53576874732971</t>
+    <t xml:space="preserve">1.57616174221039</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.58976376056671</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.53576862812042</t>
   </si>
   <si>
     <t xml:space="preserve">1.59182453155518</t>
@@ -4400,7 +4400,7 @@
     <t xml:space="preserve">1.55307996273041</t>
   </si>
   <si>
-    <t xml:space="preserve">1.5984194278717</t>
+    <t xml:space="preserve">1.59841930866241</t>
   </si>
   <si>
     <t xml:space="preserve">1.60831165313721</t>
@@ -4415,16 +4415,16 @@
     <t xml:space="preserve">1.36430323123932</t>
   </si>
   <si>
-    <t xml:space="preserve">1.41788613796234</t>
+    <t xml:space="preserve">1.41788625717163</t>
   </si>
   <si>
     <t xml:space="preserve">1.35770845413208</t>
   </si>
   <si>
-    <t xml:space="preserve">1.38326334953308</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.40799391269684</t>
+    <t xml:space="preserve">1.38326346874237</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.40799403190613</t>
   </si>
   <si>
     <t xml:space="preserve">1.41458880901337</t>
@@ -4433,13 +4433,13 @@
     <t xml:space="preserve">1.41252791881561</t>
   </si>
   <si>
-    <t xml:space="preserve">1.34451878070831</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.38820958137512</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.36718857288361</t>
+    <t xml:space="preserve">1.3445188999176</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.38820946216583</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.36718845367432</t>
   </si>
   <si>
     <t xml:space="preserve">1.36512768268585</t>
@@ -4451,7 +4451,7 @@
     <t xml:space="preserve">1.2921724319458</t>
   </si>
   <si>
-    <t xml:space="preserve">1.25219130516052</t>
+    <t xml:space="preserve">1.25219142436981</t>
   </si>
   <si>
     <t xml:space="preserve">1.25136709213257</t>
@@ -4460,25 +4460,25 @@
     <t xml:space="preserve">1.18789184093475</t>
   </si>
   <si>
-    <t xml:space="preserve">1.16934382915497</t>
+    <t xml:space="preserve">1.16934394836426</t>
   </si>
   <si>
     <t xml:space="preserve">1.2299337387085</t>
   </si>
   <si>
-    <t xml:space="preserve">1.24477219581604</t>
+    <t xml:space="preserve">1.24477207660675</t>
   </si>
   <si>
     <t xml:space="preserve">1.18830394744873</t>
   </si>
   <si>
-    <t xml:space="preserve">1.1590393781662</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.128950715065</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.05929279327393</t>
+    <t xml:space="preserve">1.15903961658478</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.12895059585571</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.05929291248322</t>
   </si>
   <si>
     <t xml:space="preserve">1.06588768959045</t>
@@ -4493,7 +4493,7 @@
     <t xml:space="preserve">1.12029492855072</t>
   </si>
   <si>
-    <t xml:space="preserve">1.08526003360748</t>
+    <t xml:space="preserve">1.0852597951889</t>
   </si>
   <si>
     <t xml:space="preserve">1.06794857978821</t>
@@ -4508,10 +4508,10 @@
     <t xml:space="preserve">1.08567214012146</t>
   </si>
   <si>
-    <t xml:space="preserve">1.08814525604248</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.11287581920624</t>
+    <t xml:space="preserve">1.08814513683319</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.11287569999695</t>
   </si>
   <si>
     <t xml:space="preserve">1.12482893466949</t>
@@ -4520,7 +4520,7 @@
     <t xml:space="preserve">1.14337682723999</t>
   </si>
   <si>
-    <t xml:space="preserve">1.18912827968597</t>
+    <t xml:space="preserve">1.18912839889526</t>
   </si>
   <si>
     <t xml:space="preserve">1.18129694461823</t>
@@ -4529,43 +4529,43 @@
     <t xml:space="preserve">1.29588198661804</t>
   </si>
   <si>
-    <t xml:space="preserve">1.32720732688904</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.33792412281036</t>
+    <t xml:space="preserve">1.32720744609833</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.33792400360107</t>
   </si>
   <si>
     <t xml:space="preserve">1.36842501163483</t>
   </si>
   <si>
-    <t xml:space="preserve">1.34987711906433</t>
+    <t xml:space="preserve">1.34987723827362</t>
   </si>
   <si>
     <t xml:space="preserve">1.35647189617157</t>
   </si>
   <si>
-    <t xml:space="preserve">1.35070145130157</t>
+    <t xml:space="preserve">1.35070133209229</t>
   </si>
   <si>
     <t xml:space="preserve">1.30659854412079</t>
   </si>
   <si>
-    <t xml:space="preserve">1.26290798187256</t>
+    <t xml:space="preserve">1.26290786266327</t>
   </si>
   <si>
     <t xml:space="preserve">1.28063154220581</t>
   </si>
   <si>
-    <t xml:space="preserve">1.28021931648254</t>
+    <t xml:space="preserve">1.28021919727325</t>
   </si>
   <si>
     <t xml:space="preserve">1.26084697246552</t>
   </si>
   <si>
-    <t xml:space="preserve">1.22004151344299</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.22045373916626</t>
+    <t xml:space="preserve">1.22004163265228</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.22045385837555</t>
   </si>
   <si>
     <t xml:space="preserve">1.24106252193451</t>
@@ -4574,10 +4574,10 @@
     <t xml:space="preserve">1.24065041542053</t>
   </si>
   <si>
-    <t xml:space="preserve">1.22333908081055</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.25301563739777</t>
+    <t xml:space="preserve">1.22333896160126</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.25301575660706</t>
   </si>
   <si>
     <t xml:space="preserve">1.21550762653351</t>
@@ -4592,7 +4592,7 @@
     <t xml:space="preserve">1.23776519298553</t>
   </si>
   <si>
-    <t xml:space="preserve">1.27609741687775</t>
+    <t xml:space="preserve">1.27609753608704</t>
   </si>
   <si>
     <t xml:space="preserve">1.33957278728485</t>
@@ -4604,22 +4604,22 @@
     <t xml:space="preserve">1.3758442401886</t>
   </si>
   <si>
-    <t xml:space="preserve">1.38120257854462</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.38985812664032</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.39686512947083</t>
+    <t xml:space="preserve">1.38120245933533</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.38985824584961</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.39686524868011</t>
   </si>
   <si>
     <t xml:space="preserve">1.3729590177536</t>
   </si>
   <si>
-    <t xml:space="preserve">1.38408768177032</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.43025135993958</t>
+    <t xml:space="preserve">1.38408780097961</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.43025147914886</t>
   </si>
   <si>
     <t xml:space="preserve">1.37337112426758</t>
@@ -4631,43 +4631,43 @@
     <t xml:space="preserve">1.34163355827332</t>
   </si>
   <si>
-    <t xml:space="preserve">1.32020032405853</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.28269243240356</t>
+    <t xml:space="preserve">1.32020044326782</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.28269231319427</t>
   </si>
   <si>
     <t xml:space="preserve">1.30330121517181</t>
   </si>
   <si>
-    <t xml:space="preserve">1.32844400405884</t>
+    <t xml:space="preserve">1.32844388484955</t>
   </si>
   <si>
     <t xml:space="preserve">1.38491201400757</t>
   </si>
   <si>
-    <t xml:space="preserve">1.3589448928833</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.31731534004211</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.33462643623352</t>
+    <t xml:space="preserve">1.35894501209259</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.31731522083282</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.33462655544281</t>
   </si>
   <si>
     <t xml:space="preserve">1.31855165958405</t>
   </si>
   <si>
-    <t xml:space="preserve">1.30824732780457</t>
+    <t xml:space="preserve">1.30824744701385</t>
   </si>
   <si>
     <t xml:space="preserve">1.34080922603607</t>
   </si>
   <si>
-    <t xml:space="preserve">1.36347889900208</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.39274346828461</t>
+    <t xml:space="preserve">1.36347901821136</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.39274334907532</t>
   </si>
   <si>
     <t xml:space="preserve">1.40181136131287</t>
@@ -4679,58 +4679,58 @@
     <t xml:space="preserve">1.41664958000183</t>
   </si>
   <si>
-    <t xml:space="preserve">1.43560981750488</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.4764152765274</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.46734738349915</t>
+    <t xml:space="preserve">1.43560969829559</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.47641515731812</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.46734726428986</t>
   </si>
   <si>
     <t xml:space="preserve">1.4694082736969</t>
   </si>
   <si>
-    <t xml:space="preserve">1.51103806495667</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.52093017101288</t>
+    <t xml:space="preserve">1.51103794574738</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.52093029022217</t>
   </si>
   <si>
     <t xml:space="preserve">1.54359984397888</t>
   </si>
   <si>
-    <t xml:space="preserve">1.56214785575867</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.58770287036896</t>
+    <t xml:space="preserve">1.56214773654938</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.58770275115967</t>
   </si>
   <si>
     <t xml:space="preserve">1.58893930912018</t>
   </si>
   <si>
-    <t xml:space="preserve">1.65942132472992</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.68992233276367</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.5600870847702</t>
+    <t xml:space="preserve">1.65942144393921</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.68992257118225</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.56008696556091</t>
   </si>
   <si>
     <t xml:space="preserve">1.51680850982666</t>
   </si>
   <si>
-    <t xml:space="preserve">1.54854607582092</t>
+    <t xml:space="preserve">1.54854595661163</t>
   </si>
   <si>
     <t xml:space="preserve">1.52711284160614</t>
   </si>
   <si>
-    <t xml:space="preserve">1.54648506641388</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.55184352397919</t>
+    <t xml:space="preserve">1.54648518562317</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.5518434047699</t>
   </si>
   <si>
     <t xml:space="preserve">1.57410097122192</t>
@@ -4742,7 +4742,7 @@
     <t xml:space="preserve">1.58193230628967</t>
   </si>
   <si>
-    <t xml:space="preserve">1.59965598583221</t>
+    <t xml:space="preserve">1.59965586662292</t>
   </si>
   <si>
     <t xml:space="preserve">1.61284554004669</t>
@@ -4754,163 +4754,163 @@
     <t xml:space="preserve">1.60872387886047</t>
   </si>
   <si>
-    <t xml:space="preserve">1.61573076248169</t>
+    <t xml:space="preserve">1.61573088169098</t>
   </si>
   <si>
     <t xml:space="preserve">1.62562298774719</t>
   </si>
   <si>
-    <t xml:space="preserve">1.60666298866272</t>
+    <t xml:space="preserve">1.60666286945343</t>
   </si>
   <si>
     <t xml:space="preserve">1.59883153438568</t>
   </si>
   <si>
-    <t xml:space="preserve">1.59017598628998</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.59718298912048</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.60171675682068</t>
+    <t xml:space="preserve">1.59017586708069</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.5971827507019</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.60171687602997</t>
   </si>
   <si>
     <t xml:space="preserve">1.60954809188843</t>
   </si>
   <si>
-    <t xml:space="preserve">1.60913586616516</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.61902809143066</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.60707497596741</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.55101907253265</t>
+    <t xml:space="preserve">1.60913598537445</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.61902821063995</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.6070750951767</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.55101919174194</t>
   </si>
   <si>
     <t xml:space="preserve">1.54978263378143</t>
   </si>
   <si>
-    <t xml:space="preserve">1.53782951831818</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.6041898727417</t>
+    <t xml:space="preserve">1.53782939910889</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.60418975353241</t>
   </si>
   <si>
     <t xml:space="preserve">1.60295331478119</t>
   </si>
   <si>
-    <t xml:space="preserve">1.59512186050415</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.5815201997757</t>
+    <t xml:space="preserve">1.59512197971344</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.58152008056641</t>
   </si>
   <si>
     <t xml:space="preserve">1.61531865596771</t>
   </si>
   <si>
-    <t xml:space="preserve">1.63633954524994</t>
+    <t xml:space="preserve">1.63633942604065</t>
   </si>
   <si>
     <t xml:space="preserve">1.67920589447021</t>
   </si>
   <si>
-    <t xml:space="preserve">1.67343533039093</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.71712589263916</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.72536969184875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.73938369750977</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.73855924606323</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.74845159053802</t>
+    <t xml:space="preserve">1.67343544960022</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.71712613105774</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.72536957263947</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.73938357830048</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.73855912685394</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.74845147132874</t>
   </si>
   <si>
     <t xml:space="preserve">1.80533182621002</t>
   </si>
   <si>
-    <t xml:space="preserve">1.82511639595032</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.7970883846283</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.8564418554306</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.85479307174683</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.89024019241333</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.90178108215332</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.92898464202881</t>
+    <t xml:space="preserve">1.82511627674103</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.79708826541901</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.85644161701202</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.85479295253754</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.89023995399475</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.90178084373474</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.92898452281952</t>
   </si>
   <si>
     <t xml:space="preserve">1.93310654163361</t>
   </si>
   <si>
-    <t xml:space="preserve">1.97349977493286</t>
+    <t xml:space="preserve">1.97349953651428</t>
   </si>
   <si>
     <t xml:space="preserve">2.0040009021759</t>
   </si>
   <si>
-    <t xml:space="preserve">2.00317645072937</t>
+    <t xml:space="preserve">2.00317668914795</t>
   </si>
   <si>
     <t xml:space="preserve">2.07489490509033</t>
   </si>
   <si>
-    <t xml:space="preserve">2.14331650733948</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.08396291732788</t>
+    <t xml:space="preserve">2.1433162689209</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.08396315574646</t>
   </si>
   <si>
     <t xml:space="preserve">2.09385514259338</t>
   </si>
   <si>
-    <t xml:space="preserve">2.12847781181335</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.098801612854</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.11941027641296</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.10457158088684</t>
+    <t xml:space="preserve">2.12847805023193</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.09880113601685</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.11941003799438</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.10457181930542</t>
   </si>
   <si>
     <t xml:space="preserve">2.14991116523743</t>
   </si>
   <si>
-    <t xml:space="preserve">2.13919448852539</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.1375458240509</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.2043182849884</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.30159211158752</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.26449584960938</t>
+    <t xml:space="preserve">2.13919472694397</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.13754558563232</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.20431852340698</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.30159187316895</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.26449632644653</t>
   </si>
   <si>
     <t xml:space="preserve">2.25295519828796</t>
@@ -4919,10 +4919,10 @@
     <t xml:space="preserve">2.15403294563293</t>
   </si>
   <si>
-    <t xml:space="preserve">2.17629051208496</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.12600517272949</t>
+    <t xml:space="preserve">2.17629027366638</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.12600493431091</t>
   </si>
   <si>
     <t xml:space="preserve">2.18700695037842</t>
@@ -4937,16 +4937,16 @@
     <t xml:space="preserve">2.20844006538391</t>
   </si>
   <si>
-    <t xml:space="preserve">2.22657585144043</t>
+    <t xml:space="preserve">2.22657608985901</t>
   </si>
   <si>
     <t xml:space="preserve">2.27026653289795</t>
   </si>
   <si>
-    <t xml:space="preserve">2.27273964881897</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.3304443359375</t>
+    <t xml:space="preserve">2.27273941040039</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.33044457435608</t>
   </si>
   <si>
     <t xml:space="preserve">2.32220053672791</t>
@@ -4955,43 +4955,43 @@
     <t xml:space="preserve">2.21833229064941</t>
   </si>
   <si>
-    <t xml:space="preserve">2.00729823112488</t>
+    <t xml:space="preserve">2.0072979927063</t>
   </si>
   <si>
     <t xml:space="preserve">2.04027223587036</t>
   </si>
   <si>
-    <t xml:space="preserve">1.89271306991577</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.89683520793915</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.84407639503479</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.87045574188232</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.96195900440216</t>
+    <t xml:space="preserve">1.89271318912506</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.89683496952057</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.8440762758255</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.87045562267303</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.96195888519287</t>
   </si>
   <si>
     <t xml:space="preserve">1.93393075466156</t>
   </si>
   <si>
-    <t xml:space="preserve">1.89848375320435</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.82181882858276</t>
+    <t xml:space="preserve">1.89848351478577</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.82181894779205</t>
   </si>
   <si>
     <t xml:space="preserve">1.84325218200684</t>
   </si>
   <si>
-    <t xml:space="preserve">1.84902238845825</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.89930784702301</t>
+    <t xml:space="preserve">1.84902262687683</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.8993079662323</t>
   </si>
   <si>
     <t xml:space="preserve">1.88776707649231</t>
@@ -5009,34 +5009,34 @@
     <t xml:space="preserve">1.94876933097839</t>
   </si>
   <si>
-    <t xml:space="preserve">1.94547176361084</t>
+    <t xml:space="preserve">1.94547140598297</t>
   </si>
   <si>
     <t xml:space="preserve">1.98339188098907</t>
   </si>
   <si>
-    <t xml:space="preserve">1.97679686546326</t>
+    <t xml:space="preserve">1.97679710388184</t>
   </si>
   <si>
     <t xml:space="preserve">2.06912446022034</t>
   </si>
   <si>
-    <t xml:space="preserve">2.07901692390442</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.16392517089844</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.20102095603943</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.23069787025452</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.26284718513489</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.25377941131592</t>
+    <t xml:space="preserve">2.079017162323</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.16392493247986</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.20102119445801</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.23069763183594</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.26284742355347</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.2537796497345</t>
   </si>
   <si>
     <t xml:space="preserve">2.1020987033844</t>
@@ -5051,7 +5051,7 @@
     <t xml:space="preserve">2.06500291824341</t>
   </si>
   <si>
-    <t xml:space="preserve">2.10045003890991</t>
+    <t xml:space="preserve">2.10045027732849</t>
   </si>
   <si>
     <t xml:space="preserve">2.0666515827179</t>
@@ -5063,7 +5063,7 @@
     <t xml:space="preserve">2.26119875907898</t>
   </si>
   <si>
-    <t xml:space="preserve">2.25048208236694</t>
+    <t xml:space="preserve">2.25048232078552</t>
   </si>
   <si>
     <t xml:space="preserve">2.2001965045929</t>
@@ -5075,19 +5075,19 @@
     <t xml:space="preserve">2.2356436252594</t>
   </si>
   <si>
-    <t xml:space="preserve">2.23481965065002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.22080564498901</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.22575163841248</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.25335788726807</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.23179030418396</t>
+    <t xml:space="preserve">2.23481941223145</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.22080540657043</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.2257513999939</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.25335764884949</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.23179006576538</t>
   </si>
   <si>
     <t xml:space="preserve">2.13603138923645</t>
@@ -5102,10 +5102,10 @@
     <t xml:space="preserve">2.12395358085632</t>
   </si>
   <si>
-    <t xml:space="preserve">2.0972101688385</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.06183981895447</t>
+    <t xml:space="preserve">2.09720993041992</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.06183958053589</t>
   </si>
   <si>
     <t xml:space="preserve">2.11618947982788</t>
@@ -5114,25 +5114,25 @@
     <t xml:space="preserve">2.16363739967346</t>
   </si>
   <si>
-    <t xml:space="preserve">2.15328526496887</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.15846157073975</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.15414786338806</t>
+    <t xml:space="preserve">2.15328502655029</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.15846133232117</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.15414810180664</t>
   </si>
   <si>
     <t xml:space="preserve">2.15501046180725</t>
   </si>
   <si>
-    <t xml:space="preserve">2.11273837089539</t>
+    <t xml:space="preserve">2.11273860931396</t>
   </si>
   <si>
     <t xml:space="preserve">2.14465832710266</t>
   </si>
   <si>
-    <t xml:space="preserve">2.14983439445496</t>
+    <t xml:space="preserve">2.14983463287354</t>
   </si>
   <si>
     <t xml:space="preserve">2.20073366165161</t>
@@ -5147,37 +5147,37 @@
     <t xml:space="preserve">2.31288361549377</t>
   </si>
   <si>
-    <t xml:space="preserve">2.34652876853943</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.37931084632874</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.36809587478638</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.31633424758911</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.28614044189453</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.32927513122559</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.34566617012024</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.37672305107117</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.40001606941223</t>
+    <t xml:space="preserve">2.34652900695801</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.37931108474731</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.36809611320496</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.31633448600769</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.28614020347595</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.32927465438843</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.34566593170166</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.37672328948975</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.40001583099365</t>
   </si>
   <si>
     <t xml:space="preserve">2.42675924301147</t>
   </si>
   <si>
-    <t xml:space="preserve">2.36550807952881</t>
+    <t xml:space="preserve">2.36550831794739</t>
   </si>
   <si>
     <t xml:space="preserve">2.35343027114868</t>
@@ -5189,16 +5189,16 @@
     <t xml:space="preserve">2.3611946105957</t>
   </si>
   <si>
-    <t xml:space="preserve">2.42072033882141</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.44056224822998</t>
+    <t xml:space="preserve">2.42072057723999</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.44056248664856</t>
   </si>
   <si>
     <t xml:space="preserve">2.47938370704651</t>
   </si>
   <si>
-    <t xml:space="preserve">2.5337336063385</t>
+    <t xml:space="preserve">2.53373336791992</t>
   </si>
   <si>
     <t xml:space="preserve">2.51302886009216</t>
@@ -5207,22 +5207,22 @@
     <t xml:space="preserve">2.56133961677551</t>
   </si>
   <si>
-    <t xml:space="preserve">2.55443787574768</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.53200817108154</t>
+    <t xml:space="preserve">2.55443811416626</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.53200793266296</t>
   </si>
   <si>
     <t xml:space="preserve">2.58376955986023</t>
   </si>
   <si>
-    <t xml:space="preserve">2.60188627243042</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.6208655834198</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.63553142547607</t>
+    <t xml:space="preserve">2.601886510849</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.62086582183838</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.63553166389465</t>
   </si>
   <si>
     <t xml:space="preserve">2.73819208145142</t>
@@ -5246,7 +5246,7 @@
     <t xml:space="preserve">2.48714780807495</t>
   </si>
   <si>
-    <t xml:space="preserve">2.44660139083862</t>
+    <t xml:space="preserve">2.44660115242004</t>
   </si>
   <si>
     <t xml:space="preserve">2.45264005661011</t>
@@ -5258,16 +5258,16 @@
     <t xml:space="preserve">2.23265314102173</t>
   </si>
   <si>
-    <t xml:space="preserve">2.28010106086731</t>
+    <t xml:space="preserve">2.28010129928589</t>
   </si>
   <si>
     <t xml:space="preserve">2.34048986434937</t>
   </si>
   <si>
-    <t xml:space="preserve">2.34911680221558</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.3154718875885</t>
+    <t xml:space="preserve">2.34911704063416</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.31547164916992</t>
   </si>
   <si>
     <t xml:space="preserve">2.38276195526123</t>
@@ -5300,13 +5300,13 @@
     <t xml:space="preserve">2.36464524269104</t>
   </si>
   <si>
-    <t xml:space="preserve">2.26198482513428</t>
+    <t xml:space="preserve">2.2619845867157</t>
   </si>
   <si>
     <t xml:space="preserve">2.23092770576477</t>
   </si>
   <si>
-    <t xml:space="preserve">2.24904417991638</t>
+    <t xml:space="preserve">2.24904441833496</t>
   </si>
   <si>
     <t xml:space="preserve">2.31115818023682</t>
@@ -5315,10 +5315,10 @@
     <t xml:space="preserve">2.38793802261353</t>
   </si>
   <si>
-    <t xml:space="preserve">2.41295623779297</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.42589664459229</t>
+    <t xml:space="preserve">2.41295599937439</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.42589688301086</t>
   </si>
   <si>
     <t xml:space="preserve">2.46989393234253</t>
@@ -5330,7 +5330,7 @@
     <t xml:space="preserve">2.57428002357483</t>
   </si>
   <si>
-    <t xml:space="preserve">2.55271291732788</t>
+    <t xml:space="preserve">2.5527126789093</t>
   </si>
   <si>
     <t xml:space="preserve">2.4388370513916</t>
@@ -5345,7 +5345,7 @@
     <t xml:space="preserve">2.46644330024719</t>
   </si>
   <si>
-    <t xml:space="preserve">2.43107271194458</t>
+    <t xml:space="preserve">2.43107295036316</t>
   </si>
   <si>
     <t xml:space="preserve">2.43279814720154</t>
@@ -5363,34 +5363,34 @@
     <t xml:space="preserve">2.48628520965576</t>
   </si>
   <si>
-    <t xml:space="preserve">2.55530071258545</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.53632164001465</t>
+    <t xml:space="preserve">2.55530047416687</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.53632140159607</t>
   </si>
   <si>
     <t xml:space="preserve">2.55357551574707</t>
   </si>
   <si>
-    <t xml:space="preserve">2.61310124397278</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.6381196975708</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.60274887084961</t>
+    <t xml:space="preserve">2.61310148239136</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.63811945915222</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.60274910926819</t>
   </si>
   <si>
     <t xml:space="preserve">2.46730589866638</t>
   </si>
   <si>
-    <t xml:space="preserve">2.57169198989868</t>
+    <t xml:space="preserve">2.5716917514801</t>
   </si>
   <si>
     <t xml:space="preserve">2.50440192222595</t>
   </si>
   <si>
-    <t xml:space="preserve">2.52683186531067</t>
+    <t xml:space="preserve">2.52683162689209</t>
   </si>
   <si>
     <t xml:space="preserve">2.51389145851135</t>
@@ -5399,7 +5399,7 @@
     <t xml:space="preserve">2.52510643005371</t>
   </si>
   <si>
-    <t xml:space="preserve">2.6476092338562</t>
+    <t xml:space="preserve">2.64760899543762</t>
   </si>
   <si>
     <t xml:space="preserve">2.70713496208191</t>
@@ -5447,16 +5447,16 @@
     <t xml:space="preserve">2.90986824035645</t>
   </si>
   <si>
-    <t xml:space="preserve">2.94696402549744</t>
+    <t xml:space="preserve">2.94696426391602</t>
   </si>
   <si>
     <t xml:space="preserve">2.94782686233521</t>
   </si>
   <si>
-    <t xml:space="preserve">2.9245343208313</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.8900260925293</t>
+    <t xml:space="preserve">2.92453408241272</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.89002633094788</t>
   </si>
   <si>
     <t xml:space="preserve">2.98319721221924</t>
@@ -5468,7 +5468,7 @@
     <t xml:space="preserve">2.98837351799011</t>
   </si>
   <si>
-    <t xml:space="preserve">2.9676685333252</t>
+    <t xml:space="preserve">2.96766877174377</t>
   </si>
   <si>
     <t xml:space="preserve">2.95214033126831</t>
@@ -5495,7 +5495,7 @@
     <t xml:space="preserve">2.64070773124695</t>
   </si>
   <si>
-    <t xml:space="preserve">2.64588379859924</t>
+    <t xml:space="preserve">2.64588356018066</t>
   </si>
   <si>
     <t xml:space="preserve">2.64502096176147</t>
@@ -5507,16 +5507,16 @@
     <t xml:space="preserve">2.62690448760986</t>
   </si>
   <si>
-    <t xml:space="preserve">2.6303551197052</t>
+    <t xml:space="preserve">2.63035535812378</t>
   </si>
   <si>
     <t xml:space="preserve">2.60965061187744</t>
   </si>
   <si>
-    <t xml:space="preserve">2.61051344871521</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.6890184879303</t>
+    <t xml:space="preserve">2.61051321029663</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.68901872634888</t>
   </si>
   <si>
     <t xml:space="preserve">2.77356243133545</t>
@@ -5531,7 +5531,7 @@
     <t xml:space="preserve">2.7200756072998</t>
   </si>
   <si>
-    <t xml:space="preserve">2.73215317726135</t>
+    <t xml:space="preserve">2.73215341567993</t>
   </si>
   <si>
     <t xml:space="preserve">2.67952871322632</t>
@@ -5546,28 +5546,28 @@
     <t xml:space="preserve">2.72611451148987</t>
   </si>
   <si>
-    <t xml:space="preserve">2.75285792350769</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.85034203529358</t>
+    <t xml:space="preserve">2.75285768508911</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.85034227371216</t>
   </si>
   <si>
     <t xml:space="preserve">2.86759614944458</t>
   </si>
   <si>
-    <t xml:space="preserve">2.84861707687378</t>
+    <t xml:space="preserve">2.8486168384552</t>
   </si>
   <si>
     <t xml:space="preserve">2.83826446533203</t>
   </si>
   <si>
-    <t xml:space="preserve">2.88916349411011</t>
+    <t xml:space="preserve">2.88916325569153</t>
   </si>
   <si>
     <t xml:space="preserve">2.81755995750427</t>
   </si>
   <si>
-    <t xml:space="preserve">2.79858064651489</t>
+    <t xml:space="preserve">2.79858040809631</t>
   </si>
   <si>
     <t xml:space="preserve">2.78564023971558</t>
@@ -5582,40 +5582,40 @@
     <t xml:space="preserve">2.8710470199585</t>
   </si>
   <si>
-    <t xml:space="preserve">2.92712211608887</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.9987256526947</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.021155834198</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.0522129535675</t>
+    <t xml:space="preserve">2.92712187767029</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.99872589111328</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.02115607261658</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.05221271514893</t>
   </si>
   <si>
     <t xml:space="preserve">3.04531121253967</t>
   </si>
   <si>
-    <t xml:space="preserve">3.03150796890259</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.06515312194824</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.07981896400452</t>
+    <t xml:space="preserve">3.03150820732117</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.06515336036682</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.07981872558594</t>
   </si>
   <si>
     <t xml:space="preserve">3.0401349067688</t>
   </si>
   <si>
-    <t xml:space="preserve">3.03323364257812</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.96249270439148</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.07895612716675</t>
+    <t xml:space="preserve">3.03323340415955</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.9624924659729</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.07895636558533</t>
   </si>
   <si>
     <t xml:space="preserve">3.11432671546936</t>
@@ -5627,16 +5627,16 @@
     <t xml:space="preserve">3.27910161018372</t>
   </si>
   <si>
-    <t xml:space="preserve">3.23510384559631</t>
+    <t xml:space="preserve">3.23510408401489</t>
   </si>
   <si>
     <t xml:space="preserve">3.19973373413086</t>
   </si>
   <si>
-    <t xml:space="preserve">3.19714546203613</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.23941731452942</t>
+    <t xml:space="preserve">3.19714570045471</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.239417552948</t>
   </si>
   <si>
     <t xml:space="preserve">3.28082680702209</t>
@@ -5645,13 +5645,13 @@
     <t xml:space="preserve">3.30239415168762</t>
   </si>
   <si>
-    <t xml:space="preserve">3.30929565429688</t>
+    <t xml:space="preserve">3.30929589271545</t>
   </si>
   <si>
     <t xml:space="preserve">3.26788640022278</t>
   </si>
   <si>
-    <t xml:space="preserve">3.27823853492737</t>
+    <t xml:space="preserve">3.27823877334595</t>
   </si>
   <si>
     <t xml:space="preserve">3.34811687469482</t>
@@ -5666,7 +5666,7 @@
     <t xml:space="preserve">3.41972064971924</t>
   </si>
   <si>
-    <t xml:space="preserve">3.4671688079834</t>
+    <t xml:space="preserve">3.46716904640198</t>
   </si>
   <si>
     <t xml:space="preserve">3.53618431091309</t>
@@ -5675,7 +5675,7 @@
     <t xml:space="preserve">3.63539433479309</t>
   </si>
   <si>
-    <t xml:space="preserve">3.6707649230957</t>
+    <t xml:space="preserve">3.67076444625854</t>
   </si>
   <si>
     <t xml:space="preserve">3.64574646949768</t>
@@ -5684,16 +5684,16 @@
     <t xml:space="preserve">3.65005993843079</t>
   </si>
   <si>
-    <t xml:space="preserve">3.72856521606445</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.83381366729736</t>
+    <t xml:space="preserve">3.72856497764587</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.83381414413452</t>
   </si>
   <si>
     <t xml:space="preserve">3.7440938949585</t>
   </si>
   <si>
-    <t xml:space="preserve">3.77860140800476</t>
+    <t xml:space="preserve">3.77860164642334</t>
   </si>
   <si>
     <t xml:space="preserve">3.76997447013855</t>
@@ -5708,22 +5708,22 @@
     <t xml:space="preserve">3.78981637954712</t>
   </si>
   <si>
-    <t xml:space="preserve">3.83467698097229</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.77083706855774</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.83812689781189</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.68888092041016</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.68715620040894</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.68197965621948</t>
+    <t xml:space="preserve">3.83467674255371</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.77083730697632</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.83812737464905</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.68888139724731</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.68715572357178</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.68197989463806</t>
   </si>
   <si>
     <t xml:space="preserve">3.63366866111755</t>
@@ -5738,10 +5738,10 @@
     <t xml:space="preserve">3.80534482002258</t>
   </si>
   <si>
-    <t xml:space="preserve">3.89420247077942</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.02791976928711</t>
+    <t xml:space="preserve">3.894202709198</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.02792024612427</t>
   </si>
   <si>
     <t xml:space="preserve">3.99772572517395</t>
@@ -5750,16 +5750,16 @@
     <t xml:space="preserve">4.07450580596924</t>
   </si>
   <si>
-    <t xml:space="preserve">4.12712955474854</t>
+    <t xml:space="preserve">4.12713003158569</t>
   </si>
   <si>
     <t xml:space="preserve">4.15646123886108</t>
   </si>
   <si>
-    <t xml:space="preserve">4.21943807601929</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.25394678115845</t>
+    <t xml:space="preserve">4.21943759918213</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.25394630432129</t>
   </si>
   <si>
     <t xml:space="preserve">4.12885522842407</t>
@@ -5768,7 +5768,7 @@
     <t xml:space="preserve">4.17544078826904</t>
   </si>
   <si>
-    <t xml:space="preserve">4.25653457641602</t>
+    <t xml:space="preserve">4.25653409957886</t>
   </si>
   <si>
     <t xml:space="preserve">4.23237895965576</t>
@@ -5792,7 +5792,7 @@
     <t xml:space="preserve">4.46013021469116</t>
   </si>
   <si>
-    <t xml:space="preserve">4.56710433959961</t>
+    <t xml:space="preserve">4.56710386276245</t>
   </si>
   <si>
     <t xml:space="preserve">4.46925115585327</t>
@@ -6900,6 +6900,9 @@
   </si>
   <si>
     <t xml:space="preserve">11.0200004577637</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.914999961853</t>
   </si>
 </sst>
 </file>
@@ -73070,7 +73073,7 @@
     </row>
     <row r="2533">
       <c r="A2533" s="1" t="n">
-        <v>46006.6916087963</v>
+        <v>46006.3333333333</v>
       </c>
       <c r="B2533" t="n">
         <v>10408563</v>
@@ -73091,6 +73094,32 @@
         <v>2295</v>
       </c>
       <c r="H2533" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2534">
+      <c r="A2534" s="1" t="n">
+        <v>46007.6912731481</v>
+      </c>
+      <c r="B2534" t="n">
+        <v>8451111</v>
+      </c>
+      <c r="C2534" t="n">
+        <v>11.0649995803833</v>
+      </c>
+      <c r="D2534" t="n">
+        <v>10.8599996566772</v>
+      </c>
+      <c r="E2534" t="n">
+        <v>11.0150003433228</v>
+      </c>
+      <c r="F2534" t="n">
+        <v>10.914999961853</v>
+      </c>
+      <c r="G2534" t="s">
+        <v>2296</v>
+      </c>
+      <c r="H2534" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/BPE.MI.xlsx
+++ b/data/BPE.MI.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2298" uniqueCount="2298">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2299" uniqueCount="2299">
   <si>
     <t xml:space="preserve">date</t>
   </si>
@@ -50,10 +50,10 @@
     <t xml:space="preserve">3.09375739097595</t>
   </si>
   <si>
-    <t xml:space="preserve">3.02301573753357</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.9546320438385</t>
+    <t xml:space="preserve">3.02301549911499</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.95463180541992</t>
   </si>
   <si>
     <t xml:space="preserve">2.95699048042297</t>
@@ -62,22 +62,22 @@
     <t xml:space="preserve">2.93340945243835</t>
   </si>
   <si>
-    <t xml:space="preserve">3.07489252090454</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.91690373420715</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.66223430633545</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.65044379234314</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.45708441734314</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.72825980186462</t>
+    <t xml:space="preserve">3.07489156723022</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.91690397262573</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.66223454475403</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.65044450759888</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.45708417892456</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.72826051712036</t>
   </si>
   <si>
     <t xml:space="preserve">2.69760513305664</t>
@@ -89,10 +89,10 @@
     <t xml:space="preserve">2.78013706207275</t>
   </si>
   <si>
-    <t xml:space="preserve">2.66695046424866</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.46651649475098</t>
+    <t xml:space="preserve">2.66695070266724</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.46651697158813</t>
   </si>
   <si>
     <t xml:space="preserve">2.59385085105896</t>
@@ -104,40 +104,40 @@
     <t xml:space="preserve">2.35804653167725</t>
   </si>
   <si>
-    <t xml:space="preserve">2.16279983520508</t>
+    <t xml:space="preserve">2.1627995967865</t>
   </si>
   <si>
     <t xml:space="preserve">2.17128896713257</t>
   </si>
   <si>
-    <t xml:space="preserve">2.1260142326355</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.87228906154633</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.83173060417175</t>
+    <t xml:space="preserve">2.12601447105408</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.87228918075562</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.83173048496246</t>
   </si>
   <si>
     <t xml:space="preserve">1.95812141895294</t>
   </si>
   <si>
-    <t xml:space="preserve">1.77042150497437</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.974156498909</t>
+    <t xml:space="preserve">1.77042126655579</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.97415626049042</t>
   </si>
   <si>
     <t xml:space="preserve">2.17411851882935</t>
   </si>
   <si>
-    <t xml:space="preserve">2.27975916862488</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.33446621894836</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.32031774520874</t>
+    <t xml:space="preserve">2.27975869178772</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.33446574211121</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.32031798362732</t>
   </si>
   <si>
     <t xml:space="preserve">2.18166470527649</t>
@@ -149,31 +149,31 @@
     <t xml:space="preserve">2.31182885169983</t>
   </si>
   <si>
-    <t xml:space="preserve">2.16468691825867</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.21844983100891</t>
+    <t xml:space="preserve">2.16468667984009</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.21845030784607</t>
   </si>
   <si>
     <t xml:space="preserve">2.2599515914917</t>
   </si>
   <si>
-    <t xml:space="preserve">2.22127985954285</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.25429177284241</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.36512064933777</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.3240909576416</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.33352279663086</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.21279072761536</t>
+    <t xml:space="preserve">2.22128009796143</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.25429201126099</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.36512017250061</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.32409048080444</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.33352255821228</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.21279096603394</t>
   </si>
   <si>
     <t xml:space="preserve">2.18072152137756</t>
@@ -188,10 +188,10 @@
     <t xml:space="preserve">2.4099235534668</t>
   </si>
   <si>
-    <t xml:space="preserve">2.44293618202209</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.3627622127533</t>
+    <t xml:space="preserve">2.44293642044067</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.36276245117188</t>
   </si>
   <si>
     <t xml:space="preserve">2.20241498947144</t>
@@ -200,82 +200,82 @@
     <t xml:space="preserve">2.2269389629364</t>
   </si>
   <si>
-    <t xml:space="preserve">2.24674606323242</t>
+    <t xml:space="preserve">2.246746301651</t>
   </si>
   <si>
     <t xml:space="preserve">2.24108743667603</t>
   </si>
   <si>
-    <t xml:space="preserve">2.20807456970215</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.14770889282227</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.05904603004456</t>
+    <t xml:space="preserve">2.20807433128357</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.14770865440369</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.05904650688171</t>
   </si>
   <si>
     <t xml:space="preserve">2.03829503059387</t>
   </si>
   <si>
-    <t xml:space="preserve">1.97321331501007</t>
+    <t xml:space="preserve">1.97321307659149</t>
   </si>
   <si>
     <t xml:space="preserve">2.00905585289001</t>
   </si>
   <si>
-    <t xml:space="preserve">1.89492607116699</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.8845499753952</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.77325046062469</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.02697658538818</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.12507176399231</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.0401816368103</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.27410006523132</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.37691116333008</t>
+    <t xml:space="preserve">1.8949259519577</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.88455057144165</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.77325093746185</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.0269763469696</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.12507200241089</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.04018187522888</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.2741003036499</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.37691068649292</t>
   </si>
   <si>
     <t xml:space="preserve">2.38398480415344</t>
   </si>
   <si>
-    <t xml:space="preserve">2.30428290367126</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.37219500541687</t>
+    <t xml:space="preserve">2.30428314208984</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.37219476699829</t>
   </si>
   <si>
     <t xml:space="preserve">2.44765210151672</t>
   </si>
   <si>
-    <t xml:space="preserve">2.45944237709045</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.37455296516418</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.45236825942993</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.41463994979858</t>
+    <t xml:space="preserve">2.45944213867188</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.37455272674561</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.45236849784851</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.41463971138</t>
   </si>
   <si>
     <t xml:space="preserve">2.50896143913269</t>
   </si>
   <si>
-    <t xml:space="preserve">2.4075653553009</t>
+    <t xml:space="preserve">2.40756511688232</t>
   </si>
   <si>
     <t xml:space="preserve">2.31937408447266</t>
@@ -287,52 +287,52 @@
     <t xml:space="preserve">2.19298338890076</t>
   </si>
   <si>
-    <t xml:space="preserve">2.13167405128479</t>
+    <t xml:space="preserve">2.13167381286621</t>
   </si>
   <si>
     <t xml:space="preserve">2.07602405548096</t>
   </si>
   <si>
-    <t xml:space="preserve">2.0703649520874</t>
+    <t xml:space="preserve">2.07036471366882</t>
   </si>
   <si>
     <t xml:space="preserve">2.06470561027527</t>
   </si>
   <si>
-    <t xml:space="preserve">2.03263592720032</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.02980613708496</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.06093287467957</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.17506194114685</t>
+    <t xml:space="preserve">2.0326361656189</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.02980589866638</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.06093311309814</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.17506146430969</t>
   </si>
   <si>
     <t xml:space="preserve">2.07319450378418</t>
   </si>
   <si>
-    <t xml:space="preserve">2.09960436820984</t>
+    <t xml:space="preserve">2.09960412979126</t>
   </si>
   <si>
     <t xml:space="preserve">2.05811381340027</t>
   </si>
   <si>
-    <t xml:space="preserve">2.22021532058716</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.33117771148682</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.28582787513733</t>
+    <t xml:space="preserve">2.22021508216858</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.33117818832397</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.28582811355591</t>
   </si>
   <si>
     <t xml:space="preserve">2.29161763191223</t>
   </si>
   <si>
-    <t xml:space="preserve">2.3138108253479</t>
+    <t xml:space="preserve">2.31381058692932</t>
   </si>
   <si>
     <t xml:space="preserve">2.19416379928589</t>
@@ -341,25 +341,25 @@
     <t xml:space="preserve">2.16618227958679</t>
   </si>
   <si>
-    <t xml:space="preserve">2.07934188842773</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.06969285011292</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.09670901298523</t>
+    <t xml:space="preserve">2.07934165000916</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.06969261169434</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.09670948982239</t>
   </si>
   <si>
     <t xml:space="preserve">2.13627028465271</t>
   </si>
   <si>
-    <t xml:space="preserve">1.99636113643646</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.87478423118591</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.82171511650085</t>
+    <t xml:space="preserve">1.99636125564575</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.87478387355804</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.82171499729156</t>
   </si>
   <si>
     <t xml:space="preserve">1.81592631340027</t>
@@ -368,160 +368,160 @@
     <t xml:space="preserve">1.76864612102509</t>
   </si>
   <si>
-    <t xml:space="preserve">1.94425702095032</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.03206157684326</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.0841658115387</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.07548213005066</t>
+    <t xml:space="preserve">1.94425749778748</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.03206181526184</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.08416557312012</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.07548236846924</t>
   </si>
   <si>
     <t xml:space="preserve">2.23468923568726</t>
   </si>
   <si>
-    <t xml:space="preserve">1.68470084667206</t>
+    <t xml:space="preserve">1.68470108509064</t>
   </si>
   <si>
     <t xml:space="preserve">1.66733288764954</t>
   </si>
   <si>
-    <t xml:space="preserve">1.62777185440063</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.53900194168091</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.58145761489868</t>
+    <t xml:space="preserve">1.62777173519135</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.53900218009949</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.58145749568939</t>
   </si>
   <si>
     <t xml:space="preserve">1.50523054599762</t>
   </si>
   <si>
-    <t xml:space="preserve">1.40391731262207</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.40488231182098</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.3045334815979</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.24567472934723</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.44733715057373</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.51487970352173</t>
+    <t xml:space="preserve">1.40391719341278</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.40488219261169</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.30453324317932</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.24567461013794</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.44733703136444</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.51487994194031</t>
   </si>
   <si>
     <t xml:space="preserve">1.63838601112366</t>
   </si>
   <si>
-    <t xml:space="preserve">1.55637037754059</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.62294805049896</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.64224541187286</t>
+    <t xml:space="preserve">1.5563702583313</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.62294816970825</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.64224565029144</t>
   </si>
   <si>
     <t xml:space="preserve">1.65189468860626</t>
   </si>
   <si>
-    <t xml:space="preserve">1.63645601272583</t>
+    <t xml:space="preserve">1.63645589351654</t>
   </si>
   <si>
     <t xml:space="preserve">1.65382421016693</t>
   </si>
   <si>
-    <t xml:space="preserve">1.7068932056427</t>
+    <t xml:space="preserve">1.70689296722412</t>
   </si>
   <si>
     <t xml:space="preserve">1.6943496465683</t>
   </si>
   <si>
-    <t xml:space="preserve">1.64899945259094</t>
+    <t xml:space="preserve">1.64899981021881</t>
   </si>
   <si>
     <t xml:space="preserve">1.65671849250793</t>
   </si>
   <si>
-    <t xml:space="preserve">1.73294508457184</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.67891132831573</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.77057635784149</t>
+    <t xml:space="preserve">1.732945561409</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.67891144752502</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.77057659626007</t>
   </si>
   <si>
     <t xml:space="preserve">1.67022728919983</t>
   </si>
   <si>
-    <t xml:space="preserve">1.46374022960663</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.5225989818573</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.530317902565</t>
+    <t xml:space="preserve">1.46374046802521</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.52259886264801</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.53031778335571</t>
   </si>
   <si>
     <t xml:space="preserve">1.73005104064941</t>
   </si>
   <si>
-    <t xml:space="preserve">1.69820916652679</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.73198056221008</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.72136688232422</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.72040188312531</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.69627976417542</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.68373584747314</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.62101793289185</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.64996457099915</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.55444025993347</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.56505441665649</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.65478932857513</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.69048988819122</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.64128041267395</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.60750937461853</t>
+    <t xml:space="preserve">1.69820892810822</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.73198008537292</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.72136700153351</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.72040212154388</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.69627964496613</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.68373572826385</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.62101781368256</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.64996469020844</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.55444037914276</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.56505417823792</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.65478897094727</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.69049000740051</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.64128029346466</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.60750925540924</t>
   </si>
   <si>
     <t xml:space="preserve">1.65285909175873</t>
   </si>
   <si>
-    <t xml:space="preserve">1.66443836688995</t>
+    <t xml:space="preserve">1.66443812847137</t>
   </si>
   <si>
     <t xml:space="preserve">1.69531464576721</t>
@@ -530,43 +530,43 @@
     <t xml:space="preserve">1.7184716463089</t>
   </si>
   <si>
-    <t xml:space="preserve">1.68759548664093</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.7445240020752</t>
+    <t xml:space="preserve">1.68759560585022</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.74452388286591</t>
   </si>
   <si>
     <t xml:space="preserve">1.74741852283478</t>
   </si>
   <si>
-    <t xml:space="preserve">1.71268260478973</t>
+    <t xml:space="preserve">1.71268272399902</t>
   </si>
   <si>
     <t xml:space="preserve">1.67987644672394</t>
   </si>
   <si>
-    <t xml:space="preserve">1.63549149036407</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.58049261569977</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.60461461544037</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.53610754013062</t>
+    <t xml:space="preserve">1.63549172878265</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.58049249649048</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.60461485385895</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.5361076593399</t>
   </si>
   <si>
     <t xml:space="preserve">1.60847413539886</t>
   </si>
   <si>
-    <t xml:space="preserve">1.61233389377594</t>
+    <t xml:space="preserve">1.61233353614807</t>
   </si>
   <si>
     <t xml:space="preserve">1.5399671792984</t>
   </si>
   <si>
-    <t xml:space="preserve">1.51584470272064</t>
+    <t xml:space="preserve">1.51584506034851</t>
   </si>
   <si>
     <t xml:space="preserve">1.54961621761322</t>
@@ -581,31 +581,31 @@
     <t xml:space="preserve">1.56119501590729</t>
   </si>
   <si>
-    <t xml:space="preserve">1.63452637195587</t>
+    <t xml:space="preserve">1.63452661037445</t>
   </si>
   <si>
     <t xml:space="preserve">1.63935089111328</t>
   </si>
   <si>
-    <t xml:space="preserve">1.61619317531586</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.67408716678619</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.77540099620819</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.81496119499207</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.73583960533142</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.82653963565826</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.86513578891754</t>
+    <t xml:space="preserve">1.61619329452515</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.67408692836761</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.77540111541748</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.81496095657349</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.73583972454071</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.82653939723969</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.86513555049896</t>
   </si>
   <si>
     <t xml:space="preserve">1.96066009998322</t>
@@ -614,46 +614,46 @@
     <t xml:space="preserve">2.05425429344177</t>
   </si>
   <si>
-    <t xml:space="preserve">2.04942941665649</t>
+    <t xml:space="preserve">2.04942989349365</t>
   </si>
   <si>
     <t xml:space="preserve">2.10153388977051</t>
   </si>
   <si>
-    <t xml:space="preserve">2.01372957229614</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.04653549194336</t>
+    <t xml:space="preserve">2.01372933387756</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.04653525352478</t>
   </si>
   <si>
     <t xml:space="preserve">2.09477996826172</t>
   </si>
   <si>
-    <t xml:space="preserve">2.0889904499054</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.06197381019592</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.04460525512695</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.9297833442688</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.90566110610962</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.88443338871002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.95004594326019</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.9867115020752</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.01565837860107</t>
+    <t xml:space="preserve">2.08899021148682</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.06197357177734</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.04460549354553</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.92978298664093</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.90566122531891</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.88443326950073</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.95004558563232</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.98671185970306</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.01565909385681</t>
   </si>
   <si>
     <t xml:space="preserve">2.01662397384644</t>
@@ -662,61 +662,61 @@
     <t xml:space="preserve">1.99539601802826</t>
   </si>
   <si>
-    <t xml:space="preserve">1.98574662208557</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.92785322666168</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.84583747386932</t>
+    <t xml:space="preserve">1.98574650287628</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.92785346508026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.84583711624146</t>
   </si>
   <si>
     <t xml:space="preserve">1.80820739269257</t>
   </si>
   <si>
-    <t xml:space="preserve">1.80048751831055</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.83715403079987</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.82750511169434</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.83329355716705</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.80531191825867</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.82846999168396</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.97513341903687</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.9355731010437</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.06679844856262</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.28196859359741</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.31477499008179</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.27907419204712</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.32152962684631</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.3707389831543</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.3321430683136</t>
+    <t xml:space="preserve">1.80048739910126</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.83715415000916</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.82750451564789</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.83329379558563</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.80531179904938</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.82847011089325</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.975133061409</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.93557322025299</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.06679797172546</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.28196883201599</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.31477522850037</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.2790744304657</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.32152986526489</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.37073922157288</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.33214282989502</t>
   </si>
   <si>
     <t xml:space="preserve">2.39486122131348</t>
@@ -725,7 +725,7 @@
     <t xml:space="preserve">2.41464161872864</t>
   </si>
   <si>
-    <t xml:space="preserve">2.39775562286377</t>
+    <t xml:space="preserve">2.39775538444519</t>
   </si>
   <si>
     <t xml:space="preserve">2.41222953796387</t>
@@ -737,61 +737,61 @@
     <t xml:space="preserve">2.48942041397095</t>
   </si>
   <si>
-    <t xml:space="preserve">2.49665713310242</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.44117617607117</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.54248976707458</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.6389787197113</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.59555888175964</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.55696272850037</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.42911505699158</t>
+    <t xml:space="preserve">2.496657371521</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.44117641448975</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.54248952865601</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.63897848129272</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.59555864334106</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.55696249008179</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.429114818573</t>
   </si>
   <si>
     <t xml:space="preserve">2.41705346107483</t>
   </si>
   <si>
-    <t xml:space="preserve">2.56178689002991</t>
+    <t xml:space="preserve">2.56178736686707</t>
   </si>
   <si>
     <t xml:space="preserve">2.53766489028931</t>
   </si>
   <si>
-    <t xml:space="preserve">2.57867288589478</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.58832240104675</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.72823119163513</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.77165126800537</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.70652174949646</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.71375799179077</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.74752902984619</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.70410943031311</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.57626104354858</t>
+    <t xml:space="preserve">2.57867312431335</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.58832216262817</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.72823143005371</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.77165102958679</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.7065212726593</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.71375775337219</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.74752926826477</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.70410919189453</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.57626128196716</t>
   </si>
   <si>
     <t xml:space="preserve">2.52801585197449</t>
@@ -800,13 +800,13 @@
     <t xml:space="preserve">2.58590936660767</t>
   </si>
   <si>
-    <t xml:space="preserve">2.59797072410583</t>
+    <t xml:space="preserve">2.59797048568726</t>
   </si>
   <si>
     <t xml:space="preserve">2.66068863868713</t>
   </si>
   <si>
-    <t xml:space="preserve">2.50871825218201</t>
+    <t xml:space="preserve">2.50871849060059</t>
   </si>
   <si>
     <t xml:space="preserve">2.42187809944153</t>
@@ -815,43 +815,43 @@
     <t xml:space="preserve">2.45082497596741</t>
   </si>
   <si>
-    <t xml:space="preserve">2.2945122718811</t>
+    <t xml:space="preserve">2.29451251029968</t>
   </si>
   <si>
     <t xml:space="preserve">2.30223107337952</t>
   </si>
   <si>
-    <t xml:space="preserve">2.38135266304016</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.32056450843811</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.24047803878784</t>
+    <t xml:space="preserve">2.38135242462158</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.32056427001953</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.24047827720642</t>
   </si>
   <si>
     <t xml:space="preserve">2.17100620269775</t>
   </si>
   <si>
-    <t xml:space="preserve">2.1478488445282</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.14495420455933</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.06293869018555</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.0262725353241</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.99732625484467</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.16135764122009</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.17004179954529</t>
+    <t xml:space="preserve">2.14784860610962</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.14495396614075</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.06293845176697</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.02627301216125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.99732613563538</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.16135787963867</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.17004156112671</t>
   </si>
   <si>
     <t xml:space="preserve">2.26749563217163</t>
@@ -860,52 +860,52 @@
     <t xml:space="preserve">2.20574259757996</t>
   </si>
   <si>
-    <t xml:space="preserve">2.11311268806458</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.11793684959412</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.18837428092957</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.25977635383606</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.22214579582214</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.16521716117859</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.16907691955566</t>
+    <t xml:space="preserve">2.113112449646</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.1179370880127</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.18837451934814</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.25977659225464</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.22214555740356</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.16521692276001</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.16907644271851</t>
   </si>
   <si>
     <t xml:space="preserve">2.27714467048645</t>
   </si>
   <si>
-    <t xml:space="preserve">2.25012707710266</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.3176703453064</t>
+    <t xml:space="preserve">2.25012731552124</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.31767010688782</t>
   </si>
   <si>
     <t xml:space="preserve">2.32635402679443</t>
   </si>
   <si>
-    <t xml:space="preserve">2.39196681976318</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.36494946479797</t>
+    <t xml:space="preserve">2.3919665813446</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.36494970321655</t>
   </si>
   <si>
     <t xml:space="preserve">2.32249402999878</t>
   </si>
   <si>
-    <t xml:space="preserve">2.3369677066803</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.29354786872864</t>
+    <t xml:space="preserve">2.33696794509888</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.29354810714722</t>
   </si>
   <si>
     <t xml:space="preserve">2.26267099380493</t>
@@ -914,7 +914,7 @@
     <t xml:space="preserve">2.25784635543823</t>
   </si>
   <si>
-    <t xml:space="preserve">2.17872500419617</t>
+    <t xml:space="preserve">2.17872524261475</t>
   </si>
   <si>
     <t xml:space="preserve">2.19512820243835</t>
@@ -932,22 +932,22 @@
     <t xml:space="preserve">2.12179636955261</t>
   </si>
   <si>
-    <t xml:space="preserve">2.10442900657654</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.21153163909912</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.36398434638977</t>
+    <t xml:space="preserve">2.10442924499512</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.21153140068054</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.36398458480835</t>
   </si>
   <si>
     <t xml:space="preserve">2.39872050285339</t>
   </si>
   <si>
-    <t xml:space="preserve">2.34661674499512</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.41946625709534</t>
+    <t xml:space="preserve">2.3466169834137</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.4194655418396</t>
   </si>
   <si>
     <t xml:space="preserve">2.48218417167664</t>
@@ -980,10 +980,10 @@
     <t xml:space="preserve">2.22696995735168</t>
   </si>
   <si>
-    <t xml:space="preserve">2.26074123382568</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.24998950958252</t>
+    <t xml:space="preserve">2.26074147224426</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.2499897480011</t>
   </si>
   <si>
     <t xml:space="preserve">2.25096726417542</t>
@@ -992,16 +992,16 @@
     <t xml:space="preserve">2.2822437286377</t>
   </si>
   <si>
-    <t xml:space="preserve">2.2793116569519</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.25292158126831</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.18450379371643</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.18548107147217</t>
+    <t xml:space="preserve">2.27931189537048</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.25292181968689</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.18450355529785</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.18548130989075</t>
   </si>
   <si>
     <t xml:space="preserve">2.13074636459351</t>
@@ -1010,19 +1010,19 @@
     <t xml:space="preserve">2.17570662498474</t>
   </si>
   <si>
-    <t xml:space="preserve">2.14833950996399</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.10924291610718</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.076988697052</t>
+    <t xml:space="preserve">2.14833974838257</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.10924339294434</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.07698893547058</t>
   </si>
   <si>
     <t xml:space="preserve">2.08089876174927</t>
   </si>
   <si>
-    <t xml:space="preserve">2.15811347961426</t>
+    <t xml:space="preserve">2.15811371803284</t>
   </si>
   <si>
     <t xml:space="preserve">2.15127182006836</t>
@@ -1031,22 +1031,22 @@
     <t xml:space="preserve">2.10631108283997</t>
   </si>
   <si>
-    <t xml:space="preserve">2.15909123420715</t>
+    <t xml:space="preserve">2.15909075737</t>
   </si>
   <si>
     <t xml:space="preserve">2.1375880241394</t>
   </si>
   <si>
-    <t xml:space="preserve">2.04082441329956</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.0535306930542</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.00075078010559</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.09067225456238</t>
+    <t xml:space="preserve">2.04082465171814</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.05353093147278</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.00075101852417</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.09067177772522</t>
   </si>
   <si>
     <t xml:space="preserve">2.081876039505</t>
@@ -1058,34 +1058,34 @@
     <t xml:space="preserve">2.14931631088257</t>
   </si>
   <si>
-    <t xml:space="preserve">2.16886496543884</t>
+    <t xml:space="preserve">2.168865442276</t>
   </si>
   <si>
     <t xml:space="preserve">2.15713572502136</t>
   </si>
   <si>
-    <t xml:space="preserve">2.13367819786072</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.27149248123169</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.34870767593384</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.29201817512512</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.29788327217102</t>
+    <t xml:space="preserve">2.1336784362793</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.27149271965027</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.34870719909668</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.29201793670654</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.29788303375244</t>
   </si>
   <si>
     <t xml:space="preserve">2.29104042053223</t>
   </si>
   <si>
-    <t xml:space="preserve">2.3223180770874</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.36434626579285</t>
+    <t xml:space="preserve">2.32231831550598</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.36434650421143</t>
   </si>
   <si>
     <t xml:space="preserve">2.41419434547424</t>
@@ -1094,25 +1094,25 @@
     <t xml:space="preserve">2.42103600502014</t>
   </si>
   <si>
-    <t xml:space="preserve">2.41908121109009</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.4337420463562</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.354572057724</t>
+    <t xml:space="preserve">2.41908144950867</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.43374180793762</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.35457253456116</t>
   </si>
   <si>
     <t xml:space="preserve">2.37021064758301</t>
   </si>
   <si>
-    <t xml:space="preserve">2.30667972564697</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.2812671661377</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.25389957427979</t>
+    <t xml:space="preserve">2.30667924880981</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.28126692771912</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.25389909744263</t>
   </si>
   <si>
     <t xml:space="preserve">2.28713083267212</t>
@@ -1136,10 +1136,10 @@
     <t xml:space="preserve">2.42005825042725</t>
   </si>
   <si>
-    <t xml:space="preserve">2.40246534347534</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.31743097305298</t>
+    <t xml:space="preserve">2.40246558189392</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.3174307346344</t>
   </si>
   <si>
     <t xml:space="preserve">2.39464569091797</t>
@@ -1148,7 +1148,7 @@
     <t xml:space="preserve">2.38389420509338</t>
   </si>
   <si>
-    <t xml:space="preserve">2.35750436782837</t>
+    <t xml:space="preserve">2.35750460624695</t>
   </si>
   <si>
     <t xml:space="preserve">2.32622790336609</t>
@@ -1163,43 +1163,43 @@
     <t xml:space="preserve">2.32915949821472</t>
   </si>
   <si>
-    <t xml:space="preserve">2.26856064796448</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.29299569129944</t>
+    <t xml:space="preserve">2.2685604095459</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.29299545288086</t>
   </si>
   <si>
     <t xml:space="preserve">2.31254363059998</t>
   </si>
   <si>
-    <t xml:space="preserve">2.34382104873657</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.30863404273987</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.27246999740601</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.23337340354919</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.21382594108582</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.27735733985901</t>
+    <t xml:space="preserve">2.34382128715515</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.30863428115845</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.27247023582458</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.23337364196777</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.21382570266724</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.27735757827759</t>
   </si>
   <si>
     <t xml:space="preserve">2.34773087501526</t>
   </si>
   <si>
-    <t xml:space="preserve">2.30081486701965</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.2421703338623</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.26269578933716</t>
+    <t xml:space="preserve">2.30081510543823</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.24217057228088</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.26269602775574</t>
   </si>
   <si>
     <t xml:space="preserve">2.29006385803223</t>
@@ -1208,10 +1208,10 @@
     <t xml:space="preserve">2.33795642852783</t>
   </si>
   <si>
-    <t xml:space="preserve">2.28615355491638</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.35359454154968</t>
+    <t xml:space="preserve">2.2861533164978</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.35359477996826</t>
   </si>
   <si>
     <t xml:space="preserve">2.42299103736877</t>
@@ -1223,31 +1223,31 @@
     <t xml:space="preserve">2.47283864021301</t>
   </si>
   <si>
-    <t xml:space="preserve">2.51437830924988</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.50704717636108</t>
+    <t xml:space="preserve">2.51437854766846</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.50704741477966</t>
   </si>
   <si>
     <t xml:space="preserve">2.43276453018188</t>
   </si>
   <si>
-    <t xml:space="preserve">2.39171361923218</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.26171851158142</t>
+    <t xml:space="preserve">2.3917133808136</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.26171827316284</t>
   </si>
   <si>
     <t xml:space="preserve">2.19525456428528</t>
   </si>
   <si>
-    <t xml:space="preserve">2.14736223220825</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.17081999778748</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.14638471603394</t>
+    <t xml:space="preserve">2.14736247062683</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.1708197593689</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.14638447761536</t>
   </si>
   <si>
     <t xml:space="preserve">2.1405200958252</t>
@@ -1256,76 +1256,76 @@
     <t xml:space="preserve">2.07210183143616</t>
   </si>
   <si>
-    <t xml:space="preserve">2.07894325256348</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.09946870803833</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.07601118087769</t>
+    <t xml:space="preserve">2.0789430141449</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.09946894645691</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.07601165771484</t>
   </si>
   <si>
     <t xml:space="preserve">2.04375720024109</t>
   </si>
   <si>
-    <t xml:space="preserve">2.05450820922852</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.04473423957825</t>
+    <t xml:space="preserve">2.05450844764709</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.04473400115967</t>
   </si>
   <si>
     <t xml:space="preserve">2.03887009620667</t>
   </si>
   <si>
-    <t xml:space="preserve">2.11315321922302</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.05939507484436</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.02616357803345</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.98804461956024</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.90105557441711</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.0896954536438</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.06721496582031</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.08578562736511</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.0398473739624</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.082852602005</t>
+    <t xml:space="preserve">2.11315298080444</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.05939555168152</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.02616405487061</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.98804473876953</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.90105545520782</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.08969521522522</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.06721472740173</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.08578586578369</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.03984761238098</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.08285284042358</t>
   </si>
   <si>
     <t xml:space="preserve">2.01345729827881</t>
   </si>
   <si>
-    <t xml:space="preserve">2.0466890335083</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.01834487915039</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.00661611557007</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.06623697280884</t>
+    <t xml:space="preserve">2.04668927192688</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.01834464073181</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.00661563873291</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.06623721122742</t>
   </si>
   <si>
     <t xml:space="preserve">2.16202306747437</t>
   </si>
   <si>
-    <t xml:space="preserve">2.24607968330383</t>
+    <t xml:space="preserve">2.24608016014099</t>
   </si>
   <si>
     <t xml:space="preserve">2.17961645126343</t>
@@ -1334,55 +1334,55 @@
     <t xml:space="preserve">2.2382607460022</t>
   </si>
   <si>
-    <t xml:space="preserve">2.22653198242188</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.19916415214539</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.27051472663879</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.21773505210876</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.07796549797058</t>
+    <t xml:space="preserve">2.22653222084045</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.19916391372681</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.27051496505737</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.21773529052734</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.07796573638916</t>
   </si>
   <si>
     <t xml:space="preserve">2.03691482543945</t>
   </si>
   <si>
-    <t xml:space="preserve">2.03105092048645</t>
+    <t xml:space="preserve">2.03105068206787</t>
   </si>
   <si>
     <t xml:space="preserve">2.09849190711975</t>
   </si>
   <si>
-    <t xml:space="preserve">2.08676290512085</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.0887176990509</t>
+    <t xml:space="preserve">2.08676242828369</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.08871793746948</t>
   </si>
   <si>
     <t xml:space="preserve">2.0476667881012</t>
   </si>
   <si>
-    <t xml:space="preserve">2.05841755867004</t>
+    <t xml:space="preserve">2.0584180355072</t>
   </si>
   <si>
     <t xml:space="preserve">2.11510801315308</t>
   </si>
   <si>
-    <t xml:space="preserve">2.05744051933289</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.03300476074219</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.07307910919189</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.07503390312195</t>
+    <t xml:space="preserve">2.05744004249573</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.03300547599792</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.07307934761047</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.07503366470337</t>
   </si>
   <si>
     <t xml:space="preserve">2.11119747161865</t>
@@ -1391,46 +1391,46 @@
     <t xml:space="preserve">2.2060067653656</t>
   </si>
   <si>
-    <t xml:space="preserve">2.22848629951477</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.20405173301697</t>
+    <t xml:space="preserve">2.22848653793335</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.20405149459839</t>
   </si>
   <si>
     <t xml:space="preserve">2.16104531288147</t>
   </si>
   <si>
-    <t xml:space="preserve">2.35261726379395</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.35066270828247</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.36776685714722</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.27686858177185</t>
+    <t xml:space="preserve">2.35261702537537</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.35066246986389</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.36776733398438</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.27686834335327</t>
   </si>
   <si>
     <t xml:space="preserve">2.29543900489807</t>
   </si>
   <si>
-    <t xml:space="preserve">2.27784562110901</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.21578049659729</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.22408843040466</t>
+    <t xml:space="preserve">2.27784514427185</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.21578001976013</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.22408771514893</t>
   </si>
   <si>
     <t xml:space="preserve">2.30179262161255</t>
   </si>
   <si>
-    <t xml:space="preserve">2.25194501876831</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.22213411331177</t>
+    <t xml:space="preserve">2.25194478034973</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.22213387489319</t>
   </si>
   <si>
     <t xml:space="preserve">2.33746767044067</t>
@@ -1439,13 +1439,13 @@
     <t xml:space="preserve">2.34186601638794</t>
   </si>
   <si>
-    <t xml:space="preserve">2.33209156990051</t>
+    <t xml:space="preserve">2.33209133148193</t>
   </si>
   <si>
     <t xml:space="preserve">2.33600091934204</t>
   </si>
   <si>
-    <t xml:space="preserve">2.28957509994507</t>
+    <t xml:space="preserve">2.28957486152649</t>
   </si>
   <si>
     <t xml:space="preserve">2.37656402587891</t>
@@ -1463,16 +1463,16 @@
     <t xml:space="preserve">2.40735197067261</t>
   </si>
   <si>
-    <t xml:space="preserve">2.38731551170349</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.20551800727844</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.29592752456665</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.32720494270325</t>
+    <t xml:space="preserve">2.38731527328491</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.20551776885986</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.29592776298523</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.32720518112183</t>
   </si>
   <si>
     <t xml:space="preserve">2.25438809394836</t>
@@ -1481,7 +1481,7 @@
     <t xml:space="preserve">2.29641652107239</t>
   </si>
   <si>
-    <t xml:space="preserve">2.24461364746094</t>
+    <t xml:space="preserve">2.24461388587952</t>
   </si>
   <si>
     <t xml:space="preserve">2.24901223182678</t>
@@ -1490,67 +1490,67 @@
     <t xml:space="preserve">2.27540230751038</t>
   </si>
   <si>
-    <t xml:space="preserve">2.28322148323059</t>
+    <t xml:space="preserve">2.28322172164917</t>
   </si>
   <si>
     <t xml:space="preserve">2.26758289337158</t>
   </si>
   <si>
-    <t xml:space="preserve">2.22359943389893</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.22995281219482</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.21040534973145</t>
+    <t xml:space="preserve">2.22359919548035</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.2299530506134</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.21040487289429</t>
   </si>
   <si>
     <t xml:space="preserve">2.22555446624756</t>
   </si>
   <si>
-    <t xml:space="preserve">2.2069833278656</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.20893883705139</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.29446148872375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.30276942253113</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.31156587600708</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.33502388000488</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.38487195968628</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.35652732849121</t>
+    <t xml:space="preserve">2.20698356628418</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.20893859863281</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.29446125030518</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.30276918411255</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.31156611442566</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.33502411842346</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.3848717212677</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.35652709007263</t>
   </si>
   <si>
     <t xml:space="preserve">2.36288022994995</t>
   </si>
   <si>
-    <t xml:space="preserve">2.38829278945923</t>
+    <t xml:space="preserve">2.38829255104065</t>
   </si>
   <si>
     <t xml:space="preserve">2.34479784965515</t>
   </si>
   <si>
-    <t xml:space="preserve">2.31547546386719</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.33013677597046</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.31889724731445</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.3306257724762</t>
+    <t xml:space="preserve">2.31547570228577</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.33013725280762</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.31889748573303</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.33062601089478</t>
   </si>
   <si>
     <t xml:space="preserve">2.31303262710571</t>
@@ -1562,37 +1562,37 @@
     <t xml:space="preserve">2.3966007232666</t>
   </si>
   <si>
-    <t xml:space="preserve">2.40539717674255</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.45231294631958</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.48749971389771</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.51584434509277</t>
+    <t xml:space="preserve">2.40539741516113</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.45231318473816</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.48749947547913</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.51584386825562</t>
   </si>
   <si>
     <t xml:space="preserve">2.442049741745</t>
   </si>
   <si>
-    <t xml:space="preserve">2.44253897666931</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.28028964996338</t>
+    <t xml:space="preserve">2.44253873825073</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.2802894115448</t>
   </si>
   <si>
     <t xml:space="preserve">2.30131077766418</t>
   </si>
   <si>
-    <t xml:space="preserve">2.33834743499756</t>
+    <t xml:space="preserve">2.33834767341614</t>
   </si>
   <si>
     <t xml:space="preserve">2.36387300491333</t>
   </si>
   <si>
-    <t xml:space="preserve">2.33484387397766</t>
+    <t xml:space="preserve">2.33484411239624</t>
   </si>
   <si>
     <t xml:space="preserve">2.28779673576355</t>
@@ -1604,70 +1604,70 @@
     <t xml:space="preserve">2.04555368423462</t>
   </si>
   <si>
-    <t xml:space="preserve">2.05306124687195</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.05356192588806</t>
+    <t xml:space="preserve">2.05306100845337</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.0535614490509</t>
   </si>
   <si>
     <t xml:space="preserve">2.21522378921509</t>
   </si>
   <si>
-    <t xml:space="preserve">2.15015816688538</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.07708525657654</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.07608437538147</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.11612415313721</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.0590672492981</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.14865756034851</t>
+    <t xml:space="preserve">2.15015864372253</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.07708501815796</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.07608413696289</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.11612462997437</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.05906748771667</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.14865732192993</t>
   </si>
   <si>
     <t xml:space="preserve">2.1741828918457</t>
   </si>
   <si>
-    <t xml:space="preserve">2.20921730995178</t>
+    <t xml:space="preserve">2.20921778678894</t>
   </si>
   <si>
     <t xml:space="preserve">2.23624515533447</t>
   </si>
   <si>
-    <t xml:space="preserve">2.17768621444702</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.16717529296875</t>
+    <t xml:space="preserve">2.1776864528656</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.16717553138733</t>
   </si>
   <si>
     <t xml:space="preserve">2.24074959754944</t>
   </si>
   <si>
-    <t xml:space="preserve">2.29730653762817</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.22973871231079</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.39390301704407</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.3448543548584</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.35786724090576</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.32433319091797</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.34535527229309</t>
+    <t xml:space="preserve">2.29730629920959</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.22973847389221</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.39390349388123</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.34485459327698</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.35786700248718</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.32433295249939</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.34535479545593</t>
   </si>
   <si>
     <t xml:space="preserve">2.35586500167847</t>
@@ -1676,34 +1676,34 @@
     <t xml:space="preserve">2.34685587882996</t>
   </si>
   <si>
-    <t xml:space="preserve">2.34935879707336</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.34034991264343</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.38639569282532</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.39440417289734</t>
+    <t xml:space="preserve">2.34935927391052</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.34034967422485</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.3863959312439</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.39440369606018</t>
   </si>
   <si>
     <t xml:space="preserve">2.3478569984436</t>
   </si>
   <si>
-    <t xml:space="preserve">2.30881810188293</t>
+    <t xml:space="preserve">2.30881762504578</t>
   </si>
   <si>
     <t xml:space="preserve">2.32483386993408</t>
   </si>
   <si>
-    <t xml:space="preserve">2.35686612129211</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.31532454490662</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.27228164672852</t>
+    <t xml:space="preserve">2.35686635971069</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.3153247833252</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.27228116989136</t>
   </si>
   <si>
     <t xml:space="preserve">2.31832766532898</t>
@@ -1712,16 +1712,16 @@
     <t xml:space="preserve">2.31582450866699</t>
   </si>
   <si>
-    <t xml:space="preserve">2.34985876083374</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.38289213180542</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.35936856269836</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.39290189743042</t>
+    <t xml:space="preserve">2.34985852241516</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.382892370224</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.35936808586121</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.392902135849</t>
   </si>
   <si>
     <t xml:space="preserve">2.38189125061035</t>
@@ -1730,19 +1730,19 @@
     <t xml:space="preserve">2.29680562019348</t>
   </si>
   <si>
-    <t xml:space="preserve">2.29079914093018</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.29230117797852</t>
+    <t xml:space="preserve">2.29079961776733</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.29230141639709</t>
   </si>
   <si>
     <t xml:space="preserve">2.31232118606567</t>
   </si>
   <si>
-    <t xml:space="preserve">2.17568373680115</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.15115928649902</t>
+    <t xml:space="preserve">2.17568421363831</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.1511595249176</t>
   </si>
   <si>
     <t xml:space="preserve">2.12112927436829</t>
@@ -1754,7 +1754,7 @@
     <t xml:space="preserve">2.04905700683594</t>
   </si>
   <si>
-    <t xml:space="preserve">2.04655504226685</t>
+    <t xml:space="preserve">2.04655480384827</t>
   </si>
   <si>
     <t xml:space="preserve">2.00200963020325</t>
@@ -1766,19 +1766,19 @@
     <t xml:space="preserve">2.04705452919006</t>
   </si>
   <si>
-    <t xml:space="preserve">2.04605412483215</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.03003787994385</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.02503323554993</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.01702523231506</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.98449218273163</t>
+    <t xml:space="preserve">2.04605436325073</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.03003764152527</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.02503299713135</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.01702547073364</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.98449242115021</t>
   </si>
   <si>
     <t xml:space="preserve">1.99700462818146</t>
@@ -1787,40 +1787,40 @@
     <t xml:space="preserve">1.92192959785461</t>
   </si>
   <si>
-    <t xml:space="preserve">1.90140926837921</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.91041851043701</t>
+    <t xml:space="preserve">1.90140914916992</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.9104186296463</t>
   </si>
   <si>
     <t xml:space="preserve">1.98048806190491</t>
   </si>
   <si>
-    <t xml:space="preserve">2.06507325172424</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.06907725334167</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.12413239479065</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.11362195014954</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.11562371253967</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.10861706733704</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.15716552734375</t>
+    <t xml:space="preserve">2.06507301330566</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.0690770149231</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.12413215637207</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.11362171173096</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.11562347412109</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.10861682891846</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.15716576576233</t>
   </si>
   <si>
     <t xml:space="preserve">2.18969821929932</t>
   </si>
   <si>
-    <t xml:space="preserve">2.1691780090332</t>
+    <t xml:space="preserve">2.16917729377747</t>
   </si>
   <si>
     <t xml:space="preserve">2.12763619422913</t>
@@ -1832,73 +1832,73 @@
     <t xml:space="preserve">2.17868757247925</t>
   </si>
   <si>
-    <t xml:space="preserve">2.20070910453796</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.99600350856781</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.91742479801178</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.88389146327972</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.85936617851257</t>
+    <t xml:space="preserve">2.20070886611938</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.9960036277771</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.91742515563965</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.88389134407043</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.8593658208847</t>
   </si>
   <si>
     <t xml:space="preserve">1.87087833881378</t>
   </si>
   <si>
-    <t xml:space="preserve">1.83684408664703</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.80631327629089</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.77027690410614</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.80881547927856</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.7747814655304</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.78829526901245</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.80080759525299</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.78529226779938</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.78779447078705</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.74925577640533</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.75576257705688</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.69169843196869</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.65516149997711</t>
+    <t xml:space="preserve">1.83684420585632</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.80631351470947</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.77027702331543</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.80881571769714</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.77478134632111</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.78829491138458</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.8008074760437</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.78529214859009</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.78779482841492</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.74925589561462</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.75576281547546</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.6916983127594</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.65516138076782</t>
   </si>
   <si>
     <t xml:space="preserve">1.60811412334442</t>
   </si>
   <si>
-    <t xml:space="preserve">1.64515161514282</t>
+    <t xml:space="preserve">1.64515149593353</t>
   </si>
   <si>
     <t xml:space="preserve">1.6326390504837</t>
   </si>
   <si>
-    <t xml:space="preserve">1.70471155643463</t>
+    <t xml:space="preserve">1.70471143722534</t>
   </si>
   <si>
     <t xml:space="preserve">1.69470131397247</t>
@@ -1907,31 +1907,31 @@
     <t xml:space="preserve">1.6806868314743</t>
   </si>
   <si>
-    <t xml:space="preserve">1.69069719314575</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.75926625728607</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.69870507717133</t>
+    <t xml:space="preserve">1.69069731235504</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.75926613807678</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.69870495796204</t>
   </si>
   <si>
     <t xml:space="preserve">1.68619251251221</t>
   </si>
   <si>
-    <t xml:space="preserve">1.71672344207764</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.72973668575287</t>
+    <t xml:space="preserve">1.71672332286835</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.72973656654358</t>
   </si>
   <si>
     <t xml:space="preserve">1.74525189399719</t>
   </si>
   <si>
-    <t xml:space="preserve">1.74775445461273</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.69670355319977</t>
+    <t xml:space="preserve">1.7477548122406</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.69670331478119</t>
   </si>
   <si>
     <t xml:space="preserve">1.71071708202362</t>
@@ -1940,31 +1940,31 @@
     <t xml:space="preserve">1.67968642711639</t>
   </si>
   <si>
-    <t xml:space="preserve">1.6952018737793</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.67568230628967</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.7362425327301</t>
+    <t xml:space="preserve">1.69520199298859</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.67568254470825</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.73624277114868</t>
   </si>
   <si>
     <t xml:space="preserve">1.74625313282013</t>
   </si>
   <si>
-    <t xml:space="preserve">1.74725425243378</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.84084832668304</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.77628326416016</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.79229927062988</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.80130839347839</t>
+    <t xml:space="preserve">1.7472540140152</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.84084820747375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.77628314495087</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.79229915142059</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.8013082742691</t>
   </si>
   <si>
     <t xml:space="preserve">1.88439202308655</t>
@@ -1973,7 +1973,7 @@
     <t xml:space="preserve">1.85235929489136</t>
   </si>
   <si>
-    <t xml:space="preserve">1.88689386844635</t>
+    <t xml:space="preserve">1.8868944644928</t>
   </si>
   <si>
     <t xml:space="preserve">1.82683408260345</t>
@@ -1982,16 +1982,16 @@
     <t xml:space="preserve">1.79780471324921</t>
   </si>
   <si>
-    <t xml:space="preserve">1.76727426052094</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.75025689601898</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.74325048923492</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.71622264385223</t>
+    <t xml:space="preserve">1.76727437973022</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.75025713443756</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.74325025081635</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.71622276306152</t>
   </si>
   <si>
     <t xml:space="preserve">1.68268942832947</t>
@@ -2000,10 +2000,10 @@
     <t xml:space="preserve">1.67468130588531</t>
   </si>
   <si>
-    <t xml:space="preserve">1.70871555805206</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.67618227005005</t>
+    <t xml:space="preserve">1.70871543884277</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.67618238925934</t>
   </si>
   <si>
     <t xml:space="preserve">1.66366982460022</t>
@@ -2012,22 +2012,22 @@
     <t xml:space="preserve">1.6411474943161</t>
   </si>
   <si>
-    <t xml:space="preserve">1.68369042873383</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.64965629577637</t>
+    <t xml:space="preserve">1.6836906671524</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.64965617656708</t>
   </si>
   <si>
     <t xml:space="preserve">1.63864469528198</t>
   </si>
   <si>
-    <t xml:space="preserve">1.69369995594025</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.70421099662781</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.66667318344116</t>
+    <t xml:space="preserve">1.69370007514954</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.70421087741852</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.66667330265045</t>
   </si>
   <si>
     <t xml:space="preserve">1.65966582298279</t>
@@ -2048,25 +2048,25 @@
     <t xml:space="preserve">1.53203785419464</t>
   </si>
   <si>
-    <t xml:space="preserve">1.53804409503937</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.52903509140015</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.53704297542572</t>
+    <t xml:space="preserve">1.53804397583008</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.52903485298157</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.53704273700714</t>
   </si>
   <si>
     <t xml:space="preserve">1.52853441238403</t>
   </si>
   <si>
-    <t xml:space="preserve">1.50601172447205</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.51051616668701</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.57658278942108</t>
+    <t xml:space="preserve">1.50601160526276</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.51051604747772</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.57658290863037</t>
   </si>
   <si>
     <t xml:space="preserve">1.55756330490112</t>
@@ -2075,22 +2075,22 @@
     <t xml:space="preserve">1.56156730651855</t>
   </si>
   <si>
-    <t xml:space="preserve">1.57508099079132</t>
+    <t xml:space="preserve">1.57508087158203</t>
   </si>
   <si>
     <t xml:space="preserve">1.47948551177979</t>
   </si>
   <si>
-    <t xml:space="preserve">1.48398947715759</t>
+    <t xml:space="preserve">1.48398959636688</t>
   </si>
   <si>
     <t xml:space="preserve">1.48649215698242</t>
   </si>
   <si>
-    <t xml:space="preserve">1.48899435997009</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.52402985095978</t>
+    <t xml:space="preserve">1.48899447917938</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.52402973175049</t>
   </si>
   <si>
     <t xml:space="preserve">1.50851452350616</t>
@@ -2099,49 +2099,49 @@
     <t xml:space="preserve">1.6416482925415</t>
   </si>
   <si>
-    <t xml:space="preserve">1.70971691608429</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.69219899177551</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.68569183349609</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.76377069950104</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.75676381587982</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.74174845218658</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.71372056007385</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.73374044895172</t>
+    <t xml:space="preserve">1.70971667766571</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.6921991109848</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.68569219112396</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.76377058029175</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.7567640542984</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.74174809455872</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.71372067928314</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.73374032974243</t>
   </si>
   <si>
     <t xml:space="preserve">1.75125825405121</t>
   </si>
   <si>
-    <t xml:space="preserve">1.7627694606781</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.81031715869904</t>
+    <t xml:space="preserve">1.76276957988739</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.8103175163269</t>
   </si>
   <si>
     <t xml:space="preserve">1.85085773468018</t>
   </si>
   <si>
-    <t xml:space="preserve">1.84585356712341</t>
+    <t xml:space="preserve">1.84585309028625</t>
   </si>
   <si>
     <t xml:space="preserve">1.83984684944153</t>
   </si>
   <si>
-    <t xml:space="preserve">1.85486245155334</t>
+    <t xml:space="preserve">1.85486280918121</t>
   </si>
   <si>
     <t xml:space="preserve">1.80030715465546</t>
@@ -2153,106 +2153,106 @@
     <t xml:space="preserve">1.77077734470367</t>
   </si>
   <si>
-    <t xml:space="preserve">1.78128826618195</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.81732404232025</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.85386121273041</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.86787462234497</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.86837530136108</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.8518590927124</t>
+    <t xml:space="preserve">1.78128814697266</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.81732428073883</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.8538613319397</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.86787438392639</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.86837553977966</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.85185885429382</t>
   </si>
   <si>
     <t xml:space="preserve">1.82633316516876</t>
   </si>
   <si>
-    <t xml:space="preserve">1.8188259601593</t>
+    <t xml:space="preserve">1.81882572174072</t>
   </si>
   <si>
     <t xml:space="preserve">1.8033105134964</t>
   </si>
   <si>
-    <t xml:space="preserve">1.83183932304382</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.8243316411972</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.82232916355133</t>
+    <t xml:space="preserve">1.83183896541595</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.82433176040649</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.82232904434204</t>
   </si>
   <si>
     <t xml:space="preserve">1.84735441207886</t>
   </si>
   <si>
-    <t xml:space="preserve">1.83334052562714</t>
+    <t xml:space="preserve">1.83334076404572</t>
   </si>
   <si>
     <t xml:space="preserve">1.851358294487</t>
   </si>
   <si>
-    <t xml:space="preserve">1.85336053371429</t>
+    <t xml:space="preserve">1.85336077213287</t>
   </si>
   <si>
     <t xml:space="preserve">1.86937665939331</t>
   </si>
   <si>
-    <t xml:space="preserve">1.87037754058838</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.89990746974945</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.93544352054596</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.98649418354034</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.02002811431885</t>
+    <t xml:space="preserve">1.87037765979767</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.89990735054016</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.93544375896454</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.9864946603775</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.02002835273743</t>
   </si>
   <si>
     <t xml:space="preserve">2.07358145713806</t>
   </si>
   <si>
-    <t xml:space="preserve">2.09360218048096</t>
+    <t xml:space="preserve">2.09360194206238</t>
   </si>
   <si>
     <t xml:space="preserve">2.07308101654053</t>
   </si>
   <si>
-    <t xml:space="preserve">2.05506372451782</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.08859705924988</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.10561418533325</t>
+    <t xml:space="preserve">2.05506324768066</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.0885968208313</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.10561394691467</t>
   </si>
   <si>
     <t xml:space="preserve">2.11161971092224</t>
   </si>
   <si>
-    <t xml:space="preserve">2.14415287971497</t>
+    <t xml:space="preserve">2.14415264129639</t>
   </si>
   <si>
     <t xml:space="preserve">2.1096179485321</t>
   </si>
   <si>
-    <t xml:space="preserve">2.10311102867126</t>
+    <t xml:space="preserve">2.10311126708984</t>
   </si>
   <si>
     <t xml:space="preserve">2.05956816673279</t>
   </si>
   <si>
-    <t xml:space="preserve">2.04805588722229</t>
+    <t xml:space="preserve">2.04805612564087</t>
   </si>
   <si>
     <t xml:space="preserve">2.00401210784912</t>
@@ -2261,13 +2261,13 @@
     <t xml:space="preserve">1.98198986053467</t>
   </si>
   <si>
-    <t xml:space="preserve">1.95196008682251</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.96947717666626</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.93494272232056</t>
+    <t xml:space="preserve">1.95195960998535</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.96947741508484</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.93494248390198</t>
   </si>
   <si>
     <t xml:space="preserve">1.97848665714264</t>
@@ -2282,10 +2282,10 @@
     <t xml:space="preserve">1.83502221107483</t>
   </si>
   <si>
-    <t xml:space="preserve">1.81070053577423</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.82933044433594</t>
+    <t xml:space="preserve">1.81070065498352</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.82933032512665</t>
   </si>
   <si>
     <t xml:space="preserve">1.78068614006042</t>
@@ -2297,13 +2297,13 @@
     <t xml:space="preserve">1.77240633964539</t>
   </si>
   <si>
-    <t xml:space="preserve">1.75998628139496</t>
+    <t xml:space="preserve">1.75998616218567</t>
   </si>
   <si>
     <t xml:space="preserve">1.7511887550354</t>
   </si>
   <si>
-    <t xml:space="preserve">1.73721623420715</t>
+    <t xml:space="preserve">1.73721635341644</t>
   </si>
   <si>
     <t xml:space="preserve">1.76774907112122</t>
@@ -2315,94 +2315,94 @@
     <t xml:space="preserve">1.71496498584747</t>
   </si>
   <si>
-    <t xml:space="preserve">1.7118593454361</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.7656786441803</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.78223812580109</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.7620564699173</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.78327322006226</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.77706336975098</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.79051768779755</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.83088231086731</t>
+    <t xml:space="preserve">1.71185946464539</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.76567876338959</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.7822380065918</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.76205635070801</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.78327333927155</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.77706348896027</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.79051792621613</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.83088219165802</t>
   </si>
   <si>
     <t xml:space="preserve">1.86503732204437</t>
   </si>
   <si>
-    <t xml:space="preserve">1.86296713352203</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.89453423023224</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.87383472919464</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.8727992773056</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.88366639614105</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.85416972637177</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.84433710575104</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.88211476802826</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.95559787750244</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.01252174377441</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.01666140556335</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.99854946136475</t>
+    <t xml:space="preserve">1.86296725273132</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.89453399181366</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.87383484840393</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.87279963493347</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.88366627693176</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.85416960716248</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.84433746337891</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.8821142911911</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.95559775829315</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.01252198219299</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.01666164398193</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.99854934215546</t>
   </si>
   <si>
     <t xml:space="preserve">1.99026954174042</t>
   </si>
   <si>
-    <t xml:space="preserve">1.97370994091034</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.98250734806061</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.96853530406952</t>
+    <t xml:space="preserve">1.97371029853821</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.98250758647919</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.96853542327881</t>
   </si>
   <si>
     <t xml:space="preserve">1.99647986888885</t>
   </si>
   <si>
-    <t xml:space="preserve">1.96439528465271</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.93955600261688</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.94576549530029</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.93541610240936</t>
+    <t xml:space="preserve">1.964395403862</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.93955612182617</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.94576513767242</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.93541622161865</t>
   </si>
   <si>
     <t xml:space="preserve">1.88625431060791</t>
@@ -2411,40 +2411,40 @@
     <t xml:space="preserve">1.87072908878326</t>
   </si>
   <si>
-    <t xml:space="preserve">1.85106527805328</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.82570719718933</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.75429427623749</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.74342668056488</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.79000103473663</t>
+    <t xml:space="preserve">1.85106515884399</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.82570731639862</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.75429391860962</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.7434264421463</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.79000115394592</t>
   </si>
   <si>
     <t xml:space="preserve">1.76257383823395</t>
   </si>
   <si>
-    <t xml:space="preserve">1.78948366641998</t>
+    <t xml:space="preserve">1.78948378562927</t>
   </si>
   <si>
     <t xml:space="preserve">1.76464343070984</t>
   </si>
   <si>
-    <t xml:space="preserve">1.79828083515167</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.65597057342529</t>
+    <t xml:space="preserve">1.79828095436096</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.655970454216</t>
   </si>
   <si>
     <t xml:space="preserve">1.62078142166138</t>
   </si>
   <si>
-    <t xml:space="preserve">1.63941121101379</t>
+    <t xml:space="preserve">1.6394110918045</t>
   </si>
   <si>
     <t xml:space="preserve">1.55868220329285</t>
@@ -2453,7 +2453,7 @@
     <t xml:space="preserve">1.59283673763275</t>
   </si>
   <si>
-    <t xml:space="preserve">1.60887932777405</t>
+    <t xml:space="preserve">1.60887944698334</t>
   </si>
   <si>
     <t xml:space="preserve">1.55764722824097</t>
@@ -2468,118 +2468,118 @@
     <t xml:space="preserve">1.57731211185455</t>
   </si>
   <si>
-    <t xml:space="preserve">1.58817911148071</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.66011035442352</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.64872622489929</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.68132770061493</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.66787254810333</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.6714950799942</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.69943976402283</t>
+    <t xml:space="preserve">1.58817899227142</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.66011023521423</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.64872610569</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.68132781982422</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.66787278652191</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.67149496078491</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.69944000244141</t>
   </si>
   <si>
     <t xml:space="preserve">1.71651697158813</t>
   </si>
   <si>
-    <t xml:space="preserve">1.72169196605682</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.72997176647186</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.78844857215881</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.80863034725189</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.79103529453278</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.81846284866333</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.86451959609985</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.8733172416687</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.81225252151489</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.82311999797821</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.90281391143799</t>
+    <t xml:space="preserve">1.72169184684753</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.72997152805328</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.78844845294952</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.8086302280426</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.79103553295135</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.81846296787262</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.86451971530914</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.87331712245941</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.81225228309631</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.8231201171875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.9028137922287</t>
   </si>
   <si>
     <t xml:space="preserve">1.84588968753815</t>
   </si>
   <si>
-    <t xml:space="preserve">1.81794500350952</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.79879832267761</t>
+    <t xml:space="preserve">1.8179452419281</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.79879856109619</t>
   </si>
   <si>
     <t xml:space="preserve">1.80966544151306</t>
   </si>
   <si>
-    <t xml:space="preserve">1.83295285701752</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.80500793457031</t>
+    <t xml:space="preserve">1.83295273780823</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.80500757694244</t>
   </si>
   <si>
     <t xml:space="preserve">1.81587553024292</t>
   </si>
   <si>
-    <t xml:space="preserve">1.79931509494781</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.80552542209625</t>
+    <t xml:space="preserve">1.79931533336639</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.80552577972412</t>
   </si>
   <si>
     <t xml:space="preserve">1.81639325618744</t>
   </si>
   <si>
-    <t xml:space="preserve">1.88263189792633</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.90333139896393</t>
+    <t xml:space="preserve">1.88263201713562</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.90333151817322</t>
   </si>
   <si>
     <t xml:space="preserve">1.94421339035034</t>
   </si>
   <si>
-    <t xml:space="preserve">1.97267496585846</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.02649402618408</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.07927799224854</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.10204815864563</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.12999176979065</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.09066295623779</t>
+    <t xml:space="preserve">1.97267520427704</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.02649426460266</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.07927823066711</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.10204792022705</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.12999200820923</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.09066271781921</t>
   </si>
   <si>
     <t xml:space="preserve">2.08962821960449</t>
@@ -2588,13 +2588,13 @@
     <t xml:space="preserve">2.10515260696411</t>
   </si>
   <si>
-    <t xml:space="preserve">2.10566997528076</t>
+    <t xml:space="preserve">2.10567021369934</t>
   </si>
   <si>
     <t xml:space="preserve">2.06582355499268</t>
   </si>
   <si>
-    <t xml:space="preserve">2.07358598709106</t>
+    <t xml:space="preserve">2.07358551025391</t>
   </si>
   <si>
     <t xml:space="preserve">2.06996321678162</t>
@@ -2606,7 +2606,7 @@
     <t xml:space="preserve">2.16155934333801</t>
   </si>
   <si>
-    <t xml:space="preserve">2.17604899406433</t>
+    <t xml:space="preserve">2.17604947090149</t>
   </si>
   <si>
     <t xml:space="preserve">2.20761632919312</t>
@@ -2615,22 +2615,22 @@
     <t xml:space="preserve">2.18329381942749</t>
   </si>
   <si>
-    <t xml:space="preserve">2.21951818466187</t>
+    <t xml:space="preserve">2.21951794624329</t>
   </si>
   <si>
     <t xml:space="preserve">2.23556017875671</t>
   </si>
   <si>
-    <t xml:space="preserve">2.25056791305542</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.24280548095703</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.25936484336853</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.28679203987122</t>
+    <t xml:space="preserve">2.25056767463684</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.24280524253845</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.25936508178711</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.28679227828979</t>
   </si>
   <si>
     <t xml:space="preserve">2.35303115844727</t>
@@ -2639,28 +2639,28 @@
     <t xml:space="preserve">2.38459801673889</t>
   </si>
   <si>
-    <t xml:space="preserve">2.37114334106445</t>
+    <t xml:space="preserve">2.37114310264587</t>
   </si>
   <si>
     <t xml:space="preserve">2.31421947479248</t>
   </si>
   <si>
-    <t xml:space="preserve">2.32715678215027</t>
+    <t xml:space="preserve">2.32715654373169</t>
   </si>
   <si>
     <t xml:space="preserve">2.32146382331848</t>
   </si>
   <si>
-    <t xml:space="preserve">2.30076432228088</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.27074980735779</t>
+    <t xml:space="preserve">2.30076456069946</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.27074956893921</t>
   </si>
   <si>
     <t xml:space="preserve">2.27437281608582</t>
   </si>
   <si>
-    <t xml:space="preserve">2.2277979850769</t>
+    <t xml:space="preserve">2.22779822349548</t>
   </si>
   <si>
     <t xml:space="preserve">2.2443573474884</t>
@@ -2672,10 +2672,10 @@
     <t xml:space="preserve">2.28368735313416</t>
   </si>
   <si>
-    <t xml:space="preserve">2.30593943595886</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.27851223945618</t>
+    <t xml:space="preserve">2.30593991279602</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.27851247787476</t>
   </si>
   <si>
     <t xml:space="preserve">2.30283403396606</t>
@@ -2684,13 +2684,13 @@
     <t xml:space="preserve">2.29972910881042</t>
   </si>
   <si>
-    <t xml:space="preserve">2.33026123046875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.31318402290344</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.34216332435608</t>
+    <t xml:space="preserve">2.33026099205017</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.31318426132202</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.3421630859375</t>
   </si>
   <si>
     <t xml:space="preserve">2.35975813865662</t>
@@ -2705,7 +2705,7 @@
     <t xml:space="preserve">2.3049042224884</t>
   </si>
   <si>
-    <t xml:space="preserve">2.31991076469421</t>
+    <t xml:space="preserve">2.31991124153137</t>
   </si>
   <si>
     <t xml:space="preserve">2.3778703212738</t>
@@ -2717,34 +2717,34 @@
     <t xml:space="preserve">2.32767415046692</t>
   </si>
   <si>
-    <t xml:space="preserve">2.33440136909485</t>
+    <t xml:space="preserve">2.33440113067627</t>
   </si>
   <si>
     <t xml:space="preserve">2.35665345191956</t>
   </si>
   <si>
-    <t xml:space="preserve">2.38873791694641</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.39080762863159</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.38045835494995</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.3882200717926</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.36700344085693</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.36079359054565</t>
+    <t xml:space="preserve">2.38873815536499</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.39080739021301</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.38045859336853</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.38822031021118</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.36700320243835</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.36079335212708</t>
   </si>
   <si>
     <t xml:space="preserve">2.37942314147949</t>
   </si>
   <si>
-    <t xml:space="preserve">2.36493301391602</t>
+    <t xml:space="preserve">2.36493325233459</t>
   </si>
   <si>
     <t xml:space="preserve">2.39494752883911</t>
@@ -2753,58 +2753,58 @@
     <t xml:space="preserve">2.30749154090881</t>
   </si>
   <si>
-    <t xml:space="preserve">2.30800890922546</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.29351925849915</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.3400936126709</t>
+    <t xml:space="preserve">2.30800914764404</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.29351949691772</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.34009385108948</t>
   </si>
   <si>
     <t xml:space="preserve">2.31939363479614</t>
   </si>
   <si>
-    <t xml:space="preserve">2.23866581916809</t>
+    <t xml:space="preserve">2.23866558074951</t>
   </si>
   <si>
     <t xml:space="preserve">2.14758682250977</t>
   </si>
   <si>
-    <t xml:space="preserve">2.19157361984253</t>
+    <t xml:space="preserve">2.19157338142395</t>
   </si>
   <si>
     <t xml:space="preserve">2.24073529243469</t>
   </si>
   <si>
-    <t xml:space="preserve">2.26505756378174</t>
+    <t xml:space="preserve">2.26505780220032</t>
   </si>
   <si>
     <t xml:space="preserve">2.24384069442749</t>
   </si>
   <si>
-    <t xml:space="preserve">2.25263786315918</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.2629873752594</t>
+    <t xml:space="preserve">2.25263810157776</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.26298713684082</t>
   </si>
   <si>
     <t xml:space="preserve">2.34630298614502</t>
   </si>
   <si>
-    <t xml:space="preserve">2.32612156867981</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.40322732925415</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.14292931556702</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.13568472862244</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.17035627365112</t>
+    <t xml:space="preserve">2.32612133026123</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.40322709083557</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.14292907714844</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.13568449020386</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.1703565120697</t>
   </si>
   <si>
     <t xml:space="preserve">2.10722327232361</t>
@@ -2813,40 +2813,40 @@
     <t xml:space="preserve">1.98509466648102</t>
   </si>
   <si>
-    <t xml:space="preserve">1.98716509342194</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.03115200996399</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.95508027076721</t>
+    <t xml:space="preserve">1.98716497421265</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.03115177154541</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.95508050918579</t>
   </si>
   <si>
     <t xml:space="preserve">1.86244928836823</t>
   </si>
   <si>
-    <t xml:space="preserve">1.72065663337708</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.67615234851837</t>
+    <t xml:space="preserve">1.72065687179565</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.67615258693695</t>
   </si>
   <si>
     <t xml:space="preserve">1.61508870124817</t>
   </si>
   <si>
-    <t xml:space="preserve">1.58093464374542</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.36617588996887</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.2999370098114</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.30304193496704</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.07172298431396</t>
+    <t xml:space="preserve">1.58093440532684</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.36617612838745</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.29993712902069</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.30304181575775</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.07172310352325</t>
   </si>
   <si>
     <t xml:space="preserve">1.31183922290802</t>
@@ -2855,13 +2855,13 @@
     <t xml:space="preserve">1.21144604682922</t>
   </si>
   <si>
-    <t xml:space="preserve">1.2073061466217</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.17522156238556</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.19333386421204</t>
+    <t xml:space="preserve">1.20730638504028</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.17522144317627</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.19333374500275</t>
   </si>
   <si>
     <t xml:space="preserve">1.33253860473633</t>
@@ -2870,52 +2870,52 @@
     <t xml:space="preserve">1.51935315132141</t>
   </si>
   <si>
-    <t xml:space="preserve">1.55712962150574</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.53280794620514</t>
+    <t xml:space="preserve">1.55712974071503</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.53280782699585</t>
   </si>
   <si>
     <t xml:space="preserve">1.50279355049133</t>
   </si>
   <si>
-    <t xml:space="preserve">1.40602290630341</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.40550518035889</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.44897425174713</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.40705728530884</t>
+    <t xml:space="preserve">1.40602278709412</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.40550529956818</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.44897437095642</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.40705716609955</t>
   </si>
   <si>
     <t xml:space="preserve">1.39567267894745</t>
   </si>
   <si>
-    <t xml:space="preserve">1.38894474506378</t>
+    <t xml:space="preserve">1.38894486427307</t>
   </si>
   <si>
     <t xml:space="preserve">1.41585457324982</t>
   </si>
   <si>
-    <t xml:space="preserve">1.41016268730164</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.34081828594208</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.35375571250916</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.29320931434631</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.1979912519455</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.14624238014221</t>
+    <t xml:space="preserve">1.41016256809235</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.34081816673279</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.35375559329987</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.2932094335556</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.19799137115479</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.1462424993515</t>
   </si>
   <si>
     <t xml:space="preserve">1.15814447402954</t>
@@ -2924,37 +2924,37 @@
     <t xml:space="preserve">1.1591796875</t>
   </si>
   <si>
-    <t xml:space="preserve">1.10898280143738</t>
+    <t xml:space="preserve">1.10898268222809</t>
   </si>
   <si>
     <t xml:space="preserve">1.10743010044098</t>
   </si>
   <si>
-    <t xml:space="preserve">1.14468955993652</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.09708070755005</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.12813019752502</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.19902634620667</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.21817302703857</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.16538906097412</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.14054977893829</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.13847959041595</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.12502467632294</t>
+    <t xml:space="preserve">1.1446897983551</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.09708058834076</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.12813031673431</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.19902646541595</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.21817326545715</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.1653892993927</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.140549659729</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.13847947120667</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.12502455711365</t>
   </si>
   <si>
     <t xml:space="preserve">1.10639560222626</t>
@@ -2963,43 +2963,43 @@
     <t xml:space="preserve">1.09397518634796</t>
   </si>
   <si>
-    <t xml:space="preserve">1.08673071861267</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.05050599575043</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.04222619533539</t>
+    <t xml:space="preserve">1.08673059940338</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.05050611495972</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.04222631454468</t>
   </si>
   <si>
     <t xml:space="preserve">1.0386039018631</t>
   </si>
   <si>
-    <t xml:space="preserve">1.08031666278839</t>
+    <t xml:space="preserve">1.0803165435791</t>
   </si>
   <si>
     <t xml:space="preserve">1.02012348175049</t>
   </si>
   <si>
-    <t xml:space="preserve">1.0024346113205</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.983425915241241</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.98421847820282</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.986858189105988</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.08982074260712</t>
+    <t xml:space="preserve">1.00243449211121</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.983425855636597</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.984218239784241</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.986858129501343</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.08982086181641</t>
   </si>
   <si>
     <t xml:space="preserve">1.12942171096802</t>
   </si>
   <si>
-    <t xml:space="preserve">1.17483115196228</t>
+    <t xml:space="preserve">1.17483103275299</t>
   </si>
   <si>
     <t xml:space="preserve">1.13364660739899</t>
@@ -3008,7 +3008,7 @@
     <t xml:space="preserve">1.16163074970245</t>
   </si>
   <si>
-    <t xml:space="preserve">1.18275201320648</t>
+    <t xml:space="preserve">1.18275189399719</t>
   </si>
   <si>
     <t xml:space="preserve">1.22076845169067</t>
@@ -3017,31 +3017,31 @@
     <t xml:space="preserve">1.22129666805267</t>
   </si>
   <si>
-    <t xml:space="preserve">1.34010004997253</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.40504550933838</t>
+    <t xml:space="preserve">1.34010028839111</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.40504539012909</t>
   </si>
   <si>
     <t xml:space="preserve">1.3849812746048</t>
   </si>
   <si>
-    <t xml:space="preserve">1.31528294086456</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.23132920265198</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.20334422588348</t>
+    <t xml:space="preserve">1.31528306007385</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.23132908344269</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.20334410667419</t>
   </si>
   <si>
     <t xml:space="preserve">1.21443283557892</t>
   </si>
   <si>
-    <t xml:space="preserve">1.29416263103485</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.26829040050507</t>
+    <t xml:space="preserve">1.29416275024414</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.26829028129578</t>
   </si>
   <si>
     <t xml:space="preserve">1.23344075679779</t>
@@ -3053,37 +3053,37 @@
     <t xml:space="preserve">1.19806385040283</t>
   </si>
   <si>
-    <t xml:space="preserve">1.22763299942017</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.16532671451569</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.17430305480957</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.14737415313721</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.16796720027924</t>
+    <t xml:space="preserve">1.22763311862946</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.1653265953064</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.17430293560028</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.14737439155579</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.16796731948853</t>
   </si>
   <si>
     <t xml:space="preserve">1.14526259899139</t>
   </si>
   <si>
-    <t xml:space="preserve">1.15371084213257</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.14843034744263</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.18327927589417</t>
+    <t xml:space="preserve">1.15371072292328</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.14843046665192</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.18327915668488</t>
   </si>
   <si>
     <t xml:space="preserve">1.17007911205292</t>
   </si>
   <si>
-    <t xml:space="preserve">1.16479957103729</t>
+    <t xml:space="preserve">1.16479933261871</t>
   </si>
   <si>
     <t xml:space="preserve">1.13417410850525</t>
@@ -3095,10 +3095,10 @@
     <t xml:space="preserve">1.31581115722656</t>
   </si>
   <si>
-    <t xml:space="preserve">1.31686747074127</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.32373106479645</t>
+    <t xml:space="preserve">1.31686735153198</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.32373118400574</t>
   </si>
   <si>
     <t xml:space="preserve">1.34115552902222</t>
@@ -3107,7 +3107,7 @@
     <t xml:space="preserve">1.31317138671875</t>
   </si>
   <si>
-    <t xml:space="preserve">1.35858082771301</t>
+    <t xml:space="preserve">1.35858070850372</t>
   </si>
   <si>
     <t xml:space="preserve">1.34590780735016</t>
@@ -3116,46 +3116,46 @@
     <t xml:space="preserve">1.29944288730621</t>
   </si>
   <si>
-    <t xml:space="preserve">1.27990615367889</t>
+    <t xml:space="preserve">1.27990627288818</t>
   </si>
   <si>
     <t xml:space="preserve">1.22657680511475</t>
   </si>
   <si>
-    <t xml:space="preserve">1.23027276992798</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.19067180156708</t>
+    <t xml:space="preserve">1.23027288913727</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.19067192077637</t>
   </si>
   <si>
     <t xml:space="preserve">1.1758873462677</t>
   </si>
   <si>
-    <t xml:space="preserve">1.12572574615479</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.0966854095459</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.08242905139923</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.14790236949921</t>
+    <t xml:space="preserve">1.12572586536407</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.09668552875519</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.08242893218994</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.14790225028992</t>
   </si>
   <si>
     <t xml:space="preserve">1.23555302619934</t>
   </si>
   <si>
-    <t xml:space="preserve">1.25139307975769</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.25244927406311</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.22288084030151</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.22604882717133</t>
+    <t xml:space="preserve">1.25139319896698</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.2524493932724</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.2228809595108</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.22604870796204</t>
   </si>
   <si>
     <t xml:space="preserve">1.23713743686676</t>
@@ -3167,25 +3167,25 @@
     <t xml:space="preserve">1.20387232303619</t>
   </si>
   <si>
-    <t xml:space="preserve">1.24030542373657</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.23977720737457</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.23080098628998</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.25667333602905</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.21495997905731</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.18222379684448</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.17905521392822</t>
+    <t xml:space="preserve">1.24030530452728</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.23977732658386</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.23080086708069</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.25667357444763</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.21496021747589</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.18222367763519</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.17905509471893</t>
   </si>
   <si>
     <t xml:space="preserve">1.14156675338745</t>
@@ -3194,31 +3194,31 @@
     <t xml:space="preserve">1.15265452861786</t>
   </si>
   <si>
-    <t xml:space="preserve">1.14684689044952</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.11569344997406</t>
+    <t xml:space="preserve">1.14684700965881</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.11569333076477</t>
   </si>
   <si>
     <t xml:space="preserve">1.13100612163544</t>
   </si>
   <si>
-    <t xml:space="preserve">1.16004717350006</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.15687870979309</t>
+    <t xml:space="preserve">1.16004729270935</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.1568785905838</t>
   </si>
   <si>
     <t xml:space="preserve">1.15635049343109</t>
   </si>
   <si>
-    <t xml:space="preserve">1.14209485054016</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.15054285526276</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.14051055908203</t>
+    <t xml:space="preserve">1.14209473133087</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.15054297447205</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.14051043987274</t>
   </si>
   <si>
     <t xml:space="preserve">1.09404492378235</t>
@@ -3227,7 +3227,7 @@
     <t xml:space="preserve">1.06447649002075</t>
   </si>
   <si>
-    <t xml:space="preserve">1.06658816337585</t>
+    <t xml:space="preserve">1.06658792495728</t>
   </si>
   <si>
     <t xml:space="preserve">1.03490722179413</t>
@@ -3236,13 +3236,13 @@
     <t xml:space="preserve">1.03226745128632</t>
   </si>
   <si>
-    <t xml:space="preserve">1.0591961145401</t>
+    <t xml:space="preserve">1.05919623374939</t>
   </si>
   <si>
     <t xml:space="preserve">1.0296276807785</t>
   </si>
   <si>
-    <t xml:space="preserve">1.0496917963028</t>
+    <t xml:space="preserve">1.04969191551208</t>
   </si>
   <si>
     <t xml:space="preserve">1.02857148647308</t>
@@ -3251,49 +3251,49 @@
     <t xml:space="preserve">1.00058650970459</t>
   </si>
   <si>
-    <t xml:space="preserve">0.926720440387726</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.965333759784698</t>
+    <t xml:space="preserve">0.926720261573792</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.965333580970764</t>
   </si>
   <si>
     <t xml:space="preserve">0.924770295619965</t>
   </si>
   <si>
-    <t xml:space="preserve">0.93335098028183</t>
+    <t xml:space="preserve">0.933350801467896</t>
   </si>
   <si>
     <t xml:space="preserve">0.938031494617462</t>
   </si>
   <si>
-    <t xml:space="preserve">0.914239346981049</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.867435276508331</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.870945632457733</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.866265118122101</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.936471223831177</t>
+    <t xml:space="preserve">0.914239287376404</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.867435157299042</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.870945513248444</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.866265058517456</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.936471283435822</t>
   </si>
   <si>
     <t xml:space="preserve">0.923990190029144</t>
   </si>
   <si>
-    <t xml:space="preserve">1.01408803462982</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.949342489242554</t>
+    <t xml:space="preserve">1.01408791542053</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.949342429637909</t>
   </si>
   <si>
     <t xml:space="preserve">0.92555034160614</t>
   </si>
   <si>
-    <t xml:space="preserve">0.938811480998993</t>
+    <t xml:space="preserve">0.938811421394348</t>
   </si>
   <si>
     <t xml:space="preserve">0.929450631141663</t>
@@ -3302,16 +3302,16 @@
     <t xml:space="preserve">0.871335625648499</t>
   </si>
   <si>
-    <t xml:space="preserve">0.808540165424347</t>
+    <t xml:space="preserve">0.808540225028992</t>
   </si>
   <si>
     <t xml:space="preserve">0.798399269580841</t>
   </si>
   <si>
-    <t xml:space="preserve">0.793328881263733</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.822971403598785</t>
+    <t xml:space="preserve">0.793328762054443</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.82297146320343</t>
   </si>
   <si>
     <t xml:space="preserve">0.844033300876617</t>
@@ -3320,37 +3320,37 @@
     <t xml:space="preserve">0.863534986972809</t>
   </si>
   <si>
-    <t xml:space="preserve">0.844813287258148</t>
+    <t xml:space="preserve">0.844813227653503</t>
   </si>
   <si>
     <t xml:space="preserve">0.817510902881622</t>
   </si>
   <si>
-    <t xml:space="preserve">0.939201533794403</t>
+    <t xml:space="preserve">0.939201653003693</t>
   </si>
   <si>
     <t xml:space="preserve">0.931400835514069</t>
   </si>
   <si>
-    <t xml:space="preserve">0.966503739356995</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.0292991399765</t>
+    <t xml:space="preserve">0.966503798961639</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.02929925918579</t>
   </si>
   <si>
     <t xml:space="preserve">1.04139041900635</t>
   </si>
   <si>
-    <t xml:space="preserve">1.10496580600739</t>
+    <t xml:space="preserve">1.10496604442596</t>
   </si>
   <si>
     <t xml:space="preserve">1.11198651790619</t>
   </si>
   <si>
-    <t xml:space="preserve">1.15801048278809</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.18258273601532</t>
+    <t xml:space="preserve">1.15801060199738</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.18258261680603</t>
   </si>
   <si>
     <t xml:space="preserve">1.18531286716461</t>
@@ -3359,31 +3359,31 @@
     <t xml:space="preserve">1.18921327590942</t>
   </si>
   <si>
-    <t xml:space="preserve">1.15840041637421</t>
+    <t xml:space="preserve">1.1584005355835</t>
   </si>
   <si>
     <t xml:space="preserve">1.17868232727051</t>
   </si>
   <si>
-    <t xml:space="preserve">1.14279913902283</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.15918064117432</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.14669942855835</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.15723061561584</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.14864957332611</t>
+    <t xml:space="preserve">1.14279925823212</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.15918052196503</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.14669954776764</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.15723049640656</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.1486496925354</t>
   </si>
   <si>
     <t xml:space="preserve">1.14240920543671</t>
   </si>
   <si>
-    <t xml:space="preserve">1.15020978450775</t>
+    <t xml:space="preserve">1.15020966529846</t>
   </si>
   <si>
     <t xml:space="preserve">1.18336260318756</t>
@@ -3392,7 +3392,7 @@
     <t xml:space="preserve">1.14435923099518</t>
   </si>
   <si>
-    <t xml:space="preserve">1.14162909984589</t>
+    <t xml:space="preserve">1.14162886142731</t>
   </si>
   <si>
     <t xml:space="preserve">1.15254998207092</t>
@@ -3401,7 +3401,7 @@
     <t xml:space="preserve">1.13694870471954</t>
   </si>
   <si>
-    <t xml:space="preserve">1.14396941661835</t>
+    <t xml:space="preserve">1.14396929740906</t>
   </si>
   <si>
     <t xml:space="preserve">1.13265824317932</t>
@@ -3410,7 +3410,7 @@
     <t xml:space="preserve">1.08702433109283</t>
   </si>
   <si>
-    <t xml:space="preserve">1.11159634590149</t>
+    <t xml:space="preserve">1.11159646511078</t>
   </si>
   <si>
     <t xml:space="preserve">1.15450012683868</t>
@@ -3419,7 +3419,7 @@
     <t xml:space="preserve">1.17010152339935</t>
   </si>
   <si>
-    <t xml:space="preserve">1.16191101074219</t>
+    <t xml:space="preserve">1.1619108915329</t>
   </si>
   <si>
     <t xml:space="preserve">1.14045894145966</t>
@@ -3428,49 +3428,49 @@
     <t xml:space="preserve">1.14981961250305</t>
   </si>
   <si>
-    <t xml:space="preserve">1.2110550403595</t>
+    <t xml:space="preserve">1.21105515956879</t>
   </si>
   <si>
     <t xml:space="preserve">1.28594160079956</t>
   </si>
   <si>
-    <t xml:space="preserve">1.27151036262512</t>
+    <t xml:space="preserve">1.27151024341583</t>
   </si>
   <si>
     <t xml:space="preserve">1.29764270782471</t>
   </si>
   <si>
-    <t xml:space="preserve">1.29959273338318</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.28360140323639</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.26331973075867</t>
+    <t xml:space="preserve">1.29959261417389</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.2836012840271</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.26331949234009</t>
   </si>
   <si>
     <t xml:space="preserve">1.25512897968292</t>
   </si>
   <si>
-    <t xml:space="preserve">1.28282129764557</t>
+    <t xml:space="preserve">1.28282141685486</t>
   </si>
   <si>
     <t xml:space="preserve">1.26448976993561</t>
   </si>
   <si>
-    <t xml:space="preserve">1.28633177280426</t>
+    <t xml:space="preserve">1.28633153438568</t>
   </si>
   <si>
     <t xml:space="preserve">1.26370966434479</t>
   </si>
   <si>
-    <t xml:space="preserve">1.22899675369263</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.19194352626801</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.22509622573853</t>
+    <t xml:space="preserve">1.22899663448334</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.19194340705872</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.22509634494781</t>
   </si>
   <si>
     <t xml:space="preserve">1.18882322311401</t>
@@ -3479,10 +3479,10 @@
     <t xml:space="preserve">1.21573543548584</t>
   </si>
   <si>
-    <t xml:space="preserve">1.19584381580353</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.20442450046539</t>
+    <t xml:space="preserve">1.19584369659424</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.20442461967468</t>
   </si>
   <si>
     <t xml:space="preserve">1.32455492019653</t>
@@ -3491,37 +3491,37 @@
     <t xml:space="preserve">1.38696026802063</t>
   </si>
   <si>
-    <t xml:space="preserve">1.48953938484192</t>
+    <t xml:space="preserve">1.48953926563263</t>
   </si>
   <si>
     <t xml:space="preserve">1.45833659172058</t>
   </si>
   <si>
-    <t xml:space="preserve">1.48212850093842</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.45521628856659</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.4524861574173</t>
+    <t xml:space="preserve">1.48212862014771</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.45521640777588</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.45248603820801</t>
   </si>
   <si>
     <t xml:space="preserve">1.46886742115021</t>
   </si>
   <si>
-    <t xml:space="preserve">1.44741547107697</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.42089319229126</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.3963211774826</t>
+    <t xml:space="preserve">1.44741559028625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.42089331150055</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.39632105827332</t>
   </si>
   <si>
     <t xml:space="preserve">1.45170593261719</t>
   </si>
   <si>
-    <t xml:space="preserve">1.43064415454865</t>
+    <t xml:space="preserve">1.43064403533936</t>
   </si>
   <si>
     <t xml:space="preserve">1.43025410175323</t>
@@ -3539,34 +3539,34 @@
     <t xml:space="preserve">1.43766474723816</t>
   </si>
   <si>
-    <t xml:space="preserve">1.44624543190002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.50709080696106</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.54765427112579</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.54102373123169</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.52815246582031</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.53673326969147</t>
+    <t xml:space="preserve">1.44624555110931</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.50709092617035</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.54765439033508</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.54102385044098</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.5281525850296</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.53673338890076</t>
   </si>
   <si>
     <t xml:space="preserve">1.51879179477692</t>
   </si>
   <si>
-    <t xml:space="preserve">1.55233478546143</t>
+    <t xml:space="preserve">1.55233466625214</t>
   </si>
   <si>
     <t xml:space="preserve">1.60069894790649</t>
   </si>
   <si>
-    <t xml:space="preserve">1.58899796009064</t>
+    <t xml:space="preserve">1.58899784088135</t>
   </si>
   <si>
     <t xml:space="preserve">1.52581238746643</t>
@@ -3575,13 +3575,13 @@
     <t xml:space="preserve">1.48758912086487</t>
   </si>
   <si>
-    <t xml:space="preserve">1.48602879047394</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.50670063495636</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.49538969993591</t>
+    <t xml:space="preserve">1.48602890968323</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.50670075416565</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.4953898191452</t>
   </si>
   <si>
     <t xml:space="preserve">1.49616980552673</t>
@@ -3593,43 +3593,43 @@
     <t xml:space="preserve">1.48173856735229</t>
   </si>
   <si>
-    <t xml:space="preserve">1.46379697322845</t>
+    <t xml:space="preserve">1.46379709243774</t>
   </si>
   <si>
     <t xml:space="preserve">1.48329865932465</t>
   </si>
   <si>
-    <t xml:space="preserve">1.48134851455688</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.47510802745819</t>
+    <t xml:space="preserve">1.48134863376617</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.47510814666748</t>
   </si>
   <si>
     <t xml:space="preserve">1.45014584064484</t>
   </si>
   <si>
-    <t xml:space="preserve">1.45872664451599</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.48485887050629</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.46808731555939</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.47666800022125</t>
+    <t xml:space="preserve">1.4587265253067</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.484858751297</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.46808743476868</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.47666823863983</t>
   </si>
   <si>
     <t xml:space="preserve">1.47549796104431</t>
   </si>
   <si>
-    <t xml:space="preserve">1.52191209793091</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.44000506401062</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.40802216529846</t>
+    <t xml:space="preserve">1.52191197872162</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.44000482559204</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.40802204608917</t>
   </si>
   <si>
     <t xml:space="preserve">1.41036236286163</t>
@@ -3644,16 +3644,16 @@
     <t xml:space="preserve">1.44507539272308</t>
   </si>
   <si>
-    <t xml:space="preserve">1.47744810581207</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.46847748756409</t>
+    <t xml:space="preserve">1.47744822502136</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.46847760677338</t>
   </si>
   <si>
     <t xml:space="preserve">1.4622368812561</t>
   </si>
   <si>
-    <t xml:space="preserve">1.47900819778442</t>
+    <t xml:space="preserve">1.479008436203</t>
   </si>
   <si>
     <t xml:space="preserve">1.50787079334259</t>
@@ -3662,7 +3662,7 @@
     <t xml:space="preserve">1.50046026706696</t>
   </si>
   <si>
-    <t xml:space="preserve">1.55857527256012</t>
+    <t xml:space="preserve">1.55857539176941</t>
   </si>
   <si>
     <t xml:space="preserve">1.57261645793915</t>
@@ -3671,7 +3671,7 @@
     <t xml:space="preserve">1.54921436309814</t>
   </si>
   <si>
-    <t xml:space="preserve">1.56403577327728</t>
+    <t xml:space="preserve">1.56403589248657</t>
   </si>
   <si>
     <t xml:space="preserve">1.56481575965881</t>
@@ -3680,16 +3680,16 @@
     <t xml:space="preserve">1.57183659076691</t>
   </si>
   <si>
-    <t xml:space="preserve">1.54219388961792</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.52776265144348</t>
+    <t xml:space="preserve">1.54219365119934</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.52776277065277</t>
   </si>
   <si>
     <t xml:space="preserve">1.55584502220154</t>
   </si>
   <si>
-    <t xml:space="preserve">1.65574705600739</t>
+    <t xml:space="preserve">1.65574717521667</t>
   </si>
   <si>
     <t xml:space="preserve">1.6923645734787</t>
@@ -3698,43 +3698,43 @@
     <t xml:space="preserve">1.61116921901703</t>
   </si>
   <si>
-    <t xml:space="preserve">1.63186609745026</t>
+    <t xml:space="preserve">1.63186585903168</t>
   </si>
   <si>
     <t xml:space="preserve">1.62151765823364</t>
   </si>
   <si>
-    <t xml:space="preserve">1.61435353755951</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.61912965774536</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.62708973884583</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.61992561817169</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.60957741737366</t>
+    <t xml:space="preserve">1.61435341835022</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.61912953853607</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.6270899772644</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.61992573738098</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.60957729816437</t>
   </si>
   <si>
     <t xml:space="preserve">1.63107025623322</t>
   </si>
   <si>
-    <t xml:space="preserve">1.6207218170166</t>
+    <t xml:space="preserve">1.62072169780731</t>
   </si>
   <si>
     <t xml:space="preserve">1.63425421714783</t>
   </si>
   <si>
-    <t xml:space="preserve">1.62231373786926</t>
+    <t xml:space="preserve">1.62231397628784</t>
   </si>
   <si>
     <t xml:space="preserve">1.6167414188385</t>
   </si>
   <si>
-    <t xml:space="preserve">1.62470173835754</t>
+    <t xml:space="preserve">1.62470161914825</t>
   </si>
   <si>
     <t xml:space="preserve">1.59922885894775</t>
@@ -3743,46 +3743,46 @@
     <t xml:space="preserve">1.57693994045258</t>
   </si>
   <si>
-    <t xml:space="preserve">1.56539750099182</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.52997398376465</t>
+    <t xml:space="preserve">1.56539738178253</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.52997410297394</t>
   </si>
   <si>
     <t xml:space="preserve">1.54470062255859</t>
   </si>
   <si>
-    <t xml:space="preserve">1.52440166473389</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.50410282611847</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.52081966400146</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.51405322551727</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.46589350700378</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.45395302772522</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.46111726760864</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.46987354755402</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.4595251083374</t>
+    <t xml:space="preserve">1.52440178394318</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.50410294532776</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.52081954479218</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.51405334472656</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.46589326858521</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.45395290851593</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.46111714839935</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.46987366676331</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.45952522754669</t>
   </si>
   <si>
     <t xml:space="preserve">1.47106766700745</t>
   </si>
   <si>
-    <t xml:space="preserve">1.43206202983856</t>
+    <t xml:space="preserve">1.43206214904785</t>
   </si>
   <si>
     <t xml:space="preserve">1.41932547092438</t>
@@ -3794,40 +3794,40 @@
     <t xml:space="preserve">1.40420091152191</t>
   </si>
   <si>
-    <t xml:space="preserve">1.410569190979</t>
+    <t xml:space="preserve">1.41056907176971</t>
   </si>
   <si>
     <t xml:space="preserve">1.36240923404694</t>
   </si>
   <si>
-    <t xml:space="preserve">1.35643887519836</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.34529447555542</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.3019106388092</t>
+    <t xml:space="preserve">1.35643899440765</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.34529459476471</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.30191075801849</t>
   </si>
   <si>
     <t xml:space="preserve">1.23584008216858</t>
   </si>
   <si>
-    <t xml:space="preserve">1.24579060077667</t>
+    <t xml:space="preserve">1.24579048156738</t>
   </si>
   <si>
     <t xml:space="preserve">1.26171123981476</t>
   </si>
   <si>
-    <t xml:space="preserve">1.28400015830994</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.28519403934479</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.30469679832458</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.28957235813141</t>
+    <t xml:space="preserve">1.28400003910065</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.28519415855408</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.30469703674316</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.28957223892212</t>
   </si>
   <si>
     <t xml:space="preserve">1.29076623916626</t>
@@ -3836,10 +3836,10 @@
     <t xml:space="preserve">1.29434847831726</t>
   </si>
   <si>
-    <t xml:space="preserve">1.31066715717316</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.31026899814606</t>
+    <t xml:space="preserve">1.31066703796387</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.31026911735535</t>
   </si>
   <si>
     <t xml:space="preserve">1.29235827922821</t>
@@ -3854,19 +3854,19 @@
     <t xml:space="preserve">1.43604218959808</t>
   </si>
   <si>
-    <t xml:space="preserve">1.4304701089859</t>
+    <t xml:space="preserve">1.43046998977661</t>
   </si>
   <si>
     <t xml:space="preserve">1.4726597070694</t>
   </si>
   <si>
-    <t xml:space="preserve">1.46231138706207</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.45474886894226</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.43683815002441</t>
+    <t xml:space="preserve">1.46231126785278</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.45474898815155</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.43683838844299</t>
   </si>
   <si>
     <t xml:space="preserve">1.41136515140533</t>
@@ -3875,19 +3875,19 @@
     <t xml:space="preserve">1.42091751098633</t>
   </si>
   <si>
-    <t xml:space="preserve">1.39783275127411</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.39305639266968</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.42290759086609</t>
+    <t xml:space="preserve">1.39783263206482</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.39305651187897</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.42290771007538</t>
   </si>
   <si>
     <t xml:space="preserve">1.42808187007904</t>
   </si>
   <si>
-    <t xml:space="preserve">1.45793306827545</t>
+    <t xml:space="preserve">1.45793318748474</t>
   </si>
   <si>
     <t xml:space="preserve">1.43882834911346</t>
@@ -3899,7 +3899,7 @@
     <t xml:space="preserve">1.44440054893494</t>
   </si>
   <si>
-    <t xml:space="preserve">1.46668934822083</t>
+    <t xml:space="preserve">1.46668946743011</t>
   </si>
   <si>
     <t xml:space="preserve">1.4758437871933</t>
@@ -3908,16 +3908,16 @@
     <t xml:space="preserve">1.4690774679184</t>
   </si>
   <si>
-    <t xml:space="preserve">1.4861923456192</t>
+    <t xml:space="preserve">1.48619210720062</t>
   </si>
   <si>
     <t xml:space="preserve">1.44718670845032</t>
   </si>
   <si>
-    <t xml:space="preserve">1.4364401102066</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.45037066936493</t>
+    <t xml:space="preserve">1.43644022941589</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.45037090778351</t>
   </si>
   <si>
     <t xml:space="preserve">1.44201242923737</t>
@@ -3929,37 +3929,37 @@
     <t xml:space="preserve">1.42370367050171</t>
   </si>
   <si>
-    <t xml:space="preserve">1.34768259525299</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.36519527435303</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.40499711036682</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.42449963092804</t>
+    <t xml:space="preserve">1.3476824760437</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.36519539356232</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.40499699115753</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.42449975013733</t>
   </si>
   <si>
     <t xml:space="preserve">1.45992314815521</t>
   </si>
   <si>
-    <t xml:space="preserve">1.51604330539703</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.50848114490509</t>
+    <t xml:space="preserve">1.51604354381561</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.5084810256958</t>
   </si>
   <si>
     <t xml:space="preserve">1.54708874225616</t>
   </si>
   <si>
-    <t xml:space="preserve">1.53873026371002</t>
+    <t xml:space="preserve">1.53873038291931</t>
   </si>
   <si>
     <t xml:space="preserve">1.57574594020844</t>
   </si>
   <si>
-    <t xml:space="preserve">1.56261134147644</t>
+    <t xml:space="preserve">1.56261122226715</t>
   </si>
   <si>
     <t xml:space="preserve">1.61753761768341</t>
@@ -3971,61 +3971,61 @@
     <t xml:space="preserve">1.61833357810974</t>
   </si>
   <si>
-    <t xml:space="preserve">1.64380657672882</t>
+    <t xml:space="preserve">1.64380669593811</t>
   </si>
   <si>
     <t xml:space="preserve">1.64539861679077</t>
   </si>
   <si>
-    <t xml:space="preserve">1.63903045654297</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.6398264169693</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.64221453666687</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.65415513515472</t>
+    <t xml:space="preserve">1.63903057575226</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.63982653617859</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.64221465587616</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.65415501594543</t>
   </si>
   <si>
     <t xml:space="preserve">1.6302741765976</t>
   </si>
   <si>
-    <t xml:space="preserve">1.62947797775269</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.6334582567215</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.59365653991699</t>
+    <t xml:space="preserve">1.6294778585434</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.63345813751221</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.59365665912628</t>
   </si>
   <si>
     <t xml:space="preserve">1.61196541786194</t>
   </si>
   <si>
-    <t xml:space="preserve">1.50808322429657</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.49932682514191</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.52639198303223</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.52400374412537</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.50609314441681</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.5319641828537</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.52758586406708</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.52002370357513</t>
+    <t xml:space="preserve">1.50808298587799</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.49932670593262</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.52639186382294</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.52400386333466</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.50609302520752</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.53196406364441</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.52758574485779</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.52002358436584</t>
   </si>
   <si>
     <t xml:space="preserve">1.53116798400879</t>
@@ -4037,16 +4037,16 @@
     <t xml:space="preserve">1.53315806388855</t>
   </si>
   <si>
-    <t xml:space="preserve">1.51325726509094</t>
+    <t xml:space="preserve">1.51325738430023</t>
   </si>
   <si>
     <t xml:space="preserve">1.47027158737183</t>
   </si>
   <si>
-    <t xml:space="preserve">1.43007183074951</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.43564426898956</t>
+    <t xml:space="preserve">1.4300719499588</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.43564414978027</t>
   </si>
   <si>
     <t xml:space="preserve">1.42887794971466</t>
@@ -4058,13 +4058,13 @@
     <t xml:space="preserve">1.35086667537689</t>
   </si>
   <si>
-    <t xml:space="preserve">1.34012031555176</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.33892631530762</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.3775337934494</t>
+    <t xml:space="preserve">1.34012043476105</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.33892607688904</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.37753391265869</t>
   </si>
   <si>
     <t xml:space="preserve">1.36439919471741</t>
@@ -4073,13 +4073,13 @@
     <t xml:space="preserve">1.35166275501251</t>
   </si>
   <si>
-    <t xml:space="preserve">1.39425039291382</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.40619087219238</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.38191187381744</t>
+    <t xml:space="preserve">1.39425051212311</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.40619111061096</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.38191199302673</t>
   </si>
   <si>
     <t xml:space="preserve">1.38907623291016</t>
@@ -4091,7 +4091,7 @@
     <t xml:space="preserve">1.47902798652649</t>
   </si>
   <si>
-    <t xml:space="preserve">1.41614151000977</t>
+    <t xml:space="preserve">1.41614139080048</t>
   </si>
   <si>
     <t xml:space="preserve">1.41375339031219</t>
@@ -4109,13 +4109,13 @@
     <t xml:space="preserve">1.42569386959076</t>
   </si>
   <si>
-    <t xml:space="preserve">1.44320631027222</t>
+    <t xml:space="preserve">1.44320642948151</t>
   </si>
   <si>
     <t xml:space="preserve">1.45435094833374</t>
   </si>
   <si>
-    <t xml:space="preserve">1.45116686820984</t>
+    <t xml:space="preserve">1.45116674900055</t>
   </si>
   <si>
     <t xml:space="preserve">1.50052082538605</t>
@@ -4124,19 +4124,19 @@
     <t xml:space="preserve">1.52917790412903</t>
   </si>
   <si>
-    <t xml:space="preserve">1.5251978635788</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.53634226322174</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.5347501039505</t>
+    <t xml:space="preserve">1.52519774436951</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.53634214401245</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.53475022315979</t>
   </si>
   <si>
     <t xml:space="preserve">1.56181538105011</t>
   </si>
   <si>
-    <t xml:space="preserve">1.55624306201935</t>
+    <t xml:space="preserve">1.55624294281006</t>
   </si>
   <si>
     <t xml:space="preserve">1.54111838340759</t>
@@ -4145,22 +4145,22 @@
     <t xml:space="preserve">1.52678990364075</t>
   </si>
   <si>
-    <t xml:space="preserve">1.49813258647919</t>
+    <t xml:space="preserve">1.49813270568848</t>
   </si>
   <si>
     <t xml:space="preserve">1.42847990989685</t>
   </si>
   <si>
-    <t xml:space="preserve">1.42330574989319</t>
+    <t xml:space="preserve">1.4233056306839</t>
   </si>
   <si>
     <t xml:space="preserve">1.48818230628967</t>
   </si>
   <si>
-    <t xml:space="preserve">1.52320766448975</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.46509730815887</t>
+    <t xml:space="preserve">1.52320754528046</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.46509742736816</t>
   </si>
   <si>
     <t xml:space="preserve">1.47624182701111</t>
@@ -4172,22 +4172,22 @@
     <t xml:space="preserve">1.57375574111938</t>
   </si>
   <si>
-    <t xml:space="preserve">1.55783522129059</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.61514949798584</t>
+    <t xml:space="preserve">1.5578351020813</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.61514937877655</t>
   </si>
   <si>
     <t xml:space="preserve">1.61276137828827</t>
   </si>
   <si>
-    <t xml:space="preserve">1.63743841648102</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.57455193996429</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.71863353252411</t>
+    <t xml:space="preserve">1.63743829727173</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.574551820755</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.71863377094269</t>
   </si>
   <si>
     <t xml:space="preserve">1.69793665409088</t>
@@ -4196,7 +4196,7 @@
     <t xml:space="preserve">1.6071891784668</t>
   </si>
   <si>
-    <t xml:space="preserve">1.56022334098816</t>
+    <t xml:space="preserve">1.56022322177887</t>
   </si>
   <si>
     <t xml:space="preserve">1.44161438941956</t>
@@ -4205,13 +4205,13 @@
     <t xml:space="preserve">1.46788358688354</t>
   </si>
   <si>
-    <t xml:space="preserve">1.32260775566101</t>
+    <t xml:space="preserve">1.32260751724243</t>
   </si>
   <si>
     <t xml:space="preserve">1.31743335723877</t>
   </si>
   <si>
-    <t xml:space="preserve">1.24857664108276</t>
+    <t xml:space="preserve">1.24857652187347</t>
   </si>
   <si>
     <t xml:space="preserve">1.11643528938293</t>
@@ -4223,22 +4223,22 @@
     <t xml:space="preserve">1.11563920974731</t>
   </si>
   <si>
-    <t xml:space="preserve">1.22708368301392</t>
+    <t xml:space="preserve">1.22708356380463</t>
   </si>
   <si>
     <t xml:space="preserve">1.13514196872711</t>
   </si>
   <si>
-    <t xml:space="preserve">1.12877368927002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.17494344711304</t>
+    <t xml:space="preserve">1.12877380847931</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.17494368553162</t>
   </si>
   <si>
     <t xml:space="preserve">1.19882452487946</t>
   </si>
   <si>
-    <t xml:space="preserve">1.28678607940674</t>
+    <t xml:space="preserve">1.28678619861603</t>
   </si>
   <si>
     <t xml:space="preserve">1.25773096084595</t>
@@ -4250,28 +4250,28 @@
     <t xml:space="preserve">1.2660893201828</t>
   </si>
   <si>
-    <t xml:space="preserve">1.24698460102081</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.23464608192444</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.243004322052</t>
+    <t xml:space="preserve">1.24698436260223</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.23464596271515</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.24300444126129</t>
   </si>
   <si>
     <t xml:space="preserve">1.25892508029938</t>
   </si>
   <si>
-    <t xml:space="preserve">1.33295595645905</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.30668687820435</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.26529335975647</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.27922391891479</t>
+    <t xml:space="preserve">1.33295607566833</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.30668699741364</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.26529324054718</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.27922379970551</t>
   </si>
   <si>
     <t xml:space="preserve">1.22429752349854</t>
@@ -4283,16 +4283,16 @@
     <t xml:space="preserve">1.27484571933746</t>
   </si>
   <si>
-    <t xml:space="preserve">1.2728556394577</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.23225796222687</t>
+    <t xml:space="preserve">1.27285552024841</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.23225784301758</t>
   </si>
   <si>
     <t xml:space="preserve">1.23504400253296</t>
   </si>
   <si>
-    <t xml:space="preserve">1.24778044223785</t>
+    <t xml:space="preserve">1.24778068065643</t>
   </si>
   <si>
     <t xml:space="preserve">1.25335276126862</t>
@@ -4301,7 +4301,7 @@
     <t xml:space="preserve">1.29753255844116</t>
   </si>
   <si>
-    <t xml:space="preserve">1.30628883838654</t>
+    <t xml:space="preserve">1.30628895759583</t>
   </si>
   <si>
     <t xml:space="preserve">1.28758215904236</t>
@@ -4310,7 +4310,7 @@
     <t xml:space="preserve">1.27404952049255</t>
   </si>
   <si>
-    <t xml:space="preserve">1.2593230009079</t>
+    <t xml:space="preserve">1.25932312011719</t>
   </si>
   <si>
     <t xml:space="preserve">1.26847732067108</t>
@@ -4319,7 +4319,7 @@
     <t xml:space="preserve">1.26011908054352</t>
   </si>
   <si>
-    <t xml:space="preserve">1.27763187885284</t>
+    <t xml:space="preserve">1.27763175964355</t>
   </si>
   <si>
     <t xml:space="preserve">1.2692734003067</t>
@@ -4328,7 +4328,7 @@
     <t xml:space="preserve">1.23822820186615</t>
   </si>
   <si>
-    <t xml:space="preserve">1.21912324428558</t>
+    <t xml:space="preserve">1.21912348270416</t>
   </si>
   <si>
     <t xml:space="preserve">1.22071540355682</t>
@@ -4340,34 +4340,34 @@
     <t xml:space="preserve">1.35325491428375</t>
   </si>
   <si>
-    <t xml:space="preserve">1.38629007339478</t>
+    <t xml:space="preserve">1.38629031181335</t>
   </si>
   <si>
     <t xml:space="preserve">1.38668823242188</t>
   </si>
   <si>
-    <t xml:space="preserve">1.37395167350769</t>
+    <t xml:space="preserve">1.3739515542984</t>
   </si>
   <si>
     <t xml:space="preserve">1.40539491176605</t>
   </si>
   <si>
-    <t xml:space="preserve">1.39862859249115</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.4073851108551</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.39027047157288</t>
+    <t xml:space="preserve">1.39862871170044</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.40738499164581</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.39027035236359</t>
   </si>
   <si>
     <t xml:space="preserve">1.48383438587189</t>
   </si>
   <si>
-    <t xml:space="preserve">1.49949705600739</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.54153907299042</t>
+    <t xml:space="preserve">1.49949717521667</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.54153895378113</t>
   </si>
   <si>
     <t xml:space="preserve">1.56049907207489</t>
@@ -4376,13 +4376,13 @@
     <t xml:space="preserve">1.55390429496765</t>
   </si>
   <si>
-    <t xml:space="preserve">1.55349218845367</t>
+    <t xml:space="preserve">1.55349206924438</t>
   </si>
   <si>
     <t xml:space="preserve">1.57987141609192</t>
   </si>
   <si>
-    <t xml:space="preserve">1.57616174221039</t>
+    <t xml:space="preserve">1.57616186141968</t>
   </si>
   <si>
     <t xml:space="preserve">1.58976376056671</t>
@@ -4391,22 +4391,22 @@
     <t xml:space="preserve">1.53576862812042</t>
   </si>
   <si>
-    <t xml:space="preserve">1.59182441234589</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.55307996273041</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.5984194278717</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.60831153392792</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.40057468414307</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.35482323169708</t>
+    <t xml:space="preserve">1.59182453155518</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.5530800819397</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.59841930866241</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.60831165313721</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.40057480335236</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.35482311248779</t>
   </si>
   <si>
     <t xml:space="preserve">1.36430323123932</t>
@@ -4415,7 +4415,7 @@
     <t xml:space="preserve">1.41788613796234</t>
   </si>
   <si>
-    <t xml:space="preserve">1.35770833492279</t>
+    <t xml:space="preserve">1.35770845413208</t>
   </si>
   <si>
     <t xml:space="preserve">1.38326334953308</t>
@@ -4424,70 +4424,70 @@
     <t xml:space="preserve">1.40799391269684</t>
   </si>
   <si>
-    <t xml:space="preserve">1.41458868980408</t>
+    <t xml:space="preserve">1.41458880901337</t>
   </si>
   <si>
     <t xml:space="preserve">1.41252791881561</t>
   </si>
   <si>
-    <t xml:space="preserve">1.34451878070831</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.38820946216583</t>
+    <t xml:space="preserve">1.3445188999176</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.38820958137512</t>
   </si>
   <si>
     <t xml:space="preserve">1.36718845367432</t>
   </si>
   <si>
-    <t xml:space="preserve">1.36512756347656</t>
+    <t xml:space="preserve">1.36512780189514</t>
   </si>
   <si>
     <t xml:space="preserve">1.34493112564087</t>
   </si>
   <si>
-    <t xml:space="preserve">1.29217231273651</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.25219142436981</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.25136697292328</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.18789184093475</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.16934394836426</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.22993385791779</t>
+    <t xml:space="preserve">1.2921724319458</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.25219130516052</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.25136709213257</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.18789196014404</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.16934382915497</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.2299337387085</t>
   </si>
   <si>
     <t xml:space="preserve">1.24477219581604</t>
   </si>
   <si>
-    <t xml:space="preserve">1.18830406665802</t>
+    <t xml:space="preserve">1.18830394744873</t>
   </si>
   <si>
     <t xml:space="preserve">1.15903949737549</t>
   </si>
   <si>
-    <t xml:space="preserve">1.128950715065</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.05929291248322</t>
+    <t xml:space="preserve">1.12895059585571</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.05929279327393</t>
   </si>
   <si>
     <t xml:space="preserve">1.06588768959045</t>
   </si>
   <si>
-    <t xml:space="preserve">1.07990169525146</t>
+    <t xml:space="preserve">1.07990157604218</t>
   </si>
   <si>
     <t xml:space="preserve">1.15326905250549</t>
   </si>
   <si>
-    <t xml:space="preserve">1.12029504776001</t>
+    <t xml:space="preserve">1.12029492855072</t>
   </si>
   <si>
     <t xml:space="preserve">1.08525991439819</t>
@@ -4496,19 +4496,19 @@
     <t xml:space="preserve">1.06794857978821</t>
   </si>
   <si>
-    <t xml:space="preserve">1.09556448459625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.06506335735321</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.08567225933075</t>
+    <t xml:space="preserve">1.09556436538696</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.0650634765625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.08567214012146</t>
   </si>
   <si>
     <t xml:space="preserve">1.08814525604248</t>
   </si>
   <si>
-    <t xml:space="preserve">1.11287593841553</t>
+    <t xml:space="preserve">1.11287581920624</t>
   </si>
   <si>
     <t xml:space="preserve">1.12482893466949</t>
@@ -4523,7 +4523,7 @@
     <t xml:space="preserve">1.18129706382751</t>
   </si>
   <si>
-    <t xml:space="preserve">1.29588210582733</t>
+    <t xml:space="preserve">1.29588198661804</t>
   </si>
   <si>
     <t xml:space="preserve">1.32720744609833</t>
@@ -4544,7 +4544,7 @@
     <t xml:space="preserve">1.35070145130157</t>
   </si>
   <si>
-    <t xml:space="preserve">1.30659866333008</t>
+    <t xml:space="preserve">1.30659854412079</t>
   </si>
   <si>
     <t xml:space="preserve">1.26290786266327</t>
@@ -4553,16 +4553,16 @@
     <t xml:space="preserve">1.28063154220581</t>
   </si>
   <si>
-    <t xml:space="preserve">1.28021919727325</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.26084697246552</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.22004163265228</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.22045385837555</t>
+    <t xml:space="preserve">1.28021931648254</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.2608470916748</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.22004151344299</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.22045373916626</t>
   </si>
   <si>
     <t xml:space="preserve">1.24106252193451</t>
@@ -4571,16 +4571,16 @@
     <t xml:space="preserve">1.24065041542053</t>
   </si>
   <si>
-    <t xml:space="preserve">1.22333908081055</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.25301563739777</t>
+    <t xml:space="preserve">1.22333896160126</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.25301575660706</t>
   </si>
   <si>
     <t xml:space="preserve">1.21550762653351</t>
   </si>
   <si>
-    <t xml:space="preserve">1.21798074245453</t>
+    <t xml:space="preserve">1.21798062324524</t>
   </si>
   <si>
     <t xml:space="preserve">1.20066940784454</t>
@@ -4592,25 +4592,25 @@
     <t xml:space="preserve">1.27609753608704</t>
   </si>
   <si>
-    <t xml:space="preserve">1.33957254886627</t>
+    <t xml:space="preserve">1.33957266807556</t>
   </si>
   <si>
     <t xml:space="preserve">1.32597088813782</t>
   </si>
   <si>
-    <t xml:space="preserve">1.37584412097931</t>
+    <t xml:space="preserve">1.3758442401886</t>
   </si>
   <si>
     <t xml:space="preserve">1.38120257854462</t>
   </si>
   <si>
-    <t xml:space="preserve">1.38985812664032</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.39686512947083</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.3729590177536</t>
+    <t xml:space="preserve">1.38985824584961</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.39686524868011</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.37295889854431</t>
   </si>
   <si>
     <t xml:space="preserve">1.38408780097961</t>
@@ -4625,37 +4625,37 @@
     <t xml:space="preserve">1.37172245979309</t>
   </si>
   <si>
-    <t xml:space="preserve">1.3416336774826</t>
+    <t xml:space="preserve">1.34163355827332</t>
   </si>
   <si>
     <t xml:space="preserve">1.32020044326782</t>
   </si>
   <si>
-    <t xml:space="preserve">1.28269243240356</t>
+    <t xml:space="preserve">1.28269231319427</t>
   </si>
   <si>
     <t xml:space="preserve">1.30330121517181</t>
   </si>
   <si>
-    <t xml:space="preserve">1.32844388484955</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.38491189479828</t>
+    <t xml:space="preserve">1.32844400405884</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.38491201400757</t>
   </si>
   <si>
     <t xml:space="preserve">1.35894501209259</t>
   </si>
   <si>
-    <t xml:space="preserve">1.31731534004211</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.3346266746521</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.31855154037476</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.30824732780457</t>
+    <t xml:space="preserve">1.31731522083282</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.33462655544281</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.31855165958405</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.30824744701385</t>
   </si>
   <si>
     <t xml:space="preserve">1.34080922603607</t>
@@ -4664,22 +4664,22 @@
     <t xml:space="preserve">1.36347889900208</t>
   </si>
   <si>
-    <t xml:space="preserve">1.39274346828461</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.40181124210358</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.41211569309235</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.41664969921112</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.43560969829559</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.4764152765274</t>
+    <t xml:space="preserve">1.39274334907532</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.40181148052216</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.41211581230164</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.41664958000183</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.43560981750488</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.47641515731812</t>
   </si>
   <si>
     <t xml:space="preserve">1.46734726428986</t>
@@ -4688,10 +4688,10 @@
     <t xml:space="preserve">1.4694082736969</t>
   </si>
   <si>
-    <t xml:space="preserve">1.51103806495667</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.52093017101288</t>
+    <t xml:space="preserve">1.51103794574738</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.52093029022217</t>
   </si>
   <si>
     <t xml:space="preserve">1.54359984397888</t>
@@ -4706,7 +4706,7 @@
     <t xml:space="preserve">1.58893930912018</t>
   </si>
   <si>
-    <t xml:space="preserve">1.6594215631485</t>
+    <t xml:space="preserve">1.65942144393921</t>
   </si>
   <si>
     <t xml:space="preserve">1.68992245197296</t>
@@ -4715,7 +4715,7 @@
     <t xml:space="preserve">1.56008696556091</t>
   </si>
   <si>
-    <t xml:space="preserve">1.51680850982666</t>
+    <t xml:space="preserve">1.51680839061737</t>
   </si>
   <si>
     <t xml:space="preserve">1.54854595661163</t>
@@ -4727,10 +4727,10 @@
     <t xml:space="preserve">1.54648518562317</t>
   </si>
   <si>
-    <t xml:space="preserve">1.55184352397919</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.57410109043121</t>
+    <t xml:space="preserve">1.55184364318848</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.57410097122192</t>
   </si>
   <si>
     <t xml:space="preserve">1.57822275161743</t>
@@ -4739,7 +4739,7 @@
     <t xml:space="preserve">1.58193230628967</t>
   </si>
   <si>
-    <t xml:space="preserve">1.59965586662292</t>
+    <t xml:space="preserve">1.59965598583221</t>
   </si>
   <si>
     <t xml:space="preserve">1.61284565925598</t>
@@ -4751,7 +4751,7 @@
     <t xml:space="preserve">1.60872387886047</t>
   </si>
   <si>
-    <t xml:space="preserve">1.61573088169098</t>
+    <t xml:space="preserve">1.61573076248169</t>
   </si>
   <si>
     <t xml:space="preserve">1.62562298774719</t>
@@ -4763,10 +4763,10 @@
     <t xml:space="preserve">1.59883153438568</t>
   </si>
   <si>
-    <t xml:space="preserve">1.5901757478714</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.59718286991119</t>
+    <t xml:space="preserve">1.59017586708069</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.5971827507019</t>
   </si>
   <si>
     <t xml:space="preserve">1.60171675682068</t>
@@ -4775,13 +4775,13 @@
     <t xml:space="preserve">1.60954809188843</t>
   </si>
   <si>
-    <t xml:space="preserve">1.60913586616516</t>
+    <t xml:space="preserve">1.60913598537445</t>
   </si>
   <si>
     <t xml:space="preserve">1.61902821063995</t>
   </si>
   <si>
-    <t xml:space="preserve">1.6070750951767</t>
+    <t xml:space="preserve">1.60707497596741</t>
   </si>
   <si>
     <t xml:space="preserve">1.55101907253265</t>
@@ -4790,7 +4790,7 @@
     <t xml:space="preserve">1.54978251457214</t>
   </si>
   <si>
-    <t xml:space="preserve">1.53782951831818</t>
+    <t xml:space="preserve">1.53782939910889</t>
   </si>
   <si>
     <t xml:space="preserve">1.60418975353241</t>
@@ -4799,13 +4799,13 @@
     <t xml:space="preserve">1.60295331478119</t>
   </si>
   <si>
-    <t xml:space="preserve">1.59512186050415</t>
+    <t xml:space="preserve">1.59512197971344</t>
   </si>
   <si>
     <t xml:space="preserve">1.58152008056641</t>
   </si>
   <si>
-    <t xml:space="preserve">1.61531853675842</t>
+    <t xml:space="preserve">1.61531865596771</t>
   </si>
   <si>
     <t xml:space="preserve">1.63633954524994</t>
@@ -4817,49 +4817,49 @@
     <t xml:space="preserve">1.67343544960022</t>
   </si>
   <si>
-    <t xml:space="preserve">1.71712613105774</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.72536957263947</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.73938357830048</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.73855924606323</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.74845147132874</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.80533194541931</t>
+    <t xml:space="preserve">1.71712589263916</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.72536969184875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.73938369750977</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.73855936527252</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.74845159053802</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.80533182621002</t>
   </si>
   <si>
     <t xml:space="preserve">1.82511639595032</t>
   </si>
   <si>
-    <t xml:space="preserve">1.79708850383759</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.85644173622131</t>
+    <t xml:space="preserve">1.79708826541901</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.85644161701202</t>
   </si>
   <si>
     <t xml:space="preserve">1.85479295253754</t>
   </si>
   <si>
-    <t xml:space="preserve">1.89024019241333</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.90178096294403</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.92898464202881</t>
+    <t xml:space="preserve">1.89023995399475</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.90178108215332</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.9289847612381</t>
   </si>
   <si>
     <t xml:space="preserve">1.93310654163361</t>
   </si>
   <si>
-    <t xml:space="preserve">1.97349965572357</t>
+    <t xml:space="preserve">1.97349977493286</t>
   </si>
   <si>
     <t xml:space="preserve">2.00400066375732</t>
@@ -4868,13 +4868,13 @@
     <t xml:space="preserve">2.00317645072937</t>
   </si>
   <si>
-    <t xml:space="preserve">2.07489490509033</t>
+    <t xml:space="preserve">2.07489514350891</t>
   </si>
   <si>
     <t xml:space="preserve">2.1433162689209</t>
   </si>
   <si>
-    <t xml:space="preserve">2.08396315574646</t>
+    <t xml:space="preserve">2.08396291732788</t>
   </si>
   <si>
     <t xml:space="preserve">2.09385514259338</t>
@@ -4886,10 +4886,10 @@
     <t xml:space="preserve">2.09880137443542</t>
   </si>
   <si>
-    <t xml:space="preserve">2.11941027641296</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.10457181930542</t>
+    <t xml:space="preserve">2.11941003799438</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.10457158088684</t>
   </si>
   <si>
     <t xml:space="preserve">2.14991116523743</t>
@@ -4904,13 +4904,13 @@
     <t xml:space="preserve">2.2043182849884</t>
   </si>
   <si>
-    <t xml:space="preserve">2.30159187316895</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.26449632644653</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.25295519828796</t>
+    <t xml:space="preserve">2.30159211158752</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.26449608802795</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.25295543670654</t>
   </si>
   <si>
     <t xml:space="preserve">2.15403294563293</t>
@@ -4919,7 +4919,7 @@
     <t xml:space="preserve">2.17629051208496</t>
   </si>
   <si>
-    <t xml:space="preserve">2.12600469589233</t>
+    <t xml:space="preserve">2.12600493431091</t>
   </si>
   <si>
     <t xml:space="preserve">2.18700695037842</t>
@@ -4931,25 +4931,25 @@
     <t xml:space="preserve">2.19525051116943</t>
   </si>
   <si>
-    <t xml:space="preserve">2.20844006538391</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.22657608985901</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.27026677131653</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.27273964881897</t>
+    <t xml:space="preserve">2.20843982696533</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.22657585144043</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.27026653289795</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.27273941040039</t>
   </si>
   <si>
     <t xml:space="preserve">2.3304443359375</t>
   </si>
   <si>
-    <t xml:space="preserve">2.32220077514648</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.21833205223083</t>
+    <t xml:space="preserve">2.32220053672791</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.21833229064941</t>
   </si>
   <si>
     <t xml:space="preserve">2.00729823112488</t>
@@ -4958,73 +4958,73 @@
     <t xml:space="preserve">2.04027223587036</t>
   </si>
   <si>
-    <t xml:space="preserve">1.89271306991577</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.89683508872986</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.84407639503479</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.87045586109161</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.96195888519287</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.93393075466156</t>
+    <t xml:space="preserve">1.89271318912506</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.89683496952057</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.84407651424408</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.87045562267303</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.96195912361145</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.93393099308014</t>
   </si>
   <si>
     <t xml:space="preserve">1.89848375320435</t>
   </si>
   <si>
-    <t xml:space="preserve">1.82181906700134</t>
+    <t xml:space="preserve">1.82181882858276</t>
   </si>
   <si>
     <t xml:space="preserve">1.84325218200684</t>
   </si>
   <si>
-    <t xml:space="preserve">1.84902250766754</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.89930784702301</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.88776695728302</t>
+    <t xml:space="preserve">1.84902238845825</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.89930772781372</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.88776707649231</t>
   </si>
   <si>
     <t xml:space="preserve">1.8737530708313</t>
   </si>
   <si>
-    <t xml:space="preserve">1.91991674900055</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.91909241676331</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.9487692117691</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.94547152519226</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.9833916425705</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.97679722309113</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.06912469863892</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.079017162323</t>
+    <t xml:space="preserve">1.91991698741913</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.9190925359726</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.94876933097839</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.94547164440155</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.98339188098907</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.97679686546326</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.06912446022034</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.07901692390442</t>
   </si>
   <si>
     <t xml:space="preserve">2.16392493247986</t>
   </si>
   <si>
-    <t xml:space="preserve">2.20102095603943</t>
+    <t xml:space="preserve">2.20102119445801</t>
   </si>
   <si>
     <t xml:space="preserve">2.23069787025452</t>
@@ -5033,13 +5033,13 @@
     <t xml:space="preserve">2.26284718513489</t>
   </si>
   <si>
-    <t xml:space="preserve">2.2537796497345</t>
+    <t xml:space="preserve">2.25377941131592</t>
   </si>
   <si>
     <t xml:space="preserve">2.1020987033844</t>
   </si>
   <si>
-    <t xml:space="preserve">2.18618273735046</t>
+    <t xml:space="preserve">2.18618249893188</t>
   </si>
   <si>
     <t xml:space="preserve">2.09797692298889</t>
@@ -5051,16 +5051,16 @@
     <t xml:space="preserve">2.10045003890991</t>
   </si>
   <si>
-    <t xml:space="preserve">2.06665134429932</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.14908671379089</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.26119899749756</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.25048232078552</t>
+    <t xml:space="preserve">2.0666515827179</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.14908695220947</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.26119875907898</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.25048208236694</t>
   </si>
   <si>
     <t xml:space="preserve">2.2001965045929</t>
@@ -5075,10 +5075,10 @@
     <t xml:space="preserve">2.23481941223145</t>
   </si>
   <si>
-    <t xml:space="preserve">2.22080564498901</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.22575187683105</t>
+    <t xml:space="preserve">2.22080540657043</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.22575163841248</t>
   </si>
   <si>
     <t xml:space="preserve">2.25335788726807</t>
@@ -5090,7 +5090,7 @@
     <t xml:space="preserve">2.13603138923645</t>
   </si>
   <si>
-    <t xml:space="preserve">2.13085532188416</t>
+    <t xml:space="preserve">2.13085508346558</t>
   </si>
   <si>
     <t xml:space="preserve">2.13516855239868</t>
@@ -5099,13 +5099,13 @@
     <t xml:space="preserve">2.12395358085632</t>
   </si>
   <si>
-    <t xml:space="preserve">2.0972101688385</t>
+    <t xml:space="preserve">2.09720993041992</t>
   </si>
   <si>
     <t xml:space="preserve">2.06183958053589</t>
   </si>
   <si>
-    <t xml:space="preserve">2.11618971824646</t>
+    <t xml:space="preserve">2.1161892414093</t>
   </si>
   <si>
     <t xml:space="preserve">2.16363739967346</t>
@@ -5114,10 +5114,10 @@
     <t xml:space="preserve">2.15328526496887</t>
   </si>
   <si>
-    <t xml:space="preserve">2.15846133232117</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.15414810180664</t>
+    <t xml:space="preserve">2.15846157073975</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.15414786338806</t>
   </si>
   <si>
     <t xml:space="preserve">2.15501046180725</t>
@@ -5129,55 +5129,55 @@
     <t xml:space="preserve">2.14465832710266</t>
   </si>
   <si>
-    <t xml:space="preserve">2.14983439445496</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.20073342323303</t>
+    <t xml:space="preserve">2.14983463287354</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.20073366165161</t>
   </si>
   <si>
     <t xml:space="preserve">2.19814538955688</t>
   </si>
   <si>
-    <t xml:space="preserve">2.24559354782104</t>
+    <t xml:space="preserve">2.24559330940247</t>
   </si>
   <si>
     <t xml:space="preserve">2.31288361549377</t>
   </si>
   <si>
-    <t xml:space="preserve">2.34652900695801</t>
+    <t xml:space="preserve">2.34652876853943</t>
   </si>
   <si>
     <t xml:space="preserve">2.37931108474731</t>
   </si>
   <si>
-    <t xml:space="preserve">2.36809611320496</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.31633448600769</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.28614020347595</t>
+    <t xml:space="preserve">2.36809587478638</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.31633424758911</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.28614044189453</t>
   </si>
   <si>
     <t xml:space="preserve">2.32927489280701</t>
   </si>
   <si>
-    <t xml:space="preserve">2.34566617012024</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.37672305107117</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.40001559257507</t>
+    <t xml:space="preserve">2.34566593170166</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.37672328948975</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.40001583099365</t>
   </si>
   <si>
     <t xml:space="preserve">2.42675924301147</t>
   </si>
   <si>
-    <t xml:space="preserve">2.36550784111023</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.35343050956726</t>
+    <t xml:space="preserve">2.36550807952881</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.35343027114868</t>
   </si>
   <si>
     <t xml:space="preserve">2.29908037185669</t>
@@ -5195,31 +5195,31 @@
     <t xml:space="preserve">2.47938370704651</t>
   </si>
   <si>
-    <t xml:space="preserve">2.5337336063385</t>
+    <t xml:space="preserve">2.53373336791992</t>
   </si>
   <si>
     <t xml:space="preserve">2.51302886009216</t>
   </si>
   <si>
-    <t xml:space="preserve">2.56133985519409</t>
+    <t xml:space="preserve">2.56133961677551</t>
   </si>
   <si>
     <t xml:space="preserve">2.55443811416626</t>
   </si>
   <si>
-    <t xml:space="preserve">2.53200817108154</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.58376979827881</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.601886510849</t>
+    <t xml:space="preserve">2.53200793266296</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.58376955986023</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.60188627243042</t>
   </si>
   <si>
     <t xml:space="preserve">2.6208655834198</t>
   </si>
   <si>
-    <t xml:space="preserve">2.6355311870575</t>
+    <t xml:space="preserve">2.63553142547607</t>
   </si>
   <si>
     <t xml:space="preserve">2.73819208145142</t>
@@ -5240,13 +5240,13 @@
     <t xml:space="preserve">2.59325933456421</t>
   </si>
   <si>
-    <t xml:space="preserve">2.48714804649353</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.44660115242004</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.45264029502869</t>
+    <t xml:space="preserve">2.48714780807495</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.44660139083862</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.45264005661011</t>
   </si>
   <si>
     <t xml:space="preserve">2.18434238433838</t>
@@ -5258,46 +5258,46 @@
     <t xml:space="preserve">2.28010129928589</t>
   </si>
   <si>
-    <t xml:space="preserve">2.34048986434937</t>
+    <t xml:space="preserve">2.34049010276794</t>
   </si>
   <si>
     <t xml:space="preserve">2.34911680221558</t>
   </si>
   <si>
-    <t xml:space="preserve">2.31547164916992</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.38276195526123</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.37240958213806</t>
+    <t xml:space="preserve">2.3154718875885</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.38276171684265</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.37240982055664</t>
   </si>
   <si>
     <t xml:space="preserve">2.36895871162415</t>
   </si>
   <si>
-    <t xml:space="preserve">2.3439404964447</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.39656519889832</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.41640734672546</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.43969988822937</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.40519189834595</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.39138889312744</t>
+    <t xml:space="preserve">2.34394073486328</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.39656496047974</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.41640710830688</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.43969964981079</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.40519213676453</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.39138913154602</t>
   </si>
   <si>
     <t xml:space="preserve">2.36464524269104</t>
   </si>
   <si>
-    <t xml:space="preserve">2.26198482513428</t>
+    <t xml:space="preserve">2.2619845867157</t>
   </si>
   <si>
     <t xml:space="preserve">2.23092770576477</t>
@@ -5306,13 +5306,13 @@
     <t xml:space="preserve">2.24904441833496</t>
   </si>
   <si>
-    <t xml:space="preserve">2.31115818023682</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.3879382610321</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.41295623779297</t>
+    <t xml:space="preserve">2.31115794181824</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.38793778419495</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.41295599937439</t>
   </si>
   <si>
     <t xml:space="preserve">2.42589664459229</t>
@@ -5333,10 +5333,10 @@
     <t xml:space="preserve">2.4388370513916</t>
   </si>
   <si>
-    <t xml:space="preserve">2.41123104095459</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.49922585487366</t>
+    <t xml:space="preserve">2.41123080253601</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.49922561645508</t>
   </si>
   <si>
     <t xml:space="preserve">2.46644330024719</t>
@@ -5351,13 +5351,13 @@
     <t xml:space="preserve">2.44142508506775</t>
   </si>
   <si>
-    <t xml:space="preserve">2.51475405693054</t>
+    <t xml:space="preserve">2.51475429534912</t>
   </si>
   <si>
     <t xml:space="preserve">2.3974277973175</t>
   </si>
   <si>
-    <t xml:space="preserve">2.48628497123718</t>
+    <t xml:space="preserve">2.48628544807434</t>
   </si>
   <si>
     <t xml:space="preserve">2.55530071258545</t>
@@ -5366,16 +5366,16 @@
     <t xml:space="preserve">2.53632140159607</t>
   </si>
   <si>
-    <t xml:space="preserve">2.55357551574707</t>
+    <t xml:space="preserve">2.55357527732849</t>
   </si>
   <si>
     <t xml:space="preserve">2.61310124397278</t>
   </si>
   <si>
-    <t xml:space="preserve">2.6381196975708</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.60274887084961</t>
+    <t xml:space="preserve">2.63811945915222</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.60274910926819</t>
   </si>
   <si>
     <t xml:space="preserve">2.46730589866638</t>
@@ -5387,13 +5387,13 @@
     <t xml:space="preserve">2.50440192222595</t>
   </si>
   <si>
-    <t xml:space="preserve">2.52683186531067</t>
+    <t xml:space="preserve">2.52683162689209</t>
   </si>
   <si>
     <t xml:space="preserve">2.51389145851135</t>
   </si>
   <si>
-    <t xml:space="preserve">2.52510666847229</t>
+    <t xml:space="preserve">2.52510643005371</t>
   </si>
   <si>
     <t xml:space="preserve">2.64760899543762</t>
@@ -5405,10 +5405,10 @@
     <t xml:space="preserve">2.70972323417664</t>
   </si>
   <si>
-    <t xml:space="preserve">2.7218005657196</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.75458335876465</t>
+    <t xml:space="preserve">2.72180080413818</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.75458312034607</t>
   </si>
   <si>
     <t xml:space="preserve">2.73301601409912</t>
@@ -5417,22 +5417,22 @@
     <t xml:space="preserve">2.83136296272278</t>
   </si>
   <si>
-    <t xml:space="preserve">2.84171509742737</t>
+    <t xml:space="preserve">2.84171533584595</t>
   </si>
   <si>
     <t xml:space="preserve">3.04444861412048</t>
   </si>
   <si>
-    <t xml:space="preserve">3.02546906471252</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.07291769981384</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.98751091957092</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.00562715530396</t>
+    <t xml:space="preserve">3.0254693031311</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.07291722297668</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.98751068115234</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.00562739372253</t>
   </si>
   <si>
     <t xml:space="preserve">3.05480074882507</t>
@@ -5459,7 +5459,7 @@
     <t xml:space="preserve">2.98319721221924</t>
   </si>
   <si>
-    <t xml:space="preserve">2.95904183387756</t>
+    <t xml:space="preserve">2.95904159545898</t>
   </si>
   <si>
     <t xml:space="preserve">2.98837351799011</t>
@@ -5468,25 +5468,25 @@
     <t xml:space="preserve">2.96766877174377</t>
   </si>
   <si>
-    <t xml:space="preserve">2.95214033126831</t>
+    <t xml:space="preserve">2.95214009284973</t>
   </si>
   <si>
     <t xml:space="preserve">2.97457027435303</t>
   </si>
   <si>
-    <t xml:space="preserve">2.89347696304321</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.91676998138428</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.88053679466248</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.86932134628296</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.70023345947266</t>
+    <t xml:space="preserve">2.89347720146179</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.9167697429657</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.8805365562439</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.86932158470154</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.70023369789124</t>
   </si>
   <si>
     <t xml:space="preserve">2.64070749282837</t>
@@ -5495,7 +5495,7 @@
     <t xml:space="preserve">2.64588356018066</t>
   </si>
   <si>
-    <t xml:space="preserve">2.64502120018005</t>
+    <t xml:space="preserve">2.64502096176147</t>
   </si>
   <si>
     <t xml:space="preserve">2.60619950294495</t>
@@ -5504,34 +5504,34 @@
     <t xml:space="preserve">2.62690448760986</t>
   </si>
   <si>
-    <t xml:space="preserve">2.63035535812378</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.60965061187744</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.61051344871521</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.6890184879303</t>
+    <t xml:space="preserve">2.6303551197052</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.60965085029602</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.61051321029663</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.68901872634888</t>
   </si>
   <si>
     <t xml:space="preserve">2.77356243133545</t>
   </si>
   <si>
-    <t xml:space="preserve">2.82791209220886</t>
+    <t xml:space="preserve">2.82791233062744</t>
   </si>
   <si>
     <t xml:space="preserve">2.82877492904663</t>
   </si>
   <si>
-    <t xml:space="preserve">2.72007536888123</t>
+    <t xml:space="preserve">2.7200756072998</t>
   </si>
   <si>
     <t xml:space="preserve">2.73215317726135</t>
   </si>
   <si>
-    <t xml:space="preserve">2.67952871322632</t>
+    <t xml:space="preserve">2.6795289516449</t>
   </si>
   <si>
     <t xml:space="preserve">2.74681901931763</t>
@@ -5552,7 +5552,7 @@
     <t xml:space="preserve">2.86759614944458</t>
   </si>
   <si>
-    <t xml:space="preserve">2.8486168384552</t>
+    <t xml:space="preserve">2.84861707687378</t>
   </si>
   <si>
     <t xml:space="preserve">2.83826446533203</t>
@@ -5564,10 +5564,10 @@
     <t xml:space="preserve">2.81755995750427</t>
   </si>
   <si>
-    <t xml:space="preserve">2.79858064651489</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.78564023971558</t>
+    <t xml:space="preserve">2.79858040809631</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.78564047813416</t>
   </si>
   <si>
     <t xml:space="preserve">2.86414527893066</t>
@@ -5576,10 +5576,10 @@
     <t xml:space="preserve">2.89433979988098</t>
   </si>
   <si>
-    <t xml:space="preserve">2.87104678153992</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.92712211608887</t>
+    <t xml:space="preserve">2.8710470199585</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.92712187767029</t>
   </si>
   <si>
     <t xml:space="preserve">2.9987256526947</t>
@@ -5594,10 +5594,10 @@
     <t xml:space="preserve">3.04531121253967</t>
   </si>
   <si>
-    <t xml:space="preserve">3.03150820732117</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.06515312194824</t>
+    <t xml:space="preserve">3.03150796890259</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.06515336036682</t>
   </si>
   <si>
     <t xml:space="preserve">3.07981896400452</t>
@@ -5606,13 +5606,13 @@
     <t xml:space="preserve">3.0401349067688</t>
   </si>
   <si>
-    <t xml:space="preserve">3.03323364257812</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.9624924659729</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.07895612716675</t>
+    <t xml:space="preserve">3.03323340415955</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.96249270439148</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.07895636558533</t>
   </si>
   <si>
     <t xml:space="preserve">3.11432671546936</t>
@@ -5627,10 +5627,10 @@
     <t xml:space="preserve">3.23510408401489</t>
   </si>
   <si>
-    <t xml:space="preserve">3.19973349571228</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.19714570045471</t>
+    <t xml:space="preserve">3.19973373413086</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.19714546203613</t>
   </si>
   <si>
     <t xml:space="preserve">3.239417552948</t>
@@ -5639,10 +5639,10 @@
     <t xml:space="preserve">3.28082680702209</t>
   </si>
   <si>
-    <t xml:space="preserve">3.30239415168762</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.30929565429688</t>
+    <t xml:space="preserve">3.3023943901062</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.30929589271545</t>
   </si>
   <si>
     <t xml:space="preserve">3.26788640022278</t>
@@ -5654,25 +5654,25 @@
     <t xml:space="preserve">3.3481171131134</t>
   </si>
   <si>
-    <t xml:space="preserve">3.4499146938324</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.42921042442322</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.41972041130066</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.4671688079834</t>
+    <t xml:space="preserve">3.44991493225098</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.42921018600464</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.41972064971924</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.46716904640198</t>
   </si>
   <si>
     <t xml:space="preserve">3.53618431091309</t>
   </si>
   <si>
-    <t xml:space="preserve">3.63539409637451</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.67076468467712</t>
+    <t xml:space="preserve">3.63539433479309</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.6707649230957</t>
   </si>
   <si>
     <t xml:space="preserve">3.64574646949768</t>
@@ -5684,40 +5684,40 @@
     <t xml:space="preserve">3.72856497764587</t>
   </si>
   <si>
-    <t xml:space="preserve">3.83381390571594</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.74409413337708</t>
+    <t xml:space="preserve">3.83381366729736</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.7440938949585</t>
   </si>
   <si>
     <t xml:space="preserve">3.77860164642334</t>
   </si>
   <si>
-    <t xml:space="preserve">3.76997423171997</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.85969471931458</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.83122563362122</t>
+    <t xml:space="preserve">3.76997447013855</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.85969519615173</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.83122587203979</t>
   </si>
   <si>
     <t xml:space="preserve">3.78981637954712</t>
   </si>
   <si>
-    <t xml:space="preserve">3.83467650413513</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.77083706855774</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.83812713623047</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.68888115882874</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.68715596199036</t>
+    <t xml:space="preserve">3.83467674255371</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.77083683013916</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.83812737464905</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.68888092041016</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.68715620040894</t>
   </si>
   <si>
     <t xml:space="preserve">3.68197965621948</t>
@@ -5726,7 +5726,7 @@
     <t xml:space="preserve">3.63366866111755</t>
   </si>
   <si>
-    <t xml:space="preserve">3.73460412025452</t>
+    <t xml:space="preserve">3.73460388183594</t>
   </si>
   <si>
     <t xml:space="preserve">3.80965852737427</t>
@@ -5735,40 +5735,40 @@
     <t xml:space="preserve">3.80534482002258</t>
   </si>
   <si>
-    <t xml:space="preserve">3.89420247077942</t>
+    <t xml:space="preserve">3.894202709198</t>
   </si>
   <si>
     <t xml:space="preserve">4.02792024612427</t>
   </si>
   <si>
-    <t xml:space="preserve">3.99772548675537</t>
+    <t xml:space="preserve">3.99772572517395</t>
   </si>
   <si>
     <t xml:space="preserve">4.07450580596924</t>
   </si>
   <si>
-    <t xml:space="preserve">4.12712955474854</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.15646171569824</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.21943807601929</t>
+    <t xml:space="preserve">4.12713003158569</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.15646123886108</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.21943759918213</t>
   </si>
   <si>
     <t xml:space="preserve">4.25394630432129</t>
   </si>
   <si>
-    <t xml:space="preserve">4.12885522842407</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.1754412651062</t>
+    <t xml:space="preserve">4.12885475158691</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.17544078826904</t>
   </si>
   <si>
     <t xml:space="preserve">4.25653409957886</t>
   </si>
   <si>
-    <t xml:space="preserve">4.23237943649292</t>
+    <t xml:space="preserve">4.2323784828186</t>
   </si>
   <si>
     <t xml:space="preserve">4.10642576217651</t>
@@ -5786,19 +5786,19 @@
     <t xml:space="preserve">4.32382440567017</t>
   </si>
   <si>
-    <t xml:space="preserve">4.46013021469116</t>
+    <t xml:space="preserve">4.460129737854</t>
   </si>
   <si>
     <t xml:space="preserve">4.56710433959961</t>
   </si>
   <si>
-    <t xml:space="preserve">4.46925067901611</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.44730186462402</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.38420057296753</t>
+    <t xml:space="preserve">4.46925115585327</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.44730234146118</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.38420104980469</t>
   </si>
   <si>
     <t xml:space="preserve">4.41072130203247</t>
@@ -5810,7 +5810,7 @@
     <t xml:space="preserve">4.40066146850586</t>
   </si>
   <si>
-    <t xml:space="preserve">4.48205423355103</t>
+    <t xml:space="preserve">4.48205375671387</t>
   </si>
   <si>
     <t xml:space="preserve">4.39425992965698</t>
@@ -5819,19 +5819,19 @@
     <t xml:space="preserve">4.52137804031372</t>
   </si>
   <si>
-    <t xml:space="preserve">4.5094895362854</t>
+    <t xml:space="preserve">4.50949001312256</t>
   </si>
   <si>
     <t xml:space="preserve">4.51772022247314</t>
   </si>
   <si>
-    <t xml:space="preserve">4.37505531311035</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.35310697555542</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.47107982635498</t>
+    <t xml:space="preserve">4.37505483627319</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.35310745239258</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.47107934951782</t>
   </si>
   <si>
     <t xml:space="preserve">4.49760103225708</t>
@@ -5840,7 +5840,7 @@
     <t xml:space="preserve">4.43724250793457</t>
   </si>
   <si>
-    <t xml:space="preserve">4.27720165252686</t>
+    <t xml:space="preserve">4.27720212936401</t>
   </si>
   <si>
     <t xml:space="preserve">4.26805686950684</t>
@@ -5870,13 +5870,13 @@
     <t xml:space="preserve">4.4098072052002</t>
   </si>
   <si>
-    <t xml:space="preserve">4.39243078231812</t>
+    <t xml:space="preserve">4.39243125915527</t>
   </si>
   <si>
     <t xml:space="preserve">4.44181489944458</t>
   </si>
   <si>
-    <t xml:space="preserve">4.38968753814697</t>
+    <t xml:space="preserve">4.38968801498413</t>
   </si>
   <si>
     <t xml:space="preserve">4.3174409866333</t>
@@ -5891,7 +5891,7 @@
     <t xml:space="preserve">4.61283016204834</t>
   </si>
   <si>
-    <t xml:space="preserve">4.70611047744751</t>
+    <t xml:space="preserve">4.70611095428467</t>
   </si>
   <si>
     <t xml:space="preserve">4.64575290679932</t>
@@ -5900,13 +5900,13 @@
     <t xml:space="preserve">4.84145975112915</t>
   </si>
   <si>
-    <t xml:space="preserve">4.79939222335815</t>
+    <t xml:space="preserve">4.799391746521</t>
   </si>
   <si>
     <t xml:space="preserve">4.82134008407593</t>
   </si>
   <si>
-    <t xml:space="preserve">4.75549459457397</t>
+    <t xml:space="preserve">4.75549507141113</t>
   </si>
   <si>
     <t xml:space="preserve">4.7335467338562</t>
@@ -5915,13 +5915,13 @@
     <t xml:space="preserve">4.68782043457031</t>
   </si>
   <si>
-    <t xml:space="preserve">4.75183725357056</t>
+    <t xml:space="preserve">4.7518367767334</t>
   </si>
   <si>
     <t xml:space="preserve">4.77744340896606</t>
   </si>
   <si>
-    <t xml:space="preserve">4.80305004119873</t>
+    <t xml:space="preserve">4.80304956436157</t>
   </si>
   <si>
     <t xml:space="preserve">4.81768226623535</t>
@@ -5930,7 +5930,7 @@
     <t xml:space="preserve">4.98046636581421</t>
   </si>
   <si>
-    <t xml:space="preserve">4.96217632293701</t>
+    <t xml:space="preserve">4.96217584609985</t>
   </si>
   <si>
     <t xml:space="preserve">5.03533744812012</t>
@@ -5960,13 +5960,13 @@
     <t xml:space="preserve">4.27354383468628</t>
   </si>
   <si>
-    <t xml:space="preserve">4.32109880447388</t>
+    <t xml:space="preserve">4.32109832763672</t>
   </si>
   <si>
     <t xml:space="preserve">4.34121799468994</t>
   </si>
   <si>
-    <t xml:space="preserve">4.36956834793091</t>
+    <t xml:space="preserve">4.36956787109375</t>
   </si>
   <si>
     <t xml:space="preserve">4.35767936706543</t>
@@ -5987,7 +5987,7 @@
     <t xml:space="preserve">4.51497650146484</t>
   </si>
   <si>
-    <t xml:space="preserve">4.53052377700806</t>
+    <t xml:space="preserve">4.5305233001709</t>
   </si>
   <si>
     <t xml:space="preserve">4.51040410995483</t>
@@ -5996,28 +5996,28 @@
     <t xml:space="preserve">4.56618976593018</t>
   </si>
   <si>
-    <t xml:space="preserve">4.52686548233032</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.5543007850647</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.5360107421875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.62746238708496</t>
+    <t xml:space="preserve">4.52686500549316</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.55430126190186</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.53601026535034</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.6274619102478</t>
   </si>
   <si>
     <t xml:space="preserve">4.61831712722778</t>
   </si>
   <si>
-    <t xml:space="preserve">4.48662710189819</t>
+    <t xml:space="preserve">4.48662662506104</t>
   </si>
   <si>
     <t xml:space="preserve">4.46559238433838</t>
   </si>
   <si>
-    <t xml:space="preserve">4.49485683441162</t>
+    <t xml:space="preserve">4.49485731124878</t>
   </si>
   <si>
     <t xml:space="preserve">4.39700365066528</t>
@@ -6038,10 +6038,10 @@
     <t xml:space="preserve">4.46284914016724</t>
   </si>
   <si>
-    <t xml:space="preserve">4.53692531585693</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.54972791671753</t>
+    <t xml:space="preserve">4.53692483901978</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.54972839355469</t>
   </si>
   <si>
     <t xml:space="preserve">4.5122332572937</t>
@@ -6065,10 +6065,10 @@
     <t xml:space="preserve">4.4674220085144</t>
   </si>
   <si>
-    <t xml:space="preserve">4.67867565155029</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.7756142616272</t>
+    <t xml:space="preserve">4.67867517471313</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.77561473846436</t>
   </si>
   <si>
     <t xml:space="preserve">4.82499837875366</t>
@@ -6077,16 +6077,16 @@
     <t xml:space="preserve">4.86523723602295</t>
   </si>
   <si>
-    <t xml:space="preserve">5.26579618453979</t>
+    <t xml:space="preserve">5.26579570770264</t>
   </si>
   <si>
     <t xml:space="preserve">5.36639308929443</t>
   </si>
   <si>
-    <t xml:space="preserve">5.33529996871948</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.34078645706177</t>
+    <t xml:space="preserve">5.33529949188232</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.34078693389893</t>
   </si>
   <si>
     <t xml:space="preserve">5.33164167404175</t>
@@ -6098,7 +6098,7 @@
     <t xml:space="preserve">5.35541868209839</t>
   </si>
   <si>
-    <t xml:space="preserve">5.27677059173584</t>
+    <t xml:space="preserve">5.27677011489868</t>
   </si>
   <si>
     <t xml:space="preserve">5.22738647460938</t>
@@ -6140,10 +6140,10 @@
     <t xml:space="preserve">5.46516084671021</t>
   </si>
   <si>
-    <t xml:space="preserve">5.22555780410767</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.36456441879272</t>
+    <t xml:space="preserve">5.22555732727051</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.36456394195557</t>
   </si>
   <si>
     <t xml:space="preserve">5.3682222366333</t>
@@ -6152,13 +6152,13 @@
     <t xml:space="preserve">5.47430658340454</t>
   </si>
   <si>
-    <t xml:space="preserve">5.55112552642822</t>
+    <t xml:space="preserve">5.55112600326538</t>
   </si>
   <si>
     <t xml:space="preserve">5.43223857879639</t>
   </si>
   <si>
-    <t xml:space="preserve">5.55844163894653</t>
+    <t xml:space="preserve">5.55844211578369</t>
   </si>
   <si>
     <t xml:space="preserve">5.44504165649414</t>
@@ -6167,16 +6167,16 @@
     <t xml:space="preserve">5.4395546913147</t>
   </si>
   <si>
-    <t xml:space="preserve">5.42675161361694</t>
+    <t xml:space="preserve">5.42675113677979</t>
   </si>
   <si>
     <t xml:space="preserve">5.34444427490234</t>
   </si>
   <si>
-    <t xml:space="preserve">5.24933433532715</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.19812154769897</t>
+    <t xml:space="preserve">5.24933481216431</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.19812202453613</t>
   </si>
   <si>
     <t xml:space="preserve">5.23287343978882</t>
@@ -6194,7 +6194,7 @@
     <t xml:space="preserve">5.54380941390991</t>
   </si>
   <si>
-    <t xml:space="preserve">5.38651275634766</t>
+    <t xml:space="preserve">5.3865122795105</t>
   </si>
   <si>
     <t xml:space="preserve">5.29323148727417</t>
@@ -6218,19 +6218,19 @@
     <t xml:space="preserve">5.68098735809326</t>
   </si>
   <si>
-    <t xml:space="preserve">5.54929685592651</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.50174140930176</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.48162269592285</t>
+    <t xml:space="preserve">5.54929637908936</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.50174188613892</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.48162221908569</t>
   </si>
   <si>
     <t xml:space="preserve">5.53100633621216</t>
   </si>
   <si>
-    <t xml:space="preserve">5.60965442657471</t>
+    <t xml:space="preserve">5.60965490341187</t>
   </si>
   <si>
     <t xml:space="preserve">5.44687032699585</t>
@@ -6290,7 +6290,7 @@
     <t xml:space="preserve">6.12361431121826</t>
   </si>
   <si>
-    <t xml:space="preserve">6.03947830200195</t>
+    <t xml:space="preserve">6.03947877883911</t>
   </si>
   <si>
     <t xml:space="preserve">6.03033304214478</t>
@@ -6305,13 +6305,13 @@
     <t xml:space="preserve">6.30285978317261</t>
   </si>
   <si>
-    <t xml:space="preserve">5.82548093795776</t>
+    <t xml:space="preserve">5.82548141479492</t>
   </si>
   <si>
     <t xml:space="preserve">5.73220062255859</t>
   </si>
   <si>
-    <t xml:space="preserve">5.87852334976196</t>
+    <t xml:space="preserve">5.8785228729248</t>
   </si>
   <si>
     <t xml:space="preserve">5.90230083465576</t>
@@ -6323,7 +6323,7 @@
     <t xml:space="preserve">5.84742975234985</t>
   </si>
   <si>
-    <t xml:space="preserve">6.04679441452026</t>
+    <t xml:space="preserve">6.04679489135742</t>
   </si>
   <si>
     <t xml:space="preserve">6.13641738891602</t>
@@ -6338,7 +6338,7 @@
     <t xml:space="preserve">6.22055339813232</t>
   </si>
   <si>
-    <t xml:space="preserve">6.36321830749512</t>
+    <t xml:space="preserve">6.36321783065796</t>
   </si>
   <si>
     <t xml:space="preserve">6.48942184448242</t>
@@ -6356,7 +6356,7 @@
     <t xml:space="preserve">6.85157060623169</t>
   </si>
   <si>
-    <t xml:space="preserve">6.5607533454895</t>
+    <t xml:space="preserve">6.56075382232666</t>
   </si>
   <si>
     <t xml:space="preserve">6.77475118637085</t>
@@ -6392,19 +6392,19 @@
     <t xml:space="preserve">6.91375780105591</t>
   </si>
   <si>
-    <t xml:space="preserve">6.95765447616577</t>
+    <t xml:space="preserve">6.95765495300293</t>
   </si>
   <si>
     <t xml:space="preserve">7.01618385314941</t>
   </si>
   <si>
-    <t xml:space="preserve">7.1094651222229</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.08020067214966</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.00520944595337</t>
+    <t xml:space="preserve">7.10946464538574</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.0802001953125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.00520992279053</t>
   </si>
   <si>
     <t xml:space="preserve">6.82413530349731</t>
@@ -6434,13 +6434,13 @@
     <t xml:space="preserve">5.67915821075439</t>
   </si>
   <si>
-    <t xml:space="preserve">5.88766860961914</t>
+    <t xml:space="preserve">5.8876690864563</t>
   </si>
   <si>
     <t xml:space="preserve">6.05959796905518</t>
   </si>
   <si>
-    <t xml:space="preserve">6.16019487380981</t>
+    <t xml:space="preserve">6.16019535064697</t>
   </si>
   <si>
     <t xml:space="preserve">6.06874322891235</t>
@@ -6467,16 +6467,16 @@
     <t xml:space="preserve">6.72902488708496</t>
   </si>
   <si>
-    <t xml:space="preserve">6.76377725601196</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.71622228622437</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.94668054580688</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.17165231704712</t>
+    <t xml:space="preserve">6.7637767791748</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.71622180938721</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.94668102264404</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.17165184020996</t>
   </si>
   <si>
     <t xml:space="preserve">7.17713928222656</t>
@@ -6485,7 +6485,7 @@
     <t xml:space="preserve">7.26859092712402</t>
   </si>
   <si>
-    <t xml:space="preserve">7.28505277633667</t>
+    <t xml:space="preserve">7.28505229949951</t>
   </si>
   <si>
     <t xml:space="preserve">7.20091676712036</t>
@@ -6906,6 +6906,9 @@
   </si>
   <si>
     <t xml:space="preserve">11.3999996185303</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.4700002670288</t>
   </si>
 </sst>
 </file>
@@ -73154,7 +73157,7 @@
     </row>
     <row r="2536">
       <c r="A2536" s="1" t="n">
-        <v>46009.6912037037</v>
+        <v>46009.3333333333</v>
       </c>
       <c r="B2536" t="n">
         <v>13875134</v>
@@ -73175,6 +73178,32 @@
         <v>2297</v>
       </c>
       <c r="H2536" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2537">
+      <c r="A2537" s="1" t="n">
+        <v>46010.6921296296</v>
+      </c>
+      <c r="B2537" t="n">
+        <v>26830051</v>
+      </c>
+      <c r="C2537" t="n">
+        <v>11.5100002288818</v>
+      </c>
+      <c r="D2537" t="n">
+        <v>11.3599996566772</v>
+      </c>
+      <c r="E2537" t="n">
+        <v>11.4499998092651</v>
+      </c>
+      <c r="F2537" t="n">
+        <v>11.4700002670288</v>
+      </c>
+      <c r="G2537" t="s">
+        <v>2298</v>
+      </c>
+      <c r="H2537" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/BPE.MI.xlsx
+++ b/data/BPE.MI.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2304" uniqueCount="2304">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2305" uniqueCount="2305">
   <si>
     <t xml:space="preserve">date</t>
   </si>
@@ -38,58 +38,58 @@
     <t xml:space="preserve">ticker</t>
   </si>
   <si>
-    <t xml:space="preserve">3.1975109577179</t>
+    <t xml:space="preserve">3.19751143455505</t>
   </si>
   <si>
     <t xml:space="preserve">BPE.MI</t>
   </si>
   <si>
-    <t xml:space="preserve">3.23759841918945</t>
+    <t xml:space="preserve">3.23759794235229</t>
   </si>
   <si>
     <t xml:space="preserve">3.09375715255737</t>
   </si>
   <si>
-    <t xml:space="preserve">3.02301573753357</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.95463228225708</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.95699024200439</t>
+    <t xml:space="preserve">3.02301549911499</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.95463156700134</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.95699048042297</t>
   </si>
   <si>
     <t xml:space="preserve">2.93340945243835</t>
   </si>
   <si>
-    <t xml:space="preserve">3.07489252090454</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.91690373420715</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.66223430633545</t>
+    <t xml:space="preserve">3.07489204406738</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.91690397262573</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.66223454475403</t>
   </si>
   <si>
     <t xml:space="preserve">2.6504442691803</t>
   </si>
   <si>
-    <t xml:space="preserve">2.45708465576172</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.72825980186462</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.69760513305664</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.62686395645142</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.78013730049133</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.66695046424866</t>
+    <t xml:space="preserve">2.45708417892456</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.7282600402832</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.69760489463806</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.62686371803284</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.78013706207275</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.66695070266724</t>
   </si>
   <si>
     <t xml:space="preserve">2.46651697158813</t>
@@ -98,13 +98,13 @@
     <t xml:space="preserve">2.59385085105896</t>
   </si>
   <si>
-    <t xml:space="preserve">2.53018379211426</t>
+    <t xml:space="preserve">2.53018403053284</t>
   </si>
   <si>
     <t xml:space="preserve">2.35804653167725</t>
   </si>
   <si>
-    <t xml:space="preserve">2.16279983520508</t>
+    <t xml:space="preserve">2.16280007362366</t>
   </si>
   <si>
     <t xml:space="preserve">2.17128896713257</t>
@@ -116,58 +116,58 @@
     <t xml:space="preserve">1.87228894233704</t>
   </si>
   <si>
-    <t xml:space="preserve">1.83173072338104</t>
+    <t xml:space="preserve">1.83173060417175</t>
   </si>
   <si>
     <t xml:space="preserve">1.95812177658081</t>
   </si>
   <si>
-    <t xml:space="preserve">1.77042126655579</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.97415626049042</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.17411875724792</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.27975916862488</t>
+    <t xml:space="preserve">1.77042090892792</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.974156498909</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.17411828041077</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.2797589302063</t>
   </si>
   <si>
     <t xml:space="preserve">2.33446645736694</t>
   </si>
   <si>
-    <t xml:space="preserve">2.32031774520874</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.18166470527649</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.40284991264343</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.31182861328125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.16468667984009</t>
+    <t xml:space="preserve">2.32031750679016</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.18166494369507</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.40284967422485</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.31182885169983</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.16468691825867</t>
   </si>
   <si>
     <t xml:space="preserve">2.21845006942749</t>
   </si>
   <si>
-    <t xml:space="preserve">2.2599515914917</t>
+    <t xml:space="preserve">2.25995206832886</t>
   </si>
   <si>
     <t xml:space="preserve">2.22128009796143</t>
   </si>
   <si>
-    <t xml:space="preserve">2.25429201126099</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.36512088775635</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.32409048080444</t>
+    <t xml:space="preserve">2.25429224967957</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.36512064933777</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.3240909576416</t>
   </si>
   <si>
     <t xml:space="preserve">2.33352279663086</t>
@@ -176,13 +176,13 @@
     <t xml:space="preserve">2.21279048919678</t>
   </si>
   <si>
-    <t xml:space="preserve">2.18072175979614</t>
+    <t xml:space="preserve">2.18072128295898</t>
   </si>
   <si>
     <t xml:space="preserve">2.20524525642395</t>
   </si>
   <si>
-    <t xml:space="preserve">2.22505259513855</t>
+    <t xml:space="preserve">2.22505283355713</t>
   </si>
   <si>
     <t xml:space="preserve">2.40992331504822</t>
@@ -191,13 +191,13 @@
     <t xml:space="preserve">2.44293618202209</t>
   </si>
   <si>
-    <t xml:space="preserve">2.36276197433472</t>
+    <t xml:space="preserve">2.36276245117188</t>
   </si>
   <si>
     <t xml:space="preserve">2.20241475105286</t>
   </si>
   <si>
-    <t xml:space="preserve">2.22693920135498</t>
+    <t xml:space="preserve">2.2269389629364</t>
   </si>
   <si>
     <t xml:space="preserve">2.24674654006958</t>
@@ -209,10 +209,10 @@
     <t xml:space="preserve">2.20807456970215</t>
   </si>
   <si>
-    <t xml:space="preserve">2.14770865440369</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.05904603004456</t>
+    <t xml:space="preserve">2.14770913124084</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.05904626846313</t>
   </si>
   <si>
     <t xml:space="preserve">2.03829503059387</t>
@@ -221,43 +221,43 @@
     <t xml:space="preserve">1.9732129573822</t>
   </si>
   <si>
-    <t xml:space="preserve">2.00905561447144</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.89492619037628</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.88455057144165</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.77325093746185</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.02697658538818</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.12507176399231</t>
+    <t xml:space="preserve">2.00905585289001</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.89492630958557</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.88455009460449</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.77325046062469</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.02697682380676</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.12507152557373</t>
   </si>
   <si>
     <t xml:space="preserve">2.04018187522888</t>
   </si>
   <si>
-    <t xml:space="preserve">2.27410006523132</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.37691116333008</t>
+    <t xml:space="preserve">2.2741003036499</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.3769109249115</t>
   </si>
   <si>
     <t xml:space="preserve">2.38398480415344</t>
   </si>
   <si>
-    <t xml:space="preserve">2.30428314208984</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.37219452857971</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.44765162467957</t>
+    <t xml:space="preserve">2.30428290367126</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.37219476699829</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.44765210151672</t>
   </si>
   <si>
     <t xml:space="preserve">2.45944213867188</t>
@@ -266,7 +266,7 @@
     <t xml:space="preserve">2.37455272674561</t>
   </si>
   <si>
-    <t xml:space="preserve">2.45236825942993</t>
+    <t xml:space="preserve">2.45236802101135</t>
   </si>
   <si>
     <t xml:space="preserve">2.41463994979858</t>
@@ -275,10 +275,10 @@
     <t xml:space="preserve">2.50896120071411</t>
   </si>
   <si>
-    <t xml:space="preserve">2.40756559371948</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.31937456130981</t>
+    <t xml:space="preserve">2.4075653553009</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.31937432289124</t>
   </si>
   <si>
     <t xml:space="preserve">2.21750688552856</t>
@@ -287,28 +287,28 @@
     <t xml:space="preserve">2.19298362731934</t>
   </si>
   <si>
-    <t xml:space="preserve">2.13167381286621</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.07602405548096</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.07036447525024</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.06470584869385</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.0326361656189</t>
+    <t xml:space="preserve">2.13167405128479</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.07602381706238</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.07036471366882</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.06470537185669</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.03263640403748</t>
   </si>
   <si>
     <t xml:space="preserve">2.02980589866638</t>
   </si>
   <si>
-    <t xml:space="preserve">2.06093287467957</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.17506170272827</t>
+    <t xml:space="preserve">2.06093311309814</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.17506194114685</t>
   </si>
   <si>
     <t xml:space="preserve">2.07319474220276</t>
@@ -317,37 +317,37 @@
     <t xml:space="preserve">2.09960460662842</t>
   </si>
   <si>
-    <t xml:space="preserve">2.05811405181885</t>
+    <t xml:space="preserve">2.05811429023743</t>
   </si>
   <si>
     <t xml:space="preserve">2.22021532058716</t>
   </si>
   <si>
-    <t xml:space="preserve">2.33117818832397</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.28582835197449</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.29161810874939</t>
+    <t xml:space="preserve">2.3311779499054</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.28582811355591</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.29161763191223</t>
   </si>
   <si>
     <t xml:space="preserve">2.31381058692932</t>
   </si>
   <si>
-    <t xml:space="preserve">2.19416403770447</t>
+    <t xml:space="preserve">2.19416379928589</t>
   </si>
   <si>
     <t xml:space="preserve">2.16618227958679</t>
   </si>
   <si>
-    <t xml:space="preserve">2.07934188842773</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.06969285011292</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.09670925140381</t>
+    <t xml:space="preserve">2.07934165000916</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.06969261169434</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.09670901298523</t>
   </si>
   <si>
     <t xml:space="preserve">2.13627028465271</t>
@@ -356,22 +356,22 @@
     <t xml:space="preserve">1.99636089801788</t>
   </si>
   <si>
-    <t xml:space="preserve">1.87478423118591</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.82171535491943</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.81592643260956</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.76864624023438</t>
+    <t xml:space="preserve">1.87478399276733</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.82171511650085</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.81592607498169</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.7686460018158</t>
   </si>
   <si>
     <t xml:space="preserve">1.9442572593689</t>
   </si>
   <si>
-    <t xml:space="preserve">2.03206157684326</t>
+    <t xml:space="preserve">2.03206181526184</t>
   </si>
   <si>
     <t xml:space="preserve">2.0841658115387</t>
@@ -380,19 +380,19 @@
     <t xml:space="preserve">2.07548236846924</t>
   </si>
   <si>
-    <t xml:space="preserve">2.23468947410583</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.68470096588135</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.66733288764954</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.62777185440063</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.53900194168091</t>
+    <t xml:space="preserve">2.23468923568726</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.68470084667206</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.66733300685883</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.62777209281921</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.5390020608902</t>
   </si>
   <si>
     <t xml:space="preserve">1.58145749568939</t>
@@ -401,67 +401,67 @@
     <t xml:space="preserve">1.50523054599762</t>
   </si>
   <si>
-    <t xml:space="preserve">1.40391719341278</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.40488243103027</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.30453324317932</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.24567461013794</t>
+    <t xml:space="preserve">1.40391731262207</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.40488219261169</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.30453336238861</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.24567472934723</t>
   </si>
   <si>
     <t xml:space="preserve">1.44733703136444</t>
   </si>
   <si>
-    <t xml:space="preserve">1.51487994194031</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.63838589191437</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.55637013912201</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.62294816970825</t>
+    <t xml:space="preserve">1.51487982273102</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.63838601112366</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.5563702583313</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.62294805049896</t>
   </si>
   <si>
     <t xml:space="preserve">1.64224553108215</t>
   </si>
   <si>
-    <t xml:space="preserve">1.65189456939697</t>
+    <t xml:space="preserve">1.65189445018768</t>
   </si>
   <si>
     <t xml:space="preserve">1.63645589351654</t>
   </si>
   <si>
-    <t xml:space="preserve">1.65382397174835</t>
+    <t xml:space="preserve">1.65382409095764</t>
   </si>
   <si>
     <t xml:space="preserve">1.70689308643341</t>
   </si>
   <si>
-    <t xml:space="preserve">1.69434928894043</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.64899957180023</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.65671873092651</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.73294544219971</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.67891120910645</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.77057611942291</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.67022776603699</t>
+    <t xml:space="preserve">1.6943496465683</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.64899945259094</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.65671861171722</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.73294520378113</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.67891108989716</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.7705762386322</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.67022752761841</t>
   </si>
   <si>
     <t xml:space="preserve">1.46374034881592</t>
@@ -479,46 +479,46 @@
     <t xml:space="preserve">1.6982090473175</t>
   </si>
   <si>
-    <t xml:space="preserve">1.73198056221008</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.72136700153351</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.72040176391602</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.69627964496613</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.68373596668243</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.62101769447327</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.64996469020844</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.55444014072418</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.56505453586578</t>
+    <t xml:space="preserve">1.73198044300079</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.72136688232422</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.72040188312531</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.69627976417542</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.68373608589172</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.62101781368256</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.64996457099915</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.55444025993347</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.56505441665649</t>
   </si>
   <si>
     <t xml:space="preserve">1.65478920936584</t>
   </si>
   <si>
-    <t xml:space="preserve">1.69049000740051</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.64128065109253</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.60750901699066</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.65285897254944</t>
+    <t xml:space="preserve">1.69048964977264</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.64128053188324</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.60750913619995</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.65285909175873</t>
   </si>
   <si>
     <t xml:space="preserve">1.66443824768066</t>
@@ -530,19 +530,19 @@
     <t xml:space="preserve">1.71847188472748</t>
   </si>
   <si>
-    <t xml:space="preserve">1.68759560585022</t>
+    <t xml:space="preserve">1.68759548664093</t>
   </si>
   <si>
     <t xml:space="preserve">1.7445240020752</t>
   </si>
   <si>
-    <t xml:space="preserve">1.74741864204407</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.71268248558044</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.67987656593323</t>
+    <t xml:space="preserve">1.74741852283478</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.71268272399902</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.67987632751465</t>
   </si>
   <si>
     <t xml:space="preserve">1.63549149036407</t>
@@ -551,10 +551,10 @@
     <t xml:space="preserve">1.58049249649048</t>
   </si>
   <si>
-    <t xml:space="preserve">1.60461449623108</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.53610742092133</t>
+    <t xml:space="preserve">1.60461461544037</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.53610777854919</t>
   </si>
   <si>
     <t xml:space="preserve">1.60847413539886</t>
@@ -563,79 +563,79 @@
     <t xml:space="preserve">1.61233353614807</t>
   </si>
   <si>
-    <t xml:space="preserve">1.53996694087982</t>
+    <t xml:space="preserve">1.5399671792984</t>
   </si>
   <si>
     <t xml:space="preserve">1.51584494113922</t>
   </si>
   <si>
-    <t xml:space="preserve">1.54961597919464</t>
+    <t xml:space="preserve">1.54961621761322</t>
   </si>
   <si>
     <t xml:space="preserve">1.55251085758209</t>
   </si>
   <si>
-    <t xml:space="preserve">1.59786057472229</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.56119477748871</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.63452661037445</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.63935124874115</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.61619329452515</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.67408680915833</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.7754008769989</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.81496143341064</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.73583984375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.82653999328613</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.86513578891754</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.96066009998322</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.05425477027893</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.04942989349365</t>
+    <t xml:space="preserve">1.59786069393158</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.56119465827942</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.63452637195587</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.63935101032257</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.61619317531586</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.67408668994904</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.77540111541748</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.81496107578278</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.73583972454071</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.82653975486755</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.86513566970825</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.96065986156464</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.05425453186035</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.04942965507507</t>
   </si>
   <si>
     <t xml:space="preserve">2.10153388977051</t>
   </si>
   <si>
-    <t xml:space="preserve">2.01372957229614</t>
+    <t xml:space="preserve">2.01372909545898</t>
   </si>
   <si>
     <t xml:space="preserve">2.04653573036194</t>
   </si>
   <si>
-    <t xml:space="preserve">2.09477972984314</t>
+    <t xml:space="preserve">2.09477949142456</t>
   </si>
   <si>
     <t xml:space="preserve">2.08899021148682</t>
   </si>
   <si>
-    <t xml:space="preserve">2.06197381019592</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.04460549354553</t>
+    <t xml:space="preserve">2.06197333335876</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.04460573196411</t>
   </si>
   <si>
     <t xml:space="preserve">1.9297833442688</t>
@@ -647,10 +647,10 @@
     <t xml:space="preserve">1.88443338871002</t>
   </si>
   <si>
-    <t xml:space="preserve">1.9500458240509</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.98671162128448</t>
+    <t xml:space="preserve">1.95004558563232</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.98671185970306</t>
   </si>
   <si>
     <t xml:space="preserve">2.01565885543823</t>
@@ -659,13 +659,13 @@
     <t xml:space="preserve">2.01662373542786</t>
   </si>
   <si>
-    <t xml:space="preserve">1.99539613723755</t>
+    <t xml:space="preserve">1.99539589881897</t>
   </si>
   <si>
     <t xml:space="preserve">1.98574686050415</t>
   </si>
   <si>
-    <t xml:space="preserve">1.92785322666168</t>
+    <t xml:space="preserve">1.92785334587097</t>
   </si>
   <si>
     <t xml:space="preserve">1.84583747386932</t>
@@ -674,10 +674,10 @@
     <t xml:space="preserve">1.80820727348328</t>
   </si>
   <si>
-    <t xml:space="preserve">1.80048751831055</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.83715379238129</t>
+    <t xml:space="preserve">1.80048727989197</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.83715403079987</t>
   </si>
   <si>
     <t xml:space="preserve">1.82750475406647</t>
@@ -686,13 +686,13 @@
     <t xml:space="preserve">1.83329391479492</t>
   </si>
   <si>
-    <t xml:space="preserve">1.80531179904938</t>
+    <t xml:space="preserve">1.80531167984009</t>
   </si>
   <si>
     <t xml:space="preserve">1.82847011089325</t>
   </si>
   <si>
-    <t xml:space="preserve">1.97513341903687</t>
+    <t xml:space="preserve">1.97513318061829</t>
   </si>
   <si>
     <t xml:space="preserve">1.93557286262512</t>
@@ -701,28 +701,28 @@
     <t xml:space="preserve">2.06679821014404</t>
   </si>
   <si>
-    <t xml:space="preserve">2.28196859359741</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.31477475166321</t>
+    <t xml:space="preserve">2.28196835517883</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.31477499008179</t>
   </si>
   <si>
     <t xml:space="preserve">2.27907419204712</t>
   </si>
   <si>
-    <t xml:space="preserve">2.32152962684631</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.3707389831543</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.33214330673218</t>
+    <t xml:space="preserve">2.32152986526489</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.37073922157288</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.3321430683136</t>
   </si>
   <si>
     <t xml:space="preserve">2.39486122131348</t>
   </si>
   <si>
-    <t xml:space="preserve">2.41464161872864</t>
+    <t xml:space="preserve">2.41464138031006</t>
   </si>
   <si>
     <t xml:space="preserve">2.39775538444519</t>
@@ -731,13 +731,13 @@
     <t xml:space="preserve">2.41222929954529</t>
   </si>
   <si>
-    <t xml:space="preserve">2.46529841423035</t>
+    <t xml:space="preserve">2.46529817581177</t>
   </si>
   <si>
     <t xml:space="preserve">2.48942065238953</t>
   </si>
   <si>
-    <t xml:space="preserve">2.49665713310242</t>
+    <t xml:space="preserve">2.49665689468384</t>
   </si>
   <si>
     <t xml:space="preserve">2.44117617607117</t>
@@ -749,19 +749,19 @@
     <t xml:space="preserve">2.63897848129272</t>
   </si>
   <si>
-    <t xml:space="preserve">2.59555864334106</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.55696249008179</t>
+    <t xml:space="preserve">2.59555888175964</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.55696272850037</t>
   </si>
   <si>
     <t xml:space="preserve">2.42911505699158</t>
   </si>
   <si>
-    <t xml:space="preserve">2.41705298423767</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.56178712844849</t>
+    <t xml:space="preserve">2.41705346107483</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.56178736686707</t>
   </si>
   <si>
     <t xml:space="preserve">2.53766489028931</t>
@@ -770,10 +770,10 @@
     <t xml:space="preserve">2.5786726474762</t>
   </si>
   <si>
-    <t xml:space="preserve">2.58832168579102</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.72823119163513</t>
+    <t xml:space="preserve">2.58832192420959</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.72823143005371</t>
   </si>
   <si>
     <t xml:space="preserve">2.77165126800537</t>
@@ -788,28 +788,28 @@
     <t xml:space="preserve">2.74752902984619</t>
   </si>
   <si>
-    <t xml:space="preserve">2.70410919189453</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.57626080513</t>
+    <t xml:space="preserve">2.70410943031311</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.57626104354858</t>
   </si>
   <si>
     <t xml:space="preserve">2.52801585197449</t>
   </si>
   <si>
-    <t xml:space="preserve">2.58590936660767</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.59797048568726</t>
+    <t xml:space="preserve">2.58590912818909</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.59797072410583</t>
   </si>
   <si>
     <t xml:space="preserve">2.66068863868713</t>
   </si>
   <si>
-    <t xml:space="preserve">2.50871849060059</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.42187786102295</t>
+    <t xml:space="preserve">2.50871825218201</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.42187809944153</t>
   </si>
   <si>
     <t xml:space="preserve">2.45082473754883</t>
@@ -818,70 +818,70 @@
     <t xml:space="preserve">2.2945122718811</t>
   </si>
   <si>
-    <t xml:space="preserve">2.30223155021667</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.38135242462158</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.32056427001953</t>
+    <t xml:space="preserve">2.30223107337952</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.38135266304016</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.32056403160095</t>
   </si>
   <si>
     <t xml:space="preserve">2.24047803878784</t>
   </si>
   <si>
-    <t xml:space="preserve">2.1710057258606</t>
+    <t xml:space="preserve">2.17100596427917</t>
   </si>
   <si>
     <t xml:space="preserve">2.14784860610962</t>
   </si>
   <si>
-    <t xml:space="preserve">2.14495420455933</t>
+    <t xml:space="preserve">2.14495444297791</t>
   </si>
   <si>
     <t xml:space="preserve">2.06293845176697</t>
   </si>
   <si>
-    <t xml:space="preserve">2.02627301216125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.99732613563538</t>
+    <t xml:space="preserve">2.0262725353241</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.9973258972168</t>
   </si>
   <si>
     <t xml:space="preserve">2.16135740280151</t>
   </si>
   <si>
-    <t xml:space="preserve">2.17004179954529</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.26749563217163</t>
+    <t xml:space="preserve">2.17004132270813</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.26749539375305</t>
   </si>
   <si>
     <t xml:space="preserve">2.20574283599854</t>
   </si>
   <si>
-    <t xml:space="preserve">2.11311268806458</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.1179370880127</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.18837451934814</t>
+    <t xml:space="preserve">2.11311221122742</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.11793732643127</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.18837404251099</t>
   </si>
   <si>
     <t xml:space="preserve">2.25977659225464</t>
   </si>
   <si>
-    <t xml:space="preserve">2.22214555740356</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.16521716117859</t>
+    <t xml:space="preserve">2.22214579582214</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.16521692276001</t>
   </si>
   <si>
     <t xml:space="preserve">2.16907644271851</t>
   </si>
   <si>
-    <t xml:space="preserve">2.27714467048645</t>
+    <t xml:space="preserve">2.27714443206787</t>
   </si>
   <si>
     <t xml:space="preserve">2.25012731552124</t>
@@ -893,19 +893,19 @@
     <t xml:space="preserve">2.32635378837585</t>
   </si>
   <si>
-    <t xml:space="preserve">2.3919665813446</t>
+    <t xml:space="preserve">2.39196681976318</t>
   </si>
   <si>
     <t xml:space="preserve">2.36494922637939</t>
   </si>
   <si>
-    <t xml:space="preserve">2.32249355316162</t>
+    <t xml:space="preserve">2.3224937915802</t>
   </si>
   <si>
     <t xml:space="preserve">2.33696746826172</t>
   </si>
   <si>
-    <t xml:space="preserve">2.29354739189148</t>
+    <t xml:space="preserve">2.29354810714722</t>
   </si>
   <si>
     <t xml:space="preserve">2.26267123222351</t>
@@ -914,16 +914,16 @@
     <t xml:space="preserve">2.25784611701965</t>
   </si>
   <si>
-    <t xml:space="preserve">2.17872548103333</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.19512820243835</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.19319891929626</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.20960187911987</t>
+    <t xml:space="preserve">2.17872524261475</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.19512844085693</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.19319868087769</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.20960235595703</t>
   </si>
   <si>
     <t xml:space="preserve">2.17390131950378</t>
@@ -932,61 +932,61 @@
     <t xml:space="preserve">2.12179660797119</t>
   </si>
   <si>
-    <t xml:space="preserve">2.10442900657654</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.21153163909912</t>
+    <t xml:space="preserve">2.10442924499512</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.21153140068054</t>
   </si>
   <si>
     <t xml:space="preserve">2.36398434638977</t>
   </si>
   <si>
-    <t xml:space="preserve">2.39872050285339</t>
+    <t xml:space="preserve">2.39872121810913</t>
   </si>
   <si>
     <t xml:space="preserve">2.3466169834137</t>
   </si>
   <si>
-    <t xml:space="preserve">2.41946601867676</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.48218393325806</t>
+    <t xml:space="preserve">2.41946578025818</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.48218417167664</t>
   </si>
   <si>
     <t xml:space="preserve">2.51836776733398</t>
   </si>
   <si>
-    <t xml:space="preserve">2.45564913749695</t>
+    <t xml:space="preserve">2.45564937591553</t>
   </si>
   <si>
     <t xml:space="preserve">2.43635177612305</t>
   </si>
   <si>
-    <t xml:space="preserve">2.29837203025818</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.26170587539673</t>
+    <t xml:space="preserve">2.29837155342102</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.26170563697815</t>
   </si>
   <si>
     <t xml:space="preserve">2.34468674659729</t>
   </si>
   <si>
-    <t xml:space="preserve">2.30609083175659</t>
+    <t xml:space="preserve">2.30609059333801</t>
   </si>
   <si>
     <t xml:space="preserve">2.25302171707153</t>
   </si>
   <si>
-    <t xml:space="preserve">2.22697043418884</t>
+    <t xml:space="preserve">2.22696995735168</t>
   </si>
   <si>
     <t xml:space="preserve">2.26074123382568</t>
   </si>
   <si>
-    <t xml:space="preserve">2.24998998641968</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.25096726417542</t>
+    <t xml:space="preserve">2.24998950958252</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.25096750259399</t>
   </si>
   <si>
     <t xml:space="preserve">2.2822437286377</t>
@@ -995,16 +995,16 @@
     <t xml:space="preserve">2.27931189537048</t>
   </si>
   <si>
-    <t xml:space="preserve">2.25292205810547</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.18450379371643</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.18548107147217</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.13074660301208</t>
+    <t xml:space="preserve">2.25292158126831</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.18450355529785</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.18548130989075</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.13074612617493</t>
   </si>
   <si>
     <t xml:space="preserve">2.17570662498474</t>
@@ -1013,22 +1013,22 @@
     <t xml:space="preserve">2.14833950996399</t>
   </si>
   <si>
-    <t xml:space="preserve">2.10924339294434</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.076988697052</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.08089876174927</t>
+    <t xml:space="preserve">2.10924315452576</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.07698893547058</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.08089852333069</t>
   </si>
   <si>
     <t xml:space="preserve">2.15811347961426</t>
   </si>
   <si>
-    <t xml:space="preserve">2.15127205848694</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.10631132125854</t>
+    <t xml:space="preserve">2.15127158164978</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.10631108283997</t>
   </si>
   <si>
     <t xml:space="preserve">2.15909075737</t>
@@ -1037,13 +1037,13 @@
     <t xml:space="preserve">2.13758778572083</t>
   </si>
   <si>
-    <t xml:space="preserve">2.04082465171814</t>
+    <t xml:space="preserve">2.04082441329956</t>
   </si>
   <si>
     <t xml:space="preserve">2.05353093147278</t>
   </si>
   <si>
-    <t xml:space="preserve">2.00075125694275</t>
+    <t xml:space="preserve">2.00075101852417</t>
   </si>
   <si>
     <t xml:space="preserve">2.0906720161438</t>
@@ -1052,7 +1052,7 @@
     <t xml:space="preserve">2.081876039505</t>
   </si>
   <si>
-    <t xml:space="preserve">2.13661026954651</t>
+    <t xml:space="preserve">2.13661050796509</t>
   </si>
   <si>
     <t xml:space="preserve">2.14931654930115</t>
@@ -1061,64 +1061,64 @@
     <t xml:space="preserve">2.16886520385742</t>
   </si>
   <si>
-    <t xml:space="preserve">2.15713596343994</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.13367819786072</t>
+    <t xml:space="preserve">2.15713572502136</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.1336784362793</t>
   </si>
   <si>
     <t xml:space="preserve">2.27149271965027</t>
   </si>
   <si>
-    <t xml:space="preserve">2.34870791435242</t>
+    <t xml:space="preserve">2.34870743751526</t>
   </si>
   <si>
     <t xml:space="preserve">2.2920184135437</t>
   </si>
   <si>
-    <t xml:space="preserve">2.29788279533386</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.29104065895081</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.32231831550598</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.36434650421143</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.41419434547424</t>
+    <t xml:space="preserve">2.29788303375244</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.29104042053223</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.3223180770874</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.36434698104858</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.41419458389282</t>
   </si>
   <si>
     <t xml:space="preserve">2.42103600502014</t>
   </si>
   <si>
-    <t xml:space="preserve">2.41908121109009</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.4337420463562</t>
+    <t xml:space="preserve">2.41908144950867</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.43374180793762</t>
   </si>
   <si>
     <t xml:space="preserve">2.35457229614258</t>
   </si>
   <si>
-    <t xml:space="preserve">2.37021064758301</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.30667948722839</t>
+    <t xml:space="preserve">2.37021088600159</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.30667924880981</t>
   </si>
   <si>
     <t xml:space="preserve">2.2812671661377</t>
   </si>
   <si>
-    <t xml:space="preserve">2.25389933586121</t>
+    <t xml:space="preserve">2.25389909744263</t>
   </si>
   <si>
     <t xml:space="preserve">2.28713083267212</t>
   </si>
   <si>
-    <t xml:space="preserve">2.2988600730896</t>
+    <t xml:space="preserve">2.29885983467102</t>
   </si>
   <si>
     <t xml:space="preserve">2.27344751358032</t>
@@ -1130,13 +1130,13 @@
     <t xml:space="preserve">2.31352090835571</t>
   </si>
   <si>
-    <t xml:space="preserve">2.45328998565674</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.42005848884583</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.40246510505676</t>
+    <t xml:space="preserve">2.45329022407532</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.42005825042725</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.40246534347534</t>
   </si>
   <si>
     <t xml:space="preserve">2.31743097305298</t>
@@ -1148,16 +1148,16 @@
     <t xml:space="preserve">2.38389420509338</t>
   </si>
   <si>
-    <t xml:space="preserve">2.35750412940979</t>
+    <t xml:space="preserve">2.35750460624695</t>
   </si>
   <si>
     <t xml:space="preserve">2.32622742652893</t>
   </si>
   <si>
-    <t xml:space="preserve">2.29690551757812</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.31938529014587</t>
+    <t xml:space="preserve">2.29690527915955</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.31938505172729</t>
   </si>
   <si>
     <t xml:space="preserve">2.32915949821472</t>
@@ -1178,13 +1178,13 @@
     <t xml:space="preserve">2.30863404273987</t>
   </si>
   <si>
-    <t xml:space="preserve">2.27247047424316</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.23337411880493</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.21382594108582</t>
+    <t xml:space="preserve">2.27247023582458</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.23337364196777</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.21382570266724</t>
   </si>
   <si>
     <t xml:space="preserve">2.27735757827759</t>
@@ -1196,7 +1196,7 @@
     <t xml:space="preserve">2.30081510543823</t>
   </si>
   <si>
-    <t xml:space="preserve">2.2421703338623</t>
+    <t xml:space="preserve">2.24217057228088</t>
   </si>
   <si>
     <t xml:space="preserve">2.26269602775574</t>
@@ -1205,25 +1205,25 @@
     <t xml:space="preserve">2.29006338119507</t>
   </si>
   <si>
-    <t xml:space="preserve">2.33795666694641</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.2861533164978</t>
+    <t xml:space="preserve">2.33795619010925</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.28615355491638</t>
   </si>
   <si>
     <t xml:space="preserve">2.35359477996826</t>
   </si>
   <si>
-    <t xml:space="preserve">2.4229907989502</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.46306467056274</t>
+    <t xml:space="preserve">2.42299103736877</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.46306443214417</t>
   </si>
   <si>
     <t xml:space="preserve">2.47283864021301</t>
   </si>
   <si>
-    <t xml:space="preserve">2.51437830924988</t>
+    <t xml:space="preserve">2.51437854766846</t>
   </si>
   <si>
     <t xml:space="preserve">2.50704741477966</t>
@@ -1232,37 +1232,37 @@
     <t xml:space="preserve">2.43276453018188</t>
   </si>
   <si>
-    <t xml:space="preserve">2.3917133808136</t>
+    <t xml:space="preserve">2.39171361923218</t>
   </si>
   <si>
     <t xml:space="preserve">2.26171851158142</t>
   </si>
   <si>
-    <t xml:space="preserve">2.19525480270386</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.14736223220825</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.1708197593689</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.14638471603394</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.1405200958252</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.07210206985474</t>
+    <t xml:space="preserve">2.19525456428528</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.14736247062683</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.17081952095032</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.14638447761536</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.14051961898804</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.07210183143616</t>
   </si>
   <si>
     <t xml:space="preserve">2.07894349098206</t>
   </si>
   <si>
-    <t xml:space="preserve">2.09946918487549</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.07601141929626</t>
+    <t xml:space="preserve">2.09946870803833</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.07601118087769</t>
   </si>
   <si>
     <t xml:space="preserve">2.04375720024109</t>
@@ -1274,7 +1274,7 @@
     <t xml:space="preserve">2.04473400115967</t>
   </si>
   <si>
-    <t xml:space="preserve">2.03887009620667</t>
+    <t xml:space="preserve">2.03886985778809</t>
   </si>
   <si>
     <t xml:space="preserve">2.11315298080444</t>
@@ -1289,19 +1289,19 @@
     <t xml:space="preserve">1.98804485797882</t>
   </si>
   <si>
-    <t xml:space="preserve">1.9010556936264</t>
+    <t xml:space="preserve">1.90105545520782</t>
   </si>
   <si>
     <t xml:space="preserve">2.08969521522522</t>
   </si>
   <si>
-    <t xml:space="preserve">2.06721472740173</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.08578610420227</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.03984785079956</t>
+    <t xml:space="preserve">2.06721448898315</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.08578586578369</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.0398473739624</t>
   </si>
   <si>
     <t xml:space="preserve">2.08285284042358</t>
@@ -1310,46 +1310,46 @@
     <t xml:space="preserve">2.01345729827881</t>
   </si>
   <si>
-    <t xml:space="preserve">2.04668927192688</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.01834440231323</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.00661563873291</t>
+    <t xml:space="preserve">2.0466890335083</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.01834464073181</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.00661587715149</t>
   </si>
   <si>
     <t xml:space="preserve">2.06623721122742</t>
   </si>
   <si>
-    <t xml:space="preserve">2.16202330589294</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.24607992172241</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.17961668968201</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.2382607460022</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.22653222084045</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.19916391372681</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.27051472663879</t>
+    <t xml:space="preserve">2.16202306747437</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.24608016014099</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.17961645126343</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.23826122283936</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.22653245925903</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.19916415214539</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.27051520347595</t>
   </si>
   <si>
     <t xml:space="preserve">2.21773552894592</t>
   </si>
   <si>
-    <t xml:space="preserve">2.07796573638916</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.03691506385803</t>
+    <t xml:space="preserve">2.07796597480774</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.03691482543945</t>
   </si>
   <si>
     <t xml:space="preserve">2.03105092048645</t>
@@ -1358,19 +1358,19 @@
     <t xml:space="preserve">2.09849190711975</t>
   </si>
   <si>
-    <t xml:space="preserve">2.08676290512085</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.08871793746948</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.0476667881012</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.05841779708862</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.11510801315308</t>
+    <t xml:space="preserve">2.08676242828369</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.08871746063232</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.04766702651978</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.0584180355072</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.1151077747345</t>
   </si>
   <si>
     <t xml:space="preserve">2.05744004249573</t>
@@ -1382,19 +1382,19 @@
     <t xml:space="preserve">2.07307958602905</t>
   </si>
   <si>
-    <t xml:space="preserve">2.07503366470337</t>
+    <t xml:space="preserve">2.07503390312195</t>
   </si>
   <si>
     <t xml:space="preserve">2.11119771003723</t>
   </si>
   <si>
-    <t xml:space="preserve">2.2060067653656</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.22848677635193</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.20405125617981</t>
+    <t xml:space="preserve">2.20600628852844</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.22848653793335</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.20405149459839</t>
   </si>
   <si>
     <t xml:space="preserve">2.16104531288147</t>
@@ -1403,52 +1403,52 @@
     <t xml:space="preserve">2.26074147224426</t>
   </si>
   <si>
-    <t xml:space="preserve">2.35261678695679</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.35066246986389</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.3677670955658</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.27686882019043</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.29543924331665</t>
+    <t xml:space="preserve">2.35261702537537</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.35066223144531</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.36776733398438</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.27686834335327</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.29543876647949</t>
   </si>
   <si>
     <t xml:space="preserve">2.27784538269043</t>
   </si>
   <si>
-    <t xml:space="preserve">2.21578001976013</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.22408843040466</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.30179238319397</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.25194478034973</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.22213387489319</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.33746767044067</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.34186601638794</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.33209180831909</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.33600115776062</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.28957509994507</t>
+    <t xml:space="preserve">2.21578049659729</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.2240879535675</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.30179262161255</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.25194454193115</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.22213363647461</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.33746743202209</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.34186625480652</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.33209133148193</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.33600091934204</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.28957486152649</t>
   </si>
   <si>
     <t xml:space="preserve">2.37656378746033</t>
@@ -1457,28 +1457,28 @@
     <t xml:space="preserve">2.37705302238464</t>
   </si>
   <si>
-    <t xml:space="preserve">2.38145112991333</t>
+    <t xml:space="preserve">2.38145160675049</t>
   </si>
   <si>
     <t xml:space="preserve">2.37900710105896</t>
   </si>
   <si>
-    <t xml:space="preserve">2.40735173225403</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.38731503486633</t>
+    <t xml:space="preserve">2.40735197067261</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.38731551170349</t>
   </si>
   <si>
     <t xml:space="preserve">2.20551776885986</t>
   </si>
   <si>
-    <t xml:space="preserve">2.29592800140381</t>
+    <t xml:space="preserve">2.29592776298523</t>
   </si>
   <si>
     <t xml:space="preserve">2.32720518112183</t>
   </si>
   <si>
-    <t xml:space="preserve">2.25438809394836</t>
+    <t xml:space="preserve">2.25438785552979</t>
   </si>
   <si>
     <t xml:space="preserve">2.29641652107239</t>
@@ -1490,7 +1490,7 @@
     <t xml:space="preserve">2.2490119934082</t>
   </si>
   <si>
-    <t xml:space="preserve">2.27540254592896</t>
+    <t xml:space="preserve">2.27540230751038</t>
   </si>
   <si>
     <t xml:space="preserve">2.28322172164917</t>
@@ -1499,10 +1499,10 @@
     <t xml:space="preserve">2.26758313179016</t>
   </si>
   <si>
-    <t xml:space="preserve">2.22359943389893</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.2299530506134</t>
+    <t xml:space="preserve">2.2235996723175</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.22995257377625</t>
   </si>
   <si>
     <t xml:space="preserve">2.21040511131287</t>
@@ -1511,7 +1511,7 @@
     <t xml:space="preserve">2.22555470466614</t>
   </si>
   <si>
-    <t xml:space="preserve">2.20698380470276</t>
+    <t xml:space="preserve">2.20698356628418</t>
   </si>
   <si>
     <t xml:space="preserve">2.20893859863281</t>
@@ -1520,37 +1520,37 @@
     <t xml:space="preserve">2.29446125030518</t>
   </si>
   <si>
-    <t xml:space="preserve">2.30276942253113</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.31156611442566</t>
+    <t xml:space="preserve">2.30276894569397</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.31156587600708</t>
   </si>
   <si>
     <t xml:space="preserve">2.33502435684204</t>
   </si>
   <si>
-    <t xml:space="preserve">2.38487195968628</t>
+    <t xml:space="preserve">2.3848717212677</t>
   </si>
   <si>
     <t xml:space="preserve">2.35652709007263</t>
   </si>
   <si>
-    <t xml:space="preserve">2.36288022994995</t>
+    <t xml:space="preserve">2.36288046836853</t>
   </si>
   <si>
     <t xml:space="preserve">2.38829278945923</t>
   </si>
   <si>
-    <t xml:space="preserve">2.34479784965515</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.31547594070435</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.33013701438904</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.31889724731445</t>
+    <t xml:space="preserve">2.34479808807373</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.31547570228577</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.33013725280762</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.31889748573303</t>
   </si>
   <si>
     <t xml:space="preserve">2.33062601089478</t>
@@ -1559,49 +1559,49 @@
     <t xml:space="preserve">2.31303262710571</t>
   </si>
   <si>
-    <t xml:space="preserve">2.30570244789124</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.3966007232666</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.40539717674255</t>
+    <t xml:space="preserve">2.30570197105408</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.39660048484802</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.40539741516113</t>
   </si>
   <si>
     <t xml:space="preserve">2.45231318473816</t>
   </si>
   <si>
-    <t xml:space="preserve">2.48749923706055</t>
+    <t xml:space="preserve">2.48749947547913</t>
   </si>
   <si>
     <t xml:space="preserve">2.51584386825562</t>
   </si>
   <si>
-    <t xml:space="preserve">2.44204950332642</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.44253897666931</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.28028964996338</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.30131053924561</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.33834743499756</t>
+    <t xml:space="preserve">2.44204998016357</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.44253921508789</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.2802894115448</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.30131077766418</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.33834767341614</t>
   </si>
   <si>
     <t xml:space="preserve">2.36387300491333</t>
   </si>
   <si>
-    <t xml:space="preserve">2.33484435081482</t>
+    <t xml:space="preserve">2.33484411239624</t>
   </si>
   <si>
     <t xml:space="preserve">2.28779673576355</t>
   </si>
   <si>
-    <t xml:space="preserve">2.15416240692139</t>
+    <t xml:space="preserve">2.15416216850281</t>
   </si>
   <si>
     <t xml:space="preserve">2.04555368423462</t>
@@ -1610,7 +1610,7 @@
     <t xml:space="preserve">2.05306100845337</t>
   </si>
   <si>
-    <t xml:space="preserve">2.05356168746948</t>
+    <t xml:space="preserve">2.05356121063232</t>
   </si>
   <si>
     <t xml:space="preserve">2.21522378921509</t>
@@ -1628,7 +1628,7 @@
     <t xml:space="preserve">2.11612439155579</t>
   </si>
   <si>
-    <t xml:space="preserve">2.05906748771667</t>
+    <t xml:space="preserve">2.0590672492981</t>
   </si>
   <si>
     <t xml:space="preserve">2.14865732192993</t>
@@ -1640,10 +1640,10 @@
     <t xml:space="preserve">2.20921778678894</t>
   </si>
   <si>
-    <t xml:space="preserve">2.23624491691589</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.1776864528656</t>
+    <t xml:space="preserve">2.23624515533447</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.17768669128418</t>
   </si>
   <si>
     <t xml:space="preserve">2.16717553138733</t>
@@ -1652,16 +1652,16 @@
     <t xml:space="preserve">2.24074935913086</t>
   </si>
   <si>
-    <t xml:space="preserve">2.29730629920959</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.22973847389221</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.39390349388123</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.3448543548584</t>
+    <t xml:space="preserve">2.29730653762817</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.22973871231079</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.39390301704407</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.34485411643982</t>
   </si>
   <si>
     <t xml:space="preserve">2.35786724090576</t>
@@ -1682,7 +1682,7 @@
     <t xml:space="preserve">2.34935903549194</t>
   </si>
   <si>
-    <t xml:space="preserve">2.34034991264343</t>
+    <t xml:space="preserve">2.34034943580627</t>
   </si>
   <si>
     <t xml:space="preserve">2.38639569282532</t>
@@ -1691,7 +1691,7 @@
     <t xml:space="preserve">2.39440369606018</t>
   </si>
   <si>
-    <t xml:space="preserve">2.34785747528076</t>
+    <t xml:space="preserve">2.34785723686218</t>
   </si>
   <si>
     <t xml:space="preserve">2.30881786346436</t>
@@ -1700,13 +1700,13 @@
     <t xml:space="preserve">2.32483386993408</t>
   </si>
   <si>
-    <t xml:space="preserve">2.35686612129211</t>
+    <t xml:space="preserve">2.35686635971069</t>
   </si>
   <si>
     <t xml:space="preserve">2.3153247833252</t>
   </si>
   <si>
-    <t xml:space="preserve">2.27228140830994</t>
+    <t xml:space="preserve">2.27228116989136</t>
   </si>
   <si>
     <t xml:space="preserve">2.31832766532898</t>
@@ -1718,7 +1718,7 @@
     <t xml:space="preserve">2.34985876083374</t>
   </si>
   <si>
-    <t xml:space="preserve">2.38289260864258</t>
+    <t xml:space="preserve">2.38289213180542</t>
   </si>
   <si>
     <t xml:space="preserve">2.35936832427979</t>
@@ -1730,7 +1730,7 @@
     <t xml:space="preserve">2.38189125061035</t>
   </si>
   <si>
-    <t xml:space="preserve">2.29680609703064</t>
+    <t xml:space="preserve">2.29680585861206</t>
   </si>
   <si>
     <t xml:space="preserve">2.29079937934875</t>
@@ -1739,40 +1739,40 @@
     <t xml:space="preserve">2.29230141639709</t>
   </si>
   <si>
-    <t xml:space="preserve">2.31232142448425</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.17568421363831</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.1511595249176</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.12112975120544</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.0685760974884</t>
+    <t xml:space="preserve">2.31232118606567</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.17568397521973</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.15115928649902</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.12112951278687</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.06857681274414</t>
   </si>
   <si>
     <t xml:space="preserve">2.04905700683594</t>
   </si>
   <si>
-    <t xml:space="preserve">2.04655504226685</t>
+    <t xml:space="preserve">2.04655480384827</t>
   </si>
   <si>
     <t xml:space="preserve">2.00200986862183</t>
   </si>
   <si>
-    <t xml:space="preserve">2.00251054763794</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.04705500602722</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.04605436325073</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.03003740310669</t>
+    <t xml:space="preserve">2.00251030921936</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.04705476760864</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.04605412483215</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.03003787994385</t>
   </si>
   <si>
     <t xml:space="preserve">2.02503299713135</t>
@@ -1781,19 +1781,19 @@
     <t xml:space="preserve">2.01702547073364</t>
   </si>
   <si>
-    <t xml:space="preserve">1.98449194431305</t>
+    <t xml:space="preserve">1.98449242115021</t>
   </si>
   <si>
     <t xml:space="preserve">1.99700462818146</t>
   </si>
   <si>
-    <t xml:space="preserve">1.92192959785461</t>
+    <t xml:space="preserve">1.92192983627319</t>
   </si>
   <si>
     <t xml:space="preserve">1.90140914916992</t>
   </si>
   <si>
-    <t xml:space="preserve">1.91041839122772</t>
+    <t xml:space="preserve">1.9104186296463</t>
   </si>
   <si>
     <t xml:space="preserve">1.98048806190491</t>
@@ -1808,13 +1808,13 @@
     <t xml:space="preserve">2.12413215637207</t>
   </si>
   <si>
-    <t xml:space="preserve">2.11362218856812</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.11562347412109</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.10861682891846</t>
+    <t xml:space="preserve">2.11362195014954</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.11562371253967</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.10861659049988</t>
   </si>
   <si>
     <t xml:space="preserve">2.15716576576233</t>
@@ -1823,13 +1823,13 @@
     <t xml:space="preserve">2.18969821929932</t>
   </si>
   <si>
-    <t xml:space="preserve">2.1691780090332</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.12763619422913</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.15216064453125</t>
+    <t xml:space="preserve">2.16917777061462</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.12763643264771</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.15216088294983</t>
   </si>
   <si>
     <t xml:space="preserve">2.17868757247925</t>
@@ -1844,7 +1844,7 @@
     <t xml:space="preserve">1.91742515563965</t>
   </si>
   <si>
-    <t xml:space="preserve">1.88389158248901</t>
+    <t xml:space="preserve">1.88389134407043</t>
   </si>
   <si>
     <t xml:space="preserve">1.85936629772186</t>
@@ -1856,10 +1856,10 @@
     <t xml:space="preserve">1.83684408664703</t>
   </si>
   <si>
-    <t xml:space="preserve">1.80631339550018</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.77027702331543</t>
+    <t xml:space="preserve">1.80631327629089</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.77027678489685</t>
   </si>
   <si>
     <t xml:space="preserve">1.80881559848785</t>
@@ -1874,19 +1874,19 @@
     <t xml:space="preserve">1.8008074760437</t>
   </si>
   <si>
-    <t xml:space="preserve">1.78529214859009</t>
+    <t xml:space="preserve">1.78529226779938</t>
   </si>
   <si>
     <t xml:space="preserve">1.78779458999634</t>
   </si>
   <si>
-    <t xml:space="preserve">1.74925577640533</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.75576281547546</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.69169855117798</t>
+    <t xml:space="preserve">1.74925601482391</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.75576257705688</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.69169819355011</t>
   </si>
   <si>
     <t xml:space="preserve">1.65516149997711</t>
@@ -1895,7 +1895,7 @@
     <t xml:space="preserve">1.60811412334442</t>
   </si>
   <si>
-    <t xml:space="preserve">1.64515173435211</t>
+    <t xml:space="preserve">1.64515149593353</t>
   </si>
   <si>
     <t xml:space="preserve">1.6326390504837</t>
@@ -1904,31 +1904,31 @@
     <t xml:space="preserve">1.70471143722534</t>
   </si>
   <si>
-    <t xml:space="preserve">1.69470107555389</t>
+    <t xml:space="preserve">1.69470119476318</t>
   </si>
   <si>
     <t xml:space="preserve">1.6806868314743</t>
   </si>
   <si>
-    <t xml:space="preserve">1.69069743156433</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.75926613807678</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.69870507717133</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.68619275093079</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.71672368049622</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.72973644733429</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.74525165557861</t>
+    <t xml:space="preserve">1.69069731235504</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.75926601886749</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.69870495796204</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.68619239330292</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.71672344207764</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.72973680496216</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.74525201320648</t>
   </si>
   <si>
     <t xml:space="preserve">1.74775469303131</t>
@@ -1937,7 +1937,7 @@
     <t xml:space="preserve">1.69670355319977</t>
   </si>
   <si>
-    <t xml:space="preserve">1.71071708202362</t>
+    <t xml:space="preserve">1.71071720123291</t>
   </si>
   <si>
     <t xml:space="preserve">1.67968642711639</t>
@@ -1946,37 +1946,37 @@
     <t xml:space="preserve">1.6952018737793</t>
   </si>
   <si>
-    <t xml:space="preserve">1.67568254470825</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.73624289035797</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.74625337123871</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.74725425243378</t>
+    <t xml:space="preserve">1.67568242549896</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.73624265193939</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.74625301361084</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.74725413322449</t>
   </si>
   <si>
     <t xml:space="preserve">1.84084820747375</t>
   </si>
   <si>
-    <t xml:space="preserve">1.77628326416016</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.7922990322113</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.80130815505981</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.88439202308655</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.85235953330994</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.8868944644928</t>
+    <t xml:space="preserve">1.77628314495087</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.79229915142059</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.80130839347839</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.88439190387726</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.85235929489136</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.88689422607422</t>
   </si>
   <si>
     <t xml:space="preserve">1.82683408260345</t>
@@ -1985,16 +1985,16 @@
     <t xml:space="preserve">1.79780471324921</t>
   </si>
   <si>
-    <t xml:space="preserve">1.76727437973022</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.75025689601898</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.74325025081635</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.71622264385223</t>
+    <t xml:space="preserve">1.76727414131165</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.75025713443756</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.74325037002563</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.71622276306152</t>
   </si>
   <si>
     <t xml:space="preserve">1.68268930912018</t>
@@ -2009,88 +2009,88 @@
     <t xml:space="preserve">1.67618238925934</t>
   </si>
   <si>
-    <t xml:space="preserve">1.66366994380951</t>
+    <t xml:space="preserve">1.66366982460022</t>
   </si>
   <si>
     <t xml:space="preserve">1.64114773273468</t>
   </si>
   <si>
-    <t xml:space="preserve">1.6836906671524</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.64965617656708</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.63864481449127</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.69369983673096</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.70421099662781</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.66667342185974</t>
+    <t xml:space="preserve">1.68369042873383</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.64965641498566</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.63864469528198</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.69370019435883</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.70421087741852</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.66667330265045</t>
   </si>
   <si>
     <t xml:space="preserve">1.6596657037735</t>
   </si>
   <si>
-    <t xml:space="preserve">1.66467082500458</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.63664317131042</t>
+    <t xml:space="preserve">1.66467094421387</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.63664329051971</t>
   </si>
   <si>
     <t xml:space="preserve">1.57357931137085</t>
   </si>
   <si>
-    <t xml:space="preserve">1.49900484085083</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.53203797340393</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.53804409503937</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.52903497219086</t>
+    <t xml:space="preserve">1.49900472164154</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.53203785419464</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.53804397583008</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.52903509140015</t>
   </si>
   <si>
     <t xml:space="preserve">1.53704285621643</t>
   </si>
   <si>
-    <t xml:space="preserve">1.52853429317474</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.50601184368134</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.51051604747772</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.57658278942108</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.55756330490112</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.56156730651855</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.57508111000061</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.47948551177979</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.48398923873901</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.48649215698242</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.48899459838867</t>
+    <t xml:space="preserve">1.52853417396545</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.50601160526276</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.51051592826843</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.57658290863037</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.55756342411041</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.56156718730927</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.57508075237274</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.47948563098907</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.48398947715759</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.48649227619171</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.48899435997009</t>
   </si>
   <si>
     <t xml:space="preserve">1.52402973175049</t>
@@ -2099,82 +2099,82 @@
     <t xml:space="preserve">1.50851452350616</t>
   </si>
   <si>
-    <t xml:space="preserve">1.64164841175079</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.70971667766571</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.69219887256622</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.68569195270538</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.76377069950104</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.75676381587982</t>
+    <t xml:space="preserve">1.64164817333221</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.70971691608429</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.69219899177551</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.68569219112396</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.76377093791962</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.75676429271698</t>
   </si>
   <si>
     <t xml:space="preserve">1.74174833297729</t>
   </si>
   <si>
-    <t xml:space="preserve">1.71372056007385</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.73374044895172</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.7512583732605</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.7627694606781</t>
+    <t xml:space="preserve">1.71372044086456</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.73374056816101</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.75125813484192</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.76276957988739</t>
   </si>
   <si>
     <t xml:space="preserve">1.81031739711761</t>
   </si>
   <si>
-    <t xml:space="preserve">1.85085773468018</t>
+    <t xml:space="preserve">1.85085737705231</t>
   </si>
   <si>
     <t xml:space="preserve">1.84585332870483</t>
   </si>
   <si>
-    <t xml:space="preserve">1.83984696865082</t>
+    <t xml:space="preserve">1.83984684944153</t>
   </si>
   <si>
     <t xml:space="preserve">1.85486257076263</t>
   </si>
   <si>
-    <t xml:space="preserve">1.80030715465546</t>
+    <t xml:space="preserve">1.80030703544617</t>
   </si>
   <si>
     <t xml:space="preserve">1.78178894519806</t>
   </si>
   <si>
-    <t xml:space="preserve">1.77077758312225</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.78128826618195</t>
+    <t xml:space="preserve">1.77077746391296</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.78128838539124</t>
   </si>
   <si>
     <t xml:space="preserve">1.81732404232025</t>
   </si>
   <si>
-    <t xml:space="preserve">1.85386109352112</t>
+    <t xml:space="preserve">1.85386157035828</t>
   </si>
   <si>
     <t xml:space="preserve">1.86787462234497</t>
   </si>
   <si>
-    <t xml:space="preserve">1.86837553977966</t>
+    <t xml:space="preserve">1.86837542057037</t>
   </si>
   <si>
     <t xml:space="preserve">1.85185885429382</t>
   </si>
   <si>
-    <t xml:space="preserve">1.82633340358734</t>
+    <t xml:space="preserve">1.82633316516876</t>
   </si>
   <si>
     <t xml:space="preserve">1.8188259601593</t>
@@ -2183,10 +2183,10 @@
     <t xml:space="preserve">1.8033105134964</t>
   </si>
   <si>
-    <t xml:space="preserve">1.83183908462524</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.8243316411972</t>
+    <t xml:space="preserve">1.83183896541595</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.82433176040649</t>
   </si>
   <si>
     <t xml:space="preserve">1.82232940196991</t>
@@ -2195,37 +2195,37 @@
     <t xml:space="preserve">1.84735441207886</t>
   </si>
   <si>
-    <t xml:space="preserve">1.83334076404572</t>
+    <t xml:space="preserve">1.83334052562714</t>
   </si>
   <si>
     <t xml:space="preserve">1.85135853290558</t>
   </si>
   <si>
-    <t xml:space="preserve">1.85336077213287</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.86937642097473</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.87037789821625</t>
+    <t xml:space="preserve">1.85336053371429</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.86937665939331</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.87037765979767</t>
   </si>
   <si>
     <t xml:space="preserve">1.89990735054016</t>
   </si>
   <si>
-    <t xml:space="preserve">1.93544328212738</t>
+    <t xml:space="preserve">1.93544352054596</t>
   </si>
   <si>
     <t xml:space="preserve">1.9864946603775</t>
   </si>
   <si>
-    <t xml:space="preserve">2.02002835273743</t>
+    <t xml:space="preserve">2.02002811431885</t>
   </si>
   <si>
     <t xml:space="preserve">2.07358145713806</t>
   </si>
   <si>
-    <t xml:space="preserve">2.09360194206238</t>
+    <t xml:space="preserve">2.09360218048096</t>
   </si>
   <si>
     <t xml:space="preserve">2.07308101654053</t>
@@ -2234,10 +2234,10 @@
     <t xml:space="preserve">2.05506348609924</t>
   </si>
   <si>
-    <t xml:space="preserve">2.08859705924988</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.10561394691467</t>
+    <t xml:space="preserve">2.0885968208313</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.10561418533325</t>
   </si>
   <si>
     <t xml:space="preserve">2.11161971092224</t>
@@ -2255,7 +2255,7 @@
     <t xml:space="preserve">2.05956792831421</t>
   </si>
   <si>
-    <t xml:space="preserve">2.04805612564087</t>
+    <t xml:space="preserve">2.04805588722229</t>
   </si>
   <si>
     <t xml:space="preserve">2.00401210784912</t>
@@ -2267,7 +2267,7 @@
     <t xml:space="preserve">1.95195984840393</t>
   </si>
   <si>
-    <t xml:space="preserve">1.96947741508484</t>
+    <t xml:space="preserve">1.96947765350342</t>
   </si>
   <si>
     <t xml:space="preserve">1.93494272232056</t>
@@ -2276,115 +2276,115 @@
     <t xml:space="preserve">1.97848665714264</t>
   </si>
   <si>
-    <t xml:space="preserve">1.9255838394165</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.87486886978149</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.83502221107483</t>
+    <t xml:space="preserve">1.92558360099792</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.87486910820007</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.83502244949341</t>
   </si>
   <si>
     <t xml:space="preserve">1.81070065498352</t>
   </si>
   <si>
-    <t xml:space="preserve">1.82933020591736</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.780686378479</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.78172075748444</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.77240657806396</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.75998628139496</t>
+    <t xml:space="preserve">1.82933056354523</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.78068614006042</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.78172039985657</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.77240645885468</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.75998640060425</t>
   </si>
   <si>
     <t xml:space="preserve">1.7511887550354</t>
   </si>
   <si>
-    <t xml:space="preserve">1.73721647262573</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.76774871349335</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.73566448688507</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.71496534347534</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.71185946464539</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.7656786441803</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.78223824501038</t>
+    <t xml:space="preserve">1.73721635341644</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.76774919033051</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.73566424846649</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.71496498584747</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.71185958385468</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.76567900180817</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.7822380065918</t>
   </si>
   <si>
     <t xml:space="preserve">1.76205635070801</t>
   </si>
   <si>
-    <t xml:space="preserve">1.78327345848083</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.77706325054169</t>
+    <t xml:space="preserve">1.78327333927155</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.77706336975098</t>
   </si>
   <si>
     <t xml:space="preserve">1.79051804542542</t>
   </si>
   <si>
-    <t xml:space="preserve">1.83088231086731</t>
+    <t xml:space="preserve">1.8308824300766</t>
   </si>
   <si>
     <t xml:space="preserve">1.86503732204437</t>
   </si>
   <si>
-    <t xml:space="preserve">1.86296701431274</t>
+    <t xml:space="preserve">1.86296725273132</t>
   </si>
   <si>
     <t xml:space="preserve">1.89453399181366</t>
   </si>
   <si>
-    <t xml:space="preserve">1.87383460998535</t>
+    <t xml:space="preserve">1.87383484840393</t>
   </si>
   <si>
     <t xml:space="preserve">1.87279963493347</t>
   </si>
   <si>
-    <t xml:space="preserve">1.88366603851318</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.85416984558105</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.84433710575104</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.88211452960968</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.95559799671173</t>
+    <t xml:space="preserve">1.88366627693176</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.85416960716248</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.84433698654175</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.8821142911911</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.95559823513031</t>
   </si>
   <si>
     <t xml:space="preserve">2.01252198219299</t>
   </si>
   <si>
-    <t xml:space="preserve">2.01666164398193</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.99854934215546</t>
+    <t xml:space="preserve">2.01666140556335</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.99854981899261</t>
   </si>
   <si>
     <t xml:space="preserve">1.98198986053467</t>
   </si>
   <si>
-    <t xml:space="preserve">1.99026954174042</t>
+    <t xml:space="preserve">1.990269780159</t>
   </si>
   <si>
     <t xml:space="preserve">1.97371029853821</t>
@@ -2393,10 +2393,10 @@
     <t xml:space="preserve">1.98250758647919</t>
   </si>
   <si>
-    <t xml:space="preserve">1.96853518486023</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.99648010730743</t>
+    <t xml:space="preserve">1.96853542327881</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.99647986888885</t>
   </si>
   <si>
     <t xml:space="preserve">1.964395403862</t>
@@ -2405,19 +2405,19 @@
     <t xml:space="preserve">1.93955612182617</t>
   </si>
   <si>
-    <t xml:space="preserve">1.94576561450958</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.93541598320007</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.88625431060791</t>
+    <t xml:space="preserve">1.945765376091</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.93541622161865</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.88625454902649</t>
   </si>
   <si>
     <t xml:space="preserve">1.87072908878326</t>
   </si>
   <si>
-    <t xml:space="preserve">1.8510650396347</t>
+    <t xml:space="preserve">1.85106515884399</t>
   </si>
   <si>
     <t xml:space="preserve">1.82570731639862</t>
@@ -2426,34 +2426,34 @@
     <t xml:space="preserve">1.7542941570282</t>
   </si>
   <si>
-    <t xml:space="preserve">1.7434264421463</t>
+    <t xml:space="preserve">1.74342620372772</t>
   </si>
   <si>
     <t xml:space="preserve">1.79000091552734</t>
   </si>
   <si>
-    <t xml:space="preserve">1.76257383823395</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.78948378562927</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.76464354991913</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.79828083515167</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.65597069263458</t>
+    <t xml:space="preserve">1.76257395744324</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.78948354721069</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.76464331150055</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.79828107357025</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.65597057342529</t>
   </si>
   <si>
     <t xml:space="preserve">1.62078142166138</t>
   </si>
   <si>
-    <t xml:space="preserve">1.63941121101379</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.55868232250214</t>
+    <t xml:space="preserve">1.63941133022308</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.55868220329285</t>
   </si>
   <si>
     <t xml:space="preserve">1.59283673763275</t>
@@ -2465,64 +2465,64 @@
     <t xml:space="preserve">1.55764722824097</t>
   </si>
   <si>
-    <t xml:space="preserve">1.58455669879913</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.59076714515686</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.57731199264526</t>
+    <t xml:space="preserve">1.58455681800842</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.59076702594757</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.57731211185455</t>
   </si>
   <si>
     <t xml:space="preserve">1.58817899227142</t>
   </si>
   <si>
-    <t xml:space="preserve">1.66011035442352</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.64872622489929</t>
+    <t xml:space="preserve">1.66011047363281</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.64872610569</t>
   </si>
   <si>
     <t xml:space="preserve">1.68132770061493</t>
   </si>
   <si>
-    <t xml:space="preserve">1.66787266731262</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.6714950799942</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.69943976402283</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.71651697158813</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.72169184684753</t>
+    <t xml:space="preserve">1.66787278652191</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.67149519920349</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.69943988323212</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.71651685237885</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.72169196605682</t>
   </si>
   <si>
     <t xml:space="preserve">1.72997164726257</t>
   </si>
   <si>
-    <t xml:space="preserve">1.78844845294952</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.80863010883331</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.79103541374207</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.81846308708191</t>
+    <t xml:space="preserve">1.7884486913681</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.80863034725189</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.79103553295135</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.81846272945404</t>
   </si>
   <si>
     <t xml:space="preserve">1.86451971530914</t>
   </si>
   <si>
-    <t xml:space="preserve">1.87331712245941</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.81225264072418</t>
+    <t xml:space="preserve">1.87331736087799</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.81225252151489</t>
   </si>
   <si>
     <t xml:space="preserve">1.8231201171875</t>
@@ -2534,49 +2534,49 @@
     <t xml:space="preserve">1.84588968753815</t>
   </si>
   <si>
-    <t xml:space="preserve">1.81794536113739</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.7987984418869</t>
+    <t xml:space="preserve">1.81794548034668</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.79879856109619</t>
   </si>
   <si>
     <t xml:space="preserve">1.80966544151306</t>
   </si>
   <si>
-    <t xml:space="preserve">1.83295261859894</t>
+    <t xml:space="preserve">1.83295249938965</t>
   </si>
   <si>
     <t xml:space="preserve">1.80500781536102</t>
   </si>
   <si>
-    <t xml:space="preserve">1.81587541103363</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.7993152141571</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.80552577972412</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.81639301776886</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.88263177871704</t>
+    <t xml:space="preserve">1.81587553024292</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.79931509494781</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.80552566051483</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.81639349460602</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.88263201713562</t>
   </si>
   <si>
     <t xml:space="preserve">1.90333127975464</t>
   </si>
   <si>
-    <t xml:space="preserve">1.94421339035034</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.97267520427704</t>
+    <t xml:space="preserve">1.94421362876892</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.97267496585846</t>
   </si>
   <si>
     <t xml:space="preserve">2.02649426460266</t>
   </si>
   <si>
-    <t xml:space="preserve">2.07927846908569</t>
+    <t xml:space="preserve">2.07927823066711</t>
   </si>
   <si>
     <t xml:space="preserve">2.10204792022705</t>
@@ -2588,19 +2588,19 @@
     <t xml:space="preserve">2.09066271781921</t>
   </si>
   <si>
-    <t xml:space="preserve">2.08962821960449</t>
+    <t xml:space="preserve">2.08962845802307</t>
   </si>
   <si>
     <t xml:space="preserve">2.10515260696411</t>
   </si>
   <si>
-    <t xml:space="preserve">2.10567045211792</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.06582379341125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.07358551025391</t>
+    <t xml:space="preserve">2.10567021369934</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.06582355499268</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.07358574867249</t>
   </si>
   <si>
     <t xml:space="preserve">2.0699634552002</t>
@@ -2609,19 +2609,19 @@
     <t xml:space="preserve">2.1367199420929</t>
   </si>
   <si>
-    <t xml:space="preserve">2.16155910491943</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.17604899406433</t>
+    <t xml:space="preserve">2.16155886650085</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.17604947090149</t>
   </si>
   <si>
     <t xml:space="preserve">2.20761632919312</t>
   </si>
   <si>
-    <t xml:space="preserve">2.18329358100891</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.21951818466187</t>
+    <t xml:space="preserve">2.18329381942749</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.21951794624329</t>
   </si>
   <si>
     <t xml:space="preserve">2.23556017875671</t>
@@ -2633,16 +2633,16 @@
     <t xml:space="preserve">2.24280571937561</t>
   </si>
   <si>
-    <t xml:space="preserve">2.25936484336853</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.28679251670837</t>
+    <t xml:space="preserve">2.25936508178711</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.28679203987122</t>
   </si>
   <si>
     <t xml:space="preserve">2.35303115844727</t>
   </si>
   <si>
-    <t xml:space="preserve">2.38459825515747</t>
+    <t xml:space="preserve">2.38459801673889</t>
   </si>
   <si>
     <t xml:space="preserve">2.37114310264587</t>
@@ -2651,10 +2651,10 @@
     <t xml:space="preserve">2.31421947479248</t>
   </si>
   <si>
-    <t xml:space="preserve">2.32715678215027</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.32146382331848</t>
+    <t xml:space="preserve">2.32715654373169</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.32146406173706</t>
   </si>
   <si>
     <t xml:space="preserve">2.30076432228088</t>
@@ -2663,31 +2663,31 @@
     <t xml:space="preserve">2.27074956893921</t>
   </si>
   <si>
-    <t xml:space="preserve">2.27437281608582</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.22779822349548</t>
+    <t xml:space="preserve">2.27437257766724</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.2277979850769</t>
   </si>
   <si>
     <t xml:space="preserve">2.2443573474884</t>
   </si>
   <si>
-    <t xml:space="preserve">2.27178454399109</t>
+    <t xml:space="preserve">2.27178478240967</t>
   </si>
   <si>
     <t xml:space="preserve">2.28368735313416</t>
   </si>
   <si>
-    <t xml:space="preserve">2.30593967437744</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.27851247787476</t>
+    <t xml:space="preserve">2.30593991279602</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.27851223945618</t>
   </si>
   <si>
     <t xml:space="preserve">2.30283403396606</t>
   </si>
   <si>
-    <t xml:space="preserve">2.29972910881042</t>
+    <t xml:space="preserve">2.299729347229</t>
   </si>
   <si>
     <t xml:space="preserve">2.33026099205017</t>
@@ -2696,31 +2696,31 @@
     <t xml:space="preserve">2.31318426132202</t>
   </si>
   <si>
-    <t xml:space="preserve">2.3421630859375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.3597583770752</t>
+    <t xml:space="preserve">2.34216332435608</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.35975813865662</t>
   </si>
   <si>
     <t xml:space="preserve">2.33698844909668</t>
   </si>
   <si>
-    <t xml:space="preserve">2.33388352394104</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.30490446090698</t>
+    <t xml:space="preserve">2.33388376235962</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.3049042224884</t>
   </si>
   <si>
     <t xml:space="preserve">2.31991124153137</t>
   </si>
   <si>
-    <t xml:space="preserve">2.37787008285522</t>
+    <t xml:space="preserve">2.37787055969238</t>
   </si>
   <si>
     <t xml:space="preserve">2.37631821632385</t>
   </si>
   <si>
-    <t xml:space="preserve">2.32767415046692</t>
+    <t xml:space="preserve">2.32767391204834</t>
   </si>
   <si>
     <t xml:space="preserve">2.33440113067627</t>
@@ -2729,31 +2729,31 @@
     <t xml:space="preserve">2.35665345191956</t>
   </si>
   <si>
-    <t xml:space="preserve">2.38873815536499</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.39080762863159</t>
+    <t xml:space="preserve">2.38873791694641</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.39080739021301</t>
   </si>
   <si>
     <t xml:space="preserve">2.38045835494995</t>
   </si>
   <si>
-    <t xml:space="preserve">2.3882200717926</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.36700344085693</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.36079335212708</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.37942290306091</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.36493325233459</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.39494729042053</t>
+    <t xml:space="preserve">2.38822031021118</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.36700320243835</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.36079359054565</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.37942314147949</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.36493301391602</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.39494776725769</t>
   </si>
   <si>
     <t xml:space="preserve">2.30749177932739</t>
@@ -2762,7 +2762,7 @@
     <t xml:space="preserve">2.30800914764404</t>
   </si>
   <si>
-    <t xml:space="preserve">2.29351925849915</t>
+    <t xml:space="preserve">2.29351902008057</t>
   </si>
   <si>
     <t xml:space="preserve">2.34009385108948</t>
@@ -2771,13 +2771,13 @@
     <t xml:space="preserve">2.31939387321472</t>
   </si>
   <si>
-    <t xml:space="preserve">2.23866558074951</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.14758682250977</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.19157314300537</t>
+    <t xml:space="preserve">2.23866581916809</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.14758658409119</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.19157338142395</t>
   </si>
   <si>
     <t xml:space="preserve">2.24073505401611</t>
@@ -2786,28 +2786,28 @@
     <t xml:space="preserve">2.26505756378174</t>
   </si>
   <si>
-    <t xml:space="preserve">2.24384093284607</t>
+    <t xml:space="preserve">2.24384045600891</t>
   </si>
   <si>
     <t xml:space="preserve">2.25263810157776</t>
   </si>
   <si>
-    <t xml:space="preserve">2.26298713684082</t>
+    <t xml:space="preserve">2.2629873752594</t>
   </si>
   <si>
     <t xml:space="preserve">2.34630346298218</t>
   </si>
   <si>
-    <t xml:space="preserve">2.32612133026123</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.40322709083557</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.14292907714844</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.13568472862244</t>
+    <t xml:space="preserve">2.32612180709839</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.40322732925415</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.14292931556702</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.13568449020386</t>
   </si>
   <si>
     <t xml:space="preserve">2.1703565120697</t>
@@ -2816,37 +2816,37 @@
     <t xml:space="preserve">2.10722327232361</t>
   </si>
   <si>
-    <t xml:space="preserve">1.98509466648102</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.98716497421265</t>
+    <t xml:space="preserve">1.98509442806244</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.98716521263123</t>
   </si>
   <si>
     <t xml:space="preserve">2.03115177154541</t>
   </si>
   <si>
-    <t xml:space="preserve">1.95508027076721</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.8624495267868</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.72065699100494</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.67615234851837</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.61508893966675</t>
+    <t xml:space="preserve">1.95508050918579</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.86244928836823</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.72065687179565</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.67615258693695</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.61508858203888</t>
   </si>
   <si>
     <t xml:space="preserve">1.58093452453613</t>
   </si>
   <si>
-    <t xml:space="preserve">1.36617600917816</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.29993712902069</t>
+    <t xml:space="preserve">1.36617588996887</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.2999370098114</t>
   </si>
   <si>
     <t xml:space="preserve">1.30304181575775</t>
@@ -2855,19 +2855,19 @@
     <t xml:space="preserve">1.07172310352325</t>
   </si>
   <si>
-    <t xml:space="preserve">1.31183910369873</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.21144616603851</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.2073061466217</t>
+    <t xml:space="preserve">1.31183922290802</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.21144604682922</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.20730638504028</t>
   </si>
   <si>
     <t xml:space="preserve">1.17522156238556</t>
   </si>
   <si>
-    <t xml:space="preserve">1.19333386421204</t>
+    <t xml:space="preserve">1.19333374500275</t>
   </si>
   <si>
     <t xml:space="preserve">1.33253860473633</t>
@@ -2879,43 +2879,43 @@
     <t xml:space="preserve">1.55712974071503</t>
   </si>
   <si>
-    <t xml:space="preserve">1.53280770778656</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.50279355049133</t>
+    <t xml:space="preserve">1.53280782699585</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.50279343128204</t>
   </si>
   <si>
     <t xml:space="preserve">1.40602290630341</t>
   </si>
   <si>
-    <t xml:space="preserve">1.40550518035889</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.44897425174713</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.40705740451813</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.39567267894745</t>
+    <t xml:space="preserve">1.40550529956818</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.44897437095642</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.40705716609955</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.39567279815674</t>
   </si>
   <si>
     <t xml:space="preserve">1.38894486427307</t>
   </si>
   <si>
-    <t xml:space="preserve">1.41585469245911</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.41016280651093</t>
+    <t xml:space="preserve">1.41585457324982</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.41016268730164</t>
   </si>
   <si>
     <t xml:space="preserve">1.34081816673279</t>
   </si>
   <si>
-    <t xml:space="preserve">1.35375559329987</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.29320931434631</t>
+    <t xml:space="preserve">1.35375547409058</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.2932094335556</t>
   </si>
   <si>
     <t xml:space="preserve">1.19799137115479</t>
@@ -2924,37 +2924,37 @@
     <t xml:space="preserve">1.14624226093292</t>
   </si>
   <si>
-    <t xml:space="preserve">1.15814459323883</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.1591796875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.10898280143738</t>
+    <t xml:space="preserve">1.15814447402954</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.15917956829071</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.1089825630188</t>
   </si>
   <si>
     <t xml:space="preserve">1.10743010044098</t>
   </si>
   <si>
-    <t xml:space="preserve">1.14468967914581</t>
+    <t xml:space="preserve">1.1446897983551</t>
   </si>
   <si>
     <t xml:space="preserve">1.09708070755005</t>
   </si>
   <si>
-    <t xml:space="preserve">1.12813031673431</t>
+    <t xml:space="preserve">1.12813019752502</t>
   </si>
   <si>
     <t xml:space="preserve">1.19902646541595</t>
   </si>
   <si>
-    <t xml:space="preserve">1.21817302703857</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.16538918018341</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.14054989814758</t>
+    <t xml:space="preserve">1.21817326545715</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.16538906097412</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.140549659729</t>
   </si>
   <si>
     <t xml:space="preserve">1.13847947120667</t>
@@ -2966,13 +2966,13 @@
     <t xml:space="preserve">1.10639560222626</t>
   </si>
   <si>
-    <t xml:space="preserve">1.09397506713867</t>
+    <t xml:space="preserve">1.09397530555725</t>
   </si>
   <si>
     <t xml:space="preserve">1.08673071861267</t>
   </si>
   <si>
-    <t xml:space="preserve">1.05050611495972</t>
+    <t xml:space="preserve">1.05050599575043</t>
   </si>
   <si>
     <t xml:space="preserve">1.04222619533539</t>
@@ -2984,43 +2984,43 @@
     <t xml:space="preserve">1.0803165435791</t>
   </si>
   <si>
-    <t xml:space="preserve">1.02012348175049</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.00243449211121</t>
+    <t xml:space="preserve">1.0201233625412</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.0024346113205</t>
   </si>
   <si>
     <t xml:space="preserve">0.983425855636597</t>
   </si>
   <si>
-    <t xml:space="preserve">0.984218239784241</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.986858248710632</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.0898209810257</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.12942159175873</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.17483115196228</t>
+    <t xml:space="preserve">0.98421847820282</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.986858129501343</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.08982086181641</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.12942171096802</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.17483103275299</t>
   </si>
   <si>
     <t xml:space="preserve">1.13364660739899</t>
   </si>
   <si>
-    <t xml:space="preserve">1.16163086891174</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.18275201320648</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.22076857089996</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.22129666805267</t>
+    <t xml:space="preserve">1.16163074970245</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.1827517747879</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.22076845169067</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.22129654884338</t>
   </si>
   <si>
     <t xml:space="preserve">1.34010016918182</t>
@@ -3029,13 +3029,13 @@
     <t xml:space="preserve">1.40504539012909</t>
   </si>
   <si>
-    <t xml:space="preserve">1.3849812746048</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.31528306007385</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.23132920265198</t>
+    <t xml:space="preserve">1.38498115539551</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.31528317928314</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.2313289642334</t>
   </si>
   <si>
     <t xml:space="preserve">1.20334410667419</t>
@@ -3044,7 +3044,7 @@
     <t xml:space="preserve">1.21443283557892</t>
   </si>
   <si>
-    <t xml:space="preserve">1.29416263103485</t>
+    <t xml:space="preserve">1.29416275024414</t>
   </si>
   <si>
     <t xml:space="preserve">1.26829028129578</t>
@@ -3059,10 +3059,10 @@
     <t xml:space="preserve">1.19806385040283</t>
   </si>
   <si>
-    <t xml:space="preserve">1.22763323783875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.1653265953064</t>
+    <t xml:space="preserve">1.22763311862946</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.16532683372498</t>
   </si>
   <si>
     <t xml:space="preserve">1.17430293560028</t>
@@ -3071,13 +3071,13 @@
     <t xml:space="preserve">1.1473742723465</t>
   </si>
   <si>
-    <t xml:space="preserve">1.16796720027924</t>
+    <t xml:space="preserve">1.16796731948853</t>
   </si>
   <si>
     <t xml:space="preserve">1.14526259899139</t>
   </si>
   <si>
-    <t xml:space="preserve">1.15371084213257</t>
+    <t xml:space="preserve">1.15371072292328</t>
   </si>
   <si>
     <t xml:space="preserve">1.14843058586121</t>
@@ -3089,16 +3089,16 @@
     <t xml:space="preserve">1.17007899284363</t>
   </si>
   <si>
-    <t xml:space="preserve">1.164799451828</t>
+    <t xml:space="preserve">1.16479957103729</t>
   </si>
   <si>
     <t xml:space="preserve">1.13417398929596</t>
   </si>
   <si>
-    <t xml:space="preserve">1.19120001792908</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.31581115722656</t>
+    <t xml:space="preserve">1.19120013713837</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.31581103801727</t>
   </si>
   <si>
     <t xml:space="preserve">1.31686735153198</t>
@@ -3113,22 +3113,22 @@
     <t xml:space="preserve">1.31317126750946</t>
   </si>
   <si>
-    <t xml:space="preserve">1.35858070850372</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.34590780735016</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.29944288730621</t>
+    <t xml:space="preserve">1.35858058929443</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.34590768814087</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.2994430065155</t>
   </si>
   <si>
     <t xml:space="preserve">1.27990627288818</t>
   </si>
   <si>
-    <t xml:space="preserve">1.22657668590546</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.23027288913727</t>
+    <t xml:space="preserve">1.22657692432404</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.23027276992798</t>
   </si>
   <si>
     <t xml:space="preserve">1.19067192077637</t>
@@ -3140,7 +3140,7 @@
     <t xml:space="preserve">1.12572586536407</t>
   </si>
   <si>
-    <t xml:space="preserve">1.09668564796448</t>
+    <t xml:space="preserve">1.09668552875519</t>
   </si>
   <si>
     <t xml:space="preserve">1.08242893218994</t>
@@ -3152,28 +3152,28 @@
     <t xml:space="preserve">1.23555302619934</t>
   </si>
   <si>
-    <t xml:space="preserve">1.25139319896698</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.25244951248169</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.22288084030151</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.22604870796204</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.23713731765747</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.21707260608673</t>
+    <t xml:space="preserve">1.25139331817627</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.2524493932724</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.2228809595108</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.22604882717133</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.23713743686676</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.21707248687744</t>
   </si>
   <si>
     <t xml:space="preserve">1.20387232303619</t>
   </si>
   <si>
-    <t xml:space="preserve">1.24030542373657</t>
+    <t xml:space="preserve">1.24030530452728</t>
   </si>
   <si>
     <t xml:space="preserve">1.23977720737457</t>
@@ -3182,13 +3182,13 @@
     <t xml:space="preserve">1.23080086708069</t>
   </si>
   <si>
-    <t xml:space="preserve">1.25667357444763</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.2149600982666</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.18222379684448</t>
+    <t xml:space="preserve">1.25667333602905</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.21496021747589</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.18222391605377</t>
   </si>
   <si>
     <t xml:space="preserve">1.17905509471893</t>
@@ -3209,16 +3209,16 @@
     <t xml:space="preserve">1.13100612163544</t>
   </si>
   <si>
-    <t xml:space="preserve">1.16004729270935</t>
+    <t xml:space="preserve">1.16004717350006</t>
   </si>
   <si>
     <t xml:space="preserve">1.15687847137451</t>
   </si>
   <si>
-    <t xml:space="preserve">1.15635061264038</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.14209473133087</t>
+    <t xml:space="preserve">1.15635049343109</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.14209485054016</t>
   </si>
   <si>
     <t xml:space="preserve">1.15054285526276</t>
@@ -3227,25 +3227,25 @@
     <t xml:space="preserve">1.14051043987274</t>
   </si>
   <si>
-    <t xml:space="preserve">1.09404492378235</t>
+    <t xml:space="preserve">1.09404504299164</t>
   </si>
   <si>
     <t xml:space="preserve">1.06447660923004</t>
   </si>
   <si>
-    <t xml:space="preserve">1.06658816337585</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.03490734100342</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.03226733207703</t>
+    <t xml:space="preserve">1.06658804416656</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.03490722179413</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.03226745128632</t>
   </si>
   <si>
     <t xml:space="preserve">1.05919623374939</t>
   </si>
   <si>
-    <t xml:space="preserve">1.0296276807785</t>
+    <t xml:space="preserve">1.02962779998779</t>
   </si>
   <si>
     <t xml:space="preserve">1.0496917963028</t>
@@ -3254,19 +3254,19 @@
     <t xml:space="preserve">1.02857148647308</t>
   </si>
   <si>
-    <t xml:space="preserve">1.00058650970459</t>
+    <t xml:space="preserve">1.00058662891388</t>
   </si>
   <si>
     <t xml:space="preserve">0.926720380783081</t>
   </si>
   <si>
-    <t xml:space="preserve">0.965333700180054</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.924770295619965</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.933350920677185</t>
+    <t xml:space="preserve">0.965333759784698</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.924770355224609</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.933351039886475</t>
   </si>
   <si>
     <t xml:space="preserve">0.938031375408173</t>
@@ -3275,22 +3275,22 @@
     <t xml:space="preserve">0.914239346981049</t>
   </si>
   <si>
-    <t xml:space="preserve">0.867435336112976</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.870945513248444</t>
+    <t xml:space="preserve">0.867435276508331</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.870945692062378</t>
   </si>
   <si>
     <t xml:space="preserve">0.866265177726746</t>
   </si>
   <si>
-    <t xml:space="preserve">0.936471402645111</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.923990190029144</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.01408803462982</t>
+    <t xml:space="preserve">0.936471283435822</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.9239901304245</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.01408791542053</t>
   </si>
   <si>
     <t xml:space="preserve">0.949342429637909</t>
@@ -3302,10 +3302,10 @@
     <t xml:space="preserve">0.938811540603638</t>
   </si>
   <si>
-    <t xml:space="preserve">0.929450511932373</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.871335566043854</t>
+    <t xml:space="preserve">0.929450750350952</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.871335625648499</t>
   </si>
   <si>
     <t xml:space="preserve">0.808540105819702</t>
@@ -3317,22 +3317,22 @@
     <t xml:space="preserve">0.793328762054443</t>
   </si>
   <si>
-    <t xml:space="preserve">0.822971403598785</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.844033241271973</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.863534867763519</t>
+    <t xml:space="preserve">0.82297146320343</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.844033300876617</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.863534986972809</t>
   </si>
   <si>
     <t xml:space="preserve">0.844813227653503</t>
   </si>
   <si>
-    <t xml:space="preserve">0.817510902881622</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.939201533794403</t>
+    <t xml:space="preserve">0.817510962486267</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.939201414585114</t>
   </si>
   <si>
     <t xml:space="preserve">0.931400716304779</t>
@@ -3341,7 +3341,7 @@
     <t xml:space="preserve">0.966503798961639</t>
   </si>
   <si>
-    <t xml:space="preserve">1.0292991399765</t>
+    <t xml:space="preserve">1.02929925918579</t>
   </si>
   <si>
     <t xml:space="preserve">1.04139041900635</t>
@@ -3350,19 +3350,19 @@
     <t xml:space="preserve">1.10496592521667</t>
   </si>
   <si>
-    <t xml:space="preserve">1.1119863986969</t>
+    <t xml:space="preserve">1.11198651790619</t>
   </si>
   <si>
     <t xml:space="preserve">1.15801060199738</t>
   </si>
   <si>
-    <t xml:space="preserve">1.18258261680603</t>
+    <t xml:space="preserve">1.18258273601532</t>
   </si>
   <si>
     <t xml:space="preserve">1.18531286716461</t>
   </si>
   <si>
-    <t xml:space="preserve">1.18921315670013</t>
+    <t xml:space="preserve">1.18921327590942</t>
   </si>
   <si>
     <t xml:space="preserve">1.1584005355835</t>
@@ -3377,7 +3377,7 @@
     <t xml:space="preserve">1.15918052196503</t>
   </si>
   <si>
-    <t xml:space="preserve">1.14669954776764</t>
+    <t xml:space="preserve">1.14669942855835</t>
   </si>
   <si>
     <t xml:space="preserve">1.15723037719727</t>
@@ -3386,28 +3386,28 @@
     <t xml:space="preserve">1.1486496925354</t>
   </si>
   <si>
-    <t xml:space="preserve">1.14240896701813</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.15020966529846</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.18336248397827</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.14435923099518</t>
+    <t xml:space="preserve">1.14240920543671</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.15020990371704</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.18336260318756</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.14435935020447</t>
   </si>
   <si>
     <t xml:space="preserve">1.14162909984589</t>
   </si>
   <si>
-    <t xml:space="preserve">1.15254998207092</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.13694858551025</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.14396929740906</t>
+    <t xml:space="preserve">1.15255010128021</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.13694870471954</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.14396917819977</t>
   </si>
   <si>
     <t xml:space="preserve">1.13265824317932</t>
@@ -3416,7 +3416,7 @@
     <t xml:space="preserve">1.08702445030212</t>
   </si>
   <si>
-    <t xml:space="preserve">1.11159634590149</t>
+    <t xml:space="preserve">1.11159646511078</t>
   </si>
   <si>
     <t xml:space="preserve">1.15450012683868</t>
@@ -3431,37 +3431,37 @@
     <t xml:space="preserve">1.14045894145966</t>
   </si>
   <si>
-    <t xml:space="preserve">1.14981985092163</t>
+    <t xml:space="preserve">1.14981973171234</t>
   </si>
   <si>
     <t xml:space="preserve">1.21105515956879</t>
   </si>
   <si>
-    <t xml:space="preserve">1.28594148159027</t>
+    <t xml:space="preserve">1.28594172000885</t>
   </si>
   <si>
     <t xml:space="preserve">1.27151036262512</t>
   </si>
   <si>
-    <t xml:space="preserve">1.29764270782471</t>
+    <t xml:space="preserve">1.29764258861542</t>
   </si>
   <si>
     <t xml:space="preserve">1.29959273338318</t>
   </si>
   <si>
-    <t xml:space="preserve">1.28360152244568</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.26331961154938</t>
+    <t xml:space="preserve">1.28360140323639</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.26331973075867</t>
   </si>
   <si>
     <t xml:space="preserve">1.25512886047363</t>
   </si>
   <si>
-    <t xml:space="preserve">1.28282117843628</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.26448965072632</t>
+    <t xml:space="preserve">1.28282129764557</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.26448976993561</t>
   </si>
   <si>
     <t xml:space="preserve">1.28633165359497</t>
@@ -3473,70 +3473,70 @@
     <t xml:space="preserve">1.22899675369263</t>
   </si>
   <si>
-    <t xml:space="preserve">1.19194352626801</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.2250964641571</t>
+    <t xml:space="preserve">1.19194328784943</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.22509634494781</t>
   </si>
   <si>
     <t xml:space="preserve">1.18882322311401</t>
   </si>
   <si>
-    <t xml:space="preserve">1.21573543548584</t>
+    <t xml:space="preserve">1.21573555469513</t>
   </si>
   <si>
     <t xml:space="preserve">1.19584381580353</t>
   </si>
   <si>
-    <t xml:space="preserve">1.20442461967468</t>
+    <t xml:space="preserve">1.20442450046539</t>
   </si>
   <si>
     <t xml:space="preserve">1.32455492019653</t>
   </si>
   <si>
-    <t xml:space="preserve">1.38696038722992</t>
+    <t xml:space="preserve">1.38696026802063</t>
   </si>
   <si>
     <t xml:space="preserve">1.48953926563263</t>
   </si>
   <si>
-    <t xml:space="preserve">1.45833647251129</t>
+    <t xml:space="preserve">1.45833671092987</t>
   </si>
   <si>
     <t xml:space="preserve">1.48212862014771</t>
   </si>
   <si>
-    <t xml:space="preserve">1.4552161693573</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.45248603820801</t>
+    <t xml:space="preserve">1.45521628856659</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.45248591899872</t>
   </si>
   <si>
     <t xml:space="preserve">1.46886742115021</t>
   </si>
   <si>
-    <t xml:space="preserve">1.44741559028625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.42089319229126</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.39632105827332</t>
+    <t xml:space="preserve">1.44741570949554</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.42089331150055</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.3963211774826</t>
   </si>
   <si>
     <t xml:space="preserve">1.45170593261719</t>
   </si>
   <si>
-    <t xml:space="preserve">1.43064403533936</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.43025410175323</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.45326602458954</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.41543281078339</t>
+    <t xml:space="preserve">1.43064415454865</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.43025422096252</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.45326614379883</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.41543292999268</t>
   </si>
   <si>
     <t xml:space="preserve">1.45287609100342</t>
@@ -3551,13 +3551,13 @@
     <t xml:space="preserve">1.50709080696106</t>
   </si>
   <si>
-    <t xml:space="preserve">1.54765427112579</t>
+    <t xml:space="preserve">1.5476541519165</t>
   </si>
   <si>
     <t xml:space="preserve">1.54102373123169</t>
   </si>
   <si>
-    <t xml:space="preserve">1.5281525850296</t>
+    <t xml:space="preserve">1.52815246582031</t>
   </si>
   <si>
     <t xml:space="preserve">1.53673350811005</t>
@@ -3566,19 +3566,19 @@
     <t xml:space="preserve">1.51879191398621</t>
   </si>
   <si>
-    <t xml:space="preserve">1.55233478546143</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.6006988286972</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.58899784088135</t>
+    <t xml:space="preserve">1.55233466625214</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.60069894790649</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.58899772167206</t>
   </si>
   <si>
     <t xml:space="preserve">1.52581226825714</t>
   </si>
   <si>
-    <t xml:space="preserve">1.48758900165558</t>
+    <t xml:space="preserve">1.48758912086487</t>
   </si>
   <si>
     <t xml:space="preserve">1.48602890968323</t>
@@ -3593,37 +3593,37 @@
     <t xml:space="preserve">1.49616980552673</t>
   </si>
   <si>
-    <t xml:space="preserve">1.48056852817535</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.48173844814301</t>
+    <t xml:space="preserve">1.48056840896606</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.48173868656158</t>
   </si>
   <si>
     <t xml:space="preserve">1.46379709243774</t>
   </si>
   <si>
-    <t xml:space="preserve">1.48329877853394</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.48134863376617</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.47510814666748</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.45014572143555</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.45872640609741</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.48485887050629</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.46808743476868</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.47666811943054</t>
+    <t xml:space="preserve">1.48329865932465</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.48134875297546</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.47510802745819</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.45014584064484</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.45872664451599</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.48485898971558</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.46808755397797</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.47666800022125</t>
   </si>
   <si>
     <t xml:space="preserve">1.47549796104431</t>
@@ -3632,10 +3632,10 @@
     <t xml:space="preserve">1.52191209793091</t>
   </si>
   <si>
-    <t xml:space="preserve">1.44000506401062</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.40802216529846</t>
+    <t xml:space="preserve">1.44000482559204</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.40802204608917</t>
   </si>
   <si>
     <t xml:space="preserve">1.41036236286163</t>
@@ -3644,16 +3644,16 @@
     <t xml:space="preserve">1.41738295555115</t>
   </si>
   <si>
-    <t xml:space="preserve">1.46106672286987</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.44507527351379</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.47744810581207</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.46847748756409</t>
+    <t xml:space="preserve">1.46106684207916</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.44507539272308</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.47744834423065</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.46847760677338</t>
   </si>
   <si>
     <t xml:space="preserve">1.4622368812561</t>
@@ -3662,10 +3662,10 @@
     <t xml:space="preserve">1.47900831699371</t>
   </si>
   <si>
-    <t xml:space="preserve">1.50787079334259</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.50046026706696</t>
+    <t xml:space="preserve">1.5078706741333</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.50046014785767</t>
   </si>
   <si>
     <t xml:space="preserve">1.55857527256012</t>
@@ -3674,7 +3674,7 @@
     <t xml:space="preserve">1.57261645793915</t>
   </si>
   <si>
-    <t xml:space="preserve">1.54921436309814</t>
+    <t xml:space="preserve">1.54921448230743</t>
   </si>
   <si>
     <t xml:space="preserve">1.56403577327728</t>
@@ -3686,31 +3686,31 @@
     <t xml:space="preserve">1.57183659076691</t>
   </si>
   <si>
-    <t xml:space="preserve">1.54219365119934</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.52776253223419</t>
+    <t xml:space="preserve">1.54219377040863</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.52776265144348</t>
   </si>
   <si>
     <t xml:space="preserve">1.55584502220154</t>
   </si>
   <si>
-    <t xml:space="preserve">1.65574705600739</t>
+    <t xml:space="preserve">1.65574717521667</t>
   </si>
   <si>
     <t xml:space="preserve">1.6923645734787</t>
   </si>
   <si>
-    <t xml:space="preserve">1.61116921901703</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.63186597824097</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.62151765823364</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.61435341835022</t>
+    <t xml:space="preserve">1.61116909980774</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.63186609745026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.62151753902435</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.61435353755951</t>
   </si>
   <si>
     <t xml:space="preserve">1.61912953853607</t>
@@ -3725,7 +3725,7 @@
     <t xml:space="preserve">1.60957729816437</t>
   </si>
   <si>
-    <t xml:space="preserve">1.63107013702393</t>
+    <t xml:space="preserve">1.63107001781464</t>
   </si>
   <si>
     <t xml:space="preserve">1.62072169780731</t>
@@ -3740,7 +3740,7 @@
     <t xml:space="preserve">1.6167414188385</t>
   </si>
   <si>
-    <t xml:space="preserve">1.62470161914825</t>
+    <t xml:space="preserve">1.62470173835754</t>
   </si>
   <si>
     <t xml:space="preserve">1.59922885894775</t>
@@ -3749,10 +3749,10 @@
     <t xml:space="preserve">1.57693982124329</t>
   </si>
   <si>
-    <t xml:space="preserve">1.56539738178253</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.52997410297394</t>
+    <t xml:space="preserve">1.56539762020111</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.52997398376465</t>
   </si>
   <si>
     <t xml:space="preserve">1.54470062255859</t>
@@ -3776,31 +3776,31 @@
     <t xml:space="preserve">1.45395290851593</t>
   </si>
   <si>
-    <t xml:space="preserve">1.46111726760864</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.46987354755402</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.4595251083374</t>
+    <t xml:space="preserve">1.46111714839935</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.46987366676331</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.45952522754669</t>
   </si>
   <si>
     <t xml:space="preserve">1.47106766700745</t>
   </si>
   <si>
-    <t xml:space="preserve">1.43206214904785</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.41932547092438</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.37315571308136</t>
+    <t xml:space="preserve">1.43206202983856</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.41932535171509</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.37315559387207</t>
   </si>
   <si>
     <t xml:space="preserve">1.40420091152191</t>
   </si>
   <si>
-    <t xml:space="preserve">1.41056907176971</t>
+    <t xml:space="preserve">1.410569190979</t>
   </si>
   <si>
     <t xml:space="preserve">1.36240923404694</t>
@@ -3809,7 +3809,7 @@
     <t xml:space="preserve">1.35643899440765</t>
   </si>
   <si>
-    <t xml:space="preserve">1.34529459476471</t>
+    <t xml:space="preserve">1.34529447555542</t>
   </si>
   <si>
     <t xml:space="preserve">1.30191075801849</t>
@@ -3824,7 +3824,7 @@
     <t xml:space="preserve">1.26171112060547</t>
   </si>
   <si>
-    <t xml:space="preserve">1.28399991989136</t>
+    <t xml:space="preserve">1.28400015830994</t>
   </si>
   <si>
     <t xml:space="preserve">1.28519415855408</t>
@@ -3836,10 +3836,10 @@
     <t xml:space="preserve">1.28957223892212</t>
   </si>
   <si>
-    <t xml:space="preserve">1.29076623916626</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.29434847831726</t>
+    <t xml:space="preserve">1.29076635837555</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.29434859752655</t>
   </si>
   <si>
     <t xml:space="preserve">1.31066703796387</t>
@@ -3857,7 +3857,7 @@
     <t xml:space="preserve">1.43922626972198</t>
   </si>
   <si>
-    <t xml:space="preserve">1.43604218959808</t>
+    <t xml:space="preserve">1.43604207038879</t>
   </si>
   <si>
     <t xml:space="preserve">1.43046998977661</t>
@@ -3872,16 +3872,16 @@
     <t xml:space="preserve">1.45474898815155</t>
   </si>
   <si>
-    <t xml:space="preserve">1.4368382692337</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.41136515140533</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.42091751098633</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.39783263206482</t>
+    <t xml:space="preserve">1.43683815002441</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.41136527061462</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.42091763019562</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.39783275127411</t>
   </si>
   <si>
     <t xml:space="preserve">1.39305651187897</t>
@@ -3893,19 +3893,19 @@
     <t xml:space="preserve">1.42808187007904</t>
   </si>
   <si>
-    <t xml:space="preserve">1.45793318748474</t>
+    <t xml:space="preserve">1.45793306827545</t>
   </si>
   <si>
     <t xml:space="preserve">1.43882834911346</t>
   </si>
   <si>
-    <t xml:space="preserve">1.46151530742645</t>
+    <t xml:space="preserve">1.46151518821716</t>
   </si>
   <si>
     <t xml:space="preserve">1.44440054893494</t>
   </si>
   <si>
-    <t xml:space="preserve">1.46668946743011</t>
+    <t xml:space="preserve">1.46668934822083</t>
   </si>
   <si>
     <t xml:space="preserve">1.4758437871933</t>
@@ -3914,10 +3914,10 @@
     <t xml:space="preserve">1.4690774679184</t>
   </si>
   <si>
-    <t xml:space="preserve">1.48619222640991</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.44718658924103</t>
+    <t xml:space="preserve">1.48619210720062</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.44718670845032</t>
   </si>
   <si>
     <t xml:space="preserve">1.43644022941589</t>
@@ -3932,64 +3932,64 @@
     <t xml:space="preserve">1.44081830978394</t>
   </si>
   <si>
-    <t xml:space="preserve">1.42370367050171</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.3476824760437</t>
+    <t xml:space="preserve">1.423703789711</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.34768259525299</t>
   </si>
   <si>
     <t xml:space="preserve">1.36519539356232</t>
   </si>
   <si>
-    <t xml:space="preserve">1.40499699115753</t>
+    <t xml:space="preserve">1.40499687194824</t>
   </si>
   <si>
     <t xml:space="preserve">1.42449975013733</t>
   </si>
   <si>
-    <t xml:space="preserve">1.45992302894592</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.51604342460632</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.5084810256958</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.54708874225616</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.53873038291931</t>
+    <t xml:space="preserve">1.45992314815521</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.51604330539703</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.50848126411438</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.54708886146545</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.53873026371002</t>
   </si>
   <si>
     <t xml:space="preserve">1.57574594020844</t>
   </si>
   <si>
-    <t xml:space="preserve">1.56261122226715</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.6175377368927</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.60002470016479</t>
+    <t xml:space="preserve">1.56261134147644</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.61753761768341</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.60002481937408</t>
   </si>
   <si>
     <t xml:space="preserve">1.61833357810974</t>
   </si>
   <si>
-    <t xml:space="preserve">1.6438068151474</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.64539849758148</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.63903057575226</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.63982653617859</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.64221465587616</t>
+    <t xml:space="preserve">1.64380657672882</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.64539873600006</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.63903045654297</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.63982617855072</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.64221453666687</t>
   </si>
   <si>
     <t xml:space="preserve">1.65415501594543</t>
@@ -4001,10 +4001,10 @@
     <t xml:space="preserve">1.6294778585434</t>
   </si>
   <si>
-    <t xml:space="preserve">1.63345813751221</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.59365653991699</t>
+    <t xml:space="preserve">1.6334582567215</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.59365665912628</t>
   </si>
   <si>
     <t xml:space="preserve">1.61196541786194</t>
@@ -4013,7 +4013,7 @@
     <t xml:space="preserve">1.50808310508728</t>
   </si>
   <si>
-    <t xml:space="preserve">1.49932670593262</t>
+    <t xml:space="preserve">1.49932658672333</t>
   </si>
   <si>
     <t xml:space="preserve">1.52639186382294</t>
@@ -4025,16 +4025,16 @@
     <t xml:space="preserve">1.50609290599823</t>
   </si>
   <si>
-    <t xml:space="preserve">1.53196406364441</t>
+    <t xml:space="preserve">1.5319641828537</t>
   </si>
   <si>
     <t xml:space="preserve">1.52758586406708</t>
   </si>
   <si>
-    <t xml:space="preserve">1.52002370357513</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.53116798400879</t>
+    <t xml:space="preserve">1.52002358436584</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.5311678647995</t>
   </si>
   <si>
     <t xml:space="preserve">1.52121758460999</t>
@@ -4046,16 +4046,16 @@
     <t xml:space="preserve">1.51325726509094</t>
   </si>
   <si>
-    <t xml:space="preserve">1.47027158737183</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.4300719499588</t>
+    <t xml:space="preserve">1.47027170658112</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.43007183074951</t>
   </si>
   <si>
     <t xml:space="preserve">1.43564414978027</t>
   </si>
   <si>
-    <t xml:space="preserve">1.42887783050537</t>
+    <t xml:space="preserve">1.42887794971466</t>
   </si>
   <si>
     <t xml:space="preserve">1.41176319122314</t>
@@ -4064,22 +4064,22 @@
     <t xml:space="preserve">1.35086679458618</t>
   </si>
   <si>
-    <t xml:space="preserve">1.34012031555176</t>
+    <t xml:space="preserve">1.34012043476105</t>
   </si>
   <si>
     <t xml:space="preserve">1.33892619609833</t>
   </si>
   <si>
-    <t xml:space="preserve">1.37753391265869</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.3643993139267</t>
+    <t xml:space="preserve">1.3775337934494</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.36439943313599</t>
   </si>
   <si>
     <t xml:space="preserve">1.35166275501251</t>
   </si>
   <si>
-    <t xml:space="preserve">1.39425039291382</t>
+    <t xml:space="preserve">1.39425051212311</t>
   </si>
   <si>
     <t xml:space="preserve">1.40619099140167</t>
@@ -4103,28 +4103,28 @@
     <t xml:space="preserve">1.41375339031219</t>
   </si>
   <si>
-    <t xml:space="preserve">1.37912583351135</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.41494750976562</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.40260875225067</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.42569375038147</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.4432065486908</t>
+    <t xml:space="preserve">1.37912571430206</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.41494739055634</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.40260887145996</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.42569363117218</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.44320642948151</t>
   </si>
   <si>
     <t xml:space="preserve">1.45435094833374</t>
   </si>
   <si>
-    <t xml:space="preserve">1.45116674900055</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.50052094459534</t>
+    <t xml:space="preserve">1.45116662979126</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.50052082538605</t>
   </si>
   <si>
     <t xml:space="preserve">1.52917790412903</t>
@@ -4139,10 +4139,10 @@
     <t xml:space="preserve">1.53475022315979</t>
   </si>
   <si>
-    <t xml:space="preserve">1.56181538105011</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.55624306201935</t>
+    <t xml:space="preserve">1.56181526184082</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.55624294281006</t>
   </si>
   <si>
     <t xml:space="preserve">1.54111838340759</t>
@@ -4151,40 +4151,40 @@
     <t xml:space="preserve">1.52678990364075</t>
   </si>
   <si>
-    <t xml:space="preserve">1.49813270568848</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.42847990989685</t>
+    <t xml:space="preserve">1.49813282489777</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.42848002910614</t>
   </si>
   <si>
     <t xml:space="preserve">1.42330574989319</t>
   </si>
   <si>
-    <t xml:space="preserve">1.48818230628967</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.52320754528046</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.46509730815887</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.4762419462204</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.54350662231445</t>
+    <t xml:space="preserve">1.48818242549896</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.52320766448975</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.46509742736816</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.47624182701111</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.54350650310516</t>
   </si>
   <si>
     <t xml:space="preserve">1.57375574111938</t>
   </si>
   <si>
-    <t xml:space="preserve">1.5578351020813</t>
+    <t xml:space="preserve">1.55783522129059</t>
   </si>
   <si>
     <t xml:space="preserve">1.61514949798584</t>
   </si>
   <si>
-    <t xml:space="preserve">1.61276149749756</t>
+    <t xml:space="preserve">1.61276137828827</t>
   </si>
   <si>
     <t xml:space="preserve">1.63743841648102</t>
@@ -4193,7 +4193,7 @@
     <t xml:space="preserve">1.574551820755</t>
   </si>
   <si>
-    <t xml:space="preserve">1.7186336517334</t>
+    <t xml:space="preserve">1.71863353252411</t>
   </si>
   <si>
     <t xml:space="preserve">1.69793665409088</t>
@@ -4202,28 +4202,28 @@
     <t xml:space="preserve">1.6071891784668</t>
   </si>
   <si>
-    <t xml:space="preserve">1.56022322177887</t>
+    <t xml:space="preserve">1.56022334098816</t>
   </si>
   <si>
     <t xml:space="preserve">1.44161450862885</t>
   </si>
   <si>
-    <t xml:space="preserve">1.46788358688354</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.32260751724243</t>
+    <t xml:space="preserve">1.46788346767426</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.32260763645172</t>
   </si>
   <si>
     <t xml:space="preserve">1.31743335723877</t>
   </si>
   <si>
-    <t xml:space="preserve">1.24857652187347</t>
+    <t xml:space="preserve">1.24857664108276</t>
   </si>
   <si>
     <t xml:space="preserve">1.11643528938293</t>
   </si>
   <si>
-    <t xml:space="preserve">1.05872297286987</t>
+    <t xml:space="preserve">1.05872285366058</t>
   </si>
   <si>
     <t xml:space="preserve">1.11563920974731</t>
@@ -4235,34 +4235,34 @@
     <t xml:space="preserve">1.13514196872711</t>
   </si>
   <si>
-    <t xml:space="preserve">1.12877380847931</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.17494368553162</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.19882452487946</t>
+    <t xml:space="preserve">1.12877357006073</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.17494356632233</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.19882464408875</t>
   </si>
   <si>
     <t xml:space="preserve">1.28678619861603</t>
   </si>
   <si>
-    <t xml:space="preserve">1.25773096084595</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.2497706413269</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.2660893201828</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.24698436260223</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.23464608192444</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.243004322052</t>
+    <t xml:space="preserve">1.25773084163666</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.24977076053619</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.26608943939209</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.24698448181152</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.23464596271515</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.24300444126129</t>
   </si>
   <si>
     <t xml:space="preserve">1.25892508029938</t>
@@ -4271,16 +4271,16 @@
     <t xml:space="preserve">1.33295607566833</t>
   </si>
   <si>
-    <t xml:space="preserve">1.30668699741364</t>
+    <t xml:space="preserve">1.30668687820435</t>
   </si>
   <si>
     <t xml:space="preserve">1.26529324054718</t>
   </si>
   <si>
-    <t xml:space="preserve">1.27922368049622</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.22429764270782</t>
+    <t xml:space="preserve">1.27922379970551</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.22429752349854</t>
   </si>
   <si>
     <t xml:space="preserve">1.22628772258759</t>
@@ -4289,22 +4289,22 @@
     <t xml:space="preserve">1.27484571933746</t>
   </si>
   <si>
-    <t xml:space="preserve">1.27285552024841</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.23225784301758</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.23504400253296</t>
+    <t xml:space="preserve">1.2728556394577</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.23225796222687</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.23504412174225</t>
   </si>
   <si>
     <t xml:space="preserve">1.24778056144714</t>
   </si>
   <si>
-    <t xml:space="preserve">1.25335276126862</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.29753255844116</t>
+    <t xml:space="preserve">1.25335288047791</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.29753267765045</t>
   </si>
   <si>
     <t xml:space="preserve">1.30628895759583</t>
@@ -4313,10 +4313,10 @@
     <t xml:space="preserve">1.28758215904236</t>
   </si>
   <si>
-    <t xml:space="preserve">1.27404952049255</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.2593230009079</t>
+    <t xml:space="preserve">1.27404963970184</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.25932312011719</t>
   </si>
   <si>
     <t xml:space="preserve">1.26847743988037</t>
@@ -4325,40 +4325,40 @@
     <t xml:space="preserve">1.26011908054352</t>
   </si>
   <si>
-    <t xml:space="preserve">1.27763175964355</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.26927328109741</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.23822820186615</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.21912348270416</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.22071540355682</t>
+    <t xml:space="preserve">1.27763187885284</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.2692734003067</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.23822832107544</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.21912324428558</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.22071552276611</t>
   </si>
   <si>
     <t xml:space="preserve">1.21116304397583</t>
   </si>
   <si>
-    <t xml:space="preserve">1.35325491428375</t>
+    <t xml:space="preserve">1.35325479507446</t>
   </si>
   <si>
     <t xml:space="preserve">1.38629019260406</t>
   </si>
   <si>
-    <t xml:space="preserve">1.38668823242188</t>
+    <t xml:space="preserve">1.38668811321259</t>
   </si>
   <si>
     <t xml:space="preserve">1.3739515542984</t>
   </si>
   <si>
-    <t xml:space="preserve">1.40539503097534</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.39862871170044</t>
+    <t xml:space="preserve">1.40539491176605</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.39862859249115</t>
   </si>
   <si>
     <t xml:space="preserve">1.40738499164581</t>
@@ -4367,16 +4367,16 @@
     <t xml:space="preserve">1.39027047157288</t>
   </si>
   <si>
-    <t xml:space="preserve">1.48383438587189</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.49949705600739</t>
+    <t xml:space="preserve">1.4838342666626</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.49949717521667</t>
   </si>
   <si>
     <t xml:space="preserve">1.54153907299042</t>
   </si>
   <si>
-    <t xml:space="preserve">1.56049919128418</t>
+    <t xml:space="preserve">1.56049907207489</t>
   </si>
   <si>
     <t xml:space="preserve">1.55390429496765</t>
@@ -4394,7 +4394,7 @@
     <t xml:space="preserve">1.58976376056671</t>
   </si>
   <si>
-    <t xml:space="preserve">1.53576862812042</t>
+    <t xml:space="preserve">1.53576850891113</t>
   </si>
   <si>
     <t xml:space="preserve">1.59182453155518</t>
@@ -4415,40 +4415,40 @@
     <t xml:space="preserve">1.35482311248779</t>
   </si>
   <si>
-    <t xml:space="preserve">1.36430335044861</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.41788613796234</t>
+    <t xml:space="preserve">1.36430323123932</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.41788625717163</t>
   </si>
   <si>
     <t xml:space="preserve">1.35770845413208</t>
   </si>
   <si>
-    <t xml:space="preserve">1.38326346874237</t>
+    <t xml:space="preserve">1.38326334953308</t>
   </si>
   <si>
     <t xml:space="preserve">1.40799403190613</t>
   </si>
   <si>
-    <t xml:space="preserve">1.41458868980408</t>
+    <t xml:space="preserve">1.41458880901337</t>
   </si>
   <si>
     <t xml:space="preserve">1.41252791881561</t>
   </si>
   <si>
-    <t xml:space="preserve">1.3445188999176</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.38820958137512</t>
+    <t xml:space="preserve">1.34451878070831</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.38820946216583</t>
   </si>
   <si>
     <t xml:space="preserve">1.36718845367432</t>
   </si>
   <si>
-    <t xml:space="preserve">1.36512768268585</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.34493112564087</t>
+    <t xml:space="preserve">1.36512756347656</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.34493100643158</t>
   </si>
   <si>
     <t xml:space="preserve">1.2921724319458</t>
@@ -4457,28 +4457,28 @@
     <t xml:space="preserve">1.25219142436981</t>
   </si>
   <si>
-    <t xml:space="preserve">1.25136697292328</t>
+    <t xml:space="preserve">1.25136709213257</t>
   </si>
   <si>
     <t xml:space="preserve">1.18789184093475</t>
   </si>
   <si>
-    <t xml:space="preserve">1.16934382915497</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.22993385791779</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.24477219581604</t>
+    <t xml:space="preserve">1.16934394836426</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.2299337387085</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.24477207660675</t>
   </si>
   <si>
     <t xml:space="preserve">1.18830394744873</t>
   </si>
   <si>
-    <t xml:space="preserve">1.15903949737549</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.128950715065</t>
+    <t xml:space="preserve">1.15903961658478</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.12895059585571</t>
   </si>
   <si>
     <t xml:space="preserve">1.05929291248322</t>
@@ -4487,7 +4487,7 @@
     <t xml:space="preserve">1.06588768959045</t>
   </si>
   <si>
-    <t xml:space="preserve">1.07990157604218</t>
+    <t xml:space="preserve">1.07990169525146</t>
   </si>
   <si>
     <t xml:space="preserve">1.15326905250549</t>
@@ -4496,7 +4496,7 @@
     <t xml:space="preserve">1.12029492855072</t>
   </si>
   <si>
-    <t xml:space="preserve">1.08525991439819</t>
+    <t xml:space="preserve">1.0852597951889</t>
   </si>
   <si>
     <t xml:space="preserve">1.06794857978821</t>
@@ -4505,10 +4505,10 @@
     <t xml:space="preserve">1.09556436538696</t>
   </si>
   <si>
-    <t xml:space="preserve">1.0650634765625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.08567225933075</t>
+    <t xml:space="preserve">1.06506335735321</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.08567214012146</t>
   </si>
   <si>
     <t xml:space="preserve">1.08814513683319</t>
@@ -4517,7 +4517,7 @@
     <t xml:space="preserve">1.11287581920624</t>
   </si>
   <si>
-    <t xml:space="preserve">1.12482881546021</t>
+    <t xml:space="preserve">1.12482905387878</t>
   </si>
   <si>
     <t xml:space="preserve">1.1433767080307</t>
@@ -4535,16 +4535,16 @@
     <t xml:space="preserve">1.32720744609833</t>
   </si>
   <si>
-    <t xml:space="preserve">1.33792412281036</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.36842501163483</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.34987711906433</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.35647201538086</t>
+    <t xml:space="preserve">1.33792400360107</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.36842489242554</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.34987723827362</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.35647189617157</t>
   </si>
   <si>
     <t xml:space="preserve">1.35070145130157</t>
@@ -4562,13 +4562,13 @@
     <t xml:space="preserve">1.28021931648254</t>
   </si>
   <si>
-    <t xml:space="preserve">1.2608470916748</t>
+    <t xml:space="preserve">1.26084697246552</t>
   </si>
   <si>
     <t xml:space="preserve">1.22004163265228</t>
   </si>
   <si>
-    <t xml:space="preserve">1.22045373916626</t>
+    <t xml:space="preserve">1.22045385837555</t>
   </si>
   <si>
     <t xml:space="preserve">1.24106252193451</t>
@@ -4583,16 +4583,16 @@
     <t xml:space="preserve">1.25301575660706</t>
   </si>
   <si>
-    <t xml:space="preserve">1.21550762653351</t>
+    <t xml:space="preserve">1.2155077457428</t>
   </si>
   <si>
     <t xml:space="preserve">1.21798062324524</t>
   </si>
   <si>
-    <t xml:space="preserve">1.20066940784454</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.23776531219482</t>
+    <t xml:space="preserve">1.20066928863525</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.23776519298553</t>
   </si>
   <si>
     <t xml:space="preserve">1.27609753608704</t>
@@ -4601,13 +4601,13 @@
     <t xml:space="preserve">1.33957278728485</t>
   </si>
   <si>
-    <t xml:space="preserve">1.32597088813782</t>
+    <t xml:space="preserve">1.32597100734711</t>
   </si>
   <si>
     <t xml:space="preserve">1.3758442401886</t>
   </si>
   <si>
-    <t xml:space="preserve">1.38120257854462</t>
+    <t xml:space="preserve">1.38120245933533</t>
   </si>
   <si>
     <t xml:space="preserve">1.38985824584961</t>
@@ -4616,7 +4616,7 @@
     <t xml:space="preserve">1.39686524868011</t>
   </si>
   <si>
-    <t xml:space="preserve">1.37295889854431</t>
+    <t xml:space="preserve">1.3729590177536</t>
   </si>
   <si>
     <t xml:space="preserve">1.38408780097961</t>
@@ -4631,13 +4631,13 @@
     <t xml:space="preserve">1.37172245979309</t>
   </si>
   <si>
-    <t xml:space="preserve">1.3416336774826</t>
+    <t xml:space="preserve">1.34163355827332</t>
   </si>
   <si>
     <t xml:space="preserve">1.32020044326782</t>
   </si>
   <si>
-    <t xml:space="preserve">1.28269243240356</t>
+    <t xml:space="preserve">1.28269231319427</t>
   </si>
   <si>
     <t xml:space="preserve">1.30330121517181</t>
@@ -4649,16 +4649,16 @@
     <t xml:space="preserve">1.38491201400757</t>
   </si>
   <si>
-    <t xml:space="preserve">1.3589448928833</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.31731522083282</t>
+    <t xml:space="preserve">1.35894501209259</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.31731510162354</t>
   </si>
   <si>
     <t xml:space="preserve">1.33462655544281</t>
   </si>
   <si>
-    <t xml:space="preserve">1.31855154037476</t>
+    <t xml:space="preserve">1.31855165958405</t>
   </si>
   <si>
     <t xml:space="preserve">1.30824744701385</t>
@@ -4676,28 +4676,28 @@
     <t xml:space="preserve">1.40181136131287</t>
   </si>
   <si>
-    <t xml:space="preserve">1.41211581230164</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.41664958000183</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.43560981750488</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.4764152765274</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.46734738349915</t>
+    <t xml:space="preserve">1.41211569309235</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.41664969921112</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.43560969829559</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.47641515731812</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.46734726428986</t>
   </si>
   <si>
     <t xml:space="preserve">1.4694082736969</t>
   </si>
   <si>
-    <t xml:space="preserve">1.51103794574738</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.52093029022217</t>
+    <t xml:space="preserve">1.51103782653809</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.52093017101288</t>
   </si>
   <si>
     <t xml:space="preserve">1.54359984397888</t>
@@ -4715,7 +4715,7 @@
     <t xml:space="preserve">1.65942144393921</t>
   </si>
   <si>
-    <t xml:space="preserve">1.68992245197296</t>
+    <t xml:space="preserve">1.68992257118225</t>
   </si>
   <si>
     <t xml:space="preserve">1.56008696556091</t>
@@ -4727,7 +4727,7 @@
     <t xml:space="preserve">1.54854595661163</t>
   </si>
   <si>
-    <t xml:space="preserve">1.52711284160614</t>
+    <t xml:space="preserve">1.52711296081543</t>
   </si>
   <si>
     <t xml:space="preserve">1.54648530483246</t>
@@ -4748,13 +4748,13 @@
     <t xml:space="preserve">1.59965586662292</t>
   </si>
   <si>
-    <t xml:space="preserve">1.61284565925598</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.62356209754944</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.60872399806976</t>
+    <t xml:space="preserve">1.61284554004669</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.62356197834015</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.60872387886047</t>
   </si>
   <si>
     <t xml:space="preserve">1.61573076248169</t>
@@ -4775,7 +4775,7 @@
     <t xml:space="preserve">1.59718286991119</t>
   </si>
   <si>
-    <t xml:space="preserve">1.60171687602997</t>
+    <t xml:space="preserve">1.60171675682068</t>
   </si>
   <si>
     <t xml:space="preserve">1.60954809188843</t>
@@ -4784,19 +4784,19 @@
     <t xml:space="preserve">1.60913598537445</t>
   </si>
   <si>
-    <t xml:space="preserve">1.61902809143066</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.60707497596741</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.55101907253265</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.54978263378143</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.53782951831818</t>
+    <t xml:space="preserve">1.61902821063995</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.6070750951767</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.55101919174194</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.54978251457214</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.53782939910889</t>
   </si>
   <si>
     <t xml:space="preserve">1.60418975353241</t>
@@ -4811,34 +4811,34 @@
     <t xml:space="preserve">1.58152008056641</t>
   </si>
   <si>
-    <t xml:space="preserve">1.61531853675842</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.63633954524994</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.67920589447021</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.67343533039093</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.71712589263916</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.72536969184875</t>
+    <t xml:space="preserve">1.61531865596771</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.63633942604065</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.67920577526093</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.67343544960022</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.71712601184845</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.72536957263947</t>
   </si>
   <si>
     <t xml:space="preserve">1.73938369750977</t>
   </si>
   <si>
-    <t xml:space="preserve">1.73855936527252</t>
+    <t xml:space="preserve">1.73855924606323</t>
   </si>
   <si>
     <t xml:space="preserve">1.74845159053802</t>
   </si>
   <si>
-    <t xml:space="preserve">1.80533194541931</t>
+    <t xml:space="preserve">1.80533182621002</t>
   </si>
   <si>
     <t xml:space="preserve">1.82511639595032</t>
@@ -4847,10 +4847,10 @@
     <t xml:space="preserve">1.7970883846283</t>
   </si>
   <si>
-    <t xml:space="preserve">1.8564418554306</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.85479295253754</t>
+    <t xml:space="preserve">1.85644161701202</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.85479319095612</t>
   </si>
   <si>
     <t xml:space="preserve">1.89024019241333</t>
@@ -4862,22 +4862,22 @@
     <t xml:space="preserve">1.92898452281952</t>
   </si>
   <si>
-    <t xml:space="preserve">1.93310654163361</t>
+    <t xml:space="preserve">1.93310630321503</t>
   </si>
   <si>
     <t xml:space="preserve">1.97349977493286</t>
   </si>
   <si>
-    <t xml:space="preserve">2.00400066375732</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.00317668914795</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.07489514350891</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.14331650733948</t>
+    <t xml:space="preserve">2.0040009021759</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.00317645072937</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.07489490509033</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.1433162689209</t>
   </si>
   <si>
     <t xml:space="preserve">2.08396315574646</t>
@@ -4886,13 +4886,13 @@
     <t xml:space="preserve">2.09385514259338</t>
   </si>
   <si>
-    <t xml:space="preserve">2.12847805023193</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.09880137443542</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.11941027641296</t>
+    <t xml:space="preserve">2.12847781181335</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.09880113601685</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.11941003799438</t>
   </si>
   <si>
     <t xml:space="preserve">2.10457181930542</t>
@@ -4910,16 +4910,16 @@
     <t xml:space="preserve">2.2043182849884</t>
   </si>
   <si>
-    <t xml:space="preserve">2.30159211158752</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.26449608802795</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.25295543670654</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.15403270721436</t>
+    <t xml:space="preserve">2.30159187316895</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.26449632644653</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.25295519828796</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.15403294563293</t>
   </si>
   <si>
     <t xml:space="preserve">2.17629027366638</t>
@@ -4934,7 +4934,7 @@
     <t xml:space="preserve">2.21503520011902</t>
   </si>
   <si>
-    <t xml:space="preserve">2.19525051116943</t>
+    <t xml:space="preserve">2.19525074958801</t>
   </si>
   <si>
     <t xml:space="preserve">2.20844006538391</t>
@@ -4955,10 +4955,10 @@
     <t xml:space="preserve">2.32220053672791</t>
   </si>
   <si>
-    <t xml:space="preserve">2.21833252906799</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.00729823112488</t>
+    <t xml:space="preserve">2.21833229064941</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.0072979927063</t>
   </si>
   <si>
     <t xml:space="preserve">2.04027223587036</t>
@@ -4970,46 +4970,46 @@
     <t xml:space="preserve">1.89683508872986</t>
   </si>
   <si>
-    <t xml:space="preserve">1.84407639503479</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.87045586109161</t>
+    <t xml:space="preserve">1.8440762758255</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.87045562267303</t>
   </si>
   <si>
     <t xml:space="preserve">1.96195888519287</t>
   </si>
   <si>
-    <t xml:space="preserve">1.93393099308014</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.89848375320435</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.82181882858276</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.84325218200684</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.84902238845825</t>
+    <t xml:space="preserve">1.93393075466156</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.89848351478577</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.82181894779205</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.84325194358826</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.84902262687683</t>
   </si>
   <si>
     <t xml:space="preserve">1.89930772781372</t>
   </si>
   <si>
-    <t xml:space="preserve">1.88776683807373</t>
+    <t xml:space="preserve">1.88776707649231</t>
   </si>
   <si>
     <t xml:space="preserve">1.8737530708313</t>
   </si>
   <si>
-    <t xml:space="preserve">1.91991698741913</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.9190925359726</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.94876933097839</t>
+    <t xml:space="preserve">1.91991674900055</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.91909229755402</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.94876909255981</t>
   </si>
   <si>
     <t xml:space="preserve">1.94547164440155</t>
@@ -5018,7 +5018,7 @@
     <t xml:space="preserve">1.98339188098907</t>
   </si>
   <si>
-    <t xml:space="preserve">1.97679686546326</t>
+    <t xml:space="preserve">1.97679710388184</t>
   </si>
   <si>
     <t xml:space="preserve">2.06912446022034</t>
@@ -5033,10 +5033,10 @@
     <t xml:space="preserve">2.20102119445801</t>
   </si>
   <si>
-    <t xml:space="preserve">2.23069787025452</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.26284718513489</t>
+    <t xml:space="preserve">2.23069763183594</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.26284742355347</t>
   </si>
   <si>
     <t xml:space="preserve">2.25377941131592</t>
@@ -5057,25 +5057,25 @@
     <t xml:space="preserve">2.10045003890991</t>
   </si>
   <si>
-    <t xml:space="preserve">2.06665182113647</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.14908695220947</t>
+    <t xml:space="preserve">2.0666515827179</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.14908671379089</t>
   </si>
   <si>
     <t xml:space="preserve">2.26119875907898</t>
   </si>
   <si>
-    <t xml:space="preserve">2.25048208236694</t>
+    <t xml:space="preserve">2.25048232078552</t>
   </si>
   <si>
     <t xml:space="preserve">2.2001965045929</t>
   </si>
   <si>
-    <t xml:space="preserve">2.24965763092041</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.23564338684082</t>
+    <t xml:space="preserve">2.24965810775757</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.23564386367798</t>
   </si>
   <si>
     <t xml:space="preserve">2.23481941223145</t>
@@ -5087,10 +5087,10 @@
     <t xml:space="preserve">2.22575163841248</t>
   </si>
   <si>
-    <t xml:space="preserve">2.25335788726807</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.23179030418396</t>
+    <t xml:space="preserve">2.25335764884949</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.23179006576538</t>
   </si>
   <si>
     <t xml:space="preserve">2.13603138923645</t>
@@ -5111,19 +5111,19 @@
     <t xml:space="preserve">2.06183958053589</t>
   </si>
   <si>
-    <t xml:space="preserve">2.1161892414093</t>
+    <t xml:space="preserve">2.11618947982788</t>
   </si>
   <si>
     <t xml:space="preserve">2.16363739967346</t>
   </si>
   <si>
-    <t xml:space="preserve">2.15328526496887</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.15846157073975</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.15414786338806</t>
+    <t xml:space="preserve">2.15328502655029</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.15846133232117</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.15414810180664</t>
   </si>
   <si>
     <t xml:space="preserve">2.15501046180725</t>
@@ -5150,22 +5150,22 @@
     <t xml:space="preserve">2.31288361549377</t>
   </si>
   <si>
-    <t xml:space="preserve">2.34652876853943</t>
+    <t xml:space="preserve">2.34652900695801</t>
   </si>
   <si>
     <t xml:space="preserve">2.37931108474731</t>
   </si>
   <si>
-    <t xml:space="preserve">2.36809587478638</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.31633424758911</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.28614044189453</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.32927489280701</t>
+    <t xml:space="preserve">2.36809611320496</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.31633448600769</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.28614020347595</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.32927465438843</t>
   </si>
   <si>
     <t xml:space="preserve">2.34566593170166</t>
@@ -5180,7 +5180,7 @@
     <t xml:space="preserve">2.42675924301147</t>
   </si>
   <si>
-    <t xml:space="preserve">2.36550807952881</t>
+    <t xml:space="preserve">2.36550831794739</t>
   </si>
   <si>
     <t xml:space="preserve">2.35343027114868</t>
@@ -5192,7 +5192,7 @@
     <t xml:space="preserve">2.3611946105957</t>
   </si>
   <si>
-    <t xml:space="preserve">2.42072033882141</t>
+    <t xml:space="preserve">2.42072057723999</t>
   </si>
   <si>
     <t xml:space="preserve">2.44056248664856</t>
@@ -5219,13 +5219,13 @@
     <t xml:space="preserve">2.58376955986023</t>
   </si>
   <si>
-    <t xml:space="preserve">2.60188627243042</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.6208655834198</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.63553142547607</t>
+    <t xml:space="preserve">2.601886510849</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.62086582183838</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.63553166389465</t>
   </si>
   <si>
     <t xml:space="preserve">2.73819208145142</t>
@@ -5249,7 +5249,7 @@
     <t xml:space="preserve">2.48714780807495</t>
   </si>
   <si>
-    <t xml:space="preserve">2.44660139083862</t>
+    <t xml:space="preserve">2.44660115242004</t>
   </si>
   <si>
     <t xml:space="preserve">2.45264005661011</t>
@@ -5264,22 +5264,22 @@
     <t xml:space="preserve">2.28010129928589</t>
   </si>
   <si>
-    <t xml:space="preserve">2.34049010276794</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.34911680221558</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.3154718875885</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.38276171684265</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.37240982055664</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.36895871162415</t>
+    <t xml:space="preserve">2.34048986434937</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.34911704063416</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.31547164916992</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.38276195526123</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.37240958213806</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.36895895004272</t>
   </si>
   <si>
     <t xml:space="preserve">2.34394073486328</t>
@@ -5291,13 +5291,13 @@
     <t xml:space="preserve">2.41640710830688</t>
   </si>
   <si>
-    <t xml:space="preserve">2.43969964981079</t>
+    <t xml:space="preserve">2.43969988822937</t>
   </si>
   <si>
     <t xml:space="preserve">2.40519213676453</t>
   </si>
   <si>
-    <t xml:space="preserve">2.39138913154602</t>
+    <t xml:space="preserve">2.39138889312744</t>
   </si>
   <si>
     <t xml:space="preserve">2.36464524269104</t>
@@ -5312,16 +5312,16 @@
     <t xml:space="preserve">2.24904441833496</t>
   </si>
   <si>
-    <t xml:space="preserve">2.31115794181824</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.38793778419495</t>
+    <t xml:space="preserve">2.31115818023682</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.38793802261353</t>
   </si>
   <si>
     <t xml:space="preserve">2.41295599937439</t>
   </si>
   <si>
-    <t xml:space="preserve">2.42589664459229</t>
+    <t xml:space="preserve">2.42589688301086</t>
   </si>
   <si>
     <t xml:space="preserve">2.46989393234253</t>
@@ -5333,7 +5333,7 @@
     <t xml:space="preserve">2.57428002357483</t>
   </si>
   <si>
-    <t xml:space="preserve">2.55271291732788</t>
+    <t xml:space="preserve">2.5527126789093</t>
   </si>
   <si>
     <t xml:space="preserve">2.4388370513916</t>
@@ -5342,7 +5342,7 @@
     <t xml:space="preserve">2.41123080253601</t>
   </si>
   <si>
-    <t xml:space="preserve">2.49922561645508</t>
+    <t xml:space="preserve">2.49922585487366</t>
   </si>
   <si>
     <t xml:space="preserve">2.46644330024719</t>
@@ -5363,19 +5363,19 @@
     <t xml:space="preserve">2.3974277973175</t>
   </si>
   <si>
-    <t xml:space="preserve">2.48628544807434</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.55530071258545</t>
+    <t xml:space="preserve">2.48628520965576</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.55530047416687</t>
   </si>
   <si>
     <t xml:space="preserve">2.53632140159607</t>
   </si>
   <si>
-    <t xml:space="preserve">2.55357527732849</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.61310124397278</t>
+    <t xml:space="preserve">2.55357551574707</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.61310148239136</t>
   </si>
   <si>
     <t xml:space="preserve">2.63811945915222</t>
@@ -5387,7 +5387,7 @@
     <t xml:space="preserve">2.46730589866638</t>
   </si>
   <si>
-    <t xml:space="preserve">2.57169198989868</t>
+    <t xml:space="preserve">2.5716917514801</t>
   </si>
   <si>
     <t xml:space="preserve">2.50440192222595</t>
@@ -5414,7 +5414,7 @@
     <t xml:space="preserve">2.72180080413818</t>
   </si>
   <si>
-    <t xml:space="preserve">2.75458312034607</t>
+    <t xml:space="preserve">2.75458335876465</t>
   </si>
   <si>
     <t xml:space="preserve">2.73301601409912</t>
@@ -5429,16 +5429,16 @@
     <t xml:space="preserve">3.04444861412048</t>
   </si>
   <si>
-    <t xml:space="preserve">3.0254693031311</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.07291722297668</t>
+    <t xml:space="preserve">3.02546906471252</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.07291746139526</t>
   </si>
   <si>
     <t xml:space="preserve">2.98751068115234</t>
   </si>
   <si>
-    <t xml:space="preserve">3.00562739372253</t>
+    <t xml:space="preserve">3.00562715530396</t>
   </si>
   <si>
     <t xml:space="preserve">3.05480074882507</t>
@@ -5450,7 +5450,7 @@
     <t xml:space="preserve">2.90986824035645</t>
   </si>
   <si>
-    <t xml:space="preserve">2.94696402549744</t>
+    <t xml:space="preserve">2.94696426391602</t>
   </si>
   <si>
     <t xml:space="preserve">2.94782686233521</t>
@@ -5459,13 +5459,13 @@
     <t xml:space="preserve">2.92453408241272</t>
   </si>
   <si>
-    <t xml:space="preserve">2.8900260925293</t>
+    <t xml:space="preserve">2.89002633094788</t>
   </si>
   <si>
     <t xml:space="preserve">2.98319721221924</t>
   </si>
   <si>
-    <t xml:space="preserve">2.95904159545898</t>
+    <t xml:space="preserve">2.95904183387756</t>
   </si>
   <si>
     <t xml:space="preserve">2.98837351799011</t>
@@ -5474,7 +5474,7 @@
     <t xml:space="preserve">2.96766877174377</t>
   </si>
   <si>
-    <t xml:space="preserve">2.95214009284973</t>
+    <t xml:space="preserve">2.95214033126831</t>
   </si>
   <si>
     <t xml:space="preserve">2.97457027435303</t>
@@ -5495,7 +5495,7 @@
     <t xml:space="preserve">2.70023369789124</t>
   </si>
   <si>
-    <t xml:space="preserve">2.64070749282837</t>
+    <t xml:space="preserve">2.64070773124695</t>
   </si>
   <si>
     <t xml:space="preserve">2.64588356018066</t>
@@ -5510,10 +5510,10 @@
     <t xml:space="preserve">2.62690448760986</t>
   </si>
   <si>
-    <t xml:space="preserve">2.6303551197052</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.60965085029602</t>
+    <t xml:space="preserve">2.63035535812378</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.60965061187744</t>
   </si>
   <si>
     <t xml:space="preserve">2.61051321029663</t>
@@ -5525,7 +5525,7 @@
     <t xml:space="preserve">2.77356243133545</t>
   </si>
   <si>
-    <t xml:space="preserve">2.82791233062744</t>
+    <t xml:space="preserve">2.82791256904602</t>
   </si>
   <si>
     <t xml:space="preserve">2.82877492904663</t>
@@ -5534,10 +5534,10 @@
     <t xml:space="preserve">2.7200756072998</t>
   </si>
   <si>
-    <t xml:space="preserve">2.73215317726135</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.6795289516449</t>
+    <t xml:space="preserve">2.73215341567993</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.67952871322632</t>
   </si>
   <si>
     <t xml:space="preserve">2.74681901931763</t>
@@ -5549,22 +5549,22 @@
     <t xml:space="preserve">2.72611451148987</t>
   </si>
   <si>
-    <t xml:space="preserve">2.75285792350769</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.85034203529358</t>
+    <t xml:space="preserve">2.75285768508911</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.85034227371216</t>
   </si>
   <si>
     <t xml:space="preserve">2.86759614944458</t>
   </si>
   <si>
-    <t xml:space="preserve">2.84861707687378</t>
+    <t xml:space="preserve">2.8486168384552</t>
   </si>
   <si>
     <t xml:space="preserve">2.83826446533203</t>
   </si>
   <si>
-    <t xml:space="preserve">2.88916349411011</t>
+    <t xml:space="preserve">2.88916325569153</t>
   </si>
   <si>
     <t xml:space="preserve">2.81755995750427</t>
@@ -5573,13 +5573,13 @@
     <t xml:space="preserve">2.79858040809631</t>
   </si>
   <si>
-    <t xml:space="preserve">2.78564047813416</t>
+    <t xml:space="preserve">2.78564023971558</t>
   </si>
   <si>
     <t xml:space="preserve">2.86414527893066</t>
   </si>
   <si>
-    <t xml:space="preserve">2.89433979988098</t>
+    <t xml:space="preserve">2.8943395614624</t>
   </si>
   <si>
     <t xml:space="preserve">2.8710470199585</t>
@@ -5588,25 +5588,25 @@
     <t xml:space="preserve">2.92712187767029</t>
   </si>
   <si>
-    <t xml:space="preserve">2.9987256526947</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.021155834198</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.0522129535675</t>
+    <t xml:space="preserve">2.99872589111328</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.02115607261658</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.05221271514893</t>
   </si>
   <si>
     <t xml:space="preserve">3.04531121253967</t>
   </si>
   <si>
-    <t xml:space="preserve">3.03150796890259</t>
+    <t xml:space="preserve">3.03150820732117</t>
   </si>
   <si>
     <t xml:space="preserve">3.06515336036682</t>
   </si>
   <si>
-    <t xml:space="preserve">3.07981896400452</t>
+    <t xml:space="preserve">3.07981872558594</t>
   </si>
   <si>
     <t xml:space="preserve">3.0401349067688</t>
@@ -5615,7 +5615,7 @@
     <t xml:space="preserve">3.03323340415955</t>
   </si>
   <si>
-    <t xml:space="preserve">2.96249270439148</t>
+    <t xml:space="preserve">2.9624924659729</t>
   </si>
   <si>
     <t xml:space="preserve">3.07895636558533</t>
@@ -5636,7 +5636,7 @@
     <t xml:space="preserve">3.19973373413086</t>
   </si>
   <si>
-    <t xml:space="preserve">3.19714546203613</t>
+    <t xml:space="preserve">3.19714570045471</t>
   </si>
   <si>
     <t xml:space="preserve">3.239417552948</t>
@@ -5645,7 +5645,7 @@
     <t xml:space="preserve">3.28082680702209</t>
   </si>
   <si>
-    <t xml:space="preserve">3.3023943901062</t>
+    <t xml:space="preserve">3.30239415168762</t>
   </si>
   <si>
     <t xml:space="preserve">3.30929589271545</t>
@@ -5654,10 +5654,10 @@
     <t xml:space="preserve">3.26788640022278</t>
   </si>
   <si>
-    <t xml:space="preserve">3.27823853492737</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.3481171131134</t>
+    <t xml:space="preserve">3.27823877334595</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.34811687469482</t>
   </si>
   <si>
     <t xml:space="preserve">3.44991493225098</t>
@@ -5678,7 +5678,7 @@
     <t xml:space="preserve">3.63539433479309</t>
   </si>
   <si>
-    <t xml:space="preserve">3.6707649230957</t>
+    <t xml:space="preserve">3.67076444625854</t>
   </si>
   <si>
     <t xml:space="preserve">3.64574646949768</t>
@@ -5690,7 +5690,7 @@
     <t xml:space="preserve">3.72856497764587</t>
   </si>
   <si>
-    <t xml:space="preserve">3.83381366729736</t>
+    <t xml:space="preserve">3.83381414413452</t>
   </si>
   <si>
     <t xml:space="preserve">3.7440938949585</t>
@@ -5702,7 +5702,7 @@
     <t xml:space="preserve">3.76997447013855</t>
   </si>
   <si>
-    <t xml:space="preserve">3.85969519615173</t>
+    <t xml:space="preserve">3.85969471931458</t>
   </si>
   <si>
     <t xml:space="preserve">3.83122587203979</t>
@@ -5714,19 +5714,19 @@
     <t xml:space="preserve">3.83467674255371</t>
   </si>
   <si>
-    <t xml:space="preserve">3.77083683013916</t>
+    <t xml:space="preserve">3.77083730697632</t>
   </si>
   <si>
     <t xml:space="preserve">3.83812737464905</t>
   </si>
   <si>
-    <t xml:space="preserve">3.68888092041016</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.68715620040894</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.68197965621948</t>
+    <t xml:space="preserve">3.68888139724731</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.68715572357178</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.68197989463806</t>
   </si>
   <si>
     <t xml:space="preserve">3.63366866111755</t>
@@ -5765,7 +5765,7 @@
     <t xml:space="preserve">4.25394630432129</t>
   </si>
   <si>
-    <t xml:space="preserve">4.12885475158691</t>
+    <t xml:space="preserve">4.12885522842407</t>
   </si>
   <si>
     <t xml:space="preserve">4.17544078826904</t>
@@ -5774,7 +5774,7 @@
     <t xml:space="preserve">4.25653409957886</t>
   </si>
   <si>
-    <t xml:space="preserve">4.2323784828186</t>
+    <t xml:space="preserve">4.23237895965576</t>
   </si>
   <si>
     <t xml:space="preserve">4.10642576217651</t>
@@ -5792,10 +5792,10 @@
     <t xml:space="preserve">4.32382440567017</t>
   </si>
   <si>
-    <t xml:space="preserve">4.460129737854</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.56710433959961</t>
+    <t xml:space="preserve">4.46013021469116</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.56710386276245</t>
   </si>
   <si>
     <t xml:space="preserve">4.46925115585327</t>
@@ -6924,6 +6924,9 @@
   </si>
   <si>
     <t xml:space="preserve">11.375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.6000003814697</t>
   </si>
 </sst>
 </file>
@@ -73276,7 +73279,7 @@
     </row>
     <row r="2540">
       <c r="A2540" s="1" t="n">
-        <v>46020.692650463</v>
+        <v>46020.3333333333</v>
       </c>
       <c r="B2540" t="n">
         <v>5289306</v>
@@ -73297,6 +73300,32 @@
         <v>2303</v>
       </c>
       <c r="H2540" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2541">
+      <c r="A2541" s="1" t="n">
+        <v>46021.6933680556</v>
+      </c>
+      <c r="B2541" t="n">
+        <v>6391637</v>
+      </c>
+      <c r="C2541" t="n">
+        <v>11.6499996185303</v>
+      </c>
+      <c r="D2541" t="n">
+        <v>11.375</v>
+      </c>
+      <c r="E2541" t="n">
+        <v>11.3800001144409</v>
+      </c>
+      <c r="F2541" t="n">
+        <v>11.6000003814697</v>
+      </c>
+      <c r="G2541" t="s">
+        <v>2304</v>
+      </c>
+      <c r="H2541" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/BPE.MI.xlsx
+++ b/data/BPE.MI.xlsx
@@ -38,67 +38,67 @@
     <t xml:space="preserve">ticker</t>
   </si>
   <si>
-    <t xml:space="preserve">3.1975109577179</t>
+    <t xml:space="preserve">3.19751143455505</t>
   </si>
   <si>
     <t xml:space="preserve">BPE.MI</t>
   </si>
   <si>
-    <t xml:space="preserve">3.23759818077087</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.09375762939453</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.02301502227783</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.9546320438385</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.95699048042297</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.93340969085693</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.07489228248596</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.91690421104431</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.66223454475403</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.6504442691803</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.45708417892456</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.7282600402832</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.69760513305664</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.62686395645142</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.78013682365417</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.66695070266724</t>
+    <t xml:space="preserve">3.23759746551514</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.09375739097595</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.02301573753357</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.95463228225708</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.95699071884155</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.93340945243835</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.07489252090454</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.91690373420715</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.66223430633545</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.65044474601746</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.45708465576172</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.72825980186462</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.69760489463806</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.62686371803284</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.78013706207275</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.66695046424866</t>
   </si>
   <si>
     <t xml:space="preserve">2.46651697158813</t>
   </si>
   <si>
-    <t xml:space="preserve">2.59385061264038</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.53018379211426</t>
+    <t xml:space="preserve">2.59385085105896</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.53018426895142</t>
   </si>
   <si>
     <t xml:space="preserve">2.35804653167725</t>
@@ -110,49 +110,49 @@
     <t xml:space="preserve">2.17128896713257</t>
   </si>
   <si>
-    <t xml:space="preserve">2.12601447105408</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.87228894233704</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.83173072338104</t>
+    <t xml:space="preserve">2.1260142326355</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.87228882312775</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.83173084259033</t>
   </si>
   <si>
     <t xml:space="preserve">1.95812153816223</t>
   </si>
   <si>
-    <t xml:space="preserve">1.77042138576508</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.97415661811829</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.17411875724792</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.2797589302063</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.33446598052979</t>
+    <t xml:space="preserve">1.7704211473465</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.97415614128113</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.17411828041077</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.27975916862488</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.33446621894836</t>
   </si>
   <si>
     <t xml:space="preserve">2.32031774520874</t>
   </si>
   <si>
-    <t xml:space="preserve">2.18166446685791</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.40284991264343</t>
+    <t xml:space="preserve">2.18166494369507</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.40285015106201</t>
   </si>
   <si>
     <t xml:space="preserve">2.31182837486267</t>
   </si>
   <si>
-    <t xml:space="preserve">2.16468667984009</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.21844959259033</t>
+    <t xml:space="preserve">2.16468644142151</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.21844983100891</t>
   </si>
   <si>
     <t xml:space="preserve">2.25995182991028</t>
@@ -161,10 +161,10 @@
     <t xml:space="preserve">2.22128009796143</t>
   </si>
   <si>
-    <t xml:space="preserve">2.25429224967957</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.36512041091919</t>
+    <t xml:space="preserve">2.25429201126099</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.36512064933777</t>
   </si>
   <si>
     <t xml:space="preserve">2.32409071922302</t>
@@ -173,13 +173,13 @@
     <t xml:space="preserve">2.33352255821228</t>
   </si>
   <si>
-    <t xml:space="preserve">2.21279048919678</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.18072152137756</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.20524525642395</t>
+    <t xml:space="preserve">2.21279072761536</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.18072104454041</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.20524549484253</t>
   </si>
   <si>
     <t xml:space="preserve">2.22505283355713</t>
@@ -194,7 +194,7 @@
     <t xml:space="preserve">2.3627622127533</t>
   </si>
   <si>
-    <t xml:space="preserve">2.20241451263428</t>
+    <t xml:space="preserve">2.20241522789001</t>
   </si>
   <si>
     <t xml:space="preserve">2.22693872451782</t>
@@ -206,28 +206,28 @@
     <t xml:space="preserve">2.24108743667603</t>
   </si>
   <si>
-    <t xml:space="preserve">2.20807456970215</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.14770889282227</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.05904579162598</t>
+    <t xml:space="preserve">2.20807480812073</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.14770865440369</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.05904603004456</t>
   </si>
   <si>
     <t xml:space="preserve">2.03829526901245</t>
   </si>
   <si>
-    <t xml:space="preserve">1.9732129573822</t>
+    <t xml:space="preserve">1.97321319580078</t>
   </si>
   <si>
     <t xml:space="preserve">2.00905585289001</t>
   </si>
   <si>
-    <t xml:space="preserve">1.8949259519577</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.88455009460449</t>
+    <t xml:space="preserve">1.89492607116699</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.88455057144165</t>
   </si>
   <si>
     <t xml:space="preserve">1.77325069904327</t>
@@ -239,64 +239,64 @@
     <t xml:space="preserve">2.12507176399231</t>
   </si>
   <si>
-    <t xml:space="preserve">2.0401816368103</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.27410054206848</t>
+    <t xml:space="preserve">2.04018187522888</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.27410006523132</t>
   </si>
   <si>
     <t xml:space="preserve">2.3769109249115</t>
   </si>
   <si>
-    <t xml:space="preserve">2.38398456573486</t>
+    <t xml:space="preserve">2.38398480415344</t>
   </si>
   <si>
     <t xml:space="preserve">2.30428290367126</t>
   </si>
   <si>
-    <t xml:space="preserve">2.37219500541687</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.44765210151672</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.45944213867188</t>
+    <t xml:space="preserve">2.37219452857971</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.4476523399353</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.4594419002533</t>
   </si>
   <si>
     <t xml:space="preserve">2.37455296516418</t>
   </si>
   <si>
-    <t xml:space="preserve">2.45236825942993</t>
+    <t xml:space="preserve">2.45236802101135</t>
   </si>
   <si>
     <t xml:space="preserve">2.41463994979858</t>
   </si>
   <si>
-    <t xml:space="preserve">2.50896143913269</t>
+    <t xml:space="preserve">2.50896120071411</t>
   </si>
   <si>
     <t xml:space="preserve">2.4075653553009</t>
   </si>
   <si>
-    <t xml:space="preserve">2.31937408447266</t>
+    <t xml:space="preserve">2.31937432289124</t>
   </si>
   <si>
     <t xml:space="preserve">2.21750712394714</t>
   </si>
   <si>
-    <t xml:space="preserve">2.19298362731934</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.13167428970337</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.07602429389954</t>
+    <t xml:space="preserve">2.19298338890076</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.13167405128479</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.07602405548096</t>
   </si>
   <si>
     <t xml:space="preserve">2.07036471366882</t>
   </si>
   <si>
-    <t xml:space="preserve">2.06470561027527</t>
+    <t xml:space="preserve">2.06470537185669</t>
   </si>
   <si>
     <t xml:space="preserve">2.0326361656189</t>
@@ -305,13 +305,13 @@
     <t xml:space="preserve">2.02980613708496</t>
   </si>
   <si>
-    <t xml:space="preserve">2.06093287467957</t>
+    <t xml:space="preserve">2.06093311309814</t>
   </si>
   <si>
     <t xml:space="preserve">2.17506170272827</t>
   </si>
   <si>
-    <t xml:space="preserve">2.07319450378418</t>
+    <t xml:space="preserve">2.07319474220276</t>
   </si>
   <si>
     <t xml:space="preserve">2.09960436820984</t>
@@ -320,10 +320,10 @@
     <t xml:space="preserve">2.05811405181885</t>
   </si>
   <si>
-    <t xml:space="preserve">2.22021532058716</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.33117818832397</t>
+    <t xml:space="preserve">2.22021555900574</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.3311779499054</t>
   </si>
   <si>
     <t xml:space="preserve">2.28582811355591</t>
@@ -332,214 +332,214 @@
     <t xml:space="preserve">2.29161763191223</t>
   </si>
   <si>
-    <t xml:space="preserve">2.31381034851074</t>
+    <t xml:space="preserve">2.31381058692932</t>
   </si>
   <si>
     <t xml:space="preserve">2.19416379928589</t>
   </si>
   <si>
-    <t xml:space="preserve">2.16618180274963</t>
+    <t xml:space="preserve">2.16618227958679</t>
   </si>
   <si>
     <t xml:space="preserve">2.07934165000916</t>
   </si>
   <si>
-    <t xml:space="preserve">2.06969261169434</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.09670925140381</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.13627028465271</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.99636077880859</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.8747843503952</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.82171535491943</t>
+    <t xml:space="preserve">2.06969285011292</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.09670948982239</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.13627004623413</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.99636113643646</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.87478387355804</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.82171499729156</t>
   </si>
   <si>
     <t xml:space="preserve">1.81592619419098</t>
   </si>
   <si>
-    <t xml:space="preserve">1.76864612102509</t>
+    <t xml:space="preserve">1.76864624023438</t>
   </si>
   <si>
     <t xml:space="preserve">1.94425714015961</t>
   </si>
   <si>
-    <t xml:space="preserve">2.03206157684326</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.08416557312012</t>
+    <t xml:space="preserve">2.03206181526184</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.0841658115387</t>
   </si>
   <si>
     <t xml:space="preserve">2.07548213005066</t>
   </si>
   <si>
-    <t xml:space="preserve">2.23468923568726</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.68470120429993</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.66733300685883</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.62777185440063</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.53900218009949</t>
+    <t xml:space="preserve">2.23468899726868</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.68470096588135</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.66733288764954</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.62777197360992</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.5390020608902</t>
   </si>
   <si>
     <t xml:space="preserve">1.58145761489868</t>
   </si>
   <si>
-    <t xml:space="preserve">1.50523066520691</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.40391731262207</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.40488243103027</t>
+    <t xml:space="preserve">1.50523054599762</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.40391719341278</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.40488231182098</t>
   </si>
   <si>
     <t xml:space="preserve">1.30453324317932</t>
   </si>
   <si>
-    <t xml:space="preserve">1.24567472934723</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.44733715057373</t>
+    <t xml:space="preserve">1.24567449092865</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.44733703136444</t>
   </si>
   <si>
     <t xml:space="preserve">1.5148800611496</t>
   </si>
   <si>
-    <t xml:space="preserve">1.63838613033295</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.55637001991272</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.62294793128967</t>
+    <t xml:space="preserve">1.63838601112366</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.55637037754059</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.62294816970825</t>
   </si>
   <si>
     <t xml:space="preserve">1.64224541187286</t>
   </si>
   <si>
-    <t xml:space="preserve">1.65189480781555</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.63645601272583</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.65382421016693</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.70689308643341</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.6943496465683</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.64899957180023</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.65671837329865</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.73294532299042</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.67891144752502</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.7705762386322</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.67022728919983</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.46374034881592</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.5225989818573</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.530317902565</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.73005080223083</t>
+    <t xml:space="preserve">1.65189468860626</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.63645589351654</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.65382409095764</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.7068932056427</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.69434976577759</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.64899981021881</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.65671873092651</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.73294544219971</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.67891132831573</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.77057611942291</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.6702276468277</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.46374046802521</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.52259886264801</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.53031778335571</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.73005104064941</t>
   </si>
   <si>
     <t xml:space="preserve">1.69820892810822</t>
   </si>
   <si>
-    <t xml:space="preserve">1.7319803237915</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.72136664390564</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.72040188312531</t>
+    <t xml:space="preserve">1.73198044300079</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.72136700153351</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.72040176391602</t>
   </si>
   <si>
     <t xml:space="preserve">1.69627964496613</t>
   </si>
   <si>
-    <t xml:space="preserve">1.68373596668243</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.62101745605469</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.64996480941772</t>
+    <t xml:space="preserve">1.68373584747314</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.62101769447327</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.64996469020844</t>
   </si>
   <si>
     <t xml:space="preserve">1.55444025993347</t>
   </si>
   <si>
-    <t xml:space="preserve">1.56505441665649</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.65478932857513</t>
+    <t xml:space="preserve">1.5650542974472</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.65478909015656</t>
   </si>
   <si>
     <t xml:space="preserve">1.69048976898193</t>
   </si>
   <si>
-    <t xml:space="preserve">1.64128041267395</t>
+    <t xml:space="preserve">1.64128065109253</t>
   </si>
   <si>
     <t xml:space="preserve">1.60750913619995</t>
   </si>
   <si>
-    <t xml:space="preserve">1.65285933017731</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.66443812847137</t>
+    <t xml:space="preserve">1.65285885334015</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.66443836688995</t>
   </si>
   <si>
     <t xml:space="preserve">1.69531464576721</t>
   </si>
   <si>
-    <t xml:space="preserve">1.71847188472748</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.68759560585022</t>
+    <t xml:space="preserve">1.71847176551819</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.68759548664093</t>
   </si>
   <si>
     <t xml:space="preserve">1.74452388286591</t>
   </si>
   <si>
-    <t xml:space="preserve">1.74741852283478</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.71268272399902</t>
+    <t xml:space="preserve">1.74741864204407</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.71268284320831</t>
   </si>
   <si>
     <t xml:space="preserve">1.67987656593323</t>
@@ -548,55 +548,55 @@
     <t xml:space="preserve">1.63549172878265</t>
   </si>
   <si>
-    <t xml:space="preserve">1.58049249649048</t>
+    <t xml:space="preserve">1.58049237728119</t>
   </si>
   <si>
     <t xml:space="preserve">1.60461461544037</t>
   </si>
   <si>
-    <t xml:space="preserve">1.53610754013062</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.60847413539886</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.61233353614807</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.53996706008911</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.51584470272064</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.54961621761322</t>
+    <t xml:space="preserve">1.5361076593399</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.60847425460815</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.61233365535736</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.53996694087982</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.51584494113922</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.54961633682251</t>
   </si>
   <si>
     <t xml:space="preserve">1.5525107383728</t>
   </si>
   <si>
-    <t xml:space="preserve">1.59786069393158</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.561194896698</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.63452637195587</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.63935077190399</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.61619317531586</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.67408692836761</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.77540099620819</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.81496143341064</t>
+    <t xml:space="preserve">1.59786057472229</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.56119477748871</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.63452649116516</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.63935089111328</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.61619329452515</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.67408680915833</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.77540111541748</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.81496107578278</t>
   </si>
   <si>
     <t xml:space="preserve">1.73583984375</t>
@@ -605,118 +605,118 @@
     <t xml:space="preserve">1.82653951644897</t>
   </si>
   <si>
-    <t xml:space="preserve">1.86513590812683</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.9606602191925</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.05425429344177</t>
+    <t xml:space="preserve">1.86513578891754</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.96065986156464</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.05425453186035</t>
   </si>
   <si>
     <t xml:space="preserve">2.04942965507507</t>
   </si>
   <si>
-    <t xml:space="preserve">2.10153388977051</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.01372885704041</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.04653573036194</t>
+    <t xml:space="preserve">2.10153365135193</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.01372909545898</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.04653549194336</t>
   </si>
   <si>
     <t xml:space="preserve">2.09477972984314</t>
   </si>
   <si>
-    <t xml:space="preserve">2.08899068832397</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.06197381019592</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.04460525512695</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.92978322505951</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.90566098690033</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.88443338871002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.95004594326019</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.98671162128448</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.01565837860107</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.0166232585907</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.99539601802826</t>
+    <t xml:space="preserve">2.08898973464966</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.06197357177734</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.04460549354553</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.92978310585022</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.90566110610962</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.88443350791931</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.95004606246948</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.98671185970306</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.01565909385681</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.01662349700928</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.99539589881897</t>
   </si>
   <si>
     <t xml:space="preserve">1.98574662208557</t>
   </si>
   <si>
-    <t xml:space="preserve">1.92785286903381</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.84583711624146</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.80820739269257</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.80048751831055</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.83715426921844</t>
+    <t xml:space="preserve">1.9278529882431</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.84583735466003</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.80820715427399</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.80048727989197</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.83715391159058</t>
   </si>
   <si>
     <t xml:space="preserve">1.82750475406647</t>
   </si>
   <si>
-    <t xml:space="preserve">1.83329379558563</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.80531179904938</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.82846987247467</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.97513329982758</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.93557286262512</t>
+    <t xml:space="preserve">1.83329403400421</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.80531167984009</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.82847023010254</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.97513318061829</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.9355731010437</t>
   </si>
   <si>
     <t xml:space="preserve">2.06679821014404</t>
   </si>
   <si>
-    <t xml:space="preserve">2.28196883201599</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.31477499008179</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.27907395362854</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.32152962684631</t>
+    <t xml:space="preserve">2.28196859359741</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.31477451324463</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.2790744304657</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.32152986526489</t>
   </si>
   <si>
     <t xml:space="preserve">2.37073874473572</t>
   </si>
   <si>
-    <t xml:space="preserve">2.33214282989502</t>
+    <t xml:space="preserve">2.33214330673218</t>
   </si>
   <si>
     <t xml:space="preserve">2.3948609828949</t>
@@ -728,37 +728,37 @@
     <t xml:space="preserve">2.39775562286377</t>
   </si>
   <si>
-    <t xml:space="preserve">2.41222929954529</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.46529841423035</t>
+    <t xml:space="preserve">2.41222953796387</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.46529817581177</t>
   </si>
   <si>
     <t xml:space="preserve">2.48942065238953</t>
   </si>
   <si>
-    <t xml:space="preserve">2.49665760993958</t>
+    <t xml:space="preserve">2.49665713310242</t>
   </si>
   <si>
     <t xml:space="preserve">2.44117617607117</t>
   </si>
   <si>
-    <t xml:space="preserve">2.54248952865601</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.6389787197113</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.59555840492249</t>
+    <t xml:space="preserve">2.54248976707458</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.63897848129272</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.59555888175964</t>
   </si>
   <si>
     <t xml:space="preserve">2.55696272850037</t>
   </si>
   <si>
-    <t xml:space="preserve">2.42911529541016</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.41705369949341</t>
+    <t xml:space="preserve">2.42911505699158</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.41705322265625</t>
   </si>
   <si>
     <t xml:space="preserve">2.56178736686707</t>
@@ -779,43 +779,43 @@
     <t xml:space="preserve">2.77165126800537</t>
   </si>
   <si>
-    <t xml:space="preserve">2.70652151107788</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.71375775337219</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.74752879142761</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.70410895347595</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.57626104354858</t>
+    <t xml:space="preserve">2.70652103424072</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.71375751495361</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.74752902984619</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.70410919189453</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.57626128196716</t>
   </si>
   <si>
     <t xml:space="preserve">2.52801585197449</t>
   </si>
   <si>
-    <t xml:space="preserve">2.58590912818909</t>
+    <t xml:space="preserve">2.58590936660767</t>
   </si>
   <si>
     <t xml:space="preserve">2.59797048568726</t>
   </si>
   <si>
-    <t xml:space="preserve">2.66068863868713</t>
+    <t xml:space="preserve">2.66068887710571</t>
   </si>
   <si>
     <t xml:space="preserve">2.50871825218201</t>
   </si>
   <si>
-    <t xml:space="preserve">2.42187809944153</t>
+    <t xml:space="preserve">2.42187762260437</t>
   </si>
   <si>
     <t xml:space="preserve">2.45082473754883</t>
   </si>
   <si>
-    <t xml:space="preserve">2.29451274871826</t>
+    <t xml:space="preserve">2.29451251029968</t>
   </si>
   <si>
     <t xml:space="preserve">2.3022313117981</t>
@@ -824,7 +824,7 @@
     <t xml:space="preserve">2.38135266304016</t>
   </si>
   <si>
-    <t xml:space="preserve">2.32056474685669</t>
+    <t xml:space="preserve">2.32056427001953</t>
   </si>
   <si>
     <t xml:space="preserve">2.24047803878784</t>
@@ -833,25 +833,25 @@
     <t xml:space="preserve">2.17100620269775</t>
   </si>
   <si>
-    <t xml:space="preserve">2.14784908294678</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.14495420455933</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.06293869018555</t>
+    <t xml:space="preserve">2.14784860610962</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.14495444297791</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.06293892860413</t>
   </si>
   <si>
     <t xml:space="preserve">2.02627277374268</t>
   </si>
   <si>
-    <t xml:space="preserve">1.9973258972168</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.16135740280151</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.17004179954529</t>
+    <t xml:space="preserve">1.99732613563538</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.16135716438293</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.17004156112671</t>
   </si>
   <si>
     <t xml:space="preserve">2.26749539375305</t>
@@ -860,13 +860,13 @@
     <t xml:space="preserve">2.20574259757996</t>
   </si>
   <si>
-    <t xml:space="preserve">2.113112449646</t>
+    <t xml:space="preserve">2.11311268806458</t>
   </si>
   <si>
     <t xml:space="preserve">2.1179370880127</t>
   </si>
   <si>
-    <t xml:space="preserve">2.18837428092957</t>
+    <t xml:space="preserve">2.18837451934814</t>
   </si>
   <si>
     <t xml:space="preserve">2.25977659225464</t>
@@ -875,52 +875,52 @@
     <t xml:space="preserve">2.22214555740356</t>
   </si>
   <si>
-    <t xml:space="preserve">2.16521716117859</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.16907644271851</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.27714490890503</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.25012731552124</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.3176703453064</t>
+    <t xml:space="preserve">2.16521692276001</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.16907691955566</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.27714467048645</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.25012707710266</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.31767010688782</t>
   </si>
   <si>
     <t xml:space="preserve">2.32635426521301</t>
   </si>
   <si>
-    <t xml:space="preserve">2.39196681976318</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.36494970321655</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.32249402999878</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.3369677066803</t>
+    <t xml:space="preserve">2.39196705818176</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.36494946479797</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.3224937915802</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.33696794509888</t>
   </si>
   <si>
     <t xml:space="preserve">2.29354810714722</t>
   </si>
   <si>
-    <t xml:space="preserve">2.26267075538635</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.25784635543823</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.17872524261475</t>
+    <t xml:space="preserve">2.26267051696777</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.25784611701965</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.17872548103333</t>
   </si>
   <si>
     <t xml:space="preserve">2.19512820243835</t>
   </si>
   <si>
-    <t xml:space="preserve">2.19319915771484</t>
+    <t xml:space="preserve">2.19319891929626</t>
   </si>
   <si>
     <t xml:space="preserve">2.20960187911987</t>
@@ -938,49 +938,49 @@
     <t xml:space="preserve">2.21153140068054</t>
   </si>
   <si>
-    <t xml:space="preserve">2.36398458480835</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.39872050285339</t>
+    <t xml:space="preserve">2.36398434638977</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.39872097969055</t>
   </si>
   <si>
     <t xml:space="preserve">2.34661674499512</t>
   </si>
   <si>
-    <t xml:space="preserve">2.41946578025818</t>
+    <t xml:space="preserve">2.41946625709534</t>
   </si>
   <si>
     <t xml:space="preserve">2.48218417167664</t>
   </si>
   <si>
-    <t xml:space="preserve">2.51836752891541</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.45564913749695</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.43635129928589</t>
+    <t xml:space="preserve">2.51836729049683</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.45564937591553</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.43635153770447</t>
   </si>
   <si>
     <t xml:space="preserve">2.2983717918396</t>
   </si>
   <si>
-    <t xml:space="preserve">2.26170611381531</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.34468626976013</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.30609059333801</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.25302219390869</t>
+    <t xml:space="preserve">2.26170516014099</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.34468674659729</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.30609083175659</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.25302171707153</t>
   </si>
   <si>
     <t xml:space="preserve">2.22697019577026</t>
   </si>
   <si>
-    <t xml:space="preserve">2.26074171066284</t>
+    <t xml:space="preserve">2.26074123382568</t>
   </si>
   <si>
     <t xml:space="preserve">2.24998950958252</t>
@@ -989,40 +989,40 @@
     <t xml:space="preserve">2.25096726417542</t>
   </si>
   <si>
-    <t xml:space="preserve">2.28224420547485</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.27931189537048</t>
+    <t xml:space="preserve">2.2822437286377</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.2793116569519</t>
   </si>
   <si>
     <t xml:space="preserve">2.25292158126831</t>
   </si>
   <si>
-    <t xml:space="preserve">2.18450379371643</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.18548130989075</t>
+    <t xml:space="preserve">2.18450331687927</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.18548107147217</t>
   </si>
   <si>
     <t xml:space="preserve">2.13074636459351</t>
   </si>
   <si>
-    <t xml:space="preserve">2.1757071018219</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.14833950996399</t>
+    <t xml:space="preserve">2.17570662498474</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.14833974838257</t>
   </si>
   <si>
     <t xml:space="preserve">2.10924339294434</t>
   </si>
   <si>
-    <t xml:space="preserve">2.076988697052</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.08089828491211</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.15811371803284</t>
+    <t xml:space="preserve">2.07698917388916</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.08089852333069</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.15811347961426</t>
   </si>
   <si>
     <t xml:space="preserve">2.15127182006836</t>
@@ -1031,16 +1031,16 @@
     <t xml:space="preserve">2.10631108283997</t>
   </si>
   <si>
-    <t xml:space="preserve">2.15909051895142</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.13758778572083</t>
+    <t xml:space="preserve">2.15909099578857</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.13758826255798</t>
   </si>
   <si>
     <t xml:space="preserve">2.04082465171814</t>
   </si>
   <si>
-    <t xml:space="preserve">2.05353045463562</t>
+    <t xml:space="preserve">2.05353093147278</t>
   </si>
   <si>
     <t xml:space="preserve">2.00075101852417</t>
@@ -1058,28 +1058,28 @@
     <t xml:space="preserve">2.14931654930115</t>
   </si>
   <si>
-    <t xml:space="preserve">2.16886520385742</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.15713596343994</t>
+    <t xml:space="preserve">2.168865442276</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.15713572502136</t>
   </si>
   <si>
     <t xml:space="preserve">2.1336784362793</t>
   </si>
   <si>
-    <t xml:space="preserve">2.27149271965027</t>
+    <t xml:space="preserve">2.27149248123169</t>
   </si>
   <si>
     <t xml:space="preserve">2.34870743751526</t>
   </si>
   <si>
-    <t xml:space="preserve">2.29201793670654</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.29788279533386</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.29104065895081</t>
+    <t xml:space="preserve">2.29201769828796</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.29788303375244</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.29103994369507</t>
   </si>
   <si>
     <t xml:space="preserve">2.3223180770874</t>
@@ -1091,7 +1091,7 @@
     <t xml:space="preserve">2.41419434547424</t>
   </si>
   <si>
-    <t xml:space="preserve">2.42103600502014</t>
+    <t xml:space="preserve">2.42103576660156</t>
   </si>
   <si>
     <t xml:space="preserve">2.41908144950867</t>
@@ -1100,46 +1100,46 @@
     <t xml:space="preserve">2.43374180793762</t>
   </si>
   <si>
-    <t xml:space="preserve">2.354572057724</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.37021064758301</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.30667972564697</t>
+    <t xml:space="preserve">2.35457229614258</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.37021040916443</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.30667948722839</t>
   </si>
   <si>
     <t xml:space="preserve">2.28126692771912</t>
   </si>
   <si>
-    <t xml:space="preserve">2.25389909744263</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.2871310710907</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.29885959625244</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.27344703674316</t>
+    <t xml:space="preserve">2.25389933586121</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.28713083267212</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.29885983467102</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.27344727516174</t>
   </si>
   <si>
     <t xml:space="preserve">2.26953744888306</t>
   </si>
   <si>
-    <t xml:space="preserve">2.31352090835571</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.45329022407532</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.42005825042725</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.40246558189392</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.31743097305298</t>
+    <t xml:space="preserve">2.31352162361145</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.45328974723816</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.42005848884583</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.40246534347534</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.3174307346344</t>
   </si>
   <si>
     <t xml:space="preserve">2.39464569091797</t>
@@ -1172,10 +1172,10 @@
     <t xml:space="preserve">2.31254386901855</t>
   </si>
   <si>
-    <t xml:space="preserve">2.34382081031799</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.30863404273987</t>
+    <t xml:space="preserve">2.34382104873657</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.30863428115845</t>
   </si>
   <si>
     <t xml:space="preserve">2.27246999740601</t>
@@ -1184,37 +1184,37 @@
     <t xml:space="preserve">2.23337364196777</t>
   </si>
   <si>
-    <t xml:space="preserve">2.21382546424866</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.27735710144043</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.34773087501526</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.30081486701965</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.2421703338623</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.26269602775574</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.29006361961365</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.33795619010925</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.2861533164978</t>
+    <t xml:space="preserve">2.21382570266724</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.27735733985901</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.34773063659668</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.30081462860107</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.24217057228088</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.26269578933716</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.29006338119507</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.33795642852783</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.28615355491638</t>
   </si>
   <si>
     <t xml:space="preserve">2.35359477996826</t>
   </si>
   <si>
-    <t xml:space="preserve">2.4229907989502</t>
+    <t xml:space="preserve">2.42299127578735</t>
   </si>
   <si>
     <t xml:space="preserve">2.46306443214417</t>
@@ -1223,10 +1223,10 @@
     <t xml:space="preserve">2.47283864021301</t>
   </si>
   <si>
-    <t xml:space="preserve">2.51437830924988</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.50704741477966</t>
+    <t xml:space="preserve">2.51437854766846</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.50704717636108</t>
   </si>
   <si>
     <t xml:space="preserve">2.43276453018188</t>
@@ -1235,31 +1235,31 @@
     <t xml:space="preserve">2.39171385765076</t>
   </si>
   <si>
-    <t xml:space="preserve">2.26171803474426</t>
+    <t xml:space="preserve">2.26171827316284</t>
   </si>
   <si>
     <t xml:space="preserve">2.19525456428528</t>
   </si>
   <si>
-    <t xml:space="preserve">2.14736175537109</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.17081952095032</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.14638447761536</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.14051985740662</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.07210183143616</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.07894325256348</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.09946846961975</t>
+    <t xml:space="preserve">2.14736199378967</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.17081928253174</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.14638423919678</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.1405200958252</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.07210206985474</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.07894349098206</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.09946918487549</t>
   </si>
   <si>
     <t xml:space="preserve">2.07601118087769</t>
@@ -1274,118 +1274,118 @@
     <t xml:space="preserve">2.04473423957825</t>
   </si>
   <si>
-    <t xml:space="preserve">2.03887033462524</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.11315321922302</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.05939531326294</t>
+    <t xml:space="preserve">2.03886985778809</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.11315274238586</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.05939555168152</t>
   </si>
   <si>
     <t xml:space="preserve">2.02616381645203</t>
   </si>
   <si>
-    <t xml:space="preserve">1.98804461956024</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.9010556936264</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.08969521522522</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.06721496582031</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.08578610420227</t>
+    <t xml:space="preserve">1.98804473876953</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.90105581283569</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.08969569206238</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.06721472740173</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.08578562736511</t>
   </si>
   <si>
     <t xml:space="preserve">2.0398473739624</t>
   </si>
   <si>
-    <t xml:space="preserve">2.08285284042358</t>
+    <t xml:space="preserve">2.08285307884216</t>
   </si>
   <si>
     <t xml:space="preserve">2.01345729827881</t>
   </si>
   <si>
-    <t xml:space="preserve">2.04668927192688</t>
+    <t xml:space="preserve">2.0466890335083</t>
   </si>
   <si>
     <t xml:space="preserve">2.01834440231323</t>
   </si>
   <si>
-    <t xml:space="preserve">2.00661563873291</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.06623697280884</t>
+    <t xml:space="preserve">2.00661587715149</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.06623721122742</t>
   </si>
   <si>
     <t xml:space="preserve">2.16202306747437</t>
   </si>
   <si>
-    <t xml:space="preserve">2.24608016014099</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.17961645126343</t>
+    <t xml:space="preserve">2.24607992172241</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.17961668968201</t>
   </si>
   <si>
     <t xml:space="preserve">2.2382607460022</t>
   </si>
   <si>
-    <t xml:space="preserve">2.22653198242188</t>
+    <t xml:space="preserve">2.22653222084045</t>
   </si>
   <si>
     <t xml:space="preserve">2.19916439056396</t>
   </si>
   <si>
-    <t xml:space="preserve">2.27051496505737</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.21773552894592</t>
+    <t xml:space="preserve">2.27051520347595</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.21773529052734</t>
   </si>
   <si>
     <t xml:space="preserve">2.07796573638916</t>
   </si>
   <si>
-    <t xml:space="preserve">2.03691482543945</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.03105068206787</t>
-  </si>
-  <si>
-    <t xml:spa